--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4BEC12-07C0-41F1-B4F9-C3964109AA85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B125E6CD-CA19-4F49-BC6B-60A2D3691AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B125E6CD-CA19-4F49-BC6B-60A2D3691AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305162CB-6E79-4F57-98CA-2E74D0B6270B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="84" windowWidth="23016" windowHeight="12516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CdA Track Testing" sheetId="12" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4550" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4560" uniqueCount="619">
   <si>
     <t>Squad</t>
   </si>
@@ -1915,6 +1915,36 @@
   </si>
   <si>
     <t>https://youtu.be/0LxxiWMMC0I</t>
+  </si>
+  <si>
+    <t>https://youtu.be/XeyvBLEKyRc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/SaacsrTJ5kM</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-25mlwkxL0c</t>
+  </si>
+  <si>
+    <t>https://youtu.be/cNebqSIw528</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-UA5mWzEQ5k</t>
+  </si>
+  <si>
+    <t>https://youtu.be/qop5eu9uYeM</t>
+  </si>
+  <si>
+    <t>https://youtu.be/uwedk0qQfcQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/8Ju853Y8MLw</t>
+  </si>
+  <si>
+    <t>https://youtu.be/nvclfAD1jNM</t>
+  </si>
+  <si>
+    <t>https://youtu.be/CKMHYanYR8g</t>
   </si>
 </sst>
 </file>
@@ -50374,7 +50404,9 @@
       <c r="D429" s="20">
         <v>1</v>
       </c>
-      <c r="E429" s="110"/>
+      <c r="E429" s="110" t="s">
+        <v>612</v>
+      </c>
       <c r="F429" s="110" t="s">
         <v>463</v>
       </c>
@@ -50483,7 +50515,9 @@
       <c r="D430" s="20">
         <v>1</v>
       </c>
-      <c r="E430" s="110"/>
+      <c r="E430" s="110" t="s">
+        <v>618</v>
+      </c>
       <c r="F430" s="110" t="s">
         <v>476</v>
       </c>
@@ -50693,7 +50727,9 @@
       <c r="D432" s="20">
         <v>2</v>
       </c>
-      <c r="E432" s="110"/>
+      <c r="E432" s="110" t="s">
+        <v>613</v>
+      </c>
       <c r="F432" s="110" t="s">
         <v>463</v>
       </c>
@@ -51016,7 +51052,9 @@
       <c r="D435" s="20">
         <v>3</v>
       </c>
-      <c r="E435" s="110"/>
+      <c r="E435" s="110" t="s">
+        <v>614</v>
+      </c>
       <c r="F435" s="110" t="s">
         <v>463</v>
       </c>
@@ -51335,7 +51373,9 @@
       <c r="D438" s="20">
         <v>4</v>
       </c>
-      <c r="E438" s="110"/>
+      <c r="E438" s="110" t="s">
+        <v>615</v>
+      </c>
       <c r="F438" s="110" t="s">
         <v>463</v>
       </c>
@@ -51656,7 +51696,9 @@
       <c r="D441" s="20">
         <v>5</v>
       </c>
-      <c r="E441" s="110"/>
+      <c r="E441" s="110" t="s">
+        <v>616</v>
+      </c>
       <c r="F441" s="110" t="s">
         <v>463</v>
       </c>
@@ -51979,7 +52021,9 @@
       <c r="D444" s="20">
         <v>6</v>
       </c>
-      <c r="E444" s="110"/>
+      <c r="E444" s="110" t="s">
+        <v>617</v>
+      </c>
       <c r="F444" s="110" t="s">
         <v>463</v>
       </c>
@@ -52191,7 +52235,9 @@
       <c r="D446" s="20">
         <v>7</v>
       </c>
-      <c r="E446" s="110"/>
+      <c r="E446" s="110" t="s">
+        <v>609</v>
+      </c>
       <c r="F446" s="110" t="s">
         <v>473</v>
       </c>
@@ -52510,7 +52556,9 @@
       <c r="D449" s="20">
         <v>8</v>
       </c>
-      <c r="E449" s="110"/>
+      <c r="E449" s="110" t="s">
+        <v>610</v>
+      </c>
       <c r="F449" s="110" t="s">
         <v>473</v>
       </c>
@@ -52829,7 +52877,9 @@
       <c r="D452" s="20">
         <v>9</v>
       </c>
-      <c r="E452" s="110"/>
+      <c r="E452" s="110" t="s">
+        <v>611</v>
+      </c>
       <c r="F452" s="110" t="s">
         <v>473</v>
       </c>
@@ -57690,6 +57740,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004F1ECC6B2649324CB24C079D2C04510D" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="608b5d954c2eb0ac10393708da8d34af">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65551c38-962b-4cee-924d-ef2df1bb8b98" xmlns:ns3="ec750ee3-7d64-422f-9b1f-0ca7238893a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af171f03bd4cf151e3e856a6839c0cc7" ns2:_="" ns3:_="">
     <xsd:import namespace="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
@@ -57937,26 +58006,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -57973,29 +58048,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54709B05-2D49-47B3-A469-02AD9C7E1462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552FC106-D28A-4947-8EBE-B0B487D28D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3443,14 +3443,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Track_TT23" displayName="Track_TT23" ref="A1:BJ542" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
-  <autoFilter ref="A1:BJ542" xr:uid="{00000000-0009-0000-0100-000002000000}">
-    <filterColumn colId="11">
-      <filters>
-        <filter val="NA"/>
-        <filter val="nil"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:BJ542" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="62">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Squad" dataDxfId="61"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Name" dataDxfId="60"/>
@@ -4037,7 +4030,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="2" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
@@ -4148,7 +4141,7 @@
       </c>
       <c r="BM2"/>
     </row>
-    <row r="3" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
@@ -4259,7 +4252,7 @@
       </c>
       <c r="BM3"/>
     </row>
-    <row r="4" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
@@ -4370,7 +4363,7 @@
       </c>
       <c r="BM4"/>
     </row>
-    <row r="5" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -4481,7 +4474,7 @@
       </c>
       <c r="BM5"/>
     </row>
-    <row r="6" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
@@ -4592,7 +4585,7 @@
       </c>
       <c r="BM6"/>
     </row>
-    <row r="7" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
@@ -4703,7 +4696,7 @@
       </c>
       <c r="BM7"/>
     </row>
-    <row r="8" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
@@ -4812,7 +4805,7 @@
       <c r="BJ8" s="4"/>
       <c r="BM8"/>
     </row>
-    <row r="9" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -4923,7 +4916,7 @@
       </c>
       <c r="BM9"/>
     </row>
-    <row r="10" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
@@ -5034,7 +5027,7 @@
       </c>
       <c r="BM10"/>
     </row>
-    <row r="11" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
@@ -5139,7 +5132,7 @@
       </c>
       <c r="BM11"/>
     </row>
-    <row r="12" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
@@ -5250,7 +5243,7 @@
       </c>
       <c r="BM12"/>
     </row>
-    <row r="13" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
@@ -5361,7 +5354,7 @@
       </c>
       <c r="BM13"/>
     </row>
-    <row r="14" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
@@ -5472,7 +5465,7 @@
       </c>
       <c r="BM14"/>
     </row>
-    <row r="15" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>16</v>
       </c>
@@ -5583,7 +5576,7 @@
       </c>
       <c r="BM15"/>
     </row>
-    <row r="16" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
@@ -5694,7 +5687,7 @@
       </c>
       <c r="BM16"/>
     </row>
-    <row r="17" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -5805,7 +5798,7 @@
       </c>
       <c r="BM17"/>
     </row>
-    <row r="18" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
@@ -5916,7 +5909,7 @@
       </c>
       <c r="BM18"/>
     </row>
-    <row r="19" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>16</v>
       </c>
@@ -6027,7 +6020,7 @@
       </c>
       <c r="BM19"/>
     </row>
-    <row r="20" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>16</v>
       </c>
@@ -6138,7 +6131,7 @@
       </c>
       <c r="BM20"/>
     </row>
-    <row r="21" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>16</v>
       </c>
@@ -6249,7 +6242,7 @@
       </c>
       <c r="BM21"/>
     </row>
-    <row r="22" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>16</v>
       </c>
@@ -6360,7 +6353,7 @@
       </c>
       <c r="BM22"/>
     </row>
-    <row r="23" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>16</v>
       </c>
@@ -6471,7 +6464,7 @@
       </c>
       <c r="BM23"/>
     </row>
-    <row r="24" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>16</v>
       </c>
@@ -6582,7 +6575,7 @@
       </c>
       <c r="BM24"/>
     </row>
-    <row r="25" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>296</v>
       </c>
@@ -6691,7 +6684,7 @@
       </c>
       <c r="BM25"/>
     </row>
-    <row r="26" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>296</v>
       </c>
@@ -6800,7 +6793,7 @@
       </c>
       <c r="BM26"/>
     </row>
-    <row r="27" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>296</v>
       </c>
@@ -6909,7 +6902,7 @@
       </c>
       <c r="BM27"/>
     </row>
-    <row r="28" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>296</v>
       </c>
@@ -7018,7 +7011,7 @@
       </c>
       <c r="BM28"/>
     </row>
-    <row r="29" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>296</v>
       </c>
@@ -7127,7 +7120,7 @@
       </c>
       <c r="BM29"/>
     </row>
-    <row r="30" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>296</v>
       </c>
@@ -7236,7 +7229,7 @@
       </c>
       <c r="BM30"/>
     </row>
-    <row r="31" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>296</v>
       </c>
@@ -7345,7 +7338,7 @@
       </c>
       <c r="BM31"/>
     </row>
-    <row r="32" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>296</v>
       </c>
@@ -7454,7 +7447,7 @@
       </c>
       <c r="BM32"/>
     </row>
-    <row r="33" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>296</v>
       </c>
@@ -7563,7 +7556,7 @@
       </c>
       <c r="BM33"/>
     </row>
-    <row r="34" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>296</v>
       </c>
@@ -7672,7 +7665,7 @@
       </c>
       <c r="BM34"/>
     </row>
-    <row r="35" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>296</v>
       </c>
@@ -7781,7 +7774,7 @@
       </c>
       <c r="BM35"/>
     </row>
-    <row r="36" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>296</v>
       </c>
@@ -7890,7 +7883,7 @@
       </c>
       <c r="BM36"/>
     </row>
-    <row r="37" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>296</v>
       </c>
@@ -7997,7 +7990,7 @@
       </c>
       <c r="BM37"/>
     </row>
-    <row r="38" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>296</v>
       </c>
@@ -8104,7 +8097,7 @@
       </c>
       <c r="BM38"/>
     </row>
-    <row r="39" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>296</v>
       </c>
@@ -8211,7 +8204,7 @@
       </c>
       <c r="BM39"/>
     </row>
-    <row r="40" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>296</v>
       </c>
@@ -8318,7 +8311,7 @@
       </c>
       <c r="BM40"/>
     </row>
-    <row r="41" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>296</v>
       </c>
@@ -8425,7 +8418,7 @@
       </c>
       <c r="BM41"/>
     </row>
-    <row r="42" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>296</v>
       </c>
@@ -8532,7 +8525,7 @@
       </c>
       <c r="BM42"/>
     </row>
-    <row r="43" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>296</v>
       </c>
@@ -8639,7 +8632,7 @@
       </c>
       <c r="BM43"/>
     </row>
-    <row r="44" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>296</v>
       </c>
@@ -8738,7 +8731,7 @@
       </c>
       <c r="BM44"/>
     </row>
-    <row r="45" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>296</v>
       </c>
@@ -8837,7 +8830,7 @@
       </c>
       <c r="BM45"/>
     </row>
-    <row r="46" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>296</v>
       </c>
@@ -8936,7 +8929,7 @@
       </c>
       <c r="BM46"/>
     </row>
-    <row r="47" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>296</v>
       </c>
@@ -9035,7 +9028,7 @@
       </c>
       <c r="BM47"/>
     </row>
-    <row r="48" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>296</v>
       </c>
@@ -9136,7 +9129,7 @@
       </c>
       <c r="BM48"/>
     </row>
-    <row r="49" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>296</v>
       </c>
@@ -9235,7 +9228,7 @@
       </c>
       <c r="BM49"/>
     </row>
-    <row r="50" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>16</v>
       </c>
@@ -9334,7 +9327,7 @@
       </c>
       <c r="BM50"/>
     </row>
-    <row r="51" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>16</v>
       </c>
@@ -9433,7 +9426,7 @@
       </c>
       <c r="BM51"/>
     </row>
-    <row r="52" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>16</v>
       </c>
@@ -9532,7 +9525,7 @@
       </c>
       <c r="BM52"/>
     </row>
-    <row r="53" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>16</v>
       </c>
@@ -9631,7 +9624,7 @@
       </c>
       <c r="BM53"/>
     </row>
-    <row r="54" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>16</v>
       </c>
@@ -9730,7 +9723,7 @@
       </c>
       <c r="BM54"/>
     </row>
-    <row r="55" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>16</v>
       </c>
@@ -9829,7 +9822,7 @@
       </c>
       <c r="BM55"/>
     </row>
-    <row r="56" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>16</v>
       </c>
@@ -9930,7 +9923,7 @@
       </c>
       <c r="BM56"/>
     </row>
-    <row r="57" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>16</v>
       </c>
@@ -10024,7 +10017,7 @@
       </c>
       <c r="BM57"/>
     </row>
-    <row r="58" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>296</v>
       </c>
@@ -10125,7 +10118,7 @@
       </c>
       <c r="BM58"/>
     </row>
-    <row r="59" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>296</v>
       </c>
@@ -10226,7 +10219,7 @@
       </c>
       <c r="BM59"/>
     </row>
-    <row r="60" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>296</v>
       </c>
@@ -10327,7 +10320,7 @@
       </c>
       <c r="BM60"/>
     </row>
-    <row r="61" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>296</v>
       </c>
@@ -10428,7 +10421,7 @@
       </c>
       <c r="BM61"/>
     </row>
-    <row r="62" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>296</v>
       </c>
@@ -10529,7 +10522,7 @@
       </c>
       <c r="BM62"/>
     </row>
-    <row r="63" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>296</v>
       </c>
@@ -10630,7 +10623,7 @@
       </c>
       <c r="BM63"/>
     </row>
-    <row r="64" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>16</v>
       </c>
@@ -10731,7 +10724,7 @@
       </c>
       <c r="BM64"/>
     </row>
-    <row r="65" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>16</v>
       </c>
@@ -10832,7 +10825,7 @@
       </c>
       <c r="BM65"/>
     </row>
-    <row r="66" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>16</v>
       </c>
@@ -10933,7 +10926,7 @@
       </c>
       <c r="BM66"/>
     </row>
-    <row r="67" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>16</v>
       </c>
@@ -11034,7 +11027,7 @@
       </c>
       <c r="BM67"/>
     </row>
-    <row r="68" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>296</v>
       </c>
@@ -11147,7 +11140,7 @@
       </c>
       <c r="BM68"/>
     </row>
-    <row r="69" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>296</v>
       </c>
@@ -11260,7 +11253,7 @@
       </c>
       <c r="BM69"/>
     </row>
-    <row r="70" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>296</v>
       </c>
@@ -11373,7 +11366,7 @@
       </c>
       <c r="BM70"/>
     </row>
-    <row r="71" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>296</v>
       </c>
@@ -11486,7 +11479,7 @@
       </c>
       <c r="BM71"/>
     </row>
-    <row r="72" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>296</v>
       </c>
@@ -11599,7 +11592,7 @@
       </c>
       <c r="BM72"/>
     </row>
-    <row r="73" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>296</v>
       </c>
@@ -11712,7 +11705,7 @@
       </c>
       <c r="BM73"/>
     </row>
-    <row r="74" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>16</v>
       </c>
@@ -11825,7 +11818,7 @@
       </c>
       <c r="BM74"/>
     </row>
-    <row r="75" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>16</v>
       </c>
@@ -11938,7 +11931,7 @@
       </c>
       <c r="BM75"/>
     </row>
-    <row r="76" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>16</v>
       </c>
@@ -12049,7 +12042,7 @@
       </c>
       <c r="BM76"/>
     </row>
-    <row r="77" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>16</v>
       </c>
@@ -12160,7 +12153,7 @@
       </c>
       <c r="BM77"/>
     </row>
-    <row r="78" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>16</v>
       </c>
@@ -12271,7 +12264,7 @@
       </c>
       <c r="BM78"/>
     </row>
-    <row r="79" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>16</v>
       </c>
@@ -12382,7 +12375,7 @@
       </c>
       <c r="BM79"/>
     </row>
-    <row r="80" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>296</v>
       </c>
@@ -12497,7 +12490,7 @@
       </c>
       <c r="BM80"/>
     </row>
-    <row r="81" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>296</v>
       </c>
@@ -12612,7 +12605,7 @@
       </c>
       <c r="BM81"/>
     </row>
-    <row r="82" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>296</v>
       </c>
@@ -12725,7 +12718,7 @@
       </c>
       <c r="BM82"/>
     </row>
-    <row r="83" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>296</v>
       </c>
@@ -12838,7 +12831,7 @@
       </c>
       <c r="BM83"/>
     </row>
-    <row r="84" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>296</v>
       </c>
@@ -12951,7 +12944,7 @@
       </c>
       <c r="BM84"/>
     </row>
-    <row r="85" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>296</v>
       </c>
@@ -13066,7 +13059,7 @@
       </c>
       <c r="BM85"/>
     </row>
-    <row r="86" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>296</v>
       </c>
@@ -13177,7 +13170,7 @@
       </c>
       <c r="BM86"/>
     </row>
-    <row r="87" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>296</v>
       </c>
@@ -13288,7 +13281,7 @@
       </c>
       <c r="BM87"/>
     </row>
-    <row r="88" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>296</v>
       </c>
@@ -13401,7 +13394,7 @@
       </c>
       <c r="BM88"/>
     </row>
-    <row r="89" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>296</v>
       </c>
@@ -13514,7 +13507,7 @@
       </c>
       <c r="BM89"/>
     </row>
-    <row r="90" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>296</v>
       </c>
@@ -13625,7 +13618,7 @@
       </c>
       <c r="BM90"/>
     </row>
-    <row r="91" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>296</v>
       </c>
@@ -13736,7 +13729,7 @@
       </c>
       <c r="BM91"/>
     </row>
-    <row r="92" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>296</v>
       </c>
@@ -13844,7 +13837,7 @@
       </c>
       <c r="BM92"/>
     </row>
-    <row r="93" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>296</v>
       </c>
@@ -13948,7 +13941,7 @@
       </c>
       <c r="BM93"/>
     </row>
-    <row r="94" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>296</v>
       </c>
@@ -14162,7 +14155,7 @@
       </c>
       <c r="BM95"/>
     </row>
-    <row r="96" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>296</v>
       </c>
@@ -14270,7 +14263,7 @@
       </c>
       <c r="BM96"/>
     </row>
-    <row r="97" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>296</v>
       </c>
@@ -14378,7 +14371,7 @@
       </c>
       <c r="BM97"/>
     </row>
-    <row r="98" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>296</v>
       </c>
@@ -14486,7 +14479,7 @@
       </c>
       <c r="BM98"/>
     </row>
-    <row r="99" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>296</v>
       </c>
@@ -14594,7 +14587,7 @@
       </c>
       <c r="BM99"/>
     </row>
-    <row r="100" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>296</v>
       </c>
@@ -14702,7 +14695,7 @@
       </c>
       <c r="BM100"/>
     </row>
-    <row r="101" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>16</v>
       </c>
@@ -14810,7 +14803,7 @@
       </c>
       <c r="BM101"/>
     </row>
-    <row r="102" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>16</v>
       </c>
@@ -14918,7 +14911,7 @@
       </c>
       <c r="BM102"/>
     </row>
-    <row r="103" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>16</v>
       </c>
@@ -15024,7 +15017,7 @@
       </c>
       <c r="BM103"/>
     </row>
-    <row r="104" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>16</v>
       </c>
@@ -15130,7 +15123,7 @@
       </c>
       <c r="BM104"/>
     </row>
-    <row r="105" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>16</v>
       </c>
@@ -15236,7 +15229,7 @@
       </c>
       <c r="BM105"/>
     </row>
-    <row r="106" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>16</v>
       </c>
@@ -15342,7 +15335,7 @@
       </c>
       <c r="BM106"/>
     </row>
-    <row r="107" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>16</v>
       </c>
@@ -15448,7 +15441,7 @@
       </c>
       <c r="BM107"/>
     </row>
-    <row r="108" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>16</v>
       </c>
@@ -15554,7 +15547,7 @@
       </c>
       <c r="BM108"/>
     </row>
-    <row r="109" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>296</v>
       </c>
@@ -15662,7 +15655,7 @@
       </c>
       <c r="BM109"/>
     </row>
-    <row r="110" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>296</v>
       </c>
@@ -15770,7 +15763,7 @@
       </c>
       <c r="BM110"/>
     </row>
-    <row r="111" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>296</v>
       </c>
@@ -15880,7 +15873,7 @@
       </c>
       <c r="BM111"/>
     </row>
-    <row r="112" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>296</v>
       </c>
@@ -15988,7 +15981,7 @@
       </c>
       <c r="BM112"/>
     </row>
-    <row r="113" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>296</v>
       </c>
@@ -16096,7 +16089,7 @@
       </c>
       <c r="BM113"/>
     </row>
-    <row r="114" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>296</v>
       </c>
@@ -16204,7 +16197,7 @@
       </c>
       <c r="BM114"/>
     </row>
-    <row r="115" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>296</v>
       </c>
@@ -16312,7 +16305,7 @@
       </c>
       <c r="BM115"/>
     </row>
-    <row r="116" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>296</v>
       </c>
@@ -16420,7 +16413,7 @@
       </c>
       <c r="BM116"/>
     </row>
-    <row r="117" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>296</v>
       </c>
@@ -16521,7 +16514,7 @@
       </c>
       <c r="BM117"/>
     </row>
-    <row r="118" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>296</v>
       </c>
@@ -16624,7 +16617,7 @@
       </c>
       <c r="BM118"/>
     </row>
-    <row r="119" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>296</v>
       </c>
@@ -16725,7 +16718,7 @@
       </c>
       <c r="BM119"/>
     </row>
-    <row r="120" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>296</v>
       </c>
@@ -16826,7 +16819,7 @@
       </c>
       <c r="BM120"/>
     </row>
-    <row r="121" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>296</v>
       </c>
@@ -16927,7 +16920,7 @@
       </c>
       <c r="BM121"/>
     </row>
-    <row r="122" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>296</v>
       </c>
@@ -17028,7 +17021,7 @@
       </c>
       <c r="BM122"/>
     </row>
-    <row r="123" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>16</v>
       </c>
@@ -17129,7 +17122,7 @@
       </c>
       <c r="BM123"/>
     </row>
-    <row r="124" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>16</v>
       </c>
@@ -17230,7 +17223,7 @@
       </c>
       <c r="BM124"/>
     </row>
-    <row r="125" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>16</v>
       </c>
@@ -17331,7 +17324,7 @@
       </c>
       <c r="BM125"/>
     </row>
-    <row r="126" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>16</v>
       </c>
@@ -17432,7 +17425,7 @@
       </c>
       <c r="BM126"/>
     </row>
-    <row r="127" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>16</v>
       </c>
@@ -17533,7 +17526,7 @@
       </c>
       <c r="BM127"/>
     </row>
-    <row r="128" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>16</v>
       </c>
@@ -17634,7 +17627,7 @@
       </c>
       <c r="BM128"/>
     </row>
-    <row r="129" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>16</v>
       </c>
@@ -17735,7 +17728,7 @@
       </c>
       <c r="BM129"/>
     </row>
-    <row r="130" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>296</v>
       </c>
@@ -17836,7 +17829,7 @@
       </c>
       <c r="BM130"/>
     </row>
-    <row r="131" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>296</v>
       </c>
@@ -17939,7 +17932,7 @@
       </c>
       <c r="BM131"/>
     </row>
-    <row r="132" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>296</v>
       </c>
@@ -18040,7 +18033,7 @@
       </c>
       <c r="BM132"/>
     </row>
-    <row r="133" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>296</v>
       </c>
@@ -18143,7 +18136,7 @@
       </c>
       <c r="BM133"/>
     </row>
-    <row r="134" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>296</v>
       </c>
@@ -18244,7 +18237,7 @@
       </c>
       <c r="BM134"/>
     </row>
-    <row r="135" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>296</v>
       </c>
@@ -18347,7 +18340,7 @@
       </c>
       <c r="BM135"/>
     </row>
-    <row r="136" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>16</v>
       </c>
@@ -18448,7 +18441,7 @@
       </c>
       <c r="BM136"/>
     </row>
-    <row r="137" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>16</v>
       </c>
@@ -18549,7 +18542,7 @@
       </c>
       <c r="BM137"/>
     </row>
-    <row r="138" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>16</v>
       </c>
@@ -18650,7 +18643,7 @@
       </c>
       <c r="BM138"/>
     </row>
-    <row r="139" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>16</v>
       </c>
@@ -18751,7 +18744,7 @@
       </c>
       <c r="BM139"/>
     </row>
-    <row r="140" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>16</v>
       </c>
@@ -18852,7 +18845,7 @@
       </c>
       <c r="BM140"/>
     </row>
-    <row r="141" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>16</v>
       </c>
@@ -18955,7 +18948,7 @@
       </c>
       <c r="BM141"/>
     </row>
-    <row r="142" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>296</v>
       </c>
@@ -19060,7 +19053,7 @@
       </c>
       <c r="BM142"/>
     </row>
-    <row r="143" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>296</v>
       </c>
@@ -19165,7 +19158,7 @@
       </c>
       <c r="BM143"/>
     </row>
-    <row r="144" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>296</v>
       </c>
@@ -19264,7 +19257,7 @@
       </c>
       <c r="BM144"/>
     </row>
-    <row r="145" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>296</v>
       </c>
@@ -19369,7 +19362,7 @@
       </c>
       <c r="BM145"/>
     </row>
-    <row r="146" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>296</v>
       </c>
@@ -19474,7 +19467,7 @@
       </c>
       <c r="BM146"/>
     </row>
-    <row r="147" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>296</v>
       </c>
@@ -19579,7 +19572,7 @@
       </c>
       <c r="BM147"/>
     </row>
-    <row r="148" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>16</v>
       </c>
@@ -19684,7 +19677,7 @@
       </c>
       <c r="BM148"/>
     </row>
-    <row r="149" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>16</v>
       </c>
@@ -19789,7 +19782,7 @@
       </c>
       <c r="BM149"/>
     </row>
-    <row r="150" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>16</v>
       </c>
@@ -19894,7 +19887,7 @@
       </c>
       <c r="BM150"/>
     </row>
-    <row r="151" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>16</v>
       </c>
@@ -19999,7 +19992,7 @@
       </c>
       <c r="BM151"/>
     </row>
-    <row r="152" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>16</v>
       </c>
@@ -20104,7 +20097,7 @@
       </c>
       <c r="BM152"/>
     </row>
-    <row r="153" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>16</v>
       </c>
@@ -20209,7 +20202,7 @@
       </c>
       <c r="BM153"/>
     </row>
-    <row r="154" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>296</v>
       </c>
@@ -20312,7 +20305,7 @@
       </c>
       <c r="BM154"/>
     </row>
-    <row r="155" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>296</v>
       </c>
@@ -20415,7 +20408,7 @@
       </c>
       <c r="BM155"/>
     </row>
-    <row r="156" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>296</v>
       </c>
@@ -20518,7 +20511,7 @@
       </c>
       <c r="BM156"/>
     </row>
-    <row r="157" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>296</v>
       </c>
@@ -20621,7 +20614,7 @@
       </c>
       <c r="BM157"/>
     </row>
-    <row r="158" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>296</v>
       </c>
@@ -20724,7 +20717,7 @@
       </c>
       <c r="BM158"/>
     </row>
-    <row r="159" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
         <v>296</v>
       </c>
@@ -20827,7 +20820,7 @@
       </c>
       <c r="BM159"/>
     </row>
-    <row r="160" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
         <v>16</v>
       </c>
@@ -20932,7 +20925,7 @@
       </c>
       <c r="BM160"/>
     </row>
-    <row r="161" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>16</v>
       </c>
@@ -21037,7 +21030,7 @@
       </c>
       <c r="BM161"/>
     </row>
-    <row r="162" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>16</v>
       </c>
@@ -21140,7 +21133,7 @@
       </c>
       <c r="BM162"/>
     </row>
-    <row r="163" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>16</v>
       </c>
@@ -21243,7 +21236,7 @@
       </c>
       <c r="BM163"/>
     </row>
-    <row r="164" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>16</v>
       </c>
@@ -21346,7 +21339,7 @@
       </c>
       <c r="BM164"/>
     </row>
-    <row r="165" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>16</v>
       </c>
@@ -21449,7 +21442,7 @@
       </c>
       <c r="BM165"/>
     </row>
-    <row r="166" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>296</v>
       </c>
@@ -21554,7 +21547,7 @@
       </c>
       <c r="BM166"/>
     </row>
-    <row r="167" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>296</v>
       </c>
@@ -21661,7 +21654,7 @@
       </c>
       <c r="BM167"/>
     </row>
-    <row r="168" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>296</v>
       </c>
@@ -21766,7 +21759,7 @@
       </c>
       <c r="BM168"/>
     </row>
-    <row r="169" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>296</v>
       </c>
@@ -21873,7 +21866,7 @@
       </c>
       <c r="BM169"/>
     </row>
-    <row r="170" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>296</v>
       </c>
@@ -21978,7 +21971,7 @@
       </c>
       <c r="BM170"/>
     </row>
-    <row r="171" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>296</v>
       </c>
@@ -22085,7 +22078,7 @@
       </c>
       <c r="BM171"/>
     </row>
-    <row r="172" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>16</v>
       </c>
@@ -22188,7 +22181,7 @@
       </c>
       <c r="BM172"/>
     </row>
-    <row r="173" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>16</v>
       </c>
@@ -22293,7 +22286,7 @@
       </c>
       <c r="BM173"/>
     </row>
-    <row r="174" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>16</v>
       </c>
@@ -22396,7 +22389,7 @@
       </c>
       <c r="BM174"/>
     </row>
-    <row r="175" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>16</v>
       </c>
@@ -22501,7 +22494,7 @@
       </c>
       <c r="BM175"/>
     </row>
-    <row r="176" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
         <v>16</v>
       </c>
@@ -22604,7 +22597,7 @@
       </c>
       <c r="BM176"/>
     </row>
-    <row r="177" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>16</v>
       </c>
@@ -22709,7 +22702,7 @@
       </c>
       <c r="BM177"/>
     </row>
-    <row r="178" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>296</v>
       </c>
@@ -22814,7 +22807,7 @@
       </c>
       <c r="BM178"/>
     </row>
-    <row r="179" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>296</v>
       </c>
@@ -22921,7 +22914,7 @@
       </c>
       <c r="BM179"/>
     </row>
-    <row r="180" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>296</v>
       </c>
@@ -23026,7 +23019,7 @@
       </c>
       <c r="BM180"/>
     </row>
-    <row r="181" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>296</v>
       </c>
@@ -23133,7 +23126,7 @@
       </c>
       <c r="BM181"/>
     </row>
-    <row r="182" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>296</v>
       </c>
@@ -23238,7 +23231,7 @@
       </c>
       <c r="BM182"/>
     </row>
-    <row r="183" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>296</v>
       </c>
@@ -23345,7 +23338,7 @@
       </c>
       <c r="BM183"/>
     </row>
-    <row r="184" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>16</v>
       </c>
@@ -23448,7 +23441,7 @@
       </c>
       <c r="BM184"/>
     </row>
-    <row r="185" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>16</v>
       </c>
@@ -23551,7 +23544,7 @@
       </c>
       <c r="BM185"/>
     </row>
-    <row r="186" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>16</v>
       </c>
@@ -23656,7 +23649,7 @@
       </c>
       <c r="BM186"/>
     </row>
-    <row r="187" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>16</v>
       </c>
@@ -23759,7 +23752,7 @@
       </c>
       <c r="BM187"/>
     </row>
-    <row r="188" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>16</v>
       </c>
@@ -23862,7 +23855,7 @@
       </c>
       <c r="BM188"/>
     </row>
-    <row r="189" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>16</v>
       </c>
@@ -23965,7 +23958,7 @@
       </c>
       <c r="BM189"/>
     </row>
-    <row r="190" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>296</v>
       </c>
@@ -24075,7 +24068,7 @@
       </c>
       <c r="BM190"/>
     </row>
-    <row r="191" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>296</v>
       </c>
@@ -24185,7 +24178,7 @@
       </c>
       <c r="BM191"/>
     </row>
-    <row r="192" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>296</v>
       </c>
@@ -24293,7 +24286,7 @@
       </c>
       <c r="BM192"/>
     </row>
-    <row r="193" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>296</v>
       </c>
@@ -24403,7 +24396,7 @@
       </c>
       <c r="BM193"/>
     </row>
-    <row r="194" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
         <v>296</v>
       </c>
@@ -24513,7 +24506,7 @@
       </c>
       <c r="BM194"/>
     </row>
-    <row r="195" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>296</v>
       </c>
@@ -24621,7 +24614,7 @@
       </c>
       <c r="BM195"/>
     </row>
-    <row r="196" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>296</v>
       </c>
@@ -24733,7 +24726,7 @@
       </c>
       <c r="BM196"/>
     </row>
-    <row r="197" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>296</v>
       </c>
@@ -24845,7 +24838,7 @@
       </c>
       <c r="BM197"/>
     </row>
-    <row r="198" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
         <v>296</v>
       </c>
@@ -24955,7 +24948,7 @@
       </c>
       <c r="BM198"/>
     </row>
-    <row r="199" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>296</v>
       </c>
@@ -25067,7 +25060,7 @@
       </c>
       <c r="BM199"/>
     </row>
-    <row r="200" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
         <v>296</v>
       </c>
@@ -25179,7 +25172,7 @@
       </c>
       <c r="BM200"/>
     </row>
-    <row r="201" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>296</v>
       </c>
@@ -25289,7 +25282,7 @@
       </c>
       <c r="BM201"/>
     </row>
-    <row r="202" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
         <v>16</v>
       </c>
@@ -25399,7 +25392,7 @@
       </c>
       <c r="BM202"/>
     </row>
-    <row r="203" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>16</v>
       </c>
@@ -25509,7 +25502,7 @@
       </c>
       <c r="BM203"/>
     </row>
-    <row r="204" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>16</v>
       </c>
@@ -25619,7 +25612,7 @@
       </c>
       <c r="BM204"/>
     </row>
-    <row r="205" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
         <v>16</v>
       </c>
@@ -25729,7 +25722,7 @@
       </c>
       <c r="BM205"/>
     </row>
-    <row r="206" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
         <v>16</v>
       </c>
@@ -25839,7 +25832,7 @@
       </c>
       <c r="BM206"/>
     </row>
-    <row r="207" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>16</v>
       </c>
@@ -25947,7 +25940,7 @@
       </c>
       <c r="BM207"/>
     </row>
-    <row r="208" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>296</v>
       </c>
@@ -26059,7 +26052,7 @@
       <c r="BJ208" s="4"/>
       <c r="BM208"/>
     </row>
-    <row r="209" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>296</v>
       </c>
@@ -26171,7 +26164,7 @@
       <c r="BJ209" s="4"/>
       <c r="BM209"/>
     </row>
-    <row r="210" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
         <v>296</v>
       </c>
@@ -26283,7 +26276,7 @@
       <c r="BJ210" s="4"/>
       <c r="BM210"/>
     </row>
-    <row r="211" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
         <v>296</v>
       </c>
@@ -26395,7 +26388,7 @@
       <c r="BJ211" s="4"/>
       <c r="BM211"/>
     </row>
-    <row r="212" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
         <v>296</v>
       </c>
@@ -26507,7 +26500,7 @@
       <c r="BJ212" s="4"/>
       <c r="BM212"/>
     </row>
-    <row r="213" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>296</v>
       </c>
@@ -26619,7 +26612,7 @@
       <c r="BJ213" s="4"/>
       <c r="BM213"/>
     </row>
-    <row r="214" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
         <v>296</v>
       </c>
@@ -26731,7 +26724,7 @@
       <c r="BJ214" s="4"/>
       <c r="BM214"/>
     </row>
-    <row r="215" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>296</v>
       </c>
@@ -26843,7 +26836,7 @@
       <c r="BJ215" s="4"/>
       <c r="BM215"/>
     </row>
-    <row r="216" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
         <v>296</v>
       </c>
@@ -26955,7 +26948,7 @@
       <c r="BJ216" s="4"/>
       <c r="BM216"/>
     </row>
-    <row r="217" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
         <v>296</v>
       </c>
@@ -27067,7 +27060,7 @@
       <c r="BJ217" s="4"/>
       <c r="BM217"/>
     </row>
-    <row r="218" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>296</v>
       </c>
@@ -27179,7 +27172,7 @@
       <c r="BJ218" s="4"/>
       <c r="BM218"/>
     </row>
-    <row r="219" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
         <v>296</v>
       </c>
@@ -27291,7 +27284,7 @@
       <c r="BJ219" s="4"/>
       <c r="BM219"/>
     </row>
-    <row r="220" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
         <v>296</v>
       </c>
@@ -27401,7 +27394,7 @@
       <c r="BJ220" s="4"/>
       <c r="BM220"/>
     </row>
-    <row r="221" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>296</v>
       </c>
@@ -27511,7 +27504,7 @@
       <c r="BJ221" s="4"/>
       <c r="BM221"/>
     </row>
-    <row r="222" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
         <v>296</v>
       </c>
@@ -27621,7 +27614,7 @@
       <c r="BJ222" s="4"/>
       <c r="BM222"/>
     </row>
-    <row r="223" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
         <v>296</v>
       </c>
@@ -27731,7 +27724,7 @@
       <c r="BJ223" s="4"/>
       <c r="BM223"/>
     </row>
-    <row r="224" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
         <v>296</v>
       </c>
@@ -27841,7 +27834,7 @@
       <c r="BJ224" s="4"/>
       <c r="BM224"/>
     </row>
-    <row r="225" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
         <v>296</v>
       </c>
@@ -27951,7 +27944,7 @@
       <c r="BJ225" s="4"/>
       <c r="BM225"/>
     </row>
-    <row r="226" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A226" s="8" t="s">
         <v>296</v>
       </c>
@@ -28052,7 +28045,7 @@
       <c r="BJ226" s="4"/>
       <c r="BM226"/>
     </row>
-    <row r="227" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A227" s="8" t="s">
         <v>296</v>
       </c>
@@ -28163,7 +28156,7 @@
       <c r="BJ227" s="4"/>
       <c r="BM227"/>
     </row>
-    <row r="228" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A228" s="8" t="s">
         <v>296</v>
       </c>
@@ -28276,7 +28269,7 @@
       <c r="BJ228" s="4"/>
       <c r="BM228"/>
     </row>
-    <row r="229" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A229" s="8" t="s">
         <v>296</v>
       </c>
@@ -28389,7 +28382,7 @@
       <c r="BJ229" s="4"/>
       <c r="BM229"/>
     </row>
-    <row r="230" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A230" s="8" t="s">
         <v>296</v>
       </c>
@@ -28502,7 +28495,7 @@
       <c r="BJ230" s="4"/>
       <c r="BM230"/>
     </row>
-    <row r="231" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>296</v>
       </c>
@@ -28617,7 +28610,7 @@
       </c>
       <c r="BM231"/>
     </row>
-    <row r="232" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>296</v>
       </c>
@@ -28732,7 +28725,7 @@
       </c>
       <c r="BM232"/>
     </row>
-    <row r="233" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
         <v>296</v>
       </c>
@@ -28847,7 +28840,7 @@
       </c>
       <c r="BM233"/>
     </row>
-    <row r="234" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>296</v>
       </c>
@@ -28962,7 +28955,7 @@
       </c>
       <c r="BM234"/>
     </row>
-    <row r="235" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A235" s="8" t="s">
         <v>296</v>
       </c>
@@ -29060,7 +29053,7 @@
       </c>
       <c r="BM235"/>
     </row>
-    <row r="236" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A236" s="8" t="s">
         <v>296</v>
       </c>
@@ -29162,7 +29155,7 @@
       </c>
       <c r="BM236"/>
     </row>
-    <row r="237" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A237" s="8" t="s">
         <v>296</v>
       </c>
@@ -29262,7 +29255,7 @@
       </c>
       <c r="BM237"/>
     </row>
-    <row r="238" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A238" s="8" t="s">
         <v>296</v>
       </c>
@@ -29364,7 +29357,7 @@
       </c>
       <c r="BM238"/>
     </row>
-    <row r="239" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A239" s="8" t="s">
         <v>296</v>
       </c>
@@ -29464,7 +29457,7 @@
       </c>
       <c r="BM239"/>
     </row>
-    <row r="240" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A240" s="8" t="s">
         <v>296</v>
       </c>
@@ -29571,7 +29564,7 @@
       </c>
       <c r="BM240"/>
     </row>
-    <row r="241" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A241" s="8" t="s">
         <v>296</v>
       </c>
@@ -29676,7 +29669,7 @@
       </c>
       <c r="BM241"/>
     </row>
-    <row r="242" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A242" s="8" t="s">
         <v>296</v>
       </c>
@@ -29783,7 +29776,7 @@
       </c>
       <c r="BM242"/>
     </row>
-    <row r="243" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A243" s="33" t="s">
         <v>296</v>
       </c>
@@ -29890,7 +29883,7 @@
       </c>
       <c r="BM243"/>
     </row>
-    <row r="244" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A244" s="8" t="s">
         <v>296</v>
       </c>
@@ -29997,7 +29990,7 @@
       </c>
       <c r="BM244"/>
     </row>
-    <row r="245" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A245" s="8" t="s">
         <v>16</v>
       </c>
@@ -30105,7 +30098,7 @@
       </c>
       <c r="BM245"/>
     </row>
-    <row r="246" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A246" s="8" t="s">
         <v>16</v>
       </c>
@@ -30211,7 +30204,7 @@
       </c>
       <c r="BM246"/>
     </row>
-    <row r="247" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A247" s="8" t="s">
         <v>16</v>
       </c>
@@ -30317,7 +30310,7 @@
       </c>
       <c r="BM247"/>
     </row>
-    <row r="248" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A248" s="8" t="s">
         <v>16</v>
       </c>
@@ -30423,7 +30416,7 @@
       </c>
       <c r="BM248"/>
     </row>
-    <row r="249" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A249" s="8" t="s">
         <v>16</v>
       </c>
@@ -30529,7 +30522,7 @@
       </c>
       <c r="BM249"/>
     </row>
-    <row r="250" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A250" s="8" t="s">
         <v>16</v>
       </c>
@@ -30635,7 +30628,7 @@
       </c>
       <c r="BM250"/>
     </row>
-    <row r="251" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A251" s="8" t="s">
         <v>296</v>
       </c>
@@ -30748,7 +30741,7 @@
       </c>
       <c r="BM251"/>
     </row>
-    <row r="252" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A252" s="8" t="s">
         <v>296</v>
       </c>
@@ -30861,7 +30854,7 @@
       </c>
       <c r="BM252"/>
     </row>
-    <row r="253" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A253" s="8" t="s">
         <v>296</v>
       </c>
@@ -30974,7 +30967,7 @@
       </c>
       <c r="BM253"/>
     </row>
-    <row r="254" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A254" s="8" t="s">
         <v>296</v>
       </c>
@@ -31087,7 +31080,7 @@
       </c>
       <c r="BM254"/>
     </row>
-    <row r="255" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A255" s="8" t="s">
         <v>296</v>
       </c>
@@ -31198,7 +31191,7 @@
       </c>
       <c r="BM255"/>
     </row>
-    <row r="256" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A256" s="8" t="s">
         <v>16</v>
       </c>
@@ -31307,7 +31300,7 @@
       </c>
       <c r="BM256"/>
     </row>
-    <row r="257" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A257" s="8" t="s">
         <v>16</v>
       </c>
@@ -31416,7 +31409,7 @@
       </c>
       <c r="BM257"/>
     </row>
-    <row r="258" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A258" s="8" t="s">
         <v>16</v>
       </c>
@@ -31525,7 +31518,7 @@
       </c>
       <c r="BM258"/>
     </row>
-    <row r="259" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A259" s="8" t="s">
         <v>16</v>
       </c>
@@ -31634,7 +31627,7 @@
       </c>
       <c r="BM259"/>
     </row>
-    <row r="260" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A260" s="8" t="s">
         <v>16</v>
       </c>
@@ -31743,7 +31736,7 @@
       </c>
       <c r="BM260"/>
     </row>
-    <row r="261" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A261" s="8" t="s">
         <v>296</v>
       </c>
@@ -31854,7 +31847,7 @@
       <c r="BJ261" s="4"/>
       <c r="BM261"/>
     </row>
-    <row r="262" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A262" s="8" t="s">
         <v>296</v>
       </c>
@@ -31965,7 +31958,7 @@
       <c r="BJ262" s="4"/>
       <c r="BM262"/>
     </row>
-    <row r="263" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A263" s="33" t="s">
         <v>296</v>
       </c>
@@ -32080,7 +32073,7 @@
       <c r="BJ263" s="4"/>
       <c r="BM263"/>
     </row>
-    <row r="264" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A264" s="33" t="s">
         <v>296</v>
       </c>
@@ -32195,7 +32188,7 @@
       <c r="BJ264" s="4"/>
       <c r="BM264"/>
     </row>
-    <row r="265" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A265" s="33" t="s">
         <v>296</v>
       </c>
@@ -32310,7 +32303,7 @@
       <c r="BJ265" s="4"/>
       <c r="BM265"/>
     </row>
-    <row r="266" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A266" s="8" t="s">
         <v>296</v>
       </c>
@@ -32423,7 +32416,7 @@
       <c r="BJ266" s="4"/>
       <c r="BM266"/>
     </row>
-    <row r="267" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A267" s="8" t="s">
         <v>296</v>
       </c>
@@ -32536,7 +32529,7 @@
       <c r="BJ267" s="4"/>
       <c r="BM267"/>
     </row>
-    <row r="268" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A268" s="8" t="s">
         <v>296</v>
       </c>
@@ -32649,7 +32642,7 @@
       <c r="BJ268" s="4"/>
       <c r="BM268"/>
     </row>
-    <row r="269" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A269" s="8" t="s">
         <v>296</v>
       </c>
@@ -32762,7 +32755,7 @@
       <c r="BJ269" s="4"/>
       <c r="BM269"/>
     </row>
-    <row r="270" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A270" s="8" t="s">
         <v>16</v>
       </c>
@@ -32871,7 +32864,7 @@
       <c r="BJ270" s="4"/>
       <c r="BM270"/>
     </row>
-    <row r="271" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A271" s="33" t="s">
         <v>16</v>
       </c>
@@ -32982,7 +32975,7 @@
       <c r="BJ271" s="4"/>
       <c r="BM271"/>
     </row>
-    <row r="272" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A272" s="8" t="s">
         <v>16</v>
       </c>
@@ -33091,7 +33084,7 @@
       <c r="BJ272" s="4"/>
       <c r="BM272"/>
     </row>
-    <row r="273" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A273" s="8" t="s">
         <v>16</v>
       </c>
@@ -33200,7 +33193,7 @@
       <c r="BJ273" s="4"/>
       <c r="BM273"/>
     </row>
-    <row r="274" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A274" s="8" t="s">
         <v>16</v>
       </c>
@@ -33309,7 +33302,7 @@
       <c r="BJ274" s="4"/>
       <c r="BM274"/>
     </row>
-    <row r="275" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A275" s="8" t="s">
         <v>16</v>
       </c>
@@ -33418,7 +33411,7 @@
       <c r="BJ275" s="4"/>
       <c r="BM275"/>
     </row>
-    <row r="276" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A276" s="8" t="s">
         <v>16</v>
       </c>
@@ -33527,7 +33520,7 @@
       <c r="BJ276" s="4"/>
       <c r="BM276"/>
     </row>
-    <row r="277" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A277" s="8" t="s">
         <v>16</v>
       </c>
@@ -33636,7 +33629,7 @@
       <c r="BJ277" s="4"/>
       <c r="BM277"/>
     </row>
-    <row r="278" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A278" s="8" t="s">
         <v>16</v>
       </c>
@@ -33745,7 +33738,7 @@
       <c r="BJ278" s="4"/>
       <c r="BM278"/>
     </row>
-    <row r="279" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A279" s="8" t="s">
         <v>296</v>
       </c>
@@ -33858,7 +33851,7 @@
       </c>
       <c r="BM279"/>
     </row>
-    <row r="280" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A280" s="8" t="s">
         <v>296</v>
       </c>
@@ -33963,7 +33956,7 @@
       </c>
       <c r="BM280"/>
     </row>
-    <row r="281" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A281" s="8" t="s">
         <v>296</v>
       </c>
@@ -34076,7 +34069,7 @@
       </c>
       <c r="BM281"/>
     </row>
-    <row r="282" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A282" s="8" t="s">
         <v>296</v>
       </c>
@@ -34181,7 +34174,7 @@
       </c>
       <c r="BM282"/>
     </row>
-    <row r="283" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A283" s="8" t="s">
         <v>296</v>
       </c>
@@ -34294,7 +34287,7 @@
       </c>
       <c r="BM283"/>
     </row>
-    <row r="284" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A284" s="8" t="s">
         <v>296</v>
       </c>
@@ -34397,7 +34390,7 @@
       </c>
       <c r="BM284"/>
     </row>
-    <row r="285" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A285" s="33" t="s">
         <v>296</v>
       </c>
@@ -34508,7 +34501,7 @@
       </c>
       <c r="BM285"/>
     </row>
-    <row r="286" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A286" s="8" t="s">
         <v>296</v>
       </c>
@@ -34611,7 +34604,7 @@
       </c>
       <c r="BM286"/>
     </row>
-    <row r="287" spans="1:65" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:65" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A287" s="8" t="s">
         <v>296</v>
       </c>
@@ -34722,7 +34715,7 @@
       </c>
       <c r="BM287"/>
     </row>
-    <row r="288" spans="1:65" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:65" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A288" s="8" t="s">
         <v>296</v>
       </c>
@@ -34827,7 +34820,7 @@
       </c>
       <c r="BM288"/>
     </row>
-    <row r="289" spans="1:65" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:65" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A289" s="8" t="s">
         <v>296</v>
       </c>
@@ -34932,7 +34925,7 @@
       </c>
       <c r="BM289"/>
     </row>
-    <row r="290" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A290" s="8" t="s">
         <v>16</v>
       </c>
@@ -35049,7 +35042,7 @@
       <c r="BJ290" s="4"/>
       <c r="BM290"/>
     </row>
-    <row r="291" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A291" s="8" t="s">
         <v>16</v>
       </c>
@@ -35164,7 +35157,7 @@
       <c r="BJ291" s="4"/>
       <c r="BM291"/>
     </row>
-    <row r="292" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A292" s="8" t="s">
         <v>16</v>
       </c>
@@ -35279,7 +35272,7 @@
       <c r="BJ292" s="4"/>
       <c r="BM292"/>
     </row>
-    <row r="293" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A293" s="8" t="s">
         <v>16</v>
       </c>
@@ -35394,7 +35387,7 @@
       <c r="BJ293" s="4"/>
       <c r="BM293"/>
     </row>
-    <row r="294" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A294" s="8" t="s">
         <v>16</v>
       </c>
@@ -35509,7 +35502,7 @@
       <c r="BJ294" s="4"/>
       <c r="BM294"/>
     </row>
-    <row r="295" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A295" s="8" t="s">
         <v>16</v>
       </c>
@@ -35624,7 +35617,7 @@
       <c r="BJ295" s="4"/>
       <c r="BM295"/>
     </row>
-    <row r="296" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A296" s="8" t="s">
         <v>16</v>
       </c>
@@ -35739,7 +35732,7 @@
       <c r="BJ296" s="4"/>
       <c r="BM296"/>
     </row>
-    <row r="297" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A297" s="8" t="s">
         <v>16</v>
       </c>
@@ -35854,7 +35847,7 @@
       <c r="BJ297" s="4"/>
       <c r="BM297"/>
     </row>
-    <row r="298" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A298" s="8" t="s">
         <v>16</v>
       </c>
@@ -36082,7 +36075,7 @@
       <c r="BJ299" s="4"/>
       <c r="BM299"/>
     </row>
-    <row r="300" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A300" s="8" t="s">
         <v>16</v>
       </c>
@@ -36197,7 +36190,7 @@
       <c r="BJ300" s="4"/>
       <c r="BM300"/>
     </row>
-    <row r="301" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A301" s="8" t="s">
         <v>16</v>
       </c>
@@ -36312,7 +36305,7 @@
       <c r="BJ301" s="4"/>
       <c r="BM301"/>
     </row>
-    <row r="302" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A302" s="33" t="s">
         <v>16</v>
       </c>
@@ -36427,7 +36420,7 @@
       <c r="BJ302" s="4"/>
       <c r="BM302"/>
     </row>
-    <row r="303" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A303" s="8" t="s">
         <v>16</v>
       </c>
@@ -36542,7 +36535,7 @@
       <c r="BJ303" s="4"/>
       <c r="BM303"/>
     </row>
-    <row r="304" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A304" s="8" t="s">
         <v>16</v>
       </c>
@@ -36657,7 +36650,7 @@
       <c r="BJ304" s="4"/>
       <c r="BM304"/>
     </row>
-    <row r="305" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A305" s="8" t="s">
         <v>16</v>
       </c>
@@ -36772,7 +36765,7 @@
       <c r="BJ305" s="4"/>
       <c r="BM305"/>
     </row>
-    <row r="306" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A306" s="8" t="s">
         <v>16</v>
       </c>
@@ -36887,7 +36880,7 @@
       <c r="BJ306" s="4"/>
       <c r="BM306"/>
     </row>
-    <row r="307" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A307" s="8" t="s">
         <v>16</v>
       </c>
@@ -37002,7 +36995,7 @@
       <c r="BJ307" s="4"/>
       <c r="BM307"/>
     </row>
-    <row r="308" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A308" s="8" t="s">
         <v>16</v>
       </c>
@@ -37121,7 +37114,7 @@
       </c>
       <c r="BM308"/>
     </row>
-    <row r="309" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A309" s="8" t="s">
         <v>16</v>
       </c>
@@ -37240,7 +37233,7 @@
       </c>
       <c r="BM309"/>
     </row>
-    <row r="310" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A310" s="8" t="s">
         <v>16</v>
       </c>
@@ -37359,7 +37352,7 @@
       </c>
       <c r="BM310"/>
     </row>
-    <row r="311" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A311" s="8" t="s">
         <v>16</v>
       </c>
@@ -37478,7 +37471,7 @@
       </c>
       <c r="BM311"/>
     </row>
-    <row r="312" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A312" s="8" t="s">
         <v>16</v>
       </c>
@@ -37597,7 +37590,7 @@
       </c>
       <c r="BM312"/>
     </row>
-    <row r="313" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A313" s="8" t="s">
         <v>16</v>
       </c>
@@ -37716,7 +37709,7 @@
       </c>
       <c r="BM313"/>
     </row>
-    <row r="314" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A314" s="8" t="s">
         <v>16</v>
       </c>
@@ -37835,7 +37828,7 @@
       </c>
       <c r="BM314"/>
     </row>
-    <row r="315" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A315" s="33" t="s">
         <v>16</v>
       </c>
@@ -37954,7 +37947,7 @@
       </c>
       <c r="BM315"/>
     </row>
-    <row r="316" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A316" s="8" t="s">
         <v>16</v>
       </c>
@@ -38073,7 +38066,7 @@
       </c>
       <c r="BM316"/>
     </row>
-    <row r="317" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A317" s="8" t="s">
         <v>16</v>
       </c>
@@ -38192,7 +38185,7 @@
       </c>
       <c r="BM317"/>
     </row>
-    <row r="318" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A318" s="8" t="s">
         <v>16</v>
       </c>
@@ -38293,7 +38286,7 @@
       </c>
       <c r="BM318"/>
     </row>
-    <row r="319" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A319" s="8" t="s">
         <v>16</v>
       </c>
@@ -38420,7 +38413,7 @@
       </c>
       <c r="BM319"/>
     </row>
-    <row r="320" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A320" s="8" t="s">
         <v>16</v>
       </c>
@@ -38545,7 +38538,7 @@
       </c>
       <c r="BM320"/>
     </row>
-    <row r="321" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A321" s="8" t="s">
         <v>16</v>
       </c>
@@ -38670,7 +38663,7 @@
       </c>
       <c r="BM321"/>
     </row>
-    <row r="322" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A322" s="8" t="s">
         <v>16</v>
       </c>
@@ -38795,7 +38788,7 @@
       </c>
       <c r="BM322"/>
     </row>
-    <row r="323" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A323" s="8" t="s">
         <v>16</v>
       </c>
@@ -38920,7 +38913,7 @@
       </c>
       <c r="BM323"/>
     </row>
-    <row r="324" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A324" s="8" t="s">
         <v>16</v>
       </c>
@@ -39045,7 +39038,7 @@
       </c>
       <c r="BM324"/>
     </row>
-    <row r="325" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A325" s="8" t="s">
         <v>296</v>
       </c>
@@ -39162,7 +39155,7 @@
       <c r="BJ325" s="4"/>
       <c r="BM325"/>
     </row>
-    <row r="326" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A326" s="8" t="s">
         <v>296</v>
       </c>
@@ -39273,7 +39266,7 @@
       <c r="BJ326" s="4"/>
       <c r="BM326"/>
     </row>
-    <row r="327" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A327" s="8" t="s">
         <v>296</v>
       </c>
@@ -39384,7 +39377,7 @@
       <c r="BJ327" s="4"/>
       <c r="BM327"/>
     </row>
-    <row r="328" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A328" s="8" t="s">
         <v>296</v>
       </c>
@@ -39495,7 +39488,7 @@
       <c r="BJ328" s="4"/>
       <c r="BM328"/>
     </row>
-    <row r="329" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A329" s="8" t="s">
         <v>296</v>
       </c>
@@ -39606,7 +39599,7 @@
       <c r="BJ329" s="4"/>
       <c r="BM329"/>
     </row>
-    <row r="330" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A330" s="8" t="s">
         <v>16</v>
       </c>
@@ -39729,7 +39722,7 @@
       </c>
       <c r="BM330"/>
     </row>
-    <row r="331" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A331" s="8" t="s">
         <v>16</v>
       </c>
@@ -39852,7 +39845,7 @@
       </c>
       <c r="BM331"/>
     </row>
-    <row r="332" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A332" s="8" t="s">
         <v>16</v>
       </c>
@@ -39975,7 +39968,7 @@
       </c>
       <c r="BM332"/>
     </row>
-    <row r="333" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A333" s="8" t="s">
         <v>16</v>
       </c>
@@ -40098,7 +40091,7 @@
       </c>
       <c r="BM333"/>
     </row>
-    <row r="334" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A334" s="8" t="s">
         <v>16</v>
       </c>
@@ -40221,7 +40214,7 @@
       </c>
       <c r="BM334"/>
     </row>
-    <row r="335" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A335" s="8" t="s">
         <v>16</v>
       </c>
@@ -40344,7 +40337,7 @@
       </c>
       <c r="BM335"/>
     </row>
-    <row r="336" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A336" s="8" t="s">
         <v>16</v>
       </c>
@@ -40463,7 +40456,7 @@
       </c>
       <c r="BM336"/>
     </row>
-    <row r="337" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A337" s="8" t="s">
         <v>16</v>
       </c>
@@ -40582,7 +40575,7 @@
       </c>
       <c r="BM337"/>
     </row>
-    <row r="338" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A338" s="8" t="s">
         <v>16</v>
       </c>
@@ -40701,7 +40694,7 @@
       </c>
       <c r="BM338"/>
     </row>
-    <row r="339" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A339" s="8" t="s">
         <v>16</v>
       </c>
@@ -40820,7 +40813,7 @@
       </c>
       <c r="BM339"/>
     </row>
-    <row r="340" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A340" s="8" t="s">
         <v>16</v>
       </c>
@@ -40939,7 +40932,7 @@
       </c>
       <c r="BM340"/>
     </row>
-    <row r="341" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A341" s="8" t="s">
         <v>16</v>
       </c>
@@ -41058,7 +41051,7 @@
       </c>
       <c r="BM341"/>
     </row>
-    <row r="342" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A342" s="8" t="s">
         <v>16</v>
       </c>
@@ -41177,7 +41170,7 @@
       </c>
       <c r="BM342"/>
     </row>
-    <row r="343" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A343" s="8" t="s">
         <v>16</v>
       </c>
@@ -41290,7 +41283,7 @@
       <c r="BJ343" s="4"/>
       <c r="BM343"/>
     </row>
-    <row r="344" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A344" s="8" t="s">
         <v>16</v>
       </c>
@@ -41403,7 +41396,7 @@
       <c r="BJ344" s="4"/>
       <c r="BM344"/>
     </row>
-    <row r="345" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A345" s="8" t="s">
         <v>16</v>
       </c>
@@ -41516,7 +41509,7 @@
       <c r="BJ345" s="4"/>
       <c r="BM345"/>
     </row>
-    <row r="346" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A346" s="8" t="s">
         <v>16</v>
       </c>
@@ -41629,7 +41622,7 @@
       <c r="BJ346" s="4"/>
       <c r="BM346"/>
     </row>
-    <row r="347" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A347" s="8" t="s">
         <v>16</v>
       </c>
@@ -41742,7 +41735,7 @@
       <c r="BJ347" s="4"/>
       <c r="BM347"/>
     </row>
-    <row r="348" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A348" s="8" t="s">
         <v>16</v>
       </c>
@@ -41855,7 +41848,7 @@
       <c r="BJ348" s="4"/>
       <c r="BM348"/>
     </row>
-    <row r="349" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A349" s="8" t="s">
         <v>16</v>
       </c>
@@ -41968,7 +41961,7 @@
       <c r="BJ349" s="4"/>
       <c r="BM349"/>
     </row>
-    <row r="350" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A350" s="8" t="s">
         <v>16</v>
       </c>
@@ -42081,7 +42074,7 @@
       <c r="BJ350" s="4"/>
       <c r="BM350"/>
     </row>
-    <row r="351" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A351" s="8" t="s">
         <v>16</v>
       </c>
@@ -42196,7 +42189,7 @@
       <c r="BJ351" s="4"/>
       <c r="BM351"/>
     </row>
-    <row r="352" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A352" s="8" t="s">
         <v>16</v>
       </c>
@@ -42311,7 +42304,7 @@
       <c r="BJ352" s="4"/>
       <c r="BM352"/>
     </row>
-    <row r="353" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A353" s="8" t="s">
         <v>16</v>
       </c>
@@ -42424,7 +42417,7 @@
       <c r="BJ353" s="4"/>
       <c r="BM353"/>
     </row>
-    <row r="354" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A354" s="8" t="s">
         <v>16</v>
       </c>
@@ -42539,7 +42532,7 @@
       <c r="BJ354" s="4"/>
       <c r="BM354"/>
     </row>
-    <row r="355" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A355" s="8" t="s">
         <v>16</v>
       </c>
@@ -42655,7 +42648,7 @@
       <c r="BK355" s="8"/>
       <c r="BM355"/>
     </row>
-    <row r="356" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A356" s="8" t="s">
         <v>16</v>
       </c>
@@ -42771,7 +42764,7 @@
       <c r="BK356" s="8"/>
       <c r="BM356"/>
     </row>
-    <row r="357" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A357" s="8" t="s">
         <v>16</v>
       </c>
@@ -42887,7 +42880,7 @@
       <c r="BK357" s="8"/>
       <c r="BM357"/>
     </row>
-    <row r="358" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A358" s="8" t="s">
         <v>16</v>
       </c>
@@ -43003,7 +42996,7 @@
       <c r="BK358" s="8"/>
       <c r="BM358"/>
     </row>
-    <row r="359" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A359" s="8" t="s">
         <v>16</v>
       </c>
@@ -43119,7 +43112,7 @@
       <c r="BK359" s="8"/>
       <c r="BM359"/>
     </row>
-    <row r="360" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A360" s="8" t="s">
         <v>16</v>
       </c>
@@ -43235,7 +43228,7 @@
       <c r="BK360" s="8"/>
       <c r="BM360"/>
     </row>
-    <row r="361" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A361" s="8" t="s">
         <v>16</v>
       </c>
@@ -43351,7 +43344,7 @@
       <c r="BK361" s="8"/>
       <c r="BM361"/>
     </row>
-    <row r="362" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A362" s="8" t="s">
         <v>16</v>
       </c>
@@ -43467,7 +43460,7 @@
       <c r="BK362" s="8"/>
       <c r="BM362"/>
     </row>
-    <row r="363" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A363" s="8" t="s">
         <v>16</v>
       </c>
@@ -43583,7 +43576,7 @@
       <c r="BK363" s="8"/>
       <c r="BM363"/>
     </row>
-    <row r="364" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A364" s="8" t="s">
         <v>16</v>
       </c>
@@ -43699,7 +43692,7 @@
       <c r="BK364" s="8"/>
       <c r="BM364"/>
     </row>
-    <row r="365" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A365" s="8" t="s">
         <v>16</v>
       </c>
@@ -43815,7 +43808,7 @@
       <c r="BK365" s="8"/>
       <c r="BM365"/>
     </row>
-    <row r="366" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A366" s="8" t="s">
         <v>16</v>
       </c>
@@ -43931,7 +43924,7 @@
       <c r="BK366" s="8"/>
       <c r="BM366"/>
     </row>
-    <row r="367" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A367" s="8" t="s">
         <v>16</v>
       </c>
@@ -44047,7 +44040,7 @@
       <c r="BK367" s="8"/>
       <c r="BM367"/>
     </row>
-    <row r="368" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A368" s="8" t="s">
         <v>16</v>
       </c>
@@ -44163,7 +44156,7 @@
       <c r="BK368" s="8"/>
       <c r="BM368"/>
     </row>
-    <row r="369" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A369" s="8" t="s">
         <v>16</v>
       </c>
@@ -44281,7 +44274,7 @@
       <c r="BK369" s="8"/>
       <c r="BM369"/>
     </row>
-    <row r="370" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A370" s="8" t="s">
         <v>16</v>
       </c>
@@ -44399,7 +44392,7 @@
       <c r="BK370" s="8"/>
       <c r="BM370"/>
     </row>
-    <row r="371" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A371" s="8" t="s">
         <v>16</v>
       </c>
@@ -44519,7 +44512,7 @@
       <c r="BK371" s="8"/>
       <c r="BM371"/>
     </row>
-    <row r="372" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A372" s="8" t="s">
         <v>16</v>
       </c>
@@ -44639,7 +44632,7 @@
       <c r="BK372" s="8"/>
       <c r="BM372"/>
     </row>
-    <row r="373" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A373" s="8" t="s">
         <v>16</v>
       </c>
@@ -44759,7 +44752,7 @@
       <c r="BK373" s="8"/>
       <c r="BM373"/>
     </row>
-    <row r="374" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A374" s="8" t="s">
         <v>16</v>
       </c>
@@ -44879,7 +44872,7 @@
       <c r="BK374" s="8"/>
       <c r="BM374"/>
     </row>
-    <row r="375" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A375" s="86" t="s">
         <v>296</v>
       </c>
@@ -44994,7 +44987,7 @@
       <c r="BK375" s="8"/>
       <c r="BM375"/>
     </row>
-    <row r="376" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A376" s="86" t="s">
         <v>296</v>
       </c>
@@ -45107,7 +45100,7 @@
       <c r="BK376" s="8"/>
       <c r="BM376"/>
     </row>
-    <row r="377" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A377" s="86" t="s">
         <v>296</v>
       </c>
@@ -45220,7 +45213,7 @@
       <c r="BK377" s="8"/>
       <c r="BM377"/>
     </row>
-    <row r="378" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A378" s="86" t="s">
         <v>296</v>
       </c>
@@ -45331,7 +45324,7 @@
       <c r="BK378" s="8"/>
       <c r="BM378"/>
     </row>
-    <row r="379" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A379" s="86" t="s">
         <v>296</v>
       </c>
@@ -45443,7 +45436,7 @@
       </c>
       <c r="BM379"/>
     </row>
-    <row r="380" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A380" s="86" t="s">
         <v>296</v>
       </c>
@@ -45538,7 +45531,7 @@
       </c>
       <c r="BM380"/>
     </row>
-    <row r="381" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A381" s="86" t="s">
         <v>296</v>
       </c>
@@ -45635,7 +45628,7 @@
       </c>
       <c r="BM381"/>
     </row>
-    <row r="382" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A382" s="8" t="s">
         <v>296</v>
       </c>
@@ -45730,7 +45723,7 @@
       </c>
       <c r="BM382"/>
     </row>
-    <row r="383" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A383" s="8" t="s">
         <v>296</v>
       </c>
@@ -45827,7 +45820,7 @@
       </c>
       <c r="BM383"/>
     </row>
-    <row r="384" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A384" s="8" t="s">
         <v>296</v>
       </c>
@@ -45922,7 +45915,7 @@
       </c>
       <c r="BM384"/>
     </row>
-    <row r="385" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A385" s="8" t="s">
         <v>16</v>
       </c>
@@ -46030,7 +46023,7 @@
       </c>
       <c r="BM385"/>
     </row>
-    <row r="386" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A386" s="8" t="s">
         <v>124</v>
       </c>
@@ -46145,7 +46138,7 @@
       </c>
       <c r="BM386"/>
     </row>
-    <row r="387" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A387" s="8" t="s">
         <v>16</v>
       </c>
@@ -46253,7 +46246,7 @@
       </c>
       <c r="BM387"/>
     </row>
-    <row r="388" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A388" s="8" t="s">
         <v>124</v>
       </c>
@@ -46368,7 +46361,7 @@
       </c>
       <c r="BM388"/>
     </row>
-    <row r="389" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A389" s="8" t="s">
         <v>16</v>
       </c>
@@ -46476,7 +46469,7 @@
       </c>
       <c r="BM389"/>
     </row>
-    <row r="390" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A390" s="8" t="s">
         <v>124</v>
       </c>
@@ -46591,7 +46584,7 @@
       </c>
       <c r="BM390"/>
     </row>
-    <row r="391" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A391" s="8" t="s">
         <v>124</v>
       </c>
@@ -46699,7 +46692,7 @@
       </c>
       <c r="BM391"/>
     </row>
-    <row r="392" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A392" s="8" t="s">
         <v>124</v>
       </c>
@@ -46816,7 +46809,7 @@
       </c>
       <c r="BM392"/>
     </row>
-    <row r="393" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A393" s="8" t="s">
         <v>124</v>
       </c>
@@ -46924,7 +46917,7 @@
       </c>
       <c r="BM393"/>
     </row>
-    <row r="394" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A394" s="8" t="s">
         <v>124</v>
       </c>
@@ -47041,7 +47034,7 @@
       </c>
       <c r="BM394"/>
     </row>
-    <row r="395" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A395" s="8" t="s">
         <v>124</v>
       </c>
@@ -47151,7 +47144,7 @@
       </c>
       <c r="BM395"/>
     </row>
-    <row r="396" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A396" s="8" t="s">
         <v>16</v>
       </c>
@@ -47264,7 +47257,7 @@
       <c r="BJ396" s="3"/>
       <c r="BM396"/>
     </row>
-    <row r="397" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A397" s="8" t="s">
         <v>16</v>
       </c>
@@ -47377,7 +47370,7 @@
       <c r="BJ397" s="3"/>
       <c r="BM397"/>
     </row>
-    <row r="398" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A398" s="8" t="s">
         <v>16</v>
       </c>
@@ -47490,7 +47483,7 @@
       <c r="BJ398" s="3"/>
       <c r="BM398"/>
     </row>
-    <row r="399" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A399" s="8" t="s">
         <v>16</v>
       </c>
@@ -47603,7 +47596,7 @@
       <c r="BJ399" s="3"/>
       <c r="BM399"/>
     </row>
-    <row r="400" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A400" s="8" t="s">
         <v>16</v>
       </c>
@@ -47716,7 +47709,7 @@
       <c r="BJ400" s="3"/>
       <c r="BM400"/>
     </row>
-    <row r="401" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A401" s="8" t="s">
         <v>16</v>
       </c>
@@ -47829,7 +47822,7 @@
       <c r="BJ401" s="3"/>
       <c r="BM401"/>
     </row>
-    <row r="402" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A402" s="8" t="s">
         <v>16</v>
       </c>
@@ -47942,7 +47935,7 @@
       <c r="BJ402" s="3"/>
       <c r="BM402"/>
     </row>
-    <row r="403" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A403" s="86" t="s">
         <v>296</v>
       </c>
@@ -48047,7 +48040,7 @@
       <c r="BJ403" s="4"/>
       <c r="BM403"/>
     </row>
-    <row r="404" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A404" s="86" t="s">
         <v>296</v>
       </c>
@@ -48154,7 +48147,7 @@
       <c r="BJ404" s="4"/>
       <c r="BM404"/>
     </row>
-    <row r="405" spans="1:65" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:65" ht="144" x14ac:dyDescent="0.3">
       <c r="A405" s="86" t="s">
         <v>296</v>
       </c>
@@ -48261,7 +48254,7 @@
       <c r="BJ405" s="4"/>
       <c r="BM405"/>
     </row>
-    <row r="406" spans="1:65" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:65" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A406" s="86" t="s">
         <v>296</v>
       </c>
@@ -48370,7 +48363,7 @@
       <c r="BJ406" s="4"/>
       <c r="BM406"/>
     </row>
-    <row r="407" spans="1:65" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:65" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A407" s="86" t="s">
         <v>296</v>
       </c>
@@ -48477,7 +48470,7 @@
       <c r="BJ407" s="4"/>
       <c r="BM407"/>
     </row>
-    <row r="408" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A408" s="86" t="s">
         <v>296</v>
       </c>
@@ -48586,7 +48579,7 @@
       <c r="BJ408" s="4"/>
       <c r="BM408"/>
     </row>
-    <row r="409" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A409" s="86" t="s">
         <v>296</v>
       </c>
@@ -48691,7 +48684,7 @@
       <c r="BJ409" s="4"/>
       <c r="BM409"/>
     </row>
-    <row r="410" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A410" s="86" t="s">
         <v>296</v>
       </c>
@@ -48800,7 +48793,7 @@
       <c r="BJ410" s="4"/>
       <c r="BM410"/>
     </row>
-    <row r="411" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A411" s="86" t="s">
         <v>296</v>
       </c>
@@ -48909,7 +48902,7 @@
       <c r="BJ411" s="4"/>
       <c r="BM411"/>
     </row>
-    <row r="412" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A412" s="86" t="s">
         <v>296</v>
       </c>
@@ -49016,7 +49009,7 @@
       <c r="BJ412" s="4"/>
       <c r="BM412"/>
     </row>
-    <row r="413" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A413" s="86" t="s">
         <v>296</v>
       </c>
@@ -49121,7 +49114,7 @@
       <c r="BJ413" s="4"/>
       <c r="BM413"/>
     </row>
-    <row r="414" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A414" s="86" t="s">
         <v>296</v>
       </c>
@@ -49228,7 +49221,7 @@
       <c r="BJ414" s="4"/>
       <c r="BM414"/>
     </row>
-    <row r="415" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A415" s="86" t="s">
         <v>296</v>
       </c>
@@ -49337,7 +49330,7 @@
       <c r="BJ415" s="4"/>
       <c r="BM415"/>
     </row>
-    <row r="416" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A416" s="86" t="s">
         <v>296</v>
       </c>
@@ -49444,7 +49437,7 @@
       <c r="BJ416" s="4"/>
       <c r="BM416"/>
     </row>
-    <row r="417" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A417" s="86" t="s">
         <v>296</v>
       </c>
@@ -49553,7 +49546,7 @@
       <c r="BJ417" s="4"/>
       <c r="BM417"/>
     </row>
-    <row r="418" spans="1:65" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:65" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A418" s="86" t="s">
         <v>296</v>
       </c>
@@ -49660,7 +49653,7 @@
       <c r="BJ418" s="4"/>
       <c r="BM418"/>
     </row>
-    <row r="419" spans="1:65" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:65" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A419" s="86" t="s">
         <v>296</v>
       </c>
@@ -49769,7 +49762,7 @@
       <c r="BJ419" s="4"/>
       <c r="BM419"/>
     </row>
-    <row r="420" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A420" s="8" t="s">
         <v>16</v>
       </c>
@@ -49884,7 +49877,7 @@
       <c r="BJ420" s="4"/>
       <c r="BM420"/>
     </row>
-    <row r="421" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A421" s="8" t="s">
         <v>16</v>
       </c>
@@ -49999,7 +49992,7 @@
       <c r="BJ421" s="4"/>
       <c r="BM421"/>
     </row>
-    <row r="422" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A422" s="8" t="s">
         <v>16</v>
       </c>
@@ -50114,7 +50107,7 @@
       <c r="BJ422" s="4"/>
       <c r="BM422"/>
     </row>
-    <row r="423" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A423" s="8" t="s">
         <v>16</v>
       </c>
@@ -50229,7 +50222,7 @@
       <c r="BJ423" s="4"/>
       <c r="BM423"/>
     </row>
-    <row r="424" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A424" s="8" t="s">
         <v>16</v>
       </c>
@@ -50344,7 +50337,7 @@
       <c r="BJ424" s="4"/>
       <c r="BM424"/>
     </row>
-    <row r="425" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A425" s="8" t="s">
         <v>16</v>
       </c>
@@ -50459,7 +50452,7 @@
       <c r="BJ425" s="4"/>
       <c r="BM425"/>
     </row>
-    <row r="426" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A426" s="8" t="s">
         <v>16</v>
       </c>
@@ -50574,7 +50567,7 @@
       <c r="BJ426" s="4"/>
       <c r="BM426"/>
     </row>
-    <row r="427" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A427" s="8" t="s">
         <v>16</v>
       </c>
@@ -50689,7 +50682,7 @@
       <c r="BJ427" s="4"/>
       <c r="BM427"/>
     </row>
-    <row r="428" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A428" s="8" t="s">
         <v>16</v>
       </c>
@@ -50802,7 +50795,7 @@
       <c r="BJ428" s="4"/>
       <c r="BM428"/>
     </row>
-    <row r="429" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A429" s="8" t="s">
         <v>16</v>
       </c>
@@ -50915,7 +50908,7 @@
       <c r="BJ429" s="4"/>
       <c r="BM429"/>
     </row>
-    <row r="430" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A430" s="8" t="s">
         <v>16</v>
       </c>
@@ -51030,7 +51023,7 @@
       <c r="BJ430" s="4"/>
       <c r="BM430"/>
     </row>
-    <row r="431" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A431" s="8" t="s">
         <v>16</v>
       </c>
@@ -51145,7 +51138,7 @@
       <c r="BJ431" s="4"/>
       <c r="BM431"/>
     </row>
-    <row r="432" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A432" s="8" t="s">
         <v>16</v>
       </c>
@@ -51260,7 +51253,7 @@
       <c r="BJ432" s="4"/>
       <c r="BM432"/>
     </row>
-    <row r="433" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A433" s="8" t="s">
         <v>16</v>
       </c>
@@ -51375,7 +51368,7 @@
       <c r="BJ433" s="4"/>
       <c r="BM433"/>
     </row>
-    <row r="434" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A434" s="8" t="s">
         <v>16</v>
       </c>
@@ -51490,7 +51483,7 @@
       <c r="BJ434" s="4"/>
       <c r="BM434"/>
     </row>
-    <row r="435" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A435" s="8" t="s">
         <v>16</v>
       </c>
@@ -51605,7 +51598,7 @@
       <c r="BJ435" s="4"/>
       <c r="BM435"/>
     </row>
-    <row r="436" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A436" s="8" t="s">
         <v>16</v>
       </c>
@@ -51714,7 +51707,7 @@
       <c r="BJ436" s="4"/>
       <c r="BM436"/>
     </row>
-    <row r="437" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A437" s="8" t="s">
         <v>16</v>
       </c>
@@ -51823,7 +51816,7 @@
       <c r="BJ437" s="4"/>
       <c r="BM437"/>
     </row>
-    <row r="438" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A438" s="8" t="s">
         <v>16</v>
       </c>
@@ -51932,7 +51925,7 @@
       <c r="BJ438" s="4"/>
       <c r="BM438"/>
     </row>
-    <row r="439" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A439" s="8" t="s">
         <v>16</v>
       </c>
@@ -52041,7 +52034,7 @@
       <c r="BJ439" s="4"/>
       <c r="BM439"/>
     </row>
-    <row r="440" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A440" s="8" t="s">
         <v>16</v>
       </c>
@@ -52150,7 +52143,7 @@
       <c r="BJ440" s="4"/>
       <c r="BM440"/>
     </row>
-    <row r="441" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A441" s="8" t="s">
         <v>16</v>
       </c>
@@ -52259,7 +52252,7 @@
       <c r="BJ441" s="4"/>
       <c r="BM441"/>
     </row>
-    <row r="442" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A442" s="8" t="s">
         <v>16</v>
       </c>
@@ -52368,7 +52361,7 @@
       <c r="BJ442" s="4"/>
       <c r="BM442"/>
     </row>
-    <row r="443" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A443" s="8" t="s">
         <v>16</v>
       </c>
@@ -52477,7 +52470,7 @@
       <c r="BJ443" s="4"/>
       <c r="BM443"/>
     </row>
-    <row r="444" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A444" s="8" t="s">
         <v>16</v>
       </c>
@@ -52590,7 +52583,7 @@
       <c r="BJ444" s="4"/>
       <c r="BM444"/>
     </row>
-    <row r="445" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A445" s="8" t="s">
         <v>16</v>
       </c>
@@ -52703,7 +52696,7 @@
       <c r="BJ445" s="4"/>
       <c r="BM445"/>
     </row>
-    <row r="446" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A446" s="8" t="s">
         <v>16</v>
       </c>
@@ -52816,7 +52809,7 @@
       <c r="BJ446" s="4"/>
       <c r="BM446"/>
     </row>
-    <row r="447" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A447" s="8" t="s">
         <v>16</v>
       </c>
@@ -52929,7 +52922,7 @@
       <c r="BJ447" s="4"/>
       <c r="BM447"/>
     </row>
-    <row r="448" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A448" s="8" t="s">
         <v>16</v>
       </c>
@@ -53042,7 +53035,7 @@
       <c r="BJ448" s="4"/>
       <c r="BM448"/>
     </row>
-    <row r="449" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A449" s="8" t="s">
         <v>16</v>
       </c>
@@ -53155,7 +53148,7 @@
       <c r="BJ449" s="4"/>
       <c r="BM449"/>
     </row>
-    <row r="450" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A450" s="8" t="s">
         <v>16</v>
       </c>
@@ -53270,7 +53263,7 @@
       <c r="BJ450" s="4"/>
       <c r="BM450"/>
     </row>
-    <row r="451" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A451" s="8" t="s">
         <v>16</v>
       </c>
@@ -53385,7 +53378,7 @@
       <c r="BJ451" s="4"/>
       <c r="BM451"/>
     </row>
-    <row r="452" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A452" s="8" t="s">
         <v>16</v>
       </c>
@@ -53500,7 +53493,7 @@
       <c r="BJ452" s="4"/>
       <c r="BM452"/>
     </row>
-    <row r="453" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A453" s="8" t="s">
         <v>16</v>
       </c>
@@ -53615,7 +53608,7 @@
       <c r="BJ453" s="4"/>
       <c r="BM453"/>
     </row>
-    <row r="454" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A454" s="8" t="s">
         <v>16</v>
       </c>
@@ -53730,7 +53723,7 @@
       <c r="BJ454" s="4"/>
       <c r="BM454"/>
     </row>
-    <row r="455" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A455" s="8" t="s">
         <v>16</v>
       </c>
@@ -53845,7 +53838,7 @@
       <c r="BJ455" s="4"/>
       <c r="BM455"/>
     </row>
-    <row r="456" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A456" s="8" t="s">
         <v>16</v>
       </c>
@@ -53960,7 +53953,7 @@
       <c r="BJ456" s="4"/>
       <c r="BM456"/>
     </row>
-    <row r="457" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A457" s="8" t="s">
         <v>16</v>
       </c>
@@ -54075,7 +54068,7 @@
       <c r="BJ457" s="4"/>
       <c r="BM457"/>
     </row>
-    <row r="458" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A458" s="8" t="s">
         <v>16</v>
       </c>
@@ -54188,7 +54181,7 @@
       <c r="BJ458" s="4"/>
       <c r="BM458"/>
     </row>
-    <row r="459" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A459" s="8" t="s">
         <v>16</v>
       </c>
@@ -54301,7 +54294,7 @@
       <c r="BJ459" s="4"/>
       <c r="BM459"/>
     </row>
-    <row r="460" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A460" s="8" t="s">
         <v>16</v>
       </c>
@@ -54414,7 +54407,7 @@
       <c r="BJ460" s="4"/>
       <c r="BM460"/>
     </row>
-    <row r="461" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A461" s="8" t="s">
         <v>16</v>
       </c>
@@ -54527,7 +54520,7 @@
       <c r="BJ461" s="4"/>
       <c r="BM461"/>
     </row>
-    <row r="462" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A462" s="8" t="s">
         <v>16</v>
       </c>
@@ -54642,7 +54635,7 @@
       <c r="BJ462" s="4"/>
       <c r="BM462"/>
     </row>
-    <row r="463" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A463" s="8" t="s">
         <v>16</v>
       </c>
@@ -54757,7 +54750,7 @@
       <c r="BJ463" s="4"/>
       <c r="BM463"/>
     </row>
-    <row r="464" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A464" s="8" t="s">
         <v>16</v>
       </c>
@@ -54872,7 +54865,7 @@
       <c r="BJ464" s="4"/>
       <c r="BM464"/>
     </row>
-    <row r="465" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A465" s="8" t="s">
         <v>16</v>
       </c>
@@ -54987,7 +54980,7 @@
       <c r="BJ465" s="4"/>
       <c r="BM465"/>
     </row>
-    <row r="466" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A466" s="8" t="s">
         <v>16</v>
       </c>
@@ -55102,7 +55095,7 @@
       <c r="BJ466" s="4"/>
       <c r="BM466"/>
     </row>
-    <row r="467" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A467" s="8" t="s">
         <v>16</v>
       </c>
@@ -55215,7 +55208,7 @@
       <c r="BJ467" s="4"/>
       <c r="BM467"/>
     </row>
-    <row r="468" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A468" s="8" t="s">
         <v>16</v>
       </c>
@@ -55328,7 +55321,7 @@
       <c r="BJ468" s="4"/>
       <c r="BM468"/>
     </row>
-    <row r="469" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A469" s="8" t="s">
         <v>16</v>
       </c>
@@ -55441,7 +55434,7 @@
       <c r="BJ469" s="4"/>
       <c r="BM469"/>
     </row>
-    <row r="470" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A470" s="8" t="s">
         <v>16</v>
       </c>
@@ -55554,7 +55547,7 @@
       <c r="BJ470" s="4"/>
       <c r="BM470"/>
     </row>
-    <row r="471" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A471" s="8" t="s">
         <v>16</v>
       </c>
@@ -55667,7 +55660,7 @@
       <c r="BJ471" s="4"/>
       <c r="BM471"/>
     </row>
-    <row r="472" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A472" s="8" t="s">
         <v>16</v>
       </c>
@@ -55780,7 +55773,7 @@
       <c r="BJ472" s="4"/>
       <c r="BM472"/>
     </row>
-    <row r="473" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A473" s="8" t="s">
         <v>16</v>
       </c>
@@ -55893,7 +55886,7 @@
       <c r="BJ473" s="4"/>
       <c r="BM473"/>
     </row>
-    <row r="474" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A474" s="8" t="s">
         <v>16</v>
       </c>
@@ -56006,7 +55999,7 @@
       <c r="BJ474" s="4"/>
       <c r="BM474"/>
     </row>
-    <row r="475" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A475" s="8" t="s">
         <v>16</v>
       </c>
@@ -56115,7 +56108,7 @@
       <c r="BJ475" s="4"/>
       <c r="BM475"/>
     </row>
-    <row r="476" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A476" s="8" t="s">
         <v>16</v>
       </c>
@@ -56224,7 +56217,7 @@
       <c r="BJ476" s="4"/>
       <c r="BM476"/>
     </row>
-    <row r="477" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A477" s="8" t="s">
         <v>16</v>
       </c>
@@ -56333,7 +56326,7 @@
       <c r="BJ477" s="4"/>
       <c r="BM477"/>
     </row>
-    <row r="478" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A478" s="8" t="s">
         <v>16</v>
       </c>
@@ -56442,7 +56435,7 @@
       <c r="BJ478" s="4"/>
       <c r="BM478"/>
     </row>
-    <row r="479" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A479" s="8" t="s">
         <v>16</v>
       </c>
@@ -56551,7 +56544,7 @@
       <c r="BJ479" s="4"/>
       <c r="BM479"/>
     </row>
-    <row r="480" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A480" s="8" t="s">
         <v>16</v>
       </c>
@@ -56660,7 +56653,7 @@
       <c r="BJ480" s="4"/>
       <c r="BM480"/>
     </row>
-    <row r="481" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A481" s="8" t="s">
         <v>16</v>
       </c>
@@ -56769,7 +56762,7 @@
       <c r="BJ481" s="4"/>
       <c r="BM481"/>
     </row>
-    <row r="482" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A482" s="8" t="s">
         <v>16</v>
       </c>
@@ -56878,7 +56871,7 @@
       <c r="BJ482" s="4"/>
       <c r="BM482"/>
     </row>
-    <row r="483" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A483" s="8" t="s">
         <v>16</v>
       </c>
@@ -56987,7 +56980,7 @@
       <c r="BJ483" s="4"/>
       <c r="BM483"/>
     </row>
-    <row r="484" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A484" s="8" t="s">
         <v>16</v>
       </c>
@@ -57096,7 +57089,7 @@
       <c r="BJ484" s="4"/>
       <c r="BM484"/>
     </row>
-    <row r="485" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A485" s="8" t="s">
         <v>16</v>
       </c>
@@ -57205,7 +57198,7 @@
       <c r="BJ485" s="4"/>
       <c r="BM485"/>
     </row>
-    <row r="486" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A486" s="8" t="s">
         <v>16</v>
       </c>
@@ -57314,7 +57307,7 @@
       <c r="BJ486" s="4"/>
       <c r="BM486"/>
     </row>
-    <row r="487" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A487" s="8" t="s">
         <v>16</v>
       </c>
@@ -57423,7 +57416,7 @@
       <c r="BJ487" s="4"/>
       <c r="BM487"/>
     </row>
-    <row r="488" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A488" s="8" t="s">
         <v>16</v>
       </c>
@@ -57532,7 +57525,7 @@
       <c r="BJ488" s="4"/>
       <c r="BM488"/>
     </row>
-    <row r="489" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A489" s="8" t="s">
         <v>16</v>
       </c>
@@ -57641,7 +57634,7 @@
       <c r="BJ489" s="4"/>
       <c r="BM489"/>
     </row>
-    <row r="490" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A490" s="8" t="s">
         <v>16</v>
       </c>
@@ -57750,7 +57743,7 @@
       <c r="BJ490" s="4"/>
       <c r="BM490"/>
     </row>
-    <row r="491" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A491" s="8" t="s">
         <v>16</v>
       </c>
@@ -57863,7 +57856,7 @@
       <c r="BJ491" s="4"/>
       <c r="BM491"/>
     </row>
-    <row r="492" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A492" s="8" t="s">
         <v>16</v>
       </c>
@@ -57976,7 +57969,7 @@
       <c r="BJ492" s="4"/>
       <c r="BM492"/>
     </row>
-    <row r="493" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A493" s="8" t="s">
         <v>16</v>
       </c>
@@ -58089,7 +58082,7 @@
       <c r="BJ493" s="4"/>
       <c r="BM493"/>
     </row>
-    <row r="494" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A494" s="8" t="s">
         <v>16</v>
       </c>
@@ -58202,7 +58195,7 @@
       <c r="BJ494" s="4"/>
       <c r="BM494"/>
     </row>
-    <row r="495" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A495" s="8" t="s">
         <v>16</v>
       </c>
@@ -58315,7 +58308,7 @@
       <c r="BJ495" s="4"/>
       <c r="BM495"/>
     </row>
-    <row r="496" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A496" s="8" t="s">
         <v>16</v>
       </c>
@@ -58428,7 +58421,7 @@
       <c r="BJ496" s="4"/>
       <c r="BM496"/>
     </row>
-    <row r="497" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A497" s="8" t="s">
         <v>16</v>
       </c>
@@ -58543,7 +58536,7 @@
       <c r="BJ497" s="4"/>
       <c r="BM497"/>
     </row>
-    <row r="498" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A498" s="8" t="s">
         <v>16</v>
       </c>
@@ -58658,7 +58651,7 @@
       <c r="BJ498" s="4"/>
       <c r="BM498"/>
     </row>
-    <row r="499" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A499" s="8" t="s">
         <v>16</v>
       </c>
@@ -58773,7 +58766,7 @@
       <c r="BJ499" s="4"/>
       <c r="BM499"/>
     </row>
-    <row r="500" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A500" s="8" t="s">
         <v>16</v>
       </c>
@@ -58888,7 +58881,7 @@
       <c r="BJ500" s="4"/>
       <c r="BM500"/>
     </row>
-    <row r="501" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A501" s="8" t="s">
         <v>16</v>
       </c>
@@ -59004,7 +58997,7 @@
       <c r="BK501" s="8"/>
       <c r="BM501"/>
     </row>
-    <row r="502" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A502" s="8" t="s">
         <v>16</v>
       </c>
@@ -59120,7 +59113,7 @@
       <c r="BK502" s="8"/>
       <c r="BM502"/>
     </row>
-    <row r="503" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A503" s="8" t="s">
         <v>16</v>
       </c>
@@ -59236,7 +59229,7 @@
       <c r="BK503" s="8"/>
       <c r="BM503"/>
     </row>
-    <row r="504" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A504" s="8" t="s">
         <v>16</v>
       </c>
@@ -59352,7 +59345,7 @@
       <c r="BK504" s="8"/>
       <c r="BM504"/>
     </row>
-    <row r="505" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A505" s="8" t="s">
         <v>16</v>
       </c>
@@ -59468,7 +59461,7 @@
       <c r="BK505" s="8"/>
       <c r="BM505"/>
     </row>
-    <row r="506" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A506" s="8" t="s">
         <v>16</v>
       </c>
@@ -59584,7 +59577,7 @@
       <c r="BK506" s="8"/>
       <c r="BM506"/>
     </row>
-    <row r="507" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A507" s="8" t="s">
         <v>16</v>
       </c>
@@ -59700,7 +59693,7 @@
       <c r="BK507" s="8"/>
       <c r="BM507"/>
     </row>
-    <row r="508" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A508" s="8" t="s">
         <v>16</v>
       </c>
@@ -59811,7 +59804,7 @@
       <c r="BK508" s="8"/>
       <c r="BM508"/>
     </row>
-    <row r="509" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A509" s="8" t="s">
         <v>16</v>
       </c>
@@ -59922,7 +59915,7 @@
       <c r="BK509" s="8"/>
       <c r="BM509"/>
     </row>
-    <row r="510" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A510" s="8" t="s">
         <v>16</v>
       </c>
@@ -60033,7 +60026,7 @@
       <c r="BK510" s="8"/>
       <c r="BM510"/>
     </row>
-    <row r="511" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A511" s="8" t="s">
         <v>16</v>
       </c>
@@ -60144,7 +60137,7 @@
       <c r="BK511" s="8"/>
       <c r="BM511"/>
     </row>
-    <row r="512" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A512" s="8" t="s">
         <v>16</v>
       </c>
@@ -60255,7 +60248,7 @@
       <c r="BK512" s="8"/>
       <c r="BM512"/>
     </row>
-    <row r="513" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A513" s="8" t="s">
         <v>16</v>
       </c>
@@ -60366,7 +60359,7 @@
       <c r="BK513" s="8"/>
       <c r="BM513"/>
     </row>
-    <row r="514" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A514" s="8" t="s">
         <v>16</v>
       </c>
@@ -60477,7 +60470,7 @@
       <c r="BK514" s="8"/>
       <c r="BM514"/>
     </row>
-    <row r="515" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A515" s="8" t="s">
         <v>16</v>
       </c>
@@ -60588,7 +60581,7 @@
       <c r="BK515" s="8"/>
       <c r="BM515"/>
     </row>
-    <row r="516" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A516" s="8" t="s">
         <v>16</v>
       </c>
@@ -60699,7 +60692,7 @@
       <c r="BK516" s="8"/>
       <c r="BM516"/>
     </row>
-    <row r="517" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A517" s="8" t="s">
         <v>16</v>
       </c>
@@ -60810,7 +60803,7 @@
       <c r="BK517" s="8"/>
       <c r="BM517"/>
     </row>
-    <row r="518" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A518" s="8" t="s">
         <v>16</v>
       </c>
@@ -60921,7 +60914,7 @@
       <c r="BK518" s="8"/>
       <c r="BM518"/>
     </row>
-    <row r="519" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A519" s="8" t="s">
         <v>16</v>
       </c>
@@ -61032,7 +61025,7 @@
       <c r="BK519" s="8"/>
       <c r="BM519"/>
     </row>
-    <row r="520" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A520" s="8" t="s">
         <v>16</v>
       </c>
@@ -61144,7 +61137,7 @@
       <c r="BK520" s="8"/>
       <c r="BM520"/>
     </row>
-    <row r="521" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A521" s="8" t="s">
         <v>16</v>
       </c>
@@ -61256,7 +61249,7 @@
       <c r="BK521" s="8"/>
       <c r="BM521"/>
     </row>
-    <row r="522" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A522" s="8" t="s">
         <v>16</v>
       </c>
@@ -61368,7 +61361,7 @@
       <c r="BK522" s="8"/>
       <c r="BM522"/>
     </row>
-    <row r="523" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A523" s="8" t="s">
         <v>16</v>
       </c>
@@ -61480,7 +61473,7 @@
       <c r="BK523" s="8"/>
       <c r="BM523"/>
     </row>
-    <row r="524" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A524" s="8" t="s">
         <v>16</v>
       </c>
@@ -61592,7 +61585,7 @@
       <c r="BK524" s="8"/>
       <c r="BM524"/>
     </row>
-    <row r="525" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A525" s="8" t="s">
         <v>16</v>
       </c>
@@ -61704,7 +61697,7 @@
       <c r="BK525" s="8"/>
       <c r="BM525"/>
     </row>
-    <row r="526" spans="1:65" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:65" ht="72" x14ac:dyDescent="0.3">
       <c r="A526" s="8" t="s">
         <v>16</v>
       </c>
@@ -61816,7 +61809,7 @@
       <c r="BK526" s="8"/>
       <c r="BM526"/>
     </row>
-    <row r="527" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A527" s="8" t="s">
         <v>16</v>
       </c>
@@ -61928,7 +61921,7 @@
       <c r="BK527" s="8"/>
       <c r="BM527"/>
     </row>
-    <row r="528" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A528" s="8" t="s">
         <v>16</v>
       </c>
@@ -62035,7 +62028,7 @@
       <c r="BK528" s="8"/>
       <c r="BM528"/>
     </row>
-    <row r="529" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A529" s="8" t="s">
         <v>16</v>
       </c>
@@ -62148,7 +62141,7 @@
       <c r="BK529" s="8"/>
       <c r="BM529"/>
     </row>
-    <row r="530" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A530" s="8" t="s">
         <v>16</v>
       </c>
@@ -62261,7 +62254,7 @@
       <c r="BK530" s="8"/>
       <c r="BM530"/>
     </row>
-    <row r="531" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A531" s="8" t="s">
         <v>16</v>
       </c>
@@ -62374,7 +62367,7 @@
       <c r="BK531" s="8"/>
       <c r="BM531"/>
     </row>
-    <row r="532" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A532" s="8" t="s">
         <v>16</v>
       </c>
@@ -62487,7 +62480,7 @@
       <c r="BK532" s="8"/>
       <c r="BM532"/>
     </row>
-    <row r="533" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A533" s="8" t="s">
         <v>16</v>
       </c>
@@ -62600,7 +62593,7 @@
       <c r="BK533" s="8"/>
       <c r="BM533"/>
     </row>
-    <row r="534" spans="1:65" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A534" s="8" t="s">
         <v>16</v>
       </c>
@@ -62713,7 +62706,7 @@
       <c r="BK534" s="8"/>
       <c r="BM534"/>
     </row>
-    <row r="535" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A535" s="8" t="s">
         <v>16</v>
       </c>
@@ -62824,7 +62817,7 @@
       <c r="BK535" s="8"/>
       <c r="BM535"/>
     </row>
-    <row r="536" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A536" s="8" t="s">
         <v>16</v>
       </c>
@@ -62935,7 +62928,7 @@
       <c r="BK536" s="8"/>
       <c r="BM536"/>
     </row>
-    <row r="537" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A537" s="8" t="s">
         <v>16</v>
       </c>
@@ -63046,7 +63039,7 @@
       <c r="BK537" s="8"/>
       <c r="BM537"/>
     </row>
-    <row r="538" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A538" s="8" t="s">
         <v>16</v>
       </c>
@@ -63157,7 +63150,7 @@
       <c r="BK538" s="8"/>
       <c r="BM538"/>
     </row>
-    <row r="539" spans="1:65" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A539" s="8" t="s">
         <v>16</v>
       </c>
@@ -63268,7 +63261,7 @@
       <c r="BK539" s="8"/>
       <c r="BM539"/>
     </row>
-    <row r="540" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A540" s="8" t="s">
         <v>16</v>
       </c>
@@ -63381,7 +63374,7 @@
       <c r="BK540" s="8"/>
       <c r="BM540"/>
     </row>
-    <row r="541" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A541" s="8" t="s">
         <v>16</v>
       </c>
@@ -63494,7 +63487,7 @@
       <c r="BK541" s="8"/>
       <c r="BM541"/>
     </row>
-    <row r="542" spans="1:65" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:65" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A542" s="8" t="s">
         <v>16</v>
       </c>

--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F18522-42B1-4272-8D48-DC8F6BC16504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91E6A9B-7CE1-42F5-B174-93F6911C10B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5099" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5261" uniqueCount="785">
   <si>
     <t>Squad</t>
   </si>
@@ -2406,6 +2406,42 @@
   </si>
   <si>
     <t>https://youtu.be/OhasA8Jhlbk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaron Gate </t>
+  </si>
+  <si>
+    <t>Baseline Pos 1</t>
+  </si>
+  <si>
+    <t>B3_T1_P05prn6</t>
+  </si>
+  <si>
+    <t>Pos J - FW</t>
+  </si>
+  <si>
+    <t>Pos E -FW</t>
+  </si>
+  <si>
+    <t>Tom sexton</t>
+  </si>
+  <si>
+    <t>B5_VP</t>
+  </si>
+  <si>
+    <t>Pos G - FW</t>
+  </si>
+  <si>
+    <t>Pos D - FW</t>
+  </si>
+  <si>
+    <t>Pos H - FW</t>
+  </si>
+  <si>
+    <t>Pos A - FW</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
 </sst>
 </file>
@@ -2538,7 +2574,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2590,6 +2626,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2665,7 +2707,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3046,110 +3088,17 @@
     <xf numFmtId="14" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3163,9 +3112,6 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3174,6 +3120,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3926,7 +3875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:BM561"/>
+  <dimension ref="A1:BM584"/>
   <sheetFormatPr defaultColWidth="15.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" style="2" bestFit="1" customWidth="1"/>
@@ -3934,8 +3883,8 @@
     <col min="3" max="3" width="12.21875" style="90" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="61.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="56.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" customWidth="1"/>
+    <col min="7" max="7" width="14" style="8" customWidth="1"/>
     <col min="8" max="8" width="26.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.6640625" style="8" customWidth="1"/>
@@ -5611,13 +5560,13 @@
       <c r="BD14" s="8">
         <v>23.2</v>
       </c>
-      <c r="BE14" s="157">
+      <c r="BE14" s="82">
         <v>1013</v>
       </c>
       <c r="BF14" s="92">
         <v>0.38</v>
       </c>
-      <c r="BG14" s="157">
+      <c r="BG14" s="82">
         <v>1.1859999999999999</v>
       </c>
       <c r="BH14" s="8">
@@ -6933,13 +6882,13 @@
       <c r="BD26" s="8">
         <v>23.6</v>
       </c>
-      <c r="BE26" s="157">
+      <c r="BE26" s="82">
         <v>1012</v>
       </c>
       <c r="BF26" s="92">
         <v>0.49</v>
       </c>
-      <c r="BG26" s="157">
+      <c r="BG26" s="82">
         <v>1.1819999999999999</v>
       </c>
       <c r="BH26" s="8">
@@ -8954,7 +8903,7 @@
         <v>2.0999999999999999E-3</v>
       </c>
       <c r="BC44" s="11"/>
-      <c r="BD44" s="155" t="s">
+      <c r="BD44" s="130" t="s">
         <v>102</v>
       </c>
       <c r="BE44" s="49">
@@ -9069,7 +9018,7 @@
         <v>2.0999999999999999E-3</v>
       </c>
       <c r="BC45" s="11"/>
-      <c r="BD45" s="155" t="s">
+      <c r="BD45" s="130" t="s">
         <v>104</v>
       </c>
       <c r="BE45" s="49">
@@ -13784,7 +13733,7 @@
       <c r="BF87" s="92">
         <v>0.63</v>
       </c>
-      <c r="BG87" s="157">
+      <c r="BG87" s="82">
         <v>1.1679999999999999</v>
       </c>
       <c r="BH87" s="8">
@@ -13899,7 +13848,7 @@
       <c r="BF88" s="92">
         <v>0.63</v>
       </c>
-      <c r="BG88" s="157">
+      <c r="BG88" s="82">
         <v>1.1679999999999999</v>
       </c>
       <c r="BH88" s="8">
@@ -14014,7 +13963,7 @@
       <c r="BF89" s="92">
         <v>0.62</v>
       </c>
-      <c r="BG89" s="157">
+      <c r="BG89" s="82">
         <v>1.165</v>
       </c>
       <c r="BH89" s="8">
@@ -14129,7 +14078,7 @@
       <c r="BF90" s="92">
         <v>0.62</v>
       </c>
-      <c r="BG90" s="157">
+      <c r="BG90" s="82">
         <v>1.165</v>
       </c>
       <c r="BH90" s="8">
@@ -14236,13 +14185,13 @@
       <c r="BD91" s="8">
         <v>22.9</v>
       </c>
-      <c r="BE91" s="157">
+      <c r="BE91" s="82">
         <v>1000</v>
       </c>
       <c r="BF91" s="92">
         <v>0.63</v>
       </c>
-      <c r="BG91" s="157">
+      <c r="BG91" s="82">
         <v>1.169</v>
       </c>
       <c r="BH91" s="8">
@@ -14349,13 +14298,13 @@
       <c r="BD92" s="8">
         <v>23.2</v>
       </c>
-      <c r="BE92" s="157">
+      <c r="BE92" s="82">
         <v>1000</v>
       </c>
       <c r="BF92" s="92">
         <v>0.63</v>
       </c>
-      <c r="BG92" s="157">
+      <c r="BG92" s="82">
         <v>1.167</v>
       </c>
       <c r="BH92" s="8">
@@ -14462,13 +14411,13 @@
       <c r="BD93" s="8">
         <v>23.2</v>
       </c>
-      <c r="BE93" s="157">
+      <c r="BE93" s="82">
         <v>1000</v>
       </c>
       <c r="BF93" s="92">
         <v>0.63</v>
       </c>
-      <c r="BG93" s="157">
+      <c r="BG93" s="82">
         <v>1.167</v>
       </c>
       <c r="BH93" s="8">
@@ -14575,13 +14524,13 @@
       <c r="BD94" s="8">
         <v>23.1</v>
       </c>
-      <c r="BE94" s="157">
+      <c r="BE94" s="82">
         <v>1000</v>
       </c>
       <c r="BF94" s="92">
         <v>0.63</v>
       </c>
-      <c r="BG94" s="157">
+      <c r="BG94" s="82">
         <v>1.1679999999999999</v>
       </c>
       <c r="BH94" s="8">
@@ -21624,10 +21573,10 @@
       <c r="M158" s="8">
         <v>0.20300000000000001</v>
       </c>
-      <c r="N158" s="140">
+      <c r="N158" s="128">
         <v>1.9400000000000001E-2</v>
       </c>
-      <c r="O158" s="142">
+      <c r="O158" s="129">
         <v>10</v>
       </c>
       <c r="P158" s="8">
@@ -24704,7 +24653,7 @@
       <c r="BE185" s="18">
         <v>1008</v>
       </c>
-      <c r="BF185" s="163">
+      <c r="BF185" s="132">
         <v>0.63</v>
       </c>
       <c r="BG185" s="48">
@@ -26653,7 +26602,7 @@
       <c r="BE202" s="80">
         <v>1001</v>
       </c>
-      <c r="BF202" s="164">
+      <c r="BF202" s="133">
         <v>0.56999999999999995</v>
       </c>
       <c r="BG202" s="81">
@@ -26776,7 +26725,7 @@
       <c r="BE203" s="80">
         <v>1001</v>
       </c>
-      <c r="BF203" s="164">
+      <c r="BF203" s="133">
         <v>0.56999999999999995</v>
       </c>
       <c r="BG203" s="81">
@@ -26899,7 +26848,7 @@
       <c r="BE204" s="80">
         <v>1001</v>
       </c>
-      <c r="BF204" s="164">
+      <c r="BF204" s="133">
         <v>0.56000000000000005</v>
       </c>
       <c r="BG204" s="81">
@@ -27022,7 +26971,7 @@
       <c r="BE205" s="80">
         <v>1001</v>
       </c>
-      <c r="BF205" s="164">
+      <c r="BF205" s="133">
         <v>0.56000000000000005</v>
       </c>
       <c r="BG205" s="81">
@@ -27145,7 +27094,7 @@
       <c r="BE206" s="80">
         <v>1001</v>
       </c>
-      <c r="BF206" s="164">
+      <c r="BF206" s="133">
         <v>0.56000000000000005</v>
       </c>
       <c r="BG206" s="81">
@@ -27268,7 +27217,7 @@
       <c r="BE207" s="80">
         <v>1000</v>
       </c>
-      <c r="BF207" s="164">
+      <c r="BF207" s="133">
         <v>0.54</v>
       </c>
       <c r="BG207" s="81">
@@ -27387,10 +27336,10 @@
       <c r="BE208" s="46">
         <v>1001</v>
       </c>
-      <c r="BF208" s="166">
+      <c r="BF208" s="135">
         <v>0.57999999999999996</v>
       </c>
-      <c r="BG208" s="168">
+      <c r="BG208" s="136">
         <v>1.161</v>
       </c>
       <c r="BH208" s="8">
@@ -27506,7 +27455,7 @@
       <c r="BE209" s="80">
         <v>1001</v>
       </c>
-      <c r="BF209" s="164">
+      <c r="BF209" s="133">
         <v>0.57999999999999996</v>
       </c>
       <c r="BG209" s="81">
@@ -27625,7 +27574,7 @@
       <c r="BE210" s="80">
         <v>1001</v>
       </c>
-      <c r="BF210" s="164">
+      <c r="BF210" s="133">
         <v>0.57999999999999996</v>
       </c>
       <c r="BG210" s="81">
@@ -27744,7 +27693,7 @@
       <c r="BE211" s="80">
         <v>1001</v>
       </c>
-      <c r="BF211" s="164">
+      <c r="BF211" s="133">
         <v>0.56000000000000005</v>
       </c>
       <c r="BG211" s="81">
@@ -27863,7 +27812,7 @@
       <c r="BE212" s="80">
         <v>1001</v>
       </c>
-      <c r="BF212" s="164">
+      <c r="BF212" s="133">
         <v>0.56000000000000005</v>
       </c>
       <c r="BG212" s="81">
@@ -27982,10 +27931,10 @@
       <c r="BE213" s="46">
         <v>1000</v>
       </c>
-      <c r="BF213" s="166">
+      <c r="BF213" s="135">
         <v>0.55000000000000004</v>
       </c>
-      <c r="BG213" s="168">
+      <c r="BG213" s="136">
         <v>1.1559999999999999</v>
       </c>
       <c r="BH213" s="8">
@@ -28101,7 +28050,7 @@
       <c r="BE214" s="80">
         <v>1000</v>
       </c>
-      <c r="BF214" s="164">
+      <c r="BF214" s="133">
         <v>0.54</v>
       </c>
       <c r="BG214" s="81">
@@ -28219,11 +28168,11 @@
       <c r="BD215" s="16">
         <v>26.9</v>
       </c>
-      <c r="BE215" s="152">
+      <c r="BE215" s="16">
         <v>1009</v>
       </c>
       <c r="BF215" s="16"/>
-      <c r="BG215" s="152">
+      <c r="BG215" s="16">
         <v>1.1639999999999999</v>
       </c>
       <c r="BH215" s="8">
@@ -28334,7 +28283,7 @@
         <v>1009</v>
       </c>
       <c r="BF216" s="46"/>
-      <c r="BG216" s="152">
+      <c r="BG216" s="16">
         <v>1.1639999999999999</v>
       </c>
       <c r="BH216" s="8">
@@ -28445,7 +28394,7 @@
         <v>1009</v>
       </c>
       <c r="BF217" s="33"/>
-      <c r="BG217" s="128">
+      <c r="BG217" s="8">
         <v>1.1639999999999999</v>
       </c>
       <c r="BH217" s="8">
@@ -28556,7 +28505,7 @@
         <v>1009</v>
       </c>
       <c r="BF218" s="33"/>
-      <c r="BG218" s="128">
+      <c r="BG218" s="8">
         <v>1.1639999999999999</v>
       </c>
       <c r="BH218" s="8">
@@ -28667,7 +28616,7 @@
         <v>1009</v>
       </c>
       <c r="BF219" s="33"/>
-      <c r="BG219" s="128">
+      <c r="BG219" s="8">
         <v>1.1639999999999999</v>
       </c>
       <c r="BH219" s="8">
@@ -29390,7 +29339,7 @@
       <c r="BE225" s="18">
         <v>1008</v>
       </c>
-      <c r="BF225" s="163">
+      <c r="BF225" s="132">
         <v>0.43</v>
       </c>
       <c r="BG225" s="48">
@@ -29515,7 +29464,7 @@
       <c r="BE226" s="18">
         <v>1008</v>
       </c>
-      <c r="BF226" s="163">
+      <c r="BF226" s="132">
         <v>0.43</v>
       </c>
       <c r="BG226" s="48">
@@ -30364,7 +30313,7 @@
       <c r="BM233"/>
     </row>
     <row r="234" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A234" s="128" t="s">
+      <c r="A234" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B234" s="8" t="s">
@@ -30373,37 +30322,37 @@
       <c r="C234" s="4">
         <v>45021</v>
       </c>
-      <c r="D234" s="128">
+      <c r="D234" s="8">
         <v>8</v>
       </c>
       <c r="E234" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="F234" s="134"/>
-      <c r="G234" s="134"/>
-      <c r="H234" s="134"/>
-      <c r="I234" s="134"/>
-      <c r="J234" s="134"/>
-      <c r="K234" s="134"/>
-      <c r="L234" s="136">
+      <c r="F234" s="10"/>
+      <c r="G234" s="10"/>
+      <c r="H234" s="10"/>
+      <c r="I234" s="10"/>
+      <c r="J234" s="10"/>
+      <c r="K234" s="10"/>
+      <c r="L234" s="55">
         <v>0.17299999999999999</v>
       </c>
       <c r="M234" s="22">
         <v>0.1822</v>
       </c>
-      <c r="N234" s="141">
+      <c r="N234" s="35">
         <v>3.7100000000000001E-2</v>
       </c>
-      <c r="O234" s="128">
+      <c r="O234" s="8">
         <v>23</v>
       </c>
-      <c r="P234" s="144">
+      <c r="P234" s="36">
         <v>57.8</v>
       </c>
-      <c r="Q234" s="128">
+      <c r="Q234" s="8">
         <v>452</v>
       </c>
-      <c r="R234" s="148">
+      <c r="R234" s="39">
         <v>1507.6</v>
       </c>
       <c r="S234" s="5" t="s">
@@ -30412,53 +30361,53 @@
       <c r="T234" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="U234" s="129"/>
+      <c r="U234" s="5"/>
       <c r="V234" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="W234" s="129"/>
+      <c r="W234" s="5"/>
       <c r="X234" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="Y234" s="128" t="s">
+      <c r="Y234" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="Z234" s="128"/>
-      <c r="AA234" s="128"/>
-      <c r="AB234" s="128"/>
-      <c r="AC234" s="128"/>
-      <c r="AD234" s="128"/>
-      <c r="AE234" s="128"/>
-      <c r="AF234" s="128"/>
-      <c r="AG234" s="128"/>
-      <c r="AH234" s="128"/>
-      <c r="AI234" s="128"/>
-      <c r="AJ234" s="128"/>
-      <c r="AK234" s="128"/>
-      <c r="AL234" s="128"/>
-      <c r="AM234" s="128"/>
-      <c r="AN234" s="128"/>
-      <c r="AO234" s="128"/>
-      <c r="AP234" s="128"/>
-      <c r="AQ234" s="128"/>
-      <c r="AR234" s="128"/>
-      <c r="AS234" s="128"/>
-      <c r="AT234" s="128"/>
-      <c r="AU234" s="128"/>
-      <c r="AV234" s="128"/>
-      <c r="AW234" s="129"/>
-      <c r="AX234" s="153"/>
-      <c r="AY234" s="153"/>
+      <c r="Z234" s="8"/>
+      <c r="AA234" s="8"/>
+      <c r="AB234" s="8"/>
+      <c r="AC234" s="8"/>
+      <c r="AD234" s="8"/>
+      <c r="AE234" s="8"/>
+      <c r="AF234" s="8"/>
+      <c r="AG234" s="8"/>
+      <c r="AH234" s="8"/>
+      <c r="AI234" s="8"/>
+      <c r="AJ234" s="8"/>
+      <c r="AK234" s="8"/>
+      <c r="AL234" s="8"/>
+      <c r="AM234" s="8"/>
+      <c r="AN234" s="8"/>
+      <c r="AO234" s="8"/>
+      <c r="AP234" s="8"/>
+      <c r="AQ234" s="8"/>
+      <c r="AR234" s="8"/>
+      <c r="AS234" s="8"/>
+      <c r="AT234" s="8"/>
+      <c r="AU234" s="8"/>
+      <c r="AV234" s="8"/>
+      <c r="AW234" s="5"/>
+      <c r="AX234" s="3"/>
+      <c r="AY234" s="3"/>
       <c r="AZ234" s="8">
         <v>200</v>
       </c>
-      <c r="BA234" s="128">
+      <c r="BA234" s="8">
         <v>111.6</v>
       </c>
-      <c r="BB234" s="128">
+      <c r="BB234" s="8">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="BC234" s="128">
+      <c r="BC234" s="8">
         <v>98.5</v>
       </c>
       <c r="BD234" s="32" t="s">
@@ -31179,101 +31128,101 @@
       <c r="BM240"/>
     </row>
     <row r="241" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A241" s="128" t="s">
+      <c r="A241" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B241" s="128" t="s">
+      <c r="B241" s="8" t="s">
         <v>168</v>
       </c>
       <c r="C241" s="4">
         <v>45030</v>
       </c>
-      <c r="D241" s="128">
+      <c r="D241" s="8">
         <v>5</v>
       </c>
       <c r="E241" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="F241" s="134"/>
-      <c r="G241" s="134"/>
-      <c r="H241" s="134"/>
-      <c r="I241" s="134"/>
-      <c r="J241" s="134"/>
-      <c r="K241" s="134"/>
-      <c r="L241" s="136">
+      <c r="F241" s="10"/>
+      <c r="G241" s="10"/>
+      <c r="H241" s="10"/>
+      <c r="I241" s="10"/>
+      <c r="J241" s="10"/>
+      <c r="K241" s="10"/>
+      <c r="L241" s="55">
         <v>0.17699999999999999</v>
       </c>
       <c r="M241" s="22">
         <v>0.18049999999999999</v>
       </c>
-      <c r="N241" s="141">
+      <c r="N241" s="35">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="O241" s="128">
+      <c r="O241" s="8">
         <v>4</v>
       </c>
-      <c r="P241" s="128">
+      <c r="P241" s="8">
         <v>57.2</v>
       </c>
-      <c r="Q241" s="128">
+      <c r="Q241" s="8">
         <v>443</v>
       </c>
-      <c r="R241" s="149">
+      <c r="R241" s="38">
         <v>1509.9</v>
       </c>
-      <c r="S241" s="128" t="s">
+      <c r="S241" s="8" t="s">
         <v>20</v>
       </c>
       <c r="T241" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="U241" s="129"/>
+      <c r="U241" s="5"/>
       <c r="V241" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="W241" s="129"/>
-      <c r="X241" s="149" t="s">
+      <c r="W241" s="5"/>
+      <c r="X241" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="Y241" s="149" t="s">
+      <c r="Y241" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="Z241" s="149"/>
-      <c r="AA241" s="149"/>
-      <c r="AB241" s="149"/>
-      <c r="AC241" s="149"/>
-      <c r="AD241" s="149"/>
-      <c r="AE241" s="149"/>
-      <c r="AF241" s="149"/>
-      <c r="AG241" s="149"/>
-      <c r="AH241" s="149"/>
-      <c r="AI241" s="149"/>
-      <c r="AJ241" s="149"/>
-      <c r="AK241" s="149"/>
-      <c r="AL241" s="149"/>
-      <c r="AM241" s="149"/>
-      <c r="AN241" s="149"/>
-      <c r="AO241" s="149"/>
-      <c r="AP241" s="149"/>
-      <c r="AQ241" s="149"/>
-      <c r="AR241" s="149"/>
-      <c r="AS241" s="149"/>
-      <c r="AT241" s="149"/>
-      <c r="AU241" s="149"/>
-      <c r="AV241" s="149"/>
-      <c r="AW241" s="129"/>
-      <c r="AX241" s="153"/>
-      <c r="AY241" s="153"/>
-      <c r="AZ241" s="128">
+      <c r="Z241" s="38"/>
+      <c r="AA241" s="38"/>
+      <c r="AB241" s="38"/>
+      <c r="AC241" s="38"/>
+      <c r="AD241" s="38"/>
+      <c r="AE241" s="38"/>
+      <c r="AF241" s="38"/>
+      <c r="AG241" s="38"/>
+      <c r="AH241" s="38"/>
+      <c r="AI241" s="38"/>
+      <c r="AJ241" s="38"/>
+      <c r="AK241" s="38"/>
+      <c r="AL241" s="38"/>
+      <c r="AM241" s="38"/>
+      <c r="AN241" s="38"/>
+      <c r="AO241" s="38"/>
+      <c r="AP241" s="38"/>
+      <c r="AQ241" s="38"/>
+      <c r="AR241" s="38"/>
+      <c r="AS241" s="38"/>
+      <c r="AT241" s="38"/>
+      <c r="AU241" s="38"/>
+      <c r="AV241" s="38"/>
+      <c r="AW241" s="5"/>
+      <c r="AX241" s="3"/>
+      <c r="AY241" s="3"/>
+      <c r="AZ241" s="8">
         <v>200</v>
       </c>
-      <c r="BA241" s="128">
+      <c r="BA241" s="8">
         <v>111.6</v>
       </c>
-      <c r="BB241" s="128">
+      <c r="BB241" s="8">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="BC241" s="128"/>
+      <c r="BC241" s="8"/>
       <c r="BD241" s="32" t="s">
         <v>182</v>
       </c>
@@ -31436,10 +31385,10 @@
       <c r="M243" s="22">
         <v>0.1837</v>
       </c>
-      <c r="N243" s="140">
+      <c r="N243" s="128">
         <v>2.3E-2</v>
       </c>
-      <c r="O243" s="142">
+      <c r="O243" s="129">
         <v>15</v>
       </c>
       <c r="P243" s="33">
@@ -31510,7 +31459,7 @@
       <c r="BE243" s="49">
         <v>1017</v>
       </c>
-      <c r="BF243" s="165">
+      <c r="BF243" s="134">
         <v>0.53</v>
       </c>
       <c r="BG243" s="82">
@@ -31625,7 +31574,7 @@
       <c r="BE244" s="49">
         <v>1017</v>
       </c>
-      <c r="BF244" s="165">
+      <c r="BF244" s="134">
         <v>0.53</v>
       </c>
       <c r="BG244" s="82">
@@ -31740,7 +31689,7 @@
       <c r="BE245" s="49">
         <v>1017</v>
       </c>
-      <c r="BF245" s="165">
+      <c r="BF245" s="134">
         <v>0.53</v>
       </c>
       <c r="BG245" s="82">
@@ -31855,7 +31804,7 @@
       <c r="BE246" s="49">
         <v>1016</v>
       </c>
-      <c r="BF246" s="165">
+      <c r="BF246" s="134">
         <v>0.53</v>
       </c>
       <c r="BG246" s="82">
@@ -31972,10 +31921,10 @@
       <c r="BE247" s="49">
         <v>1014</v>
       </c>
-      <c r="BF247" s="165">
+      <c r="BF247" s="134">
         <v>0.64</v>
       </c>
-      <c r="BG247" s="157">
+      <c r="BG247" s="82">
         <v>1.175</v>
       </c>
       <c r="BH247" s="8">
@@ -32087,10 +32036,10 @@
       <c r="BE248" s="49">
         <v>1014</v>
       </c>
-      <c r="BF248" s="165">
+      <c r="BF248" s="134">
         <v>0.64</v>
       </c>
-      <c r="BG248" s="157">
+      <c r="BG248" s="82">
         <v>1.175</v>
       </c>
       <c r="BH248" s="8">
@@ -32202,7 +32151,7 @@
       <c r="BE249" s="49">
         <v>1014</v>
       </c>
-      <c r="BF249" s="165">
+      <c r="BF249" s="134">
         <v>0.61</v>
       </c>
       <c r="BG249" s="82">
@@ -32317,7 +32266,7 @@
       <c r="BE250" s="49">
         <v>1014</v>
       </c>
-      <c r="BF250" s="165">
+      <c r="BF250" s="134">
         <v>0.61</v>
       </c>
       <c r="BG250" s="82">
@@ -32432,7 +32381,7 @@
       <c r="BE251" s="49">
         <v>1014</v>
       </c>
-      <c r="BF251" s="165">
+      <c r="BF251" s="134">
         <v>0.61</v>
       </c>
       <c r="BG251" s="82">
@@ -32547,7 +32496,7 @@
       <c r="BE252" s="49">
         <v>1014</v>
       </c>
-      <c r="BF252" s="165">
+      <c r="BF252" s="134">
         <v>0.61</v>
       </c>
       <c r="BG252" s="82">
@@ -32662,7 +32611,7 @@
       <c r="BE253" s="49">
         <v>1014</v>
       </c>
-      <c r="BF253" s="165">
+      <c r="BF253" s="134">
         <v>0.61</v>
       </c>
       <c r="BG253" s="82">
@@ -32777,7 +32726,7 @@
       <c r="BE254" s="49">
         <v>1014</v>
       </c>
-      <c r="BF254" s="165">
+      <c r="BF254" s="134">
         <v>0.61</v>
       </c>
       <c r="BG254" s="82">
@@ -32893,7 +32842,7 @@
         <v>1016</v>
       </c>
       <c r="BF255" s="49"/>
-      <c r="BG255" s="157"/>
+      <c r="BG255" s="82"/>
       <c r="BH255" s="8">
         <v>2096</v>
       </c>
@@ -33443,97 +33392,95 @@
       <c r="BM260"/>
     </row>
     <row r="261" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A261" s="128" t="s">
+      <c r="A261" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="B261" s="128" t="s">
+      <c r="B261" s="8" t="s">
         <v>321</v>
       </c>
       <c r="C261" s="4">
         <v>45061</v>
       </c>
-      <c r="D261" s="130">
+      <c r="D261" s="20">
         <v>2</v>
       </c>
       <c r="E261" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="F261" s="134"/>
-      <c r="G261" s="134"/>
-      <c r="H261" s="128"/>
-      <c r="I261" s="128"/>
-      <c r="J261" s="128"/>
-      <c r="K261" s="134"/>
-      <c r="L261" s="135"/>
+      <c r="F261" s="10"/>
+      <c r="G261" s="10"/>
+      <c r="H261" s="8"/>
+      <c r="K261" s="10"/>
+      <c r="L261" s="25"/>
       <c r="M261" s="26">
         <v>0.19439999999999999</v>
       </c>
-      <c r="N261" s="134"/>
-      <c r="O261" s="134"/>
-      <c r="P261" s="134"/>
-      <c r="Q261" s="134"/>
-      <c r="R261" s="134"/>
+      <c r="N261" s="10"/>
+      <c r="O261" s="10"/>
+      <c r="P261" s="10"/>
+      <c r="Q261" s="10"/>
+      <c r="R261" s="10"/>
       <c r="S261" s="8" t="s">
         <v>359</v>
       </c>
       <c r="T261" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="U261" s="129"/>
+      <c r="U261" s="5"/>
       <c r="V261" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="W261" s="129" t="s">
+      <c r="W261" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="X261" s="129" t="s">
+      <c r="X261" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="Y261" s="129" t="s">
+      <c r="Y261" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="Z261" s="129"/>
-      <c r="AA261" s="129"/>
-      <c r="AB261" s="129"/>
-      <c r="AC261" s="129"/>
-      <c r="AD261" s="129"/>
-      <c r="AE261" s="129"/>
-      <c r="AF261" s="129"/>
-      <c r="AG261" s="129"/>
-      <c r="AH261" s="129"/>
-      <c r="AI261" s="129"/>
-      <c r="AJ261" s="129"/>
-      <c r="AK261" s="129"/>
-      <c r="AL261" s="129"/>
-      <c r="AM261" s="129"/>
-      <c r="AN261" s="129"/>
-      <c r="AO261" s="129"/>
-      <c r="AP261" s="129"/>
-      <c r="AQ261" s="129"/>
-      <c r="AR261" s="129"/>
-      <c r="AS261" s="129"/>
-      <c r="AT261" s="129"/>
-      <c r="AU261" s="129"/>
-      <c r="AV261" s="129"/>
-      <c r="AW261" s="128">
+      <c r="Z261" s="5"/>
+      <c r="AA261" s="5"/>
+      <c r="AB261" s="5"/>
+      <c r="AC261" s="5"/>
+      <c r="AD261" s="5"/>
+      <c r="AE261" s="5"/>
+      <c r="AF261" s="5"/>
+      <c r="AG261" s="5"/>
+      <c r="AH261" s="5"/>
+      <c r="AI261" s="5"/>
+      <c r="AJ261" s="5"/>
+      <c r="AK261" s="5"/>
+      <c r="AL261" s="5"/>
+      <c r="AM261" s="5"/>
+      <c r="AN261" s="5"/>
+      <c r="AO261" s="5"/>
+      <c r="AP261" s="5"/>
+      <c r="AQ261" s="5"/>
+      <c r="AR261" s="5"/>
+      <c r="AS261" s="5"/>
+      <c r="AT261" s="5"/>
+      <c r="AU261" s="5"/>
+      <c r="AV261" s="5"/>
+      <c r="AW261" s="8">
         <v>66.7</v>
       </c>
-      <c r="AX261" s="128">
+      <c r="AX261" s="8">
         <v>8.3000000000000007</v>
       </c>
-      <c r="AY261" s="128">
+      <c r="AY261" s="8">
         <v>75.2</v>
       </c>
-      <c r="AZ261" s="128">
+      <c r="AZ261" s="8">
         <v>200</v>
       </c>
-      <c r="BA261" s="128">
+      <c r="BA261" s="8">
         <v>104.6</v>
       </c>
-      <c r="BB261" s="128">
+      <c r="BB261" s="8">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="BC261" s="128">
+      <c r="BC261" s="8">
         <v>0.99739999999999995</v>
       </c>
       <c r="BD261" s="32" t="s">
@@ -33752,7 +33699,7 @@
       <c r="BC263" s="33">
         <v>0.99739999999999995</v>
       </c>
-      <c r="BD263" s="155" t="s">
+      <c r="BD263" s="130" t="s">
         <v>354</v>
       </c>
       <c r="BE263" s="33">
@@ -33973,7 +33920,7 @@
         <v>1016</v>
       </c>
       <c r="BF265" s="73"/>
-      <c r="BG265" s="128"/>
+      <c r="BG265" s="8"/>
       <c r="BH265" s="8">
         <v>2096</v>
       </c>
@@ -34206,104 +34153,102 @@
       <c r="BM267"/>
     </row>
     <row r="268" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A268" s="128" t="s">
+      <c r="A268" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="B268" s="128" t="s">
+      <c r="B268" s="8" t="s">
         <v>301</v>
       </c>
       <c r="C268" s="4">
         <v>45068</v>
       </c>
-      <c r="D268" s="130">
+      <c r="D268" s="20">
         <v>3</v>
       </c>
       <c r="E268" s="37" t="s">
         <v>304</v>
       </c>
-      <c r="F268" s="134"/>
-      <c r="G268" s="134"/>
-      <c r="H268" s="128"/>
-      <c r="I268" s="128"/>
-      <c r="J268" s="128"/>
-      <c r="K268" s="134"/>
-      <c r="L268" s="135">
+      <c r="F268" s="10"/>
+      <c r="G268" s="10"/>
+      <c r="H268" s="8"/>
+      <c r="K268" s="10"/>
+      <c r="L268" s="25">
         <v>0.17199999999999999</v>
       </c>
       <c r="M268" s="22">
         <v>0.17680000000000001</v>
       </c>
-      <c r="N268" s="134"/>
-      <c r="O268" s="134"/>
-      <c r="P268" s="145">
+      <c r="N268" s="10"/>
+      <c r="O268" s="10"/>
+      <c r="P268" s="69">
         <v>53.7</v>
       </c>
-      <c r="Q268" s="130">
+      <c r="Q268" s="20">
         <v>360</v>
       </c>
-      <c r="R268" s="134"/>
-      <c r="S268" s="151"/>
-      <c r="T268" s="128" t="s">
+      <c r="R268" s="10"/>
+      <c r="S268" s="65"/>
+      <c r="T268" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="U268" s="129" t="s">
+      <c r="U268" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="V268" s="129" t="s">
+      <c r="V268" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="W268" s="129" t="s">
+      <c r="W268" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="X268" s="129" t="s">
+      <c r="X268" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="Y268" s="129" t="s">
+      <c r="Y268" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="Z268" s="129"/>
-      <c r="AA268" s="129"/>
-      <c r="AB268" s="129"/>
-      <c r="AC268" s="129"/>
-      <c r="AD268" s="129"/>
-      <c r="AE268" s="129"/>
-      <c r="AF268" s="129"/>
-      <c r="AG268" s="129"/>
-      <c r="AH268" s="129"/>
-      <c r="AI268" s="129"/>
-      <c r="AJ268" s="129"/>
-      <c r="AK268" s="129"/>
-      <c r="AL268" s="129"/>
-      <c r="AM268" s="129"/>
-      <c r="AN268" s="129"/>
-      <c r="AO268" s="129"/>
-      <c r="AP268" s="129"/>
-      <c r="AQ268" s="129"/>
-      <c r="AR268" s="129"/>
-      <c r="AS268" s="129"/>
-      <c r="AT268" s="129"/>
-      <c r="AU268" s="129"/>
-      <c r="AV268" s="129"/>
-      <c r="AW268" s="128">
+      <c r="Z268" s="5"/>
+      <c r="AA268" s="5"/>
+      <c r="AB268" s="5"/>
+      <c r="AC268" s="5"/>
+      <c r="AD268" s="5"/>
+      <c r="AE268" s="5"/>
+      <c r="AF268" s="5"/>
+      <c r="AG268" s="5"/>
+      <c r="AH268" s="5"/>
+      <c r="AI268" s="5"/>
+      <c r="AJ268" s="5"/>
+      <c r="AK268" s="5"/>
+      <c r="AL268" s="5"/>
+      <c r="AM268" s="5"/>
+      <c r="AN268" s="5"/>
+      <c r="AO268" s="5"/>
+      <c r="AP268" s="5"/>
+      <c r="AQ268" s="5"/>
+      <c r="AR268" s="5"/>
+      <c r="AS268" s="5"/>
+      <c r="AT268" s="5"/>
+      <c r="AU268" s="5"/>
+      <c r="AV268" s="5"/>
+      <c r="AW268" s="8">
         <v>71.400000000000006</v>
       </c>
-      <c r="AX268" s="128">
+      <c r="AX268" s="8">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AY268" s="129"/>
-      <c r="AZ268" s="128">
+      <c r="AY268" s="5"/>
+      <c r="AZ268" s="8">
         <v>200</v>
       </c>
-      <c r="BA268" s="128" t="s">
+      <c r="BA268" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="BB268" s="128">
+      <c r="BB268" s="8">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="BC268" s="128">
+      <c r="BC268" s="8">
         <v>99.74</v>
       </c>
-      <c r="BD268" s="156">
+      <c r="BD268" s="66">
         <v>25.7</v>
       </c>
       <c r="BE268" s="67">
@@ -34321,104 +34266,102 @@
       <c r="BM268"/>
     </row>
     <row r="269" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A269" s="128" t="s">
+      <c r="A269" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="B269" s="128" t="s">
+      <c r="B269" s="8" t="s">
         <v>301</v>
       </c>
       <c r="C269" s="4">
         <v>45068</v>
       </c>
-      <c r="D269" s="130">
+      <c r="D269" s="20">
         <v>4</v>
       </c>
       <c r="E269" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="F269" s="134"/>
-      <c r="G269" s="134"/>
-      <c r="H269" s="128"/>
-      <c r="I269" s="128"/>
-      <c r="J269" s="128"/>
-      <c r="K269" s="134"/>
-      <c r="L269" s="135">
+      <c r="F269" s="10"/>
+      <c r="G269" s="10"/>
+      <c r="H269" s="8"/>
+      <c r="K269" s="10"/>
+      <c r="L269" s="25">
         <v>0.17299999999999999</v>
       </c>
       <c r="M269" s="26">
         <v>0.1777</v>
       </c>
-      <c r="N269" s="134"/>
-      <c r="O269" s="134"/>
-      <c r="P269" s="145">
+      <c r="N269" s="10"/>
+      <c r="O269" s="10"/>
+      <c r="P269" s="69">
         <v>53.3</v>
       </c>
-      <c r="Q269" s="130">
+      <c r="Q269" s="20">
         <v>356</v>
       </c>
-      <c r="R269" s="134"/>
-      <c r="S269" s="151"/>
-      <c r="T269" s="128" t="s">
+      <c r="R269" s="10"/>
+      <c r="S269" s="65"/>
+      <c r="T269" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="U269" s="129" t="s">
+      <c r="U269" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="V269" s="129" t="s">
+      <c r="V269" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="W269" s="129" t="s">
+      <c r="W269" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="X269" s="129" t="s">
+      <c r="X269" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="Y269" s="129" t="s">
+      <c r="Y269" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="Z269" s="129"/>
-      <c r="AA269" s="129"/>
-      <c r="AB269" s="129"/>
-      <c r="AC269" s="129"/>
-      <c r="AD269" s="129"/>
-      <c r="AE269" s="129"/>
-      <c r="AF269" s="129"/>
-      <c r="AG269" s="129"/>
-      <c r="AH269" s="129"/>
-      <c r="AI269" s="129"/>
-      <c r="AJ269" s="129"/>
-      <c r="AK269" s="129"/>
-      <c r="AL269" s="129"/>
-      <c r="AM269" s="129"/>
-      <c r="AN269" s="129"/>
-      <c r="AO269" s="129"/>
-      <c r="AP269" s="129"/>
-      <c r="AQ269" s="129"/>
-      <c r="AR269" s="129"/>
-      <c r="AS269" s="129"/>
-      <c r="AT269" s="129"/>
-      <c r="AU269" s="129"/>
-      <c r="AV269" s="129"/>
-      <c r="AW269" s="128">
+      <c r="Z269" s="5"/>
+      <c r="AA269" s="5"/>
+      <c r="AB269" s="5"/>
+      <c r="AC269" s="5"/>
+      <c r="AD269" s="5"/>
+      <c r="AE269" s="5"/>
+      <c r="AF269" s="5"/>
+      <c r="AG269" s="5"/>
+      <c r="AH269" s="5"/>
+      <c r="AI269" s="5"/>
+      <c r="AJ269" s="5"/>
+      <c r="AK269" s="5"/>
+      <c r="AL269" s="5"/>
+      <c r="AM269" s="5"/>
+      <c r="AN269" s="5"/>
+      <c r="AO269" s="5"/>
+      <c r="AP269" s="5"/>
+      <c r="AQ269" s="5"/>
+      <c r="AR269" s="5"/>
+      <c r="AS269" s="5"/>
+      <c r="AT269" s="5"/>
+      <c r="AU269" s="5"/>
+      <c r="AV269" s="5"/>
+      <c r="AW269" s="8">
         <v>71.5</v>
       </c>
-      <c r="AX269" s="128">
+      <c r="AX269" s="8">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AY269" s="129"/>
-      <c r="AZ269" s="128">
+      <c r="AY269" s="5"/>
+      <c r="AZ269" s="8">
         <v>200</v>
       </c>
-      <c r="BA269" s="128" t="s">
+      <c r="BA269" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="BB269" s="128">
+      <c r="BB269" s="8">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="BC269" s="128">
+      <c r="BC269" s="8">
         <v>99.74</v>
       </c>
-      <c r="BD269" s="156">
+      <c r="BD269" s="66">
         <v>26</v>
       </c>
       <c r="BE269" s="67">
@@ -34436,101 +34379,99 @@
       <c r="BM269"/>
     </row>
     <row r="270" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A270" s="128" t="s">
+      <c r="A270" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="B270" s="128" t="s">
+      <c r="B270" s="8" t="s">
         <v>301</v>
       </c>
       <c r="C270" s="4">
         <v>45068</v>
       </c>
-      <c r="D270" s="130">
+      <c r="D270" s="20">
         <v>5</v>
       </c>
       <c r="E270" s="37" t="s">
         <v>306</v>
       </c>
-      <c r="F270" s="134"/>
-      <c r="G270" s="134"/>
-      <c r="H270" s="128"/>
-      <c r="I270" s="128"/>
-      <c r="J270" s="128"/>
-      <c r="K270" s="134"/>
-      <c r="L270" s="135">
+      <c r="F270" s="10"/>
+      <c r="G270" s="10"/>
+      <c r="H270" s="8"/>
+      <c r="K270" s="10"/>
+      <c r="L270" s="25">
         <v>0.17399999999999999</v>
       </c>
       <c r="M270" s="26">
         <v>0.17680000000000001</v>
       </c>
-      <c r="N270" s="134"/>
-      <c r="O270" s="134"/>
-      <c r="P270" s="145">
+      <c r="N270" s="10"/>
+      <c r="O270" s="10"/>
+      <c r="P270" s="69">
         <v>53.9</v>
       </c>
-      <c r="Q270" s="130">
+      <c r="Q270" s="20">
         <v>361</v>
       </c>
-      <c r="R270" s="134"/>
-      <c r="S270" s="151"/>
-      <c r="T270" s="128" t="s">
+      <c r="R270" s="10"/>
+      <c r="S270" s="65"/>
+      <c r="T270" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="U270" s="129" t="s">
+      <c r="U270" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="V270" s="129" t="s">
+      <c r="V270" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="W270" s="129" t="s">
+      <c r="W270" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="X270" s="129" t="s">
+      <c r="X270" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="Y270" s="129" t="s">
+      <c r="Y270" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="Z270" s="129"/>
-      <c r="AA270" s="129"/>
-      <c r="AB270" s="129"/>
-      <c r="AC270" s="129"/>
-      <c r="AD270" s="129"/>
-      <c r="AE270" s="129"/>
-      <c r="AF270" s="129"/>
-      <c r="AG270" s="129"/>
-      <c r="AH270" s="129"/>
-      <c r="AI270" s="129"/>
-      <c r="AJ270" s="129"/>
-      <c r="AK270" s="129"/>
-      <c r="AL270" s="129"/>
-      <c r="AM270" s="129"/>
-      <c r="AN270" s="129"/>
-      <c r="AO270" s="129"/>
-      <c r="AP270" s="129"/>
-      <c r="AQ270" s="129"/>
-      <c r="AR270" s="129"/>
-      <c r="AS270" s="129"/>
-      <c r="AT270" s="129"/>
-      <c r="AU270" s="129"/>
-      <c r="AV270" s="129"/>
-      <c r="AW270" s="128">
+      <c r="Z270" s="5"/>
+      <c r="AA270" s="5"/>
+      <c r="AB270" s="5"/>
+      <c r="AC270" s="5"/>
+      <c r="AD270" s="5"/>
+      <c r="AE270" s="5"/>
+      <c r="AF270" s="5"/>
+      <c r="AG270" s="5"/>
+      <c r="AH270" s="5"/>
+      <c r="AI270" s="5"/>
+      <c r="AJ270" s="5"/>
+      <c r="AK270" s="5"/>
+      <c r="AL270" s="5"/>
+      <c r="AM270" s="5"/>
+      <c r="AN270" s="5"/>
+      <c r="AO270" s="5"/>
+      <c r="AP270" s="5"/>
+      <c r="AQ270" s="5"/>
+      <c r="AR270" s="5"/>
+      <c r="AS270" s="5"/>
+      <c r="AT270" s="5"/>
+      <c r="AU270" s="5"/>
+      <c r="AV270" s="5"/>
+      <c r="AW270" s="8">
         <v>71.599999999999994</v>
       </c>
-      <c r="AX270" s="128">
+      <c r="AX270" s="8">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AY270" s="129"/>
-      <c r="AZ270" s="128">
+      <c r="AY270" s="5"/>
+      <c r="AZ270" s="8">
         <v>200</v>
       </c>
-      <c r="BA270" s="128" t="s">
+      <c r="BA270" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="BB270" s="128">
+      <c r="BB270" s="8">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="BC270" s="128">
+      <c r="BC270" s="8">
         <v>99.74</v>
       </c>
       <c r="BD270" s="66">
@@ -35097,10 +35038,10 @@
       <c r="BD275" s="8">
         <v>25.4</v>
       </c>
-      <c r="BE275" s="128">
+      <c r="BE275" s="8">
         <v>1001</v>
       </c>
-      <c r="BF275" s="141">
+      <c r="BF275" s="35">
         <v>0.48</v>
       </c>
       <c r="BG275" s="48">
@@ -35114,40 +35055,38 @@
       <c r="BM275"/>
     </row>
     <row r="276" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A276" s="128" t="s">
+      <c r="A276" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B276" s="128" t="s">
+      <c r="B276" s="8" t="s">
         <v>141</v>
       </c>
       <c r="C276" s="4">
         <v>45068</v>
       </c>
-      <c r="D276" s="128">
+      <c r="D276" s="8">
         <v>2</v>
       </c>
       <c r="E276" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="F276" s="134"/>
-      <c r="G276" s="134"/>
-      <c r="H276" s="134"/>
-      <c r="I276" s="134"/>
-      <c r="J276" s="134"/>
-      <c r="K276" s="134"/>
-      <c r="L276" s="134"/>
+      <c r="F276" s="10"/>
+      <c r="G276" s="10"/>
+      <c r="H276" s="10"/>
+      <c r="I276" s="10"/>
+      <c r="J276" s="10"/>
+      <c r="K276" s="10"/>
+      <c r="L276" s="10"/>
       <c r="M276" s="8">
         <v>0.17499999999999999</v>
       </c>
-      <c r="N276" s="128"/>
-      <c r="O276" s="128"/>
-      <c r="P276" s="128">
+      <c r="P276" s="8">
         <v>56.2</v>
       </c>
-      <c r="Q276" s="128">
+      <c r="Q276" s="8">
         <v>424</v>
       </c>
-      <c r="R276" s="128">
+      <c r="R276" s="8">
         <v>1509.4</v>
       </c>
       <c r="S276" s="8" t="s">
@@ -35156,62 +35095,62 @@
       <c r="T276" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="U276" s="152" t="s">
+      <c r="U276" s="16" t="s">
         <v>93</v>
       </c>
       <c r="V276" s="8"/>
-      <c r="W276" s="152" t="s">
+      <c r="W276" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="X276" s="128" t="s">
+      <c r="X276" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="Y276" s="128" t="s">
+      <c r="Y276" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="Z276" s="128"/>
-      <c r="AA276" s="128"/>
-      <c r="AB276" s="128"/>
-      <c r="AC276" s="128"/>
-      <c r="AD276" s="128"/>
-      <c r="AE276" s="128"/>
-      <c r="AF276" s="128"/>
-      <c r="AG276" s="128"/>
-      <c r="AH276" s="128"/>
-      <c r="AI276" s="128"/>
-      <c r="AJ276" s="128"/>
-      <c r="AK276" s="128"/>
-      <c r="AL276" s="128"/>
-      <c r="AM276" s="128"/>
-      <c r="AN276" s="128"/>
-      <c r="AO276" s="128"/>
-      <c r="AP276" s="128"/>
-      <c r="AQ276" s="128"/>
-      <c r="AR276" s="128"/>
-      <c r="AS276" s="128"/>
-      <c r="AT276" s="128"/>
-      <c r="AU276" s="128"/>
-      <c r="AV276" s="128"/>
-      <c r="AW276" s="128"/>
-      <c r="AX276" s="128"/>
-      <c r="AY276" s="128"/>
-      <c r="AZ276" s="152">
+      <c r="Z276" s="8"/>
+      <c r="AA276" s="8"/>
+      <c r="AB276" s="8"/>
+      <c r="AC276" s="8"/>
+      <c r="AD276" s="8"/>
+      <c r="AE276" s="8"/>
+      <c r="AF276" s="8"/>
+      <c r="AG276" s="8"/>
+      <c r="AH276" s="8"/>
+      <c r="AI276" s="8"/>
+      <c r="AJ276" s="8"/>
+      <c r="AK276" s="8"/>
+      <c r="AL276" s="8"/>
+      <c r="AM276" s="8"/>
+      <c r="AN276" s="8"/>
+      <c r="AO276" s="8"/>
+      <c r="AP276" s="8"/>
+      <c r="AQ276" s="8"/>
+      <c r="AR276" s="8"/>
+      <c r="AS276" s="8"/>
+      <c r="AT276" s="8"/>
+      <c r="AU276" s="8"/>
+      <c r="AV276" s="8"/>
+      <c r="AW276" s="8"/>
+      <c r="AX276" s="8"/>
+      <c r="AY276" s="8"/>
+      <c r="AZ276" s="16">
         <v>200</v>
       </c>
-      <c r="BA276" s="128">
+      <c r="BA276" s="8">
         <v>111.6</v>
       </c>
-      <c r="BB276" s="152">
+      <c r="BB276" s="16">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="BC276" s="128"/>
+      <c r="BC276" s="8"/>
       <c r="BD276" s="8">
         <v>25.5</v>
       </c>
-      <c r="BE276" s="128">
+      <c r="BE276" s="8">
         <v>1001</v>
       </c>
-      <c r="BF276" s="141">
+      <c r="BF276" s="35">
         <v>0.47</v>
       </c>
       <c r="BG276" s="48">
@@ -35317,10 +35256,10 @@
       <c r="BD277" s="8">
         <v>25.8</v>
       </c>
-      <c r="BE277" s="128">
+      <c r="BE277" s="8">
         <v>1001</v>
       </c>
-      <c r="BF277" s="141">
+      <c r="BF277" s="35">
         <v>0.47</v>
       </c>
       <c r="BG277" s="48">
@@ -35426,10 +35365,10 @@
       <c r="BD278" s="8">
         <v>26</v>
       </c>
-      <c r="BE278" s="128">
+      <c r="BE278" s="8">
         <v>1000</v>
       </c>
-      <c r="BF278" s="141">
+      <c r="BF278" s="35">
         <v>0.46</v>
       </c>
       <c r="BG278" s="48">
@@ -35535,10 +35474,10 @@
       <c r="BD279" s="8">
         <v>26.3</v>
       </c>
-      <c r="BE279" s="128">
+      <c r="BE279" s="8">
         <v>1000</v>
       </c>
-      <c r="BF279" s="141">
+      <c r="BF279" s="35">
         <v>0.46</v>
       </c>
       <c r="BG279" s="48">
@@ -35647,10 +35586,10 @@
       <c r="BE280" s="8">
         <v>1000</v>
       </c>
-      <c r="BF280" s="163">
+      <c r="BF280" s="132">
         <v>0.46</v>
       </c>
-      <c r="BG280" s="128">
+      <c r="BG280" s="8">
         <v>1.1559999999999999</v>
       </c>
       <c r="BH280" s="8">
@@ -35756,10 +35695,10 @@
       <c r="BE281" s="8">
         <v>1000</v>
       </c>
-      <c r="BF281" s="163">
+      <c r="BF281" s="132">
         <v>0.46</v>
       </c>
-      <c r="BG281" s="128">
+      <c r="BG281" s="8">
         <v>1.155</v>
       </c>
       <c r="BH281" s="8">
@@ -35865,10 +35804,10 @@
       <c r="BE282" s="8">
         <v>1000</v>
       </c>
-      <c r="BF282" s="163">
+      <c r="BF282" s="132">
         <v>0.46</v>
       </c>
-      <c r="BG282" s="128">
+      <c r="BG282" s="8">
         <v>1.155</v>
       </c>
       <c r="BH282" s="8">
@@ -35974,10 +35913,10 @@
       <c r="BE283" s="8">
         <v>999</v>
       </c>
-      <c r="BF283" s="163">
+      <c r="BF283" s="132">
         <v>0.46</v>
       </c>
-      <c r="BG283" s="128">
+      <c r="BG283" s="8">
         <v>1.1539999999999999</v>
       </c>
       <c r="BH283" s="8">
@@ -36645,13 +36584,13 @@
         <v>99.74</v>
       </c>
       <c r="BD289" s="57"/>
-      <c r="BE289" s="161" t="s">
+      <c r="BE289" s="131" t="s">
         <v>162</v>
       </c>
       <c r="BF289" s="70" t="s">
         <v>162</v>
       </c>
-      <c r="BG289" s="170"/>
+      <c r="BG289" s="138"/>
       <c r="BH289" s="8">
         <v>2096</v>
       </c>
@@ -36754,13 +36693,13 @@
         <v>99.74</v>
       </c>
       <c r="BD290" s="57"/>
-      <c r="BE290" s="161" t="s">
+      <c r="BE290" s="131" t="s">
         <v>162</v>
       </c>
       <c r="BF290" s="70" t="s">
         <v>162</v>
       </c>
-      <c r="BG290" s="170"/>
+      <c r="BG290" s="138"/>
       <c r="BH290" s="8">
         <v>2096</v>
       </c>
@@ -36863,13 +36802,13 @@
         <v>99.74</v>
       </c>
       <c r="BD291" s="57"/>
-      <c r="BE291" s="161" t="s">
+      <c r="BE291" s="131" t="s">
         <v>162</v>
       </c>
       <c r="BF291" s="70" t="s">
         <v>162</v>
       </c>
-      <c r="BG291" s="169"/>
+      <c r="BG291" s="137"/>
       <c r="BH291" s="8">
         <v>2096</v>
       </c>
@@ -37081,7 +37020,7 @@
         <v>99.74</v>
       </c>
       <c r="BD293" s="57"/>
-      <c r="BE293" s="161" t="s">
+      <c r="BE293" s="131" t="s">
         <v>162</v>
       </c>
       <c r="BF293" s="70" t="s">
@@ -37403,7 +37342,7 @@
       <c r="BD296" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="BE296" s="160"/>
+      <c r="BE296" s="83"/>
       <c r="BF296" s="70"/>
       <c r="BG296" s="93">
         <v>1.1759999999999999</v>
@@ -37509,7 +37448,7 @@
       <c r="BD297" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="BE297" s="160"/>
+      <c r="BE297" s="83"/>
       <c r="BF297" s="70"/>
       <c r="BG297" s="93">
         <v>1.1739999999999999</v>
@@ -37615,7 +37554,7 @@
       <c r="BD298" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="BE298" s="160"/>
+      <c r="BE298" s="83"/>
       <c r="BF298" s="70"/>
       <c r="BG298" s="93">
         <v>1.1739999999999999</v>
@@ -37721,7 +37660,7 @@
       <c r="BD299" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="BE299" s="160"/>
+      <c r="BE299" s="83"/>
       <c r="BF299" s="70"/>
       <c r="BG299" s="93">
         <v>1.1719999999999999</v>
@@ -37823,7 +37762,7 @@
         <v>1012</v>
       </c>
       <c r="BF300" s="33"/>
-      <c r="BG300" s="128"/>
+      <c r="BG300" s="8"/>
       <c r="BH300" s="8">
         <v>2096</v>
       </c>
@@ -37925,7 +37864,7 @@
         <v>1012</v>
       </c>
       <c r="BF301" s="73"/>
-      <c r="BG301" s="128"/>
+      <c r="BG301" s="8"/>
       <c r="BH301" s="8">
         <v>2096</v>
       </c>
@@ -38028,7 +37967,7 @@
         <v>1012</v>
       </c>
       <c r="BF302" s="33"/>
-      <c r="BG302" s="128"/>
+      <c r="BG302" s="8"/>
       <c r="BH302" s="8">
         <v>2096</v>
       </c>
@@ -38130,7 +38069,7 @@
         <v>1012</v>
       </c>
       <c r="BF303" s="73"/>
-      <c r="BG303" s="128"/>
+      <c r="BG303" s="8"/>
       <c r="BH303" s="8">
         <v>2096</v>
       </c>
@@ -38230,7 +38169,7 @@
         <v>1012</v>
       </c>
       <c r="BF304" s="33"/>
-      <c r="BG304" s="128"/>
+      <c r="BG304" s="8"/>
       <c r="BH304" s="8">
         <v>2096</v>
       </c>
@@ -38337,7 +38276,7 @@
         <v>1012</v>
       </c>
       <c r="BF305" s="73"/>
-      <c r="BG305" s="128"/>
+      <c r="BG305" s="8"/>
       <c r="BH305" s="8">
         <v>2096</v>
       </c>
@@ -38442,7 +38381,7 @@
         <v>1012</v>
       </c>
       <c r="BF306" s="33"/>
-      <c r="BG306" s="128"/>
+      <c r="BG306" s="8"/>
       <c r="BH306" s="8">
         <v>2096</v>
       </c>
@@ -38549,7 +38488,7 @@
         <v>1012</v>
       </c>
       <c r="BF307" s="73"/>
-      <c r="BG307" s="128"/>
+      <c r="BG307" s="8"/>
       <c r="BH307" s="8">
         <v>2096</v>
       </c>
@@ -38560,93 +38499,91 @@
       <c r="BM307"/>
     </row>
     <row r="308" spans="1:65" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A308" s="128" t="s">
+      <c r="A308" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="B308" s="128" t="s">
+      <c r="B308" s="8" t="s">
         <v>321</v>
       </c>
       <c r="C308" s="4">
         <v>45097</v>
       </c>
-      <c r="D308" s="130">
+      <c r="D308" s="20">
         <v>4</v>
       </c>
-      <c r="E308" s="133" t="s">
+      <c r="E308" s="37" t="s">
         <v>313</v>
       </c>
-      <c r="F308" s="134"/>
-      <c r="G308" s="134"/>
-      <c r="H308" s="128"/>
-      <c r="I308" s="128"/>
-      <c r="J308" s="128"/>
-      <c r="K308" s="134"/>
-      <c r="L308" s="135">
+      <c r="F308" s="10"/>
+      <c r="G308" s="10"/>
+      <c r="H308" s="8"/>
+      <c r="K308" s="10"/>
+      <c r="L308" s="25">
         <v>0.183</v>
       </c>
       <c r="M308" s="26">
         <v>0.17760000000000001</v>
       </c>
-      <c r="N308" s="134"/>
-      <c r="O308" s="134"/>
-      <c r="P308" s="145"/>
-      <c r="Q308" s="146">
+      <c r="N308" s="10"/>
+      <c r="O308" s="10"/>
+      <c r="P308" s="69"/>
+      <c r="Q308" s="68">
         <v>420</v>
       </c>
-      <c r="R308" s="130"/>
-      <c r="S308" s="128" t="s">
+      <c r="R308" s="20"/>
+      <c r="S308" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="T308" s="128" t="s">
+      <c r="T308" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="U308" s="128"/>
-      <c r="V308" s="128" t="s">
+      <c r="U308" s="8"/>
+      <c r="V308" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="W308" s="128" t="s">
+      <c r="W308" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="X308" s="128" t="s">
+      <c r="X308" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="Y308" s="128" t="s">
+      <c r="Y308" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="Z308" s="128"/>
-      <c r="AA308" s="128"/>
-      <c r="AB308" s="128"/>
-      <c r="AC308" s="128"/>
-      <c r="AD308" s="128"/>
-      <c r="AE308" s="128"/>
-      <c r="AF308" s="128"/>
-      <c r="AG308" s="128"/>
-      <c r="AH308" s="128"/>
-      <c r="AI308" s="128"/>
-      <c r="AJ308" s="128"/>
-      <c r="AK308" s="128"/>
-      <c r="AL308" s="128"/>
-      <c r="AM308" s="128"/>
-      <c r="AN308" s="128"/>
-      <c r="AO308" s="128"/>
-      <c r="AP308" s="128"/>
-      <c r="AQ308" s="128"/>
-      <c r="AR308" s="128"/>
-      <c r="AS308" s="128"/>
-      <c r="AT308" s="128"/>
-      <c r="AU308" s="128"/>
-      <c r="AV308" s="128"/>
-      <c r="AW308" s="128"/>
-      <c r="AX308" s="128"/>
-      <c r="AY308" s="128"/>
-      <c r="AZ308" s="128">
+      <c r="Z308" s="8"/>
+      <c r="AA308" s="8"/>
+      <c r="AB308" s="8"/>
+      <c r="AC308" s="8"/>
+      <c r="AD308" s="8"/>
+      <c r="AE308" s="8"/>
+      <c r="AF308" s="8"/>
+      <c r="AG308" s="8"/>
+      <c r="AH308" s="8"/>
+      <c r="AI308" s="8"/>
+      <c r="AJ308" s="8"/>
+      <c r="AK308" s="8"/>
+      <c r="AL308" s="8"/>
+      <c r="AM308" s="8"/>
+      <c r="AN308" s="8"/>
+      <c r="AO308" s="8"/>
+      <c r="AP308" s="8"/>
+      <c r="AQ308" s="8"/>
+      <c r="AR308" s="8"/>
+      <c r="AS308" s="8"/>
+      <c r="AT308" s="8"/>
+      <c r="AU308" s="8"/>
+      <c r="AV308" s="8"/>
+      <c r="AW308" s="8"/>
+      <c r="AX308" s="8"/>
+      <c r="AY308" s="8"/>
+      <c r="AZ308" s="8">
         <v>200</v>
       </c>
-      <c r="BA308" s="128"/>
-      <c r="BB308" s="128">
+      <c r="BA308" s="8"/>
+      <c r="BB308" s="8">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="BC308" s="128">
+      <c r="BC308" s="8">
         <v>99.74</v>
       </c>
       <c r="BD308" s="32" t="s">
@@ -38873,10 +38810,10 @@
       <c r="BE310" s="60">
         <v>1012</v>
       </c>
-      <c r="BF310" s="160">
+      <c r="BF310" s="83">
         <v>37.799999999999997</v>
       </c>
-      <c r="BG310" s="160">
+      <c r="BG310" s="83">
         <v>1.18</v>
       </c>
       <c r="BH310" s="8">
@@ -38988,10 +38925,10 @@
       <c r="BE311" s="60">
         <v>1012</v>
       </c>
-      <c r="BF311" s="160">
+      <c r="BF311" s="83">
         <v>37.799999999999997</v>
       </c>
-      <c r="BG311" s="160">
+      <c r="BG311" s="83">
         <v>1.18</v>
       </c>
       <c r="BH311" s="8">
@@ -39103,10 +39040,10 @@
       <c r="BE312" s="60">
         <v>1012</v>
       </c>
-      <c r="BF312" s="160">
+      <c r="BF312" s="83">
         <v>37.799999999999997</v>
       </c>
-      <c r="BG312" s="160">
+      <c r="BG312" s="83">
         <v>1.18</v>
       </c>
       <c r="BH312" s="8">
@@ -39218,10 +39155,10 @@
       <c r="BE313" s="60">
         <v>1012</v>
       </c>
-      <c r="BF313" s="160">
+      <c r="BF313" s="83">
         <v>37.799999999999997</v>
       </c>
-      <c r="BG313" s="160">
+      <c r="BG313" s="83">
         <v>1.18</v>
       </c>
       <c r="BH313" s="8">
@@ -39326,7 +39263,7 @@
       <c r="BF314" s="49">
         <v>51</v>
       </c>
-      <c r="BG314" s="157"/>
+      <c r="BG314" s="82"/>
       <c r="BH314" s="8">
         <v>2096</v>
       </c>
@@ -39439,7 +39376,7 @@
       <c r="BF315" s="49">
         <v>51</v>
       </c>
-      <c r="BG315" s="157"/>
+      <c r="BG315" s="82"/>
       <c r="BH315" s="8">
         <v>2096</v>
       </c>
@@ -39550,7 +39487,7 @@
       <c r="BF316" s="49">
         <v>51</v>
       </c>
-      <c r="BG316" s="157"/>
+      <c r="BG316" s="82"/>
       <c r="BH316" s="8">
         <v>2096</v>
       </c>
@@ -39663,7 +39600,7 @@
       <c r="BF317" s="49">
         <v>51</v>
       </c>
-      <c r="BG317" s="157"/>
+      <c r="BG317" s="82"/>
       <c r="BH317" s="8">
         <v>2096</v>
       </c>
@@ -39776,7 +39713,7 @@
       <c r="BF318" s="49">
         <v>51</v>
       </c>
-      <c r="BG318" s="157"/>
+      <c r="BG318" s="82"/>
       <c r="BH318" s="8">
         <v>2096</v>
       </c>
@@ -39804,7 +39741,7 @@
       <c r="G319" s="10"/>
       <c r="H319" s="8"/>
       <c r="K319" s="10"/>
-      <c r="L319" s="134"/>
+      <c r="L319" s="10"/>
       <c r="M319" s="55">
         <v>0.161</v>
       </c>
@@ -39885,7 +39822,7 @@
       <c r="BE319" s="105">
         <v>997</v>
       </c>
-      <c r="BF319" s="160">
+      <c r="BF319" s="83">
         <v>49</v>
       </c>
       <c r="BG319" s="106">
@@ -39916,7 +39853,7 @@
       <c r="G320" s="10"/>
       <c r="H320" s="8"/>
       <c r="K320" s="10"/>
-      <c r="L320" s="134"/>
+      <c r="L320" s="10"/>
       <c r="M320" s="55">
         <v>0.161</v>
       </c>
@@ -39997,7 +39934,7 @@
       <c r="BE320" s="105">
         <v>997</v>
       </c>
-      <c r="BF320" s="160">
+      <c r="BF320" s="83">
         <v>49</v>
       </c>
       <c r="BG320" s="106">
@@ -40109,7 +40046,7 @@
       <c r="BE321" s="108">
         <v>997.1</v>
       </c>
-      <c r="BF321" s="138">
+      <c r="BF321" s="107">
         <v>49.6</v>
       </c>
       <c r="BG321" s="106"/>
@@ -40221,7 +40158,7 @@
       <c r="BE322" s="105">
         <v>997</v>
       </c>
-      <c r="BF322" s="160">
+      <c r="BF322" s="83">
         <v>49</v>
       </c>
       <c r="BG322" s="106">
@@ -40333,7 +40270,7 @@
       <c r="BE323" s="105">
         <v>997</v>
       </c>
-      <c r="BF323" s="160">
+      <c r="BF323" s="83">
         <v>49</v>
       </c>
       <c r="BG323" s="106">
@@ -40445,7 +40382,7 @@
       <c r="BE324" s="108">
         <v>997</v>
       </c>
-      <c r="BF324" s="138">
+      <c r="BF324" s="107">
         <v>48</v>
       </c>
       <c r="BG324" s="106"/>
@@ -40557,7 +40494,7 @@
       <c r="BE325" s="105">
         <v>996</v>
       </c>
-      <c r="BF325" s="160">
+      <c r="BF325" s="83">
         <v>49</v>
       </c>
       <c r="BG325" s="106">
@@ -40781,7 +40718,7 @@
       <c r="BE327" s="108">
         <v>997</v>
       </c>
-      <c r="BF327" s="138">
+      <c r="BF327" s="107">
         <v>47</v>
       </c>
       <c r="BG327" s="106"/>
@@ -40893,7 +40830,7 @@
       <c r="BE328" s="105">
         <v>996</v>
       </c>
-      <c r="BF328" s="160">
+      <c r="BF328" s="83">
         <v>47</v>
       </c>
       <c r="BG328" s="106">
@@ -41005,7 +40942,7 @@
       <c r="BE329" s="105">
         <v>996</v>
       </c>
-      <c r="BF329" s="160">
+      <c r="BF329" s="83">
         <v>47</v>
       </c>
       <c r="BG329" s="106">
@@ -41117,7 +41054,7 @@
       <c r="BE330" s="108">
         <v>997</v>
       </c>
-      <c r="BF330" s="138">
+      <c r="BF330" s="107">
         <v>47</v>
       </c>
       <c r="BG330" s="106"/>
@@ -41227,7 +41164,7 @@
       <c r="BE331" s="105">
         <v>995</v>
       </c>
-      <c r="BF331" s="160">
+      <c r="BF331" s="83">
         <v>47</v>
       </c>
       <c r="BG331" s="106">
@@ -41337,7 +41274,7 @@
       <c r="BE332" s="105">
         <v>996</v>
       </c>
-      <c r="BF332" s="160">
+      <c r="BF332" s="83">
         <v>47</v>
       </c>
       <c r="BG332" s="106">
@@ -41447,7 +41384,7 @@
       <c r="BE333" s="108">
         <v>997</v>
       </c>
-      <c r="BF333" s="138">
+      <c r="BF333" s="107">
         <v>45</v>
       </c>
       <c r="BG333" s="106"/>
@@ -41557,7 +41494,7 @@
       <c r="BE334" s="105">
         <v>995</v>
       </c>
-      <c r="BF334" s="160">
+      <c r="BF334" s="83">
         <v>47</v>
       </c>
       <c r="BG334" s="106">
@@ -41667,7 +41604,7 @@
       <c r="BE335" s="105">
         <v>995</v>
       </c>
-      <c r="BF335" s="160">
+      <c r="BF335" s="83">
         <v>47</v>
       </c>
       <c r="BG335" s="106">
@@ -41777,7 +41714,7 @@
       <c r="BE336" s="108">
         <v>997</v>
       </c>
-      <c r="BF336" s="138">
+      <c r="BF336" s="107">
         <v>45</v>
       </c>
       <c r="BG336" s="106"/>
@@ -41889,7 +41826,7 @@
       <c r="BE337" s="110">
         <v>1013</v>
       </c>
-      <c r="BF337" s="158">
+      <c r="BF337" s="109">
         <v>52.4</v>
       </c>
       <c r="BG337" s="111"/>
@@ -41999,7 +41936,7 @@
       <c r="BE338" s="110">
         <v>1013</v>
       </c>
-      <c r="BF338" s="158">
+      <c r="BF338" s="109">
         <v>52.4</v>
       </c>
       <c r="BG338" s="111"/>
@@ -42107,7 +42044,7 @@
       <c r="BE339" s="108">
         <v>1013</v>
       </c>
-      <c r="BF339" s="138">
+      <c r="BF339" s="107">
         <v>52.4</v>
       </c>
       <c r="BG339" s="106"/>
@@ -42217,7 +42154,7 @@
       <c r="BE340" s="110">
         <v>1013</v>
       </c>
-      <c r="BF340" s="158">
+      <c r="BF340" s="109">
         <v>52.4</v>
       </c>
       <c r="BG340" s="111"/>
@@ -42327,7 +42264,7 @@
       <c r="BE341" s="110">
         <v>1013</v>
       </c>
-      <c r="BF341" s="158">
+      <c r="BF341" s="109">
         <v>52.4</v>
       </c>
       <c r="BG341" s="111"/>
@@ -42435,7 +42372,7 @@
       <c r="BE342" s="108">
         <v>1013</v>
       </c>
-      <c r="BF342" s="138">
+      <c r="BF342" s="107">
         <v>52.4</v>
       </c>
       <c r="BG342" s="106"/>
@@ -42547,7 +42484,7 @@
       <c r="BE343" s="110">
         <v>1012</v>
       </c>
-      <c r="BF343" s="158">
+      <c r="BF343" s="109">
         <v>52.5</v>
       </c>
       <c r="BG343" s="111"/>
@@ -42659,7 +42596,7 @@
       <c r="BE344" s="110">
         <v>1012</v>
       </c>
-      <c r="BF344" s="158">
+      <c r="BF344" s="109">
         <v>52.5</v>
       </c>
       <c r="BG344" s="111"/>
@@ -42769,7 +42706,7 @@
       <c r="BE345" s="108">
         <v>1012</v>
       </c>
-      <c r="BF345" s="138">
+      <c r="BF345" s="107">
         <v>52.5</v>
       </c>
       <c r="BG345" s="106"/>
@@ -42863,9 +42800,9 @@
       <c r="AX346" s="5">
         <v>7.9</v>
       </c>
-      <c r="AY346" s="56" t="e">
+      <c r="AY346" s="56">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AZ346" s="8">
         <v>200</v>
@@ -42878,13 +42815,13 @@
       <c r="BD346" s="109">
         <v>25.4</v>
       </c>
-      <c r="BE346" s="158">
+      <c r="BE346" s="109">
         <v>1012</v>
       </c>
-      <c r="BF346" s="158">
+      <c r="BF346" s="109">
         <v>52.9</v>
       </c>
-      <c r="BG346" s="129"/>
+      <c r="BG346" s="5"/>
       <c r="BH346" s="5"/>
       <c r="BI346" s="5"/>
       <c r="BJ346" s="4" t="s">
@@ -42912,7 +42849,7 @@
       <c r="G347" s="10"/>
       <c r="H347" s="8"/>
       <c r="K347" s="10"/>
-      <c r="L347" s="134"/>
+      <c r="L347" s="10"/>
       <c r="M347" s="109">
         <v>0.15570000000000001</v>
       </c>
@@ -42975,9 +42912,9 @@
       <c r="AX347" s="5">
         <v>8</v>
       </c>
-      <c r="AY347" s="56" t="e">
+      <c r="AY347" s="56">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AZ347" s="8">
         <v>200</v>
@@ -42990,13 +42927,13 @@
       <c r="BD347" s="109">
         <v>25.4</v>
       </c>
-      <c r="BE347" s="158">
+      <c r="BE347" s="109">
         <v>1012</v>
       </c>
-      <c r="BF347" s="158">
+      <c r="BF347" s="109">
         <v>52.9</v>
       </c>
-      <c r="BG347" s="129"/>
+      <c r="BG347" s="5"/>
       <c r="BH347" s="5"/>
       <c r="BI347" s="5"/>
       <c r="BJ347" s="4" t="s">
@@ -43024,7 +42961,7 @@
       <c r="G348" s="10"/>
       <c r="H348" s="8"/>
       <c r="K348" s="10"/>
-      <c r="L348" s="134"/>
+      <c r="L348" s="10"/>
       <c r="M348" s="109">
         <v>0.15429999999999999</v>
       </c>
@@ -43087,9 +43024,9 @@
       <c r="AX348" s="5">
         <v>8.1</v>
       </c>
-      <c r="AY348" s="56" t="e">
+      <c r="AY348" s="56">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AZ348" s="8">
         <v>200</v>
@@ -43100,13 +43037,13 @@
       <c r="BD348" s="107">
         <v>25.4</v>
       </c>
-      <c r="BE348" s="138">
+      <c r="BE348" s="107">
         <v>1012</v>
       </c>
-      <c r="BF348" s="138">
+      <c r="BF348" s="107">
         <v>52.9</v>
       </c>
-      <c r="BG348" s="159"/>
+      <c r="BG348" s="114"/>
       <c r="BH348" s="5"/>
       <c r="BI348" s="5"/>
       <c r="BJ348" s="4" t="s">
@@ -43134,7 +43071,7 @@
       <c r="G349" s="10"/>
       <c r="H349" s="8"/>
       <c r="K349" s="10"/>
-      <c r="L349" s="134"/>
+      <c r="L349" s="10"/>
       <c r="M349" s="115">
         <v>0.17799999999999999</v>
       </c>
@@ -43195,9 +43132,9 @@
       <c r="AX349" s="5">
         <v>7.9</v>
       </c>
-      <c r="AY349" s="56" t="e">
+      <c r="AY349" s="56">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AZ349" s="8">
         <v>200</v>
@@ -43210,13 +43147,13 @@
       <c r="BD349" s="109">
         <v>25.8</v>
       </c>
-      <c r="BE349" s="158">
+      <c r="BE349" s="109">
         <v>1012</v>
       </c>
-      <c r="BF349" s="158">
+      <c r="BF349" s="109">
         <v>51.8</v>
       </c>
-      <c r="BG349" s="129"/>
+      <c r="BG349" s="5"/>
       <c r="BH349" s="5"/>
       <c r="BI349" s="5"/>
       <c r="BJ349" s="4" t="s">
@@ -43244,7 +43181,7 @@
       <c r="G350" s="10"/>
       <c r="H350" s="8"/>
       <c r="K350" s="10"/>
-      <c r="L350" s="134"/>
+      <c r="L350" s="10"/>
       <c r="M350" s="115">
         <v>0.17480000000000001</v>
       </c>
@@ -43305,9 +43242,9 @@
       <c r="AX350" s="5">
         <v>8</v>
       </c>
-      <c r="AY350" s="56" t="e">
+      <c r="AY350" s="56">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AZ350" s="8">
         <v>200</v>
@@ -43320,13 +43257,13 @@
       <c r="BD350" s="109">
         <v>25.8</v>
       </c>
-      <c r="BE350" s="158">
+      <c r="BE350" s="109">
         <v>1012</v>
       </c>
-      <c r="BF350" s="158">
+      <c r="BF350" s="109">
         <v>51.8</v>
       </c>
-      <c r="BG350" s="129"/>
+      <c r="BG350" s="5"/>
       <c r="BH350" s="5"/>
       <c r="BI350" s="5"/>
       <c r="BJ350" s="4" t="s">
@@ -43354,7 +43291,7 @@
       <c r="G351" s="10"/>
       <c r="H351" s="8"/>
       <c r="K351" s="10"/>
-      <c r="L351" s="134"/>
+      <c r="L351" s="10"/>
       <c r="M351" s="115">
         <v>0.17449999999999999</v>
       </c>
@@ -43415,9 +43352,9 @@
       <c r="AX351" s="5">
         <v>8.1</v>
       </c>
-      <c r="AY351" s="56" t="e">
+      <c r="AY351" s="56">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AZ351" s="8">
         <v>200</v>
@@ -43428,13 +43365,13 @@
       <c r="BD351" s="107">
         <v>25.8</v>
       </c>
-      <c r="BE351" s="138">
+      <c r="BE351" s="107">
         <v>1012</v>
       </c>
-      <c r="BF351" s="138">
+      <c r="BF351" s="107">
         <v>51.8</v>
       </c>
-      <c r="BG351" s="159"/>
+      <c r="BG351" s="114"/>
       <c r="BH351" s="5"/>
       <c r="BI351" s="103" t="s">
         <v>460</v>
@@ -43464,7 +43401,7 @@
       <c r="G352" s="10"/>
       <c r="H352" s="8"/>
       <c r="K352" s="10"/>
-      <c r="L352" s="134"/>
+      <c r="L352" s="10"/>
       <c r="M352" s="115">
         <v>0.17299999999999999</v>
       </c>
@@ -43525,9 +43462,9 @@
       <c r="AX352" s="5">
         <v>7.9</v>
       </c>
-      <c r="AY352" s="56" t="e">
+      <c r="AY352" s="56">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AZ352" s="8">
         <v>200</v>
@@ -43540,13 +43477,13 @@
       <c r="BD352" s="109">
         <v>26.3</v>
       </c>
-      <c r="BE352" s="158">
+      <c r="BE352" s="109">
         <v>1012</v>
       </c>
-      <c r="BF352" s="158">
+      <c r="BF352" s="109">
         <v>51.3</v>
       </c>
-      <c r="BG352" s="129"/>
+      <c r="BG352" s="5"/>
       <c r="BH352" s="8"/>
       <c r="BI352" s="5"/>
       <c r="BJ352" s="4" t="s">
@@ -43574,7 +43511,7 @@
       <c r="G353" s="10"/>
       <c r="H353" s="8"/>
       <c r="K353" s="10"/>
-      <c r="L353" s="134"/>
+      <c r="L353" s="10"/>
       <c r="M353" s="115">
         <v>0.17230000000000001</v>
       </c>
@@ -43635,9 +43572,9 @@
       <c r="AX353" s="5">
         <v>8</v>
       </c>
-      <c r="AY353" s="56" t="e">
+      <c r="AY353" s="56">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AZ353" s="8">
         <v>200</v>
@@ -43650,13 +43587,13 @@
       <c r="BD353" s="109">
         <v>26.3</v>
       </c>
-      <c r="BE353" s="158">
+      <c r="BE353" s="109">
         <v>1012</v>
       </c>
-      <c r="BF353" s="158">
+      <c r="BF353" s="109">
         <v>51.3</v>
       </c>
-      <c r="BG353" s="129"/>
+      <c r="BG353" s="5"/>
       <c r="BH353" s="5"/>
       <c r="BI353" s="5"/>
       <c r="BJ353" s="4" t="s">
@@ -43684,7 +43621,7 @@
       <c r="G354" s="10"/>
       <c r="H354" s="8"/>
       <c r="K354" s="10"/>
-      <c r="L354" s="134"/>
+      <c r="L354" s="10"/>
       <c r="M354" s="107">
         <v>0.17299999999999999</v>
       </c>
@@ -43745,9 +43682,9 @@
       <c r="AX354" s="5">
         <v>8.1</v>
       </c>
-      <c r="AY354" s="56" t="e">
+      <c r="AY354" s="56">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AZ354" s="8">
         <v>200</v>
@@ -43758,13 +43695,13 @@
       <c r="BD354" s="107">
         <v>26.3</v>
       </c>
-      <c r="BE354" s="138">
+      <c r="BE354" s="107">
         <v>1012</v>
       </c>
-      <c r="BF354" s="138">
+      <c r="BF354" s="107">
         <v>51.3</v>
       </c>
-      <c r="BG354" s="159"/>
+      <c r="BG354" s="114"/>
       <c r="BH354" s="5"/>
       <c r="BI354" s="5"/>
       <c r="BJ354" s="4" t="s">
@@ -43863,10 +43800,10 @@
       <c r="BD355" s="109">
         <v>24.8</v>
       </c>
-      <c r="BE355" s="158">
+      <c r="BE355" s="109">
         <v>1012</v>
       </c>
-      <c r="BF355" s="158">
+      <c r="BF355" s="109">
         <v>53.5</v>
       </c>
       <c r="BG355" s="5"/>
@@ -43969,10 +43906,10 @@
       <c r="BD356" s="5">
         <v>25</v>
       </c>
-      <c r="BE356" s="159">
+      <c r="BE356" s="114">
         <v>1012</v>
       </c>
-      <c r="BF356" s="160">
+      <c r="BF356" s="83">
         <v>53</v>
       </c>
       <c r="BG356" s="114">
@@ -44077,10 +44014,10 @@
       <c r="BD357" s="109">
         <v>24.8</v>
       </c>
-      <c r="BE357" s="158">
+      <c r="BE357" s="109">
         <v>1012</v>
       </c>
-      <c r="BF357" s="158">
+      <c r="BF357" s="109">
         <v>53.5</v>
       </c>
       <c r="BG357" s="5"/>
@@ -44186,7 +44123,7 @@
       <c r="BE358" s="105">
         <v>1012</v>
       </c>
-      <c r="BF358" s="160">
+      <c r="BF358" s="83">
         <v>54</v>
       </c>
       <c r="BG358" s="106">
@@ -44294,7 +44231,7 @@
       <c r="BE359" s="110">
         <v>1012</v>
       </c>
-      <c r="BF359" s="158">
+      <c r="BF359" s="109">
         <v>53</v>
       </c>
       <c r="BG359" s="116"/>
@@ -44400,7 +44337,7 @@
       <c r="BE360" s="105">
         <v>1012</v>
       </c>
-      <c r="BF360" s="160">
+      <c r="BF360" s="83">
         <v>53</v>
       </c>
       <c r="BG360" s="106">
@@ -44506,7 +44443,7 @@
       <c r="BE361" s="110">
         <v>1012</v>
       </c>
-      <c r="BF361" s="158">
+      <c r="BF361" s="109">
         <v>53</v>
       </c>
       <c r="BG361" s="116"/>
@@ -44610,7 +44547,7 @@
       <c r="BE362" s="105">
         <v>1012</v>
       </c>
-      <c r="BF362" s="160">
+      <c r="BF362" s="83">
         <v>53</v>
       </c>
       <c r="BG362" s="106">
@@ -44716,7 +44653,7 @@
       <c r="BE363" s="110">
         <v>1012</v>
       </c>
-      <c r="BF363" s="158">
+      <c r="BF363" s="109">
         <v>53</v>
       </c>
       <c r="BG363" s="116"/>
@@ -44820,7 +44757,7 @@
       <c r="BE364" s="105">
         <v>1012</v>
       </c>
-      <c r="BF364" s="160">
+      <c r="BF364" s="83">
         <v>53</v>
       </c>
       <c r="BG364" s="106">
@@ -44926,7 +44863,7 @@
       <c r="BE365" s="110">
         <v>1012</v>
       </c>
-      <c r="BF365" s="158">
+      <c r="BF365" s="109">
         <v>53</v>
       </c>
       <c r="BG365" s="116"/>
@@ -45030,7 +44967,7 @@
       <c r="BE366" s="105">
         <v>1012</v>
       </c>
-      <c r="BF366" s="160">
+      <c r="BF366" s="83">
         <v>54</v>
       </c>
       <c r="BG366" s="106">
@@ -45135,13 +45072,13 @@
       <c r="BD367" s="109">
         <v>25.1</v>
       </c>
-      <c r="BE367" s="158">
+      <c r="BE367" s="109">
         <v>1011</v>
       </c>
-      <c r="BF367" s="158">
+      <c r="BF367" s="109">
         <v>54.2</v>
       </c>
-      <c r="BG367" s="167"/>
+      <c r="BG367" s="101"/>
       <c r="BH367" s="5"/>
       <c r="BI367" s="5"/>
       <c r="BJ367" s="4" t="s">
@@ -45241,13 +45178,13 @@
       <c r="BD368" s="5">
         <v>25.1</v>
       </c>
-      <c r="BE368" s="159">
+      <c r="BE368" s="114">
         <v>1011</v>
       </c>
-      <c r="BF368" s="160">
+      <c r="BF368" s="83">
         <v>54</v>
       </c>
-      <c r="BG368" s="159">
+      <c r="BG368" s="114">
         <v>1.173</v>
       </c>
       <c r="BH368" s="5"/>
@@ -45349,13 +45286,13 @@
       <c r="BD369" s="109">
         <v>25.1</v>
       </c>
-      <c r="BE369" s="158">
+      <c r="BE369" s="109">
         <v>1011</v>
       </c>
-      <c r="BF369" s="158">
+      <c r="BF369" s="109">
         <v>54.2</v>
       </c>
-      <c r="BG369" s="167"/>
+      <c r="BG369" s="101"/>
       <c r="BH369" s="5"/>
       <c r="BI369" s="5"/>
       <c r="BJ369" s="4" t="s">
@@ -45455,13 +45392,13 @@
       <c r="BD370" s="5">
         <v>25.2</v>
       </c>
-      <c r="BE370" s="159">
+      <c r="BE370" s="114">
         <v>1011</v>
       </c>
-      <c r="BF370" s="160">
+      <c r="BF370" s="83">
         <v>54</v>
       </c>
-      <c r="BG370" s="159">
+      <c r="BG370" s="114">
         <v>1.173</v>
       </c>
       <c r="BH370" s="5"/>
@@ -45563,13 +45500,13 @@
       <c r="BD371" s="109">
         <v>25.1</v>
       </c>
-      <c r="BE371" s="158">
+      <c r="BE371" s="109">
         <v>1011</v>
       </c>
-      <c r="BF371" s="158">
+      <c r="BF371" s="109">
         <v>54.2</v>
       </c>
-      <c r="BG371" s="167"/>
+      <c r="BG371" s="101"/>
       <c r="BH371" s="5"/>
       <c r="BI371" s="5"/>
       <c r="BJ371" s="4" t="s">
@@ -45669,13 +45606,13 @@
       <c r="BD372" s="5">
         <v>25.2</v>
       </c>
-      <c r="BE372" s="159">
+      <c r="BE372" s="114">
         <v>1011</v>
       </c>
-      <c r="BF372" s="160">
+      <c r="BF372" s="83">
         <v>54</v>
       </c>
-      <c r="BG372" s="159">
+      <c r="BG372" s="114">
         <v>1.173</v>
       </c>
       <c r="BH372" s="5"/>
@@ -45775,13 +45712,13 @@
       <c r="BD373" s="109">
         <v>25.2</v>
       </c>
-      <c r="BE373" s="158">
+      <c r="BE373" s="109">
         <v>1005</v>
       </c>
-      <c r="BF373" s="158">
+      <c r="BF373" s="109">
         <v>41</v>
       </c>
-      <c r="BG373" s="167"/>
+      <c r="BG373" s="101"/>
       <c r="BH373" s="5"/>
       <c r="BI373" s="5"/>
       <c r="BJ373" s="4" t="s">
@@ -45879,13 +45816,13 @@
       <c r="BD374" s="109">
         <v>25.2</v>
       </c>
-      <c r="BE374" s="158">
+      <c r="BE374" s="109">
         <v>1005</v>
       </c>
-      <c r="BF374" s="158">
+      <c r="BF374" s="109">
         <v>41</v>
       </c>
-      <c r="BG374" s="167"/>
+      <c r="BG374" s="101"/>
       <c r="BH374" s="5"/>
       <c r="BI374" s="5"/>
       <c r="BJ374" s="4" t="s">
@@ -45983,13 +45920,13 @@
       <c r="BD375" s="109">
         <v>25.2</v>
       </c>
-      <c r="BE375" s="158">
+      <c r="BE375" s="109">
         <v>1005</v>
       </c>
-      <c r="BF375" s="158">
+      <c r="BF375" s="109">
         <v>41</v>
       </c>
-      <c r="BG375" s="167"/>
+      <c r="BG375" s="101"/>
       <c r="BH375" s="5"/>
       <c r="BI375" s="84" t="s">
         <v>466</v>
@@ -46089,13 +46026,13 @@
       <c r="BD376" s="107">
         <v>25.2</v>
       </c>
-      <c r="BE376" s="138">
+      <c r="BE376" s="107">
         <v>1005</v>
       </c>
-      <c r="BF376" s="138">
+      <c r="BF376" s="107">
         <v>41</v>
       </c>
-      <c r="BG376" s="129"/>
+      <c r="BG376" s="5"/>
       <c r="BH376" s="5"/>
       <c r="BI376" s="5"/>
       <c r="BJ376" s="4" t="s">
@@ -46193,13 +46130,13 @@
       <c r="BD377" s="109">
         <v>25.2</v>
       </c>
-      <c r="BE377" s="158">
+      <c r="BE377" s="109">
         <v>1005</v>
       </c>
-      <c r="BF377" s="158">
+      <c r="BF377" s="109">
         <v>41</v>
       </c>
-      <c r="BG377" s="167"/>
+      <c r="BG377" s="101"/>
       <c r="BH377" s="5"/>
       <c r="BI377" s="5"/>
       <c r="BJ377" s="4" t="s">
@@ -46297,13 +46234,13 @@
       <c r="BD378" s="109">
         <v>25.2</v>
       </c>
-      <c r="BE378" s="158">
+      <c r="BE378" s="109">
         <v>1005</v>
       </c>
-      <c r="BF378" s="158">
+      <c r="BF378" s="109">
         <v>41</v>
       </c>
-      <c r="BG378" s="167"/>
+      <c r="BG378" s="101"/>
       <c r="BH378" s="5"/>
       <c r="BI378" s="5"/>
       <c r="BJ378" s="4" t="s">
@@ -46403,13 +46340,13 @@
       <c r="BD379" s="109">
         <v>25.2</v>
       </c>
-      <c r="BE379" s="158">
+      <c r="BE379" s="109">
         <v>1005</v>
       </c>
-      <c r="BF379" s="158">
+      <c r="BF379" s="109">
         <v>41</v>
       </c>
-      <c r="BG379" s="167"/>
+      <c r="BG379" s="101"/>
       <c r="BH379" s="5"/>
       <c r="BI379" s="5"/>
       <c r="BJ379" s="4" t="s">
@@ -46508,13 +46445,13 @@
       <c r="BD380" s="107">
         <v>25.2</v>
       </c>
-      <c r="BE380" s="138">
+      <c r="BE380" s="107">
         <v>1005</v>
       </c>
-      <c r="BF380" s="138">
+      <c r="BF380" s="107">
         <v>41</v>
       </c>
-      <c r="BG380" s="129"/>
+      <c r="BG380" s="5"/>
       <c r="BH380" s="5"/>
       <c r="BI380" s="5"/>
       <c r="BJ380" s="4" t="s">
@@ -46607,13 +46544,13 @@
       <c r="BD381" s="109">
         <v>25.2</v>
       </c>
-      <c r="BE381" s="158">
+      <c r="BE381" s="109">
         <v>1005</v>
       </c>
-      <c r="BF381" s="158">
+      <c r="BF381" s="109">
         <v>41</v>
       </c>
-      <c r="BG381" s="167"/>
+      <c r="BG381" s="101"/>
       <c r="BH381" s="5"/>
       <c r="BI381" s="5"/>
       <c r="BJ381" s="4" t="s">
@@ -46712,13 +46649,13 @@
       <c r="BD382" s="109">
         <v>25.2</v>
       </c>
-      <c r="BE382" s="158">
+      <c r="BE382" s="109">
         <v>1005</v>
       </c>
-      <c r="BF382" s="158">
+      <c r="BF382" s="109">
         <v>41</v>
       </c>
-      <c r="BG382" s="167"/>
+      <c r="BG382" s="101"/>
       <c r="BH382" s="5"/>
       <c r="BI382" s="5"/>
       <c r="BJ382" s="4" t="s">
@@ -46817,13 +46754,13 @@
       <c r="BD383" s="109">
         <v>25.2</v>
       </c>
-      <c r="BE383" s="158">
+      <c r="BE383" s="109">
         <v>1005</v>
       </c>
-      <c r="BF383" s="158">
+      <c r="BF383" s="109">
         <v>41</v>
       </c>
-      <c r="BG383" s="167"/>
+      <c r="BG383" s="101"/>
       <c r="BH383" s="5"/>
       <c r="BI383" s="5"/>
       <c r="BJ383" s="4" t="s">
@@ -46922,13 +46859,13 @@
       <c r="BD384" s="107">
         <v>25.2</v>
       </c>
-      <c r="BE384" s="138">
+      <c r="BE384" s="107">
         <v>1005</v>
       </c>
-      <c r="BF384" s="138">
+      <c r="BF384" s="107">
         <v>41</v>
       </c>
-      <c r="BG384" s="129"/>
+      <c r="BG384" s="5"/>
       <c r="BH384" s="5"/>
       <c r="BI384" s="5"/>
       <c r="BJ384" s="4" t="s">
@@ -47027,13 +46964,13 @@
       <c r="BD385" s="109">
         <v>25.2</v>
       </c>
-      <c r="BE385" s="158">
+      <c r="BE385" s="109">
         <v>1005</v>
       </c>
-      <c r="BF385" s="158">
+      <c r="BF385" s="109">
         <v>41</v>
       </c>
-      <c r="BG385" s="167"/>
+      <c r="BG385" s="101"/>
       <c r="BH385" s="5"/>
       <c r="BI385" s="5"/>
       <c r="BJ385" s="4" t="s">
@@ -47132,13 +47069,13 @@
       <c r="BD386" s="109">
         <v>25.2</v>
       </c>
-      <c r="BE386" s="158">
+      <c r="BE386" s="109">
         <v>1005</v>
       </c>
-      <c r="BF386" s="158">
+      <c r="BF386" s="109">
         <v>41</v>
       </c>
-      <c r="BG386" s="167"/>
+      <c r="BG386" s="101"/>
       <c r="BH386" s="5"/>
       <c r="BI386" s="5"/>
       <c r="BJ386" s="4" t="s">
@@ -47237,13 +47174,13 @@
       <c r="BD387" s="109">
         <v>25.2</v>
       </c>
-      <c r="BE387" s="158">
+      <c r="BE387" s="109">
         <v>1005</v>
       </c>
-      <c r="BF387" s="158">
+      <c r="BF387" s="109">
         <v>41</v>
       </c>
-      <c r="BG387" s="167"/>
+      <c r="BG387" s="101"/>
       <c r="BH387" s="5"/>
       <c r="BI387" s="5"/>
       <c r="BJ387" s="4" t="s">
@@ -47342,13 +47279,13 @@
       <c r="BD388" s="107">
         <v>25.2</v>
       </c>
-      <c r="BE388" s="138">
+      <c r="BE388" s="107">
         <v>1005</v>
       </c>
-      <c r="BF388" s="138">
+      <c r="BF388" s="107">
         <v>41</v>
       </c>
-      <c r="BG388" s="129"/>
+      <c r="BG388" s="5"/>
       <c r="BH388" s="5"/>
       <c r="BI388" s="5"/>
       <c r="BJ388" s="4" t="s">
@@ -47447,13 +47384,13 @@
       <c r="BD389" s="109">
         <v>25.2</v>
       </c>
-      <c r="BE389" s="158">
+      <c r="BE389" s="109">
         <v>1005</v>
       </c>
-      <c r="BF389" s="158">
+      <c r="BF389" s="109">
         <v>41</v>
       </c>
-      <c r="BG389" s="167"/>
+      <c r="BG389" s="101"/>
       <c r="BH389" s="5"/>
       <c r="BI389" s="5"/>
       <c r="BJ389" s="4" t="s">
@@ -47552,13 +47489,13 @@
       <c r="BD390" s="109">
         <v>25.2</v>
       </c>
-      <c r="BE390" s="158">
+      <c r="BE390" s="109">
         <v>1005</v>
       </c>
-      <c r="BF390" s="158">
+      <c r="BF390" s="109">
         <v>41</v>
       </c>
-      <c r="BG390" s="167"/>
+      <c r="BG390" s="101"/>
       <c r="BH390" s="5"/>
       <c r="BI390" s="5"/>
       <c r="BJ390" s="4" t="s">
@@ -47655,13 +47592,13 @@
       <c r="BD391" s="109">
         <v>25.1</v>
       </c>
-      <c r="BE391" s="158">
+      <c r="BE391" s="109">
         <v>1010</v>
       </c>
-      <c r="BF391" s="158">
+      <c r="BF391" s="109">
         <v>47.7</v>
       </c>
-      <c r="BG391" s="129"/>
+      <c r="BG391" s="5"/>
       <c r="BH391" s="5"/>
       <c r="BI391" s="5"/>
       <c r="BJ391" s="4" t="s">
@@ -47758,13 +47695,13 @@
       <c r="BD392" s="109">
         <v>25.1</v>
       </c>
-      <c r="BE392" s="158">
+      <c r="BE392" s="109">
         <v>1010</v>
       </c>
-      <c r="BF392" s="158">
+      <c r="BF392" s="109">
         <v>47.7</v>
       </c>
-      <c r="BG392" s="129"/>
+      <c r="BG392" s="5"/>
       <c r="BH392" s="5"/>
       <c r="BI392" s="5"/>
       <c r="BJ392" s="4" t="s">
@@ -47861,13 +47798,13 @@
       <c r="BD393" s="109">
         <v>25.1</v>
       </c>
-      <c r="BE393" s="158">
+      <c r="BE393" s="109">
         <v>1010</v>
       </c>
-      <c r="BF393" s="158">
+      <c r="BF393" s="109">
         <v>47.7</v>
       </c>
-      <c r="BG393" s="129"/>
+      <c r="BG393" s="5"/>
       <c r="BH393" s="5"/>
       <c r="BI393" s="5"/>
       <c r="BJ393" s="4" t="s">
@@ -47964,13 +47901,13 @@
       <c r="BD394" s="109">
         <v>25.1</v>
       </c>
-      <c r="BE394" s="158">
+      <c r="BE394" s="109">
         <v>1010</v>
       </c>
-      <c r="BF394" s="158">
+      <c r="BF394" s="109">
         <v>47.7</v>
       </c>
-      <c r="BG394" s="167"/>
+      <c r="BG394" s="101"/>
       <c r="BH394" s="5"/>
       <c r="BI394" s="5"/>
       <c r="BJ394" s="4" t="s">
@@ -48002,8 +47939,8 @@
       <c r="M395" s="109">
         <v>0.15029999999999999</v>
       </c>
-      <c r="N395" s="134"/>
-      <c r="O395" s="134"/>
+      <c r="N395" s="10"/>
+      <c r="O395" s="10"/>
       <c r="P395" s="109">
         <v>60.5</v>
       </c>
@@ -48067,13 +48004,13 @@
       <c r="BD395" s="109">
         <v>25.9</v>
       </c>
-      <c r="BE395" s="158">
+      <c r="BE395" s="109">
         <v>1010</v>
       </c>
-      <c r="BF395" s="158">
+      <c r="BF395" s="109">
         <v>47</v>
       </c>
-      <c r="BG395" s="129"/>
+      <c r="BG395" s="5"/>
       <c r="BH395" s="5"/>
       <c r="BI395" s="5"/>
       <c r="BJ395" s="4" t="s">
@@ -48105,8 +48042,8 @@
       <c r="M396" s="109">
         <v>0.1452</v>
       </c>
-      <c r="N396" s="134"/>
-      <c r="O396" s="134"/>
+      <c r="N396" s="10"/>
+      <c r="O396" s="10"/>
       <c r="P396" s="109">
         <v>60.4</v>
       </c>
@@ -48170,13 +48107,13 @@
       <c r="BD396" s="109">
         <v>25.9</v>
       </c>
-      <c r="BE396" s="158">
+      <c r="BE396" s="109">
         <v>1010</v>
       </c>
-      <c r="BF396" s="158">
+      <c r="BF396" s="109">
         <v>47</v>
       </c>
-      <c r="BG396" s="129"/>
+      <c r="BG396" s="5"/>
       <c r="BH396" s="5"/>
       <c r="BI396" s="5"/>
       <c r="BJ396" s="4" t="s">
@@ -48378,10 +48315,10 @@
       <c r="BD398" s="109">
         <v>25.9</v>
       </c>
-      <c r="BE398" s="158">
+      <c r="BE398" s="109">
         <v>1010</v>
       </c>
-      <c r="BF398" s="158">
+      <c r="BF398" s="109">
         <v>47</v>
       </c>
       <c r="BG398" s="101"/>
@@ -48483,10 +48420,10 @@
       <c r="BD399" s="109">
         <v>26.4</v>
       </c>
-      <c r="BE399" s="158">
+      <c r="BE399" s="109">
         <v>1010</v>
       </c>
-      <c r="BF399" s="158">
+      <c r="BF399" s="109">
         <v>46.5</v>
       </c>
       <c r="BG399" s="5"/>
@@ -48586,10 +48523,10 @@
       <c r="BD400" s="109">
         <v>26.4</v>
       </c>
-      <c r="BE400" s="158">
+      <c r="BE400" s="109">
         <v>1010</v>
       </c>
-      <c r="BF400" s="158">
+      <c r="BF400" s="109">
         <v>46.5</v>
       </c>
       <c r="BG400" s="5"/>
@@ -48689,10 +48626,10 @@
       <c r="BD401" s="109">
         <v>26.4</v>
       </c>
-      <c r="BE401" s="158">
+      <c r="BE401" s="109">
         <v>1010</v>
       </c>
-      <c r="BF401" s="158">
+      <c r="BF401" s="109">
         <v>46.5</v>
       </c>
       <c r="BG401" s="5"/>
@@ -48792,10 +48729,10 @@
       <c r="BD402" s="109">
         <v>26.4</v>
       </c>
-      <c r="BE402" s="158">
+      <c r="BE402" s="109">
         <v>1010</v>
       </c>
-      <c r="BF402" s="158">
+      <c r="BF402" s="109">
         <v>46.5</v>
       </c>
       <c r="BG402" s="5"/>
@@ -48826,7 +48763,7 @@
       <c r="G403" s="10"/>
       <c r="H403" s="8"/>
       <c r="K403" s="10"/>
-      <c r="L403" s="134"/>
+      <c r="L403" s="10"/>
       <c r="M403" s="109">
         <v>0.15570000000000001</v>
       </c>
@@ -48893,13 +48830,13 @@
       <c r="BD403" s="109">
         <v>26.4</v>
       </c>
-      <c r="BE403" s="158">
+      <c r="BE403" s="109">
         <v>1010</v>
       </c>
-      <c r="BF403" s="158">
+      <c r="BF403" s="109">
         <v>46.5</v>
       </c>
-      <c r="BG403" s="129"/>
+      <c r="BG403" s="5"/>
       <c r="BH403" s="5"/>
       <c r="BI403" s="5"/>
       <c r="BJ403" s="4" t="s">
@@ -48927,7 +48864,7 @@
       <c r="G404" s="10"/>
       <c r="H404" s="8"/>
       <c r="K404" s="10"/>
-      <c r="L404" s="134"/>
+      <c r="L404" s="10"/>
       <c r="M404" s="109">
         <v>0.15909999999999999</v>
       </c>
@@ -48994,13 +48931,13 @@
       <c r="BD404" s="109">
         <v>26.4</v>
       </c>
-      <c r="BE404" s="158">
+      <c r="BE404" s="109">
         <v>1010</v>
       </c>
-      <c r="BF404" s="158">
+      <c r="BF404" s="109">
         <v>46.5</v>
       </c>
-      <c r="BG404" s="129"/>
+      <c r="BG404" s="5"/>
       <c r="BH404" s="5"/>
       <c r="BI404" s="5" t="s">
         <v>477</v>
@@ -49030,7 +48967,7 @@
       <c r="G405" s="10"/>
       <c r="H405" s="8"/>
       <c r="K405" s="10"/>
-      <c r="L405" s="134"/>
+      <c r="L405" s="10"/>
       <c r="M405" s="109">
         <v>0.15759999999999999</v>
       </c>
@@ -49097,13 +49034,13 @@
       <c r="BD405" s="109">
         <v>26.4</v>
       </c>
-      <c r="BE405" s="158">
+      <c r="BE405" s="109">
         <v>1010</v>
       </c>
-      <c r="BF405" s="158">
+      <c r="BF405" s="109">
         <v>46.5</v>
       </c>
-      <c r="BG405" s="129"/>
+      <c r="BG405" s="5"/>
       <c r="BH405" s="5"/>
       <c r="BI405" s="5"/>
       <c r="BJ405" s="4" t="s">
@@ -49131,7 +49068,7 @@
       <c r="G406" s="10"/>
       <c r="H406" s="8"/>
       <c r="K406" s="10"/>
-      <c r="L406" s="134"/>
+      <c r="L406" s="10"/>
       <c r="M406" s="109">
         <v>0.15809999999999999</v>
       </c>
@@ -49198,13 +49135,13 @@
       <c r="BD406" s="109">
         <v>26.4</v>
       </c>
-      <c r="BE406" s="158">
+      <c r="BE406" s="109">
         <v>1010</v>
       </c>
-      <c r="BF406" s="158">
+      <c r="BF406" s="109">
         <v>46.5</v>
       </c>
-      <c r="BG406" s="129"/>
+      <c r="BG406" s="5"/>
       <c r="BH406" s="5"/>
       <c r="BI406" s="5"/>
       <c r="BJ406" s="4" t="s">
@@ -49299,13 +49236,13 @@
       <c r="BD407" s="109">
         <v>26.7</v>
       </c>
-      <c r="BE407" s="158">
+      <c r="BE407" s="109">
         <v>1010</v>
       </c>
-      <c r="BF407" s="158">
+      <c r="BF407" s="109">
         <v>46.7</v>
       </c>
-      <c r="BG407" s="129"/>
+      <c r="BG407" s="5"/>
       <c r="BH407" s="5"/>
       <c r="BI407" s="5"/>
       <c r="BJ407" s="4" t="s">
@@ -49400,13 +49337,13 @@
       <c r="BD408" s="109">
         <v>26.7</v>
       </c>
-      <c r="BE408" s="158">
+      <c r="BE408" s="109">
         <v>1010</v>
       </c>
-      <c r="BF408" s="158">
+      <c r="BF408" s="109">
         <v>46.7</v>
       </c>
-      <c r="BG408" s="129"/>
+      <c r="BG408" s="5"/>
       <c r="BH408" s="5"/>
       <c r="BI408" s="5"/>
       <c r="BJ408" s="4" t="s">
@@ -49501,13 +49438,13 @@
       <c r="BD409" s="109">
         <v>26.7</v>
       </c>
-      <c r="BE409" s="158">
+      <c r="BE409" s="109">
         <v>1010</v>
       </c>
-      <c r="BF409" s="158">
+      <c r="BF409" s="109">
         <v>46.7</v>
       </c>
-      <c r="BG409" s="129"/>
+      <c r="BG409" s="5"/>
       <c r="BH409" s="5"/>
       <c r="BI409" s="5"/>
       <c r="BJ409" s="4" t="s">
@@ -49602,13 +49539,13 @@
       <c r="BD410" s="109">
         <v>26.7</v>
       </c>
-      <c r="BE410" s="158">
+      <c r="BE410" s="109">
         <v>1010</v>
       </c>
-      <c r="BF410" s="158">
+      <c r="BF410" s="109">
         <v>46.7</v>
       </c>
-      <c r="BG410" s="129"/>
+      <c r="BG410" s="5"/>
       <c r="BH410" s="5"/>
       <c r="BI410" s="5"/>
       <c r="BJ410" s="4" t="s">
@@ -52721,13 +52658,13 @@
       <c r="BD440" s="5">
         <v>26.4</v>
       </c>
-      <c r="BE440" s="129">
+      <c r="BE440" s="5">
         <v>1008</v>
       </c>
-      <c r="BF440" s="160">
+      <c r="BF440" s="83">
         <v>44.4</v>
       </c>
-      <c r="BG440" s="160"/>
+      <c r="BG440" s="83"/>
       <c r="BH440" s="5"/>
       <c r="BI440" s="5"/>
       <c r="BJ440" s="4" t="s">
@@ -52827,13 +52764,13 @@
       <c r="BD441" s="107">
         <v>25.5</v>
       </c>
-      <c r="BE441" s="138">
+      <c r="BE441" s="107">
         <v>1012</v>
       </c>
-      <c r="BF441" s="138">
+      <c r="BF441" s="107">
         <v>39.4</v>
       </c>
-      <c r="BG441" s="160"/>
+      <c r="BG441" s="83"/>
       <c r="BH441" s="5"/>
       <c r="BI441" s="5"/>
       <c r="BJ441" s="4" t="s">
@@ -52933,13 +52870,13 @@
       <c r="BD442" s="107">
         <v>25.5</v>
       </c>
-      <c r="BE442" s="138">
+      <c r="BE442" s="107">
         <v>1012</v>
       </c>
-      <c r="BF442" s="138">
+      <c r="BF442" s="107">
         <v>39.4</v>
       </c>
-      <c r="BG442" s="159"/>
+      <c r="BG442" s="114"/>
       <c r="BH442" s="5"/>
       <c r="BI442" s="5"/>
       <c r="BJ442" s="4" t="s">
@@ -53039,13 +52976,13 @@
       <c r="BD443" s="107">
         <v>25.5</v>
       </c>
-      <c r="BE443" s="138">
+      <c r="BE443" s="107">
         <v>1012</v>
       </c>
-      <c r="BF443" s="138">
+      <c r="BF443" s="107">
         <v>39.4</v>
       </c>
-      <c r="BG443" s="159"/>
+      <c r="BG443" s="114"/>
       <c r="BH443" s="5"/>
       <c r="BI443" s="5"/>
       <c r="BJ443" s="4" t="s">
@@ -53145,13 +53082,13 @@
       <c r="BD444" s="107">
         <v>25.5</v>
       </c>
-      <c r="BE444" s="138">
+      <c r="BE444" s="107">
         <v>1012</v>
       </c>
-      <c r="BF444" s="138">
+      <c r="BF444" s="107">
         <v>39.4</v>
       </c>
-      <c r="BG444" s="159"/>
+      <c r="BG444" s="114"/>
       <c r="BH444" s="5"/>
       <c r="BI444" s="5"/>
       <c r="BJ444" s="4" t="s">
@@ -53256,7 +53193,7 @@
       <c r="BE445" s="108">
         <v>1012</v>
       </c>
-      <c r="BF445" s="138">
+      <c r="BF445" s="107">
         <v>39.4</v>
       </c>
       <c r="BG445" s="106"/>
@@ -53364,7 +53301,7 @@
       <c r="BE446" s="108">
         <v>1012</v>
       </c>
-      <c r="BF446" s="138">
+      <c r="BF446" s="107">
         <v>39.4</v>
       </c>
       <c r="BG446" s="106"/>
@@ -53400,7 +53337,7 @@
       <c r="K447" s="20">
         <v>507</v>
       </c>
-      <c r="L447" s="135">
+      <c r="L447" s="25">
         <v>0.155</v>
       </c>
       <c r="M447" s="22">
@@ -53472,7 +53409,7 @@
       <c r="BE447" s="108">
         <v>1012</v>
       </c>
-      <c r="BF447" s="138">
+      <c r="BF447" s="107">
         <v>39.4</v>
       </c>
       <c r="BG447" s="106"/>
@@ -53510,7 +53447,7 @@
       <c r="K448" s="20">
         <v>507</v>
       </c>
-      <c r="L448" s="135">
+      <c r="L448" s="25">
         <v>0.154</v>
       </c>
       <c r="M448" s="22">
@@ -53582,7 +53519,7 @@
       <c r="BE448" s="108">
         <v>1012</v>
       </c>
-      <c r="BF448" s="138">
+      <c r="BF448" s="107">
         <v>39.4</v>
       </c>
       <c r="BG448" s="106"/>
@@ -53618,7 +53555,7 @@
       <c r="K449" s="20">
         <v>507</v>
       </c>
-      <c r="L449" s="135">
+      <c r="L449" s="25">
         <v>0.14899999999999999</v>
       </c>
       <c r="M449" s="22">
@@ -53690,7 +53627,7 @@
       <c r="BE449" s="118">
         <v>1012</v>
       </c>
-      <c r="BF449" s="138">
+      <c r="BF449" s="107">
         <v>40</v>
       </c>
       <c r="BG449" s="119"/>
@@ -53726,7 +53663,7 @@
       <c r="K450" s="20">
         <v>507</v>
       </c>
-      <c r="L450" s="135">
+      <c r="L450" s="25">
         <v>0.15</v>
       </c>
       <c r="M450" s="22">
@@ -53798,7 +53735,7 @@
       <c r="BE450" s="108">
         <v>1012</v>
       </c>
-      <c r="BF450" s="138">
+      <c r="BF450" s="107">
         <v>40</v>
       </c>
       <c r="BG450" s="106"/>
@@ -53834,7 +53771,7 @@
       <c r="K451" s="20">
         <v>507</v>
       </c>
-      <c r="L451" s="135">
+      <c r="L451" s="25">
         <v>0.155</v>
       </c>
       <c r="M451" s="22">
@@ -53906,7 +53843,7 @@
       <c r="BE451" s="108">
         <v>1012</v>
       </c>
-      <c r="BF451" s="138">
+      <c r="BF451" s="107">
         <v>40</v>
       </c>
       <c r="BG451" s="106"/>
@@ -53942,7 +53879,7 @@
       <c r="K452" s="20">
         <v>507</v>
       </c>
-      <c r="L452" s="135">
+      <c r="L452" s="25">
         <v>0.156</v>
       </c>
       <c r="M452" s="22">
@@ -54014,7 +53951,7 @@
       <c r="BE452" s="108">
         <v>1012</v>
       </c>
-      <c r="BF452" s="138">
+      <c r="BF452" s="107">
         <v>40</v>
       </c>
       <c r="BG452" s="106"/>
@@ -54127,7 +54064,7 @@
       <c r="BE453" s="108">
         <v>1012</v>
       </c>
-      <c r="BF453" s="138">
+      <c r="BF453" s="107">
         <v>40</v>
       </c>
       <c r="BG453" s="106"/>
@@ -54240,7 +54177,7 @@
       <c r="BE454" s="108">
         <v>1012</v>
       </c>
-      <c r="BF454" s="138">
+      <c r="BF454" s="107">
         <v>40</v>
       </c>
       <c r="BG454" s="106"/>
@@ -54353,7 +54290,7 @@
       <c r="BE455" s="118">
         <v>1012</v>
       </c>
-      <c r="BF455" s="138">
+      <c r="BF455" s="107">
         <v>40</v>
       </c>
       <c r="BG455" s="119"/>
@@ -54466,7 +54403,7 @@
       <c r="BE456" s="108">
         <v>1012</v>
       </c>
-      <c r="BF456" s="138">
+      <c r="BF456" s="107">
         <v>40</v>
       </c>
       <c r="BG456" s="106"/>
@@ -54579,7 +54516,7 @@
       <c r="BE457" s="108">
         <v>1011</v>
       </c>
-      <c r="BF457" s="138">
+      <c r="BF457" s="107">
         <v>40</v>
       </c>
       <c r="BG457" s="106"/>
@@ -54692,7 +54629,7 @@
       <c r="BE458" s="108">
         <v>1011</v>
       </c>
-      <c r="BF458" s="138">
+      <c r="BF458" s="107">
         <v>40</v>
       </c>
       <c r="BG458" s="106"/>
@@ -54803,7 +54740,7 @@
       <c r="BE459" s="108">
         <v>1011</v>
       </c>
-      <c r="BF459" s="138">
+      <c r="BF459" s="107">
         <v>40</v>
       </c>
       <c r="BG459" s="106"/>
@@ -54916,7 +54853,7 @@
       <c r="BE460" s="108">
         <v>1011</v>
       </c>
-      <c r="BF460" s="138">
+      <c r="BF460" s="107">
         <v>40</v>
       </c>
       <c r="BG460" s="106"/>
@@ -55029,7 +54966,7 @@
       <c r="BE461" s="118">
         <v>1011</v>
       </c>
-      <c r="BF461" s="138">
+      <c r="BF461" s="107">
         <v>39.6</v>
       </c>
       <c r="BG461" s="119"/>
@@ -55140,7 +55077,7 @@
       <c r="BE462" s="108">
         <v>1011</v>
       </c>
-      <c r="BF462" s="138">
+      <c r="BF462" s="107">
         <v>39.6</v>
       </c>
       <c r="BG462" s="106"/>
@@ -55155,109 +55092,109 @@
       <c r="A463" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B463" s="129" t="s">
+      <c r="B463" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C463" s="4">
         <v>45239</v>
       </c>
-      <c r="D463" s="130">
+      <c r="D463" s="20">
         <v>5</v>
       </c>
-      <c r="E463" s="131" t="s">
+      <c r="E463" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="F463" s="134"/>
-      <c r="G463" s="134"/>
-      <c r="H463" s="128">
+      <c r="F463" s="10"/>
+      <c r="G463" s="10"/>
+      <c r="H463" s="8">
         <v>0.17080000000000001</v>
       </c>
-      <c r="I463" s="128">
+      <c r="I463" s="8">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="J463" s="128">
+      <c r="J463" s="8">
         <v>1.2515000000000001</v>
       </c>
-      <c r="K463" s="130">
+      <c r="K463" s="20">
         <v>504</v>
       </c>
-      <c r="L463" s="135"/>
-      <c r="M463" s="139">
+      <c r="L463" s="25"/>
+      <c r="M463" s="120">
         <v>0.1711</v>
       </c>
-      <c r="N463" s="134"/>
-      <c r="O463" s="134"/>
-      <c r="P463" s="138">
+      <c r="N463" s="10"/>
+      <c r="O463" s="10"/>
+      <c r="P463" s="107">
         <v>65.400000000000006</v>
       </c>
-      <c r="Q463" s="138">
+      <c r="Q463" s="107">
         <v>605</v>
       </c>
-      <c r="R463" s="147">
+      <c r="R463" s="112">
         <v>750</v>
       </c>
-      <c r="S463" s="129" t="s">
+      <c r="S463" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="T463" s="129" t="s">
+      <c r="T463" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="U463" s="129"/>
-      <c r="V463" s="129" t="s">
+      <c r="U463" s="5"/>
+      <c r="V463" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="W463" s="129"/>
-      <c r="X463" s="129"/>
-      <c r="Y463" s="129" t="s">
+      <c r="W463" s="5"/>
+      <c r="X463" s="5"/>
+      <c r="Y463" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="Z463" s="129"/>
-      <c r="AA463" s="129"/>
-      <c r="AB463" s="129"/>
-      <c r="AC463" s="129"/>
-      <c r="AD463" s="129"/>
-      <c r="AE463" s="129"/>
-      <c r="AF463" s="129"/>
-      <c r="AG463" s="129"/>
-      <c r="AH463" s="129"/>
-      <c r="AI463" s="129"/>
-      <c r="AJ463" s="129"/>
-      <c r="AK463" s="129"/>
-      <c r="AL463" s="129"/>
-      <c r="AM463" s="129"/>
-      <c r="AN463" s="129"/>
-      <c r="AO463" s="129"/>
-      <c r="AP463" s="129"/>
-      <c r="AQ463" s="129"/>
-      <c r="AR463" s="129"/>
-      <c r="AS463" s="129"/>
-      <c r="AT463" s="129"/>
-      <c r="AU463" s="129"/>
-      <c r="AV463" s="129"/>
-      <c r="AW463" s="129"/>
-      <c r="AX463" s="129"/>
-      <c r="AY463" s="129">
+      <c r="Z463" s="5"/>
+      <c r="AA463" s="5"/>
+      <c r="AB463" s="5"/>
+      <c r="AC463" s="5"/>
+      <c r="AD463" s="5"/>
+      <c r="AE463" s="5"/>
+      <c r="AF463" s="5"/>
+      <c r="AG463" s="5"/>
+      <c r="AH463" s="5"/>
+      <c r="AI463" s="5"/>
+      <c r="AJ463" s="5"/>
+      <c r="AK463" s="5"/>
+      <c r="AL463" s="5"/>
+      <c r="AM463" s="5"/>
+      <c r="AN463" s="5"/>
+      <c r="AO463" s="5"/>
+      <c r="AP463" s="5"/>
+      <c r="AQ463" s="5"/>
+      <c r="AR463" s="5"/>
+      <c r="AS463" s="5"/>
+      <c r="AT463" s="5"/>
+      <c r="AU463" s="5"/>
+      <c r="AV463" s="5"/>
+      <c r="AW463" s="5"/>
+      <c r="AX463" s="5"/>
+      <c r="AY463" s="5">
         <v>70</v>
       </c>
-      <c r="AZ463" s="129"/>
-      <c r="BA463" s="129">
+      <c r="AZ463" s="5"/>
+      <c r="BA463" s="5">
         <v>111.6</v>
       </c>
-      <c r="BB463" s="129"/>
-      <c r="BC463" s="129"/>
+      <c r="BB463" s="5"/>
+      <c r="BC463" s="5"/>
       <c r="BD463" s="107">
         <v>26.7</v>
       </c>
       <c r="BE463" s="108">
         <v>1011</v>
       </c>
-      <c r="BF463" s="138">
+      <c r="BF463" s="107">
         <v>39.6</v>
       </c>
       <c r="BG463" s="106"/>
       <c r="BH463" s="5"/>
       <c r="BI463" s="5"/>
-      <c r="BJ463" s="131" t="s">
+      <c r="BJ463" s="4" t="s">
         <v>741</v>
       </c>
       <c r="BM463"/>
@@ -55362,7 +55299,7 @@
       <c r="BE464" s="108">
         <v>1011</v>
       </c>
-      <c r="BF464" s="138">
+      <c r="BF464" s="107">
         <v>39.6</v>
       </c>
       <c r="BG464" s="106"/>
@@ -55470,10 +55407,10 @@
       <c r="BD465" s="107">
         <v>24.5</v>
       </c>
-      <c r="BE465" s="138">
+      <c r="BE465" s="107">
         <v>1013</v>
       </c>
-      <c r="BF465" s="138">
+      <c r="BF465" s="107">
         <v>47.7</v>
       </c>
       <c r="BG465" s="106"/>
@@ -55585,10 +55522,10 @@
       <c r="BD466" s="107">
         <v>24.5</v>
       </c>
-      <c r="BE466" s="138">
+      <c r="BE466" s="107">
         <v>1013</v>
       </c>
-      <c r="BF466" s="138">
+      <c r="BF466" s="107">
         <v>47.7</v>
       </c>
       <c r="BG466" s="106"/>
@@ -55700,10 +55637,10 @@
       <c r="BD467" s="107">
         <v>24.5</v>
       </c>
-      <c r="BE467" s="138">
+      <c r="BE467" s="107">
         <v>1013</v>
       </c>
-      <c r="BF467" s="138">
+      <c r="BF467" s="107">
         <v>47.7</v>
       </c>
       <c r="BG467" s="119"/>
@@ -55813,10 +55750,10 @@
       <c r="BD468" s="107">
         <v>24.5</v>
       </c>
-      <c r="BE468" s="138">
+      <c r="BE468" s="107">
         <v>1013</v>
       </c>
-      <c r="BF468" s="138">
+      <c r="BF468" s="107">
         <v>47.7</v>
       </c>
       <c r="BG468" s="106"/>
@@ -55926,10 +55863,10 @@
       <c r="BD469" s="107">
         <v>24.9</v>
       </c>
-      <c r="BE469" s="138">
+      <c r="BE469" s="107">
         <v>1012</v>
       </c>
-      <c r="BF469" s="138">
+      <c r="BF469" s="107">
         <v>45.5</v>
       </c>
       <c r="BG469" s="106"/>
@@ -56039,10 +55976,10 @@
       <c r="BD470" s="107">
         <v>24.9</v>
       </c>
-      <c r="BE470" s="138">
+      <c r="BE470" s="107">
         <v>1012</v>
       </c>
-      <c r="BF470" s="138">
+      <c r="BF470" s="107">
         <v>45.5</v>
       </c>
       <c r="BG470" s="106"/>
@@ -56152,10 +56089,10 @@
       <c r="BD471" s="107">
         <v>24.9</v>
       </c>
-      <c r="BE471" s="138">
+      <c r="BE471" s="107">
         <v>1012</v>
       </c>
-      <c r="BF471" s="138">
+      <c r="BF471" s="107">
         <v>45.5</v>
       </c>
       <c r="BG471" s="119"/>
@@ -56263,7 +56200,7 @@
       <c r="BD472" s="107">
         <v>24.9</v>
       </c>
-      <c r="BE472" s="138">
+      <c r="BE472" s="107">
         <v>1012</v>
       </c>
       <c r="BF472" s="107">
@@ -56374,7 +56311,7 @@
       <c r="BD473" s="107">
         <v>24.9</v>
       </c>
-      <c r="BE473" s="138">
+      <c r="BE473" s="107">
         <v>1012</v>
       </c>
       <c r="BF473" s="107">
@@ -56487,7 +56424,7 @@
       <c r="BD474" s="107">
         <v>24.9</v>
       </c>
-      <c r="BE474" s="138">
+      <c r="BE474" s="107">
         <v>1012</v>
       </c>
       <c r="BF474" s="107">
@@ -56600,7 +56537,7 @@
       <c r="BD475" s="107">
         <v>24.9</v>
       </c>
-      <c r="BE475" s="138">
+      <c r="BE475" s="107">
         <v>1012</v>
       </c>
       <c r="BF475" s="107">
@@ -56731,89 +56668,89 @@
       <c r="A477" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B477" s="129" t="s">
+      <c r="B477" s="5" t="s">
         <v>301</v>
       </c>
       <c r="C477" s="4">
         <v>45243</v>
       </c>
-      <c r="D477" s="128">
+      <c r="D477" s="8">
         <v>1</v>
       </c>
       <c r="E477" s="104"/>
-      <c r="F477" s="134"/>
-      <c r="G477" s="134"/>
-      <c r="H477" s="128">
+      <c r="F477" s="10"/>
+      <c r="G477" s="10"/>
+      <c r="H477" s="8">
         <v>0.15759999999999999</v>
       </c>
-      <c r="I477" s="128">
+      <c r="I477" s="8">
         <v>1E-3</v>
       </c>
-      <c r="J477" s="128">
+      <c r="J477" s="8">
         <v>1.272</v>
       </c>
-      <c r="K477" s="134"/>
-      <c r="L477" s="134"/>
-      <c r="M477" s="138">
+      <c r="K477" s="10"/>
+      <c r="L477" s="10"/>
+      <c r="M477" s="107">
         <v>0.1605</v>
       </c>
-      <c r="N477" s="134"/>
-      <c r="O477" s="134"/>
-      <c r="P477" s="143">
+      <c r="N477" s="10"/>
+      <c r="O477" s="10"/>
+      <c r="P477" s="121">
         <v>60.6</v>
       </c>
-      <c r="Q477" s="138">
+      <c r="Q477" s="107">
         <v>454</v>
       </c>
-      <c r="R477" s="147">
+      <c r="R477" s="112">
         <v>750</v>
       </c>
       <c r="S477" s="56"/>
       <c r="T477" s="56"/>
-      <c r="U477" s="150"/>
-      <c r="V477" s="150"/>
+      <c r="U477" s="56"/>
+      <c r="V477" s="56"/>
       <c r="W477" s="56"/>
       <c r="X477" s="56"/>
-      <c r="Y477" s="150"/>
-      <c r="Z477" s="150"/>
-      <c r="AA477" s="150"/>
-      <c r="AB477" s="150"/>
-      <c r="AC477" s="150"/>
-      <c r="AD477" s="150"/>
-      <c r="AE477" s="129"/>
-      <c r="AF477" s="129"/>
-      <c r="AG477" s="129"/>
-      <c r="AH477" s="129"/>
-      <c r="AI477" s="129"/>
-      <c r="AJ477" s="129"/>
-      <c r="AK477" s="129"/>
-      <c r="AL477" s="129"/>
-      <c r="AM477" s="129"/>
-      <c r="AN477" s="129"/>
-      <c r="AO477" s="129"/>
-      <c r="AP477" s="129"/>
-      <c r="AQ477" s="129"/>
-      <c r="AR477" s="129"/>
-      <c r="AS477" s="129"/>
-      <c r="AT477" s="129"/>
-      <c r="AU477" s="129"/>
-      <c r="AV477" s="129"/>
-      <c r="AW477" s="129"/>
-      <c r="AX477" s="129"/>
+      <c r="Y477" s="56"/>
+      <c r="Z477" s="56"/>
+      <c r="AA477" s="56"/>
+      <c r="AB477" s="56"/>
+      <c r="AC477" s="56"/>
+      <c r="AD477" s="56"/>
+      <c r="AE477" s="5"/>
+      <c r="AF477" s="5"/>
+      <c r="AG477" s="5"/>
+      <c r="AH477" s="5"/>
+      <c r="AI477" s="5"/>
+      <c r="AJ477" s="5"/>
+      <c r="AK477" s="5"/>
+      <c r="AL477" s="5"/>
+      <c r="AM477" s="5"/>
+      <c r="AN477" s="5"/>
+      <c r="AO477" s="5"/>
+      <c r="AP477" s="5"/>
+      <c r="AQ477" s="5"/>
+      <c r="AR477" s="5"/>
+      <c r="AS477" s="5"/>
+      <c r="AT477" s="5"/>
+      <c r="AU477" s="5"/>
+      <c r="AV477" s="5"/>
+      <c r="AW477" s="5"/>
+      <c r="AX477" s="5"/>
       <c r="AY477" s="5"/>
       <c r="AZ477" s="5"/>
       <c r="BA477" s="5">
         <v>113.4</v>
       </c>
       <c r="BB477" s="5"/>
-      <c r="BC477" s="129"/>
-      <c r="BD477" s="138">
+      <c r="BC477" s="5"/>
+      <c r="BD477" s="107">
         <v>25.1</v>
       </c>
-      <c r="BE477" s="138">
+      <c r="BE477" s="107">
         <v>1012</v>
       </c>
-      <c r="BF477" s="138">
+      <c r="BF477" s="107">
         <v>44.6</v>
       </c>
       <c r="BG477" s="119"/>
@@ -56830,89 +56767,89 @@
       <c r="A478" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B478" s="129" t="s">
+      <c r="B478" s="5" t="s">
         <v>301</v>
       </c>
       <c r="C478" s="4">
         <v>45243</v>
       </c>
-      <c r="D478" s="128">
+      <c r="D478" s="8">
         <v>2</v>
       </c>
-      <c r="E478" s="132"/>
-      <c r="F478" s="134"/>
-      <c r="G478" s="134"/>
-      <c r="H478" s="128">
+      <c r="E478" s="104"/>
+      <c r="F478" s="10"/>
+      <c r="G478" s="10"/>
+      <c r="H478" s="8">
         <v>0.15190000000000001</v>
       </c>
-      <c r="I478" s="128">
+      <c r="I478" s="8">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="J478" s="128">
+      <c r="J478" s="8">
         <v>1.272</v>
       </c>
-      <c r="K478" s="134"/>
-      <c r="L478" s="134"/>
-      <c r="M478" s="137">
+      <c r="K478" s="10"/>
+      <c r="L478" s="10"/>
+      <c r="M478" s="115">
         <v>0.156</v>
       </c>
-      <c r="N478" s="134"/>
-      <c r="O478" s="134"/>
-      <c r="P478" s="143">
+      <c r="N478" s="10"/>
+      <c r="O478" s="10"/>
+      <c r="P478" s="121">
         <v>61.4</v>
       </c>
-      <c r="Q478" s="138">
+      <c r="Q478" s="107">
         <v>459</v>
       </c>
-      <c r="R478" s="147">
+      <c r="R478" s="112">
         <v>750</v>
       </c>
-      <c r="S478" s="150"/>
-      <c r="T478" s="150"/>
-      <c r="U478" s="150"/>
-      <c r="V478" s="150"/>
-      <c r="W478" s="150"/>
-      <c r="X478" s="150"/>
-      <c r="Y478" s="150"/>
-      <c r="Z478" s="150"/>
-      <c r="AA478" s="150"/>
-      <c r="AB478" s="150"/>
-      <c r="AC478" s="150"/>
-      <c r="AD478" s="150"/>
-      <c r="AE478" s="129"/>
-      <c r="AF478" s="129"/>
-      <c r="AG478" s="129"/>
-      <c r="AH478" s="129"/>
-      <c r="AI478" s="129"/>
-      <c r="AJ478" s="129"/>
-      <c r="AK478" s="129"/>
-      <c r="AL478" s="129"/>
-      <c r="AM478" s="129"/>
-      <c r="AN478" s="129"/>
-      <c r="AO478" s="129"/>
-      <c r="AP478" s="129"/>
-      <c r="AQ478" s="129"/>
-      <c r="AR478" s="129"/>
-      <c r="AS478" s="129"/>
-      <c r="AT478" s="129"/>
-      <c r="AU478" s="129"/>
-      <c r="AV478" s="129"/>
-      <c r="AW478" s="129"/>
-      <c r="AX478" s="129"/>
-      <c r="AY478" s="129"/>
-      <c r="AZ478" s="129"/>
-      <c r="BA478" s="129">
+      <c r="S478" s="56"/>
+      <c r="T478" s="56"/>
+      <c r="U478" s="56"/>
+      <c r="V478" s="56"/>
+      <c r="W478" s="56"/>
+      <c r="X478" s="56"/>
+      <c r="Y478" s="56"/>
+      <c r="Z478" s="56"/>
+      <c r="AA478" s="56"/>
+      <c r="AB478" s="56"/>
+      <c r="AC478" s="56"/>
+      <c r="AD478" s="56"/>
+      <c r="AE478" s="5"/>
+      <c r="AF478" s="5"/>
+      <c r="AG478" s="5"/>
+      <c r="AH478" s="5"/>
+      <c r="AI478" s="5"/>
+      <c r="AJ478" s="5"/>
+      <c r="AK478" s="5"/>
+      <c r="AL478" s="5"/>
+      <c r="AM478" s="5"/>
+      <c r="AN478" s="5"/>
+      <c r="AO478" s="5"/>
+      <c r="AP478" s="5"/>
+      <c r="AQ478" s="5"/>
+      <c r="AR478" s="5"/>
+      <c r="AS478" s="5"/>
+      <c r="AT478" s="5"/>
+      <c r="AU478" s="5"/>
+      <c r="AV478" s="5"/>
+      <c r="AW478" s="5"/>
+      <c r="AX478" s="5"/>
+      <c r="AY478" s="5"/>
+      <c r="AZ478" s="5"/>
+      <c r="BA478" s="5">
         <v>113.4</v>
       </c>
-      <c r="BB478" s="129"/>
-      <c r="BC478" s="129"/>
-      <c r="BD478" s="138">
+      <c r="BB478" s="5"/>
+      <c r="BC478" s="5"/>
+      <c r="BD478" s="107">
         <v>25.1</v>
       </c>
-      <c r="BE478" s="138">
+      <c r="BE478" s="107">
         <v>1012</v>
       </c>
-      <c r="BF478" s="138">
+      <c r="BF478" s="107">
         <v>44.6</v>
       </c>
       <c r="BG478" s="106"/>
@@ -56920,7 +56857,7 @@
         <v>2096</v>
       </c>
       <c r="BI478" s="5"/>
-      <c r="BJ478" s="131" t="s">
+      <c r="BJ478" s="4" t="s">
         <v>700</v>
       </c>
       <c r="BM478"/>
@@ -56929,89 +56866,89 @@
       <c r="A479" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B479" s="129" t="s">
+      <c r="B479" s="5" t="s">
         <v>301</v>
       </c>
       <c r="C479" s="4">
         <v>45243</v>
       </c>
-      <c r="D479" s="128">
+      <c r="D479" s="8">
         <v>3</v>
       </c>
-      <c r="E479" s="132"/>
-      <c r="F479" s="134"/>
-      <c r="G479" s="134"/>
-      <c r="H479" s="128">
+      <c r="E479" s="104"/>
+      <c r="F479" s="10"/>
+      <c r="G479" s="10"/>
+      <c r="H479" s="8">
         <v>0.159</v>
       </c>
-      <c r="I479" s="128">
+      <c r="I479" s="8">
         <v>1E-4</v>
       </c>
-      <c r="J479" s="128">
+      <c r="J479" s="8">
         <v>1.272</v>
       </c>
-      <c r="K479" s="134"/>
-      <c r="L479" s="134"/>
-      <c r="M479" s="137">
+      <c r="K479" s="10"/>
+      <c r="L479" s="10"/>
+      <c r="M479" s="115">
         <v>0.159</v>
       </c>
-      <c r="N479" s="134"/>
-      <c r="O479" s="134"/>
-      <c r="P479" s="143">
+      <c r="N479" s="10"/>
+      <c r="O479" s="10"/>
+      <c r="P479" s="121">
         <v>61</v>
       </c>
-      <c r="Q479" s="138">
+      <c r="Q479" s="107">
         <v>469</v>
       </c>
-      <c r="R479" s="147">
+      <c r="R479" s="112">
         <v>750</v>
       </c>
-      <c r="S479" s="150"/>
-      <c r="T479" s="150"/>
-      <c r="U479" s="150"/>
-      <c r="V479" s="150"/>
-      <c r="W479" s="150"/>
-      <c r="X479" s="150"/>
-      <c r="Y479" s="150"/>
-      <c r="Z479" s="150"/>
-      <c r="AA479" s="150"/>
-      <c r="AB479" s="150"/>
-      <c r="AC479" s="150"/>
-      <c r="AD479" s="150"/>
-      <c r="AE479" s="129"/>
-      <c r="AF479" s="129"/>
-      <c r="AG479" s="129"/>
-      <c r="AH479" s="129"/>
-      <c r="AI479" s="129"/>
-      <c r="AJ479" s="129"/>
-      <c r="AK479" s="129"/>
-      <c r="AL479" s="129"/>
-      <c r="AM479" s="129"/>
-      <c r="AN479" s="129"/>
-      <c r="AO479" s="129"/>
-      <c r="AP479" s="129"/>
-      <c r="AQ479" s="129"/>
-      <c r="AR479" s="129"/>
-      <c r="AS479" s="129"/>
-      <c r="AT479" s="129"/>
-      <c r="AU479" s="129"/>
-      <c r="AV479" s="129"/>
-      <c r="AW479" s="129"/>
-      <c r="AX479" s="129"/>
-      <c r="AY479" s="129"/>
-      <c r="AZ479" s="129"/>
-      <c r="BA479" s="154">
+      <c r="S479" s="56"/>
+      <c r="T479" s="56"/>
+      <c r="U479" s="56"/>
+      <c r="V479" s="56"/>
+      <c r="W479" s="56"/>
+      <c r="X479" s="56"/>
+      <c r="Y479" s="56"/>
+      <c r="Z479" s="56"/>
+      <c r="AA479" s="56"/>
+      <c r="AB479" s="56"/>
+      <c r="AC479" s="56"/>
+      <c r="AD479" s="56"/>
+      <c r="AE479" s="5"/>
+      <c r="AF479" s="5"/>
+      <c r="AG479" s="5"/>
+      <c r="AH479" s="5"/>
+      <c r="AI479" s="5"/>
+      <c r="AJ479" s="5"/>
+      <c r="AK479" s="5"/>
+      <c r="AL479" s="5"/>
+      <c r="AM479" s="5"/>
+      <c r="AN479" s="5"/>
+      <c r="AO479" s="5"/>
+      <c r="AP479" s="5"/>
+      <c r="AQ479" s="5"/>
+      <c r="AR479" s="5"/>
+      <c r="AS479" s="5"/>
+      <c r="AT479" s="5"/>
+      <c r="AU479" s="5"/>
+      <c r="AV479" s="5"/>
+      <c r="AW479" s="5"/>
+      <c r="AX479" s="5"/>
+      <c r="AY479" s="5"/>
+      <c r="AZ479" s="5"/>
+      <c r="BA479" s="117">
         <v>117</v>
       </c>
-      <c r="BB479" s="129"/>
-      <c r="BC479" s="129"/>
+      <c r="BB479" s="5"/>
+      <c r="BC479" s="5"/>
       <c r="BD479" s="107">
         <v>25.1</v>
       </c>
-      <c r="BE479" s="138">
+      <c r="BE479" s="107">
         <v>1012</v>
       </c>
-      <c r="BF479" s="138">
+      <c r="BF479" s="107">
         <v>44.6</v>
       </c>
       <c r="BG479" s="106"/>
@@ -57019,7 +56956,7 @@
         <v>2096</v>
       </c>
       <c r="BI479" s="5"/>
-      <c r="BJ479" s="131" t="s">
+      <c r="BJ479" s="4" t="s">
         <v>699</v>
       </c>
       <c r="BM479"/>
@@ -57107,10 +57044,10 @@
       <c r="BD480" s="107">
         <v>25.1</v>
       </c>
-      <c r="BE480" s="138">
+      <c r="BE480" s="107">
         <v>1012</v>
       </c>
-      <c r="BF480" s="138">
+      <c r="BF480" s="107">
         <v>44.6</v>
       </c>
       <c r="BG480" s="106"/>
@@ -57206,10 +57143,10 @@
       <c r="BD481" s="107">
         <v>25.3</v>
       </c>
-      <c r="BE481" s="138">
+      <c r="BE481" s="107">
         <v>1012</v>
       </c>
-      <c r="BF481" s="138">
+      <c r="BF481" s="107">
         <v>44.3</v>
       </c>
       <c r="BG481" s="106"/>
@@ -57307,10 +57244,10 @@
       <c r="BD482" s="107">
         <v>25.3</v>
       </c>
-      <c r="BE482" s="138">
+      <c r="BE482" s="107">
         <v>1012</v>
       </c>
-      <c r="BF482" s="138">
+      <c r="BF482" s="107">
         <v>44.3</v>
       </c>
       <c r="BG482" s="106"/>
@@ -57406,10 +57343,10 @@
       <c r="BD483" s="107">
         <v>25.3</v>
       </c>
-      <c r="BE483" s="138">
+      <c r="BE483" s="107">
         <v>1012</v>
       </c>
-      <c r="BF483" s="138">
+      <c r="BF483" s="107">
         <v>44.3</v>
       </c>
       <c r="BG483" s="106"/>
@@ -57505,10 +57442,10 @@
       <c r="BD484" s="107">
         <v>25.6</v>
       </c>
-      <c r="BE484" s="138">
+      <c r="BE484" s="107">
         <v>1011</v>
       </c>
-      <c r="BF484" s="138">
+      <c r="BF484" s="107">
         <v>44.1</v>
       </c>
       <c r="BG484" s="106"/>
@@ -57525,89 +57462,89 @@
       <c r="A485" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B485" s="129" t="s">
+      <c r="B485" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C485" s="4">
         <v>45243</v>
       </c>
-      <c r="D485" s="128">
+      <c r="D485" s="8">
         <v>3</v>
       </c>
-      <c r="E485" s="131"/>
-      <c r="F485" s="134"/>
-      <c r="G485" s="134"/>
-      <c r="H485" s="128">
+      <c r="E485" s="4"/>
+      <c r="F485" s="10"/>
+      <c r="G485" s="10"/>
+      <c r="H485" s="8">
         <v>0.1777</v>
       </c>
-      <c r="I485" s="128">
+      <c r="I485" s="8">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="J485" s="128">
+      <c r="J485" s="8">
         <v>1.2370000000000001</v>
       </c>
-      <c r="K485" s="134"/>
-      <c r="L485" s="134"/>
-      <c r="M485" s="137">
+      <c r="K485" s="10"/>
+      <c r="L485" s="10"/>
+      <c r="M485" s="115">
         <v>0.17929999999999999</v>
       </c>
-      <c r="N485" s="134"/>
-      <c r="O485" s="134"/>
-      <c r="P485" s="143">
+      <c r="N485" s="10"/>
+      <c r="O485" s="10"/>
+      <c r="P485" s="121">
         <v>63.1</v>
       </c>
-      <c r="Q485" s="138">
+      <c r="Q485" s="107">
         <v>588</v>
       </c>
-      <c r="R485" s="147">
+      <c r="R485" s="112">
         <v>750</v>
       </c>
-      <c r="S485" s="129"/>
-      <c r="T485" s="129"/>
-      <c r="U485" s="129"/>
-      <c r="V485" s="129"/>
-      <c r="W485" s="129"/>
-      <c r="X485" s="129"/>
-      <c r="Y485" s="129"/>
-      <c r="Z485" s="129"/>
-      <c r="AA485" s="129"/>
-      <c r="AB485" s="129"/>
-      <c r="AC485" s="129"/>
-      <c r="AD485" s="129"/>
-      <c r="AE485" s="129"/>
-      <c r="AF485" s="129"/>
-      <c r="AG485" s="129"/>
-      <c r="AH485" s="129"/>
-      <c r="AI485" s="129"/>
-      <c r="AJ485" s="129"/>
-      <c r="AK485" s="129"/>
-      <c r="AL485" s="129"/>
-      <c r="AM485" s="129"/>
-      <c r="AN485" s="129"/>
-      <c r="AO485" s="129"/>
-      <c r="AP485" s="129"/>
-      <c r="AQ485" s="129"/>
-      <c r="AR485" s="129"/>
-      <c r="AS485" s="129"/>
-      <c r="AT485" s="129"/>
-      <c r="AU485" s="129"/>
-      <c r="AV485" s="129"/>
-      <c r="AW485" s="129"/>
-      <c r="AX485" s="129"/>
-      <c r="AY485" s="129"/>
-      <c r="AZ485" s="129"/>
-      <c r="BA485" s="129">
+      <c r="S485" s="5"/>
+      <c r="T485" s="5"/>
+      <c r="U485" s="5"/>
+      <c r="V485" s="5"/>
+      <c r="W485" s="5"/>
+      <c r="X485" s="5"/>
+      <c r="Y485" s="5"/>
+      <c r="Z485" s="5"/>
+      <c r="AA485" s="5"/>
+      <c r="AB485" s="5"/>
+      <c r="AC485" s="5"/>
+      <c r="AD485" s="5"/>
+      <c r="AE485" s="5"/>
+      <c r="AF485" s="5"/>
+      <c r="AG485" s="5"/>
+      <c r="AH485" s="5"/>
+      <c r="AI485" s="5"/>
+      <c r="AJ485" s="5"/>
+      <c r="AK485" s="5"/>
+      <c r="AL485" s="5"/>
+      <c r="AM485" s="5"/>
+      <c r="AN485" s="5"/>
+      <c r="AO485" s="5"/>
+      <c r="AP485" s="5"/>
+      <c r="AQ485" s="5"/>
+      <c r="AR485" s="5"/>
+      <c r="AS485" s="5"/>
+      <c r="AT485" s="5"/>
+      <c r="AU485" s="5"/>
+      <c r="AV485" s="5"/>
+      <c r="AW485" s="5"/>
+      <c r="AX485" s="5"/>
+      <c r="AY485" s="5"/>
+      <c r="AZ485" s="5"/>
+      <c r="BA485" s="5">
         <v>113.4</v>
       </c>
-      <c r="BB485" s="129"/>
-      <c r="BC485" s="129"/>
+      <c r="BB485" s="5"/>
+      <c r="BC485" s="5"/>
       <c r="BD485" s="107">
         <v>25.6</v>
       </c>
-      <c r="BE485" s="138">
+      <c r="BE485" s="107">
         <v>1011</v>
       </c>
-      <c r="BF485" s="138">
+      <c r="BF485" s="107">
         <v>44.1</v>
       </c>
       <c r="BG485" s="106"/>
@@ -57615,7 +57552,7 @@
         <v>2096</v>
       </c>
       <c r="BI485" s="5"/>
-      <c r="BJ485" s="131" t="s">
+      <c r="BJ485" s="4" t="s">
         <v>707</v>
       </c>
       <c r="BM485"/>
@@ -57703,10 +57640,10 @@
       <c r="BD486" s="107">
         <v>25.6</v>
       </c>
-      <c r="BE486" s="138">
+      <c r="BE486" s="107">
         <v>1011</v>
       </c>
-      <c r="BF486" s="138">
+      <c r="BF486" s="107">
         <v>44.1</v>
       </c>
       <c r="BG486" s="106"/>
@@ -57802,10 +57739,10 @@
       <c r="BD487" s="107">
         <v>26</v>
       </c>
-      <c r="BE487" s="138">
+      <c r="BE487" s="107">
         <v>1012</v>
       </c>
-      <c r="BF487" s="138">
+      <c r="BF487" s="107">
         <v>43</v>
       </c>
       <c r="BG487" s="106"/>
@@ -57901,10 +57838,10 @@
       <c r="BD488" s="107">
         <v>26</v>
       </c>
-      <c r="BE488" s="138">
+      <c r="BE488" s="107">
         <v>1012</v>
       </c>
-      <c r="BF488" s="138">
+      <c r="BF488" s="107">
         <v>43</v>
       </c>
       <c r="BG488" s="106"/>
@@ -57921,89 +57858,89 @@
       <c r="A489" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B489" s="129" t="s">
+      <c r="B489" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C489" s="4">
         <v>45243</v>
       </c>
-      <c r="D489" s="130">
+      <c r="D489" s="20">
         <v>7</v>
       </c>
       <c r="E489" s="4"/>
-      <c r="F489" s="134"/>
-      <c r="G489" s="134"/>
-      <c r="H489" s="128">
+      <c r="F489" s="10"/>
+      <c r="G489" s="10"/>
+      <c r="H489" s="8">
         <v>0.1772</v>
       </c>
-      <c r="I489" s="128">
+      <c r="I489" s="8">
         <v>2E-3</v>
       </c>
-      <c r="J489" s="128">
+      <c r="J489" s="8">
         <v>1.2370000000000001</v>
       </c>
-      <c r="K489" s="134"/>
-      <c r="L489" s="134"/>
-      <c r="M489" s="137">
+      <c r="K489" s="10"/>
+      <c r="L489" s="10"/>
+      <c r="M489" s="115">
         <v>0.1769</v>
       </c>
-      <c r="N489" s="134"/>
-      <c r="O489" s="134"/>
-      <c r="P489" s="143">
+      <c r="N489" s="10"/>
+      <c r="O489" s="10"/>
+      <c r="P489" s="121">
         <v>63.5</v>
       </c>
-      <c r="Q489" s="138">
+      <c r="Q489" s="107">
         <v>596</v>
       </c>
-      <c r="R489" s="147">
+      <c r="R489" s="112">
         <v>750</v>
       </c>
       <c r="S489" s="5"/>
       <c r="T489" s="5"/>
-      <c r="U489" s="129"/>
-      <c r="V489" s="129"/>
+      <c r="U489" s="5"/>
+      <c r="V489" s="5"/>
       <c r="W489" s="5"/>
       <c r="X489" s="5"/>
-      <c r="Y489" s="129"/>
-      <c r="Z489" s="129"/>
-      <c r="AA489" s="129"/>
-      <c r="AB489" s="129"/>
-      <c r="AC489" s="129"/>
-      <c r="AD489" s="129"/>
-      <c r="AE489" s="129"/>
-      <c r="AF489" s="129"/>
-      <c r="AG489" s="129"/>
-      <c r="AH489" s="129"/>
-      <c r="AI489" s="129"/>
-      <c r="AJ489" s="129"/>
-      <c r="AK489" s="129"/>
-      <c r="AL489" s="129"/>
-      <c r="AM489" s="129"/>
-      <c r="AN489" s="129"/>
-      <c r="AO489" s="129"/>
-      <c r="AP489" s="129"/>
-      <c r="AQ489" s="129"/>
-      <c r="AR489" s="129"/>
-      <c r="AS489" s="129"/>
-      <c r="AT489" s="129"/>
-      <c r="AU489" s="129"/>
-      <c r="AV489" s="129"/>
-      <c r="AW489" s="129"/>
-      <c r="AX489" s="129"/>
+      <c r="Y489" s="5"/>
+      <c r="Z489" s="5"/>
+      <c r="AA489" s="5"/>
+      <c r="AB489" s="5"/>
+      <c r="AC489" s="5"/>
+      <c r="AD489" s="5"/>
+      <c r="AE489" s="5"/>
+      <c r="AF489" s="5"/>
+      <c r="AG489" s="5"/>
+      <c r="AH489" s="5"/>
+      <c r="AI489" s="5"/>
+      <c r="AJ489" s="5"/>
+      <c r="AK489" s="5"/>
+      <c r="AL489" s="5"/>
+      <c r="AM489" s="5"/>
+      <c r="AN489" s="5"/>
+      <c r="AO489" s="5"/>
+      <c r="AP489" s="5"/>
+      <c r="AQ489" s="5"/>
+      <c r="AR489" s="5"/>
+      <c r="AS489" s="5"/>
+      <c r="AT489" s="5"/>
+      <c r="AU489" s="5"/>
+      <c r="AV489" s="5"/>
+      <c r="AW489" s="5"/>
+      <c r="AX489" s="5"/>
       <c r="AY489" s="5"/>
       <c r="AZ489" s="5"/>
       <c r="BA489" s="117">
         <v>117</v>
       </c>
       <c r="BB489" s="5"/>
-      <c r="BC489" s="129"/>
+      <c r="BC489" s="5"/>
       <c r="BD489" s="117">
         <v>25</v>
       </c>
       <c r="BE489" s="105">
         <v>1012</v>
       </c>
-      <c r="BF489" s="162">
+      <c r="BF489" s="122">
         <v>54</v>
       </c>
       <c r="BG489" s="106">
@@ -58097,7 +58034,7 @@
       <c r="BE490" s="124">
         <v>1012</v>
       </c>
-      <c r="BF490" s="162">
+      <c r="BF490" s="122">
         <v>54</v>
       </c>
       <c r="BG490" s="119">
@@ -58198,7 +58135,7 @@
       <c r="BE491" s="105">
         <v>1012</v>
       </c>
-      <c r="BF491" s="162">
+      <c r="BF491" s="122">
         <v>53</v>
       </c>
       <c r="BG491" s="106">
@@ -58299,7 +58236,7 @@
       <c r="BE492" s="105">
         <v>1012</v>
       </c>
-      <c r="BF492" s="162">
+      <c r="BF492" s="122">
         <v>53</v>
       </c>
       <c r="BG492" s="106">
@@ -58400,7 +58337,7 @@
       <c r="BE493" s="105">
         <v>1012</v>
       </c>
-      <c r="BF493" s="162">
+      <c r="BF493" s="122">
         <v>53</v>
       </c>
       <c r="BG493" s="106">
@@ -58501,7 +58438,7 @@
       <c r="BE494" s="105">
         <v>1012</v>
       </c>
-      <c r="BF494" s="162">
+      <c r="BF494" s="122">
         <v>54</v>
       </c>
       <c r="BG494" s="106">
@@ -58602,7 +58539,7 @@
       <c r="BE495" s="105">
         <v>1012</v>
       </c>
-      <c r="BF495" s="162">
+      <c r="BF495" s="122">
         <v>54</v>
       </c>
       <c r="BG495" s="106">
@@ -58703,7 +58640,7 @@
       <c r="BE496" s="105">
         <v>1011</v>
       </c>
-      <c r="BF496" s="162">
+      <c r="BF496" s="122">
         <v>54</v>
       </c>
       <c r="BG496" s="106">
@@ -58722,89 +58659,89 @@
       <c r="A497" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B497" s="129" t="s">
+      <c r="B497" s="5" t="s">
         <v>207</v>
       </c>
       <c r="C497" s="4">
         <v>45243</v>
       </c>
-      <c r="D497" s="130">
+      <c r="D497" s="20">
         <v>1</v>
       </c>
-      <c r="E497" s="131"/>
-      <c r="F497" s="134"/>
-      <c r="G497" s="134"/>
-      <c r="H497" s="128">
+      <c r="E497" s="4"/>
+      <c r="F497" s="10"/>
+      <c r="G497" s="10"/>
+      <c r="H497" s="8">
         <v>0.16969999999999999</v>
       </c>
-      <c r="I497" s="128">
+      <c r="I497" s="8">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="J497" s="128">
+      <c r="J497" s="8">
         <v>1.163</v>
       </c>
-      <c r="K497" s="134"/>
-      <c r="L497" s="134"/>
-      <c r="M497" s="137">
+      <c r="K497" s="10"/>
+      <c r="L497" s="10"/>
+      <c r="M497" s="115">
         <v>0.16200000000000001</v>
       </c>
-      <c r="N497" s="134"/>
-      <c r="O497" s="134"/>
-      <c r="P497" s="143">
+      <c r="N497" s="10"/>
+      <c r="O497" s="10"/>
+      <c r="P497" s="121">
         <v>66</v>
       </c>
-      <c r="Q497" s="138">
+      <c r="Q497" s="107">
         <v>616</v>
       </c>
-      <c r="R497" s="147">
+      <c r="R497" s="112">
         <v>750</v>
       </c>
-      <c r="S497" s="129"/>
-      <c r="T497" s="129"/>
-      <c r="U497" s="129"/>
-      <c r="V497" s="129"/>
-      <c r="W497" s="129"/>
-      <c r="X497" s="129"/>
-      <c r="Y497" s="129"/>
-      <c r="Z497" s="129"/>
-      <c r="AA497" s="129"/>
-      <c r="AB497" s="129"/>
-      <c r="AC497" s="129"/>
-      <c r="AD497" s="129"/>
-      <c r="AE497" s="129"/>
-      <c r="AF497" s="129"/>
-      <c r="AG497" s="129"/>
-      <c r="AH497" s="129"/>
-      <c r="AI497" s="129"/>
-      <c r="AJ497" s="129"/>
-      <c r="AK497" s="129"/>
-      <c r="AL497" s="129"/>
-      <c r="AM497" s="129"/>
-      <c r="AN497" s="129"/>
-      <c r="AO497" s="129"/>
-      <c r="AP497" s="129"/>
-      <c r="AQ497" s="129"/>
-      <c r="AR497" s="129"/>
-      <c r="AS497" s="129"/>
-      <c r="AT497" s="129"/>
-      <c r="AU497" s="129"/>
-      <c r="AV497" s="129"/>
-      <c r="AW497" s="129"/>
-      <c r="AX497" s="129"/>
-      <c r="AY497" s="129"/>
-      <c r="AZ497" s="129"/>
-      <c r="BA497" s="154">
+      <c r="S497" s="5"/>
+      <c r="T497" s="5"/>
+      <c r="U497" s="5"/>
+      <c r="V497" s="5"/>
+      <c r="W497" s="5"/>
+      <c r="X497" s="5"/>
+      <c r="Y497" s="5"/>
+      <c r="Z497" s="5"/>
+      <c r="AA497" s="5"/>
+      <c r="AB497" s="5"/>
+      <c r="AC497" s="5"/>
+      <c r="AD497" s="5"/>
+      <c r="AE497" s="5"/>
+      <c r="AF497" s="5"/>
+      <c r="AG497" s="5"/>
+      <c r="AH497" s="5"/>
+      <c r="AI497" s="5"/>
+      <c r="AJ497" s="5"/>
+      <c r="AK497" s="5"/>
+      <c r="AL497" s="5"/>
+      <c r="AM497" s="5"/>
+      <c r="AN497" s="5"/>
+      <c r="AO497" s="5"/>
+      <c r="AP497" s="5"/>
+      <c r="AQ497" s="5"/>
+      <c r="AR497" s="5"/>
+      <c r="AS497" s="5"/>
+      <c r="AT497" s="5"/>
+      <c r="AU497" s="5"/>
+      <c r="AV497" s="5"/>
+      <c r="AW497" s="5"/>
+      <c r="AX497" s="5"/>
+      <c r="AY497" s="5"/>
+      <c r="AZ497" s="5"/>
+      <c r="BA497" s="117">
         <v>117</v>
       </c>
-      <c r="BB497" s="129"/>
-      <c r="BC497" s="129"/>
+      <c r="BB497" s="5"/>
+      <c r="BC497" s="5"/>
       <c r="BD497" s="117">
         <v>25.1</v>
       </c>
       <c r="BE497" s="105">
         <v>1011</v>
       </c>
-      <c r="BF497" s="162">
+      <c r="BF497" s="122">
         <v>54</v>
       </c>
       <c r="BG497" s="106">
@@ -58814,7 +58751,7 @@
         <v>2096</v>
       </c>
       <c r="BI497" s="5"/>
-      <c r="BJ497" s="131" t="s">
+      <c r="BJ497" s="4" t="s">
         <v>717</v>
       </c>
       <c r="BM497"/>
@@ -58905,7 +58842,7 @@
       <c r="BE498" s="105">
         <v>1011</v>
       </c>
-      <c r="BF498" s="162">
+      <c r="BF498" s="122">
         <v>54</v>
       </c>
       <c r="BG498" s="106">
@@ -59006,7 +58943,7 @@
       <c r="BE499" s="105">
         <v>1011</v>
       </c>
-      <c r="BF499" s="162">
+      <c r="BF499" s="122">
         <v>54</v>
       </c>
       <c r="BG499" s="106">
@@ -59107,7 +59044,7 @@
       <c r="BE500" s="105">
         <v>1011</v>
       </c>
-      <c r="BF500" s="162">
+      <c r="BF500" s="122">
         <v>54</v>
       </c>
       <c r="BG500" s="106">
@@ -59216,7 +59153,7 @@
       <c r="BE501" s="105">
         <v>1010</v>
       </c>
-      <c r="BF501" s="162">
+      <c r="BF501" s="122">
         <v>52</v>
       </c>
       <c r="BG501" s="106">
@@ -59436,7 +59373,7 @@
       <c r="BE503" s="105">
         <v>1010</v>
       </c>
-      <c r="BF503" s="162">
+      <c r="BF503" s="122">
         <v>50</v>
       </c>
       <c r="BG503" s="106">
@@ -59546,7 +59483,7 @@
       <c r="BE504" s="105">
         <v>1010</v>
       </c>
-      <c r="BF504" s="162">
+      <c r="BF504" s="122">
         <v>51</v>
       </c>
       <c r="BG504" s="106">
@@ -59656,7 +59593,7 @@
       <c r="BE505" s="105">
         <v>1010</v>
       </c>
-      <c r="BF505" s="162">
+      <c r="BF505" s="122">
         <v>48</v>
       </c>
       <c r="BG505" s="106">
@@ -59766,7 +59703,7 @@
       <c r="BE506" s="105">
         <v>1010</v>
       </c>
-      <c r="BF506" s="162">
+      <c r="BF506" s="122">
         <v>48</v>
       </c>
       <c r="BG506" s="106">
@@ -59876,7 +59813,7 @@
       <c r="BE507" s="105">
         <v>1010</v>
       </c>
-      <c r="BF507" s="162">
+      <c r="BF507" s="122">
         <v>52</v>
       </c>
       <c r="BG507" s="106">
@@ -59986,7 +59923,7 @@
       <c r="BE508" s="105">
         <v>1010</v>
       </c>
-      <c r="BF508" s="162">
+      <c r="BF508" s="122">
         <v>52</v>
       </c>
       <c r="BG508" s="106">
@@ -60096,7 +60033,7 @@
       <c r="BE509" s="105">
         <v>1010</v>
       </c>
-      <c r="BF509" s="162">
+      <c r="BF509" s="122">
         <v>50</v>
       </c>
       <c r="BG509" s="106">
@@ -60206,7 +60143,7 @@
       <c r="BE510" s="105">
         <v>1010</v>
       </c>
-      <c r="BF510" s="162">
+      <c r="BF510" s="122">
         <v>48</v>
       </c>
       <c r="BG510" s="106">
@@ -60316,7 +60253,7 @@
       <c r="BE511" s="105">
         <v>1010</v>
       </c>
-      <c r="BF511" s="162">
+      <c r="BF511" s="122">
         <v>48</v>
       </c>
       <c r="BG511" s="106">
@@ -60426,7 +60363,7 @@
       <c r="BE512" s="105">
         <v>1009</v>
       </c>
-      <c r="BF512" s="162">
+      <c r="BF512" s="122">
         <v>50</v>
       </c>
       <c r="BG512" s="106">
@@ -60470,7 +60407,9 @@
         <v>1.2725</v>
       </c>
       <c r="K513" s="10"/>
-      <c r="L513" s="107"/>
+      <c r="L513" s="139">
+        <v>0.14799999999999999</v>
+      </c>
       <c r="M513" s="107">
         <v>0.17050000000000001</v>
       </c>
@@ -60534,7 +60473,7 @@
       <c r="BE513" s="105">
         <v>1010</v>
       </c>
-      <c r="BF513" s="162">
+      <c r="BF513" s="122">
         <v>52</v>
       </c>
       <c r="BG513" s="106">
@@ -60578,7 +60517,9 @@
         <v>1.2515000000000001</v>
       </c>
       <c r="K514" s="10"/>
-      <c r="L514" s="107"/>
+      <c r="L514" s="25">
+        <v>0.161</v>
+      </c>
       <c r="M514" s="107">
         <v>0.15970000000000001</v>
       </c>
@@ -60642,7 +60583,7 @@
       <c r="BE514" s="105">
         <v>1010</v>
       </c>
-      <c r="BF514" s="162">
+      <c r="BF514" s="122">
         <v>52</v>
       </c>
       <c r="BG514" s="106">
@@ -60686,7 +60627,9 @@
         <v>1.2515000000000001</v>
       </c>
       <c r="K515" s="10"/>
-      <c r="L515" s="107"/>
+      <c r="L515" s="25">
+        <v>0.161</v>
+      </c>
       <c r="M515" s="107">
         <v>0.1598</v>
       </c>
@@ -60750,7 +60693,7 @@
       <c r="BE515" s="105">
         <v>1010</v>
       </c>
-      <c r="BF515" s="162">
+      <c r="BF515" s="122">
         <v>51</v>
       </c>
       <c r="BG515" s="106">
@@ -60794,7 +60737,9 @@
         <v>1.2515000000000001</v>
       </c>
       <c r="K516" s="10"/>
-      <c r="L516" s="107"/>
+      <c r="L516" s="139" t="s">
+        <v>784</v>
+      </c>
       <c r="M516" s="107">
         <v>0.17130000000000001</v>
       </c>
@@ -60858,7 +60803,7 @@
       <c r="BE516" s="105">
         <v>1010</v>
       </c>
-      <c r="BF516" s="162">
+      <c r="BF516" s="122">
         <v>48</v>
       </c>
       <c r="BG516" s="106">
@@ -60902,7 +60847,9 @@
         <v>1.2515000000000001</v>
       </c>
       <c r="K517" s="10"/>
-      <c r="L517" s="10"/>
+      <c r="L517" s="25">
+        <v>0.16</v>
+      </c>
       <c r="M517" s="107">
         <v>0.16239999999999999</v>
       </c>
@@ -60966,7 +60913,7 @@
       <c r="BE517" s="105">
         <v>1009</v>
       </c>
-      <c r="BF517" s="162">
+      <c r="BF517" s="122">
         <v>50</v>
       </c>
       <c r="BG517" s="106">
@@ -61010,7 +60957,9 @@
         <v>1.2515000000000001</v>
       </c>
       <c r="K518" s="10"/>
-      <c r="L518" s="10"/>
+      <c r="L518" s="25">
+        <v>0.16300000000000001</v>
+      </c>
       <c r="M518" s="107">
         <v>0.16309999999999999</v>
       </c>
@@ -61074,7 +61023,7 @@
       <c r="BE518" s="105">
         <v>1009</v>
       </c>
-      <c r="BF518" s="162">
+      <c r="BF518" s="122">
         <v>50</v>
       </c>
       <c r="BG518" s="106">
@@ -61118,7 +61067,9 @@
         <v>1.2515000000000001</v>
       </c>
       <c r="K519" s="10"/>
-      <c r="L519" s="10"/>
+      <c r="L519" s="25">
+        <v>0.16500000000000001</v>
+      </c>
       <c r="M519" s="107">
         <v>0.17069999999999999</v>
       </c>
@@ -61182,7 +61133,7 @@
       <c r="BE519" s="105">
         <v>1009</v>
       </c>
-      <c r="BF519" s="162">
+      <c r="BF519" s="122">
         <v>50</v>
       </c>
       <c r="BG519" s="106">
@@ -61226,7 +61177,9 @@
         <v>1.2569999999999999</v>
       </c>
       <c r="K520" s="10"/>
-      <c r="L520" s="10"/>
+      <c r="L520" s="25">
+        <v>0.19700000000000001</v>
+      </c>
       <c r="M520" s="107">
         <v>0.19700000000000001</v>
       </c>
@@ -61294,7 +61247,7 @@
       <c r="BE520" s="105">
         <v>1009</v>
       </c>
-      <c r="BF520" s="162">
+      <c r="BF520" s="122">
         <v>61</v>
       </c>
       <c r="BG520" s="106">
@@ -61338,7 +61291,9 @@
         <v>1.2569999999999999</v>
       </c>
       <c r="K521" s="10"/>
-      <c r="L521" s="10"/>
+      <c r="L521" s="25">
+        <v>0.19800000000000001</v>
+      </c>
       <c r="M521" s="107">
         <v>0.19359999999999999</v>
       </c>
@@ -61406,7 +61361,7 @@
       <c r="BE521" s="105">
         <v>1009</v>
       </c>
-      <c r="BF521" s="162">
+      <c r="BF521" s="122">
         <v>62</v>
       </c>
       <c r="BG521" s="106">
@@ -61450,7 +61405,9 @@
         <v>1.2569999999999999</v>
       </c>
       <c r="K522" s="10"/>
-      <c r="L522" s="10"/>
+      <c r="L522" s="25">
+        <v>0.20100000000000001</v>
+      </c>
       <c r="M522" s="107">
         <v>0.1946</v>
       </c>
@@ -61518,7 +61475,7 @@
       <c r="BE522" s="105">
         <v>1009</v>
       </c>
-      <c r="BF522" s="162">
+      <c r="BF522" s="122">
         <v>60</v>
       </c>
       <c r="BG522" s="106">
@@ -61562,7 +61519,9 @@
         <v>1.2569999999999999</v>
       </c>
       <c r="K523" s="10"/>
-      <c r="L523" s="10"/>
+      <c r="L523" s="25">
+        <v>0.20200000000000001</v>
+      </c>
       <c r="M523" s="107">
         <v>0.19409999999999999</v>
       </c>
@@ -61630,7 +61589,7 @@
       <c r="BE523" s="105">
         <v>1009</v>
       </c>
-      <c r="BF523" s="162">
+      <c r="BF523" s="122">
         <v>59</v>
       </c>
       <c r="BG523" s="106">
@@ -61674,7 +61633,9 @@
         <v>1.2569999999999999</v>
       </c>
       <c r="K524" s="10"/>
-      <c r="L524" s="10"/>
+      <c r="L524" s="25">
+        <v>0.20399999999999999</v>
+      </c>
       <c r="M524" s="107">
         <v>0.19750000000000001</v>
       </c>
@@ -61742,7 +61703,7 @@
       <c r="BE524" s="105">
         <v>1009</v>
       </c>
-      <c r="BF524" s="162">
+      <c r="BF524" s="122">
         <v>60</v>
       </c>
       <c r="BG524" s="106">
@@ -61786,7 +61747,9 @@
         <v>1.2569999999999999</v>
       </c>
       <c r="K525" s="10"/>
-      <c r="L525" s="10"/>
+      <c r="L525" s="25">
+        <v>0.19900000000000001</v>
+      </c>
       <c r="M525" s="107">
         <v>0.191</v>
       </c>
@@ -61854,7 +61817,7 @@
       <c r="BE525" s="105">
         <v>1009</v>
       </c>
-      <c r="BF525" s="162">
+      <c r="BF525" s="122">
         <v>58</v>
       </c>
       <c r="BG525" s="106">
@@ -61898,7 +61861,9 @@
         <v>1.2569999999999999</v>
       </c>
       <c r="K526" s="10"/>
-      <c r="L526" s="10"/>
+      <c r="L526" s="25">
+        <v>0.20300000000000001</v>
+      </c>
       <c r="M526" s="107">
         <v>0.19070000000000001</v>
       </c>
@@ -61966,7 +61931,7 @@
       <c r="BE526" s="105">
         <v>1009</v>
       </c>
-      <c r="BF526" s="162">
+      <c r="BF526" s="122">
         <v>58</v>
       </c>
       <c r="BG526" s="106">
@@ -62008,7 +61973,9 @@
         <v>1.2569999999999999</v>
       </c>
       <c r="K527" s="10"/>
-      <c r="L527" s="10"/>
+      <c r="L527" s="25">
+        <v>0.20100000000000001</v>
+      </c>
       <c r="M527" s="107">
         <v>0.19040000000000001</v>
       </c>
@@ -62076,7 +62043,7 @@
       <c r="BE527" s="105">
         <v>1009</v>
       </c>
-      <c r="BF527" s="162">
+      <c r="BF527" s="122">
         <v>58</v>
       </c>
       <c r="BG527" s="106">
@@ -62120,7 +62087,9 @@
         <v>1.2645</v>
       </c>
       <c r="K528" s="10"/>
-      <c r="L528" s="10"/>
+      <c r="L528" s="25">
+        <v>0.17399999999999999</v>
+      </c>
       <c r="M528" s="107">
         <v>0.17330000000000001</v>
       </c>
@@ -62188,7 +62157,7 @@
       <c r="BE528" s="105">
         <v>1009</v>
       </c>
-      <c r="BF528" s="162">
+      <c r="BF528" s="122">
         <v>62</v>
       </c>
       <c r="BG528" s="106">
@@ -62232,7 +62201,9 @@
         <v>1.2645</v>
       </c>
       <c r="K529" s="10"/>
-      <c r="L529" s="10"/>
+      <c r="L529" s="25">
+        <v>0.17100000000000001</v>
+      </c>
       <c r="M529" s="107"/>
       <c r="N529" s="10"/>
       <c r="O529" s="10"/>
@@ -62292,7 +62263,7 @@
       <c r="BE529" s="105">
         <v>1009</v>
       </c>
-      <c r="BF529" s="162">
+      <c r="BF529" s="122">
         <v>61</v>
       </c>
       <c r="BG529" s="106">
@@ -62338,7 +62309,9 @@
         <v>1.2645</v>
       </c>
       <c r="K530" s="10"/>
-      <c r="L530" s="10"/>
+      <c r="L530" s="25">
+        <v>0.17299999999999999</v>
+      </c>
       <c r="M530" s="107">
         <v>0.1694</v>
       </c>
@@ -62406,7 +62379,7 @@
       <c r="BE530" s="105">
         <v>1009</v>
       </c>
-      <c r="BF530" s="162">
+      <c r="BF530" s="122">
         <v>60</v>
       </c>
       <c r="BG530" s="106">
@@ -62450,7 +62423,9 @@
         <v>1.2645</v>
       </c>
       <c r="K531" s="10"/>
-      <c r="L531" s="10"/>
+      <c r="L531" s="25">
+        <v>0.17499999999999999</v>
+      </c>
       <c r="M531" s="107">
         <v>0.1739</v>
       </c>
@@ -62518,7 +62493,7 @@
       <c r="BE531" s="105">
         <v>1009</v>
       </c>
-      <c r="BF531" s="162">
+      <c r="BF531" s="122">
         <v>60</v>
       </c>
       <c r="BG531" s="106">
@@ -62562,7 +62537,9 @@
         <v>1.2645</v>
       </c>
       <c r="K532" s="10"/>
-      <c r="L532" s="10"/>
+      <c r="L532" s="25">
+        <v>0.17399999999999999</v>
+      </c>
       <c r="M532" s="107">
         <v>0.17150000000000001</v>
       </c>
@@ -62674,7 +62651,9 @@
         <v>1.2645</v>
       </c>
       <c r="K533" s="10"/>
-      <c r="L533" s="10"/>
+      <c r="L533" s="25">
+        <v>0.17599999999999999</v>
+      </c>
       <c r="M533" s="107">
         <v>0.17030000000000001</v>
       </c>
@@ -62742,7 +62721,7 @@
       <c r="BE533" s="105">
         <v>1009</v>
       </c>
-      <c r="BF533" s="162">
+      <c r="BF533" s="122">
         <v>58</v>
       </c>
       <c r="BG533" s="106">
@@ -62786,7 +62765,9 @@
         <v>1.272</v>
       </c>
       <c r="K534" s="10"/>
-      <c r="L534" s="10"/>
+      <c r="L534" s="25">
+        <v>0.16300000000000001</v>
+      </c>
       <c r="M534" s="107">
         <v>0.15820000000000001</v>
       </c>
@@ -62854,7 +62835,7 @@
       <c r="BE534" s="105">
         <v>1009</v>
       </c>
-      <c r="BF534" s="162">
+      <c r="BF534" s="122">
         <v>61</v>
       </c>
       <c r="BG534" s="106">
@@ -62898,7 +62879,9 @@
         <v>1.272</v>
       </c>
       <c r="K535" s="10"/>
-      <c r="L535" s="10"/>
+      <c r="L535" s="25">
+        <v>0.16500000000000001</v>
+      </c>
       <c r="M535" s="107">
         <v>0.1608</v>
       </c>
@@ -62966,7 +62949,7 @@
       <c r="BE535" s="105">
         <v>1009</v>
       </c>
-      <c r="BF535" s="162">
+      <c r="BF535" s="122">
         <v>62</v>
       </c>
       <c r="BG535" s="106">
@@ -63010,7 +62993,9 @@
         <v>1.272</v>
       </c>
       <c r="K536" s="10"/>
-      <c r="L536" s="10"/>
+      <c r="L536" s="25">
+        <v>0.16200000000000001</v>
+      </c>
       <c r="M536" s="107">
         <v>0.15920000000000001</v>
       </c>
@@ -63078,7 +63063,7 @@
       <c r="BE536" s="105">
         <v>1009</v>
       </c>
-      <c r="BF536" s="162">
+      <c r="BF536" s="122">
         <v>61</v>
       </c>
       <c r="BG536" s="106">
@@ -63122,7 +63107,9 @@
         <v>1.272</v>
       </c>
       <c r="K537" s="10"/>
-      <c r="L537" s="10"/>
+      <c r="L537" s="25">
+        <v>0.16300000000000001</v>
+      </c>
       <c r="M537" s="107">
         <v>0.15820000000000001</v>
       </c>
@@ -63190,7 +63177,7 @@
       <c r="BE537" s="105">
         <v>1009</v>
       </c>
-      <c r="BF537" s="162">
+      <c r="BF537" s="122">
         <v>59</v>
       </c>
       <c r="BG537" s="106">
@@ -63234,7 +63221,9 @@
         <v>1.272</v>
       </c>
       <c r="K538" s="10"/>
-      <c r="L538" s="10"/>
+      <c r="L538" s="25">
+        <v>0.161</v>
+      </c>
       <c r="M538" s="107">
         <v>0.15790000000000001</v>
       </c>
@@ -63302,7 +63291,7 @@
       <c r="BE538" s="105">
         <v>1009</v>
       </c>
-      <c r="BF538" s="162">
+      <c r="BF538" s="122">
         <v>60</v>
       </c>
       <c r="BG538" s="106">
@@ -63346,7 +63335,9 @@
         <v>1.272</v>
       </c>
       <c r="K539" s="10"/>
-      <c r="L539" s="10"/>
+      <c r="L539" s="25">
+        <v>0.159</v>
+      </c>
       <c r="M539" s="107">
         <v>0.1605</v>
       </c>
@@ -63414,7 +63405,7 @@
       <c r="BE539" s="105">
         <v>1009</v>
       </c>
-      <c r="BF539" s="162">
+      <c r="BF539" s="122">
         <v>58</v>
       </c>
       <c r="BG539" s="106">
@@ -63458,7 +63449,9 @@
         <v>1.272</v>
       </c>
       <c r="K540" s="10"/>
-      <c r="L540" s="10"/>
+      <c r="L540" s="25">
+        <v>0.16</v>
+      </c>
       <c r="M540" s="107">
         <v>0.15609999999999999</v>
       </c>
@@ -63526,7 +63519,7 @@
       <c r="BE540" s="105">
         <v>1009</v>
       </c>
-      <c r="BF540" s="162">
+      <c r="BF540" s="122">
         <v>58</v>
       </c>
       <c r="BG540" s="106">
@@ -63570,7 +63563,9 @@
         <v>1.272</v>
       </c>
       <c r="K541" s="10"/>
-      <c r="L541" s="10"/>
+      <c r="L541" s="25">
+        <v>0.161</v>
+      </c>
       <c r="M541" s="107">
         <v>0.15490000000000001</v>
       </c>
@@ -63638,7 +63633,7 @@
       <c r="BE541" s="105">
         <v>1009</v>
       </c>
-      <c r="BF541" s="162">
+      <c r="BF541" s="122">
         <v>58</v>
       </c>
       <c r="BG541" s="106">
@@ -63682,7 +63677,9 @@
         <v>1.272</v>
       </c>
       <c r="K542" s="10"/>
-      <c r="L542" s="10"/>
+      <c r="L542" s="25">
+        <v>0.159</v>
+      </c>
       <c r="M542" s="107">
         <v>0.158</v>
       </c>
@@ -63750,7 +63747,7 @@
       <c r="BE542" s="105">
         <v>1009</v>
       </c>
-      <c r="BF542" s="162">
+      <c r="BF542" s="122">
         <v>58</v>
       </c>
       <c r="BG542" s="106">
@@ -63766,7 +63763,7 @@
       <c r="BK542" s="8"/>
       <c r="BM542"/>
     </row>
-    <row r="543" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
         <v>296</v>
       </c>
@@ -63794,7 +63791,9 @@
         <v>1.298</v>
       </c>
       <c r="K543" s="10"/>
-      <c r="L543" s="10"/>
+      <c r="L543" s="25">
+        <v>0.16200000000000001</v>
+      </c>
       <c r="M543" s="107">
         <v>0.15939999999999999</v>
       </c>
@@ -63862,7 +63861,7 @@
       <c r="BE543" s="105">
         <v>1004</v>
       </c>
-      <c r="BF543" s="162">
+      <c r="BF543" s="122">
         <v>64</v>
       </c>
       <c r="BG543" s="106">
@@ -63878,7 +63877,7 @@
       <c r="BK543" s="8"/>
       <c r="BM543"/>
     </row>
-    <row r="544" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A544" s="3" t="s">
         <v>296</v>
       </c>
@@ -63906,7 +63905,9 @@
         <v>1.298</v>
       </c>
       <c r="K544" s="10"/>
-      <c r="L544" s="10"/>
+      <c r="L544" s="25">
+        <v>0.161</v>
+      </c>
       <c r="M544" s="107">
         <v>0.1603</v>
       </c>
@@ -63974,7 +63975,7 @@
       <c r="BE544" s="105">
         <v>1004</v>
       </c>
-      <c r="BF544" s="162">
+      <c r="BF544" s="122">
         <v>64</v>
       </c>
       <c r="BG544" s="106">
@@ -63990,7 +63991,7 @@
       <c r="BK544" s="8"/>
       <c r="BM544"/>
     </row>
-    <row r="545" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
         <v>296</v>
       </c>
@@ -64018,7 +64019,7 @@
         <v>1.298</v>
       </c>
       <c r="K545" s="10"/>
-      <c r="L545" s="10"/>
+      <c r="L545" s="25"/>
       <c r="M545" s="107">
         <v>0.16059999999999999</v>
       </c>
@@ -64086,7 +64087,7 @@
       <c r="BE545" s="105">
         <v>1004</v>
       </c>
-      <c r="BF545" s="162">
+      <c r="BF545" s="122">
         <v>62</v>
       </c>
       <c r="BG545" s="106">
@@ -64102,7 +64103,7 @@
       <c r="BK545" s="8"/>
       <c r="BM545"/>
     </row>
-    <row r="546" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A546" s="3" t="s">
         <v>296</v>
       </c>
@@ -64130,7 +64131,9 @@
         <v>1.298</v>
       </c>
       <c r="K546" s="10"/>
-      <c r="L546" s="10"/>
+      <c r="L546" s="25">
+        <v>0.16200000000000001</v>
+      </c>
       <c r="M546" s="107">
         <v>0.16270000000000001</v>
       </c>
@@ -64198,7 +64201,7 @@
       <c r="BE546" s="105">
         <v>1004</v>
       </c>
-      <c r="BF546" s="162">
+      <c r="BF546" s="122">
         <v>62</v>
       </c>
       <c r="BG546" s="106">
@@ -64214,7 +64217,7 @@
       <c r="BK546" s="8"/>
       <c r="BM546"/>
     </row>
-    <row r="547" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
         <v>296</v>
       </c>
@@ -64242,7 +64245,9 @@
         <v>1.298</v>
       </c>
       <c r="K547" s="10"/>
-      <c r="L547" s="10"/>
+      <c r="L547" s="25">
+        <v>0.16300000000000001</v>
+      </c>
       <c r="M547" s="107">
         <v>0.16270000000000001</v>
       </c>
@@ -64310,7 +64315,7 @@
       <c r="BE547" s="105">
         <v>1004</v>
       </c>
-      <c r="BF547" s="162">
+      <c r="BF547" s="122">
         <v>61</v>
       </c>
       <c r="BG547" s="106">
@@ -64326,7 +64331,7 @@
       <c r="BK547" s="8"/>
       <c r="BM547"/>
     </row>
-    <row r="548" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A548" s="3" t="s">
         <v>296</v>
       </c>
@@ -64354,7 +64359,9 @@
         <v>1.298</v>
       </c>
       <c r="K548" s="10"/>
-      <c r="L548" s="10"/>
+      <c r="L548" s="25">
+        <v>0.16300000000000001</v>
+      </c>
       <c r="M548" s="107">
         <v>0.16059999999999999</v>
       </c>
@@ -64422,7 +64429,7 @@
       <c r="BE548" s="105">
         <v>1004</v>
       </c>
-      <c r="BF548" s="162">
+      <c r="BF548" s="122">
         <v>61</v>
       </c>
       <c r="BG548" s="106">
@@ -64438,7 +64445,7 @@
       <c r="BK548" s="8"/>
       <c r="BM548"/>
     </row>
-    <row r="549" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
         <v>296</v>
       </c>
@@ -64466,7 +64473,9 @@
         <v>1.298</v>
       </c>
       <c r="K549" s="10"/>
-      <c r="L549" s="10"/>
+      <c r="L549" s="25">
+        <v>0.16300000000000001</v>
+      </c>
       <c r="M549" s="107"/>
       <c r="N549" s="10"/>
       <c r="O549" s="10"/>
@@ -64532,7 +64541,7 @@
       <c r="BE549" s="105">
         <v>1004</v>
       </c>
-      <c r="BF549" s="162">
+      <c r="BF549" s="122">
         <v>61</v>
       </c>
       <c r="BG549" s="106">
@@ -64548,7 +64557,7 @@
       <c r="BK549" s="8"/>
       <c r="BM549"/>
     </row>
-    <row r="550" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A550" s="3" t="s">
         <v>296</v>
       </c>
@@ -64576,7 +64585,9 @@
         <v>1.2515000000000001</v>
       </c>
       <c r="K550" s="10"/>
-      <c r="L550" s="10"/>
+      <c r="L550" s="25">
+        <v>0.157</v>
+      </c>
       <c r="M550" s="107">
         <v>0.15570000000000001</v>
       </c>
@@ -64644,7 +64655,7 @@
       <c r="BE550" s="105">
         <v>1004</v>
       </c>
-      <c r="BF550" s="162">
+      <c r="BF550" s="122">
         <v>64</v>
       </c>
       <c r="BG550" s="106">
@@ -64660,7 +64671,7 @@
       <c r="BK550" s="8"/>
       <c r="BM550"/>
     </row>
-    <row r="551" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
         <v>296</v>
       </c>
@@ -64688,7 +64699,9 @@
         <v>1.2515000000000001</v>
       </c>
       <c r="K551" s="10"/>
-      <c r="L551" s="10"/>
+      <c r="L551" s="25">
+        <v>0.158</v>
+      </c>
       <c r="M551" s="107">
         <v>0.155</v>
       </c>
@@ -64756,7 +64769,7 @@
       <c r="BE551" s="105">
         <v>1004</v>
       </c>
-      <c r="BF551" s="162">
+      <c r="BF551" s="122">
         <v>64</v>
       </c>
       <c r="BG551" s="106">
@@ -64772,7 +64785,7 @@
       <c r="BK551" s="8"/>
       <c r="BM551"/>
     </row>
-    <row r="552" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A552" s="3" t="s">
         <v>296</v>
       </c>
@@ -64800,7 +64813,9 @@
         <v>1.2515000000000001</v>
       </c>
       <c r="K552" s="10"/>
-      <c r="L552" s="10"/>
+      <c r="L552" s="25">
+        <v>0.152</v>
+      </c>
       <c r="M552" s="107">
         <v>0.1542</v>
       </c>
@@ -64868,7 +64883,7 @@
       <c r="BE552" s="105">
         <v>1004</v>
       </c>
-      <c r="BF552" s="162">
+      <c r="BF552" s="122">
         <v>64</v>
       </c>
       <c r="BG552" s="106">
@@ -64884,7 +64899,7 @@
       <c r="BK552" s="8"/>
       <c r="BM552"/>
     </row>
-    <row r="553" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
         <v>296</v>
       </c>
@@ -64912,7 +64927,9 @@
         <v>1.2515000000000001</v>
       </c>
       <c r="K553" s="10"/>
-      <c r="L553" s="10"/>
+      <c r="L553" s="25">
+        <v>0.155</v>
+      </c>
       <c r="M553" s="107">
         <v>0.15640000000000001</v>
       </c>
@@ -64980,7 +64997,7 @@
       <c r="BE553" s="105">
         <v>1004</v>
       </c>
-      <c r="BF553" s="162">
+      <c r="BF553" s="122">
         <v>62</v>
       </c>
       <c r="BG553" s="106">
@@ -64996,7 +65013,7 @@
       <c r="BK553" s="8"/>
       <c r="BM553"/>
     </row>
-    <row r="554" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A554" s="3" t="s">
         <v>296</v>
       </c>
@@ -65024,7 +65041,9 @@
         <v>1.2515000000000001</v>
       </c>
       <c r="K554" s="10"/>
-      <c r="L554" s="10"/>
+      <c r="L554" s="25">
+        <v>0.159</v>
+      </c>
       <c r="M554" s="107">
         <v>0.15659999999999999</v>
       </c>
@@ -65092,7 +65111,7 @@
       <c r="BE554" s="105">
         <v>1004</v>
       </c>
-      <c r="BF554" s="162">
+      <c r="BF554" s="122">
         <v>62</v>
       </c>
       <c r="BG554" s="106">
@@ -65108,7 +65127,7 @@
       <c r="BK554" s="8"/>
       <c r="BM554"/>
     </row>
-    <row r="555" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A555" s="3" t="s">
         <v>296</v>
       </c>
@@ -65136,7 +65155,9 @@
         <v>1.2515000000000001</v>
       </c>
       <c r="K555" s="10"/>
-      <c r="L555" s="10"/>
+      <c r="L555" s="25">
+        <v>0.158</v>
+      </c>
       <c r="M555" s="107">
         <v>0.157</v>
       </c>
@@ -65204,7 +65225,7 @@
       <c r="BE555" s="105">
         <v>1004</v>
       </c>
-      <c r="BF555" s="162">
+      <c r="BF555" s="122">
         <v>61</v>
       </c>
       <c r="BG555" s="106">
@@ -65220,7 +65241,7 @@
       <c r="BK555" s="8"/>
       <c r="BM555"/>
     </row>
-    <row r="556" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A556" s="3" t="s">
         <v>296</v>
       </c>
@@ -65248,7 +65269,9 @@
         <v>1.2395</v>
       </c>
       <c r="K556" s="10"/>
-      <c r="L556" s="10"/>
+      <c r="L556" s="25">
+        <v>0.152</v>
+      </c>
       <c r="M556" s="107">
         <v>0.15140000000000001</v>
       </c>
@@ -65316,7 +65339,7 @@
       <c r="BE556" s="105">
         <v>1004</v>
       </c>
-      <c r="BF556" s="162">
+      <c r="BF556" s="122">
         <v>64</v>
       </c>
       <c r="BG556" s="106">
@@ -65332,7 +65355,7 @@
       <c r="BK556" s="8"/>
       <c r="BM556"/>
     </row>
-    <row r="557" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A557" s="3" t="s">
         <v>296</v>
       </c>
@@ -65360,7 +65383,9 @@
         <v>1.2395</v>
       </c>
       <c r="K557" s="10"/>
-      <c r="L557" s="10"/>
+      <c r="L557" s="25">
+        <v>0.155</v>
+      </c>
       <c r="M557" s="107">
         <v>0.15049999999999999</v>
       </c>
@@ -65428,7 +65453,7 @@
       <c r="BE557" s="105">
         <v>1004</v>
       </c>
-      <c r="BF557" s="162">
+      <c r="BF557" s="122">
         <v>64</v>
       </c>
       <c r="BG557" s="106">
@@ -65444,7 +65469,7 @@
       <c r="BK557" s="8"/>
       <c r="BM557"/>
     </row>
-    <row r="558" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A558" s="3" t="s">
         <v>296</v>
       </c>
@@ -65472,7 +65497,9 @@
         <v>1.2395</v>
       </c>
       <c r="K558" s="10"/>
-      <c r="L558" s="10"/>
+      <c r="L558" s="25">
+        <v>0.156</v>
+      </c>
       <c r="M558" s="107">
         <v>0.15290000000000001</v>
       </c>
@@ -65540,7 +65567,7 @@
       <c r="BE558" s="105">
         <v>1004</v>
       </c>
-      <c r="BF558" s="162">
+      <c r="BF558" s="122">
         <v>64</v>
       </c>
       <c r="BG558" s="106">
@@ -65556,7 +65583,7 @@
       <c r="BK558" s="8"/>
       <c r="BM558"/>
     </row>
-    <row r="559" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
         <v>296</v>
       </c>
@@ -65584,7 +65611,9 @@
         <v>1.2395</v>
       </c>
       <c r="K559" s="10"/>
-      <c r="L559" s="10"/>
+      <c r="L559" s="25">
+        <v>0.154</v>
+      </c>
       <c r="M559" s="107">
         <v>0.15160000000000001</v>
       </c>
@@ -65652,7 +65681,7 @@
       <c r="BE559" s="105">
         <v>1004</v>
       </c>
-      <c r="BF559" s="162">
+      <c r="BF559" s="122">
         <v>62</v>
       </c>
       <c r="BG559" s="106">
@@ -65668,7 +65697,7 @@
       <c r="BK559" s="8"/>
       <c r="BM559"/>
     </row>
-    <row r="560" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A560" s="3" t="s">
         <v>296</v>
       </c>
@@ -65696,7 +65725,9 @@
         <v>1.2395</v>
       </c>
       <c r="K560" s="10"/>
-      <c r="L560" s="10"/>
+      <c r="L560" s="25">
+        <v>0.155</v>
+      </c>
       <c r="M560" s="107">
         <v>0.15010000000000001</v>
       </c>
@@ -65764,7 +65795,7 @@
       <c r="BE560" s="105">
         <v>1004</v>
       </c>
-      <c r="BF560" s="162">
+      <c r="BF560" s="122">
         <v>62</v>
       </c>
       <c r="BG560" s="106">
@@ -65780,7 +65811,7 @@
       <c r="BK560" s="8"/>
       <c r="BM560"/>
     </row>
-    <row r="561" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
         <v>296</v>
       </c>
@@ -65808,7 +65839,9 @@
         <v>1.2395</v>
       </c>
       <c r="K561" s="10"/>
-      <c r="L561" s="10"/>
+      <c r="L561" s="25">
+        <v>0.159</v>
+      </c>
       <c r="M561" s="107">
         <v>0.15229999999999999</v>
       </c>
@@ -65876,7 +65909,7 @@
       <c r="BE561" s="105">
         <v>1004</v>
       </c>
-      <c r="BF561" s="162">
+      <c r="BF561" s="122">
         <v>61</v>
       </c>
       <c r="BG561" s="106">
@@ -65891,6 +65924,2561 @@
       </c>
       <c r="BK561" s="8"/>
       <c r="BM561"/>
+    </row>
+    <row r="562" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A562" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B562" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="C562" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D562" s="20">
+        <v>1</v>
+      </c>
+      <c r="E562" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="F562" s="10"/>
+      <c r="G562" s="10"/>
+      <c r="H562" s="8">
+        <v>0.1701</v>
+      </c>
+      <c r="I562" s="8">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="J562" s="8">
+        <v>1.2084999999999999</v>
+      </c>
+      <c r="K562" s="10"/>
+      <c r="L562" s="25">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="M562" s="107">
+        <v>0.1736</v>
+      </c>
+      <c r="N562" s="10"/>
+      <c r="O562" s="10"/>
+      <c r="P562" s="121">
+        <v>62.9</v>
+      </c>
+      <c r="Q562" s="107">
+        <v>567</v>
+      </c>
+      <c r="R562" s="112">
+        <v>755.6</v>
+      </c>
+      <c r="S562" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="T562" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="U562" s="5"/>
+      <c r="V562" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="W562" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="X562" s="5"/>
+      <c r="Y562" s="5"/>
+      <c r="Z562" s="5"/>
+      <c r="AA562" s="5"/>
+      <c r="AB562" s="5"/>
+      <c r="AC562" s="5"/>
+      <c r="AD562" s="5"/>
+      <c r="AE562" s="5"/>
+      <c r="AF562" s="5"/>
+      <c r="AG562" s="5"/>
+      <c r="AH562" s="5"/>
+      <c r="AI562" s="5"/>
+      <c r="AJ562" s="5"/>
+      <c r="AK562" s="5"/>
+      <c r="AL562" s="5"/>
+      <c r="AM562" s="5"/>
+      <c r="AN562" s="5"/>
+      <c r="AO562" s="5"/>
+      <c r="AP562" s="5"/>
+      <c r="AQ562" s="5"/>
+      <c r="AR562" s="5"/>
+      <c r="AS562" s="5"/>
+      <c r="AT562" s="5"/>
+      <c r="AU562" s="5"/>
+      <c r="AV562" s="5"/>
+      <c r="AW562" s="5"/>
+      <c r="AX562" s="5"/>
+      <c r="AY562" s="5"/>
+      <c r="AZ562" s="5"/>
+      <c r="BA562" s="117">
+        <v>117</v>
+      </c>
+      <c r="BB562" s="5"/>
+      <c r="BC562" s="5"/>
+      <c r="BD562" s="117">
+        <v>24.4</v>
+      </c>
+      <c r="BE562" s="105">
+        <v>1006</v>
+      </c>
+      <c r="BF562" s="122">
+        <v>53</v>
+      </c>
+      <c r="BG562" s="106">
+        <v>1.17</v>
+      </c>
+      <c r="BH562" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI562" s="5"/>
+      <c r="BJ562" s="4"/>
+      <c r="BK562" s="8"/>
+      <c r="BM562"/>
+    </row>
+    <row r="563" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A563" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B563" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="C563" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D563" s="20">
+        <v>2</v>
+      </c>
+      <c r="E563" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="F563" s="10"/>
+      <c r="G563" s="10"/>
+      <c r="H563" s="8">
+        <v>0.16889999999999999</v>
+      </c>
+      <c r="I563" s="8">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="J563" s="8">
+        <v>1.2084999999999999</v>
+      </c>
+      <c r="K563" s="10"/>
+      <c r="L563" s="25">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="M563" s="107">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="N563" s="10"/>
+      <c r="O563" s="10"/>
+      <c r="P563" s="121">
+        <v>63.5</v>
+      </c>
+      <c r="Q563" s="107">
+        <v>551</v>
+      </c>
+      <c r="R563" s="112">
+        <v>756.2</v>
+      </c>
+      <c r="S563" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="T563" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="U563" s="5"/>
+      <c r="V563" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="W563" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="X563" s="5"/>
+      <c r="Y563" s="5"/>
+      <c r="Z563" s="5"/>
+      <c r="AA563" s="5"/>
+      <c r="AB563" s="5"/>
+      <c r="AC563" s="5"/>
+      <c r="AD563" s="5"/>
+      <c r="AE563" s="5"/>
+      <c r="AF563" s="5"/>
+      <c r="AG563" s="5"/>
+      <c r="AH563" s="5"/>
+      <c r="AI563" s="5"/>
+      <c r="AJ563" s="5"/>
+      <c r="AK563" s="5"/>
+      <c r="AL563" s="5"/>
+      <c r="AM563" s="5"/>
+      <c r="AN563" s="5"/>
+      <c r="AO563" s="5"/>
+      <c r="AP563" s="5"/>
+      <c r="AQ563" s="5"/>
+      <c r="AR563" s="5"/>
+      <c r="AS563" s="5"/>
+      <c r="AT563" s="5"/>
+      <c r="AU563" s="5"/>
+      <c r="AV563" s="5"/>
+      <c r="AW563" s="5"/>
+      <c r="AX563" s="5"/>
+      <c r="AY563" s="5"/>
+      <c r="AZ563" s="5"/>
+      <c r="BA563" s="117">
+        <v>117</v>
+      </c>
+      <c r="BB563" s="5"/>
+      <c r="BC563" s="5"/>
+      <c r="BD563" s="117">
+        <v>24.8</v>
+      </c>
+      <c r="BE563" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF563" s="122">
+        <v>62</v>
+      </c>
+      <c r="BG563" s="106">
+        <v>1.167</v>
+      </c>
+      <c r="BH563" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI563" s="5"/>
+      <c r="BJ563" s="4"/>
+      <c r="BK563" s="8"/>
+      <c r="BM563"/>
+    </row>
+    <row r="564" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A564" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B564" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="C564" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D564" s="20">
+        <v>3</v>
+      </c>
+      <c r="E564" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="F564" s="10"/>
+      <c r="G564" s="10"/>
+      <c r="H564" s="8">
+        <v>0.17419999999999999</v>
+      </c>
+      <c r="I564" s="8">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="J564" s="8">
+        <v>1.2084999999999999</v>
+      </c>
+      <c r="K564" s="10"/>
+      <c r="L564" s="25"/>
+      <c r="M564" s="107">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="N564" s="10"/>
+      <c r="O564" s="10"/>
+      <c r="P564" s="121">
+        <v>62.2</v>
+      </c>
+      <c r="Q564" s="107">
+        <v>534</v>
+      </c>
+      <c r="R564" s="112">
+        <v>756.2</v>
+      </c>
+      <c r="S564" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="T564" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="U564" s="5"/>
+      <c r="V564" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="W564" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="X564" s="5"/>
+      <c r="Y564" s="5"/>
+      <c r="Z564" s="5"/>
+      <c r="AA564" s="5"/>
+      <c r="AB564" s="5"/>
+      <c r="AC564" s="5"/>
+      <c r="AD564" s="5"/>
+      <c r="AE564" s="5"/>
+      <c r="AF564" s="5"/>
+      <c r="AG564" s="5"/>
+      <c r="AH564" s="5"/>
+      <c r="AI564" s="5"/>
+      <c r="AJ564" s="5"/>
+      <c r="AK564" s="5"/>
+      <c r="AL564" s="5"/>
+      <c r="AM564" s="5"/>
+      <c r="AN564" s="5"/>
+      <c r="AO564" s="5"/>
+      <c r="AP564" s="5"/>
+      <c r="AQ564" s="5"/>
+      <c r="AR564" s="5"/>
+      <c r="AS564" s="5"/>
+      <c r="AT564" s="5"/>
+      <c r="AU564" s="5"/>
+      <c r="AV564" s="5"/>
+      <c r="AW564" s="5"/>
+      <c r="AX564" s="5"/>
+      <c r="AY564" s="5"/>
+      <c r="AZ564" s="5"/>
+      <c r="BA564" s="117">
+        <v>117</v>
+      </c>
+      <c r="BB564" s="5"/>
+      <c r="BC564" s="5"/>
+      <c r="BD564" s="117">
+        <v>25.1</v>
+      </c>
+      <c r="BE564" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF564" s="122">
+        <v>51</v>
+      </c>
+      <c r="BG564" s="106">
+        <v>1.167</v>
+      </c>
+      <c r="BH564" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI564" s="5"/>
+      <c r="BJ564" s="4"/>
+      <c r="BK564" s="8"/>
+      <c r="BM564"/>
+    </row>
+    <row r="565" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A565" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B565" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="C565" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D565" s="20">
+        <v>4</v>
+      </c>
+      <c r="E565" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="F565" s="10"/>
+      <c r="G565" s="10"/>
+      <c r="H565" s="8">
+        <v>0.17050000000000001</v>
+      </c>
+      <c r="I565" s="8">
+        <v>1.8E-3</v>
+      </c>
+      <c r="J565" s="8">
+        <v>1.2084999999999999</v>
+      </c>
+      <c r="K565" s="10"/>
+      <c r="L565" s="25">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="M565" s="107">
+        <v>0.17219999999999999</v>
+      </c>
+      <c r="N565" s="10"/>
+      <c r="O565" s="10"/>
+      <c r="P565" s="121">
+        <v>63</v>
+      </c>
+      <c r="Q565" s="107">
+        <v>560</v>
+      </c>
+      <c r="R565" s="112">
+        <v>756.1</v>
+      </c>
+      <c r="S565" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="T565" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="U565" s="5"/>
+      <c r="V565" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="W565" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="X565" s="5"/>
+      <c r="Y565" s="5"/>
+      <c r="Z565" s="5"/>
+      <c r="AA565" s="5"/>
+      <c r="AB565" s="5"/>
+      <c r="AC565" s="5"/>
+      <c r="AD565" s="5"/>
+      <c r="AE565" s="5"/>
+      <c r="AF565" s="5"/>
+      <c r="AG565" s="5"/>
+      <c r="AH565" s="5"/>
+      <c r="AI565" s="5"/>
+      <c r="AJ565" s="5"/>
+      <c r="AK565" s="5"/>
+      <c r="AL565" s="5"/>
+      <c r="AM565" s="5"/>
+      <c r="AN565" s="5"/>
+      <c r="AO565" s="5"/>
+      <c r="AP565" s="5"/>
+      <c r="AQ565" s="5"/>
+      <c r="AR565" s="5"/>
+      <c r="AS565" s="5"/>
+      <c r="AT565" s="5"/>
+      <c r="AU565" s="5"/>
+      <c r="AV565" s="5"/>
+      <c r="AW565" s="5"/>
+      <c r="AX565" s="5"/>
+      <c r="AY565" s="5"/>
+      <c r="AZ565" s="5"/>
+      <c r="BA565" s="117">
+        <v>117</v>
+      </c>
+      <c r="BB565" s="5"/>
+      <c r="BC565" s="5"/>
+      <c r="BD565" s="117">
+        <v>25.9</v>
+      </c>
+      <c r="BE565" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF565" s="122">
+        <v>56</v>
+      </c>
+      <c r="BG565" s="106">
+        <v>1.1619999999999999</v>
+      </c>
+      <c r="BH565" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI565" s="5"/>
+      <c r="BJ565" s="4"/>
+      <c r="BK565" s="8"/>
+      <c r="BM565"/>
+    </row>
+    <row r="566" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A566" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B566" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="C566" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D566" s="20">
+        <v>5</v>
+      </c>
+      <c r="E566" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="F566" s="10"/>
+      <c r="G566" s="10"/>
+      <c r="H566" s="8">
+        <v>0.16739999999999999</v>
+      </c>
+      <c r="I566" s="8">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="J566" s="8">
+        <v>1.2084999999999999</v>
+      </c>
+      <c r="K566" s="10"/>
+      <c r="L566" s="25">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="M566" s="107">
+        <v>0.1663</v>
+      </c>
+      <c r="N566" s="10"/>
+      <c r="O566" s="10"/>
+      <c r="P566" s="121">
+        <v>63.7</v>
+      </c>
+      <c r="Q566" s="107">
+        <v>581</v>
+      </c>
+      <c r="R566" s="112">
+        <v>756.6</v>
+      </c>
+      <c r="S566" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="T566" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="U566" s="5"/>
+      <c r="V566" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="W566" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="X566" s="5"/>
+      <c r="Y566" s="5"/>
+      <c r="Z566" s="5"/>
+      <c r="AA566" s="5"/>
+      <c r="AB566" s="5"/>
+      <c r="AC566" s="5"/>
+      <c r="AD566" s="5"/>
+      <c r="AE566" s="5"/>
+      <c r="AF566" s="5"/>
+      <c r="AG566" s="5"/>
+      <c r="AH566" s="5"/>
+      <c r="AI566" s="5"/>
+      <c r="AJ566" s="5"/>
+      <c r="AK566" s="5"/>
+      <c r="AL566" s="5"/>
+      <c r="AM566" s="5"/>
+      <c r="AN566" s="5"/>
+      <c r="AO566" s="5"/>
+      <c r="AP566" s="5"/>
+      <c r="AQ566" s="5"/>
+      <c r="AR566" s="5"/>
+      <c r="AS566" s="5"/>
+      <c r="AT566" s="5"/>
+      <c r="AU566" s="5"/>
+      <c r="AV566" s="5"/>
+      <c r="AW566" s="5"/>
+      <c r="AX566" s="5"/>
+      <c r="AY566" s="5"/>
+      <c r="AZ566" s="5"/>
+      <c r="BA566" s="117">
+        <v>117</v>
+      </c>
+      <c r="BB566" s="5"/>
+      <c r="BC566" s="5"/>
+      <c r="BD566" s="117">
+        <v>25.9</v>
+      </c>
+      <c r="BE566" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF566" s="122">
+        <v>56</v>
+      </c>
+      <c r="BG566" s="106">
+        <v>1.1619999999999999</v>
+      </c>
+      <c r="BH566" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI566" s="5"/>
+      <c r="BJ566" s="4"/>
+      <c r="BK566" s="8"/>
+      <c r="BM566"/>
+    </row>
+    <row r="567" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A567" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B567" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="C567" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D567" s="20">
+        <v>6</v>
+      </c>
+      <c r="E567" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="F567" s="10"/>
+      <c r="G567" s="10"/>
+      <c r="H567" s="8">
+        <v>0.17069999999999999</v>
+      </c>
+      <c r="I567" s="8">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="J567" s="8">
+        <v>1.2084999999999999</v>
+      </c>
+      <c r="K567" s="10"/>
+      <c r="L567" s="25">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="M567" s="107">
+        <v>0.1699</v>
+      </c>
+      <c r="N567" s="10"/>
+      <c r="O567" s="10"/>
+      <c r="P567" s="121">
+        <v>63.7</v>
+      </c>
+      <c r="Q567" s="107">
+        <v>558</v>
+      </c>
+      <c r="R567" s="112">
+        <v>756.5</v>
+      </c>
+      <c r="S567" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="T567" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="U567" s="5"/>
+      <c r="V567" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="W567" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="X567" s="5"/>
+      <c r="Y567" s="5"/>
+      <c r="Z567" s="5"/>
+      <c r="AA567" s="5"/>
+      <c r="AB567" s="5"/>
+      <c r="AC567" s="5"/>
+      <c r="AD567" s="5"/>
+      <c r="AE567" s="5"/>
+      <c r="AF567" s="5"/>
+      <c r="AG567" s="5"/>
+      <c r="AH567" s="5"/>
+      <c r="AI567" s="5"/>
+      <c r="AJ567" s="5"/>
+      <c r="AK567" s="5"/>
+      <c r="AL567" s="5"/>
+      <c r="AM567" s="5"/>
+      <c r="AN567" s="5"/>
+      <c r="AO567" s="5"/>
+      <c r="AP567" s="5"/>
+      <c r="AQ567" s="5"/>
+      <c r="AR567" s="5"/>
+      <c r="AS567" s="5"/>
+      <c r="AT567" s="5"/>
+      <c r="AU567" s="5"/>
+      <c r="AV567" s="5"/>
+      <c r="AW567" s="5"/>
+      <c r="AX567" s="5"/>
+      <c r="AY567" s="5"/>
+      <c r="AZ567" s="5"/>
+      <c r="BA567" s="117">
+        <v>117</v>
+      </c>
+      <c r="BB567" s="5"/>
+      <c r="BC567" s="5"/>
+      <c r="BD567" s="117">
+        <v>26.4</v>
+      </c>
+      <c r="BE567" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF567" s="122">
+        <v>48</v>
+      </c>
+      <c r="BG567" s="106">
+        <v>1.1619999999999999</v>
+      </c>
+      <c r="BH567" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI567" s="5"/>
+      <c r="BJ567" s="4"/>
+      <c r="BK567" s="8"/>
+      <c r="BM567"/>
+    </row>
+    <row r="568" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A568" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B568" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="C568" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D568" s="20">
+        <v>1</v>
+      </c>
+      <c r="E568" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="F568" s="10"/>
+      <c r="G568" s="10"/>
+      <c r="H568" s="8">
+        <v>0.1673</v>
+      </c>
+      <c r="I568" s="8">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="J568" s="8">
+        <v>1.258</v>
+      </c>
+      <c r="K568" s="10"/>
+      <c r="L568" s="25">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="M568" s="107">
+        <v>0.16689999999999999</v>
+      </c>
+      <c r="N568" s="10"/>
+      <c r="O568" s="10"/>
+      <c r="P568" s="121">
+        <v>63.4</v>
+      </c>
+      <c r="Q568" s="107">
+        <v>553</v>
+      </c>
+      <c r="R568" s="112">
+        <v>754</v>
+      </c>
+      <c r="S568" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="T568" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="U568" s="5"/>
+      <c r="V568" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="W568" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="X568" s="5"/>
+      <c r="Y568" s="5"/>
+      <c r="Z568" s="5"/>
+      <c r="AA568" s="5"/>
+      <c r="AB568" s="5"/>
+      <c r="AC568" s="5"/>
+      <c r="AD568" s="5"/>
+      <c r="AE568" s="5"/>
+      <c r="AF568" s="5"/>
+      <c r="AG568" s="5"/>
+      <c r="AH568" s="5"/>
+      <c r="AI568" s="5"/>
+      <c r="AJ568" s="5"/>
+      <c r="AK568" s="5"/>
+      <c r="AL568" s="5"/>
+      <c r="AM568" s="5"/>
+      <c r="AN568" s="5"/>
+      <c r="AO568" s="5"/>
+      <c r="AP568" s="5"/>
+      <c r="AQ568" s="5"/>
+      <c r="AR568" s="5"/>
+      <c r="AS568" s="5"/>
+      <c r="AT568" s="5"/>
+      <c r="AU568" s="5"/>
+      <c r="AV568" s="5"/>
+      <c r="AW568" s="5"/>
+      <c r="AX568" s="5"/>
+      <c r="AY568" s="5"/>
+      <c r="AZ568" s="5"/>
+      <c r="BA568" s="117">
+        <v>117</v>
+      </c>
+      <c r="BB568" s="5"/>
+      <c r="BC568" s="5"/>
+      <c r="BD568" s="117">
+        <v>24.4</v>
+      </c>
+      <c r="BE568" s="105">
+        <v>1006</v>
+      </c>
+      <c r="BF568" s="122">
+        <v>53</v>
+      </c>
+      <c r="BG568" s="106">
+        <v>1.171</v>
+      </c>
+      <c r="BH568" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI568" s="5"/>
+      <c r="BJ568" s="4"/>
+      <c r="BK568" s="8"/>
+      <c r="BM568"/>
+    </row>
+    <row r="569" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A569" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B569" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="C569" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D569" s="20">
+        <v>2</v>
+      </c>
+      <c r="E569" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="F569" s="10"/>
+      <c r="G569" s="10"/>
+      <c r="H569" s="8">
+        <v>0.16109999999999999</v>
+      </c>
+      <c r="I569" s="8">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="J569" s="8">
+        <v>1.258</v>
+      </c>
+      <c r="K569" s="10"/>
+      <c r="L569" s="25">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="M569" s="107">
+        <v>0.16320000000000001</v>
+      </c>
+      <c r="N569" s="10"/>
+      <c r="O569" s="10"/>
+      <c r="P569" s="121">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="Q569" s="107">
+        <v>566</v>
+      </c>
+      <c r="R569" s="112">
+        <v>753.9</v>
+      </c>
+      <c r="S569" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="T569" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="U569" s="5"/>
+      <c r="V569" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="W569" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="X569" s="5"/>
+      <c r="Y569" s="5"/>
+      <c r="Z569" s="5"/>
+      <c r="AA569" s="5"/>
+      <c r="AB569" s="5"/>
+      <c r="AC569" s="5"/>
+      <c r="AD569" s="5"/>
+      <c r="AE569" s="5"/>
+      <c r="AF569" s="5"/>
+      <c r="AG569" s="5"/>
+      <c r="AH569" s="5"/>
+      <c r="AI569" s="5"/>
+      <c r="AJ569" s="5"/>
+      <c r="AK569" s="5"/>
+      <c r="AL569" s="5"/>
+      <c r="AM569" s="5"/>
+      <c r="AN569" s="5"/>
+      <c r="AO569" s="5"/>
+      <c r="AP569" s="5"/>
+      <c r="AQ569" s="5"/>
+      <c r="AR569" s="5"/>
+      <c r="AS569" s="5"/>
+      <c r="AT569" s="5"/>
+      <c r="AU569" s="5"/>
+      <c r="AV569" s="5"/>
+      <c r="AW569" s="5"/>
+      <c r="AX569" s="5"/>
+      <c r="AY569" s="5"/>
+      <c r="AZ569" s="5"/>
+      <c r="BA569" s="117">
+        <v>117</v>
+      </c>
+      <c r="BB569" s="5"/>
+      <c r="BC569" s="5"/>
+      <c r="BD569" s="117">
+        <v>24.4</v>
+      </c>
+      <c r="BE569" s="105">
+        <v>1006</v>
+      </c>
+      <c r="BF569" s="122">
+        <v>53</v>
+      </c>
+      <c r="BG569" s="106">
+        <v>1.17</v>
+      </c>
+      <c r="BH569" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI569" s="5"/>
+      <c r="BJ569" s="4"/>
+      <c r="BK569" s="8"/>
+      <c r="BM569"/>
+    </row>
+    <row r="570" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A570" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B570" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="C570" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D570" s="20">
+        <v>3</v>
+      </c>
+      <c r="E570" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="F570" s="10"/>
+      <c r="G570" s="10"/>
+      <c r="H570" s="8">
+        <v>0.1696</v>
+      </c>
+      <c r="I570" s="8">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="J570" s="8">
+        <v>1.258</v>
+      </c>
+      <c r="K570" s="10"/>
+      <c r="L570" s="25">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="M570" s="107">
+        <v>0.16719999999999999</v>
+      </c>
+      <c r="N570" s="10"/>
+      <c r="O570" s="10"/>
+      <c r="P570" s="121">
+        <v>63.8</v>
+      </c>
+      <c r="Q570" s="107">
+        <v>559</v>
+      </c>
+      <c r="R570" s="112">
+        <v>755.2</v>
+      </c>
+      <c r="S570" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="T570" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="U570" s="5"/>
+      <c r="V570" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="W570" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="X570" s="5"/>
+      <c r="Y570" s="5"/>
+      <c r="Z570" s="5"/>
+      <c r="AA570" s="5"/>
+      <c r="AB570" s="5"/>
+      <c r="AC570" s="5"/>
+      <c r="AD570" s="5"/>
+      <c r="AE570" s="5"/>
+      <c r="AF570" s="5"/>
+      <c r="AG570" s="5"/>
+      <c r="AH570" s="5"/>
+      <c r="AI570" s="5"/>
+      <c r="AJ570" s="5"/>
+      <c r="AK570" s="5"/>
+      <c r="AL570" s="5"/>
+      <c r="AM570" s="5"/>
+      <c r="AN570" s="5"/>
+      <c r="AO570" s="5"/>
+      <c r="AP570" s="5"/>
+      <c r="AQ570" s="5"/>
+      <c r="AR570" s="5"/>
+      <c r="AS570" s="5"/>
+      <c r="AT570" s="5"/>
+      <c r="AU570" s="5"/>
+      <c r="AV570" s="5"/>
+      <c r="AW570" s="5"/>
+      <c r="AX570" s="5"/>
+      <c r="AY570" s="5"/>
+      <c r="AZ570" s="5"/>
+      <c r="BA570" s="117">
+        <v>117</v>
+      </c>
+      <c r="BB570" s="5"/>
+      <c r="BC570" s="5"/>
+      <c r="BD570" s="117">
+        <v>25.1</v>
+      </c>
+      <c r="BE570" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF570" s="122">
+        <v>51</v>
+      </c>
+      <c r="BG570" s="106">
+        <v>1.167</v>
+      </c>
+      <c r="BH570" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI570" s="5"/>
+      <c r="BJ570" s="4"/>
+      <c r="BK570" s="8"/>
+      <c r="BM570"/>
+    </row>
+    <row r="571" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A571" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B571" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="C571" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D571" s="20">
+        <v>4</v>
+      </c>
+      <c r="E571" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="F571" s="10"/>
+      <c r="G571" s="10"/>
+      <c r="H571" s="8">
+        <v>0.16789999999999999</v>
+      </c>
+      <c r="I571" s="8">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="J571" s="8">
+        <v>1.258</v>
+      </c>
+      <c r="K571" s="10"/>
+      <c r="L571" s="25"/>
+      <c r="M571" s="107">
+        <v>0.16839999999999999</v>
+      </c>
+      <c r="N571" s="10"/>
+      <c r="O571" s="10"/>
+      <c r="P571" s="121">
+        <v>63.5</v>
+      </c>
+      <c r="Q571" s="107">
+        <v>570</v>
+      </c>
+      <c r="R571" s="112">
+        <v>754.1</v>
+      </c>
+      <c r="S571" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="T571" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="U571" s="5"/>
+      <c r="V571" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="W571" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="X571" s="5"/>
+      <c r="Y571" s="5"/>
+      <c r="Z571" s="5"/>
+      <c r="AA571" s="5"/>
+      <c r="AB571" s="5"/>
+      <c r="AC571" s="5"/>
+      <c r="AD571" s="5"/>
+      <c r="AE571" s="5"/>
+      <c r="AF571" s="5"/>
+      <c r="AG571" s="5"/>
+      <c r="AH571" s="5"/>
+      <c r="AI571" s="5"/>
+      <c r="AJ571" s="5"/>
+      <c r="AK571" s="5"/>
+      <c r="AL571" s="5"/>
+      <c r="AM571" s="5"/>
+      <c r="AN571" s="5"/>
+      <c r="AO571" s="5"/>
+      <c r="AP571" s="5"/>
+      <c r="AQ571" s="5"/>
+      <c r="AR571" s="5"/>
+      <c r="AS571" s="5"/>
+      <c r="AT571" s="5"/>
+      <c r="AU571" s="5"/>
+      <c r="AV571" s="5"/>
+      <c r="AW571" s="5"/>
+      <c r="AX571" s="5"/>
+      <c r="AY571" s="5"/>
+      <c r="AZ571" s="5"/>
+      <c r="BA571" s="117">
+        <v>117</v>
+      </c>
+      <c r="BB571" s="5"/>
+      <c r="BC571" s="5"/>
+      <c r="BD571" s="117">
+        <v>25.7</v>
+      </c>
+      <c r="BE571" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF571" s="122">
+        <v>61</v>
+      </c>
+      <c r="BG571" s="106">
+        <v>1.163</v>
+      </c>
+      <c r="BH571" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI571" s="5"/>
+      <c r="BJ571" s="4"/>
+      <c r="BK571" s="8"/>
+      <c r="BM571"/>
+    </row>
+    <row r="572" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A572" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B572" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="C572" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D572" s="20">
+        <v>5</v>
+      </c>
+      <c r="E572" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="F572" s="10"/>
+      <c r="G572" s="10"/>
+      <c r="H572" s="8">
+        <v>0.16170000000000001</v>
+      </c>
+      <c r="I572" s="8">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="J572" s="8">
+        <v>1.258</v>
+      </c>
+      <c r="K572" s="10"/>
+      <c r="L572" s="25"/>
+      <c r="M572" s="107">
+        <v>0.1633</v>
+      </c>
+      <c r="N572" s="10"/>
+      <c r="O572" s="10"/>
+      <c r="P572" s="121">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="Q572" s="107">
+        <v>572</v>
+      </c>
+      <c r="R572" s="112">
+        <v>754.5</v>
+      </c>
+      <c r="S572" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="T572" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="U572" s="5"/>
+      <c r="V572" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="W572" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="X572" s="5"/>
+      <c r="Y572" s="5"/>
+      <c r="Z572" s="5"/>
+      <c r="AA572" s="5"/>
+      <c r="AB572" s="5"/>
+      <c r="AC572" s="5"/>
+      <c r="AD572" s="5"/>
+      <c r="AE572" s="5"/>
+      <c r="AF572" s="5"/>
+      <c r="AG572" s="5"/>
+      <c r="AH572" s="5"/>
+      <c r="AI572" s="5"/>
+      <c r="AJ572" s="5"/>
+      <c r="AK572" s="5"/>
+      <c r="AL572" s="5"/>
+      <c r="AM572" s="5"/>
+      <c r="AN572" s="5"/>
+      <c r="AO572" s="5"/>
+      <c r="AP572" s="5"/>
+      <c r="AQ572" s="5"/>
+      <c r="AR572" s="5"/>
+      <c r="AS572" s="5"/>
+      <c r="AT572" s="5"/>
+      <c r="AU572" s="5"/>
+      <c r="AV572" s="5"/>
+      <c r="AW572" s="5"/>
+      <c r="AX572" s="5"/>
+      <c r="AY572" s="5"/>
+      <c r="AZ572" s="5"/>
+      <c r="BA572" s="117">
+        <v>117</v>
+      </c>
+      <c r="BB572" s="5"/>
+      <c r="BC572" s="5"/>
+      <c r="BD572" s="117">
+        <v>25.9</v>
+      </c>
+      <c r="BE572" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF572" s="122">
+        <v>56</v>
+      </c>
+      <c r="BG572" s="106">
+        <v>1.1619999999999999</v>
+      </c>
+      <c r="BH572" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI572" s="5"/>
+      <c r="BJ572" s="4"/>
+      <c r="BK572" s="8"/>
+      <c r="BM572"/>
+    </row>
+    <row r="573" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A573" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B573" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="C573" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D573" s="20">
+        <v>6</v>
+      </c>
+      <c r="E573" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="F573" s="10"/>
+      <c r="G573" s="10"/>
+      <c r="H573" s="8">
+        <v>0.16789999999999999</v>
+      </c>
+      <c r="I573" s="8">
+        <v>2E-3</v>
+      </c>
+      <c r="J573" s="8">
+        <v>1.258</v>
+      </c>
+      <c r="K573" s="10"/>
+      <c r="L573" s="25"/>
+      <c r="M573" s="107">
+        <v>0.16819999999999999</v>
+      </c>
+      <c r="N573" s="10"/>
+      <c r="O573" s="10"/>
+      <c r="P573" s="121">
+        <v>62.9</v>
+      </c>
+      <c r="Q573" s="107">
+        <v>557</v>
+      </c>
+      <c r="R573" s="112">
+        <v>754.3</v>
+      </c>
+      <c r="S573" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="T573" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="U573" s="5"/>
+      <c r="V573" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="W573" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="X573" s="5"/>
+      <c r="Y573" s="5"/>
+      <c r="Z573" s="5"/>
+      <c r="AA573" s="5"/>
+      <c r="AB573" s="5"/>
+      <c r="AC573" s="5"/>
+      <c r="AD573" s="5"/>
+      <c r="AE573" s="5"/>
+      <c r="AF573" s="5"/>
+      <c r="AG573" s="5"/>
+      <c r="AH573" s="5"/>
+      <c r="AI573" s="5"/>
+      <c r="AJ573" s="5"/>
+      <c r="AK573" s="5"/>
+      <c r="AL573" s="5"/>
+      <c r="AM573" s="5"/>
+      <c r="AN573" s="5"/>
+      <c r="AO573" s="5"/>
+      <c r="AP573" s="5"/>
+      <c r="AQ573" s="5"/>
+      <c r="AR573" s="5"/>
+      <c r="AS573" s="5"/>
+      <c r="AT573" s="5"/>
+      <c r="AU573" s="5"/>
+      <c r="AV573" s="5"/>
+      <c r="AW573" s="5"/>
+      <c r="AX573" s="5"/>
+      <c r="AY573" s="5"/>
+      <c r="AZ573" s="5"/>
+      <c r="BA573" s="117">
+        <v>117</v>
+      </c>
+      <c r="BB573" s="5"/>
+      <c r="BC573" s="5"/>
+      <c r="BD573" s="117">
+        <v>26.4</v>
+      </c>
+      <c r="BE573" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF573" s="122">
+        <v>48</v>
+      </c>
+      <c r="BG573" s="106">
+        <v>1.1619999999999999</v>
+      </c>
+      <c r="BH573" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI573" s="5"/>
+      <c r="BJ573" s="4"/>
+      <c r="BK573" s="8"/>
+      <c r="BM573"/>
+    </row>
+    <row r="574" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A574" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B574" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C574" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D574" s="20">
+        <v>1</v>
+      </c>
+      <c r="E574" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="F574" s="10"/>
+      <c r="G574" s="10"/>
+      <c r="H574" s="8">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="I574" s="8">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="J574" s="8">
+        <v>1.2905</v>
+      </c>
+      <c r="K574" s="10"/>
+      <c r="L574" s="25">
+        <v>0.16</v>
+      </c>
+      <c r="M574" s="107">
+        <v>0.16489999999999999</v>
+      </c>
+      <c r="N574" s="10"/>
+      <c r="O574" s="10"/>
+      <c r="P574" s="121">
+        <v>60.8</v>
+      </c>
+      <c r="Q574" s="107">
+        <v>475</v>
+      </c>
+      <c r="R574" s="112">
+        <v>755.5</v>
+      </c>
+      <c r="S574" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="T574" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="U574" s="5"/>
+      <c r="V574" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="W574" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="X574" s="5"/>
+      <c r="Y574" s="5"/>
+      <c r="Z574" s="5"/>
+      <c r="AA574" s="5"/>
+      <c r="AB574" s="5"/>
+      <c r="AC574" s="5"/>
+      <c r="AD574" s="5"/>
+      <c r="AE574" s="5"/>
+      <c r="AF574" s="5"/>
+      <c r="AG574" s="5"/>
+      <c r="AH574" s="5"/>
+      <c r="AI574" s="5"/>
+      <c r="AJ574" s="5"/>
+      <c r="AK574" s="5"/>
+      <c r="AL574" s="5"/>
+      <c r="AM574" s="5"/>
+      <c r="AN574" s="5"/>
+      <c r="AO574" s="5"/>
+      <c r="AP574" s="5"/>
+      <c r="AQ574" s="5"/>
+      <c r="AR574" s="5"/>
+      <c r="AS574" s="5"/>
+      <c r="AT574" s="5"/>
+      <c r="AU574" s="5"/>
+      <c r="AV574" s="5"/>
+      <c r="AW574" s="5"/>
+      <c r="AX574" s="5"/>
+      <c r="AY574" s="5"/>
+      <c r="AZ574" s="5"/>
+      <c r="BA574" s="117">
+        <v>111.6</v>
+      </c>
+      <c r="BB574" s="5"/>
+      <c r="BC574" s="5"/>
+      <c r="BD574" s="117">
+        <v>24.4</v>
+      </c>
+      <c r="BE574" s="105">
+        <v>1006</v>
+      </c>
+      <c r="BF574" s="122">
+        <v>53</v>
+      </c>
+      <c r="BG574" s="106">
+        <v>1.171</v>
+      </c>
+      <c r="BH574" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI574" s="5"/>
+      <c r="BJ574" s="4"/>
+      <c r="BK574" s="8"/>
+      <c r="BM574"/>
+    </row>
+    <row r="575" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A575" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B575" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C575" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D575" s="20">
+        <v>2</v>
+      </c>
+      <c r="E575" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="F575" s="10"/>
+      <c r="G575" s="10"/>
+      <c r="H575" s="8">
+        <v>0.16</v>
+      </c>
+      <c r="I575" s="8">
+        <v>1.5E-3</v>
+      </c>
+      <c r="J575" s="8">
+        <v>1.2905</v>
+      </c>
+      <c r="K575" s="10"/>
+      <c r="L575" s="25">
+        <v>0.159</v>
+      </c>
+      <c r="M575" s="107">
+        <v>0.16139999999999999</v>
+      </c>
+      <c r="N575" s="10"/>
+      <c r="O575" s="10"/>
+      <c r="P575" s="121">
+        <v>61.2</v>
+      </c>
+      <c r="Q575" s="107">
+        <v>487</v>
+      </c>
+      <c r="R575" s="112">
+        <v>755.3</v>
+      </c>
+      <c r="S575" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="T575" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="U575" s="5"/>
+      <c r="V575" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="W575" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="X575" s="5"/>
+      <c r="Y575" s="5"/>
+      <c r="Z575" s="5"/>
+      <c r="AA575" s="5"/>
+      <c r="AB575" s="5"/>
+      <c r="AC575" s="5"/>
+      <c r="AD575" s="5"/>
+      <c r="AE575" s="5"/>
+      <c r="AF575" s="5"/>
+      <c r="AG575" s="5"/>
+      <c r="AH575" s="5"/>
+      <c r="AI575" s="5"/>
+      <c r="AJ575" s="5"/>
+      <c r="AK575" s="5"/>
+      <c r="AL575" s="5"/>
+      <c r="AM575" s="5"/>
+      <c r="AN575" s="5"/>
+      <c r="AO575" s="5"/>
+      <c r="AP575" s="5"/>
+      <c r="AQ575" s="5"/>
+      <c r="AR575" s="5"/>
+      <c r="AS575" s="5"/>
+      <c r="AT575" s="5"/>
+      <c r="AU575" s="5"/>
+      <c r="AV575" s="5"/>
+      <c r="AW575" s="5"/>
+      <c r="AX575" s="5"/>
+      <c r="AY575" s="5"/>
+      <c r="AZ575" s="5"/>
+      <c r="BA575" s="117">
+        <v>111.6</v>
+      </c>
+      <c r="BB575" s="5"/>
+      <c r="BC575" s="5"/>
+      <c r="BD575" s="117">
+        <v>24.4</v>
+      </c>
+      <c r="BE575" s="105">
+        <v>1006</v>
+      </c>
+      <c r="BF575" s="122">
+        <v>53</v>
+      </c>
+      <c r="BG575" s="106">
+        <v>1.17</v>
+      </c>
+      <c r="BH575" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI575" s="5"/>
+      <c r="BJ575" s="4"/>
+      <c r="BK575" s="8"/>
+      <c r="BM575"/>
+    </row>
+    <row r="576" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A576" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B576" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C576" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D576" s="20">
+        <v>3</v>
+      </c>
+      <c r="E576" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="F576" s="10"/>
+      <c r="G576" s="10"/>
+      <c r="H576" s="8">
+        <v>0.1636</v>
+      </c>
+      <c r="I576" s="8">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="J576" s="8">
+        <v>1.2905</v>
+      </c>
+      <c r="K576" s="10"/>
+      <c r="L576" s="25">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="M576" s="107">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="N576" s="10"/>
+      <c r="O576" s="10"/>
+      <c r="P576" s="121">
+        <v>61.8</v>
+      </c>
+      <c r="Q576" s="107">
+        <v>497</v>
+      </c>
+      <c r="R576" s="112">
+        <v>756</v>
+      </c>
+      <c r="S576" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="T576" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="U576" s="5"/>
+      <c r="V576" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="W576" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="X576" s="5"/>
+      <c r="Y576" s="5"/>
+      <c r="Z576" s="5"/>
+      <c r="AA576" s="5"/>
+      <c r="AB576" s="5"/>
+      <c r="AC576" s="5"/>
+      <c r="AD576" s="5"/>
+      <c r="AE576" s="5"/>
+      <c r="AF576" s="5"/>
+      <c r="AG576" s="5"/>
+      <c r="AH576" s="5"/>
+      <c r="AI576" s="5"/>
+      <c r="AJ576" s="5"/>
+      <c r="AK576" s="5"/>
+      <c r="AL576" s="5"/>
+      <c r="AM576" s="5"/>
+      <c r="AN576" s="5"/>
+      <c r="AO576" s="5"/>
+      <c r="AP576" s="5"/>
+      <c r="AQ576" s="5"/>
+      <c r="AR576" s="5"/>
+      <c r="AS576" s="5"/>
+      <c r="AT576" s="5"/>
+      <c r="AU576" s="5"/>
+      <c r="AV576" s="5"/>
+      <c r="AW576" s="5"/>
+      <c r="AX576" s="5"/>
+      <c r="AY576" s="5"/>
+      <c r="AZ576" s="5"/>
+      <c r="BA576" s="117">
+        <v>111.6</v>
+      </c>
+      <c r="BB576" s="5"/>
+      <c r="BC576" s="5"/>
+      <c r="BD576" s="117">
+        <v>25.1</v>
+      </c>
+      <c r="BE576" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF576" s="122">
+        <v>51</v>
+      </c>
+      <c r="BG576" s="106">
+        <v>1.167</v>
+      </c>
+      <c r="BH576" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI576" s="5"/>
+      <c r="BJ576" s="4"/>
+      <c r="BK576" s="8"/>
+      <c r="BM576"/>
+    </row>
+    <row r="577" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A577" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B577" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C577" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D577" s="20">
+        <v>4</v>
+      </c>
+      <c r="E577" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="F577" s="10"/>
+      <c r="G577" s="10"/>
+      <c r="H577" s="8">
+        <v>0.1696</v>
+      </c>
+      <c r="I577" s="8">
+        <v>1.4E-3</v>
+      </c>
+      <c r="J577" s="8">
+        <v>1.2905</v>
+      </c>
+      <c r="K577" s="10"/>
+      <c r="L577" s="25">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="M577" s="107">
+        <v>0.16719999999999999</v>
+      </c>
+      <c r="N577" s="10"/>
+      <c r="O577" s="10"/>
+      <c r="P577" s="121">
+        <v>61.4</v>
+      </c>
+      <c r="Q577" s="107">
+        <v>492</v>
+      </c>
+      <c r="R577" s="112">
+        <v>756.1</v>
+      </c>
+      <c r="S577" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="T577" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="U577" s="5"/>
+      <c r="V577" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="W577" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="X577" s="5"/>
+      <c r="Y577" s="5"/>
+      <c r="Z577" s="5"/>
+      <c r="AA577" s="5"/>
+      <c r="AB577" s="5"/>
+      <c r="AC577" s="5"/>
+      <c r="AD577" s="5"/>
+      <c r="AE577" s="5"/>
+      <c r="AF577" s="5"/>
+      <c r="AG577" s="5"/>
+      <c r="AH577" s="5"/>
+      <c r="AI577" s="5"/>
+      <c r="AJ577" s="5"/>
+      <c r="AK577" s="5"/>
+      <c r="AL577" s="5"/>
+      <c r="AM577" s="5"/>
+      <c r="AN577" s="5"/>
+      <c r="AO577" s="5"/>
+      <c r="AP577" s="5"/>
+      <c r="AQ577" s="5"/>
+      <c r="AR577" s="5"/>
+      <c r="AS577" s="5"/>
+      <c r="AT577" s="5"/>
+      <c r="AU577" s="5"/>
+      <c r="AV577" s="5"/>
+      <c r="AW577" s="5"/>
+      <c r="AX577" s="5"/>
+      <c r="AY577" s="5"/>
+      <c r="AZ577" s="5"/>
+      <c r="BA577" s="117">
+        <v>111.6</v>
+      </c>
+      <c r="BB577" s="5"/>
+      <c r="BC577" s="5"/>
+      <c r="BD577" s="117">
+        <v>25.7</v>
+      </c>
+      <c r="BE577" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF577" s="122">
+        <v>61</v>
+      </c>
+      <c r="BG577" s="106">
+        <v>1.163</v>
+      </c>
+      <c r="BH577" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI577" s="5"/>
+      <c r="BJ577" s="4"/>
+      <c r="BK577" s="8"/>
+      <c r="BM577"/>
+    </row>
+    <row r="578" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A578" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B578" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C578" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D578" s="20">
+        <v>5</v>
+      </c>
+      <c r="E578" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="F578" s="10"/>
+      <c r="G578" s="10"/>
+      <c r="H578" s="8">
+        <v>0.1605</v>
+      </c>
+      <c r="I578" s="8">
+        <v>2E-3</v>
+      </c>
+      <c r="J578" s="8">
+        <v>1.2905</v>
+      </c>
+      <c r="K578" s="10"/>
+      <c r="L578" s="25"/>
+      <c r="M578" s="107">
+        <v>0.16109999999999999</v>
+      </c>
+      <c r="N578" s="10"/>
+      <c r="O578" s="10"/>
+      <c r="P578" s="121">
+        <v>62.3</v>
+      </c>
+      <c r="Q578" s="107">
+        <v>506</v>
+      </c>
+      <c r="R578" s="112">
+        <v>756</v>
+      </c>
+      <c r="S578" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="T578" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="U578" s="5"/>
+      <c r="V578" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="W578" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="X578" s="5"/>
+      <c r="Y578" s="5"/>
+      <c r="Z578" s="5"/>
+      <c r="AA578" s="5"/>
+      <c r="AB578" s="5"/>
+      <c r="AC578" s="5"/>
+      <c r="AD578" s="5"/>
+      <c r="AE578" s="5"/>
+      <c r="AF578" s="5"/>
+      <c r="AG578" s="5"/>
+      <c r="AH578" s="5"/>
+      <c r="AI578" s="5"/>
+      <c r="AJ578" s="5"/>
+      <c r="AK578" s="5"/>
+      <c r="AL578" s="5"/>
+      <c r="AM578" s="5"/>
+      <c r="AN578" s="5"/>
+      <c r="AO578" s="5"/>
+      <c r="AP578" s="5"/>
+      <c r="AQ578" s="5"/>
+      <c r="AR578" s="5"/>
+      <c r="AS578" s="5"/>
+      <c r="AT578" s="5"/>
+      <c r="AU578" s="5"/>
+      <c r="AV578" s="5"/>
+      <c r="AW578" s="5"/>
+      <c r="AX578" s="5"/>
+      <c r="AY578" s="5"/>
+      <c r="AZ578" s="5"/>
+      <c r="BA578" s="117">
+        <v>111.6</v>
+      </c>
+      <c r="BB578" s="5"/>
+      <c r="BC578" s="5"/>
+      <c r="BD578" s="117">
+        <v>25.9</v>
+      </c>
+      <c r="BE578" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF578" s="122">
+        <v>56</v>
+      </c>
+      <c r="BG578" s="106">
+        <v>1.1619999999999999</v>
+      </c>
+      <c r="BH578" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI578" s="5"/>
+      <c r="BJ578" s="4"/>
+      <c r="BK578" s="8"/>
+      <c r="BM578"/>
+    </row>
+    <row r="579" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A579" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B579" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C579" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D579" s="20">
+        <v>6</v>
+      </c>
+      <c r="E579" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="F579" s="10"/>
+      <c r="G579" s="10"/>
+      <c r="H579" s="8">
+        <v>0.16189999999999999</v>
+      </c>
+      <c r="I579" s="8">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="J579" s="8">
+        <v>1.2905</v>
+      </c>
+      <c r="K579" s="10"/>
+      <c r="L579" s="25"/>
+      <c r="M579" s="107">
+        <v>0.16139999999999999</v>
+      </c>
+      <c r="N579" s="10"/>
+      <c r="O579" s="10"/>
+      <c r="P579" s="121">
+        <v>63</v>
+      </c>
+      <c r="Q579" s="107">
+        <v>527</v>
+      </c>
+      <c r="R579" s="112">
+        <v>756.5</v>
+      </c>
+      <c r="S579" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="T579" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="U579" s="5"/>
+      <c r="V579" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="W579" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="X579" s="5"/>
+      <c r="Y579" s="5"/>
+      <c r="Z579" s="5"/>
+      <c r="AA579" s="5"/>
+      <c r="AB579" s="5"/>
+      <c r="AC579" s="5"/>
+      <c r="AD579" s="5"/>
+      <c r="AE579" s="5"/>
+      <c r="AF579" s="5"/>
+      <c r="AG579" s="5"/>
+      <c r="AH579" s="5"/>
+      <c r="AI579" s="5"/>
+      <c r="AJ579" s="5"/>
+      <c r="AK579" s="5"/>
+      <c r="AL579" s="5"/>
+      <c r="AM579" s="5"/>
+      <c r="AN579" s="5"/>
+      <c r="AO579" s="5"/>
+      <c r="AP579" s="5"/>
+      <c r="AQ579" s="5"/>
+      <c r="AR579" s="5"/>
+      <c r="AS579" s="5"/>
+      <c r="AT579" s="5"/>
+      <c r="AU579" s="5"/>
+      <c r="AV579" s="5"/>
+      <c r="AW579" s="5"/>
+      <c r="AX579" s="5"/>
+      <c r="AY579" s="5"/>
+      <c r="AZ579" s="5"/>
+      <c r="BA579" s="117">
+        <v>111.6</v>
+      </c>
+      <c r="BB579" s="5"/>
+      <c r="BC579" s="5"/>
+      <c r="BD579" s="117">
+        <v>26.4</v>
+      </c>
+      <c r="BE579" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF579" s="122">
+        <v>48</v>
+      </c>
+      <c r="BG579" s="106">
+        <v>1.1619999999999999</v>
+      </c>
+      <c r="BH579" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI579" s="5"/>
+      <c r="BJ579" s="4"/>
+      <c r="BK579" s="8"/>
+      <c r="BM579"/>
+    </row>
+    <row r="580" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A580" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B580" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C580" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D580" s="20">
+        <v>1</v>
+      </c>
+      <c r="E580" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="F580" s="10"/>
+      <c r="G580" s="10"/>
+      <c r="H580" s="8">
+        <v>0.18</v>
+      </c>
+      <c r="I580" s="8">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="J580" s="8">
+        <v>1.2655000000000001</v>
+      </c>
+      <c r="K580" s="10"/>
+      <c r="L580" s="25">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="M580" s="107">
+        <v>0.17480000000000001</v>
+      </c>
+      <c r="N580" s="10"/>
+      <c r="O580" s="10"/>
+      <c r="P580" s="121">
+        <v>59.4</v>
+      </c>
+      <c r="Q580" s="107">
+        <v>480</v>
+      </c>
+      <c r="R580" s="112">
+        <v>755.4</v>
+      </c>
+      <c r="S580" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="T580" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="U580" s="5"/>
+      <c r="V580" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="W580" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="X580" s="5"/>
+      <c r="Y580" s="5"/>
+      <c r="Z580" s="5"/>
+      <c r="AA580" s="5"/>
+      <c r="AB580" s="5"/>
+      <c r="AC580" s="5"/>
+      <c r="AD580" s="5"/>
+      <c r="AE580" s="5"/>
+      <c r="AF580" s="5"/>
+      <c r="AG580" s="5"/>
+      <c r="AH580" s="5"/>
+      <c r="AI580" s="5"/>
+      <c r="AJ580" s="5"/>
+      <c r="AK580" s="5"/>
+      <c r="AL580" s="5"/>
+      <c r="AM580" s="5"/>
+      <c r="AN580" s="5"/>
+      <c r="AO580" s="5"/>
+      <c r="AP580" s="5"/>
+      <c r="AQ580" s="5"/>
+      <c r="AR580" s="5"/>
+      <c r="AS580" s="5"/>
+      <c r="AT580" s="5"/>
+      <c r="AU580" s="5"/>
+      <c r="AV580" s="5"/>
+      <c r="AW580" s="5"/>
+      <c r="AX580" s="5"/>
+      <c r="AY580" s="5"/>
+      <c r="AZ580" s="5"/>
+      <c r="BA580" s="117">
+        <v>111.6</v>
+      </c>
+      <c r="BB580" s="5"/>
+      <c r="BC580" s="5"/>
+      <c r="BD580" s="117">
+        <v>24.4</v>
+      </c>
+      <c r="BE580" s="105">
+        <v>1006</v>
+      </c>
+      <c r="BF580" s="122">
+        <v>53</v>
+      </c>
+      <c r="BG580" s="106">
+        <v>1.171</v>
+      </c>
+      <c r="BH580" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI580" s="5"/>
+      <c r="BJ580" s="4"/>
+      <c r="BK580" s="8"/>
+      <c r="BM580"/>
+    </row>
+    <row r="581" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A581" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B581" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C581" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D581" s="20">
+        <v>2</v>
+      </c>
+      <c r="E581" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="F581" s="10"/>
+      <c r="G581" s="10"/>
+      <c r="H581" s="8">
+        <v>0.17219999999999999</v>
+      </c>
+      <c r="I581" s="8">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="J581" s="8">
+        <v>1.2655000000000001</v>
+      </c>
+      <c r="K581" s="10"/>
+      <c r="L581" s="25">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="M581" s="107">
+        <v>0.16839999999999999</v>
+      </c>
+      <c r="N581" s="10"/>
+      <c r="O581" s="10"/>
+      <c r="P581" s="121">
+        <v>57.9</v>
+      </c>
+      <c r="Q581" s="107">
+        <v>434</v>
+      </c>
+      <c r="R581" s="112">
+        <v>757.7</v>
+      </c>
+      <c r="S581" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="T581" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="U581" s="5"/>
+      <c r="V581" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="W581" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="X581" s="5"/>
+      <c r="Y581" s="5"/>
+      <c r="Z581" s="5"/>
+      <c r="AA581" s="5"/>
+      <c r="AB581" s="5"/>
+      <c r="AC581" s="5"/>
+      <c r="AD581" s="5"/>
+      <c r="AE581" s="5"/>
+      <c r="AF581" s="5"/>
+      <c r="AG581" s="5"/>
+      <c r="AH581" s="5"/>
+      <c r="AI581" s="5"/>
+      <c r="AJ581" s="5"/>
+      <c r="AK581" s="5"/>
+      <c r="AL581" s="5"/>
+      <c r="AM581" s="5"/>
+      <c r="AN581" s="5"/>
+      <c r="AO581" s="5"/>
+      <c r="AP581" s="5"/>
+      <c r="AQ581" s="5"/>
+      <c r="AR581" s="5"/>
+      <c r="AS581" s="5"/>
+      <c r="AT581" s="5"/>
+      <c r="AU581" s="5"/>
+      <c r="AV581" s="5"/>
+      <c r="AW581" s="5"/>
+      <c r="AX581" s="5"/>
+      <c r="AY581" s="5"/>
+      <c r="AZ581" s="5"/>
+      <c r="BA581" s="117">
+        <v>111.6</v>
+      </c>
+      <c r="BB581" s="5"/>
+      <c r="BC581" s="5"/>
+      <c r="BD581" s="117">
+        <v>24.8</v>
+      </c>
+      <c r="BE581" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF581" s="122">
+        <v>62</v>
+      </c>
+      <c r="BG581" s="106">
+        <v>1.167</v>
+      </c>
+      <c r="BH581" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI581" s="5"/>
+      <c r="BJ581" s="4"/>
+      <c r="BK581" s="8"/>
+      <c r="BM581"/>
+    </row>
+    <row r="582" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A582" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B582" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C582" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D582" s="20">
+        <v>3</v>
+      </c>
+      <c r="E582" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="F582" s="10"/>
+      <c r="G582" s="10"/>
+      <c r="H582" s="8"/>
+      <c r="J582" s="8">
+        <v>1.2655000000000001</v>
+      </c>
+      <c r="K582" s="10"/>
+      <c r="L582" s="25">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="M582" s="107">
+        <v>0.16789999999999999</v>
+      </c>
+      <c r="N582" s="10"/>
+      <c r="O582" s="10"/>
+      <c r="P582" s="121">
+        <v>59.1</v>
+      </c>
+      <c r="Q582" s="107">
+        <v>456</v>
+      </c>
+      <c r="R582" s="112">
+        <v>757</v>
+      </c>
+      <c r="S582" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="T582" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="U582" s="5"/>
+      <c r="V582" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="W582" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="X582" s="5"/>
+      <c r="Y582" s="5"/>
+      <c r="Z582" s="5"/>
+      <c r="AA582" s="5"/>
+      <c r="AB582" s="5"/>
+      <c r="AC582" s="5"/>
+      <c r="AD582" s="5"/>
+      <c r="AE582" s="5"/>
+      <c r="AF582" s="5"/>
+      <c r="AG582" s="5"/>
+      <c r="AH582" s="5"/>
+      <c r="AI582" s="5"/>
+      <c r="AJ582" s="5"/>
+      <c r="AK582" s="5"/>
+      <c r="AL582" s="5"/>
+      <c r="AM582" s="5"/>
+      <c r="AN582" s="5"/>
+      <c r="AO582" s="5"/>
+      <c r="AP582" s="5"/>
+      <c r="AQ582" s="5"/>
+      <c r="AR582" s="5"/>
+      <c r="AS582" s="5"/>
+      <c r="AT582" s="5"/>
+      <c r="AU582" s="5"/>
+      <c r="AV582" s="5"/>
+      <c r="AW582" s="5"/>
+      <c r="AX582" s="5"/>
+      <c r="AY582" s="5"/>
+      <c r="AZ582" s="5"/>
+      <c r="BA582" s="117">
+        <v>111.6</v>
+      </c>
+      <c r="BB582" s="5"/>
+      <c r="BC582" s="5"/>
+      <c r="BD582" s="117">
+        <v>25.1</v>
+      </c>
+      <c r="BE582" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF582" s="122">
+        <v>51</v>
+      </c>
+      <c r="BG582" s="106">
+        <v>1.167</v>
+      </c>
+      <c r="BH582" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI582" s="5"/>
+      <c r="BJ582" s="4"/>
+      <c r="BK582" s="8"/>
+      <c r="BM582"/>
+    </row>
+    <row r="583" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A583" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B583" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C583" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D583" s="20">
+        <v>4</v>
+      </c>
+      <c r="E583" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="F583" s="10"/>
+      <c r="G583" s="10"/>
+      <c r="H583" s="8">
+        <v>0.18160000000000001</v>
+      </c>
+      <c r="I583" s="8">
+        <v>2.3E-3</v>
+      </c>
+      <c r="J583" s="8">
+        <v>1.2655000000000001</v>
+      </c>
+      <c r="K583" s="10"/>
+      <c r="L583" s="25"/>
+      <c r="M583" s="107">
+        <v>0.17519999999999999</v>
+      </c>
+      <c r="N583" s="10"/>
+      <c r="O583" s="10"/>
+      <c r="P583" s="121">
+        <v>59.7</v>
+      </c>
+      <c r="Q583" s="107">
+        <v>472</v>
+      </c>
+      <c r="R583" s="112">
+        <v>755.7</v>
+      </c>
+      <c r="S583" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="T583" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="U583" s="5"/>
+      <c r="V583" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="W583" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="X583" s="5"/>
+      <c r="Y583" s="5"/>
+      <c r="Z583" s="5"/>
+      <c r="AA583" s="5"/>
+      <c r="AB583" s="5"/>
+      <c r="AC583" s="5"/>
+      <c r="AD583" s="5"/>
+      <c r="AE583" s="5"/>
+      <c r="AF583" s="5"/>
+      <c r="AG583" s="5"/>
+      <c r="AH583" s="5"/>
+      <c r="AI583" s="5"/>
+      <c r="AJ583" s="5"/>
+      <c r="AK583" s="5"/>
+      <c r="AL583" s="5"/>
+      <c r="AM583" s="5"/>
+      <c r="AN583" s="5"/>
+      <c r="AO583" s="5"/>
+      <c r="AP583" s="5"/>
+      <c r="AQ583" s="5"/>
+      <c r="AR583" s="5"/>
+      <c r="AS583" s="5"/>
+      <c r="AT583" s="5"/>
+      <c r="AU583" s="5"/>
+      <c r="AV583" s="5"/>
+      <c r="AW583" s="5"/>
+      <c r="AX583" s="5"/>
+      <c r="AY583" s="5"/>
+      <c r="AZ583" s="5"/>
+      <c r="BA583" s="117">
+        <v>111.6</v>
+      </c>
+      <c r="BB583" s="5"/>
+      <c r="BC583" s="5"/>
+      <c r="BD583" s="117">
+        <v>25.7</v>
+      </c>
+      <c r="BE583" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF583" s="122">
+        <v>61</v>
+      </c>
+      <c r="BG583" s="106">
+        <v>1.163</v>
+      </c>
+      <c r="BH583" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI583" s="5"/>
+      <c r="BJ583" s="4"/>
+      <c r="BK583" s="8"/>
+      <c r="BM583"/>
+    </row>
+    <row r="584" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A584" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B584" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C584" s="4">
+        <v>45267</v>
+      </c>
+      <c r="D584" s="20">
+        <v>5</v>
+      </c>
+      <c r="E584" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="F584" s="10"/>
+      <c r="G584" s="10"/>
+      <c r="H584" s="8">
+        <v>0.17480000000000001</v>
+      </c>
+      <c r="I584" s="8">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="J584" s="8">
+        <v>1.2655000000000001</v>
+      </c>
+      <c r="K584" s="10"/>
+      <c r="L584" s="25"/>
+      <c r="M584" s="107">
+        <v>0.1668</v>
+      </c>
+      <c r="N584" s="10"/>
+      <c r="O584" s="10"/>
+      <c r="P584" s="121">
+        <v>59.3</v>
+      </c>
+      <c r="Q584" s="107">
+        <v>454</v>
+      </c>
+      <c r="R584" s="112">
+        <v>757.2</v>
+      </c>
+      <c r="S584" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="T584" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="U584" s="5"/>
+      <c r="V584" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="W584" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="X584" s="5"/>
+      <c r="Y584" s="5"/>
+      <c r="Z584" s="5"/>
+      <c r="AA584" s="5"/>
+      <c r="AB584" s="5"/>
+      <c r="AC584" s="5"/>
+      <c r="AD584" s="5"/>
+      <c r="AE584" s="5"/>
+      <c r="AF584" s="5"/>
+      <c r="AG584" s="5"/>
+      <c r="AH584" s="5"/>
+      <c r="AI584" s="5"/>
+      <c r="AJ584" s="5"/>
+      <c r="AK584" s="5"/>
+      <c r="AL584" s="5"/>
+      <c r="AM584" s="5"/>
+      <c r="AN584" s="5"/>
+      <c r="AO584" s="5"/>
+      <c r="AP584" s="5"/>
+      <c r="AQ584" s="5"/>
+      <c r="AR584" s="5"/>
+      <c r="AS584" s="5"/>
+      <c r="AT584" s="5"/>
+      <c r="AU584" s="5"/>
+      <c r="AV584" s="5"/>
+      <c r="AW584" s="5"/>
+      <c r="AX584" s="5"/>
+      <c r="AY584" s="5"/>
+      <c r="AZ584" s="5"/>
+      <c r="BA584" s="117">
+        <v>111.6</v>
+      </c>
+      <c r="BB584" s="5"/>
+      <c r="BC584" s="5"/>
+      <c r="BD584" s="117">
+        <v>25.9</v>
+      </c>
+      <c r="BE584" s="105">
+        <v>1005</v>
+      </c>
+      <c r="BF584" s="122">
+        <v>56</v>
+      </c>
+      <c r="BG584" s="106">
+        <v>1.1619999999999999</v>
+      </c>
+      <c r="BH584" s="5">
+        <v>2096</v>
+      </c>
+      <c r="BI584" s="5"/>
+      <c r="BJ584" s="4"/>
+      <c r="BK584" s="8"/>
+      <c r="BM584"/>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
@@ -66161,6 +68749,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
@@ -66168,15 +68765,6 @@
     <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -66199,6 +68787,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -66213,12 +68809,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91E6A9B-7CE1-42F5-B174-93F6911C10B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6657AEA-9A49-4CAC-9FB3-0B70A417032E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CdA Track Testing" sheetId="12" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5261" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5261" uniqueCount="784">
   <si>
     <t>Squad</t>
   </si>
@@ -2406,9 +2406,6 @@
   </si>
   <si>
     <t>https://youtu.be/OhasA8Jhlbk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Gate </t>
   </si>
   <si>
     <t>Baseline Pos 1</t>
@@ -60738,7 +60735,7 @@
       </c>
       <c r="K516" s="10"/>
       <c r="L516" s="139" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="M516" s="107">
         <v>0.17130000000000001</v>
@@ -65925,12 +65922,12 @@
       <c r="BK561" s="8"/>
       <c r="BM561"/>
     </row>
-    <row r="562" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A562" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B562" s="3" t="s">
-        <v>773</v>
+        <v>17</v>
       </c>
       <c r="C562" s="4">
         <v>45267</v>
@@ -65939,7 +65936,7 @@
         <v>1</v>
       </c>
       <c r="E562" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F562" s="10"/>
       <c r="G562" s="10"/>
@@ -65971,7 +65968,7 @@
         <v>755.6</v>
       </c>
       <c r="S562" s="5" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="T562" s="5" t="s">
         <v>752</v>
@@ -66037,12 +66034,12 @@
       <c r="BK562" s="8"/>
       <c r="BM562"/>
     </row>
-    <row r="563" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>773</v>
+        <v>17</v>
       </c>
       <c r="C563" s="4">
         <v>45267</v>
@@ -66051,7 +66048,7 @@
         <v>2</v>
       </c>
       <c r="E563" s="4" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F563" s="10"/>
       <c r="G563" s="10"/>
@@ -66083,7 +66080,7 @@
         <v>756.2</v>
       </c>
       <c r="S563" s="5" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="T563" s="5" t="s">
         <v>752</v>
@@ -66149,12 +66146,12 @@
       <c r="BK563" s="8"/>
       <c r="BM563"/>
     </row>
-    <row r="564" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A564" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B564" s="3" t="s">
-        <v>773</v>
+        <v>17</v>
       </c>
       <c r="C564" s="4">
         <v>45267</v>
@@ -66163,7 +66160,7 @@
         <v>3</v>
       </c>
       <c r="E564" s="4" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F564" s="10"/>
       <c r="G564" s="10"/>
@@ -66193,7 +66190,7 @@
         <v>756.2</v>
       </c>
       <c r="S564" s="5" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="T564" s="5" t="s">
         <v>752</v>
@@ -66259,12 +66256,12 @@
       <c r="BK564" s="8"/>
       <c r="BM564"/>
     </row>
-    <row r="565" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A565" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>773</v>
+        <v>17</v>
       </c>
       <c r="C565" s="4">
         <v>45267</v>
@@ -66273,7 +66270,7 @@
         <v>4</v>
       </c>
       <c r="E565" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F565" s="10"/>
       <c r="G565" s="10"/>
@@ -66305,7 +66302,7 @@
         <v>756.1</v>
       </c>
       <c r="S565" s="5" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="T565" s="5" t="s">
         <v>752</v>
@@ -66371,12 +66368,12 @@
       <c r="BK565" s="8"/>
       <c r="BM565"/>
     </row>
-    <row r="566" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A566" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B566" s="3" t="s">
-        <v>773</v>
+        <v>17</v>
       </c>
       <c r="C566" s="4">
         <v>45267</v>
@@ -66385,7 +66382,7 @@
         <v>5</v>
       </c>
       <c r="E566" s="4" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F566" s="10"/>
       <c r="G566" s="10"/>
@@ -66417,7 +66414,7 @@
         <v>756.6</v>
       </c>
       <c r="S566" s="5" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="T566" s="5" t="s">
         <v>752</v>
@@ -66483,12 +66480,12 @@
       <c r="BK566" s="8"/>
       <c r="BM566"/>
     </row>
-    <row r="567" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A567" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>773</v>
+        <v>17</v>
       </c>
       <c r="C567" s="4">
         <v>45267</v>
@@ -66497,7 +66494,7 @@
         <v>6</v>
       </c>
       <c r="E567" s="4" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F567" s="10"/>
       <c r="G567" s="10"/>
@@ -66529,7 +66526,7 @@
         <v>756.5</v>
       </c>
       <c r="S567" s="5" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="T567" s="5" t="s">
         <v>752</v>
@@ -66600,7 +66597,7 @@
         <v>16</v>
       </c>
       <c r="B568" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C568" s="4">
         <v>45267</v>
@@ -66609,7 +66606,7 @@
         <v>1</v>
       </c>
       <c r="E568" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F568" s="10"/>
       <c r="G568" s="10"/>
@@ -66641,7 +66638,7 @@
         <v>754</v>
       </c>
       <c r="S568" s="5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="T568" s="5" t="s">
         <v>752</v>
@@ -66712,7 +66709,7 @@
         <v>16</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C569" s="4">
         <v>45267</v>
@@ -66721,7 +66718,7 @@
         <v>2</v>
       </c>
       <c r="E569" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F569" s="10"/>
       <c r="G569" s="10"/>
@@ -66753,7 +66750,7 @@
         <v>753.9</v>
       </c>
       <c r="S569" s="5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="T569" s="5" t="s">
         <v>752</v>
@@ -66824,7 +66821,7 @@
         <v>16</v>
       </c>
       <c r="B570" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C570" s="4">
         <v>45267</v>
@@ -66833,7 +66830,7 @@
         <v>3</v>
       </c>
       <c r="E570" s="4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F570" s="10"/>
       <c r="G570" s="10"/>
@@ -66865,7 +66862,7 @@
         <v>755.2</v>
       </c>
       <c r="S570" s="5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="T570" s="5" t="s">
         <v>752</v>
@@ -66936,7 +66933,7 @@
         <v>16</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C571" s="4">
         <v>45267</v>
@@ -66945,7 +66942,7 @@
         <v>4</v>
       </c>
       <c r="E571" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F571" s="10"/>
       <c r="G571" s="10"/>
@@ -66975,7 +66972,7 @@
         <v>754.1</v>
       </c>
       <c r="S571" s="5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="T571" s="5" t="s">
         <v>752</v>
@@ -67046,7 +67043,7 @@
         <v>16</v>
       </c>
       <c r="B572" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C572" s="4">
         <v>45267</v>
@@ -67055,7 +67052,7 @@
         <v>5</v>
       </c>
       <c r="E572" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F572" s="10"/>
       <c r="G572" s="10"/>
@@ -67085,7 +67082,7 @@
         <v>754.5</v>
       </c>
       <c r="S572" s="5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="T572" s="5" t="s">
         <v>752</v>
@@ -67151,12 +67148,12 @@
       <c r="BK572" s="8"/>
       <c r="BM572"/>
     </row>
-    <row r="573" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A573" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C573" s="4">
         <v>45267</v>
@@ -67165,7 +67162,7 @@
         <v>6</v>
       </c>
       <c r="E573" s="4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F573" s="10"/>
       <c r="G573" s="10"/>
@@ -67195,7 +67192,7 @@
         <v>754.3</v>
       </c>
       <c r="S573" s="5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="T573" s="5" t="s">
         <v>752</v>
@@ -67261,7 +67258,7 @@
       <c r="BK573" s="8"/>
       <c r="BM573"/>
     </row>
-    <row r="574" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A574" s="3" t="s">
         <v>296</v>
       </c>
@@ -67275,7 +67272,7 @@
         <v>1</v>
       </c>
       <c r="E574" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F574" s="10"/>
       <c r="G574" s="10"/>
@@ -67373,7 +67370,7 @@
       <c r="BK574" s="8"/>
       <c r="BM574"/>
     </row>
-    <row r="575" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A575" s="3" t="s">
         <v>296</v>
       </c>
@@ -67387,7 +67384,7 @@
         <v>2</v>
       </c>
       <c r="E575" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F575" s="10"/>
       <c r="G575" s="10"/>
@@ -67485,7 +67482,7 @@
       <c r="BK575" s="8"/>
       <c r="BM575"/>
     </row>
-    <row r="576" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A576" s="3" t="s">
         <v>296</v>
       </c>
@@ -67499,7 +67496,7 @@
         <v>3</v>
       </c>
       <c r="E576" s="4" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="F576" s="10"/>
       <c r="G576" s="10"/>
@@ -67597,7 +67594,7 @@
       <c r="BK576" s="8"/>
       <c r="BM576"/>
     </row>
-    <row r="577" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A577" s="3" t="s">
         <v>296</v>
       </c>
@@ -67611,7 +67608,7 @@
         <v>4</v>
       </c>
       <c r="E577" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F577" s="10"/>
       <c r="G577" s="10"/>
@@ -67709,7 +67706,7 @@
       <c r="BK577" s="8"/>
       <c r="BM577"/>
     </row>
-    <row r="578" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A578" s="3" t="s">
         <v>296</v>
       </c>
@@ -67723,7 +67720,7 @@
         <v>5</v>
       </c>
       <c r="E578" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F578" s="10"/>
       <c r="G578" s="10"/>
@@ -67819,7 +67816,7 @@
       <c r="BK578" s="8"/>
       <c r="BM578"/>
     </row>
-    <row r="579" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A579" s="3" t="s">
         <v>296</v>
       </c>
@@ -67833,7 +67830,7 @@
         <v>6</v>
       </c>
       <c r="E579" s="4" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="F579" s="10"/>
       <c r="G579" s="10"/>
@@ -67929,7 +67926,7 @@
       <c r="BK579" s="8"/>
       <c r="BM579"/>
     </row>
-    <row r="580" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A580" s="3" t="s">
         <v>296</v>
       </c>
@@ -67943,7 +67940,7 @@
         <v>1</v>
       </c>
       <c r="E580" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F580" s="10"/>
       <c r="G580" s="10"/>
@@ -68041,7 +68038,7 @@
       <c r="BK580" s="8"/>
       <c r="BM580"/>
     </row>
-    <row r="581" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A581" s="3" t="s">
         <v>296</v>
       </c>
@@ -68055,7 +68052,7 @@
         <v>2</v>
       </c>
       <c r="E581" s="4" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="F581" s="10"/>
       <c r="G581" s="10"/>
@@ -68153,7 +68150,7 @@
       <c r="BK581" s="8"/>
       <c r="BM581"/>
     </row>
-    <row r="582" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A582" s="3" t="s">
         <v>296</v>
       </c>
@@ -68167,7 +68164,7 @@
         <v>3</v>
       </c>
       <c r="E582" s="4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F582" s="10"/>
       <c r="G582" s="10"/>
@@ -68260,7 +68257,7 @@
       <c r="BK582" s="8"/>
       <c r="BM582"/>
     </row>
-    <row r="583" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A583" s="3" t="s">
         <v>296</v>
       </c>
@@ -68274,7 +68271,7 @@
         <v>4</v>
       </c>
       <c r="E583" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F583" s="10"/>
       <c r="G583" s="10"/>
@@ -68370,7 +68367,7 @@
       <c r="BK583" s="8"/>
       <c r="BM583"/>
     </row>
-    <row r="584" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A584" s="3" t="s">
         <v>296</v>
       </c>
@@ -68384,7 +68381,7 @@
         <v>5</v>
       </c>
       <c r="E584" s="4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F584" s="10"/>
       <c r="G584" s="10"/>
@@ -68749,15 +68746,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
@@ -68765,6 +68753,15 @@
     <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -68787,14 +68784,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -68809,4 +68798,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6657AEA-9A49-4CAC-9FB3-0B70A417032E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E4D809-C644-42C1-88DF-A50EC4A4E1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66592,12 +66592,12 @@
       <c r="BK567" s="8"/>
       <c r="BM567"/>
     </row>
-    <row r="568" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A568" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B568" s="3" t="s">
-        <v>777</v>
+        <v>207</v>
       </c>
       <c r="C568" s="4">
         <v>45267</v>
@@ -66704,12 +66704,12 @@
       <c r="BK568" s="8"/>
       <c r="BM568"/>
     </row>
-    <row r="569" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>777</v>
+        <v>207</v>
       </c>
       <c r="C569" s="4">
         <v>45267</v>
@@ -66816,12 +66816,12 @@
       <c r="BK569" s="8"/>
       <c r="BM569"/>
     </row>
-    <row r="570" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A570" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B570" s="3" t="s">
-        <v>777</v>
+        <v>207</v>
       </c>
       <c r="C570" s="4">
         <v>45267</v>
@@ -66928,12 +66928,12 @@
       <c r="BK570" s="8"/>
       <c r="BM570"/>
     </row>
-    <row r="571" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A571" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>777</v>
+        <v>207</v>
       </c>
       <c r="C571" s="4">
         <v>45267</v>
@@ -67038,12 +67038,12 @@
       <c r="BK571" s="8"/>
       <c r="BM571"/>
     </row>
-    <row r="572" spans="1:65" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A572" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B572" s="3" t="s">
-        <v>777</v>
+        <v>207</v>
       </c>
       <c r="C572" s="4">
         <v>45267</v>

--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E4D809-C644-42C1-88DF-A50EC4A4E1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900CEA56-AA6D-4098-B752-A86F226EE00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5261" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5261" uniqueCount="783">
   <si>
     <t>Squad</t>
   </si>
@@ -2418,9 +2418,6 @@
   </si>
   <si>
     <t>Pos E -FW</t>
-  </si>
-  <si>
-    <t>Tom sexton</t>
   </si>
   <si>
     <t>B5_VP</t>
@@ -60735,7 +60732,7 @@
       </c>
       <c r="K516" s="10"/>
       <c r="L516" s="139" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="M516" s="107">
         <v>0.17130000000000001</v>
@@ -66638,7 +66635,7 @@
         <v>754</v>
       </c>
       <c r="S568" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="T568" s="5" t="s">
         <v>752</v>
@@ -66718,7 +66715,7 @@
         <v>2</v>
       </c>
       <c r="E569" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F569" s="10"/>
       <c r="G569" s="10"/>
@@ -66750,7 +66747,7 @@
         <v>753.9</v>
       </c>
       <c r="S569" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="T569" s="5" t="s">
         <v>752</v>
@@ -66830,7 +66827,7 @@
         <v>3</v>
       </c>
       <c r="E570" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F570" s="10"/>
       <c r="G570" s="10"/>
@@ -66862,7 +66859,7 @@
         <v>755.2</v>
       </c>
       <c r="S570" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="T570" s="5" t="s">
         <v>752</v>
@@ -66972,7 +66969,7 @@
         <v>754.1</v>
       </c>
       <c r="S571" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="T571" s="5" t="s">
         <v>752</v>
@@ -67052,7 +67049,7 @@
         <v>5</v>
       </c>
       <c r="E572" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F572" s="10"/>
       <c r="G572" s="10"/>
@@ -67082,7 +67079,7 @@
         <v>754.5</v>
       </c>
       <c r="S572" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="T572" s="5" t="s">
         <v>752</v>
@@ -67153,7 +67150,7 @@
         <v>16</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>777</v>
+        <v>207</v>
       </c>
       <c r="C573" s="4">
         <v>45267</v>
@@ -67162,7 +67159,7 @@
         <v>6</v>
       </c>
       <c r="E573" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F573" s="10"/>
       <c r="G573" s="10"/>
@@ -67192,7 +67189,7 @@
         <v>754.3</v>
       </c>
       <c r="S573" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="T573" s="5" t="s">
         <v>752</v>
@@ -67384,7 +67381,7 @@
         <v>2</v>
       </c>
       <c r="E575" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F575" s="10"/>
       <c r="G575" s="10"/>
@@ -67496,7 +67493,7 @@
         <v>3</v>
       </c>
       <c r="E576" s="4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F576" s="10"/>
       <c r="G576" s="10"/>
@@ -67720,7 +67717,7 @@
         <v>5</v>
       </c>
       <c r="E578" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F578" s="10"/>
       <c r="G578" s="10"/>
@@ -67830,7 +67827,7 @@
         <v>6</v>
       </c>
       <c r="E579" s="4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F579" s="10"/>
       <c r="G579" s="10"/>
@@ -68052,7 +68049,7 @@
         <v>2</v>
       </c>
       <c r="E581" s="4" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="F581" s="10"/>
       <c r="G581" s="10"/>
@@ -68164,7 +68161,7 @@
         <v>3</v>
       </c>
       <c r="E582" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F582" s="10"/>
       <c r="G582" s="10"/>
@@ -68381,7 +68378,7 @@
         <v>5</v>
       </c>
       <c r="E584" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F584" s="10"/>
       <c r="G584" s="10"/>
@@ -68498,6 +68495,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004F1ECC6B2649324CB24C079D2C04510D" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="608b5d954c2eb0ac10393708da8d34af">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65551c38-962b-4cee-924d-ef2df1bb8b98" xmlns:ns3="ec750ee3-7d64-422f-9b1f-0ca7238893a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af171f03bd4cf151e3e856a6839c0cc7" ns2:_="" ns3:_="">
     <xsd:import namespace="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
@@ -68745,40 +68761,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
-    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -68801,9 +68787,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
+    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7145F994-E316-4C63-8521-C4394650620C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45EA1AC7-3529-46D6-A8D8-BF521A9936C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5768" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5793" uniqueCount="893">
   <si>
     <t>Squad</t>
   </si>
@@ -2691,6 +2691,81 @@
   </si>
   <si>
     <t>https://youtu.be/Bn2s2OQzosA</t>
+  </si>
+  <si>
+    <t>https://youtu.be/OH1PZTt63Lk</t>
+  </si>
+  <si>
+    <t>https://youtu.be/47dA6oedSZE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/yalNPZ41SZo</t>
+  </si>
+  <si>
+    <t>https://youtu.be/vEolGhj5_zs</t>
+  </si>
+  <si>
+    <t>https://youtu.be/R4OO-yp3vZs</t>
+  </si>
+  <si>
+    <t>https://youtu.be/tdf0pOypaRE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/jmEbNCR8r8U</t>
+  </si>
+  <si>
+    <t>https://youtu.be/COVZHJttJF4</t>
+  </si>
+  <si>
+    <t>https://youtu.be/3vM2hfSE12Y</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Vb6KZDgY_o8</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ZgFZrlvhlso</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0AtAVy18B9w</t>
+  </si>
+  <si>
+    <t>https://youtu.be/GAMxLRQt7Ko</t>
+  </si>
+  <si>
+    <t>https://youtu.be/bQmDYuGWqA0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/1BSGxNsqZbo</t>
+  </si>
+  <si>
+    <t>https://youtu.be/vVJCgxickcc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/RRC0F-VI8Ao</t>
+  </si>
+  <si>
+    <t>https://youtu.be/qRNbtwrSBqs</t>
+  </si>
+  <si>
+    <t>https://youtu.be/W85EK3bXMws</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ZUR8RlJg3bQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/I4oXnBtUl-4</t>
+  </si>
+  <si>
+    <t>https://youtu.be/1gftK_54qc4</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Z79VDmQCJFA</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Y3JkSkVU6Gc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Y_N7CFY6HbQ</t>
   </si>
 </sst>
 </file>
@@ -3838,12 +3913,10 @@
     <sheetNames>
       <sheetName val="CdA Track Testing"/>
       <sheetName val="Data cut from table - to sort"/>
-      <sheetName val="Track CdA Aero Testing Database"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4193,7 +4266,7 @@
     <col min="2" max="2" width="20.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.21875" style="90" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30" style="2" customWidth="1"/>
     <col min="7" max="7" width="102.5546875" style="2" customWidth="1"/>
     <col min="8" max="8" width="18.21875" customWidth="1"/>
     <col min="9" max="9" width="14" style="8" customWidth="1"/>
@@ -72037,9 +72110,15 @@
       </c>
       <c r="G625" s="109"/>
       <c r="H625" s="109"/>
-      <c r="I625" s="109"/>
-      <c r="J625" s="109"/>
-      <c r="K625" s="109"/>
+      <c r="I625" s="109">
+        <v>0.19209999999999999</v>
+      </c>
+      <c r="J625" s="109">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="K625" s="109">
+        <v>1.2735000000000001</v>
+      </c>
       <c r="L625" s="109"/>
       <c r="M625" s="109">
         <v>0.186</v>
@@ -72144,9 +72223,15 @@
       </c>
       <c r="G626" s="109"/>
       <c r="H626" s="109"/>
-      <c r="I626" s="109"/>
-      <c r="J626" s="109"/>
-      <c r="K626" s="109"/>
+      <c r="I626" s="109">
+        <v>0.19450000000000001</v>
+      </c>
+      <c r="J626" s="109">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="K626" s="109">
+        <v>1.2735000000000001</v>
+      </c>
       <c r="L626" s="109"/>
       <c r="M626" s="109">
         <v>0.188</v>
@@ -72251,9 +72336,15 @@
       </c>
       <c r="G627" s="109"/>
       <c r="H627" s="109"/>
-      <c r="I627" s="109"/>
-      <c r="J627" s="109"/>
-      <c r="K627" s="109"/>
+      <c r="I627" s="109">
+        <v>0.19370000000000001</v>
+      </c>
+      <c r="J627" s="109">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="K627" s="109">
+        <v>1.2735000000000001</v>
+      </c>
       <c r="L627" s="109"/>
       <c r="M627" s="109">
         <v>0.184</v>
@@ -72358,9 +72449,15 @@
       </c>
       <c r="G628" s="109"/>
       <c r="H628" s="109"/>
-      <c r="I628" s="109"/>
-      <c r="J628" s="109"/>
-      <c r="K628" s="109"/>
+      <c r="I628" s="109">
+        <v>0.18920000000000001</v>
+      </c>
+      <c r="J628" s="109">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="K628" s="109">
+        <v>1.2735000000000001</v>
+      </c>
       <c r="L628" s="109"/>
       <c r="M628" s="109">
         <v>0.183</v>
@@ -72465,9 +72562,15 @@
       </c>
       <c r="G629" s="109"/>
       <c r="H629" s="109"/>
-      <c r="I629" s="109"/>
-      <c r="J629" s="109"/>
-      <c r="K629" s="109"/>
+      <c r="I629" s="109">
+        <v>0.19009999999999999</v>
+      </c>
+      <c r="J629" s="109">
+        <v>1.5E-3</v>
+      </c>
+      <c r="K629" s="109">
+        <v>1.2735000000000001</v>
+      </c>
       <c r="L629" s="109"/>
       <c r="M629" s="109">
         <v>0.18099999999999999</v>
@@ -72572,9 +72675,15 @@
       </c>
       <c r="G630" s="109"/>
       <c r="H630" s="109"/>
-      <c r="I630" s="109"/>
-      <c r="J630" s="109"/>
-      <c r="K630" s="109"/>
+      <c r="I630" s="109">
+        <v>0.19270000000000001</v>
+      </c>
+      <c r="J630" s="109">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="K630" s="109">
+        <v>1.2735000000000001</v>
+      </c>
       <c r="L630" s="109"/>
       <c r="M630" s="109">
         <v>0.183</v>
@@ -72677,9 +72786,15 @@
       </c>
       <c r="G631" s="109"/>
       <c r="H631" s="109"/>
-      <c r="I631" s="109"/>
-      <c r="J631" s="109"/>
-      <c r="K631" s="109"/>
+      <c r="I631" s="109">
+        <v>0.1958</v>
+      </c>
+      <c r="J631" s="109">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="K631" s="109">
+        <v>1.2735000000000001</v>
+      </c>
       <c r="L631" s="109"/>
       <c r="M631" s="109">
         <v>0.184</v>
@@ -72784,9 +72899,15 @@
       </c>
       <c r="G632" s="109"/>
       <c r="H632" s="109"/>
-      <c r="I632" s="109"/>
-      <c r="J632" s="109"/>
-      <c r="K632" s="109"/>
+      <c r="I632" s="109">
+        <v>0.18790000000000001</v>
+      </c>
+      <c r="J632" s="109">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="K632" s="109">
+        <v>1.2735000000000001</v>
+      </c>
       <c r="L632" s="109"/>
       <c r="M632" s="109">
         <v>0.182</v>
@@ -72891,9 +73012,15 @@
       </c>
       <c r="G633" s="109"/>
       <c r="H633" s="109"/>
-      <c r="I633" s="109"/>
-      <c r="J633" s="109"/>
-      <c r="K633" s="109"/>
+      <c r="I633" s="109">
+        <v>0.188</v>
+      </c>
+      <c r="J633" s="109">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="K633" s="109">
+        <v>1.2735000000000001</v>
+      </c>
       <c r="L633" s="109"/>
       <c r="M633" s="109"/>
       <c r="N633" s="113">
@@ -75703,7 +75830,9 @@
       <c r="D659" s="109">
         <v>1</v>
       </c>
-      <c r="E659" s="148"/>
+      <c r="E659" s="148" t="s">
+        <v>877</v>
+      </c>
       <c r="F659" s="109"/>
       <c r="G659" s="109"/>
       <c r="I659" s="109">
@@ -75800,7 +75929,9 @@
       <c r="D660" s="109">
         <v>2</v>
       </c>
-      <c r="E660" s="148"/>
+      <c r="E660" s="148" t="s">
+        <v>883</v>
+      </c>
       <c r="F660" s="109"/>
       <c r="G660" s="109"/>
       <c r="I660" s="109">
@@ -75897,7 +76028,9 @@
       <c r="D661" s="109">
         <v>3</v>
       </c>
-      <c r="E661" s="148"/>
+      <c r="E661" s="148" t="s">
+        <v>871</v>
+      </c>
       <c r="F661" s="109"/>
       <c r="G661" s="109"/>
       <c r="I661" s="109">
@@ -75984,7 +76117,9 @@
       <c r="D662" s="109">
         <v>4</v>
       </c>
-      <c r="E662" s="148"/>
+      <c r="E662" s="148" t="s">
+        <v>875</v>
+      </c>
       <c r="F662" s="109"/>
       <c r="G662" s="109"/>
       <c r="I662" s="109">
@@ -76083,7 +76218,9 @@
       <c r="D663" s="109">
         <v>5</v>
       </c>
-      <c r="E663" s="148"/>
+      <c r="E663" s="148" t="s">
+        <v>892</v>
+      </c>
       <c r="F663" s="109"/>
       <c r="G663" s="109"/>
       <c r="I663" s="109">
@@ -76172,7 +76309,9 @@
       <c r="D664" s="109">
         <v>6</v>
       </c>
-      <c r="E664" s="148"/>
+      <c r="E664" s="148" t="s">
+        <v>885</v>
+      </c>
       <c r="F664" s="109"/>
       <c r="G664" s="109"/>
       <c r="I664" s="109">
@@ -76257,7 +76396,9 @@
       <c r="D665" s="109">
         <v>7</v>
       </c>
-      <c r="E665" s="148"/>
+      <c r="E665" s="148" t="s">
+        <v>889</v>
+      </c>
       <c r="F665" s="109"/>
       <c r="G665" s="109"/>
       <c r="I665" s="109">
@@ -76348,7 +76489,9 @@
       <c r="D666" s="109">
         <v>1</v>
       </c>
-      <c r="E666" s="148"/>
+      <c r="E666" s="148" t="s">
+        <v>878</v>
+      </c>
       <c r="F666" s="109"/>
       <c r="G666" s="109"/>
       <c r="I666" s="109">
@@ -76439,7 +76582,9 @@
       <c r="D667" s="109">
         <v>2</v>
       </c>
-      <c r="E667" s="148"/>
+      <c r="E667" s="148" t="s">
+        <v>868</v>
+      </c>
       <c r="F667" s="109"/>
       <c r="G667" s="109"/>
       <c r="I667" s="109">
@@ -76536,7 +76681,9 @@
       <c r="D668" s="109">
         <v>3</v>
       </c>
-      <c r="E668" s="148"/>
+      <c r="E668" s="148" t="s">
+        <v>872</v>
+      </c>
       <c r="F668" s="109"/>
       <c r="G668" s="109"/>
       <c r="I668" s="109">
@@ -76633,7 +76780,9 @@
       <c r="D669" s="109">
         <v>4</v>
       </c>
-      <c r="E669" s="148"/>
+      <c r="E669" s="148" t="s">
+        <v>876</v>
+      </c>
       <c r="F669" s="109"/>
       <c r="G669" s="109"/>
       <c r="I669" s="109">
@@ -76730,7 +76879,9 @@
       <c r="D670" s="109">
         <v>5</v>
       </c>
-      <c r="E670" s="148"/>
+      <c r="E670" s="148" t="s">
+        <v>880</v>
+      </c>
       <c r="F670" s="109"/>
       <c r="G670" s="109"/>
       <c r="I670" s="109">
@@ -76829,7 +76980,9 @@
       <c r="D671" s="109">
         <v>6</v>
       </c>
-      <c r="E671" s="148"/>
+      <c r="E671" s="148" t="s">
+        <v>886</v>
+      </c>
       <c r="F671" s="109"/>
       <c r="G671" s="109"/>
       <c r="I671" s="109">
@@ -76926,7 +77079,9 @@
       <c r="D672" s="109">
         <v>1</v>
       </c>
-      <c r="E672" s="148"/>
+      <c r="E672" s="148" t="s">
+        <v>879</v>
+      </c>
       <c r="F672" s="109"/>
       <c r="G672" s="109"/>
       <c r="I672" s="109">
@@ -77023,7 +77178,9 @@
       <c r="D673" s="109">
         <v>2</v>
       </c>
-      <c r="E673" s="148"/>
+      <c r="E673" s="148" t="s">
+        <v>870</v>
+      </c>
       <c r="F673" s="109"/>
       <c r="G673" s="109"/>
       <c r="I673" s="109">
@@ -77122,7 +77279,9 @@
       <c r="D674" s="109">
         <v>3</v>
       </c>
-      <c r="E674" s="148"/>
+      <c r="E674" s="148" t="s">
+        <v>873</v>
+      </c>
       <c r="F674" s="109"/>
       <c r="G674" s="109"/>
       <c r="I674" s="109">
@@ -77221,7 +77380,9 @@
       <c r="D675" s="109">
         <v>4</v>
       </c>
-      <c r="E675" s="148"/>
+      <c r="E675" s="148" t="s">
+        <v>890</v>
+      </c>
       <c r="F675" s="109"/>
       <c r="G675" s="109"/>
       <c r="I675" s="109">
@@ -77310,7 +77471,9 @@
       <c r="D676" s="109">
         <v>5</v>
       </c>
-      <c r="E676" s="148"/>
+      <c r="E676" s="148" t="s">
+        <v>881</v>
+      </c>
       <c r="F676" s="109"/>
       <c r="G676" s="109"/>
       <c r="I676" s="109">
@@ -77391,7 +77554,9 @@
       <c r="D677" s="109">
         <v>6</v>
       </c>
-      <c r="E677" s="148"/>
+      <c r="E677" s="148" t="s">
+        <v>887</v>
+      </c>
       <c r="F677" s="109"/>
       <c r="G677" s="109"/>
       <c r="I677" s="109">
@@ -77482,7 +77647,9 @@
       <c r="D678" s="109">
         <v>1</v>
       </c>
-      <c r="E678" s="148"/>
+      <c r="E678" s="148" t="s">
+        <v>882</v>
+      </c>
       <c r="F678" s="109"/>
       <c r="G678" s="109"/>
       <c r="I678" s="109">
@@ -77581,7 +77748,9 @@
       <c r="D679" s="109">
         <v>2</v>
       </c>
-      <c r="E679" s="148"/>
+      <c r="E679" s="148" t="s">
+        <v>869</v>
+      </c>
       <c r="F679" s="109"/>
       <c r="G679" s="109"/>
       <c r="I679" s="109">
@@ -77670,7 +77839,9 @@
       <c r="D680" s="109">
         <v>3</v>
       </c>
-      <c r="E680" s="148"/>
+      <c r="E680" s="148" t="s">
+        <v>874</v>
+      </c>
       <c r="F680" s="109"/>
       <c r="G680" s="109"/>
       <c r="I680" s="109">
@@ -77759,7 +77930,9 @@
       <c r="D681" s="109">
         <v>4</v>
       </c>
-      <c r="E681" s="148"/>
+      <c r="E681" s="148" t="s">
+        <v>891</v>
+      </c>
       <c r="F681" s="109"/>
       <c r="G681" s="109"/>
       <c r="I681" s="109">
@@ -77858,7 +78031,9 @@
       <c r="D682" s="109">
         <v>5</v>
       </c>
-      <c r="E682" s="148"/>
+      <c r="E682" s="148" t="s">
+        <v>884</v>
+      </c>
       <c r="F682" s="109"/>
       <c r="G682" s="109"/>
       <c r="I682" s="109">
@@ -77957,7 +78132,9 @@
       <c r="D683" s="109">
         <v>6</v>
       </c>
-      <c r="E683" s="148"/>
+      <c r="E683" s="148" t="s">
+        <v>888</v>
+      </c>
       <c r="F683" s="109"/>
       <c r="G683" s="109"/>
       <c r="I683" s="109">
@@ -78096,6 +78273,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004F1ECC6B2649324CB24C079D2C04510D" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="608b5d954c2eb0ac10393708da8d34af">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65551c38-962b-4cee-924d-ef2df1bb8b98" xmlns:ns3="ec750ee3-7d64-422f-9b1f-0ca7238893a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af171f03bd4cf151e3e856a6839c0cc7" ns2:_="" ns3:_="">
     <xsd:import namespace="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
@@ -78343,26 +78539,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -78379,29 +78581,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97D89CF-C6D6-454B-8A10-3559FD56978D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC94960-8AD9-41D2-9D75-B706A0B58D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6025" uniqueCount="938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6025" uniqueCount="937">
   <si>
     <t>Squad</t>
   </si>
@@ -2736,9 +2736,6 @@
   </si>
   <si>
     <t>https://youtu.be/Y_N7CFY6HbQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Gate </t>
   </si>
   <si>
     <t>Pos J</t>
@@ -4066,10 +4063,12 @@
     <sheetNames>
       <sheetName val="CdA Track Testing"/>
       <sheetName val="Data cut from table - to sort"/>
+      <sheetName val="Track CdA Aero Testing Database"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -74687,7 +74686,7 @@
         <v>867</v>
       </c>
       <c r="F659" s="146" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G659" s="107">
         <v>0.1842</v>
@@ -74787,7 +74786,7 @@
         <v>873</v>
       </c>
       <c r="F660" s="146" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G660" s="107">
         <v>0.19700000000000001</v>
@@ -74887,7 +74886,7 @@
         <v>861</v>
       </c>
       <c r="F661" s="146" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G661" s="107">
         <v>0.1852</v>
@@ -74977,7 +74976,7 @@
         <v>865</v>
       </c>
       <c r="F662" s="146" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G662" s="107">
         <v>0.18540000000000001</v>
@@ -75079,7 +75078,7 @@
         <v>882</v>
       </c>
       <c r="F663" s="146" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G663" s="107">
         <v>0.19950000000000001</v>
@@ -75171,7 +75170,7 @@
         <v>875</v>
       </c>
       <c r="F664" s="146" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G664" s="107">
         <v>0.18429999999999999</v>
@@ -75259,7 +75258,7 @@
         <v>879</v>
       </c>
       <c r="F665" s="146" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="G665" s="107">
         <v>0.17530000000000001</v>
@@ -75447,7 +75446,7 @@
         <v>858</v>
       </c>
       <c r="F667" s="146" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G667" s="107">
         <v>0.16209999999999999</v>
@@ -75747,7 +75746,7 @@
         <v>870</v>
       </c>
       <c r="F670" s="146" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G670" s="107">
         <v>0.1643</v>
@@ -76151,7 +76150,7 @@
         <v>863</v>
       </c>
       <c r="F674" s="146" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G674" s="107">
         <v>0.17319999999999999</v>
@@ -76429,7 +76428,7 @@
         <v>877</v>
       </c>
       <c r="F677" s="146" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G677" s="107">
         <v>0.1794</v>
@@ -76625,7 +76624,7 @@
         <v>859</v>
       </c>
       <c r="F679" s="146" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G679" s="107">
         <v>0.1555</v>
@@ -76911,7 +76910,7 @@
         <v>874</v>
       </c>
       <c r="F682" s="146" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G682" s="107">
         <v>0.15790000000000001</v>
@@ -77100,7 +77099,7 @@
         <v>1</v>
       </c>
       <c r="E684" s="146" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F684" s="146" t="s">
         <v>92</v>
@@ -77202,10 +77201,10 @@
         <v>2</v>
       </c>
       <c r="E685" s="161" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F685" s="146" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G685" s="107">
         <v>0.1646</v>
@@ -77289,7 +77288,7 @@
         <v>2096</v>
       </c>
       <c r="BH685" s="5" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="686" spans="1:60" x14ac:dyDescent="0.3">
@@ -77306,7 +77305,7 @@
         <v>3</v>
       </c>
       <c r="E686" s="146" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F686" s="146" t="s">
         <v>801</v>
@@ -77393,7 +77392,7 @@
         <v>2096</v>
       </c>
       <c r="BH686" s="5" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="687" spans="1:60" x14ac:dyDescent="0.3">
@@ -77410,7 +77409,7 @@
         <v>4</v>
       </c>
       <c r="E687" s="146" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F687" s="146" t="s">
         <v>92</v>
@@ -77497,7 +77496,7 @@
         <v>2096</v>
       </c>
       <c r="BH687" s="5" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="688" spans="1:60" x14ac:dyDescent="0.3">
@@ -77514,10 +77513,10 @@
         <v>5</v>
       </c>
       <c r="E688" s="146" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F688" s="146" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G688" s="107">
         <v>0.16300000000000001</v>
@@ -77601,7 +77600,7 @@
         <v>2096</v>
       </c>
       <c r="BH688" s="5" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="689" spans="1:60" x14ac:dyDescent="0.3">
@@ -77618,7 +77617,7 @@
         <v>6</v>
       </c>
       <c r="E689" s="146" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F689" s="146" t="s">
         <v>801</v>
@@ -77705,7 +77704,7 @@
         <v>2096</v>
       </c>
       <c r="BH689" s="5" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="690" spans="1:60" x14ac:dyDescent="0.3">
@@ -77722,7 +77721,7 @@
         <v>1</v>
       </c>
       <c r="E690" s="146" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F690" s="146" t="s">
         <v>92</v>
@@ -77825,7 +77824,7 @@
         <v>2</v>
       </c>
       <c r="E691" s="146" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F691" s="146" t="s">
         <v>771</v>
@@ -77913,7 +77912,7 @@
         <v>2096</v>
       </c>
       <c r="BH691" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="692" spans="1:60" x14ac:dyDescent="0.3">
@@ -77930,7 +77929,7 @@
         <v>3</v>
       </c>
       <c r="E692" s="146" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="F692" s="146" t="s">
         <v>92</v>
@@ -78015,7 +78014,7 @@
         <v>2096</v>
       </c>
       <c r="BH692" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="693" spans="1:60" x14ac:dyDescent="0.3">
@@ -78032,7 +78031,7 @@
         <v>4</v>
       </c>
       <c r="E693" s="146" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F693" s="146" t="s">
         <v>771</v>
@@ -78132,7 +78131,7 @@
         <v>5</v>
       </c>
       <c r="E694" s="146" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F694" s="146" t="s">
         <v>92</v>
@@ -78217,7 +78216,7 @@
         <v>2096</v>
       </c>
       <c r="BH694" s="5" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="695" spans="1:60" x14ac:dyDescent="0.3">
@@ -78234,7 +78233,7 @@
         <v>6</v>
       </c>
       <c r="E695" s="146" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F695" s="146" t="s">
         <v>771</v>
@@ -78319,7 +78318,7 @@
         <v>2096</v>
       </c>
       <c r="BH695" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="696" spans="1:60" x14ac:dyDescent="0.3">
@@ -78336,7 +78335,7 @@
         <v>1</v>
       </c>
       <c r="E696" s="146" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F696" s="146" t="s">
         <v>92</v>
@@ -78419,7 +78418,7 @@
         <v>2096</v>
       </c>
       <c r="BH696" s="5" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="697" spans="1:60" x14ac:dyDescent="0.3">
@@ -78436,10 +78435,10 @@
         <v>2</v>
       </c>
       <c r="E697" s="146" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F697" s="146" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G697" s="107">
         <v>0.1694</v>
@@ -78519,7 +78518,7 @@
         <v>2096</v>
       </c>
       <c r="BH697" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="698" spans="1:60" x14ac:dyDescent="0.3">
@@ -78536,7 +78535,7 @@
         <v>3</v>
       </c>
       <c r="E698" s="146" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F698" s="146" t="s">
         <v>92</v>
@@ -78634,10 +78633,10 @@
         <v>4</v>
       </c>
       <c r="E699" s="146" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F699" s="146" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G699" s="107">
         <v>0.1714</v>
@@ -78717,7 +78716,7 @@
         <v>2096</v>
       </c>
       <c r="BH699" s="5" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="700" spans="1:60" x14ac:dyDescent="0.3">
@@ -78734,7 +78733,7 @@
         <v>5</v>
       </c>
       <c r="E700" s="146" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F700" s="146" t="s">
         <v>92</v>
@@ -78832,10 +78831,10 @@
         <v>6</v>
       </c>
       <c r="E701" s="146" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F701" s="146" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G701" s="107">
         <v>0.1673</v>
@@ -78915,7 +78914,7 @@
         <v>2096</v>
       </c>
       <c r="BH701" s="5" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="702" spans="1:60" x14ac:dyDescent="0.3">
@@ -78923,7 +78922,7 @@
         <v>16</v>
       </c>
       <c r="B702" s="107" t="s">
-        <v>883</v>
+        <v>17</v>
       </c>
       <c r="C702" s="138">
         <v>45313</v>
@@ -78932,10 +78931,10 @@
         <v>1</v>
       </c>
       <c r="E702" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F702" s="146" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G702" s="107">
         <v>0.16020000000000001</v>
@@ -79031,7 +79030,7 @@
         <v>16</v>
       </c>
       <c r="B703" s="107" t="s">
-        <v>883</v>
+        <v>17</v>
       </c>
       <c r="C703" s="138">
         <v>45313</v>
@@ -79040,10 +79039,10 @@
         <v>2</v>
       </c>
       <c r="E703" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F703" s="146" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G703" s="159"/>
       <c r="H703" s="159"/>
@@ -79135,7 +79134,7 @@
         <v>16</v>
       </c>
       <c r="B704" s="107" t="s">
-        <v>883</v>
+        <v>17</v>
       </c>
       <c r="C704" s="138">
         <v>45313</v>
@@ -79144,10 +79143,10 @@
         <v>3</v>
       </c>
       <c r="E704" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="F704" s="146" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G704" s="107">
         <v>0.1704</v>
@@ -79175,7 +79174,7 @@
         <v>755.7</v>
       </c>
       <c r="R704" s="160" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="S704" s="107" t="s">
         <v>740</v>
@@ -79243,7 +79242,7 @@
         <v>16</v>
       </c>
       <c r="B705" s="107" t="s">
-        <v>883</v>
+        <v>17</v>
       </c>
       <c r="C705" s="138">
         <v>45313</v>
@@ -79252,10 +79251,10 @@
         <v>4</v>
       </c>
       <c r="E705" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F705" s="146" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G705" s="107">
         <v>0.16889999999999999</v>
@@ -79351,7 +79350,7 @@
         <v>16</v>
       </c>
       <c r="B706" s="107" t="s">
-        <v>883</v>
+        <v>17</v>
       </c>
       <c r="C706" s="138">
         <v>45313</v>
@@ -79360,10 +79359,10 @@
         <v>5</v>
       </c>
       <c r="E706" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="F706" s="146" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G706" s="107">
         <v>0.16900000000000001</v>
@@ -79391,7 +79390,7 @@
         <v>755.8</v>
       </c>
       <c r="R706" s="160" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="S706" s="107" t="s">
         <v>740</v>
@@ -79459,7 +79458,7 @@
         <v>16</v>
       </c>
       <c r="B707" s="107" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C707" s="138">
         <v>45313</v>
@@ -79468,7 +79467,7 @@
         <v>1</v>
       </c>
       <c r="E707" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="F707" s="146" t="s">
         <v>616</v>
@@ -79506,7 +79505,7 @@
       </c>
       <c r="T707" s="107"/>
       <c r="U707" s="107" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="V707" s="107"/>
       <c r="W707" s="107"/>
@@ -79567,7 +79566,7 @@
         <v>16</v>
       </c>
       <c r="B708" s="107" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C708" s="138">
         <v>45313</v>
@@ -79576,7 +79575,7 @@
         <v>2</v>
       </c>
       <c r="E708" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F708" s="146" t="s">
         <v>616</v>
@@ -79614,7 +79613,7 @@
       </c>
       <c r="T708" s="107"/>
       <c r="U708" s="107" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="V708" s="107"/>
       <c r="W708" s="107"/>
@@ -79675,7 +79674,7 @@
         <v>16</v>
       </c>
       <c r="B709" s="107" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C709" s="138">
         <v>45313</v>
@@ -79684,10 +79683,10 @@
         <v>3</v>
       </c>
       <c r="E709" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F709" s="146" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G709" s="107">
         <v>0.191</v>
@@ -79722,7 +79721,7 @@
       </c>
       <c r="T709" s="107"/>
       <c r="U709" s="107" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="V709" s="107"/>
       <c r="W709" s="107"/>
@@ -79783,7 +79782,7 @@
         <v>16</v>
       </c>
       <c r="B710" s="107" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C710" s="138">
         <v>45313</v>
@@ -79792,7 +79791,7 @@
         <v>4</v>
       </c>
       <c r="E710" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F710" s="146" t="s">
         <v>616</v>
@@ -79830,7 +79829,7 @@
       </c>
       <c r="T710" s="107"/>
       <c r="U710" s="107" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="V710" s="107"/>
       <c r="W710" s="107"/>
@@ -79891,7 +79890,7 @@
         <v>16</v>
       </c>
       <c r="B711" s="107" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C711" s="138">
         <v>45313</v>
@@ -79900,10 +79899,10 @@
         <v>5</v>
       </c>
       <c r="E711" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F711" s="146" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G711" s="107">
         <v>0.186</v>
@@ -79938,7 +79937,7 @@
       </c>
       <c r="T711" s="107"/>
       <c r="U711" s="107" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="V711" s="107"/>
       <c r="W711" s="107"/>
@@ -79999,7 +79998,7 @@
         <v>16</v>
       </c>
       <c r="B712" s="107" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C712" s="138">
         <v>45313</v>
@@ -80008,7 +80007,7 @@
         <v>6</v>
       </c>
       <c r="E712" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F712" s="146" t="s">
         <v>616</v>
@@ -80046,7 +80045,7 @@
       </c>
       <c r="T712" s="107"/>
       <c r="U712" s="107" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="V712" s="107"/>
       <c r="W712" s="107"/>
@@ -80107,7 +80106,7 @@
         <v>16</v>
       </c>
       <c r="B713" s="107" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C713" s="138">
         <v>45313</v>
@@ -80116,7 +80115,7 @@
         <v>7</v>
       </c>
       <c r="E713" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F713" s="146" t="s">
         <v>616</v>
@@ -80154,7 +80153,7 @@
       </c>
       <c r="T713" s="107"/>
       <c r="U713" s="107" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="V713" s="107"/>
       <c r="W713" s="107"/>
@@ -80224,7 +80223,7 @@
         <v>1</v>
       </c>
       <c r="E714" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F714" s="146" t="s">
         <v>92</v>
@@ -80332,10 +80331,10 @@
         <v>2</v>
       </c>
       <c r="E715" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F715" s="146" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G715" s="107">
         <v>0.15229999999999999</v>
@@ -80440,10 +80439,10 @@
         <v>3</v>
       </c>
       <c r="E716" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="F716" s="146" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="G716" s="107">
         <v>0.1525</v>
@@ -80548,7 +80547,7 @@
         <v>4</v>
       </c>
       <c r="E717" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F717" s="146" t="s">
         <v>96</v>
@@ -80656,10 +80655,10 @@
         <v>5</v>
       </c>
       <c r="E718" s="162" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F718" s="146" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G718" s="107">
         <v>0.15129999999999999</v>
@@ -80764,10 +80763,10 @@
         <v>6</v>
       </c>
       <c r="E719" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F719" s="146" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="G719" s="107">
         <v>0.15310000000000001</v>
@@ -80872,10 +80871,10 @@
         <v>7</v>
       </c>
       <c r="E720" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F720" s="146" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G720" s="107">
         <v>0.15154999999999999</v>
@@ -81034,6 +81033,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004F1ECC6B2649324CB24C079D2C04510D" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="608b5d954c2eb0ac10393708da8d34af">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65551c38-962b-4cee-924d-ef2df1bb8b98" xmlns:ns3="ec750ee3-7d64-422f-9b1f-0ca7238893a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af171f03bd4cf151e3e856a6839c0cc7" ns2:_="" ns3:_="">
     <xsd:import namespace="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
@@ -81281,26 +81299,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -81317,29 +81341,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC94960-8AD9-41D2-9D75-B706A0B58D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB68EF83-DE27-4EFE-95C6-1C41FF0A4F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6025" uniqueCount="937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6064" uniqueCount="945">
   <si>
     <t>Squad</t>
   </si>
@@ -2898,6 +2898,30 @@
   </si>
   <si>
     <t>https://youtu.be/qsx0qRsHTyI</t>
+  </si>
+  <si>
+    <t>Pos A FW</t>
+  </si>
+  <si>
+    <t>Pos B FW</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UgpmVes83_8</t>
+  </si>
+  <si>
+    <t>https://youtu.be/_z0pjAJpfxI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/qdHqcayI7L0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Kxkzs8nE_30</t>
+  </si>
+  <si>
+    <t>https://youtu.be/pYZ6m5uWfBs</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sjySGA9TDtc</t>
   </si>
 </sst>
 </file>
@@ -4063,12 +4087,10 @@
     <sheetNames>
       <sheetName val="CdA Track Testing"/>
       <sheetName val="Data cut from table - to sort"/>
-      <sheetName val="Track CdA Aero Testing Database"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4409,7 +4431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:BM721"/>
+  <dimension ref="A1:BM726"/>
   <sheetFormatPr defaultColWidth="15.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" style="2" bestFit="1" customWidth="1"/>
@@ -80963,22 +80985,62 @@
       </c>
       <c r="BH720" s="5"/>
     </row>
-    <row r="721" spans="7:60" x14ac:dyDescent="0.3">
-      <c r="G721" s="107"/>
-      <c r="H721" s="107"/>
-      <c r="I721" s="107"/>
+    <row r="721" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A721" s="107" t="s">
+        <v>16</v>
+      </c>
+      <c r="B721" s="107" t="s">
+        <v>120</v>
+      </c>
+      <c r="C721" s="138">
+        <v>45316</v>
+      </c>
+      <c r="D721" s="107">
+        <v>1</v>
+      </c>
+      <c r="E721" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="F721" s="146" t="s">
+        <v>92</v>
+      </c>
+      <c r="G721" s="107">
+        <v>0.17680000000000001</v>
+      </c>
+      <c r="H721" s="107">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I721" s="107">
+        <v>1.244</v>
+      </c>
       <c r="J721" s="107"/>
-      <c r="K721" s="107"/>
-      <c r="L721" s="111"/>
+      <c r="K721" s="107">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="L721" s="111">
+        <v>0.18110000000000001</v>
+      </c>
       <c r="M721" s="107"/>
       <c r="N721" s="107"/>
-      <c r="O721" s="141"/>
-      <c r="P721" s="142"/>
-      <c r="Q721" s="107"/>
-      <c r="R721" s="107"/>
-      <c r="S721" s="107"/>
+      <c r="O721" s="141">
+        <v>60.4</v>
+      </c>
+      <c r="P721" s="142">
+        <v>515</v>
+      </c>
+      <c r="Q721" s="107">
+        <v>756.6</v>
+      </c>
+      <c r="R721" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="S721" s="107" t="s">
+        <v>20</v>
+      </c>
       <c r="T721" s="107"/>
-      <c r="U721" s="107"/>
+      <c r="U721" s="107" t="s">
+        <v>75</v>
+      </c>
       <c r="V721" s="107"/>
       <c r="W721" s="107"/>
       <c r="X721" s="107"/>
@@ -81009,15 +81071,567 @@
       <c r="AW721" s="5"/>
       <c r="AX721" s="5"/>
       <c r="AY721" s="5"/>
-      <c r="AZ721" s="5"/>
+      <c r="AZ721" s="5">
+        <v>117</v>
+      </c>
       <c r="BA721" s="5"/>
       <c r="BB721" s="5"/>
-      <c r="BC721" s="5"/>
-      <c r="BD721" s="157"/>
-      <c r="BE721" s="158"/>
-      <c r="BF721" s="154"/>
-      <c r="BG721" s="5"/>
+      <c r="BC721" s="5">
+        <v>25.7</v>
+      </c>
+      <c r="BD721" s="157">
+        <v>1006</v>
+      </c>
+      <c r="BE721" s="158">
+        <v>49</v>
+      </c>
+      <c r="BF721" s="154">
+        <v>1.1659999999999999</v>
+      </c>
+      <c r="BG721" s="152">
+        <v>2096</v>
+      </c>
       <c r="BH721" s="5"/>
+      <c r="BK721" s="8"/>
+      <c r="BM721"/>
+    </row>
+    <row r="722" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A722" s="107" t="s">
+        <v>16</v>
+      </c>
+      <c r="B722" s="107" t="s">
+        <v>120</v>
+      </c>
+      <c r="C722" s="138">
+        <v>45682</v>
+      </c>
+      <c r="D722" s="107">
+        <v>2</v>
+      </c>
+      <c r="E722" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="F722" s="146" t="s">
+        <v>937</v>
+      </c>
+      <c r="G722" s="107">
+        <v>0.17319999999999999</v>
+      </c>
+      <c r="H722" s="107">
+        <v>4.3E-3</v>
+      </c>
+      <c r="I722" s="107">
+        <v>1.244</v>
+      </c>
+      <c r="J722" s="107"/>
+      <c r="K722" s="107">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="L722" s="111">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="M722" s="107"/>
+      <c r="N722" s="107"/>
+      <c r="O722" s="141">
+        <v>64</v>
+      </c>
+      <c r="P722" s="142">
+        <v>527</v>
+      </c>
+      <c r="Q722" s="107">
+        <v>758.4</v>
+      </c>
+      <c r="R722" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="S722" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="T722" s="107"/>
+      <c r="U722" s="107" t="s">
+        <v>75</v>
+      </c>
+      <c r="V722" s="107"/>
+      <c r="W722" s="107"/>
+      <c r="X722" s="107"/>
+      <c r="Y722" s="107"/>
+      <c r="Z722" s="107"/>
+      <c r="AA722" s="107"/>
+      <c r="AB722" s="107"/>
+      <c r="AC722" s="107"/>
+      <c r="AD722" s="5"/>
+      <c r="AE722" s="5"/>
+      <c r="AF722" s="5"/>
+      <c r="AG722" s="5"/>
+      <c r="AH722" s="5"/>
+      <c r="AI722" s="5"/>
+      <c r="AJ722" s="5"/>
+      <c r="AK722" s="5"/>
+      <c r="AL722" s="5"/>
+      <c r="AM722" s="5"/>
+      <c r="AN722" s="5"/>
+      <c r="AO722" s="5"/>
+      <c r="AP722" s="5"/>
+      <c r="AQ722" s="5"/>
+      <c r="AR722" s="5"/>
+      <c r="AS722" s="5"/>
+      <c r="AT722" s="5"/>
+      <c r="AU722" s="5"/>
+      <c r="AV722" s="5"/>
+      <c r="AW722" s="5"/>
+      <c r="AX722" s="5"/>
+      <c r="AY722" s="5"/>
+      <c r="AZ722" s="5">
+        <v>117</v>
+      </c>
+      <c r="BA722" s="5"/>
+      <c r="BB722" s="5"/>
+      <c r="BC722" s="5">
+        <v>25.7</v>
+      </c>
+      <c r="BD722" s="157">
+        <v>1006</v>
+      </c>
+      <c r="BE722" s="158">
+        <v>49</v>
+      </c>
+      <c r="BF722" s="154">
+        <v>1.1659999999999999</v>
+      </c>
+      <c r="BG722" s="152">
+        <v>2096</v>
+      </c>
+      <c r="BH722" s="5"/>
+      <c r="BK722" s="8"/>
+      <c r="BM722"/>
+    </row>
+    <row r="723" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A723" s="107" t="s">
+        <v>16</v>
+      </c>
+      <c r="B723" s="107" t="s">
+        <v>120</v>
+      </c>
+      <c r="C723" s="138">
+        <v>46047</v>
+      </c>
+      <c r="D723" s="107">
+        <v>3</v>
+      </c>
+      <c r="E723" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="F723" s="146" t="s">
+        <v>938</v>
+      </c>
+      <c r="G723" s="107">
+        <v>0.17369999999999999</v>
+      </c>
+      <c r="H723" s="107">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="I723" s="107">
+        <v>1.244</v>
+      </c>
+      <c r="J723" s="107"/>
+      <c r="K723" s="107">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="L723" s="111">
+        <v>0.1729</v>
+      </c>
+      <c r="M723" s="107"/>
+      <c r="N723" s="107"/>
+      <c r="O723" s="141">
+        <v>61.5</v>
+      </c>
+      <c r="P723" s="142">
+        <v>539</v>
+      </c>
+      <c r="Q723" s="107">
+        <v>758.4</v>
+      </c>
+      <c r="R723" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="S723" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="T723" s="107"/>
+      <c r="U723" s="107" t="s">
+        <v>75</v>
+      </c>
+      <c r="V723" s="107"/>
+      <c r="W723" s="107"/>
+      <c r="X723" s="107"/>
+      <c r="Y723" s="107"/>
+      <c r="Z723" s="107"/>
+      <c r="AA723" s="107"/>
+      <c r="AB723" s="107"/>
+      <c r="AC723" s="107"/>
+      <c r="AD723" s="5"/>
+      <c r="AE723" s="5"/>
+      <c r="AF723" s="5"/>
+      <c r="AG723" s="5"/>
+      <c r="AH723" s="5"/>
+      <c r="AI723" s="5"/>
+      <c r="AJ723" s="5"/>
+      <c r="AK723" s="5"/>
+      <c r="AL723" s="5"/>
+      <c r="AM723" s="5"/>
+      <c r="AN723" s="5"/>
+      <c r="AO723" s="5"/>
+      <c r="AP723" s="5"/>
+      <c r="AQ723" s="5"/>
+      <c r="AR723" s="5"/>
+      <c r="AS723" s="5"/>
+      <c r="AT723" s="5"/>
+      <c r="AU723" s="5"/>
+      <c r="AV723" s="5"/>
+      <c r="AW723" s="5"/>
+      <c r="AX723" s="5"/>
+      <c r="AY723" s="5"/>
+      <c r="AZ723" s="5">
+        <v>117</v>
+      </c>
+      <c r="BA723" s="5"/>
+      <c r="BB723" s="5"/>
+      <c r="BC723" s="5">
+        <v>25.7</v>
+      </c>
+      <c r="BD723" s="157">
+        <v>1006</v>
+      </c>
+      <c r="BE723" s="158">
+        <v>49</v>
+      </c>
+      <c r="BF723" s="154">
+        <v>1.1659999999999999</v>
+      </c>
+      <c r="BG723" s="152">
+        <v>2096</v>
+      </c>
+      <c r="BH723" s="5"/>
+      <c r="BK723" s="8"/>
+      <c r="BM723"/>
+    </row>
+    <row r="724" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A724" s="107" t="s">
+        <v>16</v>
+      </c>
+      <c r="B724" s="107" t="s">
+        <v>120</v>
+      </c>
+      <c r="C724" s="138">
+        <v>46412</v>
+      </c>
+      <c r="D724" s="107">
+        <v>4</v>
+      </c>
+      <c r="E724" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="F724" s="146" t="s">
+        <v>92</v>
+      </c>
+      <c r="G724" s="107">
+        <v>0.17419999999999999</v>
+      </c>
+      <c r="H724" s="107">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="I724" s="107">
+        <v>1.244</v>
+      </c>
+      <c r="J724" s="107"/>
+      <c r="K724" s="107">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="L724" s="111">
+        <v>0.1777</v>
+      </c>
+      <c r="M724" s="107"/>
+      <c r="N724" s="107"/>
+      <c r="O724" s="141">
+        <v>61.3</v>
+      </c>
+      <c r="P724" s="142">
+        <v>538</v>
+      </c>
+      <c r="Q724" s="107">
+        <v>756.8</v>
+      </c>
+      <c r="R724" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="S724" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="T724" s="107"/>
+      <c r="U724" s="107" t="s">
+        <v>75</v>
+      </c>
+      <c r="V724" s="107"/>
+      <c r="W724" s="107"/>
+      <c r="X724" s="107"/>
+      <c r="Y724" s="107"/>
+      <c r="Z724" s="107"/>
+      <c r="AA724" s="107"/>
+      <c r="AB724" s="107"/>
+      <c r="AC724" s="107"/>
+      <c r="AD724" s="5"/>
+      <c r="AE724" s="5"/>
+      <c r="AF724" s="5"/>
+      <c r="AG724" s="5"/>
+      <c r="AH724" s="5"/>
+      <c r="AI724" s="5"/>
+      <c r="AJ724" s="5"/>
+      <c r="AK724" s="5"/>
+      <c r="AL724" s="5"/>
+      <c r="AM724" s="5"/>
+      <c r="AN724" s="5"/>
+      <c r="AO724" s="5"/>
+      <c r="AP724" s="5"/>
+      <c r="AQ724" s="5"/>
+      <c r="AR724" s="5"/>
+      <c r="AS724" s="5"/>
+      <c r="AT724" s="5"/>
+      <c r="AU724" s="5"/>
+      <c r="AV724" s="5"/>
+      <c r="AW724" s="5"/>
+      <c r="AX724" s="5"/>
+      <c r="AY724" s="5"/>
+      <c r="AZ724" s="5">
+        <v>117</v>
+      </c>
+      <c r="BA724" s="5"/>
+      <c r="BB724" s="5"/>
+      <c r="BC724" s="5">
+        <v>25.7</v>
+      </c>
+      <c r="BD724" s="157">
+        <v>1006</v>
+      </c>
+      <c r="BE724" s="158">
+        <v>49</v>
+      </c>
+      <c r="BF724" s="154">
+        <v>1.1659999999999999</v>
+      </c>
+      <c r="BG724" s="152">
+        <v>2096</v>
+      </c>
+      <c r="BH724" s="5"/>
+      <c r="BK724" s="8"/>
+      <c r="BM724"/>
+    </row>
+    <row r="725" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A725" s="107" t="s">
+        <v>16</v>
+      </c>
+      <c r="B725" s="107" t="s">
+        <v>120</v>
+      </c>
+      <c r="C725" s="138">
+        <v>46777</v>
+      </c>
+      <c r="D725" s="107">
+        <v>5</v>
+      </c>
+      <c r="E725" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="F725" s="146" t="s">
+        <v>937</v>
+      </c>
+      <c r="G725" s="107">
+        <v>0.17319999999999999</v>
+      </c>
+      <c r="H725" s="107">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="I725" s="107">
+        <v>1.244</v>
+      </c>
+      <c r="J725" s="107"/>
+      <c r="K725" s="107">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="L725" s="111">
+        <v>0.17519999999999999</v>
+      </c>
+      <c r="M725" s="107"/>
+      <c r="N725" s="107"/>
+      <c r="O725" s="141">
+        <v>61.3</v>
+      </c>
+      <c r="P725" s="142">
+        <v>540</v>
+      </c>
+      <c r="Q725" s="107">
+        <v>757.8</v>
+      </c>
+      <c r="R725" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="S725" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="T725" s="107"/>
+      <c r="U725" s="107" t="s">
+        <v>75</v>
+      </c>
+      <c r="V725" s="107"/>
+      <c r="W725" s="107"/>
+      <c r="X725" s="107"/>
+      <c r="Y725" s="107"/>
+      <c r="Z725" s="107"/>
+      <c r="AA725" s="107"/>
+      <c r="AB725" s="107"/>
+      <c r="AC725" s="107"/>
+      <c r="AD725" s="5"/>
+      <c r="AE725" s="5"/>
+      <c r="AF725" s="5"/>
+      <c r="AG725" s="5"/>
+      <c r="AH725" s="5"/>
+      <c r="AI725" s="5"/>
+      <c r="AJ725" s="5"/>
+      <c r="AK725" s="5"/>
+      <c r="AL725" s="5"/>
+      <c r="AM725" s="5"/>
+      <c r="AN725" s="5"/>
+      <c r="AO725" s="5"/>
+      <c r="AP725" s="5"/>
+      <c r="AQ725" s="5"/>
+      <c r="AR725" s="5"/>
+      <c r="AS725" s="5"/>
+      <c r="AT725" s="5"/>
+      <c r="AU725" s="5"/>
+      <c r="AV725" s="5"/>
+      <c r="AW725" s="5"/>
+      <c r="AX725" s="5"/>
+      <c r="AY725" s="5"/>
+      <c r="AZ725" s="5">
+        <v>117</v>
+      </c>
+      <c r="BA725" s="5"/>
+      <c r="BB725" s="5"/>
+      <c r="BC725" s="5">
+        <v>26.4</v>
+      </c>
+      <c r="BD725" s="157">
+        <v>1006</v>
+      </c>
+      <c r="BE725" s="158">
+        <v>47</v>
+      </c>
+      <c r="BF725" s="154">
+        <v>1.1619999999999999</v>
+      </c>
+      <c r="BG725" s="152">
+        <v>2096</v>
+      </c>
+      <c r="BH725" s="5"/>
+      <c r="BK725" s="8"/>
+      <c r="BM725"/>
+    </row>
+    <row r="726" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A726" s="107" t="s">
+        <v>16</v>
+      </c>
+      <c r="B726" s="107" t="s">
+        <v>120</v>
+      </c>
+      <c r="C726" s="138">
+        <v>47143</v>
+      </c>
+      <c r="D726" s="107">
+        <v>6</v>
+      </c>
+      <c r="E726" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="F726" s="146" t="s">
+        <v>938</v>
+      </c>
+      <c r="G726" s="107">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="H726" s="107">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="I726" s="107">
+        <v>1.244</v>
+      </c>
+      <c r="J726" s="107"/>
+      <c r="K726" s="107">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="L726" s="111">
+        <v>0.17449999999999999</v>
+      </c>
+      <c r="M726" s="107"/>
+      <c r="N726" s="107"/>
+      <c r="O726" s="141"/>
+      <c r="P726" s="142"/>
+      <c r="Q726" s="107"/>
+      <c r="R726" s="107"/>
+      <c r="S726" s="107"/>
+      <c r="T726" s="107"/>
+      <c r="U726" s="107"/>
+      <c r="V726" s="107"/>
+      <c r="W726" s="107"/>
+      <c r="X726" s="107"/>
+      <c r="Y726" s="107"/>
+      <c r="Z726" s="107"/>
+      <c r="AA726" s="107"/>
+      <c r="AB726" s="107"/>
+      <c r="AC726" s="107"/>
+      <c r="AD726" s="5"/>
+      <c r="AE726" s="5"/>
+      <c r="AF726" s="5"/>
+      <c r="AG726" s="5"/>
+      <c r="AH726" s="5"/>
+      <c r="AI726" s="5"/>
+      <c r="AJ726" s="5"/>
+      <c r="AK726" s="5"/>
+      <c r="AL726" s="5"/>
+      <c r="AM726" s="5"/>
+      <c r="AN726" s="5"/>
+      <c r="AO726" s="5"/>
+      <c r="AP726" s="5"/>
+      <c r="AQ726" s="5"/>
+      <c r="AR726" s="5"/>
+      <c r="AS726" s="5"/>
+      <c r="AT726" s="5"/>
+      <c r="AU726" s="5"/>
+      <c r="AV726" s="5"/>
+      <c r="AW726" s="5"/>
+      <c r="AX726" s="5"/>
+      <c r="AY726" s="5"/>
+      <c r="AZ726" s="5">
+        <v>117</v>
+      </c>
+      <c r="BA726" s="5"/>
+      <c r="BB726" s="5"/>
+      <c r="BC726" s="5">
+        <v>26.4</v>
+      </c>
+      <c r="BD726" s="157">
+        <v>1006</v>
+      </c>
+      <c r="BE726" s="158">
+        <v>47</v>
+      </c>
+      <c r="BF726" s="154">
+        <v>1.1619999999999999</v>
+      </c>
+      <c r="BG726" s="152">
+        <v>2096</v>
+      </c>
+      <c r="BH726" s="5"/>
+      <c r="BK726" s="8"/>
+      <c r="BM726"/>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
@@ -81033,25 +81647,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004F1ECC6B2649324CB24C079D2C04510D" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="608b5d954c2eb0ac10393708da8d34af">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65551c38-962b-4cee-924d-ef2df1bb8b98" xmlns:ns3="ec750ee3-7d64-422f-9b1f-0ca7238893a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af171f03bd4cf151e3e856a6839c0cc7" ns2:_="" ns3:_="">
     <xsd:import namespace="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
@@ -81299,32 +81894,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -81341,4 +81930,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB68EF83-DE27-4EFE-95C6-1C41FF0A4F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5C3BBC-4C95-4587-A815-9DA3C3A62ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4087,10 +4087,12 @@
     <sheetNames>
       <sheetName val="CdA Track Testing"/>
       <sheetName val="Data cut from table - to sort"/>
+      <sheetName val="Track CdA Aero Testing Database"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -81103,7 +81105,7 @@
         <v>120</v>
       </c>
       <c r="C722" s="138">
-        <v>45682</v>
+        <v>45316</v>
       </c>
       <c r="D722" s="107">
         <v>2</v>
@@ -81213,7 +81215,7 @@
         <v>120</v>
       </c>
       <c r="C723" s="138">
-        <v>46047</v>
+        <v>45316</v>
       </c>
       <c r="D723" s="107">
         <v>3</v>
@@ -81323,7 +81325,7 @@
         <v>120</v>
       </c>
       <c r="C724" s="138">
-        <v>46412</v>
+        <v>45316</v>
       </c>
       <c r="D724" s="107">
         <v>4</v>
@@ -81433,7 +81435,7 @@
         <v>120</v>
       </c>
       <c r="C725" s="138">
-        <v>46777</v>
+        <v>45316</v>
       </c>
       <c r="D725" s="107">
         <v>5</v>
@@ -81543,7 +81545,7 @@
         <v>120</v>
       </c>
       <c r="C726" s="138">
-        <v>47143</v>
+        <v>45316</v>
       </c>
       <c r="D726" s="107">
         <v>6</v>
@@ -81647,6 +81649,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004F1ECC6B2649324CB24C079D2C04510D" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="608b5d954c2eb0ac10393708da8d34af">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65551c38-962b-4cee-924d-ef2df1bb8b98" xmlns:ns3="ec750ee3-7d64-422f-9b1f-0ca7238893a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af171f03bd4cf151e3e856a6839c0cc7" ns2:_="" ns3:_="">
     <xsd:import namespace="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
@@ -81894,26 +81915,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -81930,29 +81957,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2005A6FD-C40E-4C73-84A6-084E6F0EF19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8C9AA3-F5FA-408A-A96D-9E26B17D9A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CdA Track Testing" sheetId="12" r:id="rId1"/>
@@ -2915,13 +2915,13 @@
     <t>https://youtu.be/sjySGA9TDtc</t>
   </si>
   <si>
-    <t>Skinsuit</t>
-  </si>
-  <si>
-    <t>Shoe Cover</t>
-  </si>
-  <si>
-    <t>Shoe</t>
+    <t>Clothing</t>
+  </si>
+  <si>
+    <t>Shoe cover</t>
+  </si>
+  <si>
+    <t>Shoes</t>
   </si>
 </sst>
 </file>
@@ -4087,12 +4087,10 @@
     <sheetNames>
       <sheetName val="CdA Track Testing"/>
       <sheetName val="Data cut from table - to sort"/>
-      <sheetName val="Track CdA Aero Testing Database"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4122,9 +4120,9 @@
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0400-000011000000}" name="Speed" dataDxfId="45"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Power" dataDxfId="44"/>
     <tableColumn id="22" xr3:uid="{00000000-0010-0000-0400-000016000000}" name="Distance (m)" dataDxfId="43"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Skinsuit" dataDxfId="42"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Shoe Cover" dataDxfId="41"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="Shoe" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Clothing" dataDxfId="42"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Shoe cover" dataDxfId="41"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="Shoes" dataDxfId="40"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0400-00001A000000}" name="Helmet" dataDxfId="39"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="Bike" dataDxfId="38"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="Wheels" dataDxfId="37"/>
@@ -81649,25 +81647,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004F1ECC6B2649324CB24C079D2C04510D" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="608b5d954c2eb0ac10393708da8d34af">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65551c38-962b-4cee-924d-ef2df1bb8b98" xmlns:ns3="ec750ee3-7d64-422f-9b1f-0ca7238893a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af171f03bd4cf151e3e856a6839c0cc7" ns2:_="" ns3:_="">
     <xsd:import namespace="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
@@ -81915,32 +81894,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -81957,4 +81930,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A343B16-F525-4B36-8AA0-9E7CB407AEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F13B545-A4CC-4402-8F44-F9DBDE7FC0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3433" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3433" uniqueCount="599">
   <si>
     <t>Squad</t>
   </si>
@@ -1806,9 +1806,6 @@
   </si>
   <si>
     <t>CdA - GM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Gate </t>
   </si>
   <si>
     <t>LeCol</t>
@@ -2034,7 +2031,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2218,43 +2215,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2658,16 +2630,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Track_TT23" displayName="Track_TT23" ref="A1:BH421" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60">
-  <autoFilter ref="A1:BH421" xr:uid="{00000000-0009-0000-0100-000002000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Aaron Gate"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BH421">
-    <sortCondition ref="C1:C421"/>
-  </sortState>
+  <autoFilter ref="A1:BH421" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="60">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Squad" dataDxfId="59"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Name" dataDxfId="58"/>
@@ -3203,7 +3166,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>43</v>
       </c>
@@ -3308,7 +3271,7 @@
       <c r="BH2" s="4"/>
       <c r="BM2"/>
     </row>
-    <row r="3" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>43</v>
       </c>
@@ -3416,7 +3379,7 @@
       <c r="BH3" s="4"/>
       <c r="BM3"/>
     </row>
-    <row r="4" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>43</v>
       </c>
@@ -3524,7 +3487,7 @@
       </c>
       <c r="BM4"/>
     </row>
-    <row r="5" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>43</v>
       </c>
@@ -3629,7 +3592,7 @@
       <c r="BH5" s="4"/>
       <c r="BM5"/>
     </row>
-    <row r="6" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>43</v>
       </c>
@@ -3725,7 +3688,7 @@
       <c r="BD6" s="14">
         <v>997</v>
       </c>
-      <c r="BE6" s="71">
+      <c r="BE6" s="58">
         <v>49</v>
       </c>
       <c r="BF6" s="15">
@@ -3737,7 +3700,7 @@
       <c r="BH6" s="4"/>
       <c r="BM6"/>
     </row>
-    <row r="7" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>43</v>
       </c>
@@ -3833,11 +3796,11 @@
       <c r="BD7" s="17">
         <v>997</v>
       </c>
-      <c r="BE7" s="68">
+      <c r="BE7" s="16">
         <v>48</v>
       </c>
       <c r="BF7" s="15"/>
-      <c r="BG7" s="74">
+      <c r="BG7" s="7">
         <v>2096</v>
       </c>
       <c r="BH7" s="13" t="s">
@@ -3845,7 +3808,7 @@
       </c>
       <c r="BM7"/>
     </row>
-    <row r="8" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>43</v>
       </c>
@@ -3953,7 +3916,7 @@
       <c r="BH8" s="4"/>
       <c r="BM8"/>
     </row>
-    <row r="9" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -4061,7 +4024,7 @@
       <c r="BH9" s="4"/>
       <c r="BM9"/>
     </row>
-    <row r="10" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
@@ -4166,7 +4129,7 @@
       </c>
       <c r="BM10"/>
     </row>
-    <row r="11" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>43</v>
       </c>
@@ -4262,7 +4225,7 @@
       <c r="BD11" s="14">
         <v>996</v>
       </c>
-      <c r="BE11" s="71">
+      <c r="BE11" s="58">
         <v>47</v>
       </c>
       <c r="BF11" s="15">
@@ -4274,7 +4237,7 @@
       <c r="BH11" s="4"/>
       <c r="BM11"/>
     </row>
-    <row r="12" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>43</v>
       </c>
@@ -4370,7 +4333,7 @@
       <c r="BD12" s="14">
         <v>996</v>
       </c>
-      <c r="BE12" s="71">
+      <c r="BE12" s="58">
         <v>47</v>
       </c>
       <c r="BF12" s="15">
@@ -4382,7 +4345,7 @@
       <c r="BH12" s="4"/>
       <c r="BM12"/>
     </row>
-    <row r="13" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>43</v>
       </c>
@@ -4475,11 +4438,11 @@
       <c r="BD13" s="17">
         <v>997</v>
       </c>
-      <c r="BE13" s="68">
+      <c r="BE13" s="16">
         <v>47</v>
       </c>
       <c r="BF13" s="15"/>
-      <c r="BG13" s="74">
+      <c r="BG13" s="7">
         <v>2096</v>
       </c>
       <c r="BH13" s="13" t="s">
@@ -4487,7 +4450,7 @@
       </c>
       <c r="BM13"/>
     </row>
-    <row r="14" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>43</v>
       </c>
@@ -4581,19 +4544,19 @@
       <c r="BD14" s="14">
         <v>995</v>
       </c>
-      <c r="BE14" s="71">
+      <c r="BE14" s="58">
         <v>47</v>
       </c>
       <c r="BF14" s="15">
         <v>1.157</v>
       </c>
-      <c r="BG14" s="74">
+      <c r="BG14" s="7">
         <v>2096</v>
       </c>
       <c r="BH14" s="4"/>
       <c r="BM14"/>
     </row>
-    <row r="15" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>43</v>
       </c>
@@ -4687,19 +4650,19 @@
       <c r="BD15" s="14">
         <v>996</v>
       </c>
-      <c r="BE15" s="71">
+      <c r="BE15" s="58">
         <v>47</v>
       </c>
       <c r="BF15" s="15">
         <v>1.157</v>
       </c>
-      <c r="BG15" s="74">
+      <c r="BG15" s="7">
         <v>2096</v>
       </c>
       <c r="BH15" s="4"/>
       <c r="BM15"/>
     </row>
-    <row r="16" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>43</v>
       </c>
@@ -4793,11 +4756,11 @@
       <c r="BD16" s="17">
         <v>997</v>
       </c>
-      <c r="BE16" s="68">
+      <c r="BE16" s="16">
         <v>45</v>
       </c>
       <c r="BF16" s="15"/>
-      <c r="BG16" s="74">
+      <c r="BG16" s="7">
         <v>2096</v>
       </c>
       <c r="BH16" s="13" t="s">
@@ -4805,7 +4768,7 @@
       </c>
       <c r="BM16"/>
     </row>
-    <row r="17" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>43</v>
       </c>
@@ -4899,19 +4862,19 @@
       <c r="BD17" s="14">
         <v>995</v>
       </c>
-      <c r="BE17" s="71">
+      <c r="BE17" s="58">
         <v>47</v>
       </c>
       <c r="BF17" s="15">
         <v>1.157</v>
       </c>
-      <c r="BG17" s="74">
+      <c r="BG17" s="7">
         <v>2096</v>
       </c>
       <c r="BH17" s="4"/>
       <c r="BM17"/>
     </row>
-    <row r="18" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>43</v>
       </c>
@@ -4994,7 +4957,7 @@
       <c r="AY18" s="7">
         <v>200</v>
       </c>
-      <c r="AZ18" s="66">
+      <c r="AZ18" s="4">
         <v>111.4</v>
       </c>
       <c r="BA18" s="4"/>
@@ -5005,19 +4968,19 @@
       <c r="BD18" s="14">
         <v>995</v>
       </c>
-      <c r="BE18" s="71">
+      <c r="BE18" s="58">
         <v>47</v>
       </c>
       <c r="BF18" s="15">
         <v>1.1579999999999999</v>
       </c>
-      <c r="BG18" s="74">
+      <c r="BG18" s="7">
         <v>2096</v>
       </c>
       <c r="BH18" s="4"/>
       <c r="BM18"/>
     </row>
-    <row r="19" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>43</v>
       </c>
@@ -5111,11 +5074,11 @@
       <c r="BD19" s="17">
         <v>997</v>
       </c>
-      <c r="BE19" s="68">
+      <c r="BE19" s="16">
         <v>45</v>
       </c>
       <c r="BF19" s="15"/>
-      <c r="BG19" s="74">
+      <c r="BG19" s="7">
         <v>2096</v>
       </c>
       <c r="BH19" s="13" t="s">
@@ -5123,7 +5086,7 @@
       </c>
       <c r="BM19"/>
     </row>
-    <row r="20" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>43</v>
       </c>
@@ -5218,15 +5181,15 @@
       <c r="BD20" s="19">
         <v>1013</v>
       </c>
-      <c r="BE20" s="67">
+      <c r="BE20" s="18">
         <v>52.4</v>
       </c>
       <c r="BF20" s="20"/>
-      <c r="BG20" s="66"/>
+      <c r="BG20" s="4"/>
       <c r="BH20" s="4"/>
       <c r="BM20"/>
     </row>
-    <row r="21" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>43</v>
       </c>
@@ -5321,7 +5284,7 @@
       <c r="BD21" s="19">
         <v>1013</v>
       </c>
-      <c r="BE21" s="67">
+      <c r="BE21" s="18">
         <v>52.4</v>
       </c>
       <c r="BF21" s="20"/>
@@ -5329,7 +5292,7 @@
       <c r="BH21" s="4"/>
       <c r="BM21"/>
     </row>
-    <row r="22" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>43</v>
       </c>
@@ -5422,15 +5385,15 @@
       <c r="BD22" s="17">
         <v>1013</v>
       </c>
-      <c r="BE22" s="68">
+      <c r="BE22" s="16">
         <v>52.4</v>
       </c>
       <c r="BF22" s="15"/>
-      <c r="BG22" s="66"/>
+      <c r="BG22" s="4"/>
       <c r="BH22" s="4"/>
       <c r="BM22"/>
     </row>
-    <row r="23" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>43</v>
       </c>
@@ -5525,15 +5488,15 @@
       <c r="BD23" s="19">
         <v>1013</v>
       </c>
-      <c r="BE23" s="67">
+      <c r="BE23" s="18">
         <v>52.4</v>
       </c>
       <c r="BF23" s="20"/>
-      <c r="BG23" s="66"/>
+      <c r="BG23" s="4"/>
       <c r="BH23" s="4"/>
       <c r="BM23"/>
     </row>
-    <row r="24" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>43</v>
       </c>
@@ -5628,15 +5591,15 @@
       <c r="BD24" s="19">
         <v>1013</v>
       </c>
-      <c r="BE24" s="67">
+      <c r="BE24" s="18">
         <v>52.4</v>
       </c>
       <c r="BF24" s="20"/>
-      <c r="BG24" s="66"/>
+      <c r="BG24" s="4"/>
       <c r="BH24" s="4"/>
       <c r="BM24"/>
     </row>
-    <row r="25" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>43</v>
       </c>
@@ -5729,15 +5692,15 @@
       <c r="BD25" s="17">
         <v>1013</v>
       </c>
-      <c r="BE25" s="68">
+      <c r="BE25" s="16">
         <v>52.4</v>
       </c>
       <c r="BF25" s="15"/>
-      <c r="BG25" s="66"/>
+      <c r="BG25" s="4"/>
       <c r="BH25" s="4"/>
       <c r="BM25"/>
     </row>
-    <row r="26" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>43</v>
       </c>
@@ -5835,7 +5798,7 @@
       <c r="BD26" s="19">
         <v>1012</v>
       </c>
-      <c r="BE26" s="67">
+      <c r="BE26" s="18">
         <v>52.5</v>
       </c>
       <c r="BF26" s="20"/>
@@ -5843,7 +5806,7 @@
       <c r="BH26" s="4"/>
       <c r="BM26"/>
     </row>
-    <row r="27" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>43</v>
       </c>
@@ -5949,7 +5912,7 @@
       <c r="BH27" s="4"/>
       <c r="BM27"/>
     </row>
-    <row r="28" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>43</v>
       </c>
@@ -6045,15 +6008,15 @@
       <c r="BD28" s="17">
         <v>1012</v>
       </c>
-      <c r="BE28" s="68">
+      <c r="BE28" s="16">
         <v>52.5</v>
       </c>
       <c r="BF28" s="15"/>
-      <c r="BG28" s="66"/>
+      <c r="BG28" s="4"/>
       <c r="BH28" s="4"/>
       <c r="BM28"/>
     </row>
-    <row r="29" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
@@ -6148,18 +6111,18 @@
       <c r="BC29" s="18">
         <v>25.4</v>
       </c>
-      <c r="BD29" s="67">
+      <c r="BD29" s="18">
         <v>1012</v>
       </c>
-      <c r="BE29" s="67">
+      <c r="BE29" s="18">
         <v>52.9</v>
       </c>
-      <c r="BF29" s="66"/>
+      <c r="BF29" s="4"/>
       <c r="BG29" s="4"/>
       <c r="BH29" s="4"/>
       <c r="BM29"/>
     </row>
-    <row r="30" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>43</v>
       </c>
@@ -6254,18 +6217,18 @@
       <c r="BC30" s="18">
         <v>25.4</v>
       </c>
-      <c r="BD30" s="67">
+      <c r="BD30" s="18">
         <v>1012</v>
       </c>
-      <c r="BE30" s="67">
+      <c r="BE30" s="18">
         <v>52.9</v>
       </c>
-      <c r="BF30" s="66"/>
+      <c r="BF30" s="4"/>
       <c r="BG30" s="4"/>
       <c r="BH30" s="4"/>
       <c r="BM30"/>
     </row>
-    <row r="31" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>43</v>
       </c>
@@ -6358,18 +6321,18 @@
       <c r="BC31" s="16">
         <v>25.4</v>
       </c>
-      <c r="BD31" s="68">
+      <c r="BD31" s="16">
         <v>1012</v>
       </c>
-      <c r="BE31" s="68">
+      <c r="BE31" s="16">
         <v>52.9</v>
       </c>
-      <c r="BF31" s="69"/>
-      <c r="BG31" s="66"/>
+      <c r="BF31" s="64"/>
+      <c r="BG31" s="4"/>
       <c r="BH31" s="4"/>
       <c r="BM31"/>
     </row>
-    <row r="32" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>13</v>
       </c>
@@ -6459,18 +6422,18 @@
       <c r="BC32" s="18">
         <v>25.8</v>
       </c>
-      <c r="BD32" s="67">
+      <c r="BD32" s="18">
         <v>1012</v>
       </c>
-      <c r="BE32" s="67">
+      <c r="BE32" s="18">
         <v>51.8</v>
       </c>
-      <c r="BF32" s="66"/>
-      <c r="BG32" s="66"/>
+      <c r="BF32" s="4"/>
+      <c r="BG32" s="4"/>
       <c r="BH32" s="4"/>
       <c r="BM32"/>
     </row>
-    <row r="33" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>13</v>
       </c>
@@ -6563,18 +6526,18 @@
       <c r="BC33" s="18">
         <v>25.8</v>
       </c>
-      <c r="BD33" s="67">
+      <c r="BD33" s="18">
         <v>1012</v>
       </c>
-      <c r="BE33" s="67">
+      <c r="BE33" s="18">
         <v>51.8</v>
       </c>
-      <c r="BF33" s="66"/>
-      <c r="BG33" s="66"/>
+      <c r="BF33" s="4"/>
+      <c r="BG33" s="4"/>
       <c r="BH33" s="4"/>
       <c r="BM33"/>
     </row>
-    <row r="34" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>13</v>
       </c>
@@ -6662,20 +6625,20 @@
       <c r="BC34" s="16">
         <v>25.8</v>
       </c>
-      <c r="BD34" s="68">
+      <c r="BD34" s="16">
         <v>1012</v>
       </c>
-      <c r="BE34" s="68">
+      <c r="BE34" s="16">
         <v>51.8</v>
       </c>
-      <c r="BF34" s="69"/>
-      <c r="BG34" s="66"/>
+      <c r="BF34" s="64"/>
+      <c r="BG34" s="4"/>
       <c r="BH34" s="13" t="s">
         <v>87</v>
       </c>
       <c r="BM34"/>
     </row>
-    <row r="35" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>13</v>
       </c>
@@ -6768,18 +6731,18 @@
       <c r="BC35" s="18">
         <v>26.3</v>
       </c>
-      <c r="BD35" s="67">
+      <c r="BD35" s="18">
         <v>1012</v>
       </c>
-      <c r="BE35" s="67">
+      <c r="BE35" s="18">
         <v>51.3</v>
       </c>
-      <c r="BF35" s="66"/>
+      <c r="BF35" s="4"/>
       <c r="BG35" s="7"/>
       <c r="BH35" s="4"/>
       <c r="BM35"/>
     </row>
-    <row r="36" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>13</v>
       </c>
@@ -6872,18 +6835,18 @@
       <c r="BC36" s="18">
         <v>26.3</v>
       </c>
-      <c r="BD36" s="67">
+      <c r="BD36" s="18">
         <v>1012</v>
       </c>
-      <c r="BE36" s="67">
+      <c r="BE36" s="18">
         <v>51.3</v>
       </c>
-      <c r="BF36" s="66"/>
-      <c r="BG36" s="66"/>
+      <c r="BF36" s="4"/>
+      <c r="BG36" s="4"/>
       <c r="BH36" s="4"/>
       <c r="BM36"/>
     </row>
-    <row r="37" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>13</v>
       </c>
@@ -6971,18 +6934,18 @@
       <c r="BC37" s="16">
         <v>26.3</v>
       </c>
-      <c r="BD37" s="68">
+      <c r="BD37" s="16">
         <v>1012</v>
       </c>
-      <c r="BE37" s="68">
+      <c r="BE37" s="16">
         <v>51.3</v>
       </c>
-      <c r="BF37" s="69"/>
-      <c r="BG37" s="66"/>
+      <c r="BF37" s="64"/>
+      <c r="BG37" s="4"/>
       <c r="BH37" s="4"/>
       <c r="BM37"/>
     </row>
-    <row r="38" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>43</v>
       </c>
@@ -7070,19 +7033,19 @@
       <c r="BC38" s="18">
         <v>24.8</v>
       </c>
-      <c r="BD38" s="67">
+      <c r="BD38" s="18">
         <v>1012</v>
       </c>
       <c r="BE38" s="18">
         <v>53.5</v>
       </c>
-      <c r="BF38" s="66"/>
+      <c r="BF38" s="4"/>
       <c r="BG38" s="4"/>
       <c r="BH38" s="4"/>
       <c r="BI38" s="7"/>
       <c r="BM38"/>
     </row>
-    <row r="39" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>43</v>
       </c>
@@ -7170,21 +7133,21 @@
       <c r="BC39" s="4">
         <v>25</v>
       </c>
-      <c r="BD39" s="69">
+      <c r="BD39" s="64">
         <v>1012</v>
       </c>
-      <c r="BE39" s="71">
+      <c r="BE39" s="58">
         <v>53</v>
       </c>
-      <c r="BF39" s="69">
+      <c r="BF39" s="64">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BG39" s="66"/>
+      <c r="BG39" s="4"/>
       <c r="BH39" s="4"/>
       <c r="BI39" s="7"/>
       <c r="BM39"/>
     </row>
-    <row r="40" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>43</v>
       </c>
@@ -7272,19 +7235,19 @@
       <c r="BC40" s="18">
         <v>24.8</v>
       </c>
-      <c r="BD40" s="67">
+      <c r="BD40" s="18">
         <v>1012</v>
       </c>
       <c r="BE40" s="18">
         <v>53.5</v>
       </c>
-      <c r="BF40" s="66"/>
+      <c r="BF40" s="4"/>
       <c r="BG40" s="4"/>
       <c r="BH40" s="4"/>
       <c r="BI40" s="7"/>
       <c r="BM40"/>
     </row>
-    <row r="41" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>43</v>
       </c>
@@ -7375,18 +7338,18 @@
       <c r="BD41" s="14">
         <v>1012</v>
       </c>
-      <c r="BE41" s="71">
+      <c r="BE41" s="58">
         <v>54</v>
       </c>
       <c r="BF41" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BG41" s="66"/>
+      <c r="BG41" s="4"/>
       <c r="BH41" s="4"/>
       <c r="BI41" s="7"/>
       <c r="BM41"/>
     </row>
-    <row r="42" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>43</v>
       </c>
@@ -7466,7 +7429,7 @@
       <c r="AY42" s="7">
         <v>200</v>
       </c>
-      <c r="AZ42" s="66">
+      <c r="AZ42" s="4">
         <v>111.6</v>
       </c>
       <c r="BA42" s="4"/>
@@ -7477,16 +7440,16 @@
       <c r="BD42" s="19">
         <v>1012</v>
       </c>
-      <c r="BE42" s="67">
+      <c r="BE42" s="18">
         <v>53</v>
       </c>
       <c r="BF42" s="21"/>
-      <c r="BG42" s="66"/>
+      <c r="BG42" s="4"/>
       <c r="BH42" s="4"/>
       <c r="BI42" s="7"/>
       <c r="BM42"/>
     </row>
-    <row r="43" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>43</v>
       </c>
@@ -7577,18 +7540,18 @@
       <c r="BD43" s="14">
         <v>1012</v>
       </c>
-      <c r="BE43" s="71">
+      <c r="BE43" s="58">
         <v>53</v>
       </c>
       <c r="BF43" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BG43" s="66"/>
+      <c r="BG43" s="4"/>
       <c r="BH43" s="4"/>
       <c r="BI43" s="7"/>
       <c r="BM43"/>
     </row>
-    <row r="44" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>13</v>
       </c>
@@ -7686,7 +7649,7 @@
       <c r="BI44" s="7"/>
       <c r="BM44"/>
     </row>
-    <row r="45" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>13</v>
       </c>
@@ -7775,18 +7738,18 @@
       <c r="BD45" s="14">
         <v>1012</v>
       </c>
-      <c r="BE45" s="71">
+      <c r="BE45" s="58">
         <v>53</v>
       </c>
       <c r="BF45" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BG45" s="66"/>
+      <c r="BG45" s="4"/>
       <c r="BH45" s="4"/>
       <c r="BI45" s="7"/>
       <c r="BM45"/>
     </row>
-    <row r="46" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>13</v>
       </c>
@@ -7875,7 +7838,7 @@
       <c r="BD46" s="19">
         <v>1012</v>
       </c>
-      <c r="BE46" s="67">
+      <c r="BE46" s="18">
         <v>53</v>
       </c>
       <c r="BF46" s="21"/>
@@ -7884,7 +7847,7 @@
       <c r="BI46" s="7"/>
       <c r="BM46"/>
     </row>
-    <row r="47" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>13</v>
       </c>
@@ -7984,7 +7947,7 @@
       <c r="BI47" s="7"/>
       <c r="BM47"/>
     </row>
-    <row r="48" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>13</v>
       </c>
@@ -8073,7 +8036,7 @@
       <c r="BD48" s="19">
         <v>1012</v>
       </c>
-      <c r="BE48" s="67">
+      <c r="BE48" s="18">
         <v>53</v>
       </c>
       <c r="BF48" s="21"/>
@@ -8082,7 +8045,7 @@
       <c r="BI48" s="7"/>
       <c r="BM48"/>
     </row>
-    <row r="49" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>13</v>
       </c>
@@ -8171,18 +8134,18 @@
       <c r="BD49" s="14">
         <v>1012</v>
       </c>
-      <c r="BE49" s="71">
+      <c r="BE49" s="58">
         <v>54</v>
       </c>
       <c r="BF49" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BG49" s="66"/>
+      <c r="BG49" s="4"/>
       <c r="BH49" s="4"/>
       <c r="BI49" s="7"/>
       <c r="BM49"/>
     </row>
-    <row r="50" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>43</v>
       </c>
@@ -8270,19 +8233,19 @@
       <c r="BC50" s="18">
         <v>25.1</v>
       </c>
-      <c r="BD50" s="67">
+      <c r="BD50" s="18">
         <v>1011</v>
       </c>
       <c r="BE50" s="18">
         <v>54.2</v>
       </c>
-      <c r="BF50" s="73"/>
+      <c r="BF50" s="66"/>
       <c r="BG50" s="4"/>
       <c r="BH50" s="4"/>
       <c r="BI50" s="7"/>
       <c r="BM50"/>
     </row>
-    <row r="51" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>43</v>
       </c>
@@ -8370,13 +8333,13 @@
       <c r="BC51" s="4">
         <v>25.1</v>
       </c>
-      <c r="BD51" s="69">
+      <c r="BD51" s="64">
         <v>1011</v>
       </c>
-      <c r="BE51" s="71">
+      <c r="BE51" s="58">
         <v>54</v>
       </c>
-      <c r="BF51" s="69">
+      <c r="BF51" s="64">
         <v>1.173</v>
       </c>
       <c r="BG51" s="4"/>
@@ -8384,7 +8347,7 @@
       <c r="BI51" s="7"/>
       <c r="BM51"/>
     </row>
-    <row r="52" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>43</v>
       </c>
@@ -8472,19 +8435,19 @@
       <c r="BC52" s="18">
         <v>25.1</v>
       </c>
-      <c r="BD52" s="67">
+      <c r="BD52" s="18">
         <v>1011</v>
       </c>
       <c r="BE52" s="18">
         <v>54.2</v>
       </c>
-      <c r="BF52" s="73"/>
+      <c r="BF52" s="66"/>
       <c r="BG52" s="4"/>
       <c r="BH52" s="4"/>
       <c r="BI52" s="7"/>
       <c r="BM52"/>
     </row>
-    <row r="53" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>43</v>
       </c>
@@ -8572,13 +8535,13 @@
       <c r="BC53" s="4">
         <v>25.2</v>
       </c>
-      <c r="BD53" s="69">
+      <c r="BD53" s="64">
         <v>1011</v>
       </c>
-      <c r="BE53" s="71">
+      <c r="BE53" s="58">
         <v>54</v>
       </c>
-      <c r="BF53" s="69">
+      <c r="BF53" s="64">
         <v>1.173</v>
       </c>
       <c r="BG53" s="4"/>
@@ -8586,7 +8549,7 @@
       <c r="BI53" s="7"/>
       <c r="BM53"/>
     </row>
-    <row r="54" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>43</v>
       </c>
@@ -8674,19 +8637,19 @@
       <c r="BC54" s="18">
         <v>25.1</v>
       </c>
-      <c r="BD54" s="67">
+      <c r="BD54" s="18">
         <v>1011</v>
       </c>
-      <c r="BE54" s="67">
+      <c r="BE54" s="18">
         <v>54.2</v>
       </c>
-      <c r="BF54" s="73"/>
+      <c r="BF54" s="66"/>
       <c r="BG54" s="4"/>
       <c r="BH54" s="4"/>
       <c r="BI54" s="7"/>
       <c r="BM54"/>
     </row>
-    <row r="55" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>43</v>
       </c>
@@ -8774,21 +8737,21 @@
       <c r="BC55" s="4">
         <v>25.2</v>
       </c>
-      <c r="BD55" s="69">
+      <c r="BD55" s="64">
         <v>1011</v>
       </c>
-      <c r="BE55" s="71">
+      <c r="BE55" s="58">
         <v>54</v>
       </c>
-      <c r="BF55" s="69">
+      <c r="BF55" s="64">
         <v>1.173</v>
       </c>
-      <c r="BG55" s="66"/>
+      <c r="BG55" s="4"/>
       <c r="BH55" s="4"/>
       <c r="BI55" s="7"/>
       <c r="BM55"/>
     </row>
-    <row r="56" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>13</v>
       </c>
@@ -8874,19 +8837,19 @@
       <c r="BC56" s="18">
         <v>25.2</v>
       </c>
-      <c r="BD56" s="67">
+      <c r="BD56" s="18">
         <v>1005</v>
       </c>
-      <c r="BE56" s="67">
+      <c r="BE56" s="18">
         <v>41</v>
       </c>
-      <c r="BF56" s="73"/>
-      <c r="BG56" s="66"/>
+      <c r="BF56" s="66"/>
+      <c r="BG56" s="4"/>
       <c r="BH56" s="4"/>
       <c r="BI56" s="7"/>
       <c r="BM56"/>
     </row>
-    <row r="57" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>13</v>
       </c>
@@ -8972,19 +8935,19 @@
       <c r="BC57" s="18">
         <v>25.2</v>
       </c>
-      <c r="BD57" s="67">
+      <c r="BD57" s="18">
         <v>1005</v>
       </c>
-      <c r="BE57" s="67">
+      <c r="BE57" s="18">
         <v>41</v>
       </c>
-      <c r="BF57" s="73"/>
-      <c r="BG57" s="66"/>
+      <c r="BF57" s="66"/>
+      <c r="BG57" s="4"/>
       <c r="BH57" s="4"/>
       <c r="BI57" s="7"/>
       <c r="BM57"/>
     </row>
-    <row r="58" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>13</v>
       </c>
@@ -9070,21 +9033,21 @@
       <c r="BC58" s="18">
         <v>25.2</v>
       </c>
-      <c r="BD58" s="67">
+      <c r="BD58" s="18">
         <v>1005</v>
       </c>
-      <c r="BE58" s="67">
+      <c r="BE58" s="18">
         <v>41</v>
       </c>
-      <c r="BF58" s="73"/>
-      <c r="BG58" s="66"/>
+      <c r="BF58" s="66"/>
+      <c r="BG58" s="4"/>
       <c r="BH58" s="11" t="s">
         <v>88</v>
       </c>
       <c r="BI58" s="7"/>
       <c r="BM58"/>
     </row>
-    <row r="59" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>13</v>
       </c>
@@ -9170,19 +9133,19 @@
       <c r="BC59" s="16">
         <v>25.2</v>
       </c>
-      <c r="BD59" s="68">
+      <c r="BD59" s="16">
         <v>1005</v>
       </c>
-      <c r="BE59" s="68">
+      <c r="BE59" s="16">
         <v>41</v>
       </c>
-      <c r="BF59" s="66"/>
-      <c r="BG59" s="66"/>
+      <c r="BF59" s="4"/>
+      <c r="BG59" s="4"/>
       <c r="BH59" s="4"/>
       <c r="BI59" s="7"/>
       <c r="BM59"/>
     </row>
-    <row r="60" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>13</v>
       </c>
@@ -9268,19 +9231,19 @@
       <c r="BC60" s="18">
         <v>25.2</v>
       </c>
-      <c r="BD60" s="67">
+      <c r="BD60" s="18">
         <v>1005</v>
       </c>
-      <c r="BE60" s="67">
+      <c r="BE60" s="18">
         <v>41</v>
       </c>
-      <c r="BF60" s="73"/>
-      <c r="BG60" s="66"/>
+      <c r="BF60" s="66"/>
+      <c r="BG60" s="4"/>
       <c r="BH60" s="4"/>
       <c r="BI60" s="7"/>
       <c r="BM60"/>
     </row>
-    <row r="61" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>13</v>
       </c>
@@ -9358,7 +9321,7 @@
       <c r="AY61" s="7">
         <v>200</v>
       </c>
-      <c r="AZ61" s="65">
+      <c r="AZ61" s="22">
         <v>117</v>
       </c>
       <c r="BA61" s="4"/>
@@ -9366,19 +9329,19 @@
       <c r="BC61" s="18">
         <v>25.2</v>
       </c>
-      <c r="BD61" s="67">
+      <c r="BD61" s="18">
         <v>1005</v>
       </c>
-      <c r="BE61" s="67">
+      <c r="BE61" s="18">
         <v>41</v>
       </c>
-      <c r="BF61" s="73"/>
-      <c r="BG61" s="66"/>
+      <c r="BF61" s="66"/>
+      <c r="BG61" s="4"/>
       <c r="BH61" s="4"/>
       <c r="BI61" s="7"/>
       <c r="BM61"/>
     </row>
-    <row r="62" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>43</v>
       </c>
@@ -9474,18 +9437,18 @@
       <c r="BC62" s="18">
         <v>25.2</v>
       </c>
-      <c r="BD62" s="67">
+      <c r="BD62" s="18">
         <v>1005</v>
       </c>
-      <c r="BE62" s="67">
+      <c r="BE62" s="18">
         <v>41</v>
       </c>
-      <c r="BF62" s="73"/>
-      <c r="BG62" s="66"/>
+      <c r="BF62" s="66"/>
+      <c r="BG62" s="4"/>
       <c r="BH62" s="4"/>
       <c r="BM62"/>
     </row>
-    <row r="63" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>43</v>
       </c>
@@ -9581,18 +9544,18 @@
       <c r="BC63" s="16">
         <v>25.2</v>
       </c>
-      <c r="BD63" s="68">
+      <c r="BD63" s="16">
         <v>1005</v>
       </c>
-      <c r="BE63" s="68">
+      <c r="BE63" s="16">
         <v>41</v>
       </c>
-      <c r="BF63" s="66"/>
+      <c r="BF63" s="4"/>
       <c r="BG63" s="4"/>
       <c r="BH63" s="4"/>
       <c r="BM63"/>
     </row>
-    <row r="64" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>43</v>
       </c>
@@ -9679,18 +9642,18 @@
       <c r="BC64" s="18">
         <v>25.2</v>
       </c>
-      <c r="BD64" s="67">
+      <c r="BD64" s="18">
         <v>1005</v>
       </c>
-      <c r="BE64" s="67">
+      <c r="BE64" s="18">
         <v>41</v>
       </c>
-      <c r="BF64" s="73"/>
+      <c r="BF64" s="66"/>
       <c r="BG64" s="4"/>
       <c r="BH64" s="4"/>
       <c r="BM64"/>
     </row>
-    <row r="65" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>43</v>
       </c>
@@ -9786,18 +9749,18 @@
       <c r="BC65" s="18">
         <v>25.2</v>
       </c>
-      <c r="BD65" s="67">
+      <c r="BD65" s="18">
         <v>1005</v>
       </c>
-      <c r="BE65" s="67">
+      <c r="BE65" s="18">
         <v>41</v>
       </c>
-      <c r="BF65" s="73"/>
-      <c r="BG65" s="66"/>
+      <c r="BF65" s="66"/>
+      <c r="BG65" s="4"/>
       <c r="BH65" s="4"/>
       <c r="BM65"/>
     </row>
-    <row r="66" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>43</v>
       </c>
@@ -9893,18 +9856,18 @@
       <c r="BC66" s="18">
         <v>25.2</v>
       </c>
-      <c r="BD66" s="67">
+      <c r="BD66" s="18">
         <v>1005</v>
       </c>
-      <c r="BE66" s="67">
+      <c r="BE66" s="18">
         <v>41</v>
       </c>
-      <c r="BF66" s="73"/>
+      <c r="BF66" s="66"/>
       <c r="BG66" s="4"/>
       <c r="BH66" s="4"/>
       <c r="BM66"/>
     </row>
-    <row r="67" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>43</v>
       </c>
@@ -10000,18 +9963,18 @@
       <c r="BC67" s="16">
         <v>25.2</v>
       </c>
-      <c r="BD67" s="68">
+      <c r="BD67" s="16">
         <v>1005</v>
       </c>
-      <c r="BE67" s="68">
+      <c r="BE67" s="16">
         <v>41</v>
       </c>
-      <c r="BF67" s="66"/>
-      <c r="BG67" s="66"/>
+      <c r="BF67" s="4"/>
+      <c r="BG67" s="4"/>
       <c r="BH67" s="4"/>
       <c r="BM67"/>
     </row>
-    <row r="68" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>13</v>
       </c>
@@ -10099,7 +10062,7 @@
       <c r="AY68" s="7">
         <v>200</v>
       </c>
-      <c r="AZ68" s="66">
+      <c r="AZ68" s="4">
         <v>111.6</v>
       </c>
       <c r="BA68" s="4"/>
@@ -10107,18 +10070,18 @@
       <c r="BC68" s="18">
         <v>25.2</v>
       </c>
-      <c r="BD68" s="67">
+      <c r="BD68" s="18">
         <v>1005</v>
       </c>
-      <c r="BE68" s="67">
+      <c r="BE68" s="18">
         <v>41</v>
       </c>
-      <c r="BF68" s="73"/>
-      <c r="BG68" s="66"/>
+      <c r="BF68" s="66"/>
+      <c r="BG68" s="4"/>
       <c r="BH68" s="4"/>
       <c r="BM68"/>
     </row>
-    <row r="69" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>13</v>
       </c>
@@ -10210,18 +10173,18 @@
       <c r="BC69" s="18">
         <v>25.2</v>
       </c>
-      <c r="BD69" s="67">
+      <c r="BD69" s="18">
         <v>1005</v>
       </c>
-      <c r="BE69" s="67">
+      <c r="BE69" s="18">
         <v>41</v>
       </c>
-      <c r="BF69" s="73"/>
-      <c r="BG69" s="66"/>
+      <c r="BF69" s="66"/>
+      <c r="BG69" s="4"/>
       <c r="BH69" s="4"/>
       <c r="BM69"/>
     </row>
-    <row r="70" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>13</v>
       </c>
@@ -10317,18 +10280,18 @@
       <c r="BC70" s="18">
         <v>25.2</v>
       </c>
-      <c r="BD70" s="67">
+      <c r="BD70" s="18">
         <v>1005</v>
       </c>
-      <c r="BE70" s="67">
+      <c r="BE70" s="18">
         <v>41</v>
       </c>
-      <c r="BF70" s="73"/>
-      <c r="BG70" s="66"/>
+      <c r="BF70" s="66"/>
+      <c r="BG70" s="4"/>
       <c r="BH70" s="4"/>
       <c r="BM70"/>
     </row>
-    <row r="71" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>13</v>
       </c>
@@ -10424,18 +10387,18 @@
       <c r="BC71" s="16">
         <v>25.2</v>
       </c>
-      <c r="BD71" s="68">
+      <c r="BD71" s="16">
         <v>1005</v>
       </c>
-      <c r="BE71" s="68">
+      <c r="BE71" s="16">
         <v>41</v>
       </c>
-      <c r="BF71" s="66"/>
+      <c r="BF71" s="4"/>
       <c r="BG71" s="4"/>
       <c r="BH71" s="4"/>
       <c r="BM71"/>
     </row>
-    <row r="72" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>13</v>
       </c>
@@ -10531,18 +10494,18 @@
       <c r="BC72" s="18">
         <v>25.2</v>
       </c>
-      <c r="BD72" s="67">
+      <c r="BD72" s="18">
         <v>1005</v>
       </c>
-      <c r="BE72" s="67">
+      <c r="BE72" s="18">
         <v>41</v>
       </c>
-      <c r="BF72" s="73"/>
-      <c r="BG72" s="66"/>
+      <c r="BF72" s="66"/>
+      <c r="BG72" s="4"/>
       <c r="BH72" s="4"/>
       <c r="BM72"/>
     </row>
-    <row r="73" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>13</v>
       </c>
@@ -10638,18 +10601,18 @@
       <c r="BC73" s="18">
         <v>25.2</v>
       </c>
-      <c r="BD73" s="67">
+      <c r="BD73" s="18">
         <v>1005</v>
       </c>
-      <c r="BE73" s="67">
+      <c r="BE73" s="18">
         <v>41</v>
       </c>
-      <c r="BF73" s="73"/>
-      <c r="BG73" s="66"/>
+      <c r="BF73" s="66"/>
+      <c r="BG73" s="4"/>
       <c r="BH73" s="4"/>
       <c r="BM73"/>
     </row>
-    <row r="74" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>43</v>
       </c>
@@ -10743,18 +10706,18 @@
       <c r="BC74" s="18">
         <v>25.1</v>
       </c>
-      <c r="BD74" s="67">
+      <c r="BD74" s="18">
         <v>1010</v>
       </c>
-      <c r="BE74" s="67">
+      <c r="BE74" s="18">
         <v>47.7</v>
       </c>
-      <c r="BF74" s="66"/>
+      <c r="BF74" s="4"/>
       <c r="BG74" s="4"/>
       <c r="BH74" s="4"/>
       <c r="BM74"/>
     </row>
-    <row r="75" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>43</v>
       </c>
@@ -10848,18 +10811,18 @@
       <c r="BC75" s="18">
         <v>25.1</v>
       </c>
-      <c r="BD75" s="67">
+      <c r="BD75" s="18">
         <v>1010</v>
       </c>
-      <c r="BE75" s="67">
+      <c r="BE75" s="18">
         <v>47.7</v>
       </c>
-      <c r="BF75" s="66"/>
-      <c r="BG75" s="66"/>
+      <c r="BF75" s="4"/>
+      <c r="BG75" s="4"/>
       <c r="BH75" s="4"/>
       <c r="BM75"/>
     </row>
-    <row r="76" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>43</v>
       </c>
@@ -10953,18 +10916,18 @@
       <c r="BC76" s="18">
         <v>25.1</v>
       </c>
-      <c r="BD76" s="67">
+      <c r="BD76" s="18">
         <v>1010</v>
       </c>
-      <c r="BE76" s="67">
+      <c r="BE76" s="18">
         <v>47.7</v>
       </c>
-      <c r="BF76" s="66"/>
+      <c r="BF76" s="4"/>
       <c r="BG76" s="4"/>
       <c r="BH76" s="4"/>
       <c r="BM76"/>
     </row>
-    <row r="77" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>43</v>
       </c>
@@ -11058,18 +11021,18 @@
       <c r="BC77" s="18">
         <v>25.1</v>
       </c>
-      <c r="BD77" s="67">
+      <c r="BD77" s="18">
         <v>1010</v>
       </c>
-      <c r="BE77" s="67">
+      <c r="BE77" s="18">
         <v>47.7</v>
       </c>
-      <c r="BF77" s="73"/>
+      <c r="BF77" s="66"/>
       <c r="BG77" s="4"/>
       <c r="BH77" s="4"/>
       <c r="BM77"/>
     </row>
-    <row r="78" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>43</v>
       </c>
@@ -11163,18 +11126,18 @@
       <c r="BC78" s="18">
         <v>25.9</v>
       </c>
-      <c r="BD78" s="67">
+      <c r="BD78" s="18">
         <v>1010</v>
       </c>
-      <c r="BE78" s="67">
+      <c r="BE78" s="18">
         <v>47</v>
       </c>
-      <c r="BF78" s="66"/>
-      <c r="BG78" s="66"/>
+      <c r="BF78" s="4"/>
+      <c r="BG78" s="4"/>
       <c r="BH78" s="4"/>
       <c r="BM78"/>
     </row>
-    <row r="79" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>43</v>
       </c>
@@ -11268,18 +11231,18 @@
       <c r="BC79" s="18">
         <v>25.9</v>
       </c>
-      <c r="BD79" s="67">
+      <c r="BD79" s="18">
         <v>1010</v>
       </c>
-      <c r="BE79" s="67">
+      <c r="BE79" s="18">
         <v>47</v>
       </c>
-      <c r="BF79" s="66"/>
-      <c r="BG79" s="66"/>
+      <c r="BF79" s="4"/>
+      <c r="BG79" s="4"/>
       <c r="BH79" s="4"/>
       <c r="BM79"/>
     </row>
-    <row r="80" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>13</v>
       </c>
@@ -11373,20 +11336,20 @@
       <c r="BC80" s="18">
         <v>25.9</v>
       </c>
-      <c r="BD80" s="67">
+      <c r="BD80" s="18">
         <v>1010</v>
       </c>
-      <c r="BE80" s="67">
+      <c r="BE80" s="18">
         <v>47</v>
       </c>
-      <c r="BF80" s="66"/>
-      <c r="BG80" s="66"/>
+      <c r="BF80" s="4"/>
+      <c r="BG80" s="4"/>
       <c r="BH80" s="18" t="s">
         <v>91</v>
       </c>
       <c r="BM80"/>
     </row>
-    <row r="81" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>13</v>
       </c>
@@ -11480,20 +11443,20 @@
       <c r="BC81" s="18">
         <v>25.9</v>
       </c>
-      <c r="BD81" s="67">
+      <c r="BD81" s="18">
         <v>1010</v>
       </c>
-      <c r="BE81" s="67">
+      <c r="BE81" s="18">
         <v>47</v>
       </c>
-      <c r="BF81" s="73"/>
-      <c r="BG81" s="66"/>
+      <c r="BF81" s="66"/>
+      <c r="BG81" s="4"/>
       <c r="BH81" s="18" t="s">
         <v>92</v>
       </c>
       <c r="BM81"/>
     </row>
-    <row r="82" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>13</v>
       </c>
@@ -11587,18 +11550,18 @@
       <c r="BC82" s="18">
         <v>26.4</v>
       </c>
-      <c r="BD82" s="67">
+      <c r="BD82" s="18">
         <v>1010</v>
       </c>
-      <c r="BE82" s="67">
+      <c r="BE82" s="18">
         <v>46.5</v>
       </c>
-      <c r="BF82" s="66"/>
-      <c r="BG82" s="66"/>
+      <c r="BF82" s="4"/>
+      <c r="BG82" s="4"/>
       <c r="BH82" s="4"/>
       <c r="BM82"/>
     </row>
-    <row r="83" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>13</v>
       </c>
@@ -11692,18 +11655,18 @@
       <c r="BC83" s="18">
         <v>26.4</v>
       </c>
-      <c r="BD83" s="67">
+      <c r="BD83" s="18">
         <v>1010</v>
       </c>
-      <c r="BE83" s="67">
+      <c r="BE83" s="18">
         <v>46.5</v>
       </c>
-      <c r="BF83" s="66"/>
-      <c r="BG83" s="66"/>
+      <c r="BF83" s="4"/>
+      <c r="BG83" s="4"/>
       <c r="BH83" s="4"/>
       <c r="BM83"/>
     </row>
-    <row r="84" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>13</v>
       </c>
@@ -11797,18 +11760,18 @@
       <c r="BC84" s="18">
         <v>26.4</v>
       </c>
-      <c r="BD84" s="67">
+      <c r="BD84" s="18">
         <v>1010</v>
       </c>
-      <c r="BE84" s="67">
+      <c r="BE84" s="18">
         <v>46.5</v>
       </c>
-      <c r="BF84" s="66"/>
-      <c r="BG84" s="66"/>
+      <c r="BF84" s="4"/>
+      <c r="BG84" s="4"/>
       <c r="BH84" s="4"/>
       <c r="BM84"/>
     </row>
-    <row r="85" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>13</v>
       </c>
@@ -11902,18 +11865,18 @@
       <c r="BC85" s="18">
         <v>26.4</v>
       </c>
-      <c r="BD85" s="67">
+      <c r="BD85" s="18">
         <v>1010</v>
       </c>
-      <c r="BE85" s="67">
+      <c r="BE85" s="18">
         <v>46.5</v>
       </c>
-      <c r="BF85" s="66"/>
-      <c r="BG85" s="66"/>
+      <c r="BF85" s="4"/>
+      <c r="BG85" s="4"/>
       <c r="BH85" s="4"/>
       <c r="BM85"/>
     </row>
-    <row r="86" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>43</v>
       </c>
@@ -12005,18 +11968,18 @@
       <c r="BC86" s="18">
         <v>26.4</v>
       </c>
-      <c r="BD86" s="67">
+      <c r="BD86" s="18">
         <v>1010</v>
       </c>
-      <c r="BE86" s="67">
+      <c r="BE86" s="18">
         <v>46.5</v>
       </c>
-      <c r="BF86" s="66"/>
+      <c r="BF86" s="4"/>
       <c r="BG86" s="4"/>
       <c r="BH86" s="4"/>
       <c r="BM86"/>
     </row>
-    <row r="87" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>43</v>
       </c>
@@ -12108,20 +12071,20 @@
       <c r="BC87" s="18">
         <v>26.4</v>
       </c>
-      <c r="BD87" s="67">
+      <c r="BD87" s="18">
         <v>1010</v>
       </c>
-      <c r="BE87" s="67">
+      <c r="BE87" s="18">
         <v>46.5</v>
       </c>
-      <c r="BF87" s="66"/>
+      <c r="BF87" s="4"/>
       <c r="BG87" s="4"/>
       <c r="BH87" s="4" t="s">
         <v>90</v>
       </c>
       <c r="BM87"/>
     </row>
-    <row r="88" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>43</v>
       </c>
@@ -12213,18 +12176,18 @@
       <c r="BC88" s="18">
         <v>26.4</v>
       </c>
-      <c r="BD88" s="67">
+      <c r="BD88" s="18">
         <v>1010</v>
       </c>
-      <c r="BE88" s="67">
+      <c r="BE88" s="18">
         <v>46.5</v>
       </c>
-      <c r="BF88" s="66"/>
+      <c r="BF88" s="4"/>
       <c r="BG88" s="4"/>
       <c r="BH88" s="4"/>
       <c r="BM88"/>
     </row>
-    <row r="89" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
@@ -12316,18 +12279,18 @@
       <c r="BC89" s="18">
         <v>26.4</v>
       </c>
-      <c r="BD89" s="67">
+      <c r="BD89" s="18">
         <v>1010</v>
       </c>
-      <c r="BE89" s="67">
+      <c r="BE89" s="18">
         <v>46.5</v>
       </c>
-      <c r="BF89" s="66"/>
+      <c r="BF89" s="4"/>
       <c r="BG89" s="4"/>
       <c r="BH89" s="4"/>
       <c r="BM89"/>
     </row>
-    <row r="90" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>43</v>
       </c>
@@ -12419,18 +12382,18 @@
       <c r="BC90" s="18">
         <v>26.7</v>
       </c>
-      <c r="BD90" s="67">
+      <c r="BD90" s="18">
         <v>1010</v>
       </c>
-      <c r="BE90" s="67">
+      <c r="BE90" s="18">
         <v>46.7</v>
       </c>
-      <c r="BF90" s="66"/>
+      <c r="BF90" s="4"/>
       <c r="BG90" s="4"/>
       <c r="BH90" s="4"/>
       <c r="BM90"/>
     </row>
-    <row r="91" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>43</v>
       </c>
@@ -12522,18 +12485,18 @@
       <c r="BC91" s="18">
         <v>26.7</v>
       </c>
-      <c r="BD91" s="67">
+      <c r="BD91" s="18">
         <v>1010</v>
       </c>
-      <c r="BE91" s="67">
+      <c r="BE91" s="18">
         <v>46.7</v>
       </c>
-      <c r="BF91" s="66"/>
-      <c r="BG91" s="66"/>
+      <c r="BF91" s="4"/>
+      <c r="BG91" s="4"/>
       <c r="BH91" s="4"/>
       <c r="BM91"/>
     </row>
-    <row r="92" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>13</v>
       </c>
@@ -12625,18 +12588,18 @@
       <c r="BC92" s="18">
         <v>26.7</v>
       </c>
-      <c r="BD92" s="67">
+      <c r="BD92" s="18">
         <v>1010</v>
       </c>
-      <c r="BE92" s="67">
+      <c r="BE92" s="18">
         <v>46.7</v>
       </c>
-      <c r="BF92" s="66"/>
-      <c r="BG92" s="66"/>
+      <c r="BF92" s="4"/>
+      <c r="BG92" s="4"/>
       <c r="BH92" s="4"/>
       <c r="BM92"/>
     </row>
-    <row r="93" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>13</v>
       </c>
@@ -12728,18 +12691,18 @@
       <c r="BC93" s="18">
         <v>26.7</v>
       </c>
-      <c r="BD93" s="67">
+      <c r="BD93" s="18">
         <v>1010</v>
       </c>
-      <c r="BE93" s="67">
+      <c r="BE93" s="18">
         <v>46.7</v>
       </c>
-      <c r="BF93" s="66"/>
-      <c r="BG93" s="66"/>
+      <c r="BF93" s="4"/>
+      <c r="BG93" s="4"/>
       <c r="BH93" s="4"/>
       <c r="BM93"/>
     </row>
-    <row r="94" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>13</v>
       </c>
@@ -12831,18 +12794,18 @@
       <c r="BC94" s="18">
         <v>26.7</v>
       </c>
-      <c r="BD94" s="67">
+      <c r="BD94" s="18">
         <v>1010</v>
       </c>
-      <c r="BE94" s="67">
+      <c r="BE94" s="18">
         <v>46.7</v>
       </c>
-      <c r="BF94" s="66"/>
-      <c r="BG94" s="66"/>
+      <c r="BF94" s="4"/>
+      <c r="BG94" s="4"/>
       <c r="BH94" s="4"/>
       <c r="BM94"/>
     </row>
-    <row r="95" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>13</v>
       </c>
@@ -12930,18 +12893,18 @@
       <c r="BC95" s="18">
         <v>26.7</v>
       </c>
-      <c r="BD95" s="67">
+      <c r="BD95" s="18">
         <v>1010</v>
       </c>
-      <c r="BE95" s="67">
+      <c r="BE95" s="18">
         <v>46.7</v>
       </c>
-      <c r="BF95" s="66"/>
-      <c r="BG95" s="66"/>
+      <c r="BF95" s="4"/>
+      <c r="BG95" s="4"/>
       <c r="BH95" s="4"/>
       <c r="BM95"/>
     </row>
-    <row r="96" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>13</v>
       </c>
@@ -13033,18 +12996,18 @@
       <c r="BC96" s="18">
         <v>26.7</v>
       </c>
-      <c r="BD96" s="67">
+      <c r="BD96" s="18">
         <v>1010</v>
       </c>
-      <c r="BE96" s="67">
+      <c r="BE96" s="18">
         <v>46.7</v>
       </c>
-      <c r="BF96" s="66"/>
-      <c r="BG96" s="66"/>
+      <c r="BF96" s="4"/>
+      <c r="BG96" s="4"/>
       <c r="BH96" s="4"/>
       <c r="BM96"/>
     </row>
-    <row r="97" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>13</v>
       </c>
@@ -13136,18 +13099,18 @@
       <c r="BC97" s="18">
         <v>26.7</v>
       </c>
-      <c r="BD97" s="67">
+      <c r="BD97" s="18">
         <v>1010</v>
       </c>
-      <c r="BE97" s="67">
+      <c r="BE97" s="18">
         <v>46.7</v>
       </c>
-      <c r="BF97" s="66"/>
-      <c r="BG97" s="66"/>
+      <c r="BF97" s="4"/>
+      <c r="BG97" s="4"/>
       <c r="BH97" s="4"/>
       <c r="BM97"/>
     </row>
-    <row r="98" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>13</v>
       </c>
@@ -13239,18 +13202,18 @@
       <c r="BC98" s="18">
         <v>26.7</v>
       </c>
-      <c r="BD98" s="67">
+      <c r="BD98" s="18">
         <v>1010</v>
       </c>
-      <c r="BE98" s="67">
+      <c r="BE98" s="18">
         <v>46.7</v>
       </c>
-      <c r="BF98" s="66"/>
-      <c r="BG98" s="66"/>
+      <c r="BF98" s="4"/>
+      <c r="BG98" s="4"/>
       <c r="BH98" s="4"/>
       <c r="BM98"/>
     </row>
-    <row r="99" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>43</v>
       </c>
@@ -13342,18 +13305,18 @@
       <c r="BC99" s="4">
         <v>23.9</v>
       </c>
-      <c r="BD99" s="66">
+      <c r="BD99" s="4">
         <v>1010</v>
       </c>
-      <c r="BE99" s="71">
+      <c r="BE99" s="58">
         <v>48.2</v>
       </c>
-      <c r="BF99" s="71"/>
+      <c r="BF99" s="58"/>
       <c r="BG99" s="4"/>
       <c r="BH99" s="4"/>
       <c r="BM99"/>
     </row>
-    <row r="100" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>43</v>
       </c>
@@ -13445,20 +13408,20 @@
       <c r="BC100" s="4">
         <v>23.9</v>
       </c>
-      <c r="BD100" s="66">
+      <c r="BD100" s="4">
         <v>1010</v>
       </c>
-      <c r="BE100" s="71">
+      <c r="BE100" s="58">
         <v>48.2</v>
       </c>
-      <c r="BF100" s="71"/>
+      <c r="BF100" s="58"/>
       <c r="BG100" s="4"/>
       <c r="BH100" s="13" t="s">
         <v>95</v>
       </c>
       <c r="BM100"/>
     </row>
-    <row r="101" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>43</v>
       </c>
@@ -13550,18 +13513,18 @@
       <c r="BC101" s="4">
         <v>23.9</v>
       </c>
-      <c r="BD101" s="66">
+      <c r="BD101" s="4">
         <v>1010</v>
       </c>
-      <c r="BE101" s="71">
+      <c r="BE101" s="58">
         <v>48.2</v>
       </c>
-      <c r="BF101" s="71"/>
+      <c r="BF101" s="58"/>
       <c r="BG101" s="4"/>
       <c r="BH101" s="4"/>
       <c r="BM101"/>
     </row>
-    <row r="102" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>43</v>
       </c>
@@ -13649,20 +13612,20 @@
       <c r="BC102" s="4">
         <v>24.1</v>
       </c>
-      <c r="BD102" s="66">
+      <c r="BD102" s="4">
         <v>1010</v>
       </c>
-      <c r="BE102" s="71">
+      <c r="BE102" s="58">
         <v>48.2</v>
       </c>
-      <c r="BF102" s="71"/>
+      <c r="BF102" s="58"/>
       <c r="BG102" s="4"/>
       <c r="BH102" s="4" t="s">
         <v>94</v>
       </c>
       <c r="BM102"/>
     </row>
-    <row r="103" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>43</v>
       </c>
@@ -13754,18 +13717,18 @@
       <c r="BC103" s="4">
         <v>24.1</v>
       </c>
-      <c r="BD103" s="66">
+      <c r="BD103" s="4">
         <v>1010</v>
       </c>
-      <c r="BE103" s="71">
+      <c r="BE103" s="58">
         <v>48.2</v>
       </c>
-      <c r="BF103" s="71"/>
+      <c r="BF103" s="58"/>
       <c r="BG103" s="4"/>
       <c r="BH103" s="4"/>
       <c r="BM103"/>
     </row>
-    <row r="104" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>43</v>
       </c>
@@ -13857,20 +13820,20 @@
       <c r="BC104" s="4">
         <v>24.1</v>
       </c>
-      <c r="BD104" s="66">
+      <c r="BD104" s="4">
         <v>1010</v>
       </c>
-      <c r="BE104" s="71">
+      <c r="BE104" s="58">
         <v>48.2</v>
       </c>
-      <c r="BF104" s="71"/>
-      <c r="BG104" s="66"/>
+      <c r="BF104" s="58"/>
+      <c r="BG104" s="4"/>
       <c r="BH104" s="13" t="s">
         <v>97</v>
       </c>
       <c r="BM104"/>
     </row>
-    <row r="105" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>13</v>
       </c>
@@ -13962,18 +13925,18 @@
       <c r="BC105" s="4">
         <v>24.8</v>
       </c>
-      <c r="BD105" s="66">
+      <c r="BD105" s="4">
         <v>1010</v>
       </c>
-      <c r="BE105" s="71">
+      <c r="BE105" s="58">
         <v>47</v>
       </c>
-      <c r="BF105" s="71"/>
-      <c r="BG105" s="66"/>
+      <c r="BF105" s="58"/>
+      <c r="BG105" s="4"/>
       <c r="BH105" s="4"/>
       <c r="BM105"/>
     </row>
-    <row r="106" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>13</v>
       </c>
@@ -14065,18 +14028,18 @@
       <c r="BC106" s="4">
         <v>24.8</v>
       </c>
-      <c r="BD106" s="66">
+      <c r="BD106" s="4">
         <v>1010</v>
       </c>
-      <c r="BE106" s="71">
+      <c r="BE106" s="58">
         <v>47</v>
       </c>
-      <c r="BF106" s="71"/>
-      <c r="BG106" s="66"/>
+      <c r="BF106" s="58"/>
+      <c r="BG106" s="4"/>
       <c r="BH106" s="4"/>
       <c r="BM106"/>
     </row>
-    <row r="107" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>13</v>
       </c>
@@ -14168,18 +14131,18 @@
       <c r="BC107" s="4">
         <v>24.8</v>
       </c>
-      <c r="BD107" s="66">
+      <c r="BD107" s="4">
         <v>1010</v>
       </c>
-      <c r="BE107" s="71">
+      <c r="BE107" s="58">
         <v>47</v>
       </c>
-      <c r="BF107" s="71"/>
-      <c r="BG107" s="66"/>
+      <c r="BF107" s="58"/>
+      <c r="BG107" s="4"/>
       <c r="BH107" s="4"/>
       <c r="BM107"/>
     </row>
-    <row r="108" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>13</v>
       </c>
@@ -14271,18 +14234,18 @@
       <c r="BC108" s="4">
         <v>24.8</v>
       </c>
-      <c r="BD108" s="66">
+      <c r="BD108" s="4">
         <v>1010</v>
       </c>
-      <c r="BE108" s="71">
+      <c r="BE108" s="58">
         <v>47</v>
       </c>
-      <c r="BF108" s="71"/>
-      <c r="BG108" s="66"/>
+      <c r="BF108" s="58"/>
+      <c r="BG108" s="4"/>
       <c r="BH108" s="4"/>
       <c r="BM108"/>
     </row>
-    <row r="109" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>13</v>
       </c>
@@ -14374,18 +14337,18 @@
       <c r="BC109" s="4">
         <v>24.8</v>
       </c>
-      <c r="BD109" s="66">
+      <c r="BD109" s="4">
         <v>1010</v>
       </c>
-      <c r="BE109" s="71">
+      <c r="BE109" s="58">
         <v>47</v>
       </c>
-      <c r="BF109" s="71"/>
-      <c r="BG109" s="66"/>
+      <c r="BF109" s="58"/>
+      <c r="BG109" s="4"/>
       <c r="BH109" s="4"/>
       <c r="BM109"/>
     </row>
-    <row r="110" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>13</v>
       </c>
@@ -14477,20 +14440,20 @@
       <c r="BC110" s="4">
         <v>24.8</v>
       </c>
-      <c r="BD110" s="66">
+      <c r="BD110" s="4">
         <v>1010</v>
       </c>
-      <c r="BE110" s="71">
+      <c r="BE110" s="58">
         <v>47</v>
       </c>
-      <c r="BF110" s="71"/>
-      <c r="BG110" s="66"/>
+      <c r="BF110" s="58"/>
+      <c r="BG110" s="4"/>
       <c r="BH110" s="13" t="s">
         <v>97</v>
       </c>
       <c r="BM110"/>
     </row>
-    <row r="111" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>43</v>
       </c>
@@ -14588,18 +14551,18 @@
       <c r="BC111" s="4">
         <v>25.2</v>
       </c>
-      <c r="BD111" s="66">
+      <c r="BD111" s="4">
         <v>1010</v>
       </c>
-      <c r="BE111" s="71">
+      <c r="BE111" s="58">
         <v>47</v>
       </c>
-      <c r="BF111" s="71"/>
+      <c r="BF111" s="58"/>
       <c r="BG111" s="4"/>
       <c r="BH111" s="4"/>
       <c r="BM111"/>
     </row>
-    <row r="112" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>43</v>
       </c>
@@ -14684,20 +14647,20 @@
       <c r="BC112" s="4">
         <v>25.2</v>
       </c>
-      <c r="BD112" s="66">
+      <c r="BD112" s="4">
         <v>1010</v>
       </c>
-      <c r="BE112" s="71">
+      <c r="BE112" s="58">
         <v>47</v>
       </c>
-      <c r="BF112" s="71"/>
+      <c r="BF112" s="58"/>
       <c r="BG112" s="4"/>
       <c r="BH112" s="13" t="s">
         <v>96</v>
       </c>
       <c r="BM112"/>
     </row>
-    <row r="113" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>43</v>
       </c>
@@ -14795,18 +14758,18 @@
       <c r="BC113" s="4">
         <v>25.2</v>
       </c>
-      <c r="BD113" s="66">
+      <c r="BD113" s="4">
         <v>1010</v>
       </c>
-      <c r="BE113" s="71">
+      <c r="BE113" s="58">
         <v>47</v>
       </c>
-      <c r="BF113" s="71"/>
+      <c r="BF113" s="58"/>
       <c r="BG113" s="4"/>
       <c r="BH113" s="4"/>
       <c r="BM113"/>
     </row>
-    <row r="114" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>43</v>
       </c>
@@ -14897,18 +14860,18 @@
       <c r="BC114" s="4">
         <v>25.7</v>
       </c>
-      <c r="BD114" s="66">
+      <c r="BD114" s="4">
         <v>1009</v>
       </c>
-      <c r="BE114" s="71">
+      <c r="BE114" s="58">
         <v>46.3</v>
       </c>
-      <c r="BF114" s="71"/>
+      <c r="BF114" s="58"/>
       <c r="BG114" s="4"/>
       <c r="BH114" s="4"/>
       <c r="BM114"/>
     </row>
-    <row r="115" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>43</v>
       </c>
@@ -15006,18 +14969,18 @@
       <c r="BC115" s="4">
         <v>25.7</v>
       </c>
-      <c r="BD115" s="66">
+      <c r="BD115" s="4">
         <v>1009</v>
       </c>
-      <c r="BE115" s="71">
+      <c r="BE115" s="58">
         <v>46.3</v>
       </c>
-      <c r="BF115" s="71"/>
+      <c r="BF115" s="58"/>
       <c r="BG115" s="4"/>
       <c r="BH115" s="4"/>
       <c r="BM115"/>
     </row>
-    <row r="116" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>43</v>
       </c>
@@ -15115,18 +15078,18 @@
       <c r="BC116" s="4">
         <v>25.7</v>
       </c>
-      <c r="BD116" s="66">
+      <c r="BD116" s="4">
         <v>1009</v>
       </c>
-      <c r="BE116" s="71">
+      <c r="BE116" s="58">
         <v>46.3</v>
       </c>
-      <c r="BF116" s="71"/>
-      <c r="BG116" s="66"/>
+      <c r="BF116" s="58"/>
+      <c r="BG116" s="4"/>
       <c r="BH116" s="4"/>
       <c r="BM116"/>
     </row>
-    <row r="117" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>43</v>
       </c>
@@ -15224,18 +15187,18 @@
       <c r="BC117" s="4">
         <v>25.8</v>
       </c>
-      <c r="BD117" s="66">
+      <c r="BD117" s="4">
         <v>1009</v>
       </c>
-      <c r="BE117" s="71">
+      <c r="BE117" s="58">
         <v>45.7</v>
       </c>
-      <c r="BF117" s="71"/>
-      <c r="BG117" s="66"/>
+      <c r="BF117" s="58"/>
+      <c r="BG117" s="4"/>
       <c r="BH117" s="4"/>
       <c r="BM117"/>
     </row>
-    <row r="118" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>43</v>
       </c>
@@ -15333,18 +15296,18 @@
       <c r="BC118" s="4">
         <v>25.8</v>
       </c>
-      <c r="BD118" s="66">
+      <c r="BD118" s="4">
         <v>1009</v>
       </c>
-      <c r="BE118" s="71">
+      <c r="BE118" s="58">
         <v>45.7</v>
       </c>
-      <c r="BF118" s="71"/>
-      <c r="BG118" s="66"/>
+      <c r="BF118" s="58"/>
+      <c r="BG118" s="4"/>
       <c r="BH118" s="4"/>
       <c r="BM118"/>
     </row>
-    <row r="119" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>43</v>
       </c>
@@ -15442,18 +15405,18 @@
       <c r="BC119" s="4">
         <v>25.8</v>
       </c>
-      <c r="BD119" s="66">
+      <c r="BD119" s="4">
         <v>1009</v>
       </c>
-      <c r="BE119" s="71">
+      <c r="BE119" s="58">
         <v>45.7</v>
       </c>
-      <c r="BF119" s="71"/>
-      <c r="BG119" s="66"/>
+      <c r="BF119" s="58"/>
+      <c r="BG119" s="4"/>
       <c r="BH119" s="4"/>
       <c r="BM119"/>
     </row>
-    <row r="120" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>13</v>
       </c>
@@ -15551,18 +15514,18 @@
       <c r="BC120" s="4">
         <v>26.1</v>
       </c>
-      <c r="BD120" s="66">
+      <c r="BD120" s="4">
         <v>1009</v>
       </c>
-      <c r="BE120" s="71">
+      <c r="BE120" s="58">
         <v>45.2</v>
       </c>
-      <c r="BF120" s="71"/>
-      <c r="BG120" s="66"/>
+      <c r="BF120" s="58"/>
+      <c r="BG120" s="4"/>
       <c r="BH120" s="4"/>
       <c r="BM120"/>
     </row>
-    <row r="121" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>13</v>
       </c>
@@ -15660,18 +15623,18 @@
       <c r="BC121" s="4">
         <v>26.1</v>
       </c>
-      <c r="BD121" s="66">
+      <c r="BD121" s="4">
         <v>1009</v>
       </c>
-      <c r="BE121" s="71">
+      <c r="BE121" s="58">
         <v>45.2</v>
       </c>
-      <c r="BF121" s="71"/>
-      <c r="BG121" s="66"/>
+      <c r="BF121" s="58"/>
+      <c r="BG121" s="4"/>
       <c r="BH121" s="4"/>
       <c r="BM121"/>
     </row>
-    <row r="122" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>13</v>
       </c>
@@ -15766,18 +15729,18 @@
       <c r="BC122" s="4">
         <v>26.1</v>
       </c>
-      <c r="BD122" s="66">
+      <c r="BD122" s="4">
         <v>1009</v>
       </c>
-      <c r="BE122" s="71">
+      <c r="BE122" s="58">
         <v>45.2</v>
       </c>
-      <c r="BF122" s="71"/>
-      <c r="BG122" s="66"/>
+      <c r="BF122" s="58"/>
+      <c r="BG122" s="4"/>
       <c r="BH122" s="4"/>
       <c r="BM122"/>
     </row>
-    <row r="123" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>13</v>
       </c>
@@ -15872,18 +15835,18 @@
       <c r="BC123" s="4">
         <v>26.4</v>
       </c>
-      <c r="BD123" s="66">
+      <c r="BD123" s="4">
         <v>1008</v>
       </c>
-      <c r="BE123" s="71">
+      <c r="BE123" s="58">
         <v>44.4</v>
       </c>
-      <c r="BF123" s="71"/>
-      <c r="BG123" s="66"/>
+      <c r="BF123" s="58"/>
+      <c r="BG123" s="4"/>
       <c r="BH123" s="4"/>
       <c r="BM123"/>
     </row>
-    <row r="124" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>13</v>
       </c>
@@ -15978,18 +15941,18 @@
       <c r="BC124" s="16">
         <v>25.5</v>
       </c>
-      <c r="BD124" s="68">
+      <c r="BD124" s="16">
         <v>1012</v>
       </c>
-      <c r="BE124" s="68">
+      <c r="BE124" s="16">
         <v>39.4</v>
       </c>
-      <c r="BF124" s="71"/>
-      <c r="BG124" s="66"/>
+      <c r="BF124" s="58"/>
+      <c r="BG124" s="4"/>
       <c r="BH124" s="4"/>
       <c r="BM124"/>
     </row>
-    <row r="125" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>13</v>
       </c>
@@ -16084,18 +16047,18 @@
       <c r="BC125" s="16">
         <v>25.5</v>
       </c>
-      <c r="BD125" s="68">
+      <c r="BD125" s="16">
         <v>1012</v>
       </c>
-      <c r="BE125" s="68">
+      <c r="BE125" s="16">
         <v>39.4</v>
       </c>
-      <c r="BF125" s="69"/>
-      <c r="BG125" s="66"/>
+      <c r="BF125" s="64"/>
+      <c r="BG125" s="4"/>
       <c r="BH125" s="4"/>
       <c r="BM125"/>
     </row>
-    <row r="126" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>13</v>
       </c>
@@ -16190,18 +16153,18 @@
       <c r="BC126" s="16">
         <v>25.5</v>
       </c>
-      <c r="BD126" s="68">
+      <c r="BD126" s="16">
         <v>1012</v>
       </c>
-      <c r="BE126" s="68">
+      <c r="BE126" s="16">
         <v>39.4</v>
       </c>
-      <c r="BF126" s="69"/>
-      <c r="BG126" s="66"/>
+      <c r="BF126" s="64"/>
+      <c r="BG126" s="4"/>
       <c r="BH126" s="4"/>
       <c r="BM126"/>
     </row>
-    <row r="127" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>13</v>
       </c>
@@ -16296,18 +16259,18 @@
       <c r="BC127" s="16">
         <v>25.5</v>
       </c>
-      <c r="BD127" s="68">
+      <c r="BD127" s="16">
         <v>1012</v>
       </c>
-      <c r="BE127" s="68">
+      <c r="BE127" s="16">
         <v>39.4</v>
       </c>
-      <c r="BF127" s="69"/>
-      <c r="BG127" s="66"/>
+      <c r="BF127" s="64"/>
+      <c r="BG127" s="4"/>
       <c r="BH127" s="4"/>
       <c r="BM127"/>
     </row>
-    <row r="128" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>43</v>
       </c>
@@ -16408,7 +16371,7 @@
       <c r="BD128" s="17">
         <v>1012</v>
       </c>
-      <c r="BE128" s="68">
+      <c r="BE128" s="16">
         <v>39.4</v>
       </c>
       <c r="BF128" s="15"/>
@@ -16416,7 +16379,7 @@
       <c r="BH128" s="4"/>
       <c r="BM128"/>
     </row>
-    <row r="129" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>43</v>
       </c>
@@ -16517,7 +16480,7 @@
       <c r="BD129" s="17">
         <v>1012</v>
       </c>
-      <c r="BE129" s="68">
+      <c r="BE129" s="16">
         <v>39.4</v>
       </c>
       <c r="BF129" s="15"/>
@@ -16525,7 +16488,7 @@
       <c r="BH129" s="4"/>
       <c r="BM129"/>
     </row>
-    <row r="130" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>43</v>
       </c>
@@ -16626,7 +16589,7 @@
       <c r="BD130" s="17">
         <v>1012</v>
       </c>
-      <c r="BE130" s="68">
+      <c r="BE130" s="16">
         <v>39.4</v>
       </c>
       <c r="BF130" s="15"/>
@@ -16636,7 +16599,7 @@
       </c>
       <c r="BM130"/>
     </row>
-    <row r="131" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>43</v>
       </c>
@@ -16737,7 +16700,7 @@
       <c r="BD131" s="17">
         <v>1012</v>
       </c>
-      <c r="BE131" s="68">
+      <c r="BE131" s="16">
         <v>39.4</v>
       </c>
       <c r="BF131" s="15"/>
@@ -16745,7 +16708,7 @@
       <c r="BH131" s="4"/>
       <c r="BM131"/>
     </row>
-    <row r="132" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>43</v>
       </c>
@@ -16843,10 +16806,10 @@
       <c r="BC132" s="16">
         <v>26</v>
       </c>
-      <c r="BD132" s="70">
+      <c r="BD132" s="65">
         <v>1012</v>
       </c>
-      <c r="BE132" s="68">
+      <c r="BE132" s="16">
         <v>40</v>
       </c>
       <c r="BF132" s="23"/>
@@ -16854,7 +16817,7 @@
       <c r="BH132" s="4"/>
       <c r="BM132"/>
     </row>
-    <row r="133" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>43</v>
       </c>
@@ -16955,15 +16918,15 @@
       <c r="BD133" s="17">
         <v>1012</v>
       </c>
-      <c r="BE133" s="68">
+      <c r="BE133" s="16">
         <v>40</v>
       </c>
       <c r="BF133" s="15"/>
-      <c r="BG133" s="66"/>
+      <c r="BG133" s="4"/>
       <c r="BH133" s="4"/>
       <c r="BM133"/>
     </row>
-    <row r="134" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>43</v>
       </c>
@@ -17064,15 +17027,15 @@
       <c r="BD134" s="17">
         <v>1012</v>
       </c>
-      <c r="BE134" s="68">
+      <c r="BE134" s="16">
         <v>40</v>
       </c>
       <c r="BF134" s="15"/>
-      <c r="BG134" s="66"/>
+      <c r="BG134" s="4"/>
       <c r="BH134" s="4"/>
       <c r="BM134"/>
     </row>
-    <row r="135" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>43</v>
       </c>
@@ -17088,7 +17051,7 @@
       <c r="E135" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F135" s="64" t="s">
+      <c r="F135" s="2" t="s">
         <v>549</v>
       </c>
       <c r="G135" s="7">
@@ -17173,15 +17136,15 @@
       <c r="BD135" s="17">
         <v>1012</v>
       </c>
-      <c r="BE135" s="68">
+      <c r="BE135" s="16">
         <v>40</v>
       </c>
       <c r="BF135" s="15"/>
-      <c r="BG135" s="66"/>
+      <c r="BG135" s="4"/>
       <c r="BH135" s="4"/>
       <c r="BM135"/>
     </row>
-    <row r="136" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>43</v>
       </c>
@@ -17282,15 +17245,15 @@
       <c r="BD136" s="17">
         <v>1012</v>
       </c>
-      <c r="BE136" s="68">
+      <c r="BE136" s="16">
         <v>40</v>
       </c>
       <c r="BF136" s="15"/>
-      <c r="BG136" s="66"/>
+      <c r="BG136" s="4"/>
       <c r="BH136" s="4"/>
       <c r="BM136"/>
     </row>
-    <row r="137" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>43</v>
       </c>
@@ -17399,7 +17362,7 @@
       <c r="BH137" s="4"/>
       <c r="BM137"/>
     </row>
-    <row r="138" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>43</v>
       </c>
@@ -17497,7 +17460,7 @@
       <c r="BC138" s="16">
         <v>26.3</v>
       </c>
-      <c r="BD138" s="70">
+      <c r="BD138" s="65">
         <v>1012</v>
       </c>
       <c r="BE138" s="16">
@@ -17508,7 +17471,7 @@
       <c r="BH138" s="4"/>
       <c r="BM138"/>
     </row>
-    <row r="139" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>43</v>
       </c>
@@ -17609,15 +17572,15 @@
       <c r="BD139" s="17">
         <v>1012</v>
       </c>
-      <c r="BE139" s="68">
+      <c r="BE139" s="16">
         <v>40</v>
       </c>
       <c r="BF139" s="15"/>
-      <c r="BG139" s="66"/>
+      <c r="BG139" s="4"/>
       <c r="BH139" s="4"/>
       <c r="BM139"/>
     </row>
-    <row r="140" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>43</v>
       </c>
@@ -17718,7 +17681,7 @@
       <c r="BD140" s="17">
         <v>1011</v>
       </c>
-      <c r="BE140" s="68">
+      <c r="BE140" s="16">
         <v>40</v>
       </c>
       <c r="BF140" s="15"/>
@@ -17726,7 +17689,7 @@
       <c r="BH140" s="4"/>
       <c r="BM140"/>
     </row>
-    <row r="141" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>43</v>
       </c>
@@ -17827,15 +17790,15 @@
       <c r="BD141" s="17">
         <v>1011</v>
       </c>
-      <c r="BE141" s="68">
+      <c r="BE141" s="16">
         <v>40</v>
       </c>
       <c r="BF141" s="15"/>
-      <c r="BG141" s="66"/>
+      <c r="BG141" s="4"/>
       <c r="BH141" s="4"/>
       <c r="BM141"/>
     </row>
-    <row r="142" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>13</v>
       </c>
@@ -17933,17 +17896,17 @@
       <c r="BD142" s="17">
         <v>1011</v>
       </c>
-      <c r="BE142" s="68">
+      <c r="BE142" s="16">
         <v>40</v>
       </c>
       <c r="BF142" s="15"/>
-      <c r="BG142" s="66"/>
+      <c r="BG142" s="4"/>
       <c r="BH142" s="13" t="s">
         <v>101</v>
       </c>
       <c r="BM142"/>
     </row>
-    <row r="143" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>13</v>
       </c>
@@ -18041,17 +18004,17 @@
       <c r="BD143" s="17">
         <v>1011</v>
       </c>
-      <c r="BE143" s="68">
+      <c r="BE143" s="16">
         <v>40</v>
       </c>
       <c r="BF143" s="15"/>
-      <c r="BG143" s="75"/>
+      <c r="BG143" s="13"/>
       <c r="BH143" s="13" t="s">
         <v>102</v>
       </c>
       <c r="BM143"/>
     </row>
-    <row r="144" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>13</v>
       </c>
@@ -18146,18 +18109,18 @@
       <c r="BC144" s="16">
         <v>26.7</v>
       </c>
-      <c r="BD144" s="70">
+      <c r="BD144" s="65">
         <v>1011</v>
       </c>
-      <c r="BE144" s="68">
+      <c r="BE144" s="16">
         <v>39.6</v>
       </c>
       <c r="BF144" s="23"/>
-      <c r="BG144" s="66"/>
+      <c r="BG144" s="4"/>
       <c r="BH144" s="4"/>
       <c r="BM144"/>
     </row>
-    <row r="145" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>13</v>
       </c>
@@ -18255,15 +18218,15 @@
       <c r="BD145" s="17">
         <v>1011</v>
       </c>
-      <c r="BE145" s="68">
+      <c r="BE145" s="16">
         <v>39.6</v>
       </c>
       <c r="BF145" s="15"/>
-      <c r="BG145" s="66"/>
+      <c r="BG145" s="4"/>
       <c r="BH145" s="4"/>
       <c r="BM145"/>
     </row>
-    <row r="146" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>13</v>
       </c>
@@ -18361,15 +18324,15 @@
       <c r="BD146" s="17">
         <v>1011</v>
       </c>
-      <c r="BE146" s="68">
+      <c r="BE146" s="16">
         <v>39.6</v>
       </c>
       <c r="BF146" s="15"/>
-      <c r="BG146" s="66"/>
+      <c r="BG146" s="4"/>
       <c r="BH146" s="4"/>
       <c r="BM146"/>
     </row>
-    <row r="147" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>13</v>
       </c>
@@ -18467,15 +18430,15 @@
       <c r="BD147" s="17">
         <v>1011</v>
       </c>
-      <c r="BE147" s="68">
+      <c r="BE147" s="16">
         <v>39.6</v>
       </c>
       <c r="BF147" s="15"/>
-      <c r="BG147" s="66"/>
+      <c r="BG147" s="4"/>
       <c r="BH147" s="4"/>
       <c r="BM147"/>
     </row>
-    <row r="148" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>43</v>
       </c>
@@ -18571,14 +18534,14 @@
       <c r="BC148" s="16">
         <v>24.5</v>
       </c>
-      <c r="BD148" s="68">
+      <c r="BD148" s="16">
         <v>1013</v>
       </c>
-      <c r="BE148" s="68">
+      <c r="BE148" s="16">
         <v>47.7</v>
       </c>
       <c r="BF148" s="15"/>
-      <c r="BG148" s="74">
+      <c r="BG148" s="7">
         <v>2096</v>
       </c>
       <c r="BH148" s="13" t="s">
@@ -18586,7 +18549,7 @@
       </c>
       <c r="BM148"/>
     </row>
-    <row r="149" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>43</v>
       </c>
@@ -18682,14 +18645,14 @@
       <c r="BC149" s="16">
         <v>24.5</v>
       </c>
-      <c r="BD149" s="68">
+      <c r="BD149" s="16">
         <v>1013</v>
       </c>
-      <c r="BE149" s="68">
+      <c r="BE149" s="16">
         <v>47.7</v>
       </c>
       <c r="BF149" s="15"/>
-      <c r="BG149" s="74">
+      <c r="BG149" s="7">
         <v>2096</v>
       </c>
       <c r="BH149" s="13" t="s">
@@ -18697,7 +18660,7 @@
       </c>
       <c r="BM149"/>
     </row>
-    <row r="150" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>43</v>
       </c>
@@ -18793,10 +18756,10 @@
       <c r="BC150" s="16">
         <v>24.5</v>
       </c>
-      <c r="BD150" s="68">
+      <c r="BD150" s="16">
         <v>1013</v>
       </c>
-      <c r="BE150" s="68">
+      <c r="BE150" s="16">
         <v>47.7</v>
       </c>
       <c r="BF150" s="23"/>
@@ -18806,7 +18769,7 @@
       <c r="BH150" s="4"/>
       <c r="BM150"/>
     </row>
-    <row r="151" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>43</v>
       </c>
@@ -18902,10 +18865,10 @@
       <c r="BC151" s="16">
         <v>24.5</v>
       </c>
-      <c r="BD151" s="68">
+      <c r="BD151" s="16">
         <v>1013</v>
       </c>
-      <c r="BE151" s="68">
+      <c r="BE151" s="16">
         <v>47.7</v>
       </c>
       <c r="BF151" s="15"/>
@@ -18915,7 +18878,7 @@
       <c r="BH151" s="4"/>
       <c r="BM151"/>
     </row>
-    <row r="152" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>43</v>
       </c>
@@ -19011,10 +18974,10 @@
       <c r="BC152" s="16">
         <v>24.9</v>
       </c>
-      <c r="BD152" s="68">
+      <c r="BD152" s="16">
         <v>1012</v>
       </c>
-      <c r="BE152" s="68">
+      <c r="BE152" s="16">
         <v>45.5</v>
       </c>
       <c r="BF152" s="15"/>
@@ -19024,7 +18987,7 @@
       <c r="BH152" s="13"/>
       <c r="BM152"/>
     </row>
-    <row r="153" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>43</v>
       </c>
@@ -19120,14 +19083,14 @@
       <c r="BC153" s="16">
         <v>24.9</v>
       </c>
-      <c r="BD153" s="68">
+      <c r="BD153" s="16">
         <v>1012</v>
       </c>
-      <c r="BE153" s="68">
+      <c r="BE153" s="16">
         <v>45.5</v>
       </c>
       <c r="BF153" s="15"/>
-      <c r="BG153" s="74">
+      <c r="BG153" s="7">
         <v>2096</v>
       </c>
       <c r="BH153" s="13" t="s">
@@ -19135,7 +19098,7 @@
       </c>
       <c r="BM153"/>
     </row>
-    <row r="154" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>43</v>
       </c>
@@ -19228,20 +19191,20 @@
       <c r="BC154" s="16">
         <v>24.9</v>
       </c>
-      <c r="BD154" s="68">
+      <c r="BD154" s="16">
         <v>1012</v>
       </c>
-      <c r="BE154" s="68">
+      <c r="BE154" s="16">
         <v>45.5</v>
       </c>
       <c r="BF154" s="23"/>
-      <c r="BG154" s="74">
+      <c r="BG154" s="7">
         <v>2096</v>
       </c>
       <c r="BH154" s="4"/>
       <c r="BM154"/>
     </row>
-    <row r="155" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>43</v>
       </c>
@@ -19334,20 +19297,20 @@
       <c r="BC155" s="16">
         <v>24.9</v>
       </c>
-      <c r="BD155" s="68">
+      <c r="BD155" s="16">
         <v>1012</v>
       </c>
-      <c r="BE155" s="68">
+      <c r="BE155" s="16">
         <v>45.5</v>
       </c>
       <c r="BF155" s="15"/>
-      <c r="BG155" s="74">
+      <c r="BG155" s="7">
         <v>2096</v>
       </c>
       <c r="BH155" s="4"/>
       <c r="BM155"/>
     </row>
-    <row r="156" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>43</v>
       </c>
@@ -19440,14 +19403,14 @@
       <c r="BC156" s="16">
         <v>24.9</v>
       </c>
-      <c r="BD156" s="68">
+      <c r="BD156" s="16">
         <v>1012</v>
       </c>
-      <c r="BE156" s="68">
+      <c r="BE156" s="16">
         <v>45.5</v>
       </c>
       <c r="BF156" s="15"/>
-      <c r="BG156" s="74">
+      <c r="BG156" s="7">
         <v>2096</v>
       </c>
       <c r="BH156" s="13" t="s">
@@ -19455,7 +19418,7 @@
       </c>
       <c r="BM156"/>
     </row>
-    <row r="157" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>43</v>
       </c>
@@ -19548,14 +19511,14 @@
       <c r="BC157" s="16">
         <v>24.9</v>
       </c>
-      <c r="BD157" s="68">
+      <c r="BD157" s="16">
         <v>1012</v>
       </c>
-      <c r="BE157" s="68">
+      <c r="BE157" s="16">
         <v>45.5</v>
       </c>
       <c r="BF157" s="15"/>
-      <c r="BG157" s="74">
+      <c r="BG157" s="7">
         <v>2096</v>
       </c>
       <c r="BH157" s="13" t="s">
@@ -19563,7 +19526,7 @@
       </c>
       <c r="BM157"/>
     </row>
-    <row r="158" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>43</v>
       </c>
@@ -19656,20 +19619,20 @@
       <c r="BC158" s="16">
         <v>24.9</v>
       </c>
-      <c r="BD158" s="68">
+      <c r="BD158" s="16">
         <v>1012</v>
       </c>
-      <c r="BE158" s="68">
+      <c r="BE158" s="16">
         <v>45.5</v>
       </c>
       <c r="BF158" s="15"/>
-      <c r="BG158" s="74">
+      <c r="BG158" s="7">
         <v>2096</v>
       </c>
       <c r="BH158" s="4"/>
       <c r="BM158"/>
     </row>
-    <row r="159" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>43</v>
       </c>
@@ -19762,20 +19725,20 @@
       <c r="BC159" s="16">
         <v>24.9</v>
       </c>
-      <c r="BD159" s="68">
+      <c r="BD159" s="16">
         <v>1012</v>
       </c>
-      <c r="BE159" s="68">
+      <c r="BE159" s="16">
         <v>45.5</v>
       </c>
       <c r="BF159" s="15"/>
-      <c r="BG159" s="74">
+      <c r="BG159" s="7">
         <v>2096</v>
       </c>
       <c r="BH159" s="4"/>
       <c r="BM159"/>
     </row>
-    <row r="160" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>43</v>
       </c>
@@ -19863,20 +19826,20 @@
       <c r="BC160" s="16">
         <v>25.1</v>
       </c>
-      <c r="BD160" s="68">
+      <c r="BD160" s="16">
         <v>1012</v>
       </c>
-      <c r="BE160" s="68">
+      <c r="BE160" s="16">
         <v>44.6</v>
       </c>
       <c r="BF160" s="23"/>
-      <c r="BG160" s="74">
+      <c r="BG160" s="7">
         <v>2096</v>
       </c>
       <c r="BH160" s="13"/>
       <c r="BM160"/>
     </row>
-    <row r="161" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>43</v>
       </c>
@@ -19977,7 +19940,7 @@
       <c r="BH161" s="4"/>
       <c r="BM161"/>
     </row>
-    <row r="162" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
         <v>43</v>
       </c>
@@ -20065,20 +20028,20 @@
       <c r="BC162" s="16">
         <v>25.1</v>
       </c>
-      <c r="BD162" s="68">
+      <c r="BD162" s="16">
         <v>1012</v>
       </c>
-      <c r="BE162" s="68">
+      <c r="BE162" s="16">
         <v>44.6</v>
       </c>
       <c r="BF162" s="15"/>
-      <c r="BG162" s="74">
+      <c r="BG162" s="7">
         <v>2096</v>
       </c>
       <c r="BH162" s="4"/>
       <c r="BM162"/>
     </row>
-    <row r="163" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>43</v>
       </c>
@@ -20166,7 +20129,7 @@
       <c r="BC163" s="16">
         <v>25.1</v>
       </c>
-      <c r="BD163" s="68">
+      <c r="BD163" s="16">
         <v>1012</v>
       </c>
       <c r="BE163" s="16">
@@ -20179,7 +20142,7 @@
       <c r="BH163" s="4"/>
       <c r="BM163"/>
     </row>
-    <row r="164" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
         <v>43</v>
       </c>
@@ -20267,14 +20230,14 @@
       <c r="BC164" s="16">
         <v>25.3</v>
       </c>
-      <c r="BD164" s="68">
+      <c r="BD164" s="16">
         <v>1012</v>
       </c>
-      <c r="BE164" s="68">
+      <c r="BE164" s="16">
         <v>44.3</v>
       </c>
       <c r="BF164" s="15"/>
-      <c r="BG164" s="74">
+      <c r="BG164" s="7">
         <v>2096</v>
       </c>
       <c r="BH164" s="13" t="s">
@@ -20282,7 +20245,7 @@
       </c>
       <c r="BM164"/>
     </row>
-    <row r="165" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
         <v>43</v>
       </c>
@@ -20370,20 +20333,20 @@
       <c r="BC165" s="16">
         <v>25.3</v>
       </c>
-      <c r="BD165" s="68">
+      <c r="BD165" s="16">
         <v>1012</v>
       </c>
-      <c r="BE165" s="68">
+      <c r="BE165" s="16">
         <v>44.3</v>
       </c>
       <c r="BF165" s="15"/>
-      <c r="BG165" s="74">
+      <c r="BG165" s="7">
         <v>2096</v>
       </c>
       <c r="BH165" s="4"/>
       <c r="BM165"/>
     </row>
-    <row r="166" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
         <v>13</v>
       </c>
@@ -20471,20 +20434,20 @@
       <c r="BC166" s="16">
         <v>25.3</v>
       </c>
-      <c r="BD166" s="68">
+      <c r="BD166" s="16">
         <v>1012</v>
       </c>
-      <c r="BE166" s="68">
+      <c r="BE166" s="16">
         <v>44.3</v>
       </c>
       <c r="BF166" s="15"/>
-      <c r="BG166" s="74">
+      <c r="BG166" s="7">
         <v>2096</v>
       </c>
       <c r="BH166" s="4"/>
       <c r="BM166"/>
     </row>
-    <row r="167" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
         <v>13</v>
       </c>
@@ -20572,7 +20535,7 @@
       <c r="BC167" s="16">
         <v>25.6</v>
       </c>
-      <c r="BD167" s="68">
+      <c r="BD167" s="16">
         <v>1011</v>
       </c>
       <c r="BE167" s="16">
@@ -20585,7 +20548,7 @@
       <c r="BH167" s="4"/>
       <c r="BM167"/>
     </row>
-    <row r="168" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
         <v>13</v>
       </c>
@@ -20673,7 +20636,7 @@
       <c r="BC168" s="16">
         <v>25.6</v>
       </c>
-      <c r="BD168" s="68">
+      <c r="BD168" s="16">
         <v>1011</v>
       </c>
       <c r="BE168" s="16">
@@ -20686,7 +20649,7 @@
       <c r="BH168" s="4"/>
       <c r="BM168"/>
     </row>
-    <row r="169" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
         <v>13</v>
       </c>
@@ -20774,10 +20737,10 @@
       <c r="BC169" s="16">
         <v>25.6</v>
       </c>
-      <c r="BD169" s="68">
+      <c r="BD169" s="16">
         <v>1011</v>
       </c>
-      <c r="BE169" s="68">
+      <c r="BE169" s="16">
         <v>44.1</v>
       </c>
       <c r="BF169" s="15"/>
@@ -20787,7 +20750,7 @@
       <c r="BH169" s="4"/>
       <c r="BM169"/>
     </row>
-    <row r="170" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
         <v>13</v>
       </c>
@@ -20875,20 +20838,20 @@
       <c r="BC170" s="16">
         <v>26</v>
       </c>
-      <c r="BD170" s="68">
+      <c r="BD170" s="16">
         <v>1012</v>
       </c>
-      <c r="BE170" s="68">
+      <c r="BE170" s="16">
         <v>43</v>
       </c>
       <c r="BF170" s="15"/>
-      <c r="BG170" s="74">
+      <c r="BG170" s="7">
         <v>2096</v>
       </c>
       <c r="BH170" s="4"/>
       <c r="BM170"/>
     </row>
-    <row r="171" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
         <v>13</v>
       </c>
@@ -20976,20 +20939,20 @@
       <c r="BC171" s="16">
         <v>26</v>
       </c>
-      <c r="BD171" s="68">
+      <c r="BD171" s="16">
         <v>1012</v>
       </c>
-      <c r="BE171" s="68">
+      <c r="BE171" s="16">
         <v>43</v>
       </c>
       <c r="BF171" s="15"/>
-      <c r="BG171" s="74">
+      <c r="BG171" s="7">
         <v>2096</v>
       </c>
       <c r="BH171" s="4"/>
       <c r="BM171"/>
     </row>
-    <row r="172" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
         <v>13</v>
       </c>
@@ -21080,19 +21043,19 @@
       <c r="BD172" s="14">
         <v>1012</v>
       </c>
-      <c r="BE172" s="72">
+      <c r="BE172" s="37">
         <v>54</v>
       </c>
       <c r="BF172" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BG172" s="66">
+      <c r="BG172" s="4">
         <v>2096</v>
       </c>
       <c r="BH172" s="4"/>
       <c r="BM172"/>
     </row>
-    <row r="173" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
         <v>13</v>
       </c>
@@ -21173,22 +21136,22 @@
       <c r="BC173" s="22">
         <v>25.1</v>
       </c>
-      <c r="BD173" s="76">
+      <c r="BD173" s="67">
         <v>1012</v>
       </c>
-      <c r="BE173" s="72">
+      <c r="BE173" s="37">
         <v>54</v>
       </c>
       <c r="BF173" s="23">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BG173" s="66">
+      <c r="BG173" s="4">
         <v>2096</v>
       </c>
       <c r="BH173" s="4"/>
       <c r="BM173"/>
     </row>
-    <row r="174" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
         <v>43</v>
       </c>
@@ -21279,19 +21242,19 @@
       <c r="BD174" s="14">
         <v>1012</v>
       </c>
-      <c r="BE174" s="72">
+      <c r="BE174" s="37">
         <v>53</v>
       </c>
       <c r="BF174" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BG174" s="66">
+      <c r="BG174" s="4">
         <v>2096</v>
       </c>
       <c r="BH174" s="4"/>
       <c r="BM174"/>
     </row>
-    <row r="175" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
         <v>43</v>
       </c>
@@ -21382,7 +21345,7 @@
       <c r="BD175" s="14">
         <v>1012</v>
       </c>
-      <c r="BE175" s="72">
+      <c r="BE175" s="37">
         <v>53</v>
       </c>
       <c r="BF175" s="15">
@@ -21394,7 +21357,7 @@
       <c r="BH175" s="4"/>
       <c r="BM175"/>
     </row>
-    <row r="176" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
         <v>43</v>
       </c>
@@ -21485,19 +21448,19 @@
       <c r="BD176" s="14">
         <v>1012</v>
       </c>
-      <c r="BE176" s="72">
+      <c r="BE176" s="37">
         <v>53</v>
       </c>
       <c r="BF176" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BG176" s="66">
+      <c r="BG176" s="4">
         <v>2096</v>
       </c>
       <c r="BH176" s="4"/>
       <c r="BM176"/>
     </row>
-    <row r="177" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
         <v>43</v>
       </c>
@@ -21588,7 +21551,7 @@
       <c r="BD177" s="14">
         <v>1012</v>
       </c>
-      <c r="BE177" s="72">
+      <c r="BE177" s="37">
         <v>54</v>
       </c>
       <c r="BF177" s="15">
@@ -21600,7 +21563,7 @@
       <c r="BH177" s="4"/>
       <c r="BM177"/>
     </row>
-    <row r="178" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
         <v>43</v>
       </c>
@@ -21680,7 +21643,7 @@
       <c r="AW178" s="4"/>
       <c r="AX178" s="4"/>
       <c r="AY178" s="4"/>
-      <c r="AZ178" s="65">
+      <c r="AZ178" s="22">
         <v>117</v>
       </c>
       <c r="BA178" s="4"/>
@@ -21691,19 +21654,19 @@
       <c r="BD178" s="14">
         <v>1012</v>
       </c>
-      <c r="BE178" s="72">
+      <c r="BE178" s="37">
         <v>54</v>
       </c>
       <c r="BF178" s="15">
         <v>1.175</v>
       </c>
-      <c r="BG178" s="66">
+      <c r="BG178" s="4">
         <v>2096</v>
       </c>
       <c r="BH178" s="4"/>
       <c r="BM178"/>
     </row>
-    <row r="179" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
         <v>43</v>
       </c>
@@ -21794,19 +21757,19 @@
       <c r="BD179" s="14">
         <v>1011</v>
       </c>
-      <c r="BE179" s="72">
+      <c r="BE179" s="37">
         <v>54</v>
       </c>
       <c r="BF179" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BG179" s="66">
+      <c r="BG179" s="4">
         <v>2096</v>
       </c>
       <c r="BH179" s="4"/>
       <c r="BM179"/>
     </row>
-    <row r="180" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
         <v>13</v>
       </c>
@@ -21897,19 +21860,19 @@
       <c r="BD180" s="14">
         <v>1011</v>
       </c>
-      <c r="BE180" s="72">
+      <c r="BE180" s="37">
         <v>54</v>
       </c>
       <c r="BF180" s="15">
         <v>1.173</v>
       </c>
-      <c r="BG180" s="66">
+      <c r="BG180" s="4">
         <v>2096</v>
       </c>
       <c r="BH180" s="4"/>
       <c r="BM180"/>
     </row>
-    <row r="181" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
         <v>13</v>
       </c>
@@ -22000,19 +21963,19 @@
       <c r="BD181" s="14">
         <v>1011</v>
       </c>
-      <c r="BE181" s="72">
+      <c r="BE181" s="37">
         <v>54</v>
       </c>
       <c r="BF181" s="15">
         <v>1.173</v>
       </c>
-      <c r="BG181" s="66">
+      <c r="BG181" s="4">
         <v>2096</v>
       </c>
       <c r="BH181" s="4"/>
       <c r="BM181"/>
     </row>
-    <row r="182" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
         <v>13</v>
       </c>
@@ -22103,19 +22066,19 @@
       <c r="BD182" s="14">
         <v>1011</v>
       </c>
-      <c r="BE182" s="72">
+      <c r="BE182" s="37">
         <v>54</v>
       </c>
       <c r="BF182" s="15">
         <v>1.173</v>
       </c>
-      <c r="BG182" s="66">
+      <c r="BG182" s="4">
         <v>2096</v>
       </c>
       <c r="BH182" s="4"/>
       <c r="BM182"/>
     </row>
-    <row r="183" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
         <v>13</v>
       </c>
@@ -22206,19 +22169,19 @@
       <c r="BD183" s="14">
         <v>1011</v>
       </c>
-      <c r="BE183" s="72">
+      <c r="BE183" s="37">
         <v>54</v>
       </c>
       <c r="BF183" s="15">
         <v>1.173</v>
       </c>
-      <c r="BG183" s="66">
+      <c r="BG183" s="4">
         <v>2096</v>
       </c>
       <c r="BH183" s="4"/>
       <c r="BM183"/>
     </row>
-    <row r="184" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>43</v>
       </c>
@@ -22312,20 +22275,20 @@
       <c r="BD184" s="14">
         <v>1010</v>
       </c>
-      <c r="BE184" s="72">
+      <c r="BE184" s="37">
         <v>52</v>
       </c>
       <c r="BF184" s="15">
         <v>1.177</v>
       </c>
-      <c r="BG184" s="66">
+      <c r="BG184" s="4">
         <v>2096</v>
       </c>
       <c r="BH184" s="4"/>
       <c r="BI184" s="7"/>
       <c r="BM184"/>
     </row>
-    <row r="185" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>43</v>
       </c>
@@ -22432,7 +22395,7 @@
       <c r="BI185" s="7"/>
       <c r="BM185"/>
     </row>
-    <row r="186" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>43</v>
       </c>
@@ -22539,7 +22502,7 @@
       <c r="BI186" s="7"/>
       <c r="BM186"/>
     </row>
-    <row r="187" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>43</v>
       </c>
@@ -22633,20 +22596,20 @@
       <c r="BD187" s="14">
         <v>1010</v>
       </c>
-      <c r="BE187" s="72">
+      <c r="BE187" s="37">
         <v>51</v>
       </c>
       <c r="BF187" s="15">
         <v>1.173</v>
       </c>
-      <c r="BG187" s="66">
+      <c r="BG187" s="4">
         <v>2096</v>
       </c>
       <c r="BH187" s="4"/>
       <c r="BI187" s="7"/>
       <c r="BM187"/>
     </row>
-    <row r="188" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>43</v>
       </c>
@@ -22740,7 +22703,7 @@
       <c r="BD188" s="14">
         <v>1010</v>
       </c>
-      <c r="BE188" s="72">
+      <c r="BE188" s="37">
         <v>48</v>
       </c>
       <c r="BF188" s="15">
@@ -22753,7 +22716,7 @@
       <c r="BI188" s="7"/>
       <c r="BM188"/>
     </row>
-    <row r="189" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>43</v>
       </c>
@@ -22847,20 +22810,20 @@
       <c r="BD189" s="14">
         <v>1010</v>
       </c>
-      <c r="BE189" s="72">
+      <c r="BE189" s="37">
         <v>48</v>
       </c>
       <c r="BF189" s="15">
         <v>1.1719999999999999</v>
       </c>
-      <c r="BG189" s="66">
+      <c r="BG189" s="4">
         <v>2096</v>
       </c>
       <c r="BH189" s="4"/>
       <c r="BI189" s="7"/>
       <c r="BM189"/>
     </row>
-    <row r="190" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>43</v>
       </c>
@@ -22954,7 +22917,7 @@
       <c r="BD190" s="14">
         <v>1010</v>
       </c>
-      <c r="BE190" s="72">
+      <c r="BE190" s="37">
         <v>52</v>
       </c>
       <c r="BF190" s="15">
@@ -22967,7 +22930,7 @@
       <c r="BI190" s="7"/>
       <c r="BM190"/>
     </row>
-    <row r="191" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>43</v>
       </c>
@@ -23061,7 +23024,7 @@
       <c r="BD191" s="14">
         <v>1010</v>
       </c>
-      <c r="BE191" s="72">
+      <c r="BE191" s="37">
         <v>52</v>
       </c>
       <c r="BF191" s="15">
@@ -23074,7 +23037,7 @@
       <c r="BI191" s="7"/>
       <c r="BM191"/>
     </row>
-    <row r="192" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>43</v>
       </c>
@@ -23168,7 +23131,7 @@
       <c r="BD192" s="14">
         <v>1010</v>
       </c>
-      <c r="BE192" s="72">
+      <c r="BE192" s="37">
         <v>50</v>
       </c>
       <c r="BF192" s="15">
@@ -23181,7 +23144,7 @@
       <c r="BI192" s="7"/>
       <c r="BM192"/>
     </row>
-    <row r="193" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>43</v>
       </c>
@@ -23275,7 +23238,7 @@
       <c r="BD193" s="14">
         <v>1010</v>
       </c>
-      <c r="BE193" s="72">
+      <c r="BE193" s="37">
         <v>48</v>
       </c>
       <c r="BF193" s="15">
@@ -23288,7 +23251,7 @@
       <c r="BI193" s="7"/>
       <c r="BM193"/>
     </row>
-    <row r="194" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>43</v>
       </c>
@@ -23382,7 +23345,7 @@
       <c r="BD194" s="14">
         <v>1010</v>
       </c>
-      <c r="BE194" s="72">
+      <c r="BE194" s="37">
         <v>48</v>
       </c>
       <c r="BF194" s="15">
@@ -23395,7 +23358,7 @@
       <c r="BI194" s="7"/>
       <c r="BM194"/>
     </row>
-    <row r="195" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>43</v>
       </c>
@@ -23489,20 +23452,20 @@
       <c r="BD195" s="14">
         <v>1009</v>
       </c>
-      <c r="BE195" s="72">
+      <c r="BE195" s="37">
         <v>50</v>
       </c>
       <c r="BF195" s="15">
         <v>1.17</v>
       </c>
-      <c r="BG195" s="66">
+      <c r="BG195" s="4">
         <v>2096</v>
       </c>
       <c r="BH195" s="4"/>
       <c r="BI195" s="7"/>
       <c r="BM195"/>
     </row>
-    <row r="196" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>43</v>
       </c>
@@ -23596,20 +23559,20 @@
       <c r="BD196" s="14">
         <v>1010</v>
       </c>
-      <c r="BE196" s="72">
+      <c r="BE196" s="37">
         <v>52</v>
       </c>
       <c r="BF196" s="15">
         <v>1.177</v>
       </c>
-      <c r="BG196" s="66">
+      <c r="BG196" s="4">
         <v>2096</v>
       </c>
       <c r="BH196" s="4"/>
       <c r="BI196" s="7"/>
       <c r="BM196"/>
     </row>
-    <row r="197" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>43</v>
       </c>
@@ -23703,7 +23666,7 @@
       <c r="BD197" s="14">
         <v>1010</v>
       </c>
-      <c r="BE197" s="72">
+      <c r="BE197" s="37">
         <v>52</v>
       </c>
       <c r="BF197" s="15">
@@ -23716,7 +23679,7 @@
       <c r="BI197" s="7"/>
       <c r="BM197"/>
     </row>
-    <row r="198" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>43</v>
       </c>
@@ -23810,7 +23773,7 @@
       <c r="BD198" s="14">
         <v>1010</v>
       </c>
-      <c r="BE198" s="72">
+      <c r="BE198" s="37">
         <v>51</v>
       </c>
       <c r="BF198" s="15">
@@ -23823,7 +23786,7 @@
       <c r="BI198" s="7"/>
       <c r="BM198"/>
     </row>
-    <row r="199" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>43</v>
       </c>
@@ -23914,20 +23877,20 @@
       <c r="BD199" s="14">
         <v>1010</v>
       </c>
-      <c r="BE199" s="72">
+      <c r="BE199" s="37">
         <v>48</v>
       </c>
       <c r="BF199" s="15">
         <v>1.173</v>
       </c>
-      <c r="BG199" s="66">
+      <c r="BG199" s="4">
         <v>2096</v>
       </c>
       <c r="BH199" s="4"/>
       <c r="BI199" s="7"/>
       <c r="BM199"/>
     </row>
-    <row r="200" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>43</v>
       </c>
@@ -24021,7 +23984,7 @@
       <c r="BD200" s="14">
         <v>1009</v>
       </c>
-      <c r="BE200" s="72">
+      <c r="BE200" s="37">
         <v>50</v>
       </c>
       <c r="BF200" s="15">
@@ -24034,7 +23997,7 @@
       <c r="BI200" s="7"/>
       <c r="BM200"/>
     </row>
-    <row r="201" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>43</v>
       </c>
@@ -24128,20 +24091,20 @@
       <c r="BD201" s="14">
         <v>1009</v>
       </c>
-      <c r="BE201" s="72">
+      <c r="BE201" s="37">
         <v>50</v>
       </c>
       <c r="BF201" s="15">
         <v>1.17</v>
       </c>
-      <c r="BG201" s="66">
+      <c r="BG201" s="4">
         <v>2096</v>
       </c>
       <c r="BH201" s="4"/>
       <c r="BI201" s="7"/>
       <c r="BM201"/>
     </row>
-    <row r="202" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>43</v>
       </c>
@@ -24235,20 +24198,20 @@
       <c r="BD202" s="14">
         <v>1009</v>
       </c>
-      <c r="BE202" s="72">
+      <c r="BE202" s="37">
         <v>50</v>
       </c>
       <c r="BF202" s="15">
         <v>1.17</v>
       </c>
-      <c r="BG202" s="66">
+      <c r="BG202" s="4">
         <v>2096</v>
       </c>
       <c r="BH202" s="4"/>
       <c r="BI202" s="7"/>
       <c r="BM202"/>
     </row>
-    <row r="203" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>13</v>
       </c>
@@ -24357,7 +24320,7 @@
       <c r="BI203" s="7"/>
       <c r="BM203"/>
     </row>
-    <row r="204" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>13</v>
       </c>
@@ -24466,7 +24429,7 @@
       <c r="BI204" s="7"/>
       <c r="BM204"/>
     </row>
-    <row r="205" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>13</v>
       </c>
@@ -24575,7 +24538,7 @@
       <c r="BI205" s="7"/>
       <c r="BM205"/>
     </row>
-    <row r="206" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>13</v>
       </c>
@@ -24671,7 +24634,7 @@
       <c r="BD206" s="14">
         <v>1009</v>
       </c>
-      <c r="BE206" s="72">
+      <c r="BE206" s="37">
         <v>59</v>
       </c>
       <c r="BF206" s="15">
@@ -24684,7 +24647,7 @@
       <c r="BI206" s="7"/>
       <c r="BM206"/>
     </row>
-    <row r="207" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>13</v>
       </c>
@@ -24780,7 +24743,7 @@
       <c r="BD207" s="14">
         <v>1009</v>
       </c>
-      <c r="BE207" s="72">
+      <c r="BE207" s="37">
         <v>60</v>
       </c>
       <c r="BF207" s="15">
@@ -24793,7 +24756,7 @@
       <c r="BI207" s="7"/>
       <c r="BM207"/>
     </row>
-    <row r="208" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>13</v>
       </c>
@@ -24889,20 +24852,20 @@
       <c r="BD208" s="14">
         <v>1009</v>
       </c>
-      <c r="BE208" s="72">
+      <c r="BE208" s="37">
         <v>58</v>
       </c>
       <c r="BF208" s="15">
         <v>1.171</v>
       </c>
-      <c r="BG208" s="66">
+      <c r="BG208" s="4">
         <v>2096</v>
       </c>
       <c r="BH208" s="4"/>
       <c r="BI208" s="7"/>
       <c r="BM208"/>
     </row>
-    <row r="209" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>13</v>
       </c>
@@ -24996,20 +24959,20 @@
       <c r="BD209" s="14">
         <v>1009</v>
       </c>
-      <c r="BE209" s="72">
+      <c r="BE209" s="37">
         <v>58</v>
       </c>
       <c r="BF209" s="15">
         <v>1.171</v>
       </c>
-      <c r="BG209" s="66">
+      <c r="BG209" s="4">
         <v>2096</v>
       </c>
       <c r="BH209" s="4"/>
       <c r="BI209" s="7"/>
       <c r="BM209"/>
     </row>
-    <row r="210" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>13</v>
       </c>
@@ -25105,20 +25068,20 @@
       <c r="BD210" s="14">
         <v>1009</v>
       </c>
-      <c r="BE210" s="72">
+      <c r="BE210" s="37">
         <v>58</v>
       </c>
       <c r="BF210" s="15">
         <v>1.17</v>
       </c>
-      <c r="BG210" s="66">
+      <c r="BG210" s="4">
         <v>2096</v>
       </c>
       <c r="BH210" s="4"/>
       <c r="BI210" s="7"/>
       <c r="BM210"/>
     </row>
-    <row r="211" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>13</v>
       </c>
@@ -25214,20 +25177,20 @@
       <c r="BD211" s="14">
         <v>1009</v>
       </c>
-      <c r="BE211" s="72">
+      <c r="BE211" s="37">
         <v>62</v>
       </c>
       <c r="BF211" s="15">
         <v>1.175</v>
       </c>
-      <c r="BG211" s="66">
+      <c r="BG211" s="4">
         <v>2096</v>
       </c>
       <c r="BH211" s="4"/>
       <c r="BI211" s="7"/>
       <c r="BM211"/>
     </row>
-    <row r="212" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>13</v>
       </c>
@@ -25311,7 +25274,7 @@
       <c r="BD212" s="14">
         <v>1009</v>
       </c>
-      <c r="BE212" s="72">
+      <c r="BE212" s="37">
         <v>61</v>
       </c>
       <c r="BF212" s="15">
@@ -25326,7 +25289,7 @@
       <c r="BI212" s="7"/>
       <c r="BM212"/>
     </row>
-    <row r="213" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>13</v>
       </c>
@@ -25411,7 +25374,7 @@
       <c r="AW213" s="4"/>
       <c r="AX213" s="4"/>
       <c r="AY213" s="4"/>
-      <c r="AZ213" s="65">
+      <c r="AZ213" s="22">
         <v>117</v>
       </c>
       <c r="BA213" s="4"/>
@@ -25422,20 +25385,20 @@
       <c r="BD213" s="14">
         <v>1009</v>
       </c>
-      <c r="BE213" s="72">
+      <c r="BE213" s="37">
         <v>60</v>
       </c>
       <c r="BF213" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BG213" s="66">
+      <c r="BG213" s="4">
         <v>2096</v>
       </c>
       <c r="BH213" s="4"/>
       <c r="BI213" s="7"/>
       <c r="BM213"/>
     </row>
-    <row r="214" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>13</v>
       </c>
@@ -25531,20 +25494,20 @@
       <c r="BD214" s="14">
         <v>1009</v>
       </c>
-      <c r="BE214" s="72">
+      <c r="BE214" s="37">
         <v>60</v>
       </c>
       <c r="BF214" s="15">
         <v>1.173</v>
       </c>
-      <c r="BG214" s="66">
+      <c r="BG214" s="4">
         <v>2096</v>
       </c>
       <c r="BH214" s="4"/>
       <c r="BI214" s="7"/>
       <c r="BM214"/>
     </row>
-    <row r="215" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>13</v>
       </c>
@@ -25629,7 +25592,7 @@
       <c r="AW215" s="4"/>
       <c r="AX215" s="4"/>
       <c r="AY215" s="4"/>
-      <c r="AZ215" s="65">
+      <c r="AZ215" s="22">
         <v>117</v>
       </c>
       <c r="BA215" s="4"/>
@@ -25640,20 +25603,20 @@
       <c r="BD215" s="14">
         <v>1009</v>
       </c>
-      <c r="BE215" s="72">
+      <c r="BE215" s="37">
         <v>60</v>
       </c>
       <c r="BF215" s="15">
         <v>1.173</v>
       </c>
-      <c r="BG215" s="66">
+      <c r="BG215" s="4">
         <v>2096</v>
       </c>
       <c r="BH215" s="4"/>
       <c r="BI215" s="7"/>
       <c r="BM215"/>
     </row>
-    <row r="216" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>13</v>
       </c>
@@ -25738,7 +25701,7 @@
       <c r="AW216" s="4"/>
       <c r="AX216" s="4"/>
       <c r="AY216" s="4"/>
-      <c r="AZ216" s="65">
+      <c r="AZ216" s="22">
         <v>117</v>
       </c>
       <c r="BA216" s="4"/>
@@ -25749,20 +25712,20 @@
       <c r="BD216" s="14">
         <v>1009</v>
       </c>
-      <c r="BE216" s="72">
+      <c r="BE216" s="37">
         <v>58</v>
       </c>
       <c r="BF216" s="15">
         <v>1.171</v>
       </c>
-      <c r="BG216" s="66">
+      <c r="BG216" s="4">
         <v>2096</v>
       </c>
       <c r="BH216" s="4"/>
       <c r="BI216" s="7"/>
       <c r="BM216"/>
     </row>
-    <row r="217" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>13</v>
       </c>
@@ -25858,20 +25821,20 @@
       <c r="BD217" s="14">
         <v>1009</v>
       </c>
-      <c r="BE217" s="72">
+      <c r="BE217" s="37">
         <v>61</v>
       </c>
       <c r="BF217" s="15">
         <v>1.1759999999999999</v>
       </c>
-      <c r="BG217" s="66">
+      <c r="BG217" s="4">
         <v>2096</v>
       </c>
       <c r="BH217" s="4"/>
       <c r="BI217" s="7"/>
       <c r="BM217"/>
     </row>
-    <row r="218" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>13</v>
       </c>
@@ -25967,20 +25930,20 @@
       <c r="BD218" s="14">
         <v>1009</v>
       </c>
-      <c r="BE218" s="72">
+      <c r="BE218" s="37">
         <v>62</v>
       </c>
       <c r="BF218" s="15">
         <v>1.175</v>
       </c>
-      <c r="BG218" s="66">
+      <c r="BG218" s="4">
         <v>2096</v>
       </c>
       <c r="BH218" s="4"/>
       <c r="BI218" s="7"/>
       <c r="BM218"/>
     </row>
-    <row r="219" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>13</v>
       </c>
@@ -26076,20 +26039,20 @@
       <c r="BD219" s="14">
         <v>1009</v>
       </c>
-      <c r="BE219" s="72">
+      <c r="BE219" s="37">
         <v>61</v>
       </c>
       <c r="BF219" s="15">
         <v>1.175</v>
       </c>
-      <c r="BG219" s="66">
+      <c r="BG219" s="4">
         <v>2096</v>
       </c>
       <c r="BH219" s="4"/>
       <c r="BI219" s="7"/>
       <c r="BM219"/>
     </row>
-    <row r="220" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>13</v>
       </c>
@@ -26185,20 +26148,20 @@
       <c r="BD220" s="14">
         <v>1009</v>
       </c>
-      <c r="BE220" s="72">
+      <c r="BE220" s="37">
         <v>59</v>
       </c>
       <c r="BF220" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BG220" s="66">
+      <c r="BG220" s="4">
         <v>2096</v>
       </c>
       <c r="BH220" s="4"/>
       <c r="BI220" s="7"/>
       <c r="BM220"/>
     </row>
-    <row r="221" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>13</v>
       </c>
@@ -26294,20 +26257,20 @@
       <c r="BD221" s="14">
         <v>1009</v>
       </c>
-      <c r="BE221" s="72">
+      <c r="BE221" s="37">
         <v>60</v>
       </c>
       <c r="BF221" s="15">
         <v>1.173</v>
       </c>
-      <c r="BG221" s="66">
+      <c r="BG221" s="4">
         <v>2096</v>
       </c>
       <c r="BH221" s="4"/>
       <c r="BI221" s="7"/>
       <c r="BM221"/>
     </row>
-    <row r="222" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>13</v>
       </c>
@@ -26403,20 +26366,20 @@
       <c r="BD222" s="14">
         <v>1009</v>
       </c>
-      <c r="BE222" s="72">
+      <c r="BE222" s="37">
         <v>58</v>
       </c>
       <c r="BF222" s="15">
         <v>1.171</v>
       </c>
-      <c r="BG222" s="66">
+      <c r="BG222" s="4">
         <v>2096</v>
       </c>
       <c r="BH222" s="4"/>
       <c r="BI222" s="7"/>
       <c r="BM222"/>
     </row>
-    <row r="223" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>13</v>
       </c>
@@ -26512,20 +26475,20 @@
       <c r="BD223" s="14">
         <v>1009</v>
       </c>
-      <c r="BE223" s="72">
+      <c r="BE223" s="37">
         <v>58</v>
       </c>
       <c r="BF223" s="15">
         <v>1.171</v>
       </c>
-      <c r="BG223" s="66">
+      <c r="BG223" s="4">
         <v>2096</v>
       </c>
       <c r="BH223" s="4"/>
       <c r="BI223" s="7"/>
       <c r="BM223"/>
     </row>
-    <row r="224" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>13</v>
       </c>
@@ -26621,20 +26584,20 @@
       <c r="BD224" s="14">
         <v>1009</v>
       </c>
-      <c r="BE224" s="72">
+      <c r="BE224" s="37">
         <v>58</v>
       </c>
       <c r="BF224" s="15">
         <v>1.171</v>
       </c>
-      <c r="BG224" s="66">
+      <c r="BG224" s="4">
         <v>2096</v>
       </c>
       <c r="BH224" s="4"/>
       <c r="BI224" s="7"/>
       <c r="BM224"/>
     </row>
-    <row r="225" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>13</v>
       </c>
@@ -26730,20 +26693,20 @@
       <c r="BD225" s="14">
         <v>1009</v>
       </c>
-      <c r="BE225" s="72">
+      <c r="BE225" s="37">
         <v>58</v>
       </c>
       <c r="BF225" s="15">
         <v>1.17</v>
       </c>
-      <c r="BG225" s="66">
+      <c r="BG225" s="4">
         <v>2096</v>
       </c>
       <c r="BH225" s="4"/>
       <c r="BI225" s="7"/>
       <c r="BM225"/>
     </row>
-    <row r="226" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>43</v>
       </c>
@@ -26852,7 +26815,7 @@
       <c r="BK226" s="7"/>
       <c r="BM226"/>
     </row>
-    <row r="227" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>43</v>
       </c>
@@ -26961,7 +26924,7 @@
       <c r="BK227" s="7"/>
       <c r="BM227"/>
     </row>
-    <row r="228" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>43</v>
       </c>
@@ -27067,7 +27030,7 @@
       <c r="BK228" s="7"/>
       <c r="BM228"/>
     </row>
-    <row r="229" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>43</v>
       </c>
@@ -27176,7 +27139,7 @@
       <c r="BK229" s="7"/>
       <c r="BM229"/>
     </row>
-    <row r="230" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>43</v>
       </c>
@@ -27285,7 +27248,7 @@
       <c r="BK230" s="7"/>
       <c r="BM230"/>
     </row>
-    <row r="231" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>43</v>
       </c>
@@ -27387,14 +27350,14 @@
       <c r="BF231" s="46">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BG231" s="64">
+      <c r="BG231" s="2">
         <v>2096</v>
       </c>
       <c r="BH231" s="2"/>
       <c r="BK231" s="7"/>
       <c r="BM231"/>
     </row>
-    <row r="232" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>43</v>
       </c>
@@ -27493,14 +27456,14 @@
       <c r="BF232" s="46">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BG232" s="64">
+      <c r="BG232" s="2">
         <v>2096</v>
       </c>
       <c r="BH232" s="2"/>
       <c r="BK232" s="7"/>
       <c r="BM232"/>
     </row>
-    <row r="233" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>43</v>
       </c>
@@ -27609,7 +27572,7 @@
       <c r="BK233" s="7"/>
       <c r="BM233"/>
     </row>
-    <row r="234" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>43</v>
       </c>
@@ -27718,7 +27681,7 @@
       <c r="BK234" s="7"/>
       <c r="BM234"/>
     </row>
-    <row r="235" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>43</v>
       </c>
@@ -27827,7 +27790,7 @@
       <c r="BK235" s="7"/>
       <c r="BM235"/>
     </row>
-    <row r="236" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>43</v>
       </c>
@@ -27936,7 +27899,7 @@
       <c r="BK236" s="7"/>
       <c r="BM236"/>
     </row>
-    <row r="237" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>43</v>
       </c>
@@ -28045,7 +28008,7 @@
       <c r="BK237" s="7"/>
       <c r="BM237"/>
     </row>
-    <row r="238" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>43</v>
       </c>
@@ -28147,14 +28110,14 @@
       <c r="BF238" s="46">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BG238" s="64">
+      <c r="BG238" s="2">
         <v>2096</v>
       </c>
       <c r="BH238" s="2"/>
       <c r="BK238" s="7"/>
       <c r="BM238"/>
     </row>
-    <row r="239" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>43</v>
       </c>
@@ -28263,7 +28226,7 @@
       <c r="BK239" s="7"/>
       <c r="BM239"/>
     </row>
-    <row r="240" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>43</v>
       </c>
@@ -28372,7 +28335,7 @@
       <c r="BK240" s="7"/>
       <c r="BM240"/>
     </row>
-    <row r="241" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>43</v>
       </c>
@@ -28481,7 +28444,7 @@
       <c r="BK241" s="7"/>
       <c r="BM241"/>
     </row>
-    <row r="242" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>43</v>
       </c>
@@ -28590,7 +28553,7 @@
       <c r="BK242" s="7"/>
       <c r="BM242"/>
     </row>
-    <row r="243" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>43</v>
       </c>
@@ -28699,7 +28662,7 @@
       <c r="BK243" s="7"/>
       <c r="BM243"/>
     </row>
-    <row r="244" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>43</v>
       </c>
@@ -28801,7 +28764,7 @@
       <c r="BF244" s="46">
         <v>1.163</v>
       </c>
-      <c r="BG244" s="64">
+      <c r="BG244" s="2">
         <v>2096</v>
       </c>
       <c r="BH244" s="2"/>
@@ -29452,14 +29415,14 @@
       <c r="BF250" s="46">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BG250" s="64">
+      <c r="BG250" s="2">
         <v>2096</v>
       </c>
       <c r="BH250" s="2"/>
       <c r="BK250" s="7"/>
       <c r="BM250"/>
     </row>
-    <row r="251" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>43</v>
       </c>
@@ -29568,7 +29531,7 @@
       <c r="BK251" s="7"/>
       <c r="BM251"/>
     </row>
-    <row r="252" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>43</v>
       </c>
@@ -29677,7 +29640,7 @@
       <c r="BK252" s="7"/>
       <c r="BM252"/>
     </row>
-    <row r="253" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>43</v>
       </c>
@@ -29786,7 +29749,7 @@
       <c r="BK253" s="7"/>
       <c r="BM253"/>
     </row>
-    <row r="254" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>43</v>
       </c>
@@ -29895,7 +29858,7 @@
       <c r="BK254" s="7"/>
       <c r="BM254"/>
     </row>
-    <row r="255" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>43</v>
       </c>
@@ -30001,7 +29964,7 @@
       <c r="BK255" s="7"/>
       <c r="BM255"/>
     </row>
-    <row r="256" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>43</v>
       </c>
@@ -30100,14 +30063,14 @@
       <c r="BF256" s="46">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BG256" s="64">
+      <c r="BG256" s="2">
         <v>2096</v>
       </c>
       <c r="BH256" s="2"/>
       <c r="BK256" s="7"/>
       <c r="BM256"/>
     </row>
-    <row r="257" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>43</v>
       </c>
@@ -30216,7 +30179,7 @@
       <c r="BK257" s="7"/>
       <c r="BM257"/>
     </row>
-    <row r="258" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>43</v>
       </c>
@@ -30325,7 +30288,7 @@
       <c r="BK258" s="7"/>
       <c r="BM258"/>
     </row>
-    <row r="259" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>43</v>
       </c>
@@ -30429,7 +30392,7 @@
       <c r="BK259" s="7"/>
       <c r="BM259"/>
     </row>
-    <row r="260" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>43</v>
       </c>
@@ -30535,7 +30498,7 @@
       <c r="BK260" s="7"/>
       <c r="BM260"/>
     </row>
-    <row r="261" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>43</v>
       </c>
@@ -30641,7 +30604,7 @@
       <c r="BK261" s="7"/>
       <c r="BM261"/>
     </row>
-    <row r="262" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
         <v>13</v>
       </c>
@@ -30743,14 +30706,14 @@
       <c r="BF262" s="46">
         <v>1.171</v>
       </c>
-      <c r="BG262" s="64">
+      <c r="BG262" s="2">
         <v>2096</v>
       </c>
       <c r="BH262" s="2"/>
       <c r="BK262" s="7"/>
       <c r="BM262"/>
     </row>
-    <row r="263" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>13</v>
       </c>
@@ -30852,14 +30815,14 @@
       <c r="BF263" s="46">
         <v>1.17</v>
       </c>
-      <c r="BG263" s="64">
+      <c r="BG263" s="2">
         <v>2096</v>
       </c>
       <c r="BH263" s="2"/>
       <c r="BK263" s="7"/>
       <c r="BM263"/>
     </row>
-    <row r="264" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>13</v>
       </c>
@@ -30961,14 +30924,14 @@
       <c r="BF264" s="46">
         <v>1.167</v>
       </c>
-      <c r="BG264" s="64">
+      <c r="BG264" s="2">
         <v>2096</v>
       </c>
       <c r="BH264" s="2"/>
       <c r="BK264" s="7"/>
       <c r="BM264"/>
     </row>
-    <row r="265" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>13</v>
       </c>
@@ -31067,14 +31030,14 @@
       <c r="BF265" s="46">
         <v>1.163</v>
       </c>
-      <c r="BG265" s="64">
+      <c r="BG265" s="2">
         <v>2096</v>
       </c>
       <c r="BH265" s="2"/>
       <c r="BK265" s="7"/>
       <c r="BM265"/>
     </row>
-    <row r="266" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>13</v>
       </c>
@@ -31173,14 +31136,14 @@
       <c r="BF266" s="46">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BG266" s="64">
+      <c r="BG266" s="2">
         <v>2096</v>
       </c>
       <c r="BH266" s="2"/>
       <c r="BK266" s="7"/>
       <c r="BM266"/>
     </row>
-    <row r="267" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>13</v>
       </c>
@@ -31196,7 +31159,7 @@
       <c r="E267" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="F267" s="64" t="s">
+      <c r="F267" s="2" t="s">
         <v>552</v>
       </c>
       <c r="G267" s="7">
@@ -31279,7 +31242,7 @@
       <c r="BF267" s="46">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BG267" s="64">
+      <c r="BG267" s="2">
         <v>2096</v>
       </c>
       <c r="BH267" s="2"/>
@@ -31291,7 +31254,7 @@
         <v>13</v>
       </c>
       <c r="B268" s="60" t="s">
-        <v>589</v>
+        <v>14</v>
       </c>
       <c r="C268" s="3">
         <v>45274</v>
@@ -31300,7 +31263,7 @@
         <v>1</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F268" s="63" t="s">
         <v>383</v>
@@ -31330,7 +31293,7 @@
         <v>758.9</v>
       </c>
       <c r="R268" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="S268" s="4" t="s">
         <v>579</v>
@@ -31399,7 +31362,7 @@
         <v>13</v>
       </c>
       <c r="B269" s="60" t="s">
-        <v>589</v>
+        <v>14</v>
       </c>
       <c r="C269" s="3">
         <v>45274</v>
@@ -31408,7 +31371,7 @@
         <v>2</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>556</v>
@@ -31441,7 +31404,7 @@
         <v>356</v>
       </c>
       <c r="S269" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="T269" s="4"/>
       <c r="U269" s="4" t="s">
@@ -31507,7 +31470,7 @@
         <v>13</v>
       </c>
       <c r="B270" s="60" t="s">
-        <v>589</v>
+        <v>14</v>
       </c>
       <c r="C270" s="3">
         <v>45274</v>
@@ -31516,7 +31479,7 @@
         <v>3</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F270" s="2" t="s">
         <v>556</v>
@@ -31549,7 +31512,7 @@
         <v>568</v>
       </c>
       <c r="S270" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="T270" s="4"/>
       <c r="U270" s="4" t="s">
@@ -31615,7 +31578,7 @@
         <v>13</v>
       </c>
       <c r="B271" s="60" t="s">
-        <v>589</v>
+        <v>14</v>
       </c>
       <c r="C271" s="3">
         <v>45274</v>
@@ -31624,7 +31587,7 @@
         <v>4</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F271" s="2" t="s">
         <v>556</v>
@@ -31657,7 +31620,7 @@
         <v>569</v>
       </c>
       <c r="S271" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="T271" s="4"/>
       <c r="U271" s="4" t="s">
@@ -31723,7 +31686,7 @@
         <v>13</v>
       </c>
       <c r="B272" s="60" t="s">
-        <v>589</v>
+        <v>14</v>
       </c>
       <c r="C272" s="3">
         <v>45274</v>
@@ -31732,7 +31695,7 @@
         <v>5</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F272" s="63" t="s">
         <v>383</v>
@@ -31762,7 +31725,7 @@
         <v>758</v>
       </c>
       <c r="R272" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="S272" s="4" t="s">
         <v>579</v>
@@ -31831,7 +31794,7 @@
         <v>13</v>
       </c>
       <c r="B273" s="60" t="s">
-        <v>589</v>
+        <v>14</v>
       </c>
       <c r="C273" s="3">
         <v>45274</v>
@@ -31840,9 +31803,9 @@
         <v>6</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="F273" s="64" t="s">
+        <v>594</v>
+      </c>
+      <c r="F273" s="2" t="s">
         <v>556</v>
       </c>
       <c r="G273" s="7">
@@ -31873,7 +31836,7 @@
         <v>356</v>
       </c>
       <c r="S273" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="T273" s="4"/>
       <c r="U273" s="4" t="s">
@@ -31939,7 +31902,7 @@
         <v>13</v>
       </c>
       <c r="B274" s="60" t="s">
-        <v>589</v>
+        <v>14</v>
       </c>
       <c r="C274" s="3">
         <v>45274</v>
@@ -31948,9 +31911,9 @@
         <v>7</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="F274" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F274" s="2" t="s">
         <v>556</v>
       </c>
       <c r="G274" s="7">
@@ -31981,7 +31944,7 @@
         <v>568</v>
       </c>
       <c r="S274" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="T274" s="4"/>
       <c r="U274" s="4" t="s">
@@ -32047,7 +32010,7 @@
         <v>13</v>
       </c>
       <c r="B275" s="60" t="s">
-        <v>589</v>
+        <v>14</v>
       </c>
       <c r="C275" s="3">
         <v>45274</v>
@@ -32056,9 +32019,9 @@
         <v>8</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="F275" s="64" t="s">
+        <v>596</v>
+      </c>
+      <c r="F275" s="2" t="s">
         <v>556</v>
       </c>
       <c r="G275" s="7">
@@ -32089,7 +32052,7 @@
         <v>569</v>
       </c>
       <c r="S275" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="T275" s="4"/>
       <c r="U275" s="4" t="s">
@@ -32150,7 +32113,7 @@
       <c r="BH275" s="2"/>
       <c r="BM275"/>
     </row>
-    <row r="276" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
         <v>13</v>
       </c>
@@ -32252,13 +32215,13 @@
       <c r="BF276" s="46">
         <v>1.169</v>
       </c>
-      <c r="BG276" s="64">
+      <c r="BG276" s="2">
         <v>2096</v>
       </c>
       <c r="BH276" s="2"/>
       <c r="BM276"/>
     </row>
-    <row r="277" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>13</v>
       </c>
@@ -32366,7 +32329,7 @@
       <c r="BH277" s="2"/>
       <c r="BM277"/>
     </row>
-    <row r="278" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
         <v>13</v>
       </c>
@@ -32474,7 +32437,7 @@
       <c r="BH278" s="2"/>
       <c r="BM278"/>
     </row>
-    <row r="279" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>13</v>
       </c>
@@ -32582,7 +32545,7 @@
       <c r="BH279" s="2"/>
       <c r="BM279"/>
     </row>
-    <row r="280" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>13</v>
       </c>
@@ -32690,7 +32653,7 @@
       <c r="BH280" s="2"/>
       <c r="BM280"/>
     </row>
-    <row r="281" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>13</v>
       </c>
@@ -32792,13 +32755,13 @@
       <c r="BF281" s="46">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BG281" s="64">
+      <c r="BG281" s="2">
         <v>2096</v>
       </c>
       <c r="BH281" s="2"/>
       <c r="BM281"/>
     </row>
-    <row r="282" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
         <v>13</v>
       </c>
@@ -32898,13 +32861,13 @@
       <c r="BF282" s="46">
         <v>1.161</v>
       </c>
-      <c r="BG282" s="64">
+      <c r="BG282" s="2">
         <v>2096</v>
       </c>
       <c r="BH282" s="2"/>
       <c r="BM282"/>
     </row>
-    <row r="283" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
         <v>13</v>
       </c>
@@ -33006,13 +32969,13 @@
       <c r="BF283" s="46">
         <v>1.161</v>
       </c>
-      <c r="BG283" s="64">
+      <c r="BG283" s="2">
         <v>2096</v>
       </c>
       <c r="BH283" s="2"/>
       <c r="BM283"/>
     </row>
-    <row r="284" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
         <v>13</v>
       </c>
@@ -33111,13 +33074,13 @@
       <c r="BF284" s="46">
         <v>1.161</v>
       </c>
-      <c r="BG284" s="64">
+      <c r="BG284" s="2">
         <v>2096</v>
       </c>
       <c r="BH284" s="2"/>
       <c r="BM284"/>
     </row>
-    <row r="285" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
         <v>381</v>
       </c>
@@ -33208,7 +33171,7 @@
       <c r="BF285" s="46">
         <v>1.169</v>
       </c>
-      <c r="BG285" s="64">
+      <c r="BG285" s="2">
         <v>2096</v>
       </c>
       <c r="BH285" s="2" t="s">
@@ -33216,7 +33179,7 @@
       </c>
       <c r="BM285"/>
     </row>
-    <row r="286" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
         <v>381</v>
       </c>
@@ -33307,7 +33270,7 @@
       <c r="BF286" s="46">
         <v>1.167</v>
       </c>
-      <c r="BG286" s="64">
+      <c r="BG286" s="2">
         <v>2096</v>
       </c>
       <c r="BH286" s="2" t="s">
@@ -33315,7 +33278,7 @@
       </c>
       <c r="BM286"/>
     </row>
-    <row r="287" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
         <v>381</v>
       </c>
@@ -33406,7 +33369,7 @@
       <c r="BF287" s="46">
         <v>1.1659999999999999</v>
       </c>
-      <c r="BG287" s="64">
+      <c r="BG287" s="2">
         <v>2096</v>
       </c>
       <c r="BH287" s="2" t="s">
@@ -33414,7 +33377,7 @@
       </c>
       <c r="BM287"/>
     </row>
-    <row r="288" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
         <v>381</v>
       </c>
@@ -33505,7 +33468,7 @@
       <c r="BF288" s="46">
         <v>1.1659999999999999</v>
       </c>
-      <c r="BG288" s="64">
+      <c r="BG288" s="2">
         <v>2096</v>
       </c>
       <c r="BH288" s="2" t="s">
@@ -33513,7 +33476,7 @@
       </c>
       <c r="BM288"/>
     </row>
-    <row r="289" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
         <v>43</v>
       </c>
@@ -33621,7 +33584,7 @@
       <c r="BH289" s="2"/>
       <c r="BM289"/>
     </row>
-    <row r="290" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
         <v>43</v>
       </c>
@@ -33729,7 +33692,7 @@
       <c r="BH290" s="2"/>
       <c r="BM290"/>
     </row>
-    <row r="291" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
         <v>43</v>
       </c>
@@ -33837,7 +33800,7 @@
       <c r="BH291" s="2"/>
       <c r="BM291"/>
     </row>
-    <row r="292" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
         <v>43</v>
       </c>
@@ -33945,7 +33908,7 @@
       <c r="BH292" s="2"/>
       <c r="BM292"/>
     </row>
-    <row r="293" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
         <v>43</v>
       </c>
@@ -34053,7 +34016,7 @@
       <c r="BH293" s="2"/>
       <c r="BM293"/>
     </row>
-    <row r="294" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
         <v>43</v>
       </c>
@@ -34155,13 +34118,13 @@
       <c r="BF294" s="46">
         <v>1.1719999999999999</v>
       </c>
-      <c r="BG294" s="64">
+      <c r="BG294" s="2">
         <v>2096</v>
       </c>
       <c r="BH294" s="2"/>
       <c r="BM294"/>
     </row>
-    <row r="295" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
         <v>43</v>
       </c>
@@ -34257,7 +34220,7 @@
       <c r="BH295" s="2"/>
       <c r="BM295"/>
     </row>
-    <row r="296" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
         <v>43</v>
       </c>
@@ -34353,7 +34316,7 @@
       <c r="BH296" s="2"/>
       <c r="BM296"/>
     </row>
-    <row r="297" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
         <v>43</v>
       </c>
@@ -34449,7 +34412,7 @@
       <c r="BH297" s="2"/>
       <c r="BM297"/>
     </row>
-    <row r="298" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
         <v>43</v>
       </c>
@@ -34545,7 +34508,7 @@
       <c r="BH298" s="2"/>
       <c r="BM298"/>
     </row>
-    <row r="299" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
         <v>43</v>
       </c>
@@ -34638,7 +34601,7 @@
       <c r="BH299" s="2"/>
       <c r="BM299"/>
     </row>
-    <row r="300" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
         <v>43</v>
       </c>
@@ -34730,11 +34693,11 @@
       <c r="BD300" s="44"/>
       <c r="BE300" s="45"/>
       <c r="BF300" s="46"/>
-      <c r="BG300" s="64"/>
+      <c r="BG300" s="2"/>
       <c r="BH300" s="2"/>
       <c r="BM300"/>
     </row>
-    <row r="301" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
         <v>43</v>
       </c>
@@ -34826,11 +34789,11 @@
       <c r="BD301" s="44"/>
       <c r="BE301" s="45"/>
       <c r="BF301" s="46"/>
-      <c r="BG301" s="64"/>
+      <c r="BG301" s="2"/>
       <c r="BH301" s="2"/>
       <c r="BM301"/>
     </row>
-    <row r="302" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
         <v>13</v>
       </c>
@@ -34932,12 +34895,12 @@
       <c r="BF302" s="46">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BG302" s="64">
+      <c r="BG302" s="2">
         <v>2096</v>
       </c>
       <c r="BH302" s="2"/>
     </row>
-    <row r="303" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
         <v>13</v>
       </c>
@@ -35039,12 +35002,12 @@
       <c r="BF303" s="46">
         <v>1.173</v>
       </c>
-      <c r="BG303" s="64">
+      <c r="BG303" s="2">
         <v>2096</v>
       </c>
       <c r="BH303" s="2"/>
     </row>
-    <row r="304" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
         <v>13</v>
       </c>
@@ -35146,12 +35109,12 @@
       <c r="BF304" s="46">
         <v>1.173</v>
       </c>
-      <c r="BG304" s="64">
+      <c r="BG304" s="2">
         <v>2096</v>
       </c>
       <c r="BH304" s="2"/>
     </row>
-    <row r="305" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
         <v>13</v>
       </c>
@@ -35253,12 +35216,12 @@
       <c r="BF305" s="46">
         <v>1.1719999999999999</v>
       </c>
-      <c r="BG305" s="64">
+      <c r="BG305" s="2">
         <v>2096</v>
       </c>
       <c r="BH305" s="2"/>
     </row>
-    <row r="306" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
         <v>13</v>
       </c>
@@ -35360,12 +35323,12 @@
       <c r="BF306" s="46">
         <v>1.1719999999999999</v>
       </c>
-      <c r="BG306" s="64">
+      <c r="BG306" s="2">
         <v>2096</v>
       </c>
       <c r="BH306" s="2"/>
     </row>
-    <row r="307" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
         <v>13</v>
       </c>
@@ -35467,12 +35430,12 @@
       <c r="BF307" s="46">
         <v>1.1719999999999999</v>
       </c>
-      <c r="BG307" s="64">
+      <c r="BG307" s="2">
         <v>2096</v>
       </c>
       <c r="BH307" s="2"/>
     </row>
-    <row r="308" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
         <v>13</v>
       </c>
@@ -35488,7 +35451,7 @@
       <c r="E308" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="F308" s="64" t="s">
+      <c r="F308" s="2" t="s">
         <v>553</v>
       </c>
       <c r="G308" s="7">
@@ -35574,12 +35537,12 @@
       <c r="BF308" s="46">
         <v>1.1719999999999999</v>
       </c>
-      <c r="BG308" s="64">
+      <c r="BG308" s="2">
         <v>2096</v>
       </c>
       <c r="BH308" s="2"/>
     </row>
-    <row r="309" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
         <v>13</v>
       </c>
@@ -35595,7 +35558,7 @@
       <c r="E309" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="F309" s="64" t="s">
+      <c r="F309" s="2" t="s">
         <v>553</v>
       </c>
       <c r="G309" s="7">
@@ -35681,12 +35644,12 @@
       <c r="BF309" s="46">
         <v>1.171</v>
       </c>
-      <c r="BG309" s="64">
+      <c r="BG309" s="2">
         <v>2096</v>
       </c>
       <c r="BH309" s="2"/>
     </row>
-    <row r="310" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
         <v>43</v>
       </c>
@@ -35784,12 +35747,12 @@
         <v>53.6</v>
       </c>
       <c r="BF310" s="46"/>
-      <c r="BG310" s="64">
+      <c r="BG310" s="2">
         <v>2096</v>
       </c>
       <c r="BH310" s="2"/>
     </row>
-    <row r="311" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
         <v>43</v>
       </c>
@@ -35887,12 +35850,12 @@
         <v>53.6</v>
       </c>
       <c r="BF311" s="46"/>
-      <c r="BG311" s="64">
+      <c r="BG311" s="2">
         <v>2096</v>
       </c>
       <c r="BH311" s="2"/>
     </row>
-    <row r="312" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
         <v>43</v>
       </c>
@@ -35979,12 +35942,12 @@
       <c r="BD312" s="44"/>
       <c r="BE312" s="45"/>
       <c r="BF312" s="46"/>
-      <c r="BG312" s="64">
+      <c r="BG312" s="2">
         <v>2096</v>
       </c>
       <c r="BH312" s="2"/>
     </row>
-    <row r="313" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
         <v>43</v>
       </c>
@@ -36084,12 +36047,12 @@
       <c r="BF313" s="46">
         <v>1.1759999999999999</v>
       </c>
-      <c r="BG313" s="64">
+      <c r="BG313" s="2">
         <v>2096</v>
       </c>
       <c r="BH313" s="2"/>
     </row>
-    <row r="314" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
         <v>43</v>
       </c>
@@ -36180,7 +36143,7 @@
       </c>
       <c r="BH314" s="2"/>
     </row>
-    <row r="315" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
         <v>43</v>
       </c>
@@ -36266,7 +36229,7 @@
       </c>
       <c r="BH315" s="2"/>
     </row>
-    <row r="316" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
         <v>43</v>
       </c>
@@ -36354,12 +36317,12 @@
       <c r="BF316" s="46">
         <v>1.173</v>
       </c>
-      <c r="BG316" s="64">
+      <c r="BG316" s="2">
         <v>2096</v>
       </c>
       <c r="BH316" s="2"/>
     </row>
-    <row r="317" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
         <v>43</v>
       </c>
@@ -36452,7 +36415,7 @@
       </c>
       <c r="BH317" s="2"/>
     </row>
-    <row r="318" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
         <v>43</v>
       </c>
@@ -36555,7 +36518,7 @@
       </c>
       <c r="BH318" s="2"/>
     </row>
-    <row r="319" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
         <v>43</v>
       </c>
@@ -36658,7 +36621,7 @@
       </c>
       <c r="BH319" s="2"/>
     </row>
-    <row r="320" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
         <v>43</v>
       </c>
@@ -36756,12 +36719,12 @@
       <c r="BF320" s="46">
         <v>1.171</v>
       </c>
-      <c r="BG320" s="64">
+      <c r="BG320" s="2">
         <v>2096</v>
       </c>
       <c r="BH320" s="2"/>
     </row>
-    <row r="321" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
         <v>43</v>
       </c>
@@ -36866,7 +36829,7 @@
       </c>
       <c r="BH321" s="2"/>
     </row>
-    <row r="322" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
         <v>43</v>
       </c>
@@ -36969,7 +36932,7 @@
       </c>
       <c r="BH322" s="2"/>
     </row>
-    <row r="323" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
         <v>43</v>
       </c>
@@ -37072,7 +37035,7 @@
       </c>
       <c r="BH323" s="2"/>
     </row>
-    <row r="324" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
         <v>43</v>
       </c>
@@ -37155,7 +37118,7 @@
       <c r="AW324" s="2"/>
       <c r="AX324" s="7"/>
       <c r="AY324" s="4"/>
-      <c r="AZ324" s="66">
+      <c r="AZ324" s="4">
         <v>111.6</v>
       </c>
       <c r="BA324" s="2"/>
@@ -37177,7 +37140,7 @@
       </c>
       <c r="BH324" s="2"/>
     </row>
-    <row r="325" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
         <v>43</v>
       </c>
@@ -37282,7 +37245,7 @@
       </c>
       <c r="BH325" s="2"/>
     </row>
-    <row r="326" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
         <v>43</v>
       </c>
@@ -37377,7 +37340,7 @@
       </c>
       <c r="BH326" s="2"/>
     </row>
-    <row r="327" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
         <v>43</v>
       </c>
@@ -37460,7 +37423,7 @@
       </c>
       <c r="BH327" s="2"/>
     </row>
-    <row r="328" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
         <v>43</v>
       </c>
@@ -37553,7 +37516,7 @@
       </c>
       <c r="BH328" s="2"/>
     </row>
-    <row r="329" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
         <v>13</v>
       </c>
@@ -37658,7 +37621,7 @@
       </c>
       <c r="BH329" s="2"/>
     </row>
-    <row r="330" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
         <v>13</v>
       </c>
@@ -37741,7 +37704,7 @@
       <c r="AW330" s="2"/>
       <c r="AX330" s="7"/>
       <c r="AY330" s="4"/>
-      <c r="AZ330" s="66"/>
+      <c r="AZ330" s="4"/>
       <c r="BA330" s="2"/>
       <c r="BB330" s="2"/>
       <c r="BC330" s="2"/>
@@ -37753,7 +37716,7 @@
       </c>
       <c r="BH330" s="2"/>
     </row>
-    <row r="331" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
         <v>13</v>
       </c>
@@ -37769,7 +37732,7 @@
       <c r="E331" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="F331" s="64" t="s">
+      <c r="F331" s="2" t="s">
         <v>553</v>
       </c>
       <c r="G331" s="7">
@@ -37848,7 +37811,7 @@
       </c>
       <c r="BH331" s="2"/>
     </row>
-    <row r="332" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
         <v>13</v>
       </c>
@@ -37953,7 +37916,7 @@
       </c>
       <c r="BH332" s="2"/>
     </row>
-    <row r="333" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
         <v>13</v>
       </c>
@@ -38058,7 +38021,7 @@
       </c>
       <c r="BH333" s="2"/>
     </row>
-    <row r="334" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
         <v>13</v>
       </c>
@@ -38151,7 +38114,7 @@
       <c r="BG334" s="62"/>
       <c r="BH334" s="2"/>
     </row>
-    <row r="335" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
         <v>43</v>
       </c>
@@ -38253,7 +38216,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="336" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
         <v>43</v>
       </c>
@@ -38355,7 +38318,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="337" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>43</v>
       </c>
@@ -38455,7 +38418,7 @@
       </c>
       <c r="BH337" s="2"/>
     </row>
-    <row r="338" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
         <v>43</v>
       </c>
@@ -38557,7 +38520,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="339" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
         <v>43</v>
       </c>
@@ -38657,7 +38620,7 @@
       </c>
       <c r="BH339" s="2"/>
     </row>
-    <row r="340" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
         <v>43</v>
       </c>
@@ -38759,7 +38722,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="341" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
         <v>43</v>
       </c>
@@ -38866,7 +38829,7 @@
       </c>
       <c r="BH341" s="2"/>
     </row>
-    <row r="342" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
         <v>43</v>
       </c>
@@ -38975,7 +38938,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="343" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
         <v>43</v>
       </c>
@@ -39080,7 +39043,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="344" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
         <v>43</v>
       </c>
@@ -39183,7 +39146,7 @@
       </c>
       <c r="BH344" s="2"/>
     </row>
-    <row r="345" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
         <v>43</v>
       </c>
@@ -39288,7 +39251,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="346" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
         <v>43</v>
       </c>
@@ -39393,7 +39356,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="347" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
         <v>43</v>
       </c>
@@ -39498,7 +39461,7 @@
       </c>
       <c r="BH347" s="2"/>
     </row>
-    <row r="348" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
         <v>43</v>
       </c>
@@ -39605,7 +39568,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="349" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
         <v>43</v>
       </c>
@@ -39712,7 +39675,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="350" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
         <v>43</v>
       </c>
@@ -39819,7 +39782,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="351" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
         <v>43</v>
       </c>
@@ -39926,7 +39889,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="352" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
         <v>43</v>
       </c>
@@ -40153,7 +40116,7 @@
       <c r="E354" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F354" s="64" t="s">
+      <c r="F354" s="2" t="s">
         <v>556</v>
       </c>
       <c r="G354" s="53"/>
@@ -40461,7 +40424,7 @@
       <c r="E357" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="F357" s="64" t="s">
+      <c r="F357" s="2" t="s">
         <v>556</v>
       </c>
       <c r="G357" s="7">
@@ -40549,7 +40512,7 @@
       </c>
       <c r="BH357" s="2"/>
     </row>
-    <row r="358" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
         <v>13</v>
       </c>
@@ -40653,7 +40616,7 @@
       </c>
       <c r="BH358" s="2"/>
     </row>
-    <row r="359" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
         <v>13</v>
       </c>
@@ -40757,7 +40720,7 @@
       </c>
       <c r="BH359" s="2"/>
     </row>
-    <row r="360" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
         <v>13</v>
       </c>
@@ -40861,7 +40824,7 @@
       </c>
       <c r="BH360" s="2"/>
     </row>
-    <row r="361" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
         <v>13</v>
       </c>
@@ -40965,7 +40928,7 @@
       </c>
       <c r="BH361" s="2"/>
     </row>
-    <row r="362" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
         <v>13</v>
       </c>
@@ -41069,7 +41032,7 @@
       </c>
       <c r="BH362" s="2"/>
     </row>
-    <row r="363" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
         <v>13</v>
       </c>
@@ -41173,7 +41136,7 @@
       </c>
       <c r="BH363" s="2"/>
     </row>
-    <row r="364" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
         <v>13</v>
       </c>
@@ -41279,7 +41242,7 @@
       <c r="BK364" s="7"/>
       <c r="BM364"/>
     </row>
-    <row r="365" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
         <v>13</v>
       </c>
@@ -41385,7 +41348,7 @@
       <c r="BK365" s="7"/>
       <c r="BM365"/>
     </row>
-    <row r="366" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
         <v>13</v>
       </c>
@@ -41491,7 +41454,7 @@
       <c r="BK366" s="7"/>
       <c r="BM366"/>
     </row>
-    <row r="367" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
         <v>13</v>
       </c>
@@ -41597,7 +41560,7 @@
       <c r="BK367" s="7"/>
       <c r="BM367"/>
     </row>
-    <row r="368" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
         <v>13</v>
       </c>
@@ -41703,7 +41666,7 @@
       <c r="BK368" s="7"/>
       <c r="BM368"/>
     </row>
-    <row r="369" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
         <v>13</v>
       </c>
@@ -41809,7 +41772,7 @@
       <c r="BK369" s="7"/>
       <c r="BM369"/>
     </row>
-    <row r="370" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
         <v>13</v>
       </c>
@@ -41914,7 +41877,7 @@
       <c r="BH370" s="2"/>
       <c r="BM370"/>
     </row>
-    <row r="371" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
         <v>13</v>
       </c>
@@ -42017,7 +41980,7 @@
       <c r="BH371" s="2"/>
       <c r="BM371"/>
     </row>
-    <row r="372" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
         <v>13</v>
       </c>
@@ -42123,7 +42086,7 @@
       <c r="BH372" s="2"/>
       <c r="BM372"/>
     </row>
-    <row r="373" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
         <v>13</v>
       </c>
@@ -42229,7 +42192,7 @@
       <c r="BH373" s="2"/>
       <c r="BM373"/>
     </row>
-    <row r="374" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
         <v>13</v>
       </c>
@@ -42335,7 +42298,7 @@
       <c r="BH374" s="2"/>
       <c r="BM374"/>
     </row>
-    <row r="375" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
         <v>13</v>
       </c>
@@ -42441,7 +42404,7 @@
       <c r="BH375" s="2"/>
       <c r="BM375"/>
     </row>
-    <row r="376" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
         <v>13</v>
       </c>
@@ -42547,7 +42510,7 @@
       <c r="BH376" s="2"/>
       <c r="BM376"/>
     </row>
-    <row r="377" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
         <v>13</v>
       </c>
@@ -42644,7 +42607,7 @@
       <c r="BH377" s="2"/>
       <c r="BM377"/>
     </row>
-    <row r="378" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="s">
         <v>13</v>
       </c>
@@ -42745,7 +42708,7 @@
       <c r="BH378" s="2"/>
       <c r="BM378"/>
     </row>
-    <row r="379" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="s">
         <v>13</v>
       </c>
@@ -42846,7 +42809,7 @@
       <c r="BH379" s="2"/>
       <c r="BM379"/>
     </row>
-    <row r="380" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
         <v>13</v>
       </c>
@@ -42947,7 +42910,7 @@
       <c r="BH380" s="2"/>
       <c r="BM380"/>
     </row>
-    <row r="381" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
         <v>13</v>
       </c>
@@ -43048,7 +43011,7 @@
       <c r="BH381" s="2"/>
       <c r="BM381"/>
     </row>
-    <row r="382" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
         <v>13</v>
       </c>
@@ -43149,7 +43112,7 @@
       <c r="BH382" s="2"/>
       <c r="BM382"/>
     </row>
-    <row r="383" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="s">
         <v>13</v>
       </c>
@@ -43250,7 +43213,7 @@
       <c r="BH383" s="2"/>
       <c r="BM383"/>
     </row>
-    <row r="384" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="s">
         <v>13</v>
       </c>
@@ -43351,7 +43314,7 @@
       <c r="BH384" s="2"/>
       <c r="BM384"/>
     </row>
-    <row r="385" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
         <v>13</v>
       </c>
@@ -43452,7 +43415,7 @@
       <c r="BH385" s="2"/>
       <c r="BM385"/>
     </row>
-    <row r="386" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
         <v>43</v>
       </c>
@@ -43553,7 +43516,7 @@
       <c r="BH386" s="2"/>
       <c r="BM386"/>
     </row>
-    <row r="387" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
         <v>43</v>
       </c>
@@ -43654,7 +43617,7 @@
       <c r="BH387" s="2"/>
       <c r="BM387"/>
     </row>
-    <row r="388" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
         <v>43</v>
       </c>
@@ -43755,7 +43718,7 @@
       <c r="BH388" s="2"/>
       <c r="BM388"/>
     </row>
-    <row r="389" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
         <v>43</v>
       </c>
@@ -43856,7 +43819,7 @@
       <c r="BH389" s="2"/>
       <c r="BM389"/>
     </row>
-    <row r="390" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
         <v>43</v>
       </c>
@@ -43957,7 +43920,7 @@
       <c r="BH390" s="2"/>
       <c r="BM390"/>
     </row>
-    <row r="391" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
         <v>43</v>
       </c>
@@ -44058,7 +44021,7 @@
       <c r="BH391" s="2"/>
       <c r="BM391"/>
     </row>
-    <row r="392" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
         <v>43</v>
       </c>
@@ -44159,7 +44122,7 @@
       <c r="BH392" s="2"/>
       <c r="BM392"/>
     </row>
-    <row r="393" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
         <v>43</v>
       </c>
@@ -44260,7 +44223,7 @@
       <c r="BH393" s="2"/>
       <c r="BM393"/>
     </row>
-    <row r="394" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
         <v>13</v>
       </c>
@@ -44361,7 +44324,7 @@
       <c r="BH394" s="2"/>
       <c r="BM394"/>
     </row>
-    <row r="395" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
         <v>13</v>
       </c>
@@ -44462,7 +44425,7 @@
       <c r="BH395" s="2"/>
       <c r="BM395"/>
     </row>
-    <row r="396" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
         <v>13</v>
       </c>
@@ -44563,7 +44526,7 @@
       <c r="BH396" s="2"/>
       <c r="BM396"/>
     </row>
-    <row r="397" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
         <v>13</v>
       </c>
@@ -44664,7 +44627,7 @@
       <c r="BH397" s="2"/>
       <c r="BM397"/>
     </row>
-    <row r="398" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
         <v>13</v>
       </c>
@@ -44765,7 +44728,7 @@
       <c r="BH398" s="2"/>
       <c r="BM398"/>
     </row>
-    <row r="399" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
         <v>13</v>
       </c>
@@ -44866,7 +44829,7 @@
       <c r="BH399" s="2"/>
       <c r="BM399"/>
     </row>
-    <row r="400" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
         <v>43</v>
       </c>
@@ -44970,7 +44933,7 @@
       <c r="BH400" s="2"/>
       <c r="BM400"/>
     </row>
-    <row r="401" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
         <v>43</v>
       </c>
@@ -45074,7 +45037,7 @@
       <c r="BH401" s="2"/>
       <c r="BM401"/>
     </row>
-    <row r="402" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
         <v>43</v>
       </c>
@@ -45180,7 +45143,7 @@
       </c>
       <c r="BM402"/>
     </row>
-    <row r="403" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
         <v>43</v>
       </c>
@@ -45286,7 +45249,7 @@
       </c>
       <c r="BM403"/>
     </row>
-    <row r="404" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
         <v>43</v>
       </c>
@@ -45390,7 +45353,7 @@
       <c r="BH404" s="2"/>
       <c r="BM404"/>
     </row>
-    <row r="405" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
         <v>13</v>
       </c>
@@ -45496,7 +45459,7 @@
       </c>
       <c r="BM405"/>
     </row>
-    <row r="406" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
         <v>13</v>
       </c>
@@ -45597,7 +45560,7 @@
       <c r="BH406" s="2"/>
       <c r="BM406"/>
     </row>
-    <row r="407" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
         <v>13</v>
       </c>
@@ -45680,7 +45643,7 @@
       <c r="AW407" s="2"/>
       <c r="AX407" s="7"/>
       <c r="AY407" s="4"/>
-      <c r="AZ407" s="66">
+      <c r="AZ407" s="4">
         <v>113.4</v>
       </c>
       <c r="BA407" s="2"/>
@@ -45703,7 +45666,7 @@
       </c>
       <c r="BM407"/>
     </row>
-    <row r="408" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
         <v>13</v>
       </c>
@@ -45809,7 +45772,7 @@
       </c>
       <c r="BM408"/>
     </row>
-    <row r="409" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
         <v>13</v>
       </c>
@@ -45915,7 +45878,7 @@
       </c>
       <c r="BM409"/>
     </row>
-    <row r="410" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
         <v>13</v>
       </c>
@@ -46019,7 +45982,7 @@
       </c>
       <c r="BM410"/>
     </row>
-    <row r="411" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
         <v>43</v>
       </c>
@@ -46125,7 +46088,7 @@
       </c>
       <c r="BM411"/>
     </row>
-    <row r="412" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
         <v>43</v>
       </c>
@@ -46231,7 +46194,7 @@
       </c>
       <c r="BM412"/>
     </row>
-    <row r="413" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
         <v>43</v>
       </c>
@@ -46337,7 +46300,7 @@
       </c>
       <c r="BM413"/>
     </row>
-    <row r="414" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
         <v>43</v>
       </c>
@@ -46443,7 +46406,7 @@
       </c>
       <c r="BM414"/>
     </row>
-    <row r="415" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
         <v>43</v>
       </c>
@@ -46459,7 +46422,7 @@
       <c r="E415" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="F415" s="64" t="s">
+      <c r="F415" s="2" t="s">
         <v>547</v>
       </c>
       <c r="G415" s="7">
@@ -46526,7 +46489,7 @@
       <c r="AW415" s="2"/>
       <c r="AX415" s="7"/>
       <c r="AY415" s="4"/>
-      <c r="AZ415" s="66">
+      <c r="AZ415" s="4">
         <v>113.4</v>
       </c>
       <c r="BA415" s="2"/>
@@ -46549,7 +46512,7 @@
       </c>
       <c r="BM415"/>
     </row>
-    <row r="416" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
         <v>43</v>
       </c>
@@ -46655,7 +46618,7 @@
       </c>
       <c r="BM416"/>
     </row>
-    <row r="417" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
         <v>43</v>
       </c>
@@ -46758,7 +46721,7 @@
       </c>
       <c r="BM417"/>
     </row>
-    <row r="418" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
         <v>43</v>
       </c>
@@ -46864,7 +46827,7 @@
       </c>
       <c r="BM418"/>
     </row>
-    <row r="419" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
         <v>43</v>
       </c>
@@ -46970,7 +46933,7 @@
       </c>
       <c r="BM419"/>
     </row>
-    <row r="420" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
         <v>43</v>
       </c>
@@ -47076,7 +47039,7 @@
       </c>
       <c r="BM420"/>
     </row>
-    <row r="421" spans="1:65" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
         <v>43</v>
       </c>
@@ -47446,6 +47409,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
@@ -47453,15 +47425,6 @@
     <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -47484,6 +47447,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -47498,12 +47469,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290E8A57-9223-47F5-A5F6-5EB196FEED9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65565C5D-352D-402E-8530-EC40FD60A17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2013,6 +2013,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2040,6 +2041,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2153,7 +2155,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2337,110 +2339,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2835,10 +2771,12 @@
     <sheetNames>
       <sheetName val="CdA Track Testing"/>
       <sheetName val="Data cut from table - to sort"/>
+      <sheetName val="Track CdA Aero Testing Database"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3487,13 +3425,13 @@
       <c r="BE2" s="14">
         <v>997</v>
       </c>
-      <c r="BF2" s="76">
+      <c r="BF2" s="67">
         <v>49</v>
       </c>
       <c r="BG2" s="15">
         <v>1.163</v>
       </c>
-      <c r="BH2" s="71">
+      <c r="BH2" s="7">
         <v>2096</v>
       </c>
       <c r="BI2" s="4"/>
@@ -3599,13 +3537,13 @@
       <c r="BE3" s="14">
         <v>997</v>
       </c>
-      <c r="BF3" s="76">
+      <c r="BF3" s="67">
         <v>49</v>
       </c>
       <c r="BG3" s="15">
         <v>1.163</v>
       </c>
-      <c r="BH3" s="71">
+      <c r="BH3" s="7">
         <v>2096</v>
       </c>
       <c r="BI3" s="4"/>
@@ -3711,11 +3649,11 @@
       <c r="BE4" s="17">
         <v>997.1</v>
       </c>
-      <c r="BF4" s="74">
+      <c r="BF4" s="16">
         <v>49.6</v>
       </c>
       <c r="BG4" s="15"/>
-      <c r="BH4" s="71">
+      <c r="BH4" s="7">
         <v>2096</v>
       </c>
       <c r="BI4" s="13" t="s">
@@ -3820,13 +3758,13 @@
       <c r="BE5" s="14">
         <v>997</v>
       </c>
-      <c r="BF5" s="76">
+      <c r="BF5" s="67">
         <v>49</v>
       </c>
       <c r="BG5" s="15">
         <v>1.1599999999999999</v>
       </c>
-      <c r="BH5" s="71">
+      <c r="BH5" s="7">
         <v>2096</v>
       </c>
       <c r="BI5" s="4"/>
@@ -3932,13 +3870,13 @@
       <c r="BE6" s="14">
         <v>997</v>
       </c>
-      <c r="BF6" s="76">
+      <c r="BF6" s="67">
         <v>49</v>
       </c>
       <c r="BG6" s="15">
         <v>1.161</v>
       </c>
-      <c r="BH6" s="71">
+      <c r="BH6" s="7">
         <v>2096</v>
       </c>
       <c r="BI6" s="4"/>
@@ -4044,11 +3982,11 @@
       <c r="BE7" s="17">
         <v>997</v>
       </c>
-      <c r="BF7" s="74">
+      <c r="BF7" s="16">
         <v>48</v>
       </c>
       <c r="BG7" s="15"/>
-      <c r="BH7" s="71">
+      <c r="BH7" s="7">
         <v>2096</v>
       </c>
       <c r="BI7" s="13" t="s">
@@ -4156,13 +4094,13 @@
       <c r="BE8" s="14">
         <v>996</v>
       </c>
-      <c r="BF8" s="76">
+      <c r="BF8" s="67">
         <v>49</v>
       </c>
       <c r="BG8" s="15">
         <v>1.159</v>
       </c>
-      <c r="BH8" s="71">
+      <c r="BH8" s="7">
         <v>2096</v>
       </c>
       <c r="BI8" s="4"/>
@@ -4268,13 +4206,13 @@
       <c r="BE9" s="14">
         <v>997</v>
       </c>
-      <c r="BF9" s="76">
+      <c r="BF9" s="67">
         <v>49</v>
       </c>
       <c r="BG9" s="15">
         <v>1.1599999999999999</v>
       </c>
-      <c r="BH9" s="71">
+      <c r="BH9" s="7">
         <v>2096</v>
       </c>
       <c r="BI9" s="4"/>
@@ -4377,11 +4315,11 @@
       <c r="BE10" s="17">
         <v>997</v>
       </c>
-      <c r="BF10" s="74">
+      <c r="BF10" s="16">
         <v>47</v>
       </c>
       <c r="BG10" s="15"/>
-      <c r="BH10" s="71">
+      <c r="BH10" s="7">
         <v>2096</v>
       </c>
       <c r="BI10" s="13" t="s">
@@ -4489,13 +4427,13 @@
       <c r="BE11" s="14">
         <v>996</v>
       </c>
-      <c r="BF11" s="76">
+      <c r="BF11" s="67">
         <v>47</v>
       </c>
       <c r="BG11" s="15">
         <v>1.1579999999999999</v>
       </c>
-      <c r="BH11" s="71">
+      <c r="BH11" s="7">
         <v>2096</v>
       </c>
       <c r="BI11" s="4"/>
@@ -4518,7 +4456,7 @@
       <c r="D12" s="8">
         <v>5</v>
       </c>
-      <c r="E12" s="72" t="s">
+      <c r="E12" s="10" t="s">
         <v>22</v>
       </c>
       <c r="F12" s="4" t="s">
@@ -4601,13 +4539,13 @@
       <c r="BE12" s="14">
         <v>996</v>
       </c>
-      <c r="BF12" s="76">
+      <c r="BF12" s="67">
         <v>47</v>
       </c>
       <c r="BG12" s="15">
         <v>1.159</v>
       </c>
-      <c r="BH12" s="71">
+      <c r="BH12" s="7">
         <v>2096</v>
       </c>
       <c r="BI12" s="4"/>
@@ -4710,11 +4648,11 @@
       <c r="BE13" s="17">
         <v>997</v>
       </c>
-      <c r="BF13" s="74">
+      <c r="BF13" s="16">
         <v>47</v>
       </c>
       <c r="BG13" s="15"/>
-      <c r="BH13" s="71">
+      <c r="BH13" s="7">
         <v>2096</v>
       </c>
       <c r="BI13" s="13" t="s">
@@ -4820,13 +4758,13 @@
       <c r="BE14" s="14">
         <v>995</v>
       </c>
-      <c r="BF14" s="76">
+      <c r="BF14" s="67">
         <v>47</v>
       </c>
       <c r="BG14" s="15">
         <v>1.157</v>
       </c>
-      <c r="BH14" s="71">
+      <c r="BH14" s="7">
         <v>2096</v>
       </c>
       <c r="BI14" s="4"/>
@@ -4930,13 +4868,13 @@
       <c r="BE15" s="14">
         <v>996</v>
       </c>
-      <c r="BF15" s="76">
+      <c r="BF15" s="67">
         <v>47</v>
       </c>
       <c r="BG15" s="15">
         <v>1.157</v>
       </c>
-      <c r="BH15" s="71">
+      <c r="BH15" s="7">
         <v>2096</v>
       </c>
       <c r="BI15" s="4"/>
@@ -4959,7 +4897,7 @@
       <c r="D16" s="8">
         <v>3</v>
       </c>
-      <c r="E16" s="72" t="s">
+      <c r="E16" s="10" t="s">
         <v>22</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -5040,11 +4978,11 @@
       <c r="BE16" s="17">
         <v>997</v>
       </c>
-      <c r="BF16" s="74">
+      <c r="BF16" s="16">
         <v>45</v>
       </c>
       <c r="BG16" s="15"/>
-      <c r="BH16" s="71">
+      <c r="BH16" s="7">
         <v>2096</v>
       </c>
       <c r="BI16" s="13" t="s">
@@ -5150,13 +5088,13 @@
       <c r="BE17" s="14">
         <v>995</v>
       </c>
-      <c r="BF17" s="76">
+      <c r="BF17" s="67">
         <v>47</v>
       </c>
       <c r="BG17" s="15">
         <v>1.157</v>
       </c>
-      <c r="BH17" s="71">
+      <c r="BH17" s="7">
         <v>2096</v>
       </c>
       <c r="BI17" s="4"/>
@@ -5260,13 +5198,13 @@
       <c r="BE18" s="14">
         <v>995</v>
       </c>
-      <c r="BF18" s="76">
+      <c r="BF18" s="67">
         <v>47</v>
       </c>
       <c r="BG18" s="15">
         <v>1.1579999999999999</v>
       </c>
-      <c r="BH18" s="71">
+      <c r="BH18" s="7">
         <v>2096</v>
       </c>
       <c r="BI18" s="4"/>
@@ -5370,11 +5308,11 @@
       <c r="BE19" s="17">
         <v>997</v>
       </c>
-      <c r="BF19" s="74">
+      <c r="BF19" s="16">
         <v>45</v>
       </c>
       <c r="BG19" s="15"/>
-      <c r="BH19" s="71">
+      <c r="BH19" s="7">
         <v>2096</v>
       </c>
       <c r="BI19" s="13" t="s">
@@ -5479,11 +5417,11 @@
       <c r="BE20" s="19">
         <v>1013</v>
       </c>
-      <c r="BF20" s="73">
+      <c r="BF20" s="18">
         <v>52.4</v>
       </c>
       <c r="BG20" s="20"/>
-      <c r="BH20" s="64"/>
+      <c r="BH20" s="4"/>
       <c r="BI20" s="4"/>
       <c r="BJ20" s="3" t="s">
         <v>115</v>
@@ -5586,11 +5524,11 @@
       <c r="BE21" s="19">
         <v>1013</v>
       </c>
-      <c r="BF21" s="73">
+      <c r="BF21" s="18">
         <v>52.4</v>
       </c>
       <c r="BG21" s="20"/>
-      <c r="BH21" s="64"/>
+      <c r="BH21" s="4"/>
       <c r="BI21" s="4"/>
       <c r="BJ21" s="3" t="s">
         <v>116</v>
@@ -5691,11 +5629,11 @@
       <c r="BE22" s="17">
         <v>1013</v>
       </c>
-      <c r="BF22" s="74">
+      <c r="BF22" s="16">
         <v>52.4</v>
       </c>
       <c r="BG22" s="15"/>
-      <c r="BH22" s="64"/>
+      <c r="BH22" s="4"/>
       <c r="BI22" s="4"/>
       <c r="BJ22" s="3" t="s">
         <v>117</v>
@@ -5798,11 +5736,11 @@
       <c r="BE23" s="19">
         <v>1013</v>
       </c>
-      <c r="BF23" s="73">
+      <c r="BF23" s="18">
         <v>52.4</v>
       </c>
       <c r="BG23" s="20"/>
-      <c r="BH23" s="64"/>
+      <c r="BH23" s="4"/>
       <c r="BI23" s="4"/>
       <c r="BJ23" s="3" t="s">
         <v>118</v>
@@ -5905,11 +5843,11 @@
       <c r="BE24" s="19">
         <v>1013</v>
       </c>
-      <c r="BF24" s="73">
+      <c r="BF24" s="18">
         <v>52.4</v>
       </c>
       <c r="BG24" s="20"/>
-      <c r="BH24" s="64"/>
+      <c r="BH24" s="4"/>
       <c r="BI24" s="4"/>
       <c r="BJ24" s="3" t="s">
         <v>119</v>
@@ -6010,11 +5948,11 @@
       <c r="BE25" s="17">
         <v>1013</v>
       </c>
-      <c r="BF25" s="74">
+      <c r="BF25" s="16">
         <v>52.4</v>
       </c>
       <c r="BG25" s="15"/>
-      <c r="BH25" s="64"/>
+      <c r="BH25" s="4"/>
       <c r="BI25" s="4"/>
       <c r="BJ25" s="3" t="s">
         <v>120</v>
@@ -6120,11 +6058,11 @@
       <c r="BE26" s="19">
         <v>1012</v>
       </c>
-      <c r="BF26" s="73">
+      <c r="BF26" s="18">
         <v>52.5</v>
       </c>
       <c r="BG26" s="20"/>
-      <c r="BH26" s="64"/>
+      <c r="BH26" s="4"/>
       <c r="BI26" s="4"/>
       <c r="BJ26" s="3" t="s">
         <v>121</v>
@@ -6230,11 +6168,11 @@
       <c r="BE27" s="19">
         <v>1012</v>
       </c>
-      <c r="BF27" s="73">
+      <c r="BF27" s="18">
         <v>52.5</v>
       </c>
       <c r="BG27" s="20"/>
-      <c r="BH27" s="64"/>
+      <c r="BH27" s="4"/>
       <c r="BI27" s="4"/>
       <c r="BJ27" s="3" t="s">
         <v>107</v>
@@ -6338,11 +6276,11 @@
       <c r="BE28" s="17">
         <v>1012</v>
       </c>
-      <c r="BF28" s="74">
+      <c r="BF28" s="16">
         <v>52.5</v>
       </c>
       <c r="BG28" s="15"/>
-      <c r="BH28" s="64"/>
+      <c r="BH28" s="4"/>
       <c r="BI28" s="4"/>
       <c r="BJ28" s="3" t="s">
         <v>108</v>
@@ -6445,14 +6383,14 @@
       <c r="BD29" s="18">
         <v>25.4</v>
       </c>
-      <c r="BE29" s="73">
+      <c r="BE29" s="18">
         <v>1012</v>
       </c>
-      <c r="BF29" s="73">
+      <c r="BF29" s="18">
         <v>52.9</v>
       </c>
-      <c r="BG29" s="64"/>
-      <c r="BH29" s="64"/>
+      <c r="BG29" s="4"/>
+      <c r="BH29" s="4"/>
       <c r="BI29" s="4"/>
       <c r="BJ29" s="3" t="s">
         <v>109</v>
@@ -6555,14 +6493,14 @@
       <c r="BD30" s="18">
         <v>25.4</v>
       </c>
-      <c r="BE30" s="73">
+      <c r="BE30" s="18">
         <v>1012</v>
       </c>
-      <c r="BF30" s="73">
+      <c r="BF30" s="18">
         <v>52.9</v>
       </c>
-      <c r="BG30" s="64"/>
-      <c r="BH30" s="64"/>
+      <c r="BG30" s="4"/>
+      <c r="BH30" s="4"/>
       <c r="BI30" s="4"/>
       <c r="BJ30" s="3" t="s">
         <v>110</v>
@@ -6663,14 +6601,14 @@
       <c r="BD31" s="16">
         <v>25.4</v>
       </c>
-      <c r="BE31" s="74">
+      <c r="BE31" s="16">
         <v>1012</v>
       </c>
-      <c r="BF31" s="74">
+      <c r="BF31" s="16">
         <v>52.9</v>
       </c>
-      <c r="BG31" s="67"/>
-      <c r="BH31" s="64"/>
+      <c r="BG31" s="63"/>
+      <c r="BH31" s="4"/>
       <c r="BI31" s="4"/>
       <c r="BJ31" s="3" t="s">
         <v>111</v>
@@ -6768,14 +6706,14 @@
       <c r="BD32" s="18">
         <v>25.8</v>
       </c>
-      <c r="BE32" s="73">
+      <c r="BE32" s="18">
         <v>1012</v>
       </c>
-      <c r="BF32" s="73">
+      <c r="BF32" s="18">
         <v>51.8</v>
       </c>
-      <c r="BG32" s="64"/>
-      <c r="BH32" s="64"/>
+      <c r="BG32" s="4"/>
+      <c r="BH32" s="4"/>
       <c r="BI32" s="4"/>
       <c r="BJ32" s="3" t="s">
         <v>112</v>
@@ -6876,14 +6814,14 @@
       <c r="BD33" s="18">
         <v>25.8</v>
       </c>
-      <c r="BE33" s="73">
+      <c r="BE33" s="18">
         <v>1012</v>
       </c>
-      <c r="BF33" s="73">
+      <c r="BF33" s="18">
         <v>51.8</v>
       </c>
-      <c r="BG33" s="64"/>
-      <c r="BH33" s="64"/>
+      <c r="BG33" s="4"/>
+      <c r="BH33" s="4"/>
       <c r="BI33" s="4"/>
       <c r="BJ33" s="3" t="s">
         <v>113</v>
@@ -6979,14 +6917,14 @@
       <c r="BD34" s="16">
         <v>25.8</v>
       </c>
-      <c r="BE34" s="74">
+      <c r="BE34" s="16">
         <v>1012</v>
       </c>
-      <c r="BF34" s="74">
+      <c r="BF34" s="16">
         <v>51.8</v>
       </c>
-      <c r="BG34" s="67"/>
-      <c r="BH34" s="64"/>
+      <c r="BG34" s="63"/>
+      <c r="BH34" s="4"/>
       <c r="BI34" s="13" t="s">
         <v>87</v>
       </c>
@@ -7089,14 +7027,14 @@
       <c r="BD35" s="18">
         <v>26.3</v>
       </c>
-      <c r="BE35" s="73">
+      <c r="BE35" s="18">
         <v>1012</v>
       </c>
-      <c r="BF35" s="73">
+      <c r="BF35" s="18">
         <v>51.3</v>
       </c>
-      <c r="BG35" s="64"/>
-      <c r="BH35" s="71"/>
+      <c r="BG35" s="4"/>
+      <c r="BH35" s="7"/>
       <c r="BI35" s="4"/>
       <c r="BJ35" s="3" t="s">
         <v>122</v>
@@ -7197,14 +7135,14 @@
       <c r="BD36" s="18">
         <v>26.3</v>
       </c>
-      <c r="BE36" s="73">
+      <c r="BE36" s="18">
         <v>1012</v>
       </c>
-      <c r="BF36" s="73">
+      <c r="BF36" s="18">
         <v>51.3</v>
       </c>
-      <c r="BG36" s="64"/>
-      <c r="BH36" s="64"/>
+      <c r="BG36" s="4"/>
+      <c r="BH36" s="4"/>
       <c r="BI36" s="4"/>
       <c r="BJ36" s="3" t="s">
         <v>123</v>
@@ -7300,14 +7238,14 @@
       <c r="BD37" s="16">
         <v>26.3</v>
       </c>
-      <c r="BE37" s="74">
+      <c r="BE37" s="16">
         <v>1012</v>
       </c>
-      <c r="BF37" s="74">
+      <c r="BF37" s="16">
         <v>51.3</v>
       </c>
-      <c r="BG37" s="67"/>
-      <c r="BH37" s="64"/>
+      <c r="BG37" s="63"/>
+      <c r="BH37" s="4"/>
       <c r="BI37" s="4"/>
       <c r="BJ37" s="3" t="s">
         <v>124</v>
@@ -7403,14 +7341,14 @@
       <c r="BD38" s="18">
         <v>24.8</v>
       </c>
-      <c r="BE38" s="73">
+      <c r="BE38" s="18">
         <v>1012</v>
       </c>
-      <c r="BF38" s="73">
+      <c r="BF38" s="18">
         <v>53.5</v>
       </c>
-      <c r="BG38" s="64"/>
-      <c r="BH38" s="64"/>
+      <c r="BG38" s="4"/>
+      <c r="BH38" s="4"/>
       <c r="BI38" s="4"/>
       <c r="BJ38" s="3" t="s">
         <v>131</v>
@@ -7506,16 +7444,16 @@
       <c r="BD39" s="4">
         <v>25</v>
       </c>
-      <c r="BE39" s="67">
+      <c r="BE39" s="63">
         <v>1012</v>
       </c>
-      <c r="BF39" s="76">
+      <c r="BF39" s="67">
         <v>53</v>
       </c>
-      <c r="BG39" s="67">
+      <c r="BG39" s="63">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH39" s="64"/>
+      <c r="BH39" s="4"/>
       <c r="BI39" s="4"/>
       <c r="BJ39" s="3" t="s">
         <v>132</v>
@@ -7611,14 +7549,14 @@
       <c r="BD40" s="18">
         <v>24.8</v>
       </c>
-      <c r="BE40" s="73">
+      <c r="BE40" s="18">
         <v>1012</v>
       </c>
-      <c r="BF40" s="73">
+      <c r="BF40" s="18">
         <v>53.5</v>
       </c>
-      <c r="BG40" s="64"/>
-      <c r="BH40" s="64"/>
+      <c r="BG40" s="4"/>
+      <c r="BH40" s="4"/>
       <c r="BI40" s="4"/>
       <c r="BJ40" s="3" t="s">
         <v>133</v>
@@ -7717,13 +7655,13 @@
       <c r="BE41" s="14">
         <v>1012</v>
       </c>
-      <c r="BF41" s="76">
+      <c r="BF41" s="67">
         <v>54</v>
       </c>
       <c r="BG41" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH41" s="64"/>
+      <c r="BH41" s="4"/>
       <c r="BI41" s="4"/>
       <c r="BJ41" s="3" t="s">
         <v>134</v>
@@ -7822,11 +7760,11 @@
       <c r="BE42" s="19">
         <v>1012</v>
       </c>
-      <c r="BF42" s="73">
+      <c r="BF42" s="18">
         <v>53</v>
       </c>
       <c r="BG42" s="21"/>
-      <c r="BH42" s="64"/>
+      <c r="BH42" s="4"/>
       <c r="BI42" s="4"/>
       <c r="BJ42" s="3" t="s">
         <v>135</v>
@@ -7925,13 +7863,13 @@
       <c r="BE43" s="14">
         <v>1012</v>
       </c>
-      <c r="BF43" s="76">
+      <c r="BF43" s="67">
         <v>53</v>
       </c>
       <c r="BG43" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH43" s="64"/>
+      <c r="BH43" s="4"/>
       <c r="BI43" s="4"/>
       <c r="BJ43" s="3" t="s">
         <v>136</v>
@@ -8028,11 +7966,11 @@
       <c r="BE44" s="19">
         <v>1012</v>
       </c>
-      <c r="BF44" s="73">
+      <c r="BF44" s="18">
         <v>53</v>
       </c>
       <c r="BG44" s="21"/>
-      <c r="BH44" s="64"/>
+      <c r="BH44" s="4"/>
       <c r="BI44" s="4"/>
       <c r="BJ44" s="3" t="s">
         <v>125</v>
@@ -8129,13 +8067,13 @@
       <c r="BE45" s="14">
         <v>1012</v>
       </c>
-      <c r="BF45" s="76">
+      <c r="BF45" s="67">
         <v>53</v>
       </c>
       <c r="BG45" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH45" s="64"/>
+      <c r="BH45" s="4"/>
       <c r="BI45" s="4"/>
       <c r="BJ45" s="3" t="s">
         <v>126</v>
@@ -8232,11 +8170,11 @@
       <c r="BE46" s="19">
         <v>1012</v>
       </c>
-      <c r="BF46" s="73">
+      <c r="BF46" s="18">
         <v>53</v>
       </c>
       <c r="BG46" s="21"/>
-      <c r="BH46" s="64"/>
+      <c r="BH46" s="4"/>
       <c r="BI46" s="4"/>
       <c r="BJ46" s="3" t="s">
         <v>127</v>
@@ -8333,13 +8271,13 @@
       <c r="BE47" s="14">
         <v>1012</v>
       </c>
-      <c r="BF47" s="76">
+      <c r="BF47" s="67">
         <v>53</v>
       </c>
       <c r="BG47" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH47" s="64"/>
+      <c r="BH47" s="4"/>
       <c r="BI47" s="4"/>
       <c r="BJ47" s="3" t="s">
         <v>128</v>
@@ -8436,11 +8374,11 @@
       <c r="BE48" s="19">
         <v>1012</v>
       </c>
-      <c r="BF48" s="73">
+      <c r="BF48" s="18">
         <v>53</v>
       </c>
       <c r="BG48" s="21"/>
-      <c r="BH48" s="64"/>
+      <c r="BH48" s="4"/>
       <c r="BI48" s="4"/>
       <c r="BJ48" s="3" t="s">
         <v>129</v>
@@ -8537,13 +8475,13 @@
       <c r="BE49" s="14">
         <v>1012</v>
       </c>
-      <c r="BF49" s="76">
+      <c r="BF49" s="67">
         <v>54</v>
       </c>
       <c r="BG49" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH49" s="64"/>
+      <c r="BH49" s="4"/>
       <c r="BI49" s="4"/>
       <c r="BJ49" s="3" t="s">
         <v>130</v>
@@ -8639,14 +8577,14 @@
       <c r="BD50" s="18">
         <v>25.1</v>
       </c>
-      <c r="BE50" s="73">
+      <c r="BE50" s="18">
         <v>1011</v>
       </c>
-      <c r="BF50" s="73">
+      <c r="BF50" s="18">
         <v>54.2</v>
       </c>
-      <c r="BG50" s="78"/>
-      <c r="BH50" s="64"/>
+      <c r="BG50" s="69"/>
+      <c r="BH50" s="4"/>
       <c r="BI50" s="4"/>
       <c r="BJ50" s="3" t="s">
         <v>145</v>
@@ -8742,16 +8680,16 @@
       <c r="BD51" s="4">
         <v>25.1</v>
       </c>
-      <c r="BE51" s="67">
+      <c r="BE51" s="63">
         <v>1011</v>
       </c>
-      <c r="BF51" s="76">
+      <c r="BF51" s="67">
         <v>54</v>
       </c>
-      <c r="BG51" s="67">
+      <c r="BG51" s="63">
         <v>1.173</v>
       </c>
-      <c r="BH51" s="64"/>
+      <c r="BH51" s="4"/>
       <c r="BI51" s="4"/>
       <c r="BJ51" s="3" t="s">
         <v>146</v>
@@ -8847,14 +8785,14 @@
       <c r="BD52" s="18">
         <v>25.1</v>
       </c>
-      <c r="BE52" s="73">
+      <c r="BE52" s="18">
         <v>1011</v>
       </c>
-      <c r="BF52" s="73">
+      <c r="BF52" s="18">
         <v>54.2</v>
       </c>
-      <c r="BG52" s="78"/>
-      <c r="BH52" s="64"/>
+      <c r="BG52" s="69"/>
+      <c r="BH52" s="4"/>
       <c r="BI52" s="4"/>
       <c r="BJ52" s="3" t="s">
         <v>147</v>
@@ -8950,16 +8888,16 @@
       <c r="BD53" s="4">
         <v>25.2</v>
       </c>
-      <c r="BE53" s="67">
+      <c r="BE53" s="63">
         <v>1011</v>
       </c>
-      <c r="BF53" s="76">
+      <c r="BF53" s="67">
         <v>54</v>
       </c>
-      <c r="BG53" s="67">
+      <c r="BG53" s="63">
         <v>1.173</v>
       </c>
-      <c r="BH53" s="64"/>
+      <c r="BH53" s="4"/>
       <c r="BI53" s="4"/>
       <c r="BJ53" s="3" t="s">
         <v>148</v>
@@ -9055,14 +8993,14 @@
       <c r="BD54" s="18">
         <v>25.1</v>
       </c>
-      <c r="BE54" s="73">
+      <c r="BE54" s="18">
         <v>1011</v>
       </c>
-      <c r="BF54" s="73">
+      <c r="BF54" s="18">
         <v>54.2</v>
       </c>
-      <c r="BG54" s="78"/>
-      <c r="BH54" s="64"/>
+      <c r="BG54" s="69"/>
+      <c r="BH54" s="4"/>
       <c r="BI54" s="4"/>
       <c r="BJ54" s="3" t="s">
         <v>137</v>
@@ -9158,16 +9096,16 @@
       <c r="BD55" s="4">
         <v>25.2</v>
       </c>
-      <c r="BE55" s="67">
+      <c r="BE55" s="63">
         <v>1011</v>
       </c>
-      <c r="BF55" s="76">
+      <c r="BF55" s="67">
         <v>54</v>
       </c>
-      <c r="BG55" s="67">
+      <c r="BG55" s="63">
         <v>1.173</v>
       </c>
-      <c r="BH55" s="64"/>
+      <c r="BH55" s="4"/>
       <c r="BI55" s="4"/>
       <c r="BJ55" s="3" t="s">
         <v>138</v>
@@ -9261,14 +9199,14 @@
       <c r="BD56" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE56" s="73">
+      <c r="BE56" s="18">
         <v>1005</v>
       </c>
-      <c r="BF56" s="73">
+      <c r="BF56" s="18">
         <v>41</v>
       </c>
-      <c r="BG56" s="78"/>
-      <c r="BH56" s="64"/>
+      <c r="BG56" s="69"/>
+      <c r="BH56" s="4"/>
       <c r="BI56" s="4"/>
       <c r="BJ56" s="36" t="s">
         <v>139</v>
@@ -9362,14 +9300,14 @@
       <c r="BD57" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE57" s="73">
+      <c r="BE57" s="18">
         <v>1005</v>
       </c>
-      <c r="BF57" s="73">
+      <c r="BF57" s="18">
         <v>41</v>
       </c>
-      <c r="BG57" s="78"/>
-      <c r="BH57" s="64"/>
+      <c r="BG57" s="69"/>
+      <c r="BH57" s="4"/>
       <c r="BI57" s="4"/>
       <c r="BJ57" s="3" t="s">
         <v>140</v>
@@ -9463,14 +9401,14 @@
       <c r="BD58" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE58" s="73">
+      <c r="BE58" s="18">
         <v>1005</v>
       </c>
-      <c r="BF58" s="73">
+      <c r="BF58" s="18">
         <v>41</v>
       </c>
-      <c r="BG58" s="78"/>
-      <c r="BH58" s="64"/>
+      <c r="BG58" s="69"/>
+      <c r="BH58" s="4"/>
       <c r="BI58" s="11" t="s">
         <v>88</v>
       </c>
@@ -9566,14 +9504,14 @@
       <c r="BD59" s="16">
         <v>25.2</v>
       </c>
-      <c r="BE59" s="74">
+      <c r="BE59" s="16">
         <v>1005</v>
       </c>
-      <c r="BF59" s="74">
+      <c r="BF59" s="16">
         <v>41</v>
       </c>
-      <c r="BG59" s="64"/>
-      <c r="BH59" s="64"/>
+      <c r="BG59" s="4"/>
+      <c r="BH59" s="4"/>
       <c r="BI59" s="4"/>
       <c r="BJ59" s="3" t="s">
         <v>142</v>
@@ -9667,14 +9605,14 @@
       <c r="BD60" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE60" s="73">
+      <c r="BE60" s="18">
         <v>1005</v>
       </c>
-      <c r="BF60" s="73">
+      <c r="BF60" s="18">
         <v>41</v>
       </c>
-      <c r="BG60" s="78"/>
-      <c r="BH60" s="64"/>
+      <c r="BG60" s="69"/>
+      <c r="BH60" s="4"/>
       <c r="BI60" s="4"/>
       <c r="BJ60" s="3" t="s">
         <v>143</v>
@@ -9768,14 +9706,14 @@
       <c r="BD61" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE61" s="73">
+      <c r="BE61" s="18">
         <v>1005</v>
       </c>
-      <c r="BF61" s="73">
+      <c r="BF61" s="18">
         <v>41</v>
       </c>
-      <c r="BG61" s="78"/>
-      <c r="BH61" s="64"/>
+      <c r="BG61" s="69"/>
+      <c r="BH61" s="4"/>
       <c r="BI61" s="4"/>
       <c r="BJ61" s="3" t="s">
         <v>144</v>
@@ -9885,14 +9823,14 @@
       <c r="BD62" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE62" s="73">
+      <c r="BE62" s="18">
         <v>1005</v>
       </c>
-      <c r="BF62" s="73">
+      <c r="BF62" s="18">
         <v>41</v>
       </c>
-      <c r="BG62" s="78"/>
-      <c r="BH62" s="64"/>
+      <c r="BG62" s="69"/>
+      <c r="BH62" s="4"/>
       <c r="BI62" s="4"/>
       <c r="BJ62" s="3" t="s">
         <v>154</v>
@@ -10002,14 +9940,14 @@
       <c r="BD63" s="16">
         <v>25.2</v>
       </c>
-      <c r="BE63" s="74">
+      <c r="BE63" s="16">
         <v>1005</v>
       </c>
-      <c r="BF63" s="74">
+      <c r="BF63" s="16">
         <v>41</v>
       </c>
-      <c r="BG63" s="64"/>
-      <c r="BH63" s="64"/>
+      <c r="BG63" s="4"/>
+      <c r="BH63" s="4"/>
       <c r="BI63" s="4"/>
       <c r="BJ63" s="3" t="s">
         <v>152</v>
@@ -10119,14 +10057,14 @@
       <c r="BD64" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE64" s="73">
+      <c r="BE64" s="18">
         <v>1005</v>
       </c>
-      <c r="BF64" s="73">
+      <c r="BF64" s="18">
         <v>41</v>
       </c>
-      <c r="BG64" s="78"/>
-      <c r="BH64" s="64"/>
+      <c r="BG64" s="69"/>
+      <c r="BH64" s="4"/>
       <c r="BI64" s="4"/>
       <c r="BJ64" s="3" t="s">
         <v>149</v>
@@ -10234,14 +10172,14 @@
       <c r="BD65" s="18">
         <v>25.9</v>
       </c>
-      <c r="BE65" s="73">
+      <c r="BE65" s="18">
         <v>1010</v>
       </c>
-      <c r="BF65" s="73">
+      <c r="BF65" s="18">
         <v>47</v>
       </c>
-      <c r="BG65" s="78"/>
-      <c r="BH65" s="64"/>
+      <c r="BG65" s="69"/>
+      <c r="BH65" s="4"/>
       <c r="BI65" s="18" t="s">
         <v>92</v>
       </c>
@@ -10351,14 +10289,14 @@
       <c r="BD66" s="18">
         <v>26.4</v>
       </c>
-      <c r="BE66" s="73">
+      <c r="BE66" s="18">
         <v>1010</v>
       </c>
-      <c r="BF66" s="73">
+      <c r="BF66" s="18">
         <v>46.5</v>
       </c>
-      <c r="BG66" s="64"/>
-      <c r="BH66" s="64"/>
+      <c r="BG66" s="4"/>
+      <c r="BH66" s="4"/>
       <c r="BI66" s="4"/>
       <c r="BJ66" s="3" t="s">
         <v>167</v>
@@ -10466,14 +10404,14 @@
       <c r="BD67" s="18">
         <v>26.4</v>
       </c>
-      <c r="BE67" s="73">
+      <c r="BE67" s="18">
         <v>1010</v>
       </c>
-      <c r="BF67" s="73">
+      <c r="BF67" s="18">
         <v>46.5</v>
       </c>
-      <c r="BG67" s="64"/>
-      <c r="BH67" s="64"/>
+      <c r="BG67" s="4"/>
+      <c r="BH67" s="4"/>
       <c r="BI67" s="4"/>
       <c r="BJ67" s="3" t="s">
         <v>168</v>
@@ -10583,14 +10521,14 @@
       <c r="BD68" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE68" s="73">
+      <c r="BE68" s="18">
         <v>1005</v>
       </c>
-      <c r="BF68" s="73">
+      <c r="BF68" s="18">
         <v>41</v>
       </c>
-      <c r="BG68" s="78"/>
-      <c r="BH68" s="64"/>
+      <c r="BG68" s="69"/>
+      <c r="BH68" s="4"/>
       <c r="BI68" s="4"/>
       <c r="BJ68" s="3" t="s">
         <v>153</v>
@@ -10698,14 +10636,14 @@
       <c r="BD69" s="18">
         <v>26.4</v>
       </c>
-      <c r="BE69" s="73">
+      <c r="BE69" s="18">
         <v>1010</v>
       </c>
-      <c r="BF69" s="73">
+      <c r="BF69" s="18">
         <v>46.5</v>
       </c>
-      <c r="BG69" s="64"/>
-      <c r="BH69" s="64"/>
+      <c r="BG69" s="4"/>
+      <c r="BH69" s="4"/>
       <c r="BI69" s="4"/>
       <c r="BJ69" s="3" t="s">
         <v>165</v>
@@ -10815,14 +10753,14 @@
       <c r="BD70" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE70" s="73">
+      <c r="BE70" s="18">
         <v>1005</v>
       </c>
-      <c r="BF70" s="73">
+      <c r="BF70" s="18">
         <v>41</v>
       </c>
-      <c r="BG70" s="78"/>
-      <c r="BH70" s="64"/>
+      <c r="BG70" s="69"/>
+      <c r="BH70" s="4"/>
       <c r="BI70" s="4"/>
       <c r="BJ70" s="3" t="s">
         <v>151</v>
@@ -10930,14 +10868,14 @@
       <c r="BD71" s="18">
         <v>26.4</v>
       </c>
-      <c r="BE71" s="73">
+      <c r="BE71" s="18">
         <v>1010</v>
       </c>
-      <c r="BF71" s="73">
+      <c r="BF71" s="18">
         <v>46.5</v>
       </c>
-      <c r="BG71" s="64"/>
-      <c r="BH71" s="64"/>
+      <c r="BG71" s="4"/>
+      <c r="BH71" s="4"/>
       <c r="BI71" s="4"/>
       <c r="BJ71" s="3" t="s">
         <v>166</v>
@@ -11045,14 +10983,14 @@
       <c r="BD72" s="18">
         <v>25.9</v>
       </c>
-      <c r="BE72" s="73">
+      <c r="BE72" s="18">
         <v>1010</v>
       </c>
-      <c r="BF72" s="73">
+      <c r="BF72" s="18">
         <v>47</v>
       </c>
-      <c r="BG72" s="64"/>
-      <c r="BH72" s="64"/>
+      <c r="BG72" s="4"/>
+      <c r="BH72" s="4"/>
       <c r="BI72" s="18" t="s">
         <v>91</v>
       </c>
@@ -11164,14 +11102,14 @@
       <c r="BD73" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE73" s="73">
+      <c r="BE73" s="18">
         <v>1005</v>
       </c>
-      <c r="BF73" s="73">
+      <c r="BF73" s="18">
         <v>41</v>
       </c>
-      <c r="BG73" s="78"/>
-      <c r="BH73" s="64"/>
+      <c r="BG73" s="69"/>
+      <c r="BH73" s="4"/>
       <c r="BI73" s="4"/>
       <c r="BJ73" s="3" t="s">
         <v>158</v>
@@ -11281,14 +11219,14 @@
       <c r="BD74" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE74" s="73">
+      <c r="BE74" s="18">
         <v>1005</v>
       </c>
-      <c r="BF74" s="73">
+      <c r="BF74" s="18">
         <v>41</v>
       </c>
-      <c r="BG74" s="78"/>
-      <c r="BH74" s="64"/>
+      <c r="BG74" s="69"/>
+      <c r="BH74" s="4"/>
       <c r="BI74" s="4"/>
       <c r="BJ74" s="3" t="s">
         <v>155</v>
@@ -11398,14 +11336,14 @@
       <c r="BD75" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE75" s="73">
+      <c r="BE75" s="18">
         <v>1005</v>
       </c>
-      <c r="BF75" s="73">
+      <c r="BF75" s="18">
         <v>41</v>
       </c>
-      <c r="BG75" s="78"/>
-      <c r="BH75" s="64"/>
+      <c r="BG75" s="69"/>
+      <c r="BH75" s="4"/>
       <c r="BI75" s="4"/>
       <c r="BJ75" s="3" t="s">
         <v>159</v>
@@ -11515,14 +11453,14 @@
       <c r="BD76" s="16">
         <v>25.2</v>
       </c>
-      <c r="BE76" s="74">
+      <c r="BE76" s="16">
         <v>1005</v>
       </c>
-      <c r="BF76" s="74">
+      <c r="BF76" s="16">
         <v>41</v>
       </c>
-      <c r="BG76" s="64"/>
-      <c r="BH76" s="64"/>
+      <c r="BG76" s="4"/>
+      <c r="BH76" s="4"/>
       <c r="BI76" s="4"/>
       <c r="BJ76" s="3" t="s">
         <v>156</v>
@@ -11632,14 +11570,14 @@
       <c r="BD77" s="16">
         <v>25.2</v>
       </c>
-      <c r="BE77" s="74">
+      <c r="BE77" s="16">
         <v>1005</v>
       </c>
-      <c r="BF77" s="74">
+      <c r="BF77" s="16">
         <v>41</v>
       </c>
-      <c r="BG77" s="64"/>
-      <c r="BH77" s="64"/>
+      <c r="BG77" s="4"/>
+      <c r="BH77" s="4"/>
       <c r="BI77" s="4"/>
       <c r="BJ77" s="3" t="s">
         <v>160</v>
@@ -11740,14 +11678,14 @@
       <c r="BD78" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE78" s="73">
+      <c r="BE78" s="18">
         <v>1005</v>
       </c>
-      <c r="BF78" s="73">
+      <c r="BF78" s="18">
         <v>41</v>
       </c>
-      <c r="BG78" s="78"/>
-      <c r="BH78" s="64"/>
+      <c r="BG78" s="69"/>
+      <c r="BH78" s="4"/>
       <c r="BI78" s="4"/>
       <c r="BJ78" s="3" t="s">
         <v>157</v>
@@ -11855,14 +11793,14 @@
       <c r="BD79" s="18">
         <v>25.9</v>
       </c>
-      <c r="BE79" s="73">
+      <c r="BE79" s="18">
         <v>1010</v>
       </c>
-      <c r="BF79" s="73">
+      <c r="BF79" s="18">
         <v>47</v>
       </c>
-      <c r="BG79" s="64"/>
-      <c r="BH79" s="64"/>
+      <c r="BG79" s="4"/>
+      <c r="BH79" s="4"/>
       <c r="BI79" s="4"/>
       <c r="BJ79" s="3" t="s">
         <v>161</v>
@@ -11970,14 +11908,14 @@
       <c r="BD80" s="18">
         <v>25.1</v>
       </c>
-      <c r="BE80" s="73">
+      <c r="BE80" s="18">
         <v>1010</v>
       </c>
-      <c r="BF80" s="73">
+      <c r="BF80" s="18">
         <v>47.7</v>
       </c>
-      <c r="BG80" s="64"/>
-      <c r="BH80" s="64"/>
+      <c r="BG80" s="4"/>
+      <c r="BH80" s="4"/>
       <c r="BI80" s="4"/>
       <c r="BJ80" s="3" t="s">
         <v>170</v>
@@ -12085,14 +12023,14 @@
       <c r="BD81" s="18">
         <v>25.1</v>
       </c>
-      <c r="BE81" s="73">
+      <c r="BE81" s="18">
         <v>1010</v>
       </c>
-      <c r="BF81" s="73">
+      <c r="BF81" s="18">
         <v>47.7</v>
       </c>
-      <c r="BG81" s="64"/>
-      <c r="BH81" s="64"/>
+      <c r="BG81" s="4"/>
+      <c r="BH81" s="4"/>
       <c r="BI81" s="4"/>
       <c r="BJ81" s="3" t="s">
         <v>169</v>
@@ -12200,14 +12138,14 @@
       <c r="BD82" s="18">
         <v>25.9</v>
       </c>
-      <c r="BE82" s="73">
+      <c r="BE82" s="18">
         <v>1010</v>
       </c>
-      <c r="BF82" s="73">
+      <c r="BF82" s="18">
         <v>47</v>
       </c>
-      <c r="BG82" s="64"/>
-      <c r="BH82" s="64"/>
+      <c r="BG82" s="4"/>
+      <c r="BH82" s="4"/>
       <c r="BI82" s="4"/>
       <c r="BJ82" s="3" t="s">
         <v>162</v>
@@ -12315,14 +12253,14 @@
       <c r="BD83" s="18">
         <v>25.1</v>
       </c>
-      <c r="BE83" s="73">
+      <c r="BE83" s="18">
         <v>1010</v>
       </c>
-      <c r="BF83" s="73">
+      <c r="BF83" s="18">
         <v>47.7</v>
       </c>
-      <c r="BG83" s="64"/>
-      <c r="BH83" s="64"/>
+      <c r="BG83" s="4"/>
+      <c r="BH83" s="4"/>
       <c r="BI83" s="4"/>
       <c r="BJ83" s="3" t="s">
         <v>171</v>
@@ -12430,14 +12368,14 @@
       <c r="BD84" s="18">
         <v>25.1</v>
       </c>
-      <c r="BE84" s="73">
+      <c r="BE84" s="18">
         <v>1010</v>
       </c>
-      <c r="BF84" s="73">
+      <c r="BF84" s="18">
         <v>47.7</v>
       </c>
-      <c r="BG84" s="78"/>
-      <c r="BH84" s="64"/>
+      <c r="BG84" s="69"/>
+      <c r="BH84" s="4"/>
       <c r="BI84" s="4"/>
       <c r="BJ84" s="3" t="s">
         <v>172</v>
@@ -12540,14 +12478,14 @@
       <c r="BD85" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE85" s="73">
+      <c r="BE85" s="18">
         <v>1005</v>
       </c>
-      <c r="BF85" s="73">
+      <c r="BF85" s="18">
         <v>41</v>
       </c>
-      <c r="BG85" s="78"/>
-      <c r="BH85" s="64"/>
+      <c r="BG85" s="69"/>
+      <c r="BH85" s="4"/>
       <c r="BI85" s="4"/>
       <c r="BJ85" s="3" t="s">
         <v>150</v>
@@ -12653,13 +12591,13 @@
       <c r="BD86" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE86" s="73">
+      <c r="BE86" s="18">
         <v>1010</v>
       </c>
-      <c r="BF86" s="73">
+      <c r="BF86" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG86" s="64"/>
+      <c r="BG86" s="4"/>
       <c r="BH86" s="4"/>
       <c r="BI86" s="4"/>
       <c r="BJ86" s="3" t="s">
@@ -12758,7 +12696,7 @@
         <v>85.3</v>
       </c>
       <c r="AZ87" s="4"/>
-      <c r="BA87" s="65">
+      <c r="BA87" s="22">
         <v>117</v>
       </c>
       <c r="BB87" s="4"/>
@@ -12766,14 +12704,14 @@
       <c r="BD87" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE87" s="73">
+      <c r="BE87" s="18">
         <v>1010</v>
       </c>
-      <c r="BF87" s="73">
+      <c r="BF87" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG87" s="64"/>
-      <c r="BH87" s="64"/>
+      <c r="BG87" s="4"/>
+      <c r="BH87" s="4"/>
       <c r="BI87" s="4"/>
       <c r="BJ87" s="3" t="s">
         <v>179</v>
@@ -12871,7 +12809,7 @@
         <v>78.5</v>
       </c>
       <c r="AZ88" s="4"/>
-      <c r="BA88" s="64">
+      <c r="BA88" s="4">
         <v>111.6</v>
       </c>
       <c r="BB88" s="4"/>
@@ -12879,14 +12817,14 @@
       <c r="BD88" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE88" s="73">
+      <c r="BE88" s="18">
         <v>1010</v>
       </c>
-      <c r="BF88" s="73">
+      <c r="BF88" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG88" s="64"/>
-      <c r="BH88" s="64"/>
+      <c r="BG88" s="4"/>
+      <c r="BH88" s="4"/>
       <c r="BI88" s="4"/>
       <c r="BJ88" s="3" t="s">
         <v>176</v>
@@ -12992,13 +12930,13 @@
       <c r="BD89" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE89" s="73">
+      <c r="BE89" s="18">
         <v>1010</v>
       </c>
-      <c r="BF89" s="73">
+      <c r="BF89" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG89" s="64"/>
+      <c r="BG89" s="4"/>
       <c r="BH89" s="4"/>
       <c r="BI89" s="4"/>
       <c r="BJ89" s="3" t="s">
@@ -13105,13 +13043,13 @@
       <c r="BD90" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE90" s="73">
+      <c r="BE90" s="18">
         <v>1010</v>
       </c>
-      <c r="BF90" s="73">
+      <c r="BF90" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG90" s="64"/>
+      <c r="BG90" s="4"/>
       <c r="BH90" s="4"/>
       <c r="BI90" s="4"/>
       <c r="BJ90" s="3" t="s">
@@ -13218,14 +13156,14 @@
       <c r="BD91" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE91" s="73">
+      <c r="BE91" s="18">
         <v>1010</v>
       </c>
-      <c r="BF91" s="73">
+      <c r="BF91" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG91" s="64"/>
-      <c r="BH91" s="64"/>
+      <c r="BG91" s="4"/>
+      <c r="BH91" s="4"/>
       <c r="BI91" s="4"/>
       <c r="BJ91" s="3" t="s">
         <v>174</v>
@@ -13331,14 +13269,14 @@
       <c r="BD92" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE92" s="73">
+      <c r="BE92" s="18">
         <v>1010</v>
       </c>
-      <c r="BF92" s="73">
+      <c r="BF92" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG92" s="64"/>
-      <c r="BH92" s="64"/>
+      <c r="BG92" s="4"/>
+      <c r="BH92" s="4"/>
       <c r="BI92" s="4"/>
       <c r="BJ92" s="3" t="s">
         <v>173</v>
@@ -13444,13 +13382,13 @@
       <c r="BD93" s="18">
         <v>26.4</v>
       </c>
-      <c r="BE93" s="73">
+      <c r="BE93" s="18">
         <v>1010</v>
       </c>
-      <c r="BF93" s="73">
+      <c r="BF93" s="18">
         <v>46.5</v>
       </c>
-      <c r="BG93" s="64"/>
+      <c r="BG93" s="4"/>
       <c r="BH93" s="4"/>
       <c r="BI93" s="4" t="s">
         <v>90</v>
@@ -13559,14 +13497,14 @@
       <c r="BD94" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE94" s="73">
+      <c r="BE94" s="18">
         <v>1010</v>
       </c>
-      <c r="BF94" s="73">
+      <c r="BF94" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG94" s="64"/>
-      <c r="BH94" s="64"/>
+      <c r="BG94" s="4"/>
+      <c r="BH94" s="4"/>
       <c r="BI94" s="4"/>
       <c r="BJ94" s="3" t="s">
         <v>197</v>
@@ -13672,14 +13610,14 @@
       <c r="BD95" s="18">
         <v>26.4</v>
       </c>
-      <c r="BE95" s="73">
+      <c r="BE95" s="18">
         <v>1010</v>
       </c>
-      <c r="BF95" s="73">
+      <c r="BF95" s="18">
         <v>46.5</v>
       </c>
-      <c r="BG95" s="64"/>
-      <c r="BH95" s="64"/>
+      <c r="BG95" s="4"/>
+      <c r="BH95" s="4"/>
       <c r="BI95" s="4"/>
       <c r="BJ95" s="3" t="s">
         <v>180</v>
@@ -13785,13 +13723,13 @@
       <c r="BD96" s="18">
         <v>26.4</v>
       </c>
-      <c r="BE96" s="73">
+      <c r="BE96" s="18">
         <v>1010</v>
       </c>
-      <c r="BF96" s="73">
+      <c r="BF96" s="18">
         <v>46.5</v>
       </c>
-      <c r="BG96" s="64"/>
+      <c r="BG96" s="4"/>
       <c r="BH96" s="4"/>
       <c r="BI96" s="4"/>
       <c r="BJ96" s="3" t="s">
@@ -13898,14 +13836,14 @@
       <c r="BD97" s="4">
         <v>24.8</v>
       </c>
-      <c r="BE97" s="64">
+      <c r="BE97" s="4">
         <v>1010</v>
       </c>
-      <c r="BF97" s="76">
+      <c r="BF97" s="67">
         <v>47</v>
       </c>
-      <c r="BG97" s="76"/>
-      <c r="BH97" s="64"/>
+      <c r="BG97" s="67"/>
+      <c r="BH97" s="4"/>
       <c r="BI97" s="4"/>
       <c r="BJ97" s="3" t="s">
         <v>190</v>
@@ -14011,14 +13949,14 @@
       <c r="BD98" s="18">
         <v>26.4</v>
       </c>
-      <c r="BE98" s="73">
+      <c r="BE98" s="18">
         <v>1010</v>
       </c>
-      <c r="BF98" s="73">
+      <c r="BF98" s="18">
         <v>46.5</v>
       </c>
-      <c r="BG98" s="64"/>
-      <c r="BH98" s="64"/>
+      <c r="BG98" s="4"/>
+      <c r="BH98" s="4"/>
       <c r="BI98" s="4"/>
       <c r="BJ98" s="3" t="s">
         <v>183</v>
@@ -14124,13 +14062,13 @@
       <c r="BD99" s="4">
         <v>24.8</v>
       </c>
-      <c r="BE99" s="64">
+      <c r="BE99" s="4">
         <v>1010</v>
       </c>
-      <c r="BF99" s="76">
+      <c r="BF99" s="67">
         <v>47</v>
       </c>
-      <c r="BG99" s="76"/>
+      <c r="BG99" s="67"/>
       <c r="BH99" s="4"/>
       <c r="BI99" s="4"/>
       <c r="BJ99" s="3" t="s">
@@ -14237,14 +14175,14 @@
       <c r="BD100" s="4">
         <v>24.8</v>
       </c>
-      <c r="BE100" s="64">
+      <c r="BE100" s="4">
         <v>1010</v>
       </c>
-      <c r="BF100" s="76">
+      <c r="BF100" s="67">
         <v>47</v>
       </c>
-      <c r="BG100" s="76"/>
-      <c r="BH100" s="64"/>
+      <c r="BG100" s="67"/>
+      <c r="BH100" s="4"/>
       <c r="BI100" s="4"/>
       <c r="BJ100" s="3" t="s">
         <v>191</v>
@@ -14350,14 +14288,14 @@
       <c r="BD101" s="4">
         <v>24.8</v>
       </c>
-      <c r="BE101" s="64">
+      <c r="BE101" s="4">
         <v>1010</v>
       </c>
-      <c r="BF101" s="76">
+      <c r="BF101" s="67">
         <v>47</v>
       </c>
-      <c r="BG101" s="76"/>
-      <c r="BH101" s="64"/>
+      <c r="BG101" s="67"/>
+      <c r="BH101" s="4"/>
       <c r="BI101" s="4"/>
       <c r="BJ101" s="3" t="s">
         <v>187</v>
@@ -14463,14 +14401,14 @@
       <c r="BD102" s="4">
         <v>24.8</v>
       </c>
-      <c r="BE102" s="64">
+      <c r="BE102" s="4">
         <v>1010</v>
       </c>
-      <c r="BF102" s="76">
+      <c r="BF102" s="67">
         <v>47</v>
       </c>
-      <c r="BG102" s="76"/>
-      <c r="BH102" s="64"/>
+      <c r="BG102" s="67"/>
+      <c r="BH102" s="4"/>
       <c r="BI102" s="13" t="s">
         <v>97</v>
       </c>
@@ -14578,14 +14516,14 @@
       <c r="BD103" s="4">
         <v>24.8</v>
       </c>
-      <c r="BE103" s="64">
+      <c r="BE103" s="4">
         <v>1010</v>
       </c>
-      <c r="BF103" s="76">
+      <c r="BF103" s="67">
         <v>47</v>
       </c>
-      <c r="BG103" s="76"/>
-      <c r="BH103" s="64"/>
+      <c r="BG103" s="67"/>
+      <c r="BH103" s="4"/>
       <c r="BI103" s="4"/>
       <c r="BJ103" s="3" t="s">
         <v>189</v>
@@ -14691,14 +14629,14 @@
       <c r="BD104" s="4">
         <v>23.9</v>
       </c>
-      <c r="BE104" s="64">
+      <c r="BE104" s="4">
         <v>1010</v>
       </c>
-      <c r="BF104" s="76">
+      <c r="BF104" s="67">
         <v>48.2</v>
       </c>
-      <c r="BG104" s="76"/>
-      <c r="BH104" s="64"/>
+      <c r="BG104" s="67"/>
+      <c r="BH104" s="4"/>
       <c r="BI104" s="4"/>
       <c r="BJ104" s="3" t="s">
         <v>193</v>
@@ -14804,14 +14742,14 @@
       <c r="BD105" s="4">
         <v>24.1</v>
       </c>
-      <c r="BE105" s="64">
+      <c r="BE105" s="4">
         <v>1010</v>
       </c>
-      <c r="BF105" s="76">
+      <c r="BF105" s="67">
         <v>48.2</v>
       </c>
-      <c r="BG105" s="76"/>
-      <c r="BH105" s="64"/>
+      <c r="BG105" s="67"/>
+      <c r="BH105" s="4"/>
       <c r="BI105" s="13" t="s">
         <v>97</v>
       </c>
@@ -14919,14 +14857,14 @@
       <c r="BD106" s="4">
         <v>23.9</v>
       </c>
-      <c r="BE106" s="64">
+      <c r="BE106" s="4">
         <v>1010</v>
       </c>
-      <c r="BF106" s="76">
+      <c r="BF106" s="67">
         <v>48.2</v>
       </c>
-      <c r="BG106" s="76"/>
-      <c r="BH106" s="64"/>
+      <c r="BG106" s="67"/>
+      <c r="BH106" s="4"/>
       <c r="BI106" s="4"/>
       <c r="BJ106" s="3" t="s">
         <v>195</v>
@@ -15032,14 +14970,14 @@
       <c r="BD107" s="4">
         <v>23.9</v>
       </c>
-      <c r="BE107" s="64">
+      <c r="BE107" s="4">
         <v>1010</v>
       </c>
-      <c r="BF107" s="76">
+      <c r="BF107" s="67">
         <v>48.2</v>
       </c>
-      <c r="BG107" s="76"/>
-      <c r="BH107" s="64"/>
+      <c r="BG107" s="67"/>
+      <c r="BH107" s="4"/>
       <c r="BI107" s="13" t="s">
         <v>95</v>
       </c>
@@ -15147,14 +15085,14 @@
       <c r="BD108" s="4">
         <v>24.1</v>
       </c>
-      <c r="BE108" s="64">
+      <c r="BE108" s="4">
         <v>1010</v>
       </c>
-      <c r="BF108" s="76">
+      <c r="BF108" s="67">
         <v>48.2</v>
       </c>
-      <c r="BG108" s="76"/>
-      <c r="BH108" s="64"/>
+      <c r="BG108" s="67"/>
+      <c r="BH108" s="4"/>
       <c r="BI108" s="4"/>
       <c r="BJ108" s="3" t="s">
         <v>185</v>
@@ -15253,14 +15191,14 @@
       <c r="BD109" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE109" s="73">
+      <c r="BE109" s="18">
         <v>1010</v>
       </c>
-      <c r="BF109" s="73">
+      <c r="BF109" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG109" s="64"/>
-      <c r="BH109" s="64"/>
+      <c r="BG109" s="4"/>
+      <c r="BH109" s="4"/>
       <c r="BI109" s="4"/>
       <c r="BJ109" s="3" t="s">
         <v>177</v>
@@ -15359,14 +15297,14 @@
       <c r="BD110" s="4">
         <v>24.1</v>
       </c>
-      <c r="BE110" s="64">
+      <c r="BE110" s="4">
         <v>1010</v>
       </c>
-      <c r="BF110" s="76">
+      <c r="BF110" s="67">
         <v>48.2</v>
       </c>
-      <c r="BG110" s="76"/>
-      <c r="BH110" s="64"/>
+      <c r="BG110" s="67"/>
+      <c r="BH110" s="4"/>
       <c r="BI110" s="4" t="s">
         <v>94</v>
       </c>
@@ -15477,13 +15415,13 @@
       <c r="BD111" s="4">
         <v>26.4</v>
       </c>
-      <c r="BE111" s="64">
+      <c r="BE111" s="4">
         <v>1008</v>
       </c>
-      <c r="BF111" s="76">
+      <c r="BF111" s="67">
         <v>44.4</v>
       </c>
-      <c r="BG111" s="76"/>
+      <c r="BG111" s="67"/>
       <c r="BH111" s="4"/>
       <c r="BI111" s="4"/>
       <c r="BJ111" s="3" t="s">
@@ -15593,13 +15531,13 @@
       <c r="BD112" s="4">
         <v>26.1</v>
       </c>
-      <c r="BE112" s="64">
+      <c r="BE112" s="4">
         <v>1009</v>
       </c>
-      <c r="BF112" s="76">
+      <c r="BF112" s="67">
         <v>45.2</v>
       </c>
-      <c r="BG112" s="76"/>
+      <c r="BG112" s="67"/>
       <c r="BH112" s="4"/>
       <c r="BI112" s="4"/>
       <c r="BJ112" s="3" t="s">
@@ -15709,13 +15647,13 @@
       <c r="BD113" s="16">
         <v>25.5</v>
       </c>
-      <c r="BE113" s="74">
+      <c r="BE113" s="16">
         <v>1012</v>
       </c>
-      <c r="BF113" s="74">
+      <c r="BF113" s="16">
         <v>39.4</v>
       </c>
-      <c r="BG113" s="67"/>
+      <c r="BG113" s="63"/>
       <c r="BH113" s="4"/>
       <c r="BI113" s="4"/>
       <c r="BJ113" s="3" t="s">
@@ -15825,13 +15763,13 @@
       <c r="BD114" s="16">
         <v>25.5</v>
       </c>
-      <c r="BE114" s="74">
+      <c r="BE114" s="16">
         <v>1012</v>
       </c>
-      <c r="BF114" s="74">
+      <c r="BF114" s="16">
         <v>39.4</v>
       </c>
-      <c r="BG114" s="76"/>
+      <c r="BG114" s="67"/>
       <c r="BH114" s="4"/>
       <c r="BI114" s="4"/>
       <c r="BJ114" s="3" t="s">
@@ -15943,13 +15881,13 @@
       <c r="BD115" s="4">
         <v>26.1</v>
       </c>
-      <c r="BE115" s="64">
+      <c r="BE115" s="4">
         <v>1009</v>
       </c>
-      <c r="BF115" s="76">
+      <c r="BF115" s="67">
         <v>45.2</v>
       </c>
-      <c r="BG115" s="76"/>
+      <c r="BG115" s="67"/>
       <c r="BH115" s="4"/>
       <c r="BI115" s="4"/>
       <c r="BJ115" s="3" t="s">
@@ -16059,13 +15997,13 @@
       <c r="BD116" s="16">
         <v>25.5</v>
       </c>
-      <c r="BE116" s="74">
+      <c r="BE116" s="16">
         <v>1012</v>
       </c>
-      <c r="BF116" s="74">
+      <c r="BF116" s="16">
         <v>39.4</v>
       </c>
-      <c r="BG116" s="67"/>
+      <c r="BG116" s="63"/>
       <c r="BH116" s="4"/>
       <c r="BI116" s="4"/>
       <c r="BJ116" s="3" t="s">
@@ -16177,13 +16115,13 @@
       <c r="BD117" s="4">
         <v>26.1</v>
       </c>
-      <c r="BE117" s="64">
+      <c r="BE117" s="4">
         <v>1009</v>
       </c>
-      <c r="BF117" s="76">
+      <c r="BF117" s="67">
         <v>45.2</v>
       </c>
-      <c r="BG117" s="76"/>
+      <c r="BG117" s="67"/>
       <c r="BH117" s="4"/>
       <c r="BI117" s="4"/>
       <c r="BJ117" s="3" t="s">
@@ -16293,13 +16231,13 @@
       <c r="BD118" s="16">
         <v>25.5</v>
       </c>
-      <c r="BE118" s="74">
+      <c r="BE118" s="16">
         <v>1012</v>
       </c>
-      <c r="BF118" s="74">
+      <c r="BF118" s="16">
         <v>39.4</v>
       </c>
-      <c r="BG118" s="67"/>
+      <c r="BG118" s="63"/>
       <c r="BH118" s="4"/>
       <c r="BI118" s="4"/>
       <c r="BJ118" s="3" t="s">
@@ -16411,13 +16349,13 @@
       <c r="BD119" s="4">
         <v>25.2</v>
       </c>
-      <c r="BE119" s="64">
+      <c r="BE119" s="4">
         <v>1010</v>
       </c>
-      <c r="BF119" s="76">
+      <c r="BF119" s="67">
         <v>47</v>
       </c>
-      <c r="BG119" s="76"/>
+      <c r="BG119" s="67"/>
       <c r="BH119" s="4"/>
       <c r="BI119" s="4"/>
       <c r="BJ119" s="3" t="s">
@@ -16529,13 +16467,13 @@
       <c r="BD120" s="4">
         <v>25.7</v>
       </c>
-      <c r="BE120" s="64">
+      <c r="BE120" s="4">
         <v>1009</v>
       </c>
-      <c r="BF120" s="76">
+      <c r="BF120" s="67">
         <v>46.3</v>
       </c>
-      <c r="BG120" s="76"/>
+      <c r="BG120" s="67"/>
       <c r="BH120" s="4"/>
       <c r="BI120" s="4"/>
       <c r="BJ120" s="3" t="s">
@@ -16647,13 +16585,13 @@
       <c r="BD121" s="4">
         <v>25.8</v>
       </c>
-      <c r="BE121" s="64">
+      <c r="BE121" s="4">
         <v>1009</v>
       </c>
-      <c r="BF121" s="76">
+      <c r="BF121" s="67">
         <v>45.7</v>
       </c>
-      <c r="BG121" s="76"/>
+      <c r="BG121" s="67"/>
       <c r="BH121" s="4"/>
       <c r="BI121" s="4"/>
       <c r="BJ121" s="3" t="s">
@@ -16765,13 +16703,13 @@
       <c r="BD122" s="4">
         <v>25.7</v>
       </c>
-      <c r="BE122" s="64">
+      <c r="BE122" s="4">
         <v>1009</v>
       </c>
-      <c r="BF122" s="76">
+      <c r="BF122" s="67">
         <v>46.3</v>
       </c>
-      <c r="BG122" s="76"/>
+      <c r="BG122" s="67"/>
       <c r="BH122" s="4"/>
       <c r="BI122" s="4"/>
       <c r="BJ122" s="3" t="s">
@@ -16883,13 +16821,13 @@
       <c r="BD123" s="4">
         <v>25.8</v>
       </c>
-      <c r="BE123" s="64">
+      <c r="BE123" s="4">
         <v>1009</v>
       </c>
-      <c r="BF123" s="76">
+      <c r="BF123" s="67">
         <v>45.7</v>
       </c>
-      <c r="BG123" s="76"/>
+      <c r="BG123" s="67"/>
       <c r="BH123" s="4"/>
       <c r="BI123" s="4"/>
       <c r="BJ123" s="3" t="s">
@@ -17001,13 +16939,13 @@
       <c r="BD124" s="4">
         <v>25.2</v>
       </c>
-      <c r="BE124" s="64">
+      <c r="BE124" s="4">
         <v>1010</v>
       </c>
-      <c r="BF124" s="76">
+      <c r="BF124" s="67">
         <v>47</v>
       </c>
-      <c r="BG124" s="76"/>
+      <c r="BG124" s="67"/>
       <c r="BH124" s="4"/>
       <c r="BI124" s="4"/>
       <c r="BJ124" s="3" t="s">
@@ -17119,13 +17057,13 @@
       <c r="BD125" s="4">
         <v>25.8</v>
       </c>
-      <c r="BE125" s="64">
+      <c r="BE125" s="4">
         <v>1009</v>
       </c>
-      <c r="BF125" s="76">
+      <c r="BF125" s="67">
         <v>45.7</v>
       </c>
-      <c r="BG125" s="76"/>
+      <c r="BG125" s="67"/>
       <c r="BH125" s="4"/>
       <c r="BI125" s="4"/>
       <c r="BJ125" s="3" t="s">
@@ -17237,14 +17175,14 @@
       <c r="BD126" s="16">
         <v>25.5</v>
       </c>
-      <c r="BE126" s="74">
+      <c r="BE126" s="16">
         <v>1012</v>
       </c>
-      <c r="BF126" s="74">
+      <c r="BF126" s="16">
         <v>39.4</v>
       </c>
-      <c r="BG126" s="67"/>
-      <c r="BH126" s="64"/>
+      <c r="BG126" s="63"/>
+      <c r="BH126" s="4"/>
       <c r="BI126" s="4"/>
       <c r="BJ126" s="3" t="s">
         <v>281</v>
@@ -17355,14 +17293,14 @@
       <c r="BD127" s="16">
         <v>25.5</v>
       </c>
-      <c r="BE127" s="74">
+      <c r="BE127" s="16">
         <v>1012</v>
       </c>
-      <c r="BF127" s="74">
+      <c r="BF127" s="16">
         <v>39.4</v>
       </c>
-      <c r="BG127" s="67"/>
-      <c r="BH127" s="64"/>
+      <c r="BG127" s="63"/>
+      <c r="BH127" s="4"/>
       <c r="BI127" s="4"/>
       <c r="BJ127" s="3" t="s">
         <v>208</v>
@@ -17476,11 +17414,11 @@
       <c r="BE128" s="17">
         <v>1012</v>
       </c>
-      <c r="BF128" s="74">
+      <c r="BF128" s="16">
         <v>40</v>
       </c>
       <c r="BG128" s="15"/>
-      <c r="BH128" s="64"/>
+      <c r="BH128" s="4"/>
       <c r="BI128" s="4"/>
       <c r="BJ128" s="3" t="s">
         <v>276</v>
@@ -17594,11 +17532,11 @@
       <c r="BE129" s="17">
         <v>1012</v>
       </c>
-      <c r="BF129" s="74">
+      <c r="BF129" s="16">
         <v>40</v>
       </c>
       <c r="BG129" s="15"/>
-      <c r="BH129" s="64"/>
+      <c r="BH129" s="4"/>
       <c r="BI129" s="4"/>
       <c r="BJ129" s="3" t="s">
         <v>282</v>
@@ -17712,11 +17650,11 @@
       <c r="BE130" s="17">
         <v>1012</v>
       </c>
-      <c r="BF130" s="74">
+      <c r="BF130" s="16">
         <v>40</v>
       </c>
       <c r="BG130" s="15"/>
-      <c r="BH130" s="64"/>
+      <c r="BH130" s="4"/>
       <c r="BI130" s="4"/>
       <c r="BJ130" s="3" t="s">
         <v>278</v>
@@ -17830,11 +17768,11 @@
       <c r="BE131" s="17">
         <v>1012</v>
       </c>
-      <c r="BF131" s="74">
+      <c r="BF131" s="16">
         <v>39.4</v>
       </c>
       <c r="BG131" s="15"/>
-      <c r="BH131" s="64"/>
+      <c r="BH131" s="4"/>
       <c r="BI131" s="4" t="s">
         <v>100</v>
       </c>
@@ -17947,14 +17885,14 @@
       <c r="BD132" s="16">
         <v>26</v>
       </c>
-      <c r="BE132" s="75">
+      <c r="BE132" s="66">
         <v>1012</v>
       </c>
-      <c r="BF132" s="74">
+      <c r="BF132" s="16">
         <v>40</v>
       </c>
       <c r="BG132" s="61"/>
-      <c r="BH132" s="64"/>
+      <c r="BH132" s="4"/>
       <c r="BI132" s="4"/>
       <c r="BJ132" s="3" t="s">
         <v>277</v>
@@ -18068,11 +18006,11 @@
       <c r="BE133" s="17">
         <v>1012</v>
       </c>
-      <c r="BF133" s="74">
+      <c r="BF133" s="16">
         <v>39.4</v>
       </c>
       <c r="BG133" s="15"/>
-      <c r="BH133" s="64"/>
+      <c r="BH133" s="4"/>
       <c r="BI133" s="4"/>
       <c r="BJ133" s="3" t="s">
         <v>279</v>
@@ -18170,11 +18108,11 @@
       <c r="BE134" s="23">
         <v>1010</v>
       </c>
-      <c r="BF134" s="76">
+      <c r="BF134" s="67">
         <v>47</v>
       </c>
       <c r="BG134" s="59"/>
-      <c r="BH134" s="64"/>
+      <c r="BH134" s="4"/>
       <c r="BI134" s="13" t="s">
         <v>96</v>
       </c>
@@ -18199,7 +18137,7 @@
       <c r="D135" s="8">
         <v>4</v>
       </c>
-      <c r="E135" s="63" t="s">
+      <c r="E135" s="2" t="s">
         <v>558</v>
       </c>
       <c r="F135" s="4" t="s">
@@ -18281,11 +18219,11 @@
       <c r="BE135" s="23">
         <v>1009</v>
       </c>
-      <c r="BF135" s="76">
+      <c r="BF135" s="67">
         <v>46.3</v>
       </c>
       <c r="BG135" s="59"/>
-      <c r="BH135" s="64"/>
+      <c r="BH135" s="4"/>
       <c r="BI135" s="4"/>
       <c r="BJ135" s="3" t="s">
         <v>270</v>
@@ -18395,7 +18333,7 @@
       <c r="BE136" s="17">
         <v>1012</v>
       </c>
-      <c r="BF136" s="74">
+      <c r="BF136" s="16">
         <v>45.5</v>
       </c>
       <c r="BG136" s="15"/>
@@ -18513,7 +18451,7 @@
       <c r="BE137" s="17">
         <v>1012</v>
       </c>
-      <c r="BF137" s="74">
+      <c r="BF137" s="16">
         <v>45.5</v>
       </c>
       <c r="BG137" s="15"/>
@@ -18626,10 +18564,10 @@
       <c r="BD138" s="16">
         <v>24.9</v>
       </c>
-      <c r="BE138" s="75">
+      <c r="BE138" s="66">
         <v>1012</v>
       </c>
-      <c r="BF138" s="74">
+      <c r="BF138" s="16">
         <v>45.5</v>
       </c>
       <c r="BG138" s="61"/>
@@ -18745,7 +18683,7 @@
       <c r="BE139" s="17">
         <v>1012</v>
       </c>
-      <c r="BF139" s="74">
+      <c r="BF139" s="16">
         <v>45.5</v>
       </c>
       <c r="BG139" s="15"/>
@@ -18863,7 +18801,7 @@
       <c r="BE140" s="17">
         <v>1011</v>
       </c>
-      <c r="BF140" s="74">
+      <c r="BF140" s="16">
         <v>40</v>
       </c>
       <c r="BG140" s="15"/>
@@ -18981,7 +18919,7 @@
       <c r="BE141" s="17">
         <v>1011</v>
       </c>
-      <c r="BF141" s="74">
+      <c r="BF141" s="16">
         <v>39.6</v>
       </c>
       <c r="BG141" s="15"/>
@@ -19097,7 +19035,7 @@
       <c r="BE142" s="17">
         <v>1011</v>
       </c>
-      <c r="BF142" s="74">
+      <c r="BF142" s="16">
         <v>39.6</v>
       </c>
       <c r="BG142" s="15"/>
@@ -19213,7 +19151,7 @@
       <c r="BE143" s="17">
         <v>1011</v>
       </c>
-      <c r="BF143" s="74">
+      <c r="BF143" s="16">
         <v>39.6</v>
       </c>
       <c r="BG143" s="15"/>
@@ -19326,10 +19264,10 @@
       <c r="BD144" s="16">
         <v>26.5</v>
       </c>
-      <c r="BE144" s="75">
+      <c r="BE144" s="66">
         <v>1011</v>
       </c>
-      <c r="BF144" s="74">
+      <c r="BF144" s="16">
         <v>40</v>
       </c>
       <c r="BG144" s="61"/>
@@ -19444,7 +19382,7 @@
       <c r="BE145" s="17">
         <v>1013</v>
       </c>
-      <c r="BF145" s="74">
+      <c r="BF145" s="16">
         <v>47.7</v>
       </c>
       <c r="BG145" s="15"/>
@@ -19566,7 +19504,7 @@
       <c r="BE146" s="17">
         <v>1012</v>
       </c>
-      <c r="BF146" s="74">
+      <c r="BF146" s="16">
         <v>40</v>
       </c>
       <c r="BG146" s="15"/>
@@ -19682,7 +19620,7 @@
       <c r="BE147" s="17">
         <v>1011</v>
       </c>
-      <c r="BF147" s="74">
+      <c r="BF147" s="16">
         <v>39.6</v>
       </c>
       <c r="BG147" s="15"/>
@@ -19792,10 +19730,10 @@
       <c r="BD148" s="16">
         <v>24.9</v>
       </c>
-      <c r="BE148" s="74">
+      <c r="BE148" s="16">
         <v>1012</v>
       </c>
-      <c r="BF148" s="74">
+      <c r="BF148" s="16">
         <v>45.5</v>
       </c>
       <c r="BG148" s="15"/>
@@ -19909,10 +19847,10 @@
       <c r="BD149" s="16">
         <v>24.9</v>
       </c>
-      <c r="BE149" s="74">
+      <c r="BE149" s="16">
         <v>1012</v>
       </c>
-      <c r="BF149" s="74">
+      <c r="BF149" s="16">
         <v>45.5</v>
       </c>
       <c r="BG149" s="15"/>
@@ -20029,10 +19967,10 @@
       <c r="BD150" s="16">
         <v>26.5</v>
       </c>
-      <c r="BE150" s="74">
+      <c r="BE150" s="16">
         <v>1011</v>
       </c>
-      <c r="BF150" s="74">
+      <c r="BF150" s="16">
         <v>40</v>
       </c>
       <c r="BG150" s="61"/>
@@ -20143,10 +20081,10 @@
       <c r="BD151" s="16">
         <v>24.9</v>
       </c>
-      <c r="BE151" s="74">
+      <c r="BE151" s="16">
         <v>1012</v>
       </c>
-      <c r="BF151" s="74">
+      <c r="BF151" s="16">
         <v>45.5</v>
       </c>
       <c r="BG151" s="15"/>
@@ -20260,10 +20198,10 @@
       <c r="BD152" s="16">
         <v>24.5</v>
       </c>
-      <c r="BE152" s="74">
+      <c r="BE152" s="16">
         <v>1013</v>
       </c>
-      <c r="BF152" s="74">
+      <c r="BF152" s="16">
         <v>47.7</v>
       </c>
       <c r="BG152" s="15"/>
@@ -20382,10 +20320,10 @@
       <c r="BD153" s="16">
         <v>26.3</v>
       </c>
-      <c r="BE153" s="74">
+      <c r="BE153" s="16">
         <v>1012</v>
       </c>
-      <c r="BF153" s="74">
+      <c r="BF153" s="16">
         <v>40</v>
       </c>
       <c r="BG153" s="15"/>
@@ -20496,10 +20434,10 @@
       <c r="BD154" s="16">
         <v>24.9</v>
       </c>
-      <c r="BE154" s="74">
+      <c r="BE154" s="16">
         <v>1012</v>
       </c>
-      <c r="BF154" s="74">
+      <c r="BF154" s="16">
         <v>45.5</v>
       </c>
       <c r="BG154" s="61"/>
@@ -20611,10 +20549,10 @@
       <c r="BD155" s="16">
         <v>24.5</v>
       </c>
-      <c r="BE155" s="74">
+      <c r="BE155" s="16">
         <v>1013</v>
       </c>
-      <c r="BF155" s="74">
+      <c r="BF155" s="16">
         <v>47.7</v>
       </c>
       <c r="BG155" s="15"/>
@@ -20731,10 +20669,10 @@
       <c r="BD156" s="16">
         <v>26.3</v>
       </c>
-      <c r="BE156" s="74">
+      <c r="BE156" s="16">
         <v>1012</v>
       </c>
-      <c r="BF156" s="74">
+      <c r="BF156" s="16">
         <v>40</v>
       </c>
       <c r="BG156" s="15"/>
@@ -20844,10 +20782,10 @@
       <c r="BD157" s="16">
         <v>24.5</v>
       </c>
-      <c r="BE157" s="74">
+      <c r="BE157" s="16">
         <v>1013</v>
       </c>
-      <c r="BF157" s="74">
+      <c r="BF157" s="16">
         <v>47.7</v>
       </c>
       <c r="BG157" s="15"/>
@@ -20964,10 +20902,10 @@
       <c r="BD158" s="16">
         <v>26.5</v>
       </c>
-      <c r="BE158" s="74">
+      <c r="BE158" s="16">
         <v>1011</v>
       </c>
-      <c r="BF158" s="74">
+      <c r="BF158" s="16">
         <v>40</v>
       </c>
       <c r="BG158" s="15"/>
@@ -21082,10 +21020,10 @@
       <c r="BD159" s="16">
         <v>26.3</v>
       </c>
-      <c r="BE159" s="74">
+      <c r="BE159" s="16">
         <v>1012</v>
       </c>
-      <c r="BF159" s="74">
+      <c r="BF159" s="16">
         <v>40</v>
       </c>
       <c r="BG159" s="15"/>
@@ -21188,10 +21126,10 @@
       <c r="BD160" s="16">
         <v>25.6</v>
       </c>
-      <c r="BE160" s="74">
+      <c r="BE160" s="16">
         <v>1011</v>
       </c>
-      <c r="BF160" s="74">
+      <c r="BF160" s="16">
         <v>44.1</v>
       </c>
       <c r="BG160" s="61"/>
@@ -21296,10 +21234,10 @@
       <c r="BD161" s="22">
         <v>25</v>
       </c>
-      <c r="BE161" s="67">
+      <c r="BE161" s="63">
         <v>1012</v>
       </c>
-      <c r="BF161" s="70">
+      <c r="BF161" s="65">
         <v>54</v>
       </c>
       <c r="BG161" s="15">
@@ -21406,10 +21344,10 @@
       <c r="BD162" s="16">
         <v>25.6</v>
       </c>
-      <c r="BE162" s="74">
+      <c r="BE162" s="16">
         <v>1011</v>
       </c>
-      <c r="BF162" s="74">
+      <c r="BF162" s="16">
         <v>44.1</v>
       </c>
       <c r="BG162" s="15"/>
@@ -21517,10 +21455,10 @@
       <c r="BD163" s="22">
         <v>25.2</v>
       </c>
-      <c r="BE163" s="67">
+      <c r="BE163" s="63">
         <v>1011</v>
       </c>
-      <c r="BF163" s="70">
+      <c r="BF163" s="65">
         <v>54</v>
       </c>
       <c r="BG163" s="15">
@@ -21630,10 +21568,10 @@
       <c r="BD164" s="22">
         <v>25.2</v>
       </c>
-      <c r="BE164" s="67">
+      <c r="BE164" s="63">
         <v>1011</v>
       </c>
-      <c r="BF164" s="70">
+      <c r="BF164" s="65">
         <v>54</v>
       </c>
       <c r="BG164" s="15">
@@ -21740,10 +21678,10 @@
       <c r="BD165" s="16">
         <v>25.3</v>
       </c>
-      <c r="BE165" s="74">
+      <c r="BE165" s="16">
         <v>1012</v>
       </c>
-      <c r="BF165" s="74">
+      <c r="BF165" s="16">
         <v>44.3</v>
       </c>
       <c r="BG165" s="15"/>
@@ -21848,10 +21786,10 @@
       <c r="BD166" s="16">
         <v>26</v>
       </c>
-      <c r="BE166" s="74">
+      <c r="BE166" s="16">
         <v>1012</v>
       </c>
-      <c r="BF166" s="74">
+      <c r="BF166" s="16">
         <v>43</v>
       </c>
       <c r="BG166" s="15"/>
@@ -21959,10 +21897,10 @@
       <c r="BD167" s="22">
         <v>25.1</v>
       </c>
-      <c r="BE167" s="67">
+      <c r="BE167" s="63">
         <v>1011</v>
       </c>
-      <c r="BF167" s="70">
+      <c r="BF167" s="65">
         <v>54</v>
       </c>
       <c r="BG167" s="15">
@@ -22072,10 +22010,10 @@
       <c r="BD168" s="22">
         <v>25.1</v>
       </c>
-      <c r="BE168" s="67">
+      <c r="BE168" s="63">
         <v>1011</v>
       </c>
-      <c r="BF168" s="70">
+      <c r="BF168" s="65">
         <v>54</v>
       </c>
       <c r="BG168" s="15">
@@ -22182,10 +22120,10 @@
       <c r="BD169" s="16">
         <v>26</v>
       </c>
-      <c r="BE169" s="74">
+      <c r="BE169" s="16">
         <v>1012</v>
       </c>
-      <c r="BF169" s="74">
+      <c r="BF169" s="16">
         <v>43</v>
       </c>
       <c r="BG169" s="15"/>
@@ -22290,10 +22228,10 @@
       <c r="BD170" s="16">
         <v>25.6</v>
       </c>
-      <c r="BE170" s="74">
+      <c r="BE170" s="16">
         <v>1011</v>
       </c>
-      <c r="BF170" s="74">
+      <c r="BF170" s="16">
         <v>44.1</v>
       </c>
       <c r="BG170" s="15"/>
@@ -22401,10 +22339,10 @@
       <c r="BD171" s="22">
         <v>25.1</v>
       </c>
-      <c r="BE171" s="67">
+      <c r="BE171" s="63">
         <v>1012</v>
       </c>
-      <c r="BF171" s="70">
+      <c r="BF171" s="65">
         <v>53</v>
       </c>
       <c r="BG171" s="15">
@@ -22517,7 +22455,7 @@
       <c r="BE172" s="14">
         <v>1012</v>
       </c>
-      <c r="BF172" s="70">
+      <c r="BF172" s="65">
         <v>54</v>
       </c>
       <c r="BG172" s="15">
@@ -22627,10 +22565,10 @@
       <c r="BD173" s="22">
         <v>25.1</v>
       </c>
-      <c r="BE173" s="68">
+      <c r="BE173" s="64">
         <v>1012</v>
       </c>
-      <c r="BF173" s="70">
+      <c r="BF173" s="65">
         <v>53</v>
       </c>
       <c r="BG173" s="61">
@@ -22743,7 +22681,7 @@
       <c r="BE174" s="17">
         <v>1012</v>
       </c>
-      <c r="BF174" s="74">
+      <c r="BF174" s="16">
         <v>44.6</v>
       </c>
       <c r="BG174" s="15"/>
@@ -22854,7 +22792,7 @@
       <c r="BE175" s="17">
         <v>1012</v>
       </c>
-      <c r="BF175" s="74">
+      <c r="BF175" s="16">
         <v>44.6</v>
       </c>
       <c r="BG175" s="15"/>
@@ -22965,7 +22903,7 @@
       <c r="BE176" s="17">
         <v>1012</v>
       </c>
-      <c r="BF176" s="74">
+      <c r="BF176" s="16">
         <v>44.3</v>
       </c>
       <c r="BG176" s="15"/>
@@ -23078,7 +23016,7 @@
       <c r="BE177" s="14">
         <v>1012</v>
       </c>
-      <c r="BF177" s="70">
+      <c r="BF177" s="65">
         <v>53</v>
       </c>
       <c r="BG177" s="15">
@@ -23191,7 +23129,7 @@
       <c r="BE178" s="14">
         <v>1011</v>
       </c>
-      <c r="BF178" s="70">
+      <c r="BF178" s="65">
         <v>54</v>
       </c>
       <c r="BG178" s="15">
@@ -23304,7 +23242,7 @@
       <c r="BE179" s="14">
         <v>1012</v>
       </c>
-      <c r="BF179" s="70">
+      <c r="BF179" s="65">
         <v>54</v>
       </c>
       <c r="BG179" s="15">
@@ -23417,11 +23355,11 @@
       <c r="BE180" s="17">
         <v>1012</v>
       </c>
-      <c r="BF180" s="74">
+      <c r="BF180" s="16">
         <v>44.6</v>
       </c>
       <c r="BG180" s="15"/>
-      <c r="BH180" s="71">
+      <c r="BH180" s="7">
         <v>2096</v>
       </c>
       <c r="BI180" s="4"/>
@@ -23528,7 +23466,7 @@
       <c r="BE181" s="17">
         <v>1012</v>
       </c>
-      <c r="BF181" s="74">
+      <c r="BF181" s="16">
         <v>44.3</v>
       </c>
       <c r="BG181" s="15"/>
@@ -23639,11 +23577,11 @@
       <c r="BE182" s="17">
         <v>1012</v>
       </c>
-      <c r="BF182" s="74">
+      <c r="BF182" s="16">
         <v>44.6</v>
       </c>
       <c r="BG182" s="15"/>
-      <c r="BH182" s="71">
+      <c r="BH182" s="7">
         <v>2096</v>
       </c>
       <c r="BI182" s="4"/>
@@ -23740,13 +23678,13 @@
       <c r="BE183" s="14">
         <v>1012</v>
       </c>
-      <c r="BF183" s="70">
+      <c r="BF183" s="65">
         <v>54</v>
       </c>
       <c r="BG183" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH183" s="64">
+      <c r="BH183" s="4">
         <v>2096</v>
       </c>
       <c r="BI183" s="4"/>
@@ -23857,7 +23795,7 @@
       <c r="BE184" s="42">
         <v>1004</v>
       </c>
-      <c r="BF184" s="69">
+      <c r="BF184" s="60">
         <v>61</v>
       </c>
       <c r="BG184" s="44">
@@ -23974,7 +23912,7 @@
       <c r="BE185" s="42">
         <v>1004</v>
       </c>
-      <c r="BF185" s="69">
+      <c r="BF185" s="60">
         <v>61</v>
       </c>
       <c r="BG185" s="44">
@@ -24091,7 +24029,7 @@
       <c r="BE186" s="42">
         <v>1004</v>
       </c>
-      <c r="BF186" s="69">
+      <c r="BF186" s="60">
         <v>64</v>
       </c>
       <c r="BG186" s="44">
@@ -24206,7 +24144,7 @@
       <c r="BE187" s="42">
         <v>1004</v>
       </c>
-      <c r="BF187" s="69">
+      <c r="BF187" s="60">
         <v>62</v>
       </c>
       <c r="BG187" s="44">
@@ -24323,7 +24261,7 @@
       <c r="BE188" s="42">
         <v>1004</v>
       </c>
-      <c r="BF188" s="69">
+      <c r="BF188" s="60">
         <v>62</v>
       </c>
       <c r="BG188" s="44">
@@ -24437,7 +24375,7 @@
       <c r="BE189" s="42">
         <v>1004</v>
       </c>
-      <c r="BF189" s="69">
+      <c r="BF189" s="60">
         <v>61</v>
       </c>
       <c r="BG189" s="44">
@@ -24554,7 +24492,7 @@
       <c r="BE190" s="42">
         <v>1004</v>
       </c>
-      <c r="BF190" s="69">
+      <c r="BF190" s="60">
         <v>61</v>
       </c>
       <c r="BG190" s="44">
@@ -24671,7 +24609,7 @@
       <c r="BE191" s="42">
         <v>1004</v>
       </c>
-      <c r="BF191" s="69">
+      <c r="BF191" s="60">
         <v>61</v>
       </c>
       <c r="BG191" s="44">
@@ -24788,7 +24726,7 @@
       <c r="BE192" s="42">
         <v>1004</v>
       </c>
-      <c r="BF192" s="69">
+      <c r="BF192" s="60">
         <v>62</v>
       </c>
       <c r="BG192" s="44">
@@ -24905,7 +24843,7 @@
       <c r="BE193" s="42">
         <v>1004</v>
       </c>
-      <c r="BF193" s="69">
+      <c r="BF193" s="60">
         <v>64</v>
       </c>
       <c r="BG193" s="44">
@@ -25022,7 +24960,7 @@
       <c r="BE194" s="42">
         <v>1004</v>
       </c>
-      <c r="BF194" s="69">
+      <c r="BF194" s="60">
         <v>64</v>
       </c>
       <c r="BG194" s="44">
@@ -25139,7 +25077,7 @@
       <c r="BE195" s="42">
         <v>1004</v>
       </c>
-      <c r="BF195" s="69">
+      <c r="BF195" s="60">
         <v>64</v>
       </c>
       <c r="BG195" s="44">
@@ -25256,7 +25194,7 @@
       <c r="BE196" s="42">
         <v>1004</v>
       </c>
-      <c r="BF196" s="69">
+      <c r="BF196" s="60">
         <v>64</v>
       </c>
       <c r="BG196" s="44">
@@ -25373,7 +25311,7 @@
       <c r="BE197" s="42">
         <v>1004</v>
       </c>
-      <c r="BF197" s="69">
+      <c r="BF197" s="60">
         <v>64</v>
       </c>
       <c r="BG197" s="44">
@@ -25490,7 +25428,7 @@
       <c r="BE198" s="42">
         <v>1004</v>
       </c>
-      <c r="BF198" s="69">
+      <c r="BF198" s="60">
         <v>62</v>
       </c>
       <c r="BG198" s="44">
@@ -25607,7 +25545,7 @@
       <c r="BE199" s="42">
         <v>1004</v>
       </c>
-      <c r="BF199" s="69">
+      <c r="BF199" s="60">
         <v>64</v>
       </c>
       <c r="BG199" s="44">
@@ -25724,7 +25662,7 @@
       <c r="BE200" s="42">
         <v>1004</v>
       </c>
-      <c r="BF200" s="69">
+      <c r="BF200" s="60">
         <v>64</v>
       </c>
       <c r="BG200" s="44">
@@ -25830,7 +25768,7 @@
       <c r="AX201" s="2"/>
       <c r="AY201" s="7"/>
       <c r="AZ201" s="4"/>
-      <c r="BA201" s="65">
+      <c r="BA201" s="22">
         <v>113.4</v>
       </c>
       <c r="BB201" s="2"/>
@@ -25841,13 +25779,13 @@
       <c r="BE201" s="42">
         <v>1004</v>
       </c>
-      <c r="BF201" s="69">
+      <c r="BF201" s="60">
         <v>62</v>
       </c>
       <c r="BG201" s="44">
         <v>1.165</v>
       </c>
-      <c r="BH201" s="63">
+      <c r="BH201" s="2">
         <v>2096</v>
       </c>
       <c r="BI201" s="2"/>
@@ -25958,7 +25896,7 @@
       <c r="BE202" s="42">
         <v>1004</v>
       </c>
-      <c r="BF202" s="69">
+      <c r="BF202" s="60">
         <v>62</v>
       </c>
       <c r="BG202" s="44">
@@ -27937,7 +27875,7 @@
       <c r="BE219" s="42">
         <v>1005</v>
       </c>
-      <c r="BF219" s="69">
+      <c r="BF219" s="60">
         <v>51</v>
       </c>
       <c r="BG219" s="44">
@@ -28052,7 +27990,7 @@
       <c r="BE220" s="42">
         <v>1005</v>
       </c>
-      <c r="BF220" s="69">
+      <c r="BF220" s="60">
         <v>48</v>
       </c>
       <c r="BG220" s="44">
@@ -28167,7 +28105,7 @@
       <c r="BE221" s="42">
         <v>1005</v>
       </c>
-      <c r="BF221" s="69">
+      <c r="BF221" s="60">
         <v>56</v>
       </c>
       <c r="BG221" s="44">
@@ -28284,7 +28222,7 @@
       <c r="BE222" s="42">
         <v>1006</v>
       </c>
-      <c r="BF222" s="69">
+      <c r="BF222" s="60">
         <v>53</v>
       </c>
       <c r="BG222" s="44">
@@ -28399,7 +28337,7 @@
       <c r="BE223" s="42">
         <v>1005</v>
       </c>
-      <c r="BF223" s="69">
+      <c r="BF223" s="60">
         <v>56</v>
       </c>
       <c r="BG223" s="44">
@@ -28516,7 +28454,7 @@
       <c r="BE224" s="42">
         <v>1006</v>
       </c>
-      <c r="BF224" s="69">
+      <c r="BF224" s="60">
         <v>53</v>
       </c>
       <c r="BG224" s="44">
@@ -28626,13 +28564,13 @@
       <c r="BE225" s="42">
         <v>1005</v>
       </c>
-      <c r="BF225" s="69">
+      <c r="BF225" s="60">
         <v>51</v>
       </c>
       <c r="BG225" s="44">
         <v>1.167</v>
       </c>
-      <c r="BH225" s="63">
+      <c r="BH225" s="2">
         <v>2096</v>
       </c>
       <c r="BI225" s="2"/>
@@ -30719,7 +30657,7 @@
       <c r="BG243" s="44">
         <v>1.169</v>
       </c>
-      <c r="BH243" s="63">
+      <c r="BH243" s="2">
         <v>2096</v>
       </c>
       <c r="BI243" s="2" t="s">
@@ -30746,7 +30684,7 @@
       <c r="D244" s="8">
         <v>3</v>
       </c>
-      <c r="E244" s="63" t="s">
+      <c r="E244" s="2" t="s">
         <v>383</v>
       </c>
       <c r="F244" s="4" t="s">
@@ -30826,7 +30764,7 @@
       <c r="BG244" s="44">
         <v>1.167</v>
       </c>
-      <c r="BH244" s="63">
+      <c r="BH244" s="2">
         <v>2096</v>
       </c>
       <c r="BI244" s="2" t="s">
@@ -30933,7 +30871,7 @@
       <c r="BG245" s="44">
         <v>1.1659999999999999</v>
       </c>
-      <c r="BH245" s="63">
+      <c r="BH245" s="2">
         <v>2096</v>
       </c>
       <c r="BI245" s="2" t="s">
@@ -31040,7 +30978,7 @@
       <c r="BG246" s="44">
         <v>1.1659999999999999</v>
       </c>
-      <c r="BH246" s="63">
+      <c r="BH246" s="2">
         <v>2096</v>
       </c>
       <c r="BI246" s="2" t="s">
@@ -39697,7 +39635,7 @@
         <v>81</v>
       </c>
       <c r="AZ323" s="4"/>
-      <c r="BA323" s="64">
+      <c r="BA323" s="4">
         <v>117</v>
       </c>
       <c r="BB323" s="2"/>
@@ -39714,7 +39652,7 @@
       <c r="BG323" s="44">
         <v>1.137</v>
       </c>
-      <c r="BH323" s="66">
+      <c r="BH323" s="57">
         <v>2096</v>
       </c>
       <c r="BI323" s="2"/>
@@ -40060,7 +39998,7 @@
       <c r="BG326" s="44">
         <v>1.137</v>
       </c>
-      <c r="BH326" s="66">
+      <c r="BH326" s="57">
         <v>2096</v>
       </c>
       <c r="BI326" s="2"/>
@@ -49989,10 +49927,10 @@
       <c r="BD413" s="22">
         <v>24</v>
       </c>
-      <c r="BE413" s="68">
+      <c r="BE413" s="64">
         <v>1009</v>
       </c>
-      <c r="BF413" s="77">
+      <c r="BF413" s="68">
         <v>62</v>
       </c>
       <c r="BG413" s="61">
@@ -50946,7 +50884,7 @@
       <c r="BM421"/>
       <c r="BR421"/>
     </row>
-    <row r="422" spans="1:70" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A422" s="2" t="s">
         <v>13</v>
       </c>
@@ -50954,12 +50892,12 @@
         <v>220</v>
       </c>
       <c r="C422" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D422" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D422" s="8">
         <v>1</v>
       </c>
-      <c r="E422" s="80" t="s">
+      <c r="E422" s="2" t="s">
         <v>600</v>
       </c>
       <c r="F422" s="4" t="s">
@@ -50971,30 +50909,23 @@
       <c r="H422" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="I422" s="81">
+      <c r="I422" s="7">
         <v>0.19359999999999999</v>
       </c>
-      <c r="J422" s="81">
+      <c r="J422" s="7">
         <v>0.19359999999999999</v>
       </c>
-      <c r="K422" s="82">
+      <c r="K422" s="50">
         <v>3.8E-3</v>
       </c>
-      <c r="L422" s="81"/>
-      <c r="M422" s="83"/>
+      <c r="L422" s="7"/>
       <c r="N422" s="7">
         <v>-0.44</v>
       </c>
       <c r="O422" s="4"/>
-      <c r="P422" s="81">
+      <c r="P422" s="7">
         <v>1.3065</v>
       </c>
-      <c r="Q422" s="81"/>
-      <c r="R422" s="83"/>
-      <c r="S422" s="83"/>
-      <c r="T422" s="83"/>
-      <c r="U422" s="83"/>
-      <c r="V422" s="81"/>
       <c r="W422" s="4"/>
       <c r="X422" s="4"/>
       <c r="Y422" s="4"/>
@@ -51029,16 +50960,16 @@
       <c r="BB422" s="2"/>
       <c r="BC422" s="2"/>
       <c r="BD422" s="2"/>
-      <c r="BE422" s="84"/>
-      <c r="BF422" s="85"/>
-      <c r="BG422" s="86"/>
+      <c r="BE422" s="70"/>
+      <c r="BF422" s="71"/>
+      <c r="BG422" s="72"/>
       <c r="BH422" s="2"/>
       <c r="BI422" s="2"/>
       <c r="BJ422" s="3" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="423" spans="1:70" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A423" s="2" t="s">
         <v>13</v>
       </c>
@@ -51046,12 +50977,12 @@
         <v>220</v>
       </c>
       <c r="C423" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D423" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D423" s="8">
         <v>2</v>
       </c>
-      <c r="E423" s="80" t="s">
+      <c r="E423" s="2" t="s">
         <v>450</v>
       </c>
       <c r="F423" s="4" t="s">
@@ -51063,30 +50994,23 @@
       <c r="H423" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="I423" s="81">
+      <c r="I423" s="7">
         <v>0.17957999999999999</v>
       </c>
       <c r="J423" s="7">
         <v>0.18920000000000001</v>
       </c>
-      <c r="K423" s="82">
+      <c r="K423" s="50">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="L423" s="81"/>
-      <c r="M423" s="83"/>
+      <c r="L423" s="7"/>
       <c r="N423" s="7">
         <v>-0.02</v>
       </c>
       <c r="O423" s="4"/>
-      <c r="P423" s="81">
+      <c r="P423" s="7">
         <v>1.3065</v>
       </c>
-      <c r="Q423" s="81"/>
-      <c r="R423" s="83"/>
-      <c r="S423" s="83"/>
-      <c r="T423" s="83"/>
-      <c r="U423" s="83"/>
-      <c r="V423" s="81"/>
       <c r="W423" s="4"/>
       <c r="X423" s="4"/>
       <c r="Y423" s="4"/>
@@ -51121,16 +51045,16 @@
       <c r="BB423" s="2"/>
       <c r="BC423" s="2"/>
       <c r="BD423" s="2"/>
-      <c r="BE423" s="84"/>
-      <c r="BF423" s="85"/>
-      <c r="BG423" s="86"/>
+      <c r="BE423" s="70"/>
+      <c r="BF423" s="71"/>
+      <c r="BG423" s="72"/>
       <c r="BH423" s="2"/>
       <c r="BI423" s="2"/>
       <c r="BJ423" s="3" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="424" spans="1:70" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A424" s="2" t="s">
         <v>13</v>
       </c>
@@ -51138,12 +51062,12 @@
         <v>220</v>
       </c>
       <c r="C424" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D424" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D424" s="8">
         <v>3</v>
       </c>
-      <c r="E424" s="80" t="s">
+      <c r="E424" s="2" t="s">
         <v>601</v>
       </c>
       <c r="F424" s="4" t="s">
@@ -51155,30 +51079,23 @@
       <c r="H424" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="I424" s="81">
+      <c r="I424" s="7">
         <v>0.17510000000000001</v>
       </c>
       <c r="J424" s="7">
         <v>0.188</v>
       </c>
-      <c r="K424" s="82">
+      <c r="K424" s="50">
         <v>2.3E-3</v>
       </c>
-      <c r="L424" s="81"/>
-      <c r="M424" s="83"/>
+      <c r="L424" s="7"/>
       <c r="N424" s="7">
         <v>0.16</v>
       </c>
       <c r="O424" s="4"/>
-      <c r="P424" s="81">
+      <c r="P424" s="7">
         <v>1.3065</v>
       </c>
-      <c r="Q424" s="81"/>
-      <c r="R424" s="83"/>
-      <c r="S424" s="83"/>
-      <c r="T424" s="83"/>
-      <c r="U424" s="83"/>
-      <c r="V424" s="81"/>
       <c r="W424" s="4"/>
       <c r="X424" s="4"/>
       <c r="Y424" s="4"/>
@@ -51213,16 +51130,16 @@
       <c r="BB424" s="2"/>
       <c r="BC424" s="2"/>
       <c r="BD424" s="2"/>
-      <c r="BE424" s="84"/>
-      <c r="BF424" s="85"/>
-      <c r="BG424" s="86"/>
+      <c r="BE424" s="70"/>
+      <c r="BF424" s="71"/>
+      <c r="BG424" s="72"/>
       <c r="BH424" s="2"/>
       <c r="BI424" s="2"/>
       <c r="BJ424" s="3" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="425" spans="1:70" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A425" s="2" t="s">
         <v>13</v>
       </c>
@@ -51230,12 +51147,12 @@
         <v>220</v>
       </c>
       <c r="C425" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D425" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D425" s="8">
         <v>4</v>
       </c>
-      <c r="E425" s="80" t="s">
+      <c r="E425" s="2" t="s">
         <v>600</v>
       </c>
       <c r="F425" s="4" t="s">
@@ -51247,30 +51164,23 @@
       <c r="H425" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="I425" s="81">
+      <c r="I425" s="7">
         <v>0.19370000000000001</v>
       </c>
-      <c r="J425" s="81">
+      <c r="J425" s="7">
         <v>0.19370000000000001</v>
       </c>
-      <c r="K425" s="82">
+      <c r="K425" s="50">
         <v>1.8E-3</v>
       </c>
-      <c r="L425" s="81"/>
-      <c r="M425" s="83"/>
+      <c r="L425" s="7"/>
       <c r="N425" s="7">
         <v>-0.53</v>
       </c>
       <c r="O425" s="4"/>
-      <c r="P425" s="81">
+      <c r="P425" s="7">
         <v>1.3065</v>
       </c>
-      <c r="Q425" s="81"/>
-      <c r="R425" s="83"/>
-      <c r="S425" s="83"/>
-      <c r="T425" s="83"/>
-      <c r="U425" s="83"/>
-      <c r="V425" s="81"/>
       <c r="W425" s="4"/>
       <c r="X425" s="4"/>
       <c r="Y425" s="4"/>
@@ -51305,16 +51215,16 @@
       <c r="BB425" s="2"/>
       <c r="BC425" s="2"/>
       <c r="BD425" s="2"/>
-      <c r="BE425" s="84"/>
-      <c r="BF425" s="85"/>
-      <c r="BG425" s="86"/>
+      <c r="BE425" s="70"/>
+      <c r="BF425" s="71"/>
+      <c r="BG425" s="72"/>
       <c r="BH425" s="2"/>
       <c r="BI425" s="2"/>
       <c r="BJ425" s="3" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="426" spans="1:70" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A426" s="2" t="s">
         <v>13</v>
       </c>
@@ -51322,12 +51232,12 @@
         <v>220</v>
       </c>
       <c r="C426" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D426" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D426" s="8">
         <v>5</v>
       </c>
-      <c r="E426" s="80" t="s">
+      <c r="E426" s="2" t="s">
         <v>450</v>
       </c>
       <c r="F426" s="4" t="s">
@@ -51339,30 +51249,23 @@
       <c r="H426" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="I426" s="81">
+      <c r="I426" s="7">
         <v>0.18129999999999999</v>
       </c>
       <c r="J426" s="7">
         <v>0.19089999999999999</v>
       </c>
-      <c r="K426" s="82">
+      <c r="K426" s="50">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="L426" s="81"/>
-      <c r="M426" s="83"/>
+      <c r="L426" s="7"/>
       <c r="N426" s="7">
         <v>0.01</v>
       </c>
       <c r="O426" s="4"/>
-      <c r="P426" s="81">
+      <c r="P426" s="7">
         <v>1.3065</v>
       </c>
-      <c r="Q426" s="81"/>
-      <c r="R426" s="83"/>
-      <c r="S426" s="83"/>
-      <c r="T426" s="83"/>
-      <c r="U426" s="83"/>
-      <c r="V426" s="81"/>
       <c r="W426" s="4"/>
       <c r="X426" s="4"/>
       <c r="Y426" s="4"/>
@@ -51397,16 +51300,16 @@
       <c r="BB426" s="2"/>
       <c r="BC426" s="2"/>
       <c r="BD426" s="2"/>
-      <c r="BE426" s="84"/>
-      <c r="BF426" s="85"/>
-      <c r="BG426" s="86"/>
+      <c r="BE426" s="70"/>
+      <c r="BF426" s="71"/>
+      <c r="BG426" s="72"/>
       <c r="BH426" s="2"/>
       <c r="BI426" s="2"/>
       <c r="BJ426" s="3" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="427" spans="1:70" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A427" s="2" t="s">
         <v>13</v>
       </c>
@@ -51414,12 +51317,12 @@
         <v>220</v>
       </c>
       <c r="C427" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D427" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D427" s="8">
         <v>6</v>
       </c>
-      <c r="E427" s="80" t="s">
+      <c r="E427" s="2" t="s">
         <v>601</v>
       </c>
       <c r="F427" s="4" t="s">
@@ -51431,30 +51334,23 @@
       <c r="H427" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="I427" s="81">
+      <c r="I427" s="7">
         <v>0.1726</v>
       </c>
       <c r="J427" s="7">
         <v>0.1855</v>
       </c>
-      <c r="K427" s="82">
+      <c r="K427" s="50">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="L427" s="81"/>
-      <c r="M427" s="83"/>
+      <c r="L427" s="7"/>
       <c r="N427" s="7">
         <v>0.16</v>
       </c>
       <c r="O427" s="4"/>
-      <c r="P427" s="81">
+      <c r="P427" s="7">
         <v>1.3065</v>
       </c>
-      <c r="Q427" s="81"/>
-      <c r="R427" s="83"/>
-      <c r="S427" s="83"/>
-      <c r="T427" s="83"/>
-      <c r="U427" s="83"/>
-      <c r="V427" s="81"/>
       <c r="W427" s="4"/>
       <c r="X427" s="4"/>
       <c r="Y427" s="4"/>
@@ -51489,16 +51385,16 @@
       <c r="BB427" s="2"/>
       <c r="BC427" s="2"/>
       <c r="BD427" s="2"/>
-      <c r="BE427" s="84"/>
-      <c r="BF427" s="85"/>
-      <c r="BG427" s="86"/>
+      <c r="BE427" s="70"/>
+      <c r="BF427" s="71"/>
+      <c r="BG427" s="72"/>
       <c r="BH427" s="2"/>
       <c r="BI427" s="2"/>
       <c r="BJ427" s="3" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="428" spans="1:70" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A428" s="2" t="s">
         <v>13</v>
       </c>
@@ -51506,12 +51402,12 @@
         <v>17</v>
       </c>
       <c r="C428" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D428" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D428" s="8">
         <v>1</v>
       </c>
-      <c r="E428" s="80" t="s">
+      <c r="E428" s="2" t="s">
         <v>552</v>
       </c>
       <c r="F428" s="4" t="s">
@@ -51523,30 +51419,23 @@
       <c r="H428" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="I428" s="81">
+      <c r="I428" s="7">
         <v>0.17080000000000001</v>
       </c>
-      <c r="J428" s="81">
+      <c r="J428" s="7">
         <v>0.17080000000000001</v>
       </c>
-      <c r="K428" s="82">
+      <c r="K428" s="50">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="L428" s="81"/>
-      <c r="M428" s="83"/>
+      <c r="L428" s="7"/>
       <c r="N428" s="7">
         <v>-0.43</v>
       </c>
       <c r="O428" s="4"/>
-      <c r="P428" s="81">
+      <c r="P428" s="7">
         <v>1.2809999999999999</v>
       </c>
-      <c r="Q428" s="81"/>
-      <c r="R428" s="83"/>
-      <c r="S428" s="83"/>
-      <c r="T428" s="83"/>
-      <c r="U428" s="83"/>
-      <c r="V428" s="81"/>
       <c r="W428" s="4"/>
       <c r="X428" s="4"/>
       <c r="Y428" s="4"/>
@@ -51581,9 +51470,9 @@
       <c r="BB428" s="2"/>
       <c r="BC428" s="2"/>
       <c r="BD428" s="2"/>
-      <c r="BE428" s="84"/>
-      <c r="BF428" s="85"/>
-      <c r="BG428" s="86"/>
+      <c r="BE428" s="70"/>
+      <c r="BF428" s="71"/>
+      <c r="BG428" s="72"/>
       <c r="BH428" s="2"/>
       <c r="BI428" s="2"/>
       <c r="BJ428" s="3" t="s">
@@ -51598,12 +51487,12 @@
         <v>17</v>
       </c>
       <c r="C429" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D429" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D429" s="8">
         <v>2</v>
       </c>
-      <c r="E429" s="80" t="s">
+      <c r="E429" s="2" t="s">
         <v>552</v>
       </c>
       <c r="F429" s="4" t="s">
@@ -51615,30 +51504,23 @@
       <c r="H429" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="I429" s="81">
+      <c r="I429" s="7">
         <v>0.16880000000000001</v>
       </c>
-      <c r="J429" s="81">
+      <c r="J429" s="7">
         <v>0.16880000000000001</v>
       </c>
-      <c r="K429" s="82">
+      <c r="K429" s="50">
         <v>1.5E-3</v>
       </c>
-      <c r="L429" s="81"/>
-      <c r="M429" s="83"/>
+      <c r="L429" s="7"/>
       <c r="N429" s="7">
         <v>-0.46</v>
       </c>
       <c r="O429" s="4"/>
-      <c r="P429" s="81">
+      <c r="P429" s="7">
         <v>1.2809999999999999</v>
       </c>
-      <c r="Q429" s="81"/>
-      <c r="R429" s="83"/>
-      <c r="S429" s="83"/>
-      <c r="T429" s="83"/>
-      <c r="U429" s="83"/>
-      <c r="V429" s="81"/>
       <c r="W429" s="4"/>
       <c r="X429" s="4"/>
       <c r="Y429" s="4"/>
@@ -51673,16 +51555,16 @@
       <c r="BB429" s="2"/>
       <c r="BC429" s="2"/>
       <c r="BD429" s="2"/>
-      <c r="BE429" s="84"/>
-      <c r="BF429" s="85"/>
-      <c r="BG429" s="86"/>
+      <c r="BE429" s="70"/>
+      <c r="BF429" s="71"/>
+      <c r="BG429" s="72"/>
       <c r="BH429" s="2"/>
       <c r="BI429" s="2"/>
       <c r="BJ429" s="38" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="430" spans="1:70" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A430" s="2" t="s">
         <v>13</v>
       </c>
@@ -51690,12 +51572,12 @@
         <v>17</v>
       </c>
       <c r="C430" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D430" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D430" s="8">
         <v>3</v>
       </c>
-      <c r="E430" s="80" t="s">
+      <c r="E430" s="2" t="s">
         <v>552</v>
       </c>
       <c r="F430" s="4" t="s">
@@ -51707,30 +51589,23 @@
       <c r="H430" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="I430" s="81">
+      <c r="I430" s="7">
         <v>0.16819999999999999</v>
       </c>
-      <c r="J430" s="81">
+      <c r="J430" s="7">
         <v>0.16819999999999999</v>
       </c>
-      <c r="K430" s="82">
+      <c r="K430" s="50">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="L430" s="81"/>
-      <c r="M430" s="83"/>
+      <c r="L430" s="7"/>
       <c r="N430" s="7">
         <v>-0.41</v>
       </c>
       <c r="O430" s="4"/>
-      <c r="P430" s="81">
+      <c r="P430" s="7">
         <v>1.2809999999999999</v>
       </c>
-      <c r="Q430" s="81"/>
-      <c r="R430" s="83"/>
-      <c r="S430" s="83"/>
-      <c r="T430" s="83"/>
-      <c r="U430" s="83"/>
-      <c r="V430" s="81"/>
       <c r="W430" s="4"/>
       <c r="X430" s="4"/>
       <c r="Y430" s="4"/>
@@ -51765,16 +51640,16 @@
       <c r="BB430" s="2"/>
       <c r="BC430" s="2"/>
       <c r="BD430" s="2"/>
-      <c r="BE430" s="84"/>
-      <c r="BF430" s="85"/>
-      <c r="BG430" s="86"/>
+      <c r="BE430" s="70"/>
+      <c r="BF430" s="71"/>
+      <c r="BG430" s="72"/>
       <c r="BH430" s="2"/>
       <c r="BI430" s="2"/>
       <c r="BJ430" s="3" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="431" spans="1:70" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A431" s="2" t="s">
         <v>13</v>
       </c>
@@ -51782,12 +51657,12 @@
         <v>17</v>
       </c>
       <c r="C431" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D431" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D431" s="8">
         <v>4</v>
       </c>
-      <c r="E431" s="80" t="s">
+      <c r="E431" s="2" t="s">
         <v>552</v>
       </c>
       <c r="F431" s="4" t="s">
@@ -51799,30 +51674,23 @@
       <c r="H431" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="I431" s="81">
+      <c r="I431" s="7">
         <v>0.1676</v>
       </c>
-      <c r="J431" s="81">
+      <c r="J431" s="7">
         <v>0.1676</v>
       </c>
-      <c r="K431" s="82">
+      <c r="K431" s="50">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="L431" s="81"/>
-      <c r="M431" s="83"/>
+      <c r="L431" s="7"/>
       <c r="N431" s="7">
         <v>-0.45</v>
       </c>
       <c r="O431" s="4"/>
-      <c r="P431" s="81">
+      <c r="P431" s="7">
         <v>1.2809999999999999</v>
       </c>
-      <c r="Q431" s="81"/>
-      <c r="R431" s="83"/>
-      <c r="S431" s="83"/>
-      <c r="T431" s="83"/>
-      <c r="U431" s="83"/>
-      <c r="V431" s="81"/>
       <c r="W431" s="4"/>
       <c r="X431" s="4"/>
       <c r="Y431" s="4"/>
@@ -51857,16 +51725,16 @@
       <c r="BB431" s="2"/>
       <c r="BC431" s="2"/>
       <c r="BD431" s="2"/>
-      <c r="BE431" s="84"/>
-      <c r="BF431" s="85"/>
-      <c r="BG431" s="86"/>
+      <c r="BE431" s="70"/>
+      <c r="BF431" s="71"/>
+      <c r="BG431" s="72"/>
       <c r="BH431" s="2"/>
       <c r="BI431" s="2"/>
       <c r="BJ431" s="3" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="432" spans="1:70" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A432" s="2" t="s">
         <v>13</v>
       </c>
@@ -51874,12 +51742,12 @@
         <v>17</v>
       </c>
       <c r="C432" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D432" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D432" s="8">
         <v>5</v>
       </c>
-      <c r="E432" s="80" t="s">
+      <c r="E432" s="2" t="s">
         <v>552</v>
       </c>
       <c r="F432" s="4" t="s">
@@ -51891,30 +51759,23 @@
       <c r="H432" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="I432" s="81">
+      <c r="I432" s="7">
         <v>0.16700000000000001</v>
       </c>
-      <c r="J432" s="81">
+      <c r="J432" s="7">
         <v>0.16700000000000001</v>
       </c>
-      <c r="K432" s="82">
+      <c r="K432" s="50">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="L432" s="81"/>
-      <c r="M432" s="83"/>
+      <c r="L432" s="7"/>
       <c r="N432" s="7">
         <v>-0.43</v>
       </c>
       <c r="O432" s="4"/>
-      <c r="P432" s="81">
+      <c r="P432" s="7">
         <v>1.2809999999999999</v>
       </c>
-      <c r="Q432" s="81"/>
-      <c r="R432" s="83"/>
-      <c r="S432" s="83"/>
-      <c r="T432" s="83"/>
-      <c r="U432" s="83"/>
-      <c r="V432" s="81"/>
       <c r="W432" s="4"/>
       <c r="X432" s="4"/>
       <c r="Y432" s="4"/>
@@ -51949,16 +51810,16 @@
       <c r="BB432" s="2"/>
       <c r="BC432" s="2"/>
       <c r="BD432" s="2"/>
-      <c r="BE432" s="84"/>
-      <c r="BF432" s="85"/>
-      <c r="BG432" s="86"/>
+      <c r="BE432" s="70"/>
+      <c r="BF432" s="71"/>
+      <c r="BG432" s="72"/>
       <c r="BH432" s="2"/>
       <c r="BI432" s="2"/>
       <c r="BJ432" s="3" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="433" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A433" s="2" t="s">
         <v>13</v>
       </c>
@@ -51966,12 +51827,12 @@
         <v>25</v>
       </c>
       <c r="C433" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D433" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D433" s="8">
         <v>1</v>
       </c>
-      <c r="E433" s="80" t="s">
+      <c r="E433" s="2" t="s">
         <v>547</v>
       </c>
       <c r="F433" s="4" t="s">
@@ -51983,30 +51844,23 @@
       <c r="H433" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="I433" s="81">
+      <c r="I433" s="7">
         <v>0.14879999999999999</v>
       </c>
       <c r="J433" s="7">
         <v>0.14879999999999999</v>
       </c>
-      <c r="K433" s="82">
+      <c r="K433" s="50">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="L433" s="81"/>
-      <c r="M433" s="83"/>
+      <c r="L433" s="7"/>
       <c r="N433" s="7">
         <v>-0.51</v>
       </c>
       <c r="O433" s="4"/>
-      <c r="P433" s="81">
+      <c r="P433" s="7">
         <v>1.2310000000000001</v>
       </c>
-      <c r="Q433" s="81"/>
-      <c r="R433" s="83"/>
-      <c r="S433" s="83"/>
-      <c r="T433" s="83"/>
-      <c r="U433" s="83"/>
-      <c r="V433" s="81"/>
       <c r="W433" s="4"/>
       <c r="X433" s="4"/>
       <c r="Y433" s="4"/>
@@ -52041,16 +51895,16 @@
       <c r="BB433" s="2"/>
       <c r="BC433" s="2"/>
       <c r="BD433" s="2"/>
-      <c r="BE433" s="84"/>
-      <c r="BF433" s="85"/>
-      <c r="BG433" s="86"/>
+      <c r="BE433" s="70"/>
+      <c r="BF433" s="71"/>
+      <c r="BG433" s="72"/>
       <c r="BH433" s="2"/>
       <c r="BI433" s="2"/>
       <c r="BJ433" s="3" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="434" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A434" s="2" t="s">
         <v>13</v>
       </c>
@@ -52058,12 +51912,12 @@
         <v>25</v>
       </c>
       <c r="C434" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D434" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D434" s="8">
         <v>2</v>
       </c>
-      <c r="E434" s="80" t="s">
+      <c r="E434" s="2" t="s">
         <v>215</v>
       </c>
       <c r="F434" s="4" t="s">
@@ -52075,30 +51929,23 @@
       <c r="H434" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="I434" s="81">
+      <c r="I434" s="7">
         <v>0.1484</v>
       </c>
       <c r="J434" s="7">
         <v>0.14749999999999999</v>
       </c>
-      <c r="K434" s="82">
+      <c r="K434" s="50">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="L434" s="81"/>
-      <c r="M434" s="83"/>
+      <c r="L434" s="7"/>
       <c r="N434" s="7">
         <v>-0.56000000000000005</v>
       </c>
       <c r="O434" s="4"/>
-      <c r="P434" s="81">
+      <c r="P434" s="7">
         <v>1.2310000000000001</v>
       </c>
-      <c r="Q434" s="81"/>
-      <c r="R434" s="83"/>
-      <c r="S434" s="83"/>
-      <c r="T434" s="83"/>
-      <c r="U434" s="83"/>
-      <c r="V434" s="81"/>
       <c r="W434" s="4"/>
       <c r="X434" s="4"/>
       <c r="Y434" s="4"/>
@@ -52133,16 +51980,16 @@
       <c r="BB434" s="2"/>
       <c r="BC434" s="2"/>
       <c r="BD434" s="2"/>
-      <c r="BE434" s="84"/>
-      <c r="BF434" s="85"/>
-      <c r="BG434" s="86"/>
+      <c r="BE434" s="70"/>
+      <c r="BF434" s="71"/>
+      <c r="BG434" s="72"/>
       <c r="BH434" s="2"/>
       <c r="BI434" s="2"/>
       <c r="BJ434" s="3" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="435" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A435" s="2" t="s">
         <v>13</v>
       </c>
@@ -52150,12 +51997,12 @@
         <v>25</v>
       </c>
       <c r="C435" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D435" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D435" s="8">
         <v>3</v>
       </c>
-      <c r="E435" s="80" t="s">
+      <c r="E435" s="2" t="s">
         <v>602</v>
       </c>
       <c r="F435" s="4" t="s">
@@ -52167,30 +52014,23 @@
       <c r="H435" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="I435" s="81">
+      <c r="I435" s="7">
         <v>0.1459</v>
       </c>
       <c r="J435" s="7">
         <v>0.14799999999999999</v>
       </c>
-      <c r="K435" s="82">
+      <c r="K435" s="50">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="L435" s="81"/>
-      <c r="M435" s="83"/>
+      <c r="L435" s="7"/>
       <c r="N435" s="7">
         <v>-0.41</v>
       </c>
       <c r="O435" s="4"/>
-      <c r="P435" s="81">
+      <c r="P435" s="7">
         <v>1.2310000000000001</v>
       </c>
-      <c r="Q435" s="81"/>
-      <c r="R435" s="83"/>
-      <c r="S435" s="83"/>
-      <c r="T435" s="83"/>
-      <c r="U435" s="83"/>
-      <c r="V435" s="81"/>
       <c r="W435" s="4"/>
       <c r="X435" s="4"/>
       <c r="Y435" s="4"/>
@@ -52225,16 +52065,16 @@
       <c r="BB435" s="2"/>
       <c r="BC435" s="2"/>
       <c r="BD435" s="2"/>
-      <c r="BE435" s="84"/>
-      <c r="BF435" s="85"/>
-      <c r="BG435" s="86"/>
+      <c r="BE435" s="70"/>
+      <c r="BF435" s="71"/>
+      <c r="BG435" s="72"/>
       <c r="BH435" s="2"/>
       <c r="BI435" s="2"/>
       <c r="BJ435" s="3" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="436" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A436" s="2" t="s">
         <v>13</v>
       </c>
@@ -52242,12 +52082,12 @@
         <v>25</v>
       </c>
       <c r="C436" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D436" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D436" s="8">
         <v>4</v>
       </c>
-      <c r="E436" s="80" t="s">
+      <c r="E436" s="2" t="s">
         <v>547</v>
       </c>
       <c r="F436" s="4" t="s">
@@ -52259,22 +52099,16 @@
       <c r="H436" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="I436" s="96"/>
+      <c r="I436" s="48"/>
       <c r="J436" s="48"/>
-      <c r="K436" s="97"/>
-      <c r="L436" s="96"/>
-      <c r="M436" s="96"/>
+      <c r="K436" s="51"/>
+      <c r="L436" s="48"/>
+      <c r="M436" s="48"/>
       <c r="N436" s="48"/>
       <c r="O436" s="4"/>
-      <c r="P436" s="81">
+      <c r="P436" s="7">
         <v>1.2310000000000001</v>
       </c>
-      <c r="Q436" s="81"/>
-      <c r="R436" s="83"/>
-      <c r="S436" s="83"/>
-      <c r="T436" s="83"/>
-      <c r="U436" s="83"/>
-      <c r="V436" s="81"/>
       <c r="W436" s="4"/>
       <c r="X436" s="4"/>
       <c r="Y436" s="4"/>
@@ -52309,16 +52143,16 @@
       <c r="BB436" s="2"/>
       <c r="BC436" s="2"/>
       <c r="BD436" s="2"/>
-      <c r="BE436" s="84"/>
-      <c r="BF436" s="85"/>
-      <c r="BG436" s="86"/>
+      <c r="BE436" s="70"/>
+      <c r="BF436" s="71"/>
+      <c r="BG436" s="72"/>
       <c r="BH436" s="2"/>
       <c r="BI436" s="2"/>
       <c r="BJ436" s="3" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="437" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A437" s="2" t="s">
         <v>13</v>
       </c>
@@ -52326,12 +52160,12 @@
         <v>25</v>
       </c>
       <c r="C437" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D437" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D437" s="8">
         <v>5</v>
       </c>
-      <c r="E437" s="80" t="s">
+      <c r="E437" s="2" t="s">
         <v>215</v>
       </c>
       <c r="F437" s="4" t="s">
@@ -52343,30 +52177,23 @@
       <c r="H437" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="I437" s="81">
+      <c r="I437" s="7">
         <v>0.14939</v>
       </c>
       <c r="J437" s="7">
         <v>0.14849999999999999</v>
       </c>
-      <c r="K437" s="82">
+      <c r="K437" s="50">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="L437" s="81"/>
-      <c r="M437" s="83"/>
+      <c r="L437" s="7"/>
       <c r="N437" s="7">
         <v>-0.55000000000000004</v>
       </c>
       <c r="O437" s="4"/>
-      <c r="P437" s="81">
+      <c r="P437" s="7">
         <v>1.2310000000000001</v>
       </c>
-      <c r="Q437" s="81"/>
-      <c r="R437" s="83"/>
-      <c r="S437" s="83"/>
-      <c r="T437" s="83"/>
-      <c r="U437" s="83"/>
-      <c r="V437" s="81"/>
       <c r="W437" s="4"/>
       <c r="X437" s="4"/>
       <c r="Y437" s="4"/>
@@ -52401,16 +52228,16 @@
       <c r="BB437" s="2"/>
       <c r="BC437" s="2"/>
       <c r="BD437" s="2"/>
-      <c r="BE437" s="84"/>
-      <c r="BF437" s="85"/>
-      <c r="BG437" s="86"/>
+      <c r="BE437" s="70"/>
+      <c r="BF437" s="71"/>
+      <c r="BG437" s="72"/>
       <c r="BH437" s="2"/>
       <c r="BI437" s="2"/>
       <c r="BJ437" s="3" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="438" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A438" s="2" t="s">
         <v>13</v>
       </c>
@@ -52418,12 +52245,12 @@
         <v>25</v>
       </c>
       <c r="C438" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D438" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D438" s="8">
         <v>6</v>
       </c>
-      <c r="E438" s="80" t="s">
+      <c r="E438" s="2" t="s">
         <v>602</v>
       </c>
       <c r="F438" s="4" t="s">
@@ -52435,30 +52262,23 @@
       <c r="H438" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="I438" s="81">
+      <c r="I438" s="7">
         <v>0.1482</v>
       </c>
       <c r="J438" s="7">
         <v>0.15029999999999999</v>
       </c>
-      <c r="K438" s="82">
+      <c r="K438" s="50">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="L438" s="81"/>
-      <c r="M438" s="83"/>
+      <c r="L438" s="7"/>
       <c r="N438" s="7">
         <v>-0.39</v>
       </c>
       <c r="O438" s="4"/>
-      <c r="P438" s="81">
+      <c r="P438" s="7">
         <v>1.2310000000000001</v>
       </c>
-      <c r="Q438" s="81"/>
-      <c r="R438" s="83"/>
-      <c r="S438" s="83"/>
-      <c r="T438" s="83"/>
-      <c r="U438" s="83"/>
-      <c r="V438" s="81"/>
       <c r="W438" s="4"/>
       <c r="X438" s="4"/>
       <c r="Y438" s="4"/>
@@ -52493,16 +52313,16 @@
       <c r="BB438" s="2"/>
       <c r="BC438" s="2"/>
       <c r="BD438" s="2"/>
-      <c r="BE438" s="84"/>
-      <c r="BF438" s="85"/>
-      <c r="BG438" s="86"/>
+      <c r="BE438" s="70"/>
+      <c r="BF438" s="71"/>
+      <c r="BG438" s="72"/>
       <c r="BH438" s="2"/>
       <c r="BI438" s="2"/>
       <c r="BJ438" s="3" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="439" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A439" s="2" t="s">
         <v>13</v>
       </c>
@@ -52510,12 +52330,12 @@
         <v>25</v>
       </c>
       <c r="C439" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D439" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D439" s="8">
         <v>7</v>
       </c>
-      <c r="E439" s="80" t="s">
+      <c r="E439" s="2" t="s">
         <v>552</v>
       </c>
       <c r="F439" s="4" t="s">
@@ -52527,30 +52347,23 @@
       <c r="H439" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="I439" s="81">
+      <c r="I439" s="7">
         <v>0.14929999999999999</v>
       </c>
       <c r="J439" s="7">
         <v>0.14910000000000001</v>
       </c>
-      <c r="K439" s="82">
+      <c r="K439" s="50">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="L439" s="81"/>
-      <c r="M439" s="83"/>
+      <c r="L439" s="7"/>
       <c r="N439" s="7">
         <v>-0.52</v>
       </c>
       <c r="O439" s="4"/>
-      <c r="P439" s="81">
+      <c r="P439" s="7">
         <v>1.2310000000000001</v>
       </c>
-      <c r="Q439" s="81"/>
-      <c r="R439" s="83"/>
-      <c r="S439" s="83"/>
-      <c r="T439" s="83"/>
-      <c r="U439" s="83"/>
-      <c r="V439" s="81"/>
       <c r="W439" s="4"/>
       <c r="X439" s="4"/>
       <c r="Y439" s="4"/>
@@ -52585,16 +52398,16 @@
       <c r="BB439" s="2"/>
       <c r="BC439" s="2"/>
       <c r="BD439" s="2"/>
-      <c r="BE439" s="84"/>
-      <c r="BF439" s="85"/>
-      <c r="BG439" s="86"/>
+      <c r="BE439" s="70"/>
+      <c r="BF439" s="71"/>
+      <c r="BG439" s="72"/>
       <c r="BH439" s="2"/>
       <c r="BI439" s="2"/>
       <c r="BJ439" s="3" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="440" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A440" s="2" t="s">
         <v>13</v>
       </c>
@@ -52602,12 +52415,12 @@
         <v>25</v>
       </c>
       <c r="C440" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D440" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D440" s="8">
         <v>8</v>
       </c>
-      <c r="E440" s="80" t="s">
+      <c r="E440" s="2" t="s">
         <v>552</v>
       </c>
       <c r="F440" s="4" t="s">
@@ -52619,30 +52432,23 @@
       <c r="H440" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="I440" s="81">
+      <c r="I440" s="7">
         <v>0.15160000000000001</v>
       </c>
       <c r="J440" s="7">
         <v>0.15160000000000001</v>
       </c>
-      <c r="K440" s="82">
+      <c r="K440" s="50">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="L440" s="81"/>
-      <c r="M440" s="83"/>
+      <c r="L440" s="7"/>
       <c r="N440" s="7">
         <v>-0.57999999999999996</v>
       </c>
       <c r="O440" s="4"/>
-      <c r="P440" s="81">
+      <c r="P440" s="7">
         <v>1.2310000000000001</v>
       </c>
-      <c r="Q440" s="81"/>
-      <c r="R440" s="83"/>
-      <c r="S440" s="83"/>
-      <c r="T440" s="83"/>
-      <c r="U440" s="83"/>
-      <c r="V440" s="81"/>
       <c r="W440" s="4"/>
       <c r="X440" s="4"/>
       <c r="Y440" s="4"/>
@@ -52677,16 +52483,16 @@
       <c r="BB440" s="2"/>
       <c r="BC440" s="2"/>
       <c r="BD440" s="2"/>
-      <c r="BE440" s="84"/>
-      <c r="BF440" s="85"/>
-      <c r="BG440" s="86"/>
+      <c r="BE440" s="70"/>
+      <c r="BF440" s="71"/>
+      <c r="BG440" s="72"/>
       <c r="BH440" s="2"/>
       <c r="BI440" s="2"/>
       <c r="BJ440" s="3" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="441" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A441" s="2" t="s">
         <v>43</v>
       </c>
@@ -52694,12 +52500,12 @@
         <v>46</v>
       </c>
       <c r="C441" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D441" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D441" s="8">
         <v>1</v>
       </c>
-      <c r="E441" s="80" t="s">
+      <c r="E441" s="2" t="s">
         <v>551</v>
       </c>
       <c r="F441" s="4" t="s">
@@ -52711,30 +52517,23 @@
       <c r="H441" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="I441" s="81">
+      <c r="I441" s="7">
         <v>0.16769999999999999</v>
       </c>
-      <c r="J441" s="81">
+      <c r="J441" s="7">
         <v>0.16769999999999999</v>
       </c>
-      <c r="K441" s="82">
+      <c r="K441" s="50">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="L441" s="81"/>
-      <c r="M441" s="83"/>
+      <c r="L441" s="7"/>
       <c r="N441" s="7">
         <v>-0.5</v>
       </c>
       <c r="O441" s="4"/>
-      <c r="P441" s="81">
+      <c r="P441" s="7">
         <v>1.2845</v>
       </c>
-      <c r="Q441" s="81"/>
-      <c r="R441" s="83"/>
-      <c r="S441" s="83"/>
-      <c r="T441" s="83"/>
-      <c r="U441" s="83"/>
-      <c r="V441" s="81"/>
       <c r="W441" s="4"/>
       <c r="X441" s="4"/>
       <c r="Y441" s="4"/>
@@ -52769,16 +52568,16 @@
       <c r="BB441" s="2"/>
       <c r="BC441" s="2"/>
       <c r="BD441" s="2"/>
-      <c r="BE441" s="84"/>
-      <c r="BF441" s="85"/>
-      <c r="BG441" s="86"/>
+      <c r="BE441" s="70"/>
+      <c r="BF441" s="71"/>
+      <c r="BG441" s="72"/>
       <c r="BH441" s="2"/>
       <c r="BI441" s="2"/>
       <c r="BJ441" s="3" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="442" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A442" s="2" t="s">
         <v>43</v>
       </c>
@@ -52786,12 +52585,12 @@
         <v>46</v>
       </c>
       <c r="C442" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D442" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D442" s="8">
         <v>2</v>
       </c>
-      <c r="E442" s="80" t="s">
+      <c r="E442" s="2" t="s">
         <v>552</v>
       </c>
       <c r="F442" s="4" t="s">
@@ -52803,30 +52602,23 @@
       <c r="H442" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="I442" s="81">
+      <c r="I442" s="7">
         <v>0.1681</v>
       </c>
-      <c r="J442" s="81">
+      <c r="J442" s="7">
         <v>0.1681</v>
       </c>
-      <c r="K442" s="82">
+      <c r="K442" s="50">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="L442" s="81"/>
-      <c r="M442" s="83"/>
+      <c r="L442" s="7"/>
       <c r="N442" s="7">
         <v>-0.43</v>
       </c>
       <c r="O442" s="4"/>
-      <c r="P442" s="81">
+      <c r="P442" s="7">
         <v>1.2845</v>
       </c>
-      <c r="Q442" s="81"/>
-      <c r="R442" s="83"/>
-      <c r="S442" s="83"/>
-      <c r="T442" s="83"/>
-      <c r="U442" s="83"/>
-      <c r="V442" s="81"/>
       <c r="W442" s="4"/>
       <c r="X442" s="4"/>
       <c r="Y442" s="4"/>
@@ -52861,16 +52653,16 @@
       <c r="BB442" s="2"/>
       <c r="BC442" s="2"/>
       <c r="BD442" s="2"/>
-      <c r="BE442" s="84"/>
-      <c r="BF442" s="85"/>
-      <c r="BG442" s="86"/>
+      <c r="BE442" s="70"/>
+      <c r="BF442" s="71"/>
+      <c r="BG442" s="72"/>
       <c r="BH442" s="2"/>
       <c r="BI442" s="2"/>
       <c r="BJ442" s="3" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="443" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A443" s="2" t="s">
         <v>43</v>
       </c>
@@ -52878,12 +52670,12 @@
         <v>46</v>
       </c>
       <c r="C443" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D443" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D443" s="8">
         <v>3</v>
       </c>
-      <c r="E443" s="80" t="s">
+      <c r="E443" s="2" t="s">
         <v>551</v>
       </c>
       <c r="F443" s="4" t="s">
@@ -52895,30 +52687,23 @@
       <c r="H443" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="I443" s="81">
+      <c r="I443" s="7">
         <v>0.16489999999999999</v>
       </c>
-      <c r="J443" s="81">
+      <c r="J443" s="7">
         <v>0.16489999999999999</v>
       </c>
-      <c r="K443" s="82">
+      <c r="K443" s="50">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="L443" s="81"/>
-      <c r="M443" s="83"/>
+      <c r="L443" s="7"/>
       <c r="N443" s="7">
         <v>-0.39</v>
       </c>
       <c r="O443" s="4"/>
-      <c r="P443" s="81">
+      <c r="P443" s="7">
         <v>1.2845</v>
       </c>
-      <c r="Q443" s="81"/>
-      <c r="R443" s="83"/>
-      <c r="S443" s="83"/>
-      <c r="T443" s="83"/>
-      <c r="U443" s="83"/>
-      <c r="V443" s="81"/>
       <c r="W443" s="4"/>
       <c r="X443" s="4"/>
       <c r="Y443" s="4"/>
@@ -52953,16 +52738,16 @@
       <c r="BB443" s="2"/>
       <c r="BC443" s="2"/>
       <c r="BD443" s="2"/>
-      <c r="BE443" s="84"/>
-      <c r="BF443" s="85"/>
-      <c r="BG443" s="86"/>
+      <c r="BE443" s="70"/>
+      <c r="BF443" s="71"/>
+      <c r="BG443" s="72"/>
       <c r="BH443" s="2"/>
       <c r="BI443" s="2"/>
       <c r="BJ443" s="3" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="444" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A444" s="2" t="s">
         <v>43</v>
       </c>
@@ -52970,12 +52755,12 @@
         <v>46</v>
       </c>
       <c r="C444" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D444" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D444" s="8">
         <v>4</v>
       </c>
-      <c r="E444" s="80" t="s">
+      <c r="E444" s="2" t="s">
         <v>551</v>
       </c>
       <c r="F444" s="4" t="s">
@@ -52987,30 +52772,23 @@
       <c r="H444" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="I444" s="81">
+      <c r="I444" s="7">
         <v>0.16930000000000001</v>
       </c>
-      <c r="J444" s="81">
+      <c r="J444" s="7">
         <v>0.16930000000000001</v>
       </c>
-      <c r="K444" s="82">
+      <c r="K444" s="50">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="L444" s="81"/>
-      <c r="M444" s="83"/>
+      <c r="L444" s="7"/>
       <c r="N444" s="7">
         <v>-0.39</v>
       </c>
       <c r="O444" s="4"/>
-      <c r="P444" s="81">
+      <c r="P444" s="7">
         <v>1.2845</v>
       </c>
-      <c r="Q444" s="81"/>
-      <c r="R444" s="83"/>
-      <c r="S444" s="83"/>
-      <c r="T444" s="83"/>
-      <c r="U444" s="83"/>
-      <c r="V444" s="81"/>
       <c r="W444" s="4"/>
       <c r="X444" s="4"/>
       <c r="Y444" s="4"/>
@@ -53045,16 +52823,16 @@
       <c r="BB444" s="2"/>
       <c r="BC444" s="2"/>
       <c r="BD444" s="2"/>
-      <c r="BE444" s="84"/>
-      <c r="BF444" s="85"/>
-      <c r="BG444" s="86"/>
+      <c r="BE444" s="70"/>
+      <c r="BF444" s="71"/>
+      <c r="BG444" s="72"/>
       <c r="BH444" s="2"/>
       <c r="BI444" s="2"/>
       <c r="BJ444" s="3" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="445" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A445" s="2" t="s">
         <v>43</v>
       </c>
@@ -53062,12 +52840,12 @@
         <v>46</v>
       </c>
       <c r="C445" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D445" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D445" s="8">
         <v>5</v>
       </c>
-      <c r="E445" s="80" t="s">
+      <c r="E445" s="2" t="s">
         <v>552</v>
       </c>
       <c r="F445" s="4" t="s">
@@ -53079,30 +52857,23 @@
       <c r="H445" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="I445" s="81">
+      <c r="I445" s="7">
         <v>0.1686</v>
       </c>
-      <c r="J445" s="81">
+      <c r="J445" s="7">
         <v>0.1686</v>
       </c>
-      <c r="K445" s="82">
+      <c r="K445" s="50">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="L445" s="81"/>
-      <c r="M445" s="83"/>
+      <c r="L445" s="7"/>
       <c r="N445" s="7">
         <v>-0.43</v>
       </c>
       <c r="O445" s="4"/>
-      <c r="P445" s="81">
+      <c r="P445" s="7">
         <v>1.2845</v>
       </c>
-      <c r="Q445" s="81"/>
-      <c r="R445" s="83"/>
-      <c r="S445" s="83"/>
-      <c r="T445" s="83"/>
-      <c r="U445" s="83"/>
-      <c r="V445" s="81"/>
       <c r="W445" s="4"/>
       <c r="X445" s="4"/>
       <c r="Y445" s="4"/>
@@ -53137,16 +52908,16 @@
       <c r="BB445" s="2"/>
       <c r="BC445" s="2"/>
       <c r="BD445" s="2"/>
-      <c r="BE445" s="84"/>
-      <c r="BF445" s="85"/>
-      <c r="BG445" s="86"/>
+      <c r="BE445" s="70"/>
+      <c r="BF445" s="71"/>
+      <c r="BG445" s="72"/>
       <c r="BH445" s="2"/>
       <c r="BI445" s="2"/>
       <c r="BJ445" s="3" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="446" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A446" s="2" t="s">
         <v>43</v>
       </c>
@@ -53154,12 +52925,12 @@
         <v>46</v>
       </c>
       <c r="C446" s="3">
-        <v>45013</v>
-      </c>
-      <c r="D446" s="79">
+        <v>45379</v>
+      </c>
+      <c r="D446" s="8">
         <v>6</v>
       </c>
-      <c r="E446" s="80" t="s">
+      <c r="E446" s="2" t="s">
         <v>551</v>
       </c>
       <c r="F446" s="4" t="s">
@@ -53171,30 +52942,23 @@
       <c r="H446" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="I446" s="81">
+      <c r="I446" s="7">
         <v>0.16450000000000001</v>
       </c>
-      <c r="J446" s="81">
+      <c r="J446" s="7">
         <v>0.16450000000000001</v>
       </c>
-      <c r="K446" s="82">
+      <c r="K446" s="50">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="L446" s="81"/>
-      <c r="M446" s="83"/>
+      <c r="L446" s="7"/>
       <c r="N446" s="7">
         <v>-0.46</v>
       </c>
       <c r="O446" s="4"/>
-      <c r="P446" s="81">
+      <c r="P446" s="7">
         <v>1.2845</v>
       </c>
-      <c r="Q446" s="81"/>
-      <c r="R446" s="83"/>
-      <c r="S446" s="83"/>
-      <c r="T446" s="83"/>
-      <c r="U446" s="83"/>
-      <c r="V446" s="81"/>
       <c r="W446" s="4"/>
       <c r="X446" s="4"/>
       <c r="Y446" s="4"/>
@@ -53229,29 +52993,29 @@
       <c r="BB446" s="2"/>
       <c r="BC446" s="2"/>
       <c r="BD446" s="2"/>
-      <c r="BE446" s="84"/>
-      <c r="BF446" s="85"/>
-      <c r="BG446" s="86"/>
+      <c r="BE446" s="70"/>
+      <c r="BF446" s="71"/>
+      <c r="BG446" s="72"/>
       <c r="BH446" s="2"/>
       <c r="BI446" s="2"/>
       <c r="BJ446" s="3" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="447" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A447" s="63" t="s">
+    <row r="447" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A447" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B447" s="87" t="s">
+      <c r="B447" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="C447" s="88">
-        <v>45013</v>
-      </c>
-      <c r="D447" s="89">
+      <c r="C447" s="3">
+        <v>45379</v>
+      </c>
+      <c r="D447" s="8">
         <v>7</v>
       </c>
-      <c r="E447" s="80" t="s">
+      <c r="E447" s="2" t="s">
         <v>603</v>
       </c>
       <c r="F447" s="4" t="s">
@@ -53263,70 +53027,63 @@
       <c r="H447" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="I447" s="90">
+      <c r="I447" s="7">
         <v>0.17499999999999999</v>
       </c>
-      <c r="J447" s="90">
+      <c r="J447" s="7">
         <v>0.17499999999999999</v>
       </c>
-      <c r="K447" s="91">
+      <c r="K447" s="50">
         <v>1.9E-3</v>
       </c>
-      <c r="L447" s="90"/>
-      <c r="M447" s="92"/>
-      <c r="N447" s="71">
+      <c r="L447" s="7"/>
+      <c r="N447" s="7">
         <v>-0.43</v>
       </c>
-      <c r="O447" s="64"/>
-      <c r="P447" s="81">
+      <c r="O447" s="4"/>
+      <c r="P447" s="7">
         <v>1.2845</v>
       </c>
-      <c r="Q447" s="90"/>
-      <c r="R447" s="92"/>
-      <c r="S447" s="92"/>
-      <c r="T447" s="92"/>
-      <c r="U447" s="92"/>
-      <c r="V447" s="90"/>
-      <c r="W447" s="64"/>
-      <c r="X447" s="64"/>
-      <c r="Y447" s="64"/>
-      <c r="Z447" s="71"/>
-      <c r="AA447" s="71"/>
-      <c r="AB447" s="71"/>
-      <c r="AC447" s="71"/>
-      <c r="AD447" s="71"/>
-      <c r="AE447" s="71"/>
-      <c r="AF447" s="71"/>
-      <c r="AG447" s="71"/>
-      <c r="AH447" s="71"/>
-      <c r="AI447" s="71"/>
-      <c r="AJ447" s="71"/>
-      <c r="AK447" s="71"/>
-      <c r="AL447" s="71"/>
-      <c r="AM447" s="71"/>
-      <c r="AN447" s="71"/>
-      <c r="AO447" s="71"/>
-      <c r="AP447" s="71"/>
-      <c r="AQ447" s="71"/>
-      <c r="AR447" s="71"/>
-      <c r="AS447" s="71"/>
-      <c r="AT447" s="71"/>
-      <c r="AU447" s="71"/>
-      <c r="AV447" s="71"/>
-      <c r="AW447" s="64"/>
-      <c r="AX447" s="63"/>
-      <c r="AY447" s="71"/>
-      <c r="AZ447" s="64"/>
-      <c r="BA447" s="64"/>
-      <c r="BB447" s="63"/>
-      <c r="BC447" s="63"/>
-      <c r="BD447" s="63"/>
-      <c r="BE447" s="93"/>
-      <c r="BF447" s="94"/>
-      <c r="BG447" s="95"/>
-      <c r="BH447" s="63"/>
-      <c r="BI447" s="63"/>
-      <c r="BJ447" s="88" t="s">
+      <c r="W447" s="4"/>
+      <c r="X447" s="4"/>
+      <c r="Y447" s="4"/>
+      <c r="Z447" s="7"/>
+      <c r="AA447" s="7"/>
+      <c r="AB447" s="7"/>
+      <c r="AC447" s="7"/>
+      <c r="AD447" s="7"/>
+      <c r="AE447" s="7"/>
+      <c r="AF447" s="7"/>
+      <c r="AG447" s="7"/>
+      <c r="AH447" s="7"/>
+      <c r="AI447" s="7"/>
+      <c r="AJ447" s="7"/>
+      <c r="AK447" s="7"/>
+      <c r="AL447" s="7"/>
+      <c r="AM447" s="7"/>
+      <c r="AN447" s="7"/>
+      <c r="AO447" s="7"/>
+      <c r="AP447" s="7"/>
+      <c r="AQ447" s="7"/>
+      <c r="AR447" s="7"/>
+      <c r="AS447" s="7"/>
+      <c r="AT447" s="7"/>
+      <c r="AU447" s="7"/>
+      <c r="AV447" s="7"/>
+      <c r="AW447" s="4"/>
+      <c r="AX447" s="2"/>
+      <c r="AY447" s="7"/>
+      <c r="AZ447" s="4"/>
+      <c r="BA447" s="4"/>
+      <c r="BB447" s="2"/>
+      <c r="BC447" s="2"/>
+      <c r="BD447" s="2"/>
+      <c r="BE447" s="73"/>
+      <c r="BF447" s="74"/>
+      <c r="BG447" s="75"/>
+      <c r="BH447" s="2"/>
+      <c r="BI447" s="2"/>
+      <c r="BJ447" s="3" t="s">
         <v>622</v>
       </c>
     </row>
@@ -53347,25 +53104,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004F1ECC6B2649324CB24C079D2C04510D" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="608b5d954c2eb0ac10393708da8d34af">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65551c38-962b-4cee-924d-ef2df1bb8b98" xmlns:ns3="ec750ee3-7d64-422f-9b1f-0ca7238893a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af171f03bd4cf151e3e856a6839c0cc7" ns2:_="" ns3:_="">
     <xsd:import namespace="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
@@ -53613,10 +53351,40 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
+    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -53639,20 +53407,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
-    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65565C5D-352D-402E-8530-EC40FD60A17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2D9157-7DD9-4F61-A55B-5E01121753E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52178,7 +52178,7 @@
         <v>225</v>
       </c>
       <c r="I437" s="7">
-        <v>0.14939</v>
+        <v>0.14940000000000001</v>
       </c>
       <c r="J437" s="7">
         <v>0.14849999999999999</v>
@@ -53104,6 +53104,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004F1ECC6B2649324CB24C079D2C04510D" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="608b5d954c2eb0ac10393708da8d34af">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65551c38-962b-4cee-924d-ef2df1bb8b98" xmlns:ns3="ec750ee3-7d64-422f-9b1f-0ca7238893a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af171f03bd4cf151e3e856a6839c0cc7" ns2:_="" ns3:_="">
     <xsd:import namespace="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
@@ -53351,40 +53370,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
-    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -53407,9 +53396,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
+    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53393237-D5DD-46B6-B62A-4070F2B71589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD847507-D332-435F-84E8-DC4DF16E4DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2156,7 +2156,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2364,18 +2364,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2384,27 +2372,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3901,7 +3868,7 @@
       <c r="BE6" s="14">
         <v>997</v>
       </c>
-      <c r="BF6" s="81">
+      <c r="BF6" s="63">
         <v>49</v>
       </c>
       <c r="BG6" s="15">
@@ -4013,11 +3980,11 @@
       <c r="BE7" s="17">
         <v>997</v>
       </c>
-      <c r="BF7" s="79">
+      <c r="BF7" s="16">
         <v>48</v>
       </c>
       <c r="BG7" s="15"/>
-      <c r="BH7" s="84">
+      <c r="BH7" s="7">
         <v>2096</v>
       </c>
       <c r="BI7" s="13" t="s">
@@ -4570,7 +4537,7 @@
       <c r="BE12" s="14">
         <v>996</v>
       </c>
-      <c r="BF12" s="81">
+      <c r="BF12" s="63">
         <v>47</v>
       </c>
       <c r="BG12" s="15">
@@ -4679,11 +4646,11 @@
       <c r="BE13" s="17">
         <v>997</v>
       </c>
-      <c r="BF13" s="79">
+      <c r="BF13" s="16">
         <v>47</v>
       </c>
       <c r="BG13" s="15"/>
-      <c r="BH13" s="84">
+      <c r="BH13" s="7">
         <v>2096</v>
       </c>
       <c r="BI13" s="13" t="s">
@@ -4789,13 +4756,13 @@
       <c r="BE14" s="14">
         <v>995</v>
       </c>
-      <c r="BF14" s="81">
+      <c r="BF14" s="63">
         <v>47</v>
       </c>
       <c r="BG14" s="15">
         <v>1.157</v>
       </c>
-      <c r="BH14" s="84">
+      <c r="BH14" s="7">
         <v>2096</v>
       </c>
       <c r="BI14" s="4"/>
@@ -4899,13 +4866,13 @@
       <c r="BE15" s="14">
         <v>996</v>
       </c>
-      <c r="BF15" s="81">
+      <c r="BF15" s="63">
         <v>47</v>
       </c>
       <c r="BG15" s="15">
         <v>1.157</v>
       </c>
-      <c r="BH15" s="84">
+      <c r="BH15" s="7">
         <v>2096</v>
       </c>
       <c r="BI15" s="4"/>
@@ -5009,11 +4976,11 @@
       <c r="BE16" s="17">
         <v>997</v>
       </c>
-      <c r="BF16" s="79">
+      <c r="BF16" s="16">
         <v>45</v>
       </c>
       <c r="BG16" s="15"/>
-      <c r="BH16" s="84">
+      <c r="BH16" s="7">
         <v>2096</v>
       </c>
       <c r="BI16" s="13" t="s">
@@ -5119,13 +5086,13 @@
       <c r="BE17" s="14">
         <v>995</v>
       </c>
-      <c r="BF17" s="81">
+      <c r="BF17" s="63">
         <v>47</v>
       </c>
       <c r="BG17" s="15">
         <v>1.157</v>
       </c>
-      <c r="BH17" s="84">
+      <c r="BH17" s="7">
         <v>2096</v>
       </c>
       <c r="BI17" s="4"/>
@@ -5229,13 +5196,13 @@
       <c r="BE18" s="14">
         <v>995</v>
       </c>
-      <c r="BF18" s="81">
+      <c r="BF18" s="63">
         <v>47</v>
       </c>
       <c r="BG18" s="15">
         <v>1.1579999999999999</v>
       </c>
-      <c r="BH18" s="84">
+      <c r="BH18" s="7">
         <v>2096</v>
       </c>
       <c r="BI18" s="4"/>
@@ -5339,11 +5306,11 @@
       <c r="BE19" s="17">
         <v>997</v>
       </c>
-      <c r="BF19" s="79">
+      <c r="BF19" s="16">
         <v>45</v>
       </c>
       <c r="BG19" s="15"/>
-      <c r="BH19" s="84">
+      <c r="BH19" s="7">
         <v>2096</v>
       </c>
       <c r="BI19" s="13" t="s">
@@ -5874,7 +5841,7 @@
       <c r="BE24" s="19">
         <v>1013</v>
       </c>
-      <c r="BF24" s="80">
+      <c r="BF24" s="18">
         <v>52.4</v>
       </c>
       <c r="BG24" s="20"/>
@@ -5979,11 +5946,11 @@
       <c r="BE25" s="17">
         <v>1013</v>
       </c>
-      <c r="BF25" s="79">
+      <c r="BF25" s="16">
         <v>52.4</v>
       </c>
       <c r="BG25" s="15"/>
-      <c r="BH25" s="72"/>
+      <c r="BH25" s="4"/>
       <c r="BI25" s="4"/>
       <c r="BJ25" s="3" t="s">
         <v>120</v>
@@ -6414,13 +6381,13 @@
       <c r="BD29" s="18">
         <v>25.4</v>
       </c>
-      <c r="BE29" s="80">
+      <c r="BE29" s="18">
         <v>1012</v>
       </c>
       <c r="BF29" s="18">
         <v>52.9</v>
       </c>
-      <c r="BG29" s="72"/>
+      <c r="BG29" s="4"/>
       <c r="BH29" s="4"/>
       <c r="BI29" s="4"/>
       <c r="BJ29" s="3" t="s">
@@ -6524,13 +6491,13 @@
       <c r="BD30" s="18">
         <v>25.4</v>
       </c>
-      <c r="BE30" s="80">
+      <c r="BE30" s="18">
         <v>1012</v>
       </c>
-      <c r="BF30" s="80">
+      <c r="BF30" s="18">
         <v>52.9</v>
       </c>
-      <c r="BG30" s="72"/>
+      <c r="BG30" s="4"/>
       <c r="BH30" s="4"/>
       <c r="BI30" s="4"/>
       <c r="BJ30" s="3" t="s">
@@ -6632,14 +6599,14 @@
       <c r="BD31" s="16">
         <v>25.4</v>
       </c>
-      <c r="BE31" s="79">
+      <c r="BE31" s="16">
         <v>1012</v>
       </c>
-      <c r="BF31" s="79">
+      <c r="BF31" s="16">
         <v>52.9</v>
       </c>
-      <c r="BG31" s="78"/>
-      <c r="BH31" s="72"/>
+      <c r="BG31" s="59"/>
+      <c r="BH31" s="4"/>
       <c r="BI31" s="4"/>
       <c r="BJ31" s="3" t="s">
         <v>111</v>
@@ -6737,13 +6704,13 @@
       <c r="BD32" s="18">
         <v>25.8</v>
       </c>
-      <c r="BE32" s="80">
+      <c r="BE32" s="18">
         <v>1012</v>
       </c>
-      <c r="BF32" s="80">
+      <c r="BF32" s="18">
         <v>51.8</v>
       </c>
-      <c r="BG32" s="72"/>
+      <c r="BG32" s="4"/>
       <c r="BH32" s="4"/>
       <c r="BI32" s="4"/>
       <c r="BJ32" s="3" t="s">
@@ -6845,13 +6812,13 @@
       <c r="BD33" s="18">
         <v>25.8</v>
       </c>
-      <c r="BE33" s="80">
+      <c r="BE33" s="18">
         <v>1012</v>
       </c>
-      <c r="BF33" s="80">
+      <c r="BF33" s="18">
         <v>51.8</v>
       </c>
-      <c r="BG33" s="72"/>
+      <c r="BG33" s="4"/>
       <c r="BH33" s="4"/>
       <c r="BI33" s="4"/>
       <c r="BJ33" s="3" t="s">
@@ -6948,13 +6915,13 @@
       <c r="BD34" s="16">
         <v>25.8</v>
       </c>
-      <c r="BE34" s="79">
+      <c r="BE34" s="16">
         <v>1012</v>
       </c>
-      <c r="BF34" s="79">
+      <c r="BF34" s="16">
         <v>51.8</v>
       </c>
-      <c r="BG34" s="78"/>
+      <c r="BG34" s="59"/>
       <c r="BH34" s="4"/>
       <c r="BI34" s="13" t="s">
         <v>87</v>
@@ -7058,13 +7025,13 @@
       <c r="BD35" s="18">
         <v>26.3</v>
       </c>
-      <c r="BE35" s="80">
+      <c r="BE35" s="18">
         <v>1012</v>
       </c>
-      <c r="BF35" s="80">
+      <c r="BF35" s="18">
         <v>51.3</v>
       </c>
-      <c r="BG35" s="72"/>
+      <c r="BG35" s="4"/>
       <c r="BH35" s="7"/>
       <c r="BI35" s="4"/>
       <c r="BJ35" s="3" t="s">
@@ -7166,13 +7133,13 @@
       <c r="BD36" s="18">
         <v>26.3</v>
       </c>
-      <c r="BE36" s="80">
+      <c r="BE36" s="18">
         <v>1012</v>
       </c>
-      <c r="BF36" s="80">
+      <c r="BF36" s="18">
         <v>51.3</v>
       </c>
-      <c r="BG36" s="72"/>
+      <c r="BG36" s="4"/>
       <c r="BH36" s="4"/>
       <c r="BI36" s="4"/>
       <c r="BJ36" s="3" t="s">
@@ -7269,14 +7236,14 @@
       <c r="BD37" s="16">
         <v>26.3</v>
       </c>
-      <c r="BE37" s="79">
+      <c r="BE37" s="16">
         <v>1012</v>
       </c>
-      <c r="BF37" s="79">
+      <c r="BF37" s="16">
         <v>51.3</v>
       </c>
-      <c r="BG37" s="78"/>
-      <c r="BH37" s="72"/>
+      <c r="BG37" s="59"/>
+      <c r="BH37" s="4"/>
       <c r="BI37" s="4"/>
       <c r="BJ37" s="3" t="s">
         <v>124</v>
@@ -7372,13 +7339,13 @@
       <c r="BD38" s="18">
         <v>24.8</v>
       </c>
-      <c r="BE38" s="80">
+      <c r="BE38" s="18">
         <v>1012</v>
       </c>
       <c r="BF38" s="18">
         <v>53.5</v>
       </c>
-      <c r="BG38" s="72"/>
+      <c r="BG38" s="4"/>
       <c r="BH38" s="4"/>
       <c r="BI38" s="4"/>
       <c r="BJ38" s="3" t="s">
@@ -7580,13 +7547,13 @@
       <c r="BD40" s="18">
         <v>24.8</v>
       </c>
-      <c r="BE40" s="80">
+      <c r="BE40" s="18">
         <v>1012</v>
       </c>
       <c r="BF40" s="18">
         <v>53.5</v>
       </c>
-      <c r="BG40" s="72"/>
+      <c r="BG40" s="4"/>
       <c r="BH40" s="4"/>
       <c r="BI40" s="4"/>
       <c r="BJ40" s="3" t="s">
@@ -7791,7 +7758,7 @@
       <c r="BE42" s="19">
         <v>1012</v>
       </c>
-      <c r="BF42" s="80">
+      <c r="BF42" s="18">
         <v>53</v>
       </c>
       <c r="BG42" s="21"/>
@@ -7894,13 +7861,13 @@
       <c r="BE43" s="14">
         <v>1012</v>
       </c>
-      <c r="BF43" s="81">
+      <c r="BF43" s="63">
         <v>53</v>
       </c>
       <c r="BG43" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH43" s="72"/>
+      <c r="BH43" s="4"/>
       <c r="BI43" s="4"/>
       <c r="BJ43" s="3" t="s">
         <v>136</v>
@@ -8405,7 +8372,7 @@
       <c r="BE48" s="19">
         <v>1012</v>
       </c>
-      <c r="BF48" s="80">
+      <c r="BF48" s="18">
         <v>53</v>
       </c>
       <c r="BG48" s="21"/>
@@ -8506,13 +8473,13 @@
       <c r="BE49" s="14">
         <v>1012</v>
       </c>
-      <c r="BF49" s="81">
+      <c r="BF49" s="63">
         <v>54</v>
       </c>
       <c r="BG49" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH49" s="72"/>
+      <c r="BH49" s="4"/>
       <c r="BI49" s="4"/>
       <c r="BJ49" s="3" t="s">
         <v>130</v>
@@ -8608,13 +8575,13 @@
       <c r="BD50" s="18">
         <v>25.1</v>
       </c>
-      <c r="BE50" s="80">
+      <c r="BE50" s="18">
         <v>1011</v>
       </c>
       <c r="BF50" s="18">
         <v>54.2</v>
       </c>
-      <c r="BG50" s="83"/>
+      <c r="BG50" s="64"/>
       <c r="BH50" s="4"/>
       <c r="BI50" s="4"/>
       <c r="BJ50" s="3" t="s">
@@ -8711,13 +8678,13 @@
       <c r="BD51" s="4">
         <v>25.1</v>
       </c>
-      <c r="BE51" s="78">
+      <c r="BE51" s="59">
         <v>1011</v>
       </c>
       <c r="BF51" s="63">
         <v>54</v>
       </c>
-      <c r="BG51" s="78">
+      <c r="BG51" s="59">
         <v>1.173</v>
       </c>
       <c r="BH51" s="4"/>
@@ -8816,13 +8783,13 @@
       <c r="BD52" s="18">
         <v>25.1</v>
       </c>
-      <c r="BE52" s="80">
+      <c r="BE52" s="18">
         <v>1011</v>
       </c>
       <c r="BF52" s="18">
         <v>54.2</v>
       </c>
-      <c r="BG52" s="83"/>
+      <c r="BG52" s="64"/>
       <c r="BH52" s="4"/>
       <c r="BI52" s="4"/>
       <c r="BJ52" s="3" t="s">
@@ -8919,13 +8886,13 @@
       <c r="BD53" s="4">
         <v>25.2</v>
       </c>
-      <c r="BE53" s="78">
+      <c r="BE53" s="59">
         <v>1011</v>
       </c>
       <c r="BF53" s="63">
         <v>54</v>
       </c>
-      <c r="BG53" s="78">
+      <c r="BG53" s="59">
         <v>1.173</v>
       </c>
       <c r="BH53" s="4"/>
@@ -9024,13 +8991,13 @@
       <c r="BD54" s="18">
         <v>25.1</v>
       </c>
-      <c r="BE54" s="80">
+      <c r="BE54" s="18">
         <v>1011</v>
       </c>
-      <c r="BF54" s="80">
+      <c r="BF54" s="18">
         <v>54.2</v>
       </c>
-      <c r="BG54" s="83"/>
+      <c r="BG54" s="64"/>
       <c r="BH54" s="4"/>
       <c r="BI54" s="4"/>
       <c r="BJ54" s="3" t="s">
@@ -9127,16 +9094,16 @@
       <c r="BD55" s="4">
         <v>25.2</v>
       </c>
-      <c r="BE55" s="78">
+      <c r="BE55" s="59">
         <v>1011</v>
       </c>
-      <c r="BF55" s="81">
+      <c r="BF55" s="63">
         <v>54</v>
       </c>
-      <c r="BG55" s="78">
+      <c r="BG55" s="59">
         <v>1.173</v>
       </c>
-      <c r="BH55" s="72"/>
+      <c r="BH55" s="4"/>
       <c r="BI55" s="4"/>
       <c r="BJ55" s="3" t="s">
         <v>138</v>
@@ -9230,14 +9197,14 @@
       <c r="BD56" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE56" s="80">
+      <c r="BE56" s="18">
         <v>1005</v>
       </c>
-      <c r="BF56" s="80">
+      <c r="BF56" s="18">
         <v>41</v>
       </c>
-      <c r="BG56" s="83"/>
-      <c r="BH56" s="72"/>
+      <c r="BG56" s="64"/>
+      <c r="BH56" s="4"/>
       <c r="BI56" s="4"/>
       <c r="BJ56" s="36" t="s">
         <v>139</v>
@@ -9331,14 +9298,14 @@
       <c r="BD57" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE57" s="80">
+      <c r="BE57" s="18">
         <v>1005</v>
       </c>
-      <c r="BF57" s="80">
+      <c r="BF57" s="18">
         <v>41</v>
       </c>
-      <c r="BG57" s="83"/>
-      <c r="BH57" s="72"/>
+      <c r="BG57" s="64"/>
+      <c r="BH57" s="4"/>
       <c r="BI57" s="4"/>
       <c r="BJ57" s="3" t="s">
         <v>140</v>
@@ -9432,14 +9399,14 @@
       <c r="BD58" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE58" s="80">
+      <c r="BE58" s="18">
         <v>1005</v>
       </c>
-      <c r="BF58" s="80">
+      <c r="BF58" s="18">
         <v>41</v>
       </c>
-      <c r="BG58" s="83"/>
-      <c r="BH58" s="72"/>
+      <c r="BG58" s="64"/>
+      <c r="BH58" s="4"/>
       <c r="BI58" s="11" t="s">
         <v>88</v>
       </c>
@@ -9535,14 +9502,14 @@
       <c r="BD59" s="16">
         <v>25.2</v>
       </c>
-      <c r="BE59" s="79">
+      <c r="BE59" s="16">
         <v>1005</v>
       </c>
-      <c r="BF59" s="79">
+      <c r="BF59" s="16">
         <v>41</v>
       </c>
-      <c r="BG59" s="72"/>
-      <c r="BH59" s="72"/>
+      <c r="BG59" s="4"/>
+      <c r="BH59" s="4"/>
       <c r="BI59" s="4"/>
       <c r="BJ59" s="3" t="s">
         <v>142</v>
@@ -9636,13 +9603,13 @@
       <c r="BD60" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE60" s="80">
+      <c r="BE60" s="18">
         <v>1005</v>
       </c>
-      <c r="BF60" s="80">
+      <c r="BF60" s="18">
         <v>41</v>
       </c>
-      <c r="BG60" s="83"/>
+      <c r="BG60" s="64"/>
       <c r="BH60" s="4"/>
       <c r="BI60" s="4"/>
       <c r="BJ60" s="3" t="s">
@@ -9737,14 +9704,14 @@
       <c r="BD61" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE61" s="80">
+      <c r="BE61" s="18">
         <v>1005</v>
       </c>
-      <c r="BF61" s="80">
+      <c r="BF61" s="18">
         <v>41</v>
       </c>
-      <c r="BG61" s="83"/>
-      <c r="BH61" s="72"/>
+      <c r="BG61" s="64"/>
+      <c r="BH61" s="4"/>
       <c r="BI61" s="4"/>
       <c r="BJ61" s="3" t="s">
         <v>144</v>
@@ -9854,13 +9821,13 @@
       <c r="BD62" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE62" s="80">
+      <c r="BE62" s="18">
         <v>1005</v>
       </c>
       <c r="BF62" s="18">
         <v>41</v>
       </c>
-      <c r="BG62" s="83"/>
+      <c r="BG62" s="64"/>
       <c r="BH62" s="4"/>
       <c r="BI62" s="4"/>
       <c r="BJ62" s="3" t="s">
@@ -10085,7 +10052,7 @@
       <c r="BF64" s="18">
         <v>41</v>
       </c>
-      <c r="BG64" s="83"/>
+      <c r="BG64" s="64"/>
       <c r="BH64" s="4"/>
       <c r="BI64" s="4"/>
       <c r="BJ64" s="3" t="s">
@@ -10196,13 +10163,13 @@
       <c r="BD65" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE65" s="80">
+      <c r="BE65" s="18">
         <v>1005</v>
       </c>
       <c r="BF65" s="18">
         <v>41</v>
       </c>
-      <c r="BG65" s="83"/>
+      <c r="BG65" s="64"/>
       <c r="BH65" s="4"/>
       <c r="BI65" s="4"/>
       <c r="BJ65" s="3" t="s">
@@ -10313,13 +10280,13 @@
       <c r="BD66" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE66" s="80">
+      <c r="BE66" s="18">
         <v>1005</v>
       </c>
-      <c r="BF66" s="80">
+      <c r="BF66" s="18">
         <v>41</v>
       </c>
-      <c r="BG66" s="83"/>
+      <c r="BG66" s="64"/>
       <c r="BH66" s="4"/>
       <c r="BI66" s="4"/>
       <c r="BJ66" s="3" t="s">
@@ -10430,14 +10397,14 @@
       <c r="BD67" s="16">
         <v>25.2</v>
       </c>
-      <c r="BE67" s="79">
+      <c r="BE67" s="16">
         <v>1005</v>
       </c>
-      <c r="BF67" s="79">
+      <c r="BF67" s="16">
         <v>41</v>
       </c>
-      <c r="BG67" s="72"/>
-      <c r="BH67" s="72"/>
+      <c r="BG67" s="4"/>
+      <c r="BH67" s="4"/>
       <c r="BI67" s="4"/>
       <c r="BJ67" s="3" t="s">
         <v>160</v>
@@ -10547,13 +10514,13 @@
       <c r="BD68" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE68" s="80">
+      <c r="BE68" s="18">
         <v>1005</v>
       </c>
       <c r="BF68" s="18">
         <v>41</v>
       </c>
-      <c r="BG68" s="83"/>
+      <c r="BG68" s="64"/>
       <c r="BH68" s="4"/>
       <c r="BI68" s="4"/>
       <c r="BJ68" s="3" t="s">
@@ -10590,9 +10557,7 @@
         <v>571</v>
       </c>
       <c r="I69" s="48"/>
-      <c r="J69" s="48">
-        <v>0</v>
-      </c>
+      <c r="J69" s="48"/>
       <c r="K69" s="48"/>
       <c r="L69" s="7"/>
       <c r="M69" s="7">
@@ -10774,13 +10739,13 @@
       <c r="BD70" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE70" s="80">
+      <c r="BE70" s="18">
         <v>1005</v>
       </c>
       <c r="BF70" s="18">
         <v>41</v>
       </c>
-      <c r="BG70" s="83"/>
+      <c r="BG70" s="64"/>
       <c r="BH70" s="4"/>
       <c r="BI70" s="4"/>
       <c r="BJ70" s="3" t="s">
@@ -10891,13 +10856,13 @@
       <c r="BD71" s="16">
         <v>25.2</v>
       </c>
-      <c r="BE71" s="79">
+      <c r="BE71" s="16">
         <v>1005</v>
       </c>
       <c r="BF71" s="16">
         <v>41</v>
       </c>
-      <c r="BG71" s="72"/>
+      <c r="BG71" s="4"/>
       <c r="BH71" s="4"/>
       <c r="BI71" s="4"/>
       <c r="BJ71" s="3" t="s">
@@ -11008,13 +10973,13 @@
       <c r="BD72" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE72" s="80">
+      <c r="BE72" s="18">
         <v>1005</v>
       </c>
-      <c r="BF72" s="80">
+      <c r="BF72" s="18">
         <v>41</v>
       </c>
-      <c r="BG72" s="83"/>
+      <c r="BG72" s="64"/>
       <c r="BH72" s="4"/>
       <c r="BI72" s="4"/>
       <c r="BJ72" s="3" t="s">
@@ -11125,14 +11090,14 @@
       <c r="BD73" s="18">
         <v>25.2</v>
       </c>
-      <c r="BE73" s="80">
+      <c r="BE73" s="18">
         <v>1005</v>
       </c>
-      <c r="BF73" s="80">
+      <c r="BF73" s="18">
         <v>41</v>
       </c>
-      <c r="BG73" s="83"/>
-      <c r="BH73" s="72"/>
+      <c r="BG73" s="64"/>
+      <c r="BH73" s="4"/>
       <c r="BI73" s="4"/>
       <c r="BJ73" s="3" t="s">
         <v>154</v>
@@ -11240,13 +11205,13 @@
       <c r="BD74" s="18">
         <v>25.1</v>
       </c>
-      <c r="BE74" s="80">
+      <c r="BE74" s="18">
         <v>1010</v>
       </c>
       <c r="BF74" s="18">
         <v>47.7</v>
       </c>
-      <c r="BG74" s="72"/>
+      <c r="BG74" s="4"/>
       <c r="BH74" s="4"/>
       <c r="BI74" s="4"/>
       <c r="BJ74" s="3" t="s">
@@ -11355,13 +11320,13 @@
       <c r="BD75" s="18">
         <v>25.1</v>
       </c>
-      <c r="BE75" s="80">
+      <c r="BE75" s="18">
         <v>1010</v>
       </c>
       <c r="BF75" s="18">
         <v>47.7</v>
       </c>
-      <c r="BG75" s="72"/>
+      <c r="BG75" s="4"/>
       <c r="BH75" s="4"/>
       <c r="BI75" s="4"/>
       <c r="BJ75" s="3" t="s">
@@ -11470,13 +11435,13 @@
       <c r="BD76" s="18">
         <v>25.1</v>
       </c>
-      <c r="BE76" s="80">
+      <c r="BE76" s="18">
         <v>1010</v>
       </c>
       <c r="BF76" s="18">
         <v>47.7</v>
       </c>
-      <c r="BG76" s="72"/>
+      <c r="BG76" s="4"/>
       <c r="BH76" s="4"/>
       <c r="BI76" s="4"/>
       <c r="BJ76" s="3" t="s">
@@ -11585,13 +11550,13 @@
       <c r="BD77" s="18">
         <v>25.1</v>
       </c>
-      <c r="BE77" s="80">
+      <c r="BE77" s="18">
         <v>1010</v>
       </c>
       <c r="BF77" s="18">
         <v>47.7</v>
       </c>
-      <c r="BG77" s="83"/>
+      <c r="BG77" s="64"/>
       <c r="BH77" s="4"/>
       <c r="BI77" s="4"/>
       <c r="BJ77" s="3" t="s">
@@ -11700,13 +11665,13 @@
       <c r="BD78" s="18">
         <v>25.9</v>
       </c>
-      <c r="BE78" s="80">
+      <c r="BE78" s="18">
         <v>1010</v>
       </c>
-      <c r="BF78" s="80">
+      <c r="BF78" s="18">
         <v>47</v>
       </c>
-      <c r="BG78" s="72"/>
+      <c r="BG78" s="4"/>
       <c r="BH78" s="4"/>
       <c r="BI78" s="4"/>
       <c r="BJ78" s="3" t="s">
@@ -11815,14 +11780,14 @@
       <c r="BD79" s="18">
         <v>25.9</v>
       </c>
-      <c r="BE79" s="80">
+      <c r="BE79" s="18">
         <v>1010</v>
       </c>
-      <c r="BF79" s="80">
+      <c r="BF79" s="18">
         <v>47</v>
       </c>
-      <c r="BG79" s="72"/>
-      <c r="BH79" s="72"/>
+      <c r="BG79" s="4"/>
+      <c r="BH79" s="4"/>
       <c r="BI79" s="4"/>
       <c r="BJ79" s="3" t="s">
         <v>162</v>
@@ -11930,14 +11895,14 @@
       <c r="BD80" s="18">
         <v>25.9</v>
       </c>
-      <c r="BE80" s="80">
+      <c r="BE80" s="18">
         <v>1010</v>
       </c>
-      <c r="BF80" s="80">
+      <c r="BF80" s="18">
         <v>47</v>
       </c>
-      <c r="BG80" s="72"/>
-      <c r="BH80" s="72"/>
+      <c r="BG80" s="4"/>
+      <c r="BH80" s="4"/>
       <c r="BI80" s="18" t="s">
         <v>91</v>
       </c>
@@ -12047,14 +12012,14 @@
       <c r="BD81" s="18">
         <v>25.9</v>
       </c>
-      <c r="BE81" s="80">
+      <c r="BE81" s="18">
         <v>1010</v>
       </c>
-      <c r="BF81" s="80">
+      <c r="BF81" s="18">
         <v>47</v>
       </c>
-      <c r="BG81" s="83"/>
-      <c r="BH81" s="72"/>
+      <c r="BG81" s="64"/>
+      <c r="BH81" s="4"/>
       <c r="BI81" s="18" t="s">
         <v>92</v>
       </c>
@@ -12079,7 +12044,7 @@
       <c r="D82" s="8">
         <v>3</v>
       </c>
-      <c r="E82" s="71" t="s">
+      <c r="E82" s="2" t="s">
         <v>542</v>
       </c>
       <c r="F82" s="4" t="s">
@@ -12164,14 +12129,14 @@
       <c r="BD82" s="18">
         <v>26.4</v>
       </c>
-      <c r="BE82" s="80">
+      <c r="BE82" s="18">
         <v>1010</v>
       </c>
-      <c r="BF82" s="80">
+      <c r="BF82" s="18">
         <v>46.5</v>
       </c>
-      <c r="BG82" s="72"/>
-      <c r="BH82" s="72"/>
+      <c r="BG82" s="4"/>
+      <c r="BH82" s="4"/>
       <c r="BI82" s="4"/>
       <c r="BJ82" s="3" t="s">
         <v>165</v>
@@ -12279,13 +12244,13 @@
       <c r="BD83" s="18">
         <v>26.4</v>
       </c>
-      <c r="BE83" s="80">
+      <c r="BE83" s="18">
         <v>1010</v>
       </c>
-      <c r="BF83" s="80">
+      <c r="BF83" s="18">
         <v>46.5</v>
       </c>
-      <c r="BG83" s="72"/>
+      <c r="BG83" s="4"/>
       <c r="BH83" s="4"/>
       <c r="BI83" s="4"/>
       <c r="BJ83" s="3" t="s">
@@ -12394,13 +12359,13 @@
       <c r="BD84" s="18">
         <v>26.4</v>
       </c>
-      <c r="BE84" s="80">
+      <c r="BE84" s="18">
         <v>1010</v>
       </c>
-      <c r="BF84" s="80">
+      <c r="BF84" s="18">
         <v>46.5</v>
       </c>
-      <c r="BG84" s="72"/>
+      <c r="BG84" s="4"/>
       <c r="BH84" s="4"/>
       <c r="BI84" s="4"/>
       <c r="BJ84" s="3" t="s">
@@ -12509,14 +12474,14 @@
       <c r="BD85" s="18">
         <v>26.4</v>
       </c>
-      <c r="BE85" s="80">
+      <c r="BE85" s="18">
         <v>1010</v>
       </c>
-      <c r="BF85" s="80">
+      <c r="BF85" s="18">
         <v>46.5</v>
       </c>
-      <c r="BG85" s="72"/>
-      <c r="BH85" s="72"/>
+      <c r="BG85" s="4"/>
+      <c r="BH85" s="4"/>
       <c r="BI85" s="4"/>
       <c r="BJ85" s="3" t="s">
         <v>168</v>
@@ -12622,13 +12587,13 @@
       <c r="BD86" s="18">
         <v>26.4</v>
       </c>
-      <c r="BE86" s="80">
+      <c r="BE86" s="18">
         <v>1010</v>
       </c>
       <c r="BF86" s="18">
         <v>46.5</v>
       </c>
-      <c r="BG86" s="72"/>
+      <c r="BG86" s="4"/>
       <c r="BH86" s="4"/>
       <c r="BI86" s="4"/>
       <c r="BJ86" s="3" t="s">
@@ -12856,7 +12821,7 @@
       <c r="BF88" s="18">
         <v>46.5</v>
       </c>
-      <c r="BG88" s="72"/>
+      <c r="BG88" s="4"/>
       <c r="BH88" s="4"/>
       <c r="BI88" s="4"/>
       <c r="BJ88" s="3" t="s">
@@ -12963,13 +12928,13 @@
       <c r="BD89" s="18">
         <v>26.4</v>
       </c>
-      <c r="BE89" s="80">
+      <c r="BE89" s="18">
         <v>1010</v>
       </c>
-      <c r="BF89" s="80">
+      <c r="BF89" s="18">
         <v>46.5</v>
       </c>
-      <c r="BG89" s="72"/>
+      <c r="BG89" s="4"/>
       <c r="BH89" s="4"/>
       <c r="BI89" s="4"/>
       <c r="BJ89" s="3" t="s">
@@ -13076,13 +13041,13 @@
       <c r="BD90" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE90" s="80">
+      <c r="BE90" s="18">
         <v>1010</v>
       </c>
-      <c r="BF90" s="80">
+      <c r="BF90" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG90" s="72"/>
+      <c r="BG90" s="4"/>
       <c r="BH90" s="4"/>
       <c r="BI90" s="4"/>
       <c r="BJ90" s="3" t="s">
@@ -13189,14 +13154,14 @@
       <c r="BD91" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE91" s="80">
+      <c r="BE91" s="18">
         <v>1010</v>
       </c>
-      <c r="BF91" s="80">
+      <c r="BF91" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG91" s="72"/>
-      <c r="BH91" s="72"/>
+      <c r="BG91" s="4"/>
+      <c r="BH91" s="4"/>
       <c r="BI91" s="4"/>
       <c r="BJ91" s="3" t="s">
         <v>173</v>
@@ -13302,13 +13267,13 @@
       <c r="BD92" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE92" s="80">
+      <c r="BE92" s="18">
         <v>1010</v>
       </c>
       <c r="BF92" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG92" s="72"/>
+      <c r="BG92" s="4"/>
       <c r="BH92" s="4"/>
       <c r="BI92" s="4"/>
       <c r="BJ92" s="3" t="s">
@@ -13528,13 +13493,13 @@
       <c r="BD94" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE94" s="80">
+      <c r="BE94" s="18">
         <v>1010</v>
       </c>
       <c r="BF94" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG94" s="72"/>
+      <c r="BG94" s="4"/>
       <c r="BH94" s="4"/>
       <c r="BI94" s="4"/>
       <c r="BJ94" s="3" t="s">
@@ -13571,9 +13536,7 @@
         <v>571</v>
       </c>
       <c r="I95" s="48"/>
-      <c r="J95" s="48">
-        <v>0</v>
-      </c>
+      <c r="J95" s="48"/>
       <c r="K95" s="48"/>
       <c r="L95" s="7"/>
       <c r="M95" s="7">
@@ -13634,13 +13597,13 @@
       <c r="BD95" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE95" s="80">
+      <c r="BE95" s="18">
         <v>1010</v>
       </c>
-      <c r="BF95" s="80">
+      <c r="BF95" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG95" s="72"/>
+      <c r="BG95" s="4"/>
       <c r="BH95" s="4"/>
       <c r="BI95" s="4"/>
       <c r="BJ95" s="3" t="s">
@@ -13747,13 +13710,13 @@
       <c r="BD96" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE96" s="80">
+      <c r="BE96" s="18">
         <v>1010</v>
       </c>
-      <c r="BF96" s="80">
+      <c r="BF96" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG96" s="72"/>
+      <c r="BG96" s="4"/>
       <c r="BH96" s="4"/>
       <c r="BI96" s="4"/>
       <c r="BJ96" s="3" t="s">
@@ -13860,14 +13823,14 @@
       <c r="BD97" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE97" s="80">
+      <c r="BE97" s="18">
         <v>1010</v>
       </c>
-      <c r="BF97" s="80">
+      <c r="BF97" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG97" s="72"/>
-      <c r="BH97" s="72"/>
+      <c r="BG97" s="4"/>
+      <c r="BH97" s="4"/>
       <c r="BI97" s="4"/>
       <c r="BJ97" s="3" t="s">
         <v>178</v>
@@ -13973,14 +13936,14 @@
       <c r="BD98" s="18">
         <v>26.7</v>
       </c>
-      <c r="BE98" s="80">
+      <c r="BE98" s="18">
         <v>1010</v>
       </c>
-      <c r="BF98" s="80">
+      <c r="BF98" s="18">
         <v>46.7</v>
       </c>
-      <c r="BG98" s="72"/>
-      <c r="BH98" s="72"/>
+      <c r="BG98" s="4"/>
+      <c r="BH98" s="4"/>
       <c r="BI98" s="4"/>
       <c r="BJ98" s="3" t="s">
         <v>179</v>
@@ -14086,13 +14049,13 @@
       <c r="BD99" s="4">
         <v>23.9</v>
       </c>
-      <c r="BE99" s="72">
+      <c r="BE99" s="4">
         <v>1010</v>
       </c>
       <c r="BF99" s="63">
         <v>48.2</v>
       </c>
-      <c r="BG99" s="81"/>
+      <c r="BG99" s="63"/>
       <c r="BH99" s="4"/>
       <c r="BI99" s="4"/>
       <c r="BJ99" s="3" t="s">
@@ -14199,13 +14162,13 @@
       <c r="BD100" s="4">
         <v>23.9</v>
       </c>
-      <c r="BE100" s="72">
+      <c r="BE100" s="4">
         <v>1010</v>
       </c>
       <c r="BF100" s="63">
         <v>48.2</v>
       </c>
-      <c r="BG100" s="81"/>
+      <c r="BG100" s="63"/>
       <c r="BH100" s="4"/>
       <c r="BI100" s="13" t="s">
         <v>95</v>
@@ -14314,13 +14277,13 @@
       <c r="BD101" s="4">
         <v>23.9</v>
       </c>
-      <c r="BE101" s="72">
+      <c r="BE101" s="4">
         <v>1010</v>
       </c>
       <c r="BF101" s="63">
         <v>48.2</v>
       </c>
-      <c r="BG101" s="81"/>
+      <c r="BG101" s="63"/>
       <c r="BH101" s="4"/>
       <c r="BI101" s="4"/>
       <c r="BJ101" s="3" t="s">
@@ -14357,9 +14320,7 @@
         <v>223</v>
       </c>
       <c r="I102" s="48"/>
-      <c r="J102" s="48">
-        <v>0</v>
-      </c>
+      <c r="J102" s="48"/>
       <c r="K102" s="48"/>
       <c r="L102" s="7"/>
       <c r="M102" s="7">
@@ -14420,13 +14381,13 @@
       <c r="BD102" s="4">
         <v>24.1</v>
       </c>
-      <c r="BE102" s="72">
+      <c r="BE102" s="4">
         <v>1010</v>
       </c>
-      <c r="BF102" s="81">
+      <c r="BF102" s="63">
         <v>48.2</v>
       </c>
-      <c r="BG102" s="81"/>
+      <c r="BG102" s="63"/>
       <c r="BH102" s="4"/>
       <c r="BI102" s="4" t="s">
         <v>94</v>
@@ -14535,13 +14496,13 @@
       <c r="BD103" s="4">
         <v>24.1</v>
       </c>
-      <c r="BE103" s="72">
+      <c r="BE103" s="4">
         <v>1010</v>
       </c>
-      <c r="BF103" s="81">
+      <c r="BF103" s="63">
         <v>48.2</v>
       </c>
-      <c r="BG103" s="81"/>
+      <c r="BG103" s="63"/>
       <c r="BH103" s="4"/>
       <c r="BI103" s="4"/>
       <c r="BJ103" s="3" t="s">
@@ -14648,14 +14609,14 @@
       <c r="BD104" s="4">
         <v>24.1</v>
       </c>
-      <c r="BE104" s="72">
+      <c r="BE104" s="4">
         <v>1010</v>
       </c>
-      <c r="BF104" s="81">
+      <c r="BF104" s="63">
         <v>48.2</v>
       </c>
-      <c r="BG104" s="81"/>
-      <c r="BH104" s="72"/>
+      <c r="BG104" s="63"/>
+      <c r="BH104" s="4"/>
       <c r="BI104" s="13" t="s">
         <v>97</v>
       </c>
@@ -14763,14 +14724,14 @@
       <c r="BD105" s="4">
         <v>24.8</v>
       </c>
-      <c r="BE105" s="72">
+      <c r="BE105" s="4">
         <v>1010</v>
       </c>
-      <c r="BF105" s="81">
+      <c r="BF105" s="63">
         <v>47</v>
       </c>
-      <c r="BG105" s="81"/>
-      <c r="BH105" s="72"/>
+      <c r="BG105" s="63"/>
+      <c r="BH105" s="4"/>
       <c r="BI105" s="4"/>
       <c r="BJ105" s="3" t="s">
         <v>187</v>
@@ -14876,14 +14837,14 @@
       <c r="BD106" s="4">
         <v>24.8</v>
       </c>
-      <c r="BE106" s="72">
+      <c r="BE106" s="4">
         <v>1010</v>
       </c>
-      <c r="BF106" s="81">
+      <c r="BF106" s="63">
         <v>47</v>
       </c>
-      <c r="BG106" s="81"/>
-      <c r="BH106" s="72"/>
+      <c r="BG106" s="63"/>
+      <c r="BH106" s="4"/>
       <c r="BI106" s="4"/>
       <c r="BJ106" s="3" t="s">
         <v>188</v>
@@ -14989,14 +14950,14 @@
       <c r="BD107" s="4">
         <v>24.8</v>
       </c>
-      <c r="BE107" s="72">
+      <c r="BE107" s="4">
         <v>1010</v>
       </c>
-      <c r="BF107" s="81">
+      <c r="BF107" s="63">
         <v>47</v>
       </c>
-      <c r="BG107" s="81"/>
-      <c r="BH107" s="72"/>
+      <c r="BG107" s="63"/>
+      <c r="BH107" s="4"/>
       <c r="BI107" s="4"/>
       <c r="BJ107" s="3" t="s">
         <v>189</v>
@@ -15102,13 +15063,13 @@
       <c r="BD108" s="4">
         <v>24.8</v>
       </c>
-      <c r="BE108" s="72">
+      <c r="BE108" s="4">
         <v>1010</v>
       </c>
-      <c r="BF108" s="81">
+      <c r="BF108" s="63">
         <v>47</v>
       </c>
-      <c r="BG108" s="81"/>
+      <c r="BG108" s="63"/>
       <c r="BH108" s="4"/>
       <c r="BI108" s="4"/>
       <c r="BJ108" s="3" t="s">
@@ -15215,13 +15176,13 @@
       <c r="BD109" s="4">
         <v>24.8</v>
       </c>
-      <c r="BE109" s="72">
+      <c r="BE109" s="4">
         <v>1010</v>
       </c>
-      <c r="BF109" s="81">
+      <c r="BF109" s="63">
         <v>47</v>
       </c>
-      <c r="BG109" s="81"/>
+      <c r="BG109" s="63"/>
       <c r="BH109" s="4"/>
       <c r="BI109" s="4"/>
       <c r="BJ109" s="3" t="s">
@@ -15328,14 +15289,14 @@
       <c r="BD110" s="4">
         <v>24.8</v>
       </c>
-      <c r="BE110" s="72">
+      <c r="BE110" s="4">
         <v>1010</v>
       </c>
-      <c r="BF110" s="81">
+      <c r="BF110" s="63">
         <v>47</v>
       </c>
-      <c r="BG110" s="81"/>
-      <c r="BH110" s="72"/>
+      <c r="BG110" s="63"/>
+      <c r="BH110" s="4"/>
       <c r="BI110" s="13" t="s">
         <v>97</v>
       </c>
@@ -15448,13 +15409,13 @@
       <c r="BD111" s="4">
         <v>25.2</v>
       </c>
-      <c r="BE111" s="72">
+      <c r="BE111" s="4">
         <v>1010</v>
       </c>
       <c r="BF111" s="63">
         <v>47</v>
       </c>
-      <c r="BG111" s="81"/>
+      <c r="BG111" s="63"/>
       <c r="BH111" s="4"/>
       <c r="BI111" s="4"/>
       <c r="BJ111" s="3" t="s">
@@ -15491,9 +15452,7 @@
         <v>223</v>
       </c>
       <c r="I112" s="49"/>
-      <c r="J112" s="49">
-        <v>0</v>
-      </c>
+      <c r="J112" s="49"/>
       <c r="K112" s="49"/>
       <c r="L112" s="7">
         <v>0.161</v>
@@ -15550,13 +15509,13 @@
       <c r="BD112" s="4">
         <v>25.2</v>
       </c>
-      <c r="BE112" s="72">
+      <c r="BE112" s="4">
         <v>1010</v>
       </c>
       <c r="BF112" s="63">
         <v>47</v>
       </c>
-      <c r="BG112" s="81"/>
+      <c r="BG112" s="63"/>
       <c r="BH112" s="4"/>
       <c r="BI112" s="13" t="s">
         <v>96</v>
@@ -15676,7 +15635,7 @@
       <c r="BF113" s="63">
         <v>47</v>
       </c>
-      <c r="BG113" s="81"/>
+      <c r="BG113" s="63"/>
       <c r="BH113" s="4"/>
       <c r="BI113" s="4"/>
       <c r="BJ113" s="3" t="s">
@@ -15713,9 +15672,7 @@
         <v>223</v>
       </c>
       <c r="I114" s="48"/>
-      <c r="J114" s="48">
-        <v>0</v>
-      </c>
+      <c r="J114" s="48"/>
       <c r="K114" s="48"/>
       <c r="L114" s="7"/>
       <c r="M114" s="7">
@@ -15779,13 +15736,13 @@
       <c r="BD114" s="4">
         <v>25.7</v>
       </c>
-      <c r="BE114" s="72">
+      <c r="BE114" s="4">
         <v>1009</v>
       </c>
-      <c r="BF114" s="81">
+      <c r="BF114" s="63">
         <v>46.3</v>
       </c>
-      <c r="BG114" s="81"/>
+      <c r="BG114" s="63"/>
       <c r="BH114" s="4"/>
       <c r="BI114" s="4"/>
       <c r="BJ114" s="3" t="s">
@@ -15897,13 +15854,13 @@
       <c r="BD115" s="4">
         <v>25.7</v>
       </c>
-      <c r="BE115" s="72">
+      <c r="BE115" s="4">
         <v>1009</v>
       </c>
-      <c r="BF115" s="81">
+      <c r="BF115" s="63">
         <v>46.3</v>
       </c>
-      <c r="BG115" s="81"/>
+      <c r="BG115" s="63"/>
       <c r="BH115" s="4"/>
       <c r="BI115" s="4"/>
       <c r="BJ115" s="3" t="s">
@@ -16015,14 +15972,14 @@
       <c r="BD116" s="4">
         <v>25.7</v>
       </c>
-      <c r="BE116" s="72">
+      <c r="BE116" s="4">
         <v>1009</v>
       </c>
-      <c r="BF116" s="81">
+      <c r="BF116" s="63">
         <v>46.3</v>
       </c>
-      <c r="BG116" s="81"/>
-      <c r="BH116" s="72"/>
+      <c r="BG116" s="63"/>
+      <c r="BH116" s="4"/>
       <c r="BI116" s="4"/>
       <c r="BJ116" s="3" t="s">
         <v>196</v>
@@ -16133,14 +16090,14 @@
       <c r="BD117" s="4">
         <v>25.8</v>
       </c>
-      <c r="BE117" s="72">
+      <c r="BE117" s="4">
         <v>1009</v>
       </c>
-      <c r="BF117" s="81">
+      <c r="BF117" s="63">
         <v>45.7</v>
       </c>
-      <c r="BG117" s="81"/>
-      <c r="BH117" s="72"/>
+      <c r="BG117" s="63"/>
+      <c r="BH117" s="4"/>
       <c r="BI117" s="4"/>
       <c r="BJ117" s="3" t="s">
         <v>199</v>
@@ -16251,13 +16208,13 @@
       <c r="BD118" s="4">
         <v>25.8</v>
       </c>
-      <c r="BE118" s="72">
+      <c r="BE118" s="4">
         <v>1009</v>
       </c>
-      <c r="BF118" s="81">
+      <c r="BF118" s="63">
         <v>45.7</v>
       </c>
-      <c r="BG118" s="81"/>
+      <c r="BG118" s="63"/>
       <c r="BH118" s="4"/>
       <c r="BI118" s="4"/>
       <c r="BJ118" s="3" t="s">
@@ -16369,13 +16326,13 @@
       <c r="BD119" s="4">
         <v>25.8</v>
       </c>
-      <c r="BE119" s="72">
+      <c r="BE119" s="4">
         <v>1009</v>
       </c>
-      <c r="BF119" s="81">
+      <c r="BF119" s="63">
         <v>45.7</v>
       </c>
-      <c r="BG119" s="81"/>
+      <c r="BG119" s="63"/>
       <c r="BH119" s="4"/>
       <c r="BI119" s="4"/>
       <c r="BJ119" s="3" t="s">
@@ -16487,13 +16444,13 @@
       <c r="BD120" s="4">
         <v>26.1</v>
       </c>
-      <c r="BE120" s="72">
+      <c r="BE120" s="4">
         <v>1009</v>
       </c>
       <c r="BF120" s="63">
         <v>45.2</v>
       </c>
-      <c r="BG120" s="81"/>
+      <c r="BG120" s="63"/>
       <c r="BH120" s="4"/>
       <c r="BI120" s="4"/>
       <c r="BJ120" s="3" t="s">
@@ -16605,13 +16562,13 @@
       <c r="BD121" s="4">
         <v>26.1</v>
       </c>
-      <c r="BE121" s="72">
+      <c r="BE121" s="4">
         <v>1009</v>
       </c>
       <c r="BF121" s="63">
         <v>45.2</v>
       </c>
-      <c r="BG121" s="81"/>
+      <c r="BG121" s="63"/>
       <c r="BH121" s="4"/>
       <c r="BI121" s="4"/>
       <c r="BJ121" s="3" t="s">
@@ -16721,13 +16678,13 @@
       <c r="BD122" s="4">
         <v>26.1</v>
       </c>
-      <c r="BE122" s="72">
+      <c r="BE122" s="4">
         <v>1009</v>
       </c>
       <c r="BF122" s="63">
         <v>45.2</v>
       </c>
-      <c r="BG122" s="81"/>
+      <c r="BG122" s="63"/>
       <c r="BH122" s="4"/>
       <c r="BI122" s="4"/>
       <c r="BJ122" s="3" t="s">
@@ -16837,13 +16794,13 @@
       <c r="BD123" s="4">
         <v>26.4</v>
       </c>
-      <c r="BE123" s="72">
+      <c r="BE123" s="4">
         <v>1008</v>
       </c>
-      <c r="BF123" s="81">
+      <c r="BF123" s="63">
         <v>44.4</v>
       </c>
-      <c r="BG123" s="81"/>
+      <c r="BG123" s="63"/>
       <c r="BH123" s="4"/>
       <c r="BI123" s="4"/>
       <c r="BJ123" s="3" t="s">
@@ -16953,13 +16910,13 @@
       <c r="BD124" s="16">
         <v>25.5</v>
       </c>
-      <c r="BE124" s="79">
+      <c r="BE124" s="16">
         <v>1012</v>
       </c>
-      <c r="BF124" s="79">
+      <c r="BF124" s="16">
         <v>39.4</v>
       </c>
-      <c r="BG124" s="81"/>
+      <c r="BG124" s="63"/>
       <c r="BH124" s="4"/>
       <c r="BI124" s="4"/>
       <c r="BJ124" s="3" t="s">
@@ -17069,14 +17026,14 @@
       <c r="BD125" s="16">
         <v>25.5</v>
       </c>
-      <c r="BE125" s="79">
+      <c r="BE125" s="16">
         <v>1012</v>
       </c>
-      <c r="BF125" s="79">
+      <c r="BF125" s="16">
         <v>39.4</v>
       </c>
-      <c r="BG125" s="78"/>
-      <c r="BH125" s="72"/>
+      <c r="BG125" s="59"/>
+      <c r="BH125" s="4"/>
       <c r="BI125" s="4"/>
       <c r="BJ125" s="3" t="s">
         <v>207</v>
@@ -17099,7 +17056,7 @@
       <c r="D126" s="8">
         <v>7</v>
       </c>
-      <c r="E126" s="71" t="s">
+      <c r="E126" s="2" t="s">
         <v>212</v>
       </c>
       <c r="F126" s="4" t="s">
@@ -17185,14 +17142,14 @@
       <c r="BD126" s="16">
         <v>25.5</v>
       </c>
-      <c r="BE126" s="79">
+      <c r="BE126" s="16">
         <v>1012</v>
       </c>
-      <c r="BF126" s="79">
+      <c r="BF126" s="16">
         <v>39.4</v>
       </c>
-      <c r="BG126" s="78"/>
-      <c r="BH126" s="72"/>
+      <c r="BG126" s="59"/>
+      <c r="BH126" s="4"/>
       <c r="BI126" s="4"/>
       <c r="BJ126" s="3" t="s">
         <v>272</v>
@@ -17301,13 +17258,13 @@
       <c r="BD127" s="16">
         <v>25.5</v>
       </c>
-      <c r="BE127" s="79">
+      <c r="BE127" s="16">
         <v>1012</v>
       </c>
-      <c r="BF127" s="79">
+      <c r="BF127" s="16">
         <v>39.4</v>
       </c>
-      <c r="BG127" s="78"/>
+      <c r="BG127" s="59"/>
       <c r="BH127" s="4"/>
       <c r="BI127" s="4"/>
       <c r="BJ127" s="3" t="s">
@@ -17778,7 +17735,7 @@
       <c r="BE131" s="17">
         <v>1012</v>
       </c>
-      <c r="BF131" s="79">
+      <c r="BF131" s="16">
         <v>39.4</v>
       </c>
       <c r="BG131" s="15"/>
@@ -17896,7 +17853,7 @@
       <c r="BE132" s="62">
         <v>1012</v>
       </c>
-      <c r="BF132" s="79">
+      <c r="BF132" s="16">
         <v>40</v>
       </c>
       <c r="BG132" s="58"/>
@@ -18014,11 +17971,11 @@
       <c r="BE133" s="17">
         <v>1012</v>
       </c>
-      <c r="BF133" s="79">
+      <c r="BF133" s="16">
         <v>40</v>
       </c>
       <c r="BG133" s="15"/>
-      <c r="BH133" s="72"/>
+      <c r="BH133" s="4"/>
       <c r="BI133" s="4"/>
       <c r="BJ133" s="3" t="s">
         <v>274</v>
@@ -18132,11 +18089,11 @@
       <c r="BE134" s="17">
         <v>1012</v>
       </c>
-      <c r="BF134" s="79">
+      <c r="BF134" s="16">
         <v>40</v>
       </c>
       <c r="BG134" s="15"/>
-      <c r="BH134" s="72"/>
+      <c r="BH134" s="4"/>
       <c r="BI134" s="4"/>
       <c r="BJ134" s="3" t="s">
         <v>275</v>
@@ -18250,7 +18207,7 @@
       <c r="BE135" s="17">
         <v>1012</v>
       </c>
-      <c r="BF135" s="79">
+      <c r="BF135" s="16">
         <v>40</v>
       </c>
       <c r="BG135" s="15"/>
@@ -18722,7 +18679,7 @@
       <c r="BE139" s="17">
         <v>1012</v>
       </c>
-      <c r="BF139" s="79">
+      <c r="BF139" s="16">
         <v>40</v>
       </c>
       <c r="BG139" s="15"/>
@@ -18840,7 +18797,7 @@
       <c r="BE140" s="17">
         <v>1011</v>
       </c>
-      <c r="BF140" s="79">
+      <c r="BF140" s="16">
         <v>40</v>
       </c>
       <c r="BG140" s="15"/>
@@ -18958,11 +18915,11 @@
       <c r="BE141" s="17">
         <v>1011</v>
       </c>
-      <c r="BF141" s="79">
+      <c r="BF141" s="16">
         <v>40</v>
       </c>
       <c r="BG141" s="15"/>
-      <c r="BH141" s="72"/>
+      <c r="BH141" s="4"/>
       <c r="BI141" s="4"/>
       <c r="BJ141" s="3" t="s">
         <v>317</v>
@@ -19426,7 +19383,7 @@
       <c r="BE145" s="17">
         <v>1011</v>
       </c>
-      <c r="BF145" s="79">
+      <c r="BF145" s="16">
         <v>39.6</v>
       </c>
       <c r="BG145" s="15"/>
@@ -19542,7 +19499,7 @@
       <c r="BE146" s="17">
         <v>1011</v>
       </c>
-      <c r="BF146" s="79">
+      <c r="BF146" s="16">
         <v>39.6</v>
       </c>
       <c r="BG146" s="15"/>
@@ -19658,11 +19615,11 @@
       <c r="BE147" s="17">
         <v>1011</v>
       </c>
-      <c r="BF147" s="79">
+      <c r="BF147" s="16">
         <v>39.6</v>
       </c>
       <c r="BG147" s="15"/>
-      <c r="BH147" s="72"/>
+      <c r="BH147" s="4"/>
       <c r="BI147" s="4"/>
       <c r="BJ147" s="3" t="s">
         <v>328</v>
@@ -19768,10 +19725,10 @@
       <c r="BD148" s="16">
         <v>24.5</v>
       </c>
-      <c r="BE148" s="79">
+      <c r="BE148" s="16">
         <v>1013</v>
       </c>
-      <c r="BF148" s="79">
+      <c r="BF148" s="16">
         <v>47.7</v>
       </c>
       <c r="BG148" s="15"/>
@@ -19885,10 +19842,10 @@
       <c r="BD149" s="16">
         <v>24.5</v>
       </c>
-      <c r="BE149" s="79">
+      <c r="BE149" s="16">
         <v>1013</v>
       </c>
-      <c r="BF149" s="79">
+      <c r="BF149" s="16">
         <v>47.7</v>
       </c>
       <c r="BG149" s="15"/>
@@ -20002,10 +19959,10 @@
       <c r="BD150" s="16">
         <v>24.5</v>
       </c>
-      <c r="BE150" s="79">
+      <c r="BE150" s="16">
         <v>1013</v>
       </c>
-      <c r="BF150" s="79">
+      <c r="BF150" s="16">
         <v>47.7</v>
       </c>
       <c r="BG150" s="58"/>
@@ -20117,10 +20074,10 @@
       <c r="BD151" s="16">
         <v>24.5</v>
       </c>
-      <c r="BE151" s="79">
+      <c r="BE151" s="16">
         <v>1013</v>
       </c>
-      <c r="BF151" s="79">
+      <c r="BF151" s="16">
         <v>47.7</v>
       </c>
       <c r="BG151" s="15"/>
@@ -20224,7 +20181,7 @@
       <c r="AX152" s="9"/>
       <c r="AY152" s="9"/>
       <c r="AZ152" s="9"/>
-      <c r="BA152" s="72">
+      <c r="BA152" s="4">
         <v>113.4</v>
       </c>
       <c r="BB152" s="4"/>
@@ -20232,14 +20189,14 @@
       <c r="BD152" s="16">
         <v>24.9</v>
       </c>
-      <c r="BE152" s="79">
+      <c r="BE152" s="16">
         <v>1012</v>
       </c>
-      <c r="BF152" s="79">
+      <c r="BF152" s="16">
         <v>45.5</v>
       </c>
       <c r="BG152" s="15"/>
-      <c r="BH152" s="84">
+      <c r="BH152" s="7">
         <v>2096</v>
       </c>
       <c r="BI152" s="13"/>
@@ -20347,14 +20304,14 @@
       <c r="BD153" s="16">
         <v>24.9</v>
       </c>
-      <c r="BE153" s="79">
+      <c r="BE153" s="16">
         <v>1012</v>
       </c>
-      <c r="BF153" s="79">
+      <c r="BF153" s="16">
         <v>45.5</v>
       </c>
       <c r="BG153" s="15"/>
-      <c r="BH153" s="84">
+      <c r="BH153" s="7">
         <v>2096</v>
       </c>
       <c r="BI153" s="13" t="s">
@@ -20465,14 +20422,14 @@
       <c r="BD154" s="16">
         <v>24.9</v>
       </c>
-      <c r="BE154" s="79">
+      <c r="BE154" s="16">
         <v>1012</v>
       </c>
-      <c r="BF154" s="79">
+      <c r="BF154" s="16">
         <v>45.5</v>
       </c>
       <c r="BG154" s="58"/>
-      <c r="BH154" s="84">
+      <c r="BH154" s="7">
         <v>2096</v>
       </c>
       <c r="BI154" s="4"/>
@@ -20581,14 +20538,14 @@
       <c r="BD155" s="16">
         <v>24.9</v>
       </c>
-      <c r="BE155" s="79">
+      <c r="BE155" s="16">
         <v>1012</v>
       </c>
-      <c r="BF155" s="79">
+      <c r="BF155" s="16">
         <v>45.5</v>
       </c>
       <c r="BG155" s="15"/>
-      <c r="BH155" s="84">
+      <c r="BH155" s="7">
         <v>2096</v>
       </c>
       <c r="BI155" s="4"/>
@@ -20697,14 +20654,14 @@
       <c r="BD156" s="16">
         <v>24.9</v>
       </c>
-      <c r="BE156" s="79">
+      <c r="BE156" s="16">
         <v>1012</v>
       </c>
-      <c r="BF156" s="79">
+      <c r="BF156" s="16">
         <v>45.5</v>
       </c>
       <c r="BG156" s="15"/>
-      <c r="BH156" s="84">
+      <c r="BH156" s="7">
         <v>2096</v>
       </c>
       <c r="BI156" s="13" t="s">
@@ -20815,14 +20772,14 @@
       <c r="BD157" s="16">
         <v>24.9</v>
       </c>
-      <c r="BE157" s="79">
+      <c r="BE157" s="16">
         <v>1012</v>
       </c>
-      <c r="BF157" s="79">
+      <c r="BF157" s="16">
         <v>45.5</v>
       </c>
       <c r="BG157" s="15"/>
-      <c r="BH157" s="84">
+      <c r="BH157" s="7">
         <v>2096</v>
       </c>
       <c r="BI157" s="13" t="s">
@@ -20933,14 +20890,14 @@
       <c r="BD158" s="16">
         <v>24.9</v>
       </c>
-      <c r="BE158" s="79">
+      <c r="BE158" s="16">
         <v>1012</v>
       </c>
-      <c r="BF158" s="79">
+      <c r="BF158" s="16">
         <v>45.5</v>
       </c>
       <c r="BG158" s="15"/>
-      <c r="BH158" s="84">
+      <c r="BH158" s="7">
         <v>2096</v>
       </c>
       <c r="BI158" s="4"/>
@@ -21049,14 +21006,14 @@
       <c r="BD159" s="16">
         <v>24.9</v>
       </c>
-      <c r="BE159" s="79">
+      <c r="BE159" s="16">
         <v>1012</v>
       </c>
-      <c r="BF159" s="79">
+      <c r="BF159" s="16">
         <v>45.5</v>
       </c>
       <c r="BG159" s="15"/>
-      <c r="BH159" s="84">
+      <c r="BH159" s="7">
         <v>2096</v>
       </c>
       <c r="BI159" s="4"/>
@@ -21160,7 +21117,7 @@
       <c r="BD160" s="16">
         <v>25.1</v>
       </c>
-      <c r="BE160" s="79">
+      <c r="BE160" s="16">
         <v>1012</v>
       </c>
       <c r="BF160" s="16">
@@ -21271,7 +21228,7 @@
       <c r="BD161" s="16">
         <v>25.1</v>
       </c>
-      <c r="BE161" s="79">
+      <c r="BE161" s="16">
         <v>1012</v>
       </c>
       <c r="BF161" s="16">
@@ -21382,7 +21339,7 @@
       <c r="BD162" s="16">
         <v>25.1</v>
       </c>
-      <c r="BE162" s="79">
+      <c r="BE162" s="16">
         <v>1012</v>
       </c>
       <c r="BF162" s="16">
@@ -21493,10 +21450,10 @@
       <c r="BD163" s="16">
         <v>25.1</v>
       </c>
-      <c r="BE163" s="79">
+      <c r="BE163" s="16">
         <v>1012</v>
       </c>
-      <c r="BF163" s="79">
+      <c r="BF163" s="16">
         <v>44.6</v>
       </c>
       <c r="BG163" s="15"/>
@@ -21604,10 +21561,10 @@
       <c r="BD164" s="16">
         <v>25.3</v>
       </c>
-      <c r="BE164" s="79">
+      <c r="BE164" s="16">
         <v>1012</v>
       </c>
-      <c r="BF164" s="79">
+      <c r="BF164" s="16">
         <v>44.3</v>
       </c>
       <c r="BG164" s="15"/>
@@ -21717,14 +21674,14 @@
       <c r="BD165" s="16">
         <v>25.3</v>
       </c>
-      <c r="BE165" s="79">
+      <c r="BE165" s="16">
         <v>1012</v>
       </c>
-      <c r="BF165" s="79">
+      <c r="BF165" s="16">
         <v>44.3</v>
       </c>
       <c r="BG165" s="15"/>
-      <c r="BH165" s="84">
+      <c r="BH165" s="7">
         <v>2096</v>
       </c>
       <c r="BI165" s="4"/>
@@ -21825,7 +21782,7 @@
       <c r="BD166" s="16">
         <v>25.3</v>
       </c>
-      <c r="BE166" s="79">
+      <c r="BE166" s="16">
         <v>1012</v>
       </c>
       <c r="BF166" s="16">
@@ -21933,7 +21890,7 @@
       <c r="BD167" s="16">
         <v>25.6</v>
       </c>
-      <c r="BE167" s="79">
+      <c r="BE167" s="16">
         <v>1011</v>
       </c>
       <c r="BF167" s="16">
@@ -22041,7 +21998,7 @@
       <c r="BD168" s="16">
         <v>25.6</v>
       </c>
-      <c r="BE168" s="79">
+      <c r="BE168" s="16">
         <v>1011</v>
       </c>
       <c r="BF168" s="16">
@@ -22149,10 +22106,10 @@
       <c r="BD169" s="16">
         <v>25.6</v>
       </c>
-      <c r="BE169" s="79">
+      <c r="BE169" s="16">
         <v>1011</v>
       </c>
-      <c r="BF169" s="79">
+      <c r="BF169" s="16">
         <v>44.1</v>
       </c>
       <c r="BG169" s="15"/>
@@ -22257,10 +22214,10 @@
       <c r="BD170" s="16">
         <v>26</v>
       </c>
-      <c r="BE170" s="79">
+      <c r="BE170" s="16">
         <v>1012</v>
       </c>
-      <c r="BF170" s="79">
+      <c r="BF170" s="16">
         <v>43</v>
       </c>
       <c r="BG170" s="15"/>
@@ -22365,14 +22322,14 @@
       <c r="BD171" s="16">
         <v>26</v>
       </c>
-      <c r="BE171" s="79">
+      <c r="BE171" s="16">
         <v>1012</v>
       </c>
-      <c r="BF171" s="79">
+      <c r="BF171" s="16">
         <v>43</v>
       </c>
       <c r="BG171" s="15"/>
-      <c r="BH171" s="84">
+      <c r="BH171" s="7">
         <v>2096</v>
       </c>
       <c r="BI171" s="4"/>
@@ -22476,13 +22433,13 @@
       <c r="BE172" s="14">
         <v>1012</v>
       </c>
-      <c r="BF172" s="73">
+      <c r="BF172" s="61">
         <v>54</v>
       </c>
       <c r="BG172" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH172" s="72">
+      <c r="BH172" s="4">
         <v>2096</v>
       </c>
       <c r="BI172" s="4"/>
@@ -22520,9 +22477,7 @@
         <v>378</v>
       </c>
       <c r="I173" s="48"/>
-      <c r="J173" s="48">
-        <v>0</v>
-      </c>
+      <c r="J173" s="48"/>
       <c r="K173" s="48"/>
       <c r="L173" s="7"/>
       <c r="M173" s="7">
@@ -22579,7 +22534,7 @@
       <c r="BE173" s="60">
         <v>1012</v>
       </c>
-      <c r="BF173" s="73">
+      <c r="BF173" s="61">
         <v>54</v>
       </c>
       <c r="BG173" s="58">
@@ -23031,7 +22986,7 @@
       <c r="BE177" s="14">
         <v>1012</v>
       </c>
-      <c r="BF177" s="73">
+      <c r="BF177" s="61">
         <v>54</v>
       </c>
       <c r="BG177" s="15">
@@ -23144,7 +23099,7 @@
       <c r="BE178" s="14">
         <v>1012</v>
       </c>
-      <c r="BF178" s="73">
+      <c r="BF178" s="61">
         <v>54</v>
       </c>
       <c r="BG178" s="15">
@@ -23257,13 +23212,13 @@
       <c r="BE179" s="14">
         <v>1011</v>
       </c>
-      <c r="BF179" s="73">
+      <c r="BF179" s="61">
         <v>54</v>
       </c>
       <c r="BG179" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH179" s="72">
+      <c r="BH179" s="4">
         <v>2096</v>
       </c>
       <c r="BI179" s="4"/>
@@ -23370,13 +23325,13 @@
       <c r="BE180" s="14">
         <v>1011</v>
       </c>
-      <c r="BF180" s="73">
+      <c r="BF180" s="61">
         <v>54</v>
       </c>
       <c r="BG180" s="15">
         <v>1.173</v>
       </c>
-      <c r="BH180" s="72">
+      <c r="BH180" s="4">
         <v>2096</v>
       </c>
       <c r="BI180" s="4"/>
@@ -23483,13 +23438,13 @@
       <c r="BE181" s="14">
         <v>1011</v>
       </c>
-      <c r="BF181" s="73">
+      <c r="BF181" s="61">
         <v>54</v>
       </c>
       <c r="BG181" s="15">
         <v>1.173</v>
       </c>
-      <c r="BH181" s="72">
+      <c r="BH181" s="4">
         <v>2096</v>
       </c>
       <c r="BI181" s="4"/>
@@ -23596,13 +23551,13 @@
       <c r="BE182" s="14">
         <v>1011</v>
       </c>
-      <c r="BF182" s="73">
+      <c r="BF182" s="61">
         <v>54</v>
       </c>
       <c r="BG182" s="15">
         <v>1.173</v>
       </c>
-      <c r="BH182" s="72">
+      <c r="BH182" s="4">
         <v>2096</v>
       </c>
       <c r="BI182" s="4"/>
@@ -23709,7 +23664,7 @@
       <c r="BE183" s="14">
         <v>1011</v>
       </c>
-      <c r="BF183" s="73">
+      <c r="BF183" s="61">
         <v>54</v>
       </c>
       <c r="BG183" s="15">
@@ -23824,13 +23779,13 @@
       <c r="BE184" s="14">
         <v>1010</v>
       </c>
-      <c r="BF184" s="73">
+      <c r="BF184" s="61">
         <v>52</v>
       </c>
       <c r="BG184" s="15">
         <v>1.177</v>
       </c>
-      <c r="BH184" s="72">
+      <c r="BH184" s="4">
         <v>2096</v>
       </c>
       <c r="BI184" s="4"/>
@@ -23939,13 +23894,13 @@
       <c r="BE185" s="14">
         <v>1010</v>
       </c>
-      <c r="BF185" s="73">
+      <c r="BF185" s="61">
         <v>52</v>
       </c>
       <c r="BG185" s="15">
         <v>1.175</v>
       </c>
-      <c r="BH185" s="72">
+      <c r="BH185" s="4">
         <v>2096</v>
       </c>
       <c r="BI185" s="4"/>
@@ -24054,13 +24009,13 @@
       <c r="BE186" s="14">
         <v>1010</v>
       </c>
-      <c r="BF186" s="73">
+      <c r="BF186" s="61">
         <v>50</v>
       </c>
       <c r="BG186" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH186" s="72">
+      <c r="BH186" s="4">
         <v>2096</v>
       </c>
       <c r="BI186" s="4"/>
@@ -24169,13 +24124,13 @@
       <c r="BE187" s="14">
         <v>1010</v>
       </c>
-      <c r="BF187" s="73">
+      <c r="BF187" s="61">
         <v>51</v>
       </c>
       <c r="BG187" s="15">
         <v>1.173</v>
       </c>
-      <c r="BH187" s="72">
+      <c r="BH187" s="4">
         <v>2096</v>
       </c>
       <c r="BI187" s="4"/>
@@ -24284,13 +24239,13 @@
       <c r="BE188" s="14">
         <v>1010</v>
       </c>
-      <c r="BF188" s="73">
+      <c r="BF188" s="61">
         <v>48</v>
       </c>
       <c r="BG188" s="15">
         <v>1.173</v>
       </c>
-      <c r="BH188" s="72">
+      <c r="BH188" s="4">
         <v>2096</v>
       </c>
       <c r="BI188" s="4"/>
@@ -24399,13 +24354,13 @@
       <c r="BE189" s="14">
         <v>1010</v>
       </c>
-      <c r="BF189" s="73">
+      <c r="BF189" s="61">
         <v>48</v>
       </c>
       <c r="BG189" s="15">
         <v>1.1719999999999999</v>
       </c>
-      <c r="BH189" s="72">
+      <c r="BH189" s="4">
         <v>2096</v>
       </c>
       <c r="BI189" s="4"/>
@@ -24514,13 +24469,13 @@
       <c r="BE190" s="14">
         <v>1010</v>
       </c>
-      <c r="BF190" s="73">
+      <c r="BF190" s="61">
         <v>52</v>
       </c>
       <c r="BG190" s="15">
         <v>1.177</v>
       </c>
-      <c r="BH190" s="72">
+      <c r="BH190" s="4">
         <v>2096</v>
       </c>
       <c r="BI190" s="4"/>
@@ -24629,13 +24584,13 @@
       <c r="BE191" s="14">
         <v>1010</v>
       </c>
-      <c r="BF191" s="73">
+      <c r="BF191" s="61">
         <v>52</v>
       </c>
       <c r="BG191" s="15">
         <v>1.175</v>
       </c>
-      <c r="BH191" s="72">
+      <c r="BH191" s="4">
         <v>2096</v>
       </c>
       <c r="BI191" s="4"/>
@@ -24744,13 +24699,13 @@
       <c r="BE192" s="14">
         <v>1010</v>
       </c>
-      <c r="BF192" s="73">
+      <c r="BF192" s="61">
         <v>50</v>
       </c>
       <c r="BG192" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH192" s="72">
+      <c r="BH192" s="4">
         <v>2096</v>
       </c>
       <c r="BI192" s="4"/>
@@ -24859,13 +24814,13 @@
       <c r="BE193" s="14">
         <v>1010</v>
       </c>
-      <c r="BF193" s="73">
+      <c r="BF193" s="61">
         <v>48</v>
       </c>
       <c r="BG193" s="15">
         <v>1.173</v>
       </c>
-      <c r="BH193" s="72">
+      <c r="BH193" s="4">
         <v>2096</v>
       </c>
       <c r="BI193" s="4"/>
@@ -24974,13 +24929,13 @@
       <c r="BE194" s="14">
         <v>1010</v>
       </c>
-      <c r="BF194" s="73">
+      <c r="BF194" s="61">
         <v>48</v>
       </c>
       <c r="BG194" s="15">
         <v>1.1719999999999999</v>
       </c>
-      <c r="BH194" s="72">
+      <c r="BH194" s="4">
         <v>2096</v>
       </c>
       <c r="BI194" s="4"/>
@@ -25089,13 +25044,13 @@
       <c r="BE195" s="14">
         <v>1009</v>
       </c>
-      <c r="BF195" s="73">
+      <c r="BF195" s="61">
         <v>50</v>
       </c>
       <c r="BG195" s="15">
         <v>1.17</v>
       </c>
-      <c r="BH195" s="72">
+      <c r="BH195" s="4">
         <v>2096</v>
       </c>
       <c r="BI195" s="4"/>
@@ -25201,13 +25156,13 @@
       <c r="BE196" s="14">
         <v>1010</v>
       </c>
-      <c r="BF196" s="73">
+      <c r="BF196" s="61">
         <v>52</v>
       </c>
       <c r="BG196" s="15">
         <v>1.177</v>
       </c>
-      <c r="BH196" s="72">
+      <c r="BH196" s="4">
         <v>2096</v>
       </c>
       <c r="BI196" s="4"/>
@@ -25316,13 +25271,13 @@
       <c r="BE197" s="14">
         <v>1010</v>
       </c>
-      <c r="BF197" s="73">
+      <c r="BF197" s="61">
         <v>52</v>
       </c>
       <c r="BG197" s="15">
         <v>1.175</v>
       </c>
-      <c r="BH197" s="72">
+      <c r="BH197" s="4">
         <v>2096</v>
       </c>
       <c r="BI197" s="4"/>
@@ -25347,7 +25302,7 @@
       <c r="D198" s="8">
         <v>3</v>
       </c>
-      <c r="E198" s="71" t="s">
+      <c r="E198" s="2" t="s">
         <v>213</v>
       </c>
       <c r="F198" s="4" t="s">
@@ -25431,13 +25386,13 @@
       <c r="BE198" s="14">
         <v>1010</v>
       </c>
-      <c r="BF198" s="73">
+      <c r="BF198" s="61">
         <v>51</v>
       </c>
       <c r="BG198" s="15">
         <v>1.173</v>
       </c>
-      <c r="BH198" s="72">
+      <c r="BH198" s="4">
         <v>2096</v>
       </c>
       <c r="BI198" s="4"/>
@@ -25544,13 +25499,13 @@
       <c r="BE199" s="14">
         <v>1010</v>
       </c>
-      <c r="BF199" s="73">
+      <c r="BF199" s="61">
         <v>48</v>
       </c>
       <c r="BG199" s="15">
         <v>1.173</v>
       </c>
-      <c r="BH199" s="72">
+      <c r="BH199" s="4">
         <v>2096</v>
       </c>
       <c r="BI199" s="4"/>
@@ -25575,7 +25530,7 @@
       <c r="D200" s="8">
         <v>5</v>
       </c>
-      <c r="E200" s="71" t="s">
+      <c r="E200" s="2" t="s">
         <v>213</v>
       </c>
       <c r="F200" s="4" t="s">
@@ -25659,13 +25614,13 @@
       <c r="BE200" s="14">
         <v>1009</v>
       </c>
-      <c r="BF200" s="73">
+      <c r="BF200" s="61">
         <v>50</v>
       </c>
       <c r="BG200" s="15">
         <v>1.17</v>
       </c>
-      <c r="BH200" s="72">
+      <c r="BH200" s="4">
         <v>2096</v>
       </c>
       <c r="BI200" s="4"/>
@@ -25774,13 +25729,13 @@
       <c r="BE201" s="14">
         <v>1009</v>
       </c>
-      <c r="BF201" s="73">
+      <c r="BF201" s="61">
         <v>50</v>
       </c>
       <c r="BG201" s="15">
         <v>1.17</v>
       </c>
-      <c r="BH201" s="72">
+      <c r="BH201" s="4">
         <v>2096</v>
       </c>
       <c r="BI201" s="4"/>
@@ -25805,7 +25760,7 @@
       <c r="D202" s="8">
         <v>7</v>
       </c>
-      <c r="E202" s="71" t="s">
+      <c r="E202" s="2" t="s">
         <v>218</v>
       </c>
       <c r="F202" s="4" t="s">
@@ -25889,13 +25844,13 @@
       <c r="BE202" s="14">
         <v>1009</v>
       </c>
-      <c r="BF202" s="73">
+      <c r="BF202" s="61">
         <v>50</v>
       </c>
       <c r="BG202" s="15">
         <v>1.17</v>
       </c>
-      <c r="BH202" s="72">
+      <c r="BH202" s="4">
         <v>2096</v>
       </c>
       <c r="BI202" s="4"/>
@@ -26006,13 +25961,13 @@
       <c r="BE203" s="14">
         <v>1009</v>
       </c>
-      <c r="BF203" s="73">
+      <c r="BF203" s="61">
         <v>61</v>
       </c>
       <c r="BG203" s="15">
         <v>1.1759999999999999</v>
       </c>
-      <c r="BH203" s="72">
+      <c r="BH203" s="4">
         <v>2096</v>
       </c>
       <c r="BI203" s="4"/>
@@ -26123,13 +26078,13 @@
       <c r="BE204" s="14">
         <v>1009</v>
       </c>
-      <c r="BF204" s="73">
+      <c r="BF204" s="61">
         <v>62</v>
       </c>
       <c r="BG204" s="15">
         <v>1.175</v>
       </c>
-      <c r="BH204" s="72">
+      <c r="BH204" s="4">
         <v>2096</v>
       </c>
       <c r="BI204" s="4"/>
@@ -26240,13 +26195,13 @@
       <c r="BE205" s="14">
         <v>1009</v>
       </c>
-      <c r="BF205" s="73">
+      <c r="BF205" s="61">
         <v>60</v>
       </c>
       <c r="BG205" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH205" s="72">
+      <c r="BH205" s="4">
         <v>2096</v>
       </c>
       <c r="BI205" s="4"/>
@@ -26357,13 +26312,13 @@
       <c r="BE206" s="14">
         <v>1009</v>
       </c>
-      <c r="BF206" s="73">
+      <c r="BF206" s="61">
         <v>59</v>
       </c>
       <c r="BG206" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH206" s="72">
+      <c r="BH206" s="4">
         <v>2096</v>
       </c>
       <c r="BI206" s="4"/>
@@ -26474,13 +26429,13 @@
       <c r="BE207" s="14">
         <v>1009</v>
       </c>
-      <c r="BF207" s="73">
+      <c r="BF207" s="61">
         <v>60</v>
       </c>
       <c r="BG207" s="15">
         <v>1.173</v>
       </c>
-      <c r="BH207" s="72">
+      <c r="BH207" s="4">
         <v>2096</v>
       </c>
       <c r="BI207" s="4"/>
@@ -26591,13 +26546,13 @@
       <c r="BE208" s="14">
         <v>1009</v>
       </c>
-      <c r="BF208" s="73">
+      <c r="BF208" s="61">
         <v>58</v>
       </c>
       <c r="BG208" s="15">
         <v>1.171</v>
       </c>
-      <c r="BH208" s="72">
+      <c r="BH208" s="4">
         <v>2096</v>
       </c>
       <c r="BI208" s="4"/>
@@ -26708,13 +26663,13 @@
       <c r="BE209" s="14">
         <v>1009</v>
       </c>
-      <c r="BF209" s="73">
+      <c r="BF209" s="61">
         <v>58</v>
       </c>
       <c r="BG209" s="15">
         <v>1.171</v>
       </c>
-      <c r="BH209" s="72">
+      <c r="BH209" s="4">
         <v>2096</v>
       </c>
       <c r="BI209" s="4"/>
@@ -26823,13 +26778,13 @@
       <c r="BE210" s="14">
         <v>1009</v>
       </c>
-      <c r="BF210" s="73">
+      <c r="BF210" s="61">
         <v>58</v>
       </c>
       <c r="BG210" s="15">
         <v>1.17</v>
       </c>
-      <c r="BH210" s="72">
+      <c r="BH210" s="4">
         <v>2096</v>
       </c>
       <c r="BI210" s="4"/>
@@ -26940,13 +26895,13 @@
       <c r="BE211" s="14">
         <v>1009</v>
       </c>
-      <c r="BF211" s="73">
+      <c r="BF211" s="61">
         <v>62</v>
       </c>
       <c r="BG211" s="15">
         <v>1.175</v>
       </c>
-      <c r="BH211" s="72">
+      <c r="BH211" s="4">
         <v>2096</v>
       </c>
       <c r="BI211" s="4"/>
@@ -27045,13 +27000,13 @@
       <c r="BE212" s="14">
         <v>1009</v>
       </c>
-      <c r="BF212" s="73">
+      <c r="BF212" s="61">
         <v>61</v>
       </c>
       <c r="BG212" s="15">
         <v>1.175</v>
       </c>
-      <c r="BH212" s="72">
+      <c r="BH212" s="4">
         <v>2096</v>
       </c>
       <c r="BI212" s="4" t="s">
@@ -27164,13 +27119,13 @@
       <c r="BE213" s="14">
         <v>1009</v>
       </c>
-      <c r="BF213" s="73">
+      <c r="BF213" s="61">
         <v>60</v>
       </c>
       <c r="BG213" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH213" s="72">
+      <c r="BH213" s="4">
         <v>2096</v>
       </c>
       <c r="BI213" s="4"/>
@@ -27281,13 +27236,13 @@
       <c r="BE214" s="14">
         <v>1009</v>
       </c>
-      <c r="BF214" s="73">
+      <c r="BF214" s="61">
         <v>60</v>
       </c>
       <c r="BG214" s="15">
         <v>1.173</v>
       </c>
-      <c r="BH214" s="72">
+      <c r="BH214" s="4">
         <v>2096</v>
       </c>
       <c r="BI214" s="4"/>
@@ -27398,13 +27353,13 @@
       <c r="BE215" s="14">
         <v>1009</v>
       </c>
-      <c r="BF215" s="73">
+      <c r="BF215" s="61">
         <v>60</v>
       </c>
       <c r="BG215" s="15">
         <v>1.173</v>
       </c>
-      <c r="BH215" s="72">
+      <c r="BH215" s="4">
         <v>2096</v>
       </c>
       <c r="BI215" s="4"/>
@@ -27515,13 +27470,13 @@
       <c r="BE216" s="14">
         <v>1009</v>
       </c>
-      <c r="BF216" s="73">
+      <c r="BF216" s="61">
         <v>58</v>
       </c>
       <c r="BG216" s="15">
         <v>1.171</v>
       </c>
-      <c r="BH216" s="72">
+      <c r="BH216" s="4">
         <v>2096</v>
       </c>
       <c r="BI216" s="4"/>
@@ -27632,13 +27587,13 @@
       <c r="BE217" s="14">
         <v>1009</v>
       </c>
-      <c r="BF217" s="73">
+      <c r="BF217" s="61">
         <v>61</v>
       </c>
       <c r="BG217" s="15">
         <v>1.1759999999999999</v>
       </c>
-      <c r="BH217" s="72">
+      <c r="BH217" s="4">
         <v>2096</v>
       </c>
       <c r="BI217" s="4"/>
@@ -27749,13 +27704,13 @@
       <c r="BE218" s="14">
         <v>1009</v>
       </c>
-      <c r="BF218" s="73">
+      <c r="BF218" s="61">
         <v>62</v>
       </c>
       <c r="BG218" s="15">
         <v>1.175</v>
       </c>
-      <c r="BH218" s="72">
+      <c r="BH218" s="4">
         <v>2096</v>
       </c>
       <c r="BI218" s="4"/>
@@ -27780,7 +27735,7 @@
       <c r="D219" s="8">
         <v>3</v>
       </c>
-      <c r="E219" s="71" t="s">
+      <c r="E219" s="2" t="s">
         <v>214</v>
       </c>
       <c r="F219" s="4" t="s">
@@ -27866,13 +27821,13 @@
       <c r="BE219" s="14">
         <v>1009</v>
       </c>
-      <c r="BF219" s="73">
+      <c r="BF219" s="61">
         <v>61</v>
       </c>
       <c r="BG219" s="15">
         <v>1.175</v>
       </c>
-      <c r="BH219" s="72">
+      <c r="BH219" s="4">
         <v>2096</v>
       </c>
       <c r="BI219" s="4"/>
@@ -27983,13 +27938,13 @@
       <c r="BE220" s="14">
         <v>1009</v>
       </c>
-      <c r="BF220" s="73">
+      <c r="BF220" s="61">
         <v>59</v>
       </c>
       <c r="BG220" s="15">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH220" s="72">
+      <c r="BH220" s="4">
         <v>2096</v>
       </c>
       <c r="BI220" s="4"/>
@@ -28014,7 +27969,7 @@
       <c r="D221" s="8">
         <v>5</v>
       </c>
-      <c r="E221" s="71" t="s">
+      <c r="E221" s="2" t="s">
         <v>214</v>
       </c>
       <c r="F221" s="4" t="s">
@@ -28089,7 +28044,7 @@
       <c r="AX221" s="4"/>
       <c r="AY221" s="4"/>
       <c r="AZ221" s="4"/>
-      <c r="BA221" s="82">
+      <c r="BA221" s="22">
         <v>117</v>
       </c>
       <c r="BB221" s="4"/>
@@ -28100,13 +28055,13 @@
       <c r="BE221" s="14">
         <v>1009</v>
       </c>
-      <c r="BF221" s="73">
+      <c r="BF221" s="61">
         <v>60</v>
       </c>
       <c r="BG221" s="15">
         <v>1.173</v>
       </c>
-      <c r="BH221" s="72">
+      <c r="BH221" s="4">
         <v>2096</v>
       </c>
       <c r="BI221" s="4"/>
@@ -28217,13 +28172,13 @@
       <c r="BE222" s="14">
         <v>1009</v>
       </c>
-      <c r="BF222" s="73">
+      <c r="BF222" s="61">
         <v>58</v>
       </c>
       <c r="BG222" s="15">
         <v>1.171</v>
       </c>
-      <c r="BH222" s="72">
+      <c r="BH222" s="4">
         <v>2096</v>
       </c>
       <c r="BI222" s="4"/>
@@ -28334,13 +28289,13 @@
       <c r="BE223" s="14">
         <v>1009</v>
       </c>
-      <c r="BF223" s="73">
+      <c r="BF223" s="61">
         <v>58</v>
       </c>
       <c r="BG223" s="15">
         <v>1.171</v>
       </c>
-      <c r="BH223" s="72">
+      <c r="BH223" s="4">
         <v>2096</v>
       </c>
       <c r="BI223" s="4"/>
@@ -28451,13 +28406,13 @@
       <c r="BE224" s="14">
         <v>1009</v>
       </c>
-      <c r="BF224" s="73">
+      <c r="BF224" s="61">
         <v>58</v>
       </c>
       <c r="BG224" s="15">
         <v>1.171</v>
       </c>
-      <c r="BH224" s="72">
+      <c r="BH224" s="4">
         <v>2096</v>
       </c>
       <c r="BI224" s="4"/>
@@ -28568,13 +28523,13 @@
       <c r="BE225" s="14">
         <v>1009</v>
       </c>
-      <c r="BF225" s="73">
+      <c r="BF225" s="61">
         <v>58</v>
       </c>
       <c r="BG225" s="15">
         <v>1.17</v>
       </c>
-      <c r="BH225" s="72">
+      <c r="BH225" s="4">
         <v>2096</v>
       </c>
       <c r="BI225" s="4"/>
@@ -29140,7 +29095,7 @@
       <c r="AX230" s="2"/>
       <c r="AY230" s="7"/>
       <c r="AZ230" s="4"/>
-      <c r="BA230" s="82">
+      <c r="BA230" s="22">
         <v>111.6</v>
       </c>
       <c r="BB230" s="2"/>
@@ -29157,7 +29112,7 @@
       <c r="BG230" s="44">
         <v>1.163</v>
       </c>
-      <c r="BH230" s="71">
+      <c r="BH230" s="2">
         <v>2096</v>
       </c>
       <c r="BI230" s="2"/>
@@ -29274,7 +29229,7 @@
       <c r="BG231" s="44">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BH231" s="71">
+      <c r="BH231" s="2">
         <v>2096</v>
       </c>
       <c r="BI231" s="2"/>
@@ -29388,7 +29343,7 @@
       <c r="BG232" s="44">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BH232" s="71">
+      <c r="BH232" s="2">
         <v>2096</v>
       </c>
       <c r="BI232" s="2"/>
@@ -30090,7 +30045,7 @@
       <c r="BG238" s="44">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BH238" s="71">
+      <c r="BH238" s="2">
         <v>2096</v>
       </c>
       <c r="BI238" s="2"/>
@@ -30792,7 +30747,7 @@
       <c r="BG244" s="44">
         <v>1.163</v>
       </c>
-      <c r="BH244" s="71">
+      <c r="BH244" s="2">
         <v>2096</v>
       </c>
       <c r="BI244" s="2"/>
@@ -31375,7 +31330,7 @@
       <c r="BG249" s="44">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BH249" s="71">
+      <c r="BH249" s="2">
         <v>2096</v>
       </c>
       <c r="BI249" s="2"/>
@@ -31492,7 +31447,7 @@
       <c r="BG250" s="44">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BH250" s="71">
+      <c r="BH250" s="2">
         <v>2096</v>
       </c>
       <c r="BI250" s="2"/>
@@ -32075,7 +32030,7 @@
       <c r="BG255" s="44">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BH255" s="71">
+      <c r="BH255" s="2">
         <v>2096</v>
       </c>
       <c r="BI255" s="2"/>
@@ -32190,7 +32145,7 @@
       <c r="BG256" s="44">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BH256" s="71">
+      <c r="BH256" s="2">
         <v>2096</v>
       </c>
       <c r="BI256" s="2"/>
@@ -32462,9 +32417,6 @@
         <v>330</v>
       </c>
       <c r="I259" s="7"/>
-      <c r="J259" s="7">
-        <v>0</v>
-      </c>
       <c r="K259" s="50"/>
       <c r="L259" s="7">
         <v>0.16800000000000001</v>
@@ -32764,7 +32716,7 @@
       <c r="BG261" s="44">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BH261" s="71">
+      <c r="BH261" s="2">
         <v>2096</v>
       </c>
       <c r="BI261" s="2"/>
@@ -32881,7 +32833,7 @@
       <c r="BG262" s="44">
         <v>1.171</v>
       </c>
-      <c r="BH262" s="71">
+      <c r="BH262" s="2">
         <v>2096</v>
       </c>
       <c r="BI262" s="2"/>
@@ -32998,7 +32950,7 @@
       <c r="BG263" s="44">
         <v>1.17</v>
       </c>
-      <c r="BH263" s="71">
+      <c r="BH263" s="2">
         <v>2096</v>
       </c>
       <c r="BI263" s="2"/>
@@ -33023,7 +32975,7 @@
       <c r="D264" s="8">
         <v>3</v>
       </c>
-      <c r="E264" s="71" t="s">
+      <c r="E264" s="2" t="s">
         <v>550</v>
       </c>
       <c r="F264" s="4" t="s">
@@ -33115,7 +33067,7 @@
       <c r="BG264" s="44">
         <v>1.167</v>
       </c>
-      <c r="BH264" s="71">
+      <c r="BH264" s="2">
         <v>2096</v>
       </c>
       <c r="BI264" s="2"/>
@@ -33460,7 +33412,7 @@
       <c r="BG267" s="44">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BH267" s="71">
+      <c r="BH267" s="2">
         <v>2096</v>
       </c>
       <c r="BI267" s="2"/>
@@ -34162,7 +34114,7 @@
       <c r="BG273" s="44">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BH273" s="74">
+      <c r="BH273" s="57">
         <v>2096</v>
       </c>
       <c r="BI273" s="2"/>
@@ -34978,7 +34930,7 @@
       <c r="BG280" s="44">
         <v>1.1639999999999999</v>
       </c>
-      <c r="BH280" s="71">
+      <c r="BH280" s="2">
         <v>2096</v>
       </c>
       <c r="BI280" s="2"/>
@@ -35095,7 +35047,7 @@
       <c r="BG281" s="44">
         <v>1.1619999999999999</v>
       </c>
-      <c r="BH281" s="71">
+      <c r="BH281" s="2">
         <v>2096</v>
       </c>
       <c r="BI281" s="2"/>
@@ -35480,9 +35432,6 @@
         <v>330</v>
       </c>
       <c r="I285" s="7"/>
-      <c r="J285" s="7">
-        <v>0</v>
-      </c>
       <c r="K285" s="50"/>
       <c r="L285" s="7"/>
       <c r="M285" s="7">
@@ -35587,9 +35536,6 @@
         <v>330</v>
       </c>
       <c r="I286" s="7"/>
-      <c r="J286" s="7">
-        <v>0</v>
-      </c>
       <c r="K286" s="50"/>
       <c r="L286" s="7"/>
       <c r="M286" s="7">
@@ -35694,9 +35640,6 @@
         <v>330</v>
       </c>
       <c r="I287" s="7"/>
-      <c r="J287" s="7">
-        <v>0</v>
-      </c>
       <c r="K287" s="50"/>
       <c r="L287" s="7"/>
       <c r="M287" s="7">
@@ -35801,9 +35744,6 @@
         <v>330</v>
       </c>
       <c r="I288" s="7"/>
-      <c r="J288" s="7">
-        <v>0</v>
-      </c>
       <c r="K288" s="50"/>
       <c r="L288" s="7"/>
       <c r="M288" s="7">
@@ -35868,7 +35808,7 @@
       <c r="BG288" s="44">
         <v>1.1659999999999999</v>
       </c>
-      <c r="BH288" s="71">
+      <c r="BH288" s="2">
         <v>2096</v>
       </c>
       <c r="BI288" s="2" t="s">
@@ -36455,7 +36395,7 @@
       <c r="BG293" s="44">
         <v>1.1719999999999999</v>
       </c>
-      <c r="BH293" s="71">
+      <c r="BH293" s="2">
         <v>2096</v>
       </c>
       <c r="BI293" s="2"/>
@@ -36572,7 +36512,7 @@
       <c r="BG294" s="44">
         <v>1.1719999999999999</v>
       </c>
-      <c r="BH294" s="71">
+      <c r="BH294" s="2">
         <v>2096</v>
       </c>
       <c r="BI294" s="2"/>
@@ -37097,7 +37037,7 @@
       <c r="BE299" s="42"/>
       <c r="BF299" s="43"/>
       <c r="BG299" s="44"/>
-      <c r="BH299" s="71"/>
+      <c r="BH299" s="2"/>
       <c r="BI299" s="2"/>
       <c r="BJ299" s="3" t="s">
         <v>387</v>
@@ -37202,7 +37142,7 @@
       <c r="BE300" s="42"/>
       <c r="BF300" s="43"/>
       <c r="BG300" s="44"/>
-      <c r="BH300" s="71"/>
+      <c r="BH300" s="2"/>
       <c r="BI300" s="2"/>
       <c r="BJ300" s="3" t="s">
         <v>388</v>
@@ -37307,7 +37247,7 @@
       <c r="BE301" s="42"/>
       <c r="BF301" s="43"/>
       <c r="BG301" s="44"/>
-      <c r="BH301" s="71"/>
+      <c r="BH301" s="2"/>
       <c r="BI301" s="2"/>
       <c r="BJ301" s="3" t="s">
         <v>389</v>
@@ -37422,7 +37362,7 @@
       <c r="BG302" s="44">
         <v>1.1739999999999999</v>
       </c>
-      <c r="BH302" s="71">
+      <c r="BH302" s="2">
         <v>2096</v>
       </c>
       <c r="BI302" s="2"/>
@@ -37540,7 +37480,7 @@
       <c r="BG303" s="44">
         <v>1.173</v>
       </c>
-      <c r="BH303" s="71">
+      <c r="BH303" s="2">
         <v>2096</v>
       </c>
       <c r="BI303" s="2"/>
@@ -37658,7 +37598,7 @@
       <c r="BG304" s="44">
         <v>1.173</v>
       </c>
-      <c r="BH304" s="71">
+      <c r="BH304" s="2">
         <v>2096</v>
       </c>
       <c r="BI304" s="2"/>
@@ -38012,7 +37952,7 @@
       <c r="BG307" s="44">
         <v>1.1719999999999999</v>
       </c>
-      <c r="BH307" s="71">
+      <c r="BH307" s="2">
         <v>2096</v>
       </c>
       <c r="BI307" s="2"/>
@@ -38347,7 +38287,7 @@
       <c r="AX310" s="2"/>
       <c r="AY310" s="7"/>
       <c r="AZ310" s="4"/>
-      <c r="BA310" s="72">
+      <c r="BA310" s="4">
         <v>108</v>
       </c>
       <c r="BB310" s="2"/>
@@ -38362,7 +38302,7 @@
         <v>53.6</v>
       </c>
       <c r="BG310" s="44"/>
-      <c r="BH310" s="71">
+      <c r="BH310" s="2">
         <v>2096</v>
       </c>
       <c r="BI310" s="2"/>
@@ -39000,7 +38940,7 @@
       <c r="BG316" s="44">
         <v>1.173</v>
       </c>
-      <c r="BH316" s="71">
+      <c r="BH316" s="2">
         <v>2096</v>
       </c>
       <c r="BI316" s="2"/>
@@ -39446,7 +39386,7 @@
       <c r="BG320" s="44">
         <v>1.171</v>
       </c>
-      <c r="BH320" s="71">
+      <c r="BH320" s="2">
         <v>2096</v>
       </c>
       <c r="BI320" s="2"/>
@@ -39790,7 +39730,7 @@
         <v>48.4</v>
       </c>
       <c r="BG323" s="44"/>
-      <c r="BH323" s="74">
+      <c r="BH323" s="57">
         <v>2096</v>
       </c>
       <c r="BI323" s="2"/>
@@ -40128,7 +40068,7 @@
       <c r="BE326" s="42"/>
       <c r="BF326" s="43"/>
       <c r="BG326" s="44"/>
-      <c r="BH326" s="74">
+      <c r="BH326" s="57">
         <v>2096</v>
       </c>
       <c r="BI326" s="2"/>
@@ -41087,7 +41027,7 @@
       <c r="AX335" s="2"/>
       <c r="AY335" s="7"/>
       <c r="AZ335" s="4"/>
-      <c r="BA335" s="72">
+      <c r="BA335" s="4">
         <v>111.6</v>
       </c>
       <c r="BB335" s="2"/>
@@ -41891,7 +41831,7 @@
       <c r="AX342" s="2"/>
       <c r="AY342" s="7"/>
       <c r="AZ342" s="4"/>
-      <c r="BA342" s="72">
+      <c r="BA342" s="4">
         <v>111.6</v>
       </c>
       <c r="BB342" s="2"/>
@@ -43231,9 +43171,7 @@
         <v>571</v>
       </c>
       <c r="I354" s="48"/>
-      <c r="J354" s="48">
-        <v>0</v>
-      </c>
+      <c r="J354" s="48"/>
       <c r="K354" s="51"/>
       <c r="L354" s="7"/>
       <c r="M354" s="7">
@@ -43748,7 +43686,7 @@
         <v>85.2</v>
       </c>
       <c r="AZ358" s="4"/>
-      <c r="BA358" s="72">
+      <c r="BA358" s="4">
         <v>109.7</v>
       </c>
       <c r="BB358" s="2"/>
@@ -43980,7 +43918,7 @@
         <v>85</v>
       </c>
       <c r="AZ360" s="4"/>
-      <c r="BA360" s="72">
+      <c r="BA360" s="4">
         <v>109.7</v>
       </c>
       <c r="BB360" s="2"/>
@@ -44096,7 +44034,7 @@
         <v>85</v>
       </c>
       <c r="AZ361" s="4"/>
-      <c r="BA361" s="72">
+      <c r="BA361" s="4">
         <v>109.7</v>
       </c>
       <c r="BB361" s="2"/>
@@ -44212,7 +44150,7 @@
         <v>84.9</v>
       </c>
       <c r="AZ362" s="4"/>
-      <c r="BA362" s="72">
+      <c r="BA362" s="4">
         <v>109.7</v>
       </c>
       <c r="BB362" s="2"/>
@@ -44444,7 +44382,7 @@
         <v>84.4</v>
       </c>
       <c r="AZ364" s="4"/>
-      <c r="BA364" s="72">
+      <c r="BA364" s="4">
         <v>109.7</v>
       </c>
       <c r="BB364" s="2"/>
@@ -48826,7 +48764,7 @@
       <c r="AX403" s="2"/>
       <c r="AY403" s="7"/>
       <c r="AZ403" s="4"/>
-      <c r="BA403" s="72">
+      <c r="BA403" s="4">
         <v>113.4</v>
       </c>
       <c r="BB403" s="2"/>
@@ -49552,7 +49490,7 @@
       <c r="D410" s="8">
         <v>6</v>
       </c>
-      <c r="E410" s="71" t="s">
+      <c r="E410" s="2" t="s">
         <v>214</v>
       </c>
       <c r="F410" s="4" t="s">
@@ -49976,14 +49914,14 @@
       <c r="BD413" s="10">
         <v>24.1</v>
       </c>
-      <c r="BE413" s="75">
+      <c r="BE413" s="71">
         <v>1012</v>
       </c>
-      <c r="BF413" s="76">
+      <c r="BF413" s="72">
         <v>50.2</v>
       </c>
-      <c r="BG413" s="77"/>
-      <c r="BH413" s="75">
+      <c r="BG413" s="73"/>
+      <c r="BH413" s="71">
         <v>2096</v>
       </c>
       <c r="BI413" s="2" t="s">
@@ -50098,7 +50036,7 @@
         <v>58.9</v>
       </c>
       <c r="BG414" s="44"/>
-      <c r="BH414" s="75">
+      <c r="BH414" s="71">
         <v>2096</v>
       </c>
       <c r="BI414" s="2" t="s">
@@ -50213,7 +50151,7 @@
         <v>58.9</v>
       </c>
       <c r="BG415" s="44"/>
-      <c r="BH415" s="75">
+      <c r="BH415" s="71">
         <v>2096</v>
       </c>
       <c r="BI415" s="2" t="s">
@@ -50328,7 +50266,7 @@
         <v>51.7</v>
       </c>
       <c r="BG416" s="44"/>
-      <c r="BH416" s="75">
+      <c r="BH416" s="71">
         <v>2096</v>
       </c>
       <c r="BI416" s="2" t="s">
@@ -50441,7 +50379,7 @@
         <v>51.7</v>
       </c>
       <c r="BG417" s="44"/>
-      <c r="BH417" s="75">
+      <c r="BH417" s="71">
         <v>2096</v>
       </c>
       <c r="BI417" s="2" t="s">
@@ -50556,7 +50494,7 @@
         <v>50.9</v>
       </c>
       <c r="BG418" s="44"/>
-      <c r="BH418" s="75">
+      <c r="BH418" s="71">
         <v>2096</v>
       </c>
       <c r="BI418" s="2" t="s">
@@ -50671,7 +50609,7 @@
         <v>50.2</v>
       </c>
       <c r="BG419" s="44"/>
-      <c r="BH419" s="75">
+      <c r="BH419" s="71">
         <v>2096</v>
       </c>
       <c r="BI419" s="2" t="s">
@@ -50786,7 +50724,7 @@
         <v>58.9</v>
       </c>
       <c r="BG420" s="44"/>
-      <c r="BH420" s="75">
+      <c r="BH420" s="71">
         <v>2096</v>
       </c>
       <c r="BI420" s="2" t="s">
@@ -50813,7 +50751,7 @@
       <c r="D421" s="8">
         <v>5</v>
       </c>
-      <c r="E421" s="71" t="s">
+      <c r="E421" s="2" t="s">
         <v>549</v>
       </c>
       <c r="F421" s="4" t="s">
@@ -50901,7 +50839,7 @@
         <v>58.9</v>
       </c>
       <c r="BG421" s="44"/>
-      <c r="BH421" s="75">
+      <c r="BH421" s="71">
         <v>2096</v>
       </c>
       <c r="BI421" s="2" t="s">
@@ -50950,7 +50888,7 @@
         <v>2.7000000000000001E-3</v>
       </c>
       <c r="L422" s="7"/>
-      <c r="M422" s="85">
+      <c r="M422" s="74">
         <v>0.17130000000000001</v>
       </c>
       <c r="N422" s="7">
@@ -50997,7 +50935,7 @@
       <c r="BE422" s="65"/>
       <c r="BF422" s="66"/>
       <c r="BG422" s="67"/>
-      <c r="BH422" s="71"/>
+      <c r="BH422" s="2"/>
       <c r="BI422" s="2"/>
       <c r="BJ422" s="3" t="s">
         <v>614</v>
@@ -51038,7 +50976,7 @@
         <v>1.5E-3</v>
       </c>
       <c r="L423" s="7"/>
-      <c r="M423" s="85">
+      <c r="M423" s="74">
         <v>0.17050000000000001</v>
       </c>
       <c r="N423" s="7">
@@ -51085,7 +51023,7 @@
       <c r="BE423" s="65"/>
       <c r="BF423" s="66"/>
       <c r="BG423" s="67"/>
-      <c r="BH423" s="71"/>
+      <c r="BH423" s="2"/>
       <c r="BI423" s="2"/>
       <c r="BJ423" s="38" t="s">
         <v>605</v>
@@ -51126,7 +51064,7 @@
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="L424" s="7"/>
-      <c r="M424" s="85">
+      <c r="M424" s="74">
         <v>0.16919999999999999</v>
       </c>
       <c r="N424" s="7">
@@ -51173,7 +51111,7 @@
       <c r="BE424" s="65"/>
       <c r="BF424" s="66"/>
       <c r="BG424" s="67"/>
-      <c r="BH424" s="71"/>
+      <c r="BH424" s="2"/>
       <c r="BI424" s="2"/>
       <c r="BJ424" s="3" t="s">
         <v>606</v>
@@ -51214,7 +51152,7 @@
         <v>2.3999999999999998E-3</v>
       </c>
       <c r="L425" s="7"/>
-      <c r="M425" s="85">
+      <c r="M425" s="74">
         <v>0.1671</v>
       </c>
       <c r="N425" s="7">
@@ -51261,7 +51199,7 @@
       <c r="BE425" s="65"/>
       <c r="BF425" s="66"/>
       <c r="BG425" s="67"/>
-      <c r="BH425" s="71"/>
+      <c r="BH425" s="2"/>
       <c r="BI425" s="2"/>
       <c r="BJ425" s="3" t="s">
         <v>607</v>
@@ -51302,7 +51240,7 @@
         <v>2.0999999999999999E-3</v>
       </c>
       <c r="L426" s="7"/>
-      <c r="M426" s="85">
+      <c r="M426" s="74">
         <v>0.16889999999999999</v>
       </c>
       <c r="N426" s="7">
@@ -51349,7 +51287,7 @@
       <c r="BE426" s="65"/>
       <c r="BF426" s="66"/>
       <c r="BG426" s="67"/>
-      <c r="BH426" s="71"/>
+      <c r="BH426" s="2"/>
       <c r="BI426" s="2"/>
       <c r="BJ426" s="3" t="s">
         <v>608</v>
@@ -51389,10 +51327,10 @@
       <c r="K427" s="50">
         <v>3.8E-3</v>
       </c>
-      <c r="L427" s="85">
+      <c r="L427" s="74">
         <v>0.191</v>
       </c>
-      <c r="M427" s="85">
+      <c r="M427" s="74">
         <v>0.19320000000000001</v>
       </c>
       <c r="N427" s="7">
@@ -51439,7 +51377,7 @@
       <c r="BE427" s="65"/>
       <c r="BF427" s="66"/>
       <c r="BG427" s="67"/>
-      <c r="BH427" s="71"/>
+      <c r="BH427" s="2"/>
       <c r="BI427" s="2"/>
       <c r="BJ427" s="3" t="s">
         <v>604</v>
@@ -51479,10 +51417,10 @@
       <c r="K428" s="50">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="L428" s="85">
+      <c r="L428" s="74">
         <v>0.17849999999999999</v>
       </c>
-      <c r="M428" s="85">
+      <c r="M428" s="74">
         <v>0.19009999999999999</v>
       </c>
       <c r="N428" s="7">
@@ -51529,7 +51467,7 @@
       <c r="BE428" s="65"/>
       <c r="BF428" s="66"/>
       <c r="BG428" s="67"/>
-      <c r="BH428" s="71"/>
+      <c r="BH428" s="2"/>
       <c r="BI428" s="2"/>
       <c r="BJ428" s="3" t="s">
         <v>609</v>
@@ -51569,10 +51507,10 @@
       <c r="K429" s="50">
         <v>2.3E-3</v>
       </c>
-      <c r="L429" s="85">
+      <c r="L429" s="74">
         <v>0.17299999999999999</v>
       </c>
-      <c r="M429" s="85">
+      <c r="M429" s="74">
         <v>0.18870000000000001</v>
       </c>
       <c r="N429" s="7">
@@ -51619,7 +51557,7 @@
       <c r="BE429" s="65"/>
       <c r="BF429" s="66"/>
       <c r="BG429" s="67"/>
-      <c r="BH429" s="71"/>
+      <c r="BH429" s="2"/>
       <c r="BI429" s="2"/>
       <c r="BJ429" s="3" t="s">
         <v>610</v>
@@ -51659,10 +51597,10 @@
       <c r="K430" s="50">
         <v>1.8E-3</v>
       </c>
-      <c r="L430" s="85">
+      <c r="L430" s="74">
         <v>0.1875</v>
       </c>
-      <c r="M430" s="85">
+      <c r="M430" s="74">
         <v>0.19109999999999999</v>
       </c>
       <c r="N430" s="7">
@@ -51709,7 +51647,7 @@
       <c r="BE430" s="65"/>
       <c r="BF430" s="66"/>
       <c r="BG430" s="67"/>
-      <c r="BH430" s="71"/>
+      <c r="BH430" s="2"/>
       <c r="BI430" s="2"/>
       <c r="BJ430" s="3" t="s">
         <v>611</v>
@@ -51749,10 +51687,10 @@
       <c r="K431" s="50">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="L431" s="85">
+      <c r="L431" s="74">
         <v>0.18149999999999999</v>
       </c>
-      <c r="M431" s="85">
+      <c r="M431" s="74">
         <v>0.18870000000000001</v>
       </c>
       <c r="N431" s="7">
@@ -51799,7 +51737,7 @@
       <c r="BE431" s="65"/>
       <c r="BF431" s="66"/>
       <c r="BG431" s="67"/>
-      <c r="BH431" s="71"/>
+      <c r="BH431" s="2"/>
       <c r="BI431" s="2"/>
       <c r="BJ431" s="3" t="s">
         <v>612</v>
@@ -51839,10 +51777,10 @@
       <c r="K432" s="50">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="L432" s="85">
+      <c r="L432" s="74">
         <v>0.17199999999999999</v>
       </c>
-      <c r="M432" s="85">
+      <c r="M432" s="74">
         <v>0.18629999999999999</v>
       </c>
       <c r="N432" s="7">
@@ -51889,7 +51827,7 @@
       <c r="BE432" s="65"/>
       <c r="BF432" s="66"/>
       <c r="BG432" s="67"/>
-      <c r="BH432" s="71"/>
+      <c r="BH432" s="2"/>
       <c r="BI432" s="2"/>
       <c r="BJ432" s="3" t="s">
         <v>613</v>
@@ -51929,10 +51867,10 @@
       <c r="K433" s="50">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="L433" s="85">
+      <c r="L433" s="74">
         <v>0.161</v>
       </c>
-      <c r="M433" s="85">
+      <c r="M433" s="74">
         <v>0.15440000000000001</v>
       </c>
       <c r="N433" s="7">
@@ -51979,7 +51917,7 @@
       <c r="BE433" s="65"/>
       <c r="BF433" s="66"/>
       <c r="BG433" s="67"/>
-      <c r="BH433" s="71"/>
+      <c r="BH433" s="2"/>
       <c r="BI433" s="2"/>
       <c r="BJ433" s="3" t="s">
         <v>621</v>
@@ -52019,10 +51957,10 @@
       <c r="K434" s="50">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="L434" s="85">
+      <c r="L434" s="74">
         <v>0.1585</v>
       </c>
-      <c r="M434" s="85">
+      <c r="M434" s="74">
         <v>0.1492</v>
       </c>
       <c r="N434" s="7">
@@ -52069,7 +52007,7 @@
       <c r="BE434" s="65"/>
       <c r="BF434" s="66"/>
       <c r="BG434" s="67"/>
-      <c r="BH434" s="71"/>
+      <c r="BH434" s="2"/>
       <c r="BI434" s="2"/>
       <c r="BJ434" s="3" t="s">
         <v>622</v>
@@ -52109,10 +52047,10 @@
       <c r="K435" s="50">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="L435" s="85">
+      <c r="L435" s="74">
         <v>0.153</v>
       </c>
-      <c r="M435" s="85">
+      <c r="M435" s="74">
         <v>0.1497</v>
       </c>
       <c r="N435" s="7">
@@ -52159,7 +52097,7 @@
       <c r="BE435" s="65"/>
       <c r="BF435" s="66"/>
       <c r="BG435" s="67"/>
-      <c r="BH435" s="71"/>
+      <c r="BH435" s="2"/>
       <c r="BI435" s="2"/>
       <c r="BJ435" s="3" t="s">
         <v>623</v>
@@ -52193,10 +52131,10 @@
       <c r="I436" s="48"/>
       <c r="J436" s="48"/>
       <c r="K436" s="51"/>
-      <c r="L436" s="85">
+      <c r="L436" s="74">
         <v>0.1575</v>
       </c>
-      <c r="M436" s="85">
+      <c r="M436" s="74">
         <v>0.1507</v>
       </c>
       <c r="N436" s="48"/>
@@ -52241,7 +52179,7 @@
       <c r="BE436" s="65"/>
       <c r="BF436" s="66"/>
       <c r="BG436" s="67"/>
-      <c r="BH436" s="71"/>
+      <c r="BH436" s="2"/>
       <c r="BI436" s="2"/>
       <c r="BJ436" s="3" t="s">
         <v>624</v>
@@ -52260,7 +52198,7 @@
       <c r="D437" s="8">
         <v>5</v>
       </c>
-      <c r="E437" s="71" t="s">
+      <c r="E437" s="2" t="s">
         <v>214</v>
       </c>
       <c r="F437" s="4" t="s">
@@ -52281,10 +52219,10 @@
       <c r="K437" s="50">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="L437" s="85">
+      <c r="L437" s="74">
         <v>0.1565</v>
       </c>
-      <c r="M437" s="85">
+      <c r="M437" s="74">
         <v>0.15029999999999999</v>
       </c>
       <c r="N437" s="7">
@@ -52331,7 +52269,7 @@
       <c r="BE437" s="65"/>
       <c r="BF437" s="66"/>
       <c r="BG437" s="67"/>
-      <c r="BH437" s="71"/>
+      <c r="BH437" s="2"/>
       <c r="BI437" s="2"/>
       <c r="BJ437" s="3" t="s">
         <v>625</v>
@@ -52371,10 +52309,10 @@
       <c r="K438" s="50">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="L438" s="85">
+      <c r="L438" s="74">
         <v>0.155</v>
       </c>
-      <c r="M438" s="85">
+      <c r="M438" s="74">
         <v>0.15029999999999999</v>
       </c>
       <c r="N438" s="7">
@@ -52421,7 +52359,7 @@
       <c r="BE438" s="65"/>
       <c r="BF438" s="66"/>
       <c r="BG438" s="67"/>
-      <c r="BH438" s="71"/>
+      <c r="BH438" s="2"/>
       <c r="BI438" s="2"/>
       <c r="BJ438" s="3" t="s">
         <v>626</v>
@@ -52461,10 +52399,10 @@
       <c r="K439" s="50">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="L439" s="85">
+      <c r="L439" s="74">
         <v>0.1525</v>
       </c>
-      <c r="M439" s="85">
+      <c r="M439" s="74">
         <v>0.152</v>
       </c>
       <c r="N439" s="7">
@@ -52511,7 +52449,7 @@
       <c r="BE439" s="65"/>
       <c r="BF439" s="66"/>
       <c r="BG439" s="67"/>
-      <c r="BH439" s="71"/>
+      <c r="BH439" s="2"/>
       <c r="BI439" s="2"/>
       <c r="BJ439" s="3" t="s">
         <v>627</v>
@@ -52551,10 +52489,10 @@
       <c r="K440" s="50">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="L440" s="85">
+      <c r="L440" s="74">
         <v>0.1595</v>
       </c>
-      <c r="M440" s="85">
+      <c r="M440" s="74">
         <v>0.15140000000000001</v>
       </c>
       <c r="N440" s="7">
@@ -52601,7 +52539,7 @@
       <c r="BE440" s="65"/>
       <c r="BF440" s="66"/>
       <c r="BG440" s="67"/>
-      <c r="BH440" s="71"/>
+      <c r="BH440" s="2"/>
       <c r="BI440" s="2"/>
       <c r="BJ440" s="3" t="s">
         <v>628</v>
@@ -52620,7 +52558,7 @@
       <c r="D441" s="8">
         <v>1</v>
       </c>
-      <c r="E441" s="71" t="s">
+      <c r="E441" s="2" t="s">
         <v>549</v>
       </c>
       <c r="F441" s="4" t="s">
@@ -52642,7 +52580,7 @@
         <v>4.1000000000000003E-3</v>
       </c>
       <c r="L441" s="7"/>
-      <c r="M441" s="85">
+      <c r="M441" s="74">
         <v>0.1661</v>
       </c>
       <c r="N441" s="7">
@@ -52689,7 +52627,7 @@
       <c r="BE441" s="65"/>
       <c r="BF441" s="66"/>
       <c r="BG441" s="67"/>
-      <c r="BH441" s="71"/>
+      <c r="BH441" s="2"/>
       <c r="BI441" s="2"/>
       <c r="BJ441" s="3" t="s">
         <v>629</v>
@@ -52730,7 +52668,7 @@
         <v>2.5999999999999999E-3</v>
       </c>
       <c r="L442" s="7"/>
-      <c r="M442" s="85">
+      <c r="M442" s="74">
         <v>0.1661</v>
       </c>
       <c r="N442" s="7">
@@ -52777,7 +52715,7 @@
       <c r="BE442" s="65"/>
       <c r="BF442" s="66"/>
       <c r="BG442" s="67"/>
-      <c r="BH442" s="71"/>
+      <c r="BH442" s="2"/>
       <c r="BI442" s="2"/>
       <c r="BJ442" s="3" t="s">
         <v>615</v>
@@ -52818,7 +52756,7 @@
         <v>3.7000000000000002E-3</v>
       </c>
       <c r="L443" s="7"/>
-      <c r="M443" s="85">
+      <c r="M443" s="74">
         <v>0.16539999999999999</v>
       </c>
       <c r="N443" s="7">
@@ -52865,7 +52803,7 @@
       <c r="BE443" s="65"/>
       <c r="BF443" s="66"/>
       <c r="BG443" s="67"/>
-      <c r="BH443" s="71"/>
+      <c r="BH443" s="2"/>
       <c r="BI443" s="2"/>
       <c r="BJ443" s="3" t="s">
         <v>616</v>
@@ -52906,7 +52844,7 @@
         <v>4.4999999999999997E-3</v>
       </c>
       <c r="L444" s="7"/>
-      <c r="M444" s="85">
+      <c r="M444" s="74">
         <v>0.16489999999999999</v>
       </c>
       <c r="N444" s="7">
@@ -52953,7 +52891,7 @@
       <c r="BE444" s="65"/>
       <c r="BF444" s="66"/>
       <c r="BG444" s="67"/>
-      <c r="BH444" s="71"/>
+      <c r="BH444" s="2"/>
       <c r="BI444" s="2"/>
       <c r="BJ444" s="3" t="s">
         <v>617</v>
@@ -52994,7 +52932,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="L445" s="7"/>
-      <c r="M445" s="85">
+      <c r="M445" s="74">
         <v>0.16739999999999999</v>
       </c>
       <c r="N445" s="7">
@@ -53041,7 +52979,7 @@
       <c r="BE445" s="65"/>
       <c r="BF445" s="66"/>
       <c r="BG445" s="67"/>
-      <c r="BH445" s="71"/>
+      <c r="BH445" s="2"/>
       <c r="BI445" s="2"/>
       <c r="BJ445" s="3" t="s">
         <v>618</v>
@@ -53082,7 +53020,7 @@
         <v>2.5999999999999999E-3</v>
       </c>
       <c r="L446" s="7"/>
-      <c r="M446" s="85">
+      <c r="M446" s="74">
         <v>0.16350000000000001</v>
       </c>
       <c r="N446" s="7">
@@ -53129,7 +53067,7 @@
       <c r="BE446" s="65"/>
       <c r="BF446" s="66"/>
       <c r="BG446" s="67"/>
-      <c r="BH446" s="71"/>
+      <c r="BH446" s="2"/>
       <c r="BI446" s="2"/>
       <c r="BJ446" s="3" t="s">
         <v>619</v>
@@ -53170,7 +53108,7 @@
         <v>1.9E-3</v>
       </c>
       <c r="L447" s="7"/>
-      <c r="M447" s="85">
+      <c r="M447" s="74">
         <v>0.1744</v>
       </c>
       <c r="N447" s="7">
@@ -53217,7 +53155,7 @@
       <c r="BE447" s="68"/>
       <c r="BF447" s="69"/>
       <c r="BG447" s="70"/>
-      <c r="BH447" s="71"/>
+      <c r="BH447" s="2"/>
       <c r="BI447" s="2"/>
       <c r="BJ447" s="3" t="s">
         <v>620</v>
@@ -53488,6 +53426,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
@@ -53495,15 +53442,6 @@
     <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -53526,6 +53464,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -53540,12 +53486,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD847507-D332-435F-84E8-DC4DF16E4DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DC6A4D-E49D-451D-9CF8-2DE8A1DD66D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3575" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3737" uniqueCount="649">
   <si>
     <t>Squad</t>
   </si>
@@ -1800,9 +1800,6 @@
   </si>
   <si>
     <t>CdA - GM</t>
-  </si>
-  <si>
-    <t>LeCol</t>
   </si>
   <si>
     <t>https://youtu.be/HG2AuxOdWXI</t>
@@ -1941,6 +1938,66 @@
   <si>
     <t>https://youtu.be/1irR39Fm_1Y</t>
   </si>
+  <si>
+    <t>Sprint</t>
+  </si>
+  <si>
+    <t>Sam Dakin</t>
+  </si>
+  <si>
+    <t>Rebecca Petch</t>
+  </si>
+  <si>
+    <t>Olivia King</t>
+  </si>
+  <si>
+    <t>Shaane Fulton</t>
+  </si>
+  <si>
+    <t>No undershirt</t>
+  </si>
+  <si>
+    <t>Undershirt</t>
+  </si>
+  <si>
+    <t>Pos-G-FW</t>
+  </si>
+  <si>
+    <t>Pos-H-FW</t>
+  </si>
+  <si>
+    <t>Pos-I-FW</t>
+  </si>
+  <si>
+    <t>Pos-J-FW</t>
+  </si>
+  <si>
+    <t>Pos-A-FW</t>
+  </si>
+  <si>
+    <t>ImpSport</t>
+  </si>
+  <si>
+    <t>A1/P11</t>
+  </si>
+  <si>
+    <t>Narrow ImpSport</t>
+  </si>
+  <si>
+    <t>A1/P12</t>
+  </si>
+  <si>
+    <t>Wide ImpSport</t>
+  </si>
+  <si>
+    <t>A1/P13</t>
+  </si>
+  <si>
+    <t>A1/P14</t>
+  </si>
+  <si>
+    <t>A1/P15</t>
+  </si>
 </sst>
 </file>
 
@@ -1949,7 +2006,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2051,8 +2108,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2093,6 +2156,12 @@
       <patternFill patternType="solid">
         <fgColor theme="1"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -2156,7 +2225,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2375,6 +2444,99 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2781,8 +2943,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Track_TT23" displayName="Track_TT23" ref="A1:BJ447" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
-  <autoFilter ref="A1:BJ447" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Track_TT23" displayName="Track_TT23" ref="A1:BJ477" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+  <autoFilter ref="A1:BJ477" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BJ447">
     <sortCondition ref="C1:C447"/>
   </sortState>
@@ -3117,7 +3279,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:BR447"/>
+  <dimension ref="A1:BR477"/>
   <sheetFormatPr defaultColWidth="23.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7.46484375" style="1" customWidth="1"/>
@@ -3171,7 +3333,7 @@
         <v>50</v>
       </c>
       <c r="J1" s="47" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="K1" s="47" t="s">
         <v>209</v>
@@ -3183,7 +3345,7 @@
         <v>586</v>
       </c>
       <c r="N1" s="47" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="O1" s="26" t="s">
         <v>497</v>
@@ -33441,7 +33603,7 @@
         <v>381</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>587</v>
+        <v>15</v>
       </c>
       <c r="G268" s="4" t="s">
         <v>577</v>
@@ -33534,7 +33696,7 @@
       </c>
       <c r="BI268" s="2"/>
       <c r="BJ268" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="BK268"/>
       <c r="BL268"/>
@@ -33651,7 +33813,7 @@
       </c>
       <c r="BI269" s="2"/>
       <c r="BJ269" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="BK269"/>
       <c r="BL269"/>
@@ -33768,7 +33930,7 @@
       </c>
       <c r="BI270" s="2"/>
       <c r="BJ270" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="BK270"/>
       <c r="BL270"/>
@@ -33885,7 +34047,7 @@
       </c>
       <c r="BI271" s="2"/>
       <c r="BJ271" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="BK271"/>
       <c r="BL271"/>
@@ -33909,7 +34071,7 @@
         <v>381</v>
       </c>
       <c r="F272" s="4" t="s">
-        <v>587</v>
+        <v>15</v>
       </c>
       <c r="G272" s="4" t="s">
         <v>577</v>
@@ -34002,7 +34164,7 @@
       </c>
       <c r="BI272" s="2"/>
       <c r="BJ272" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="BK272"/>
       <c r="BL272"/>
@@ -34119,7 +34281,7 @@
       </c>
       <c r="BI273" s="2"/>
       <c r="BJ273" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="BK273"/>
       <c r="BL273"/>
@@ -34236,7 +34398,7 @@
       </c>
       <c r="BI274" s="2"/>
       <c r="BJ274" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="BK274"/>
       <c r="BL274"/>
@@ -34353,7 +34515,7 @@
       </c>
       <c r="BI275" s="2"/>
       <c r="BJ275" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="BK275"/>
       <c r="BL275"/>
@@ -50938,7 +51100,7 @@
       <c r="BH422" s="2"/>
       <c r="BI422" s="2"/>
       <c r="BJ422" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="423" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -50961,7 +51123,7 @@
         <v>564</v>
       </c>
       <c r="G423" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H423" s="4" t="s">
         <v>378</v>
@@ -51026,7 +51188,7 @@
       <c r="BH423" s="2"/>
       <c r="BI423" s="2"/>
       <c r="BJ423" s="38" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="424" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51114,7 +51276,7 @@
       <c r="BH424" s="2"/>
       <c r="BI424" s="2"/>
       <c r="BJ424" s="3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="425" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51137,7 +51299,7 @@
         <v>564</v>
       </c>
       <c r="G425" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H425" s="4" t="s">
         <v>378</v>
@@ -51202,7 +51364,7 @@
       <c r="BH425" s="2"/>
       <c r="BI425" s="2"/>
       <c r="BJ425" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="426" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51225,7 +51387,7 @@
         <v>564</v>
       </c>
       <c r="G426" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H426" s="4" t="s">
         <v>378</v>
@@ -51290,7 +51452,7 @@
       <c r="BH426" s="2"/>
       <c r="BI426" s="2"/>
       <c r="BJ426" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="427" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51307,7 +51469,7 @@
         <v>1</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F427" s="4" t="s">
         <v>354</v>
@@ -51380,7 +51542,7 @@
       <c r="BH427" s="2"/>
       <c r="BI427" s="2"/>
       <c r="BJ427" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="428" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51470,7 +51632,7 @@
       <c r="BH428" s="2"/>
       <c r="BI428" s="2"/>
       <c r="BJ428" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="429" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51487,7 +51649,7 @@
         <v>3</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F429" s="4" t="s">
         <v>354</v>
@@ -51560,7 +51722,7 @@
       <c r="BH429" s="2"/>
       <c r="BI429" s="2"/>
       <c r="BJ429" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="430" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51577,7 +51739,7 @@
         <v>4</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F430" s="4" t="s">
         <v>354</v>
@@ -51650,7 +51812,7 @@
       <c r="BH430" s="2"/>
       <c r="BI430" s="2"/>
       <c r="BJ430" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="431" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51740,7 +51902,7 @@
       <c r="BH431" s="2"/>
       <c r="BI431" s="2"/>
       <c r="BJ431" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="432" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51757,7 +51919,7 @@
         <v>6</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F432" s="4" t="s">
         <v>354</v>
@@ -51830,7 +51992,7 @@
       <c r="BH432" s="2"/>
       <c r="BI432" s="2"/>
       <c r="BJ432" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="433" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -51920,7 +52082,7 @@
       <c r="BH433" s="2"/>
       <c r="BI433" s="2"/>
       <c r="BJ433" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="434" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52010,7 +52172,7 @@
       <c r="BH434" s="2"/>
       <c r="BI434" s="2"/>
       <c r="BJ434" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="435" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52027,7 +52189,7 @@
         <v>3</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F435" s="4" t="s">
         <v>354</v>
@@ -52100,7 +52262,7 @@
       <c r="BH435" s="2"/>
       <c r="BI435" s="2"/>
       <c r="BJ435" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="436" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52182,7 +52344,7 @@
       <c r="BH436" s="2"/>
       <c r="BI436" s="2"/>
       <c r="BJ436" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="437" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52272,7 +52434,7 @@
       <c r="BH437" s="2"/>
       <c r="BI437" s="2"/>
       <c r="BJ437" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="438" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52289,7 +52451,7 @@
         <v>6</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F438" s="4" t="s">
         <v>354</v>
@@ -52362,7 +52524,7 @@
       <c r="BH438" s="2"/>
       <c r="BI438" s="2"/>
       <c r="BJ438" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="439" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52452,7 +52614,7 @@
       <c r="BH439" s="2"/>
       <c r="BI439" s="2"/>
       <c r="BJ439" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="440" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52542,7 +52704,7 @@
       <c r="BH440" s="2"/>
       <c r="BI440" s="2"/>
       <c r="BJ440" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="441" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52565,7 +52727,7 @@
         <v>216</v>
       </c>
       <c r="G441" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H441" s="4" t="s">
         <v>572</v>
@@ -52630,7 +52792,7 @@
       <c r="BH441" s="2"/>
       <c r="BI441" s="2"/>
       <c r="BJ441" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="442" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52653,7 +52815,7 @@
         <v>216</v>
       </c>
       <c r="G442" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H442" s="4" t="s">
         <v>572</v>
@@ -52718,7 +52880,7 @@
       <c r="BH442" s="2"/>
       <c r="BI442" s="2"/>
       <c r="BJ442" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="443" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52741,7 +52903,7 @@
         <v>216</v>
       </c>
       <c r="G443" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H443" s="4" t="s">
         <v>572</v>
@@ -52806,7 +52968,7 @@
       <c r="BH443" s="2"/>
       <c r="BI443" s="2"/>
       <c r="BJ443" s="3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="444" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52829,7 +52991,7 @@
         <v>216</v>
       </c>
       <c r="G444" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H444" s="4" t="s">
         <v>572</v>
@@ -52894,7 +53056,7 @@
       <c r="BH444" s="2"/>
       <c r="BI444" s="2"/>
       <c r="BJ444" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="445" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52917,7 +53079,7 @@
         <v>216</v>
       </c>
       <c r="G445" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H445" s="4" t="s">
         <v>572</v>
@@ -52982,7 +53144,7 @@
       <c r="BH445" s="2"/>
       <c r="BI445" s="2"/>
       <c r="BJ445" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="446" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -53005,7 +53167,7 @@
         <v>216</v>
       </c>
       <c r="G446" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H446" s="4" t="s">
         <v>572</v>
@@ -53070,7 +53232,7 @@
       <c r="BH446" s="2"/>
       <c r="BI446" s="2"/>
       <c r="BJ446" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="447" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -53087,13 +53249,13 @@
         <v>7</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F447" s="4" t="s">
         <v>216</v>
       </c>
       <c r="G447" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H447" s="4" t="s">
         <v>572</v>
@@ -53158,8 +53320,2553 @@
       <c r="BH447" s="2"/>
       <c r="BI447" s="2"/>
       <c r="BJ447" s="3" t="s">
-        <v>620</v>
-      </c>
+        <v>619</v>
+      </c>
+    </row>
+    <row r="448" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A448" s="75" t="s">
+        <v>629</v>
+      </c>
+      <c r="B448" s="76" t="s">
+        <v>630</v>
+      </c>
+      <c r="C448" s="77">
+        <v>45384</v>
+      </c>
+      <c r="D448" s="78">
+        <v>1</v>
+      </c>
+      <c r="E448" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F448" s="100" t="s">
+        <v>634</v>
+      </c>
+      <c r="G448" s="4"/>
+      <c r="H448" s="4"/>
+      <c r="I448" s="80"/>
+      <c r="K448" s="81"/>
+      <c r="L448" s="80"/>
+      <c r="M448" s="74">
+        <v>0.2175</v>
+      </c>
+      <c r="O448" s="4"/>
+      <c r="P448" s="80"/>
+      <c r="Q448" s="80"/>
+      <c r="R448" s="82"/>
+      <c r="S448" s="82"/>
+      <c r="T448" s="82"/>
+      <c r="U448" s="82"/>
+      <c r="V448" s="80"/>
+      <c r="W448" s="4"/>
+      <c r="X448" s="4"/>
+      <c r="Y448" s="4"/>
+      <c r="Z448" s="7"/>
+      <c r="AA448" s="7"/>
+      <c r="AB448" s="7"/>
+      <c r="AC448" s="7"/>
+      <c r="AD448" s="7"/>
+      <c r="AE448" s="7"/>
+      <c r="AF448" s="7"/>
+      <c r="AG448" s="7"/>
+      <c r="AH448" s="7"/>
+      <c r="AI448" s="7"/>
+      <c r="AJ448" s="7"/>
+      <c r="AK448" s="7"/>
+      <c r="AL448" s="7"/>
+      <c r="AM448" s="7"/>
+      <c r="AN448" s="7"/>
+      <c r="AO448" s="7"/>
+      <c r="AP448" s="7"/>
+      <c r="AQ448" s="7"/>
+      <c r="AR448" s="7"/>
+      <c r="AS448" s="7"/>
+      <c r="AT448" s="7"/>
+      <c r="AU448" s="7"/>
+      <c r="AV448" s="7"/>
+      <c r="AW448" s="4"/>
+      <c r="AX448" s="2"/>
+      <c r="AY448" s="7"/>
+      <c r="AZ448" s="4"/>
+      <c r="BA448" s="4"/>
+      <c r="BB448" s="2"/>
+      <c r="BC448" s="2"/>
+      <c r="BD448" s="2"/>
+      <c r="BE448" s="83"/>
+      <c r="BF448" s="84"/>
+      <c r="BG448" s="85"/>
+      <c r="BH448" s="2"/>
+      <c r="BI448" s="2"/>
+      <c r="BJ448" s="3"/>
+    </row>
+    <row r="449" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A449" s="75" t="s">
+        <v>629</v>
+      </c>
+      <c r="B449" s="76" t="s">
+        <v>630</v>
+      </c>
+      <c r="C449" s="77">
+        <v>45384</v>
+      </c>
+      <c r="D449" s="78">
+        <v>2</v>
+      </c>
+      <c r="E449" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F449" s="100" t="s">
+        <v>635</v>
+      </c>
+      <c r="G449" s="4"/>
+      <c r="H449" s="4"/>
+      <c r="I449" s="80"/>
+      <c r="K449" s="81"/>
+      <c r="L449" s="80"/>
+      <c r="M449" s="74">
+        <v>0.20380000000000001</v>
+      </c>
+      <c r="O449" s="4"/>
+      <c r="P449" s="80"/>
+      <c r="Q449" s="80"/>
+      <c r="R449" s="82"/>
+      <c r="S449" s="82"/>
+      <c r="T449" s="82"/>
+      <c r="U449" s="82"/>
+      <c r="V449" s="80"/>
+      <c r="W449" s="4"/>
+      <c r="X449" s="4"/>
+      <c r="Y449" s="4"/>
+      <c r="Z449" s="7"/>
+      <c r="AA449" s="7"/>
+      <c r="AB449" s="7"/>
+      <c r="AC449" s="7"/>
+      <c r="AD449" s="7"/>
+      <c r="AE449" s="7"/>
+      <c r="AF449" s="7"/>
+      <c r="AG449" s="7"/>
+      <c r="AH449" s="7"/>
+      <c r="AI449" s="7"/>
+      <c r="AJ449" s="7"/>
+      <c r="AK449" s="7"/>
+      <c r="AL449" s="7"/>
+      <c r="AM449" s="7"/>
+      <c r="AN449" s="7"/>
+      <c r="AO449" s="7"/>
+      <c r="AP449" s="7"/>
+      <c r="AQ449" s="7"/>
+      <c r="AR449" s="7"/>
+      <c r="AS449" s="7"/>
+      <c r="AT449" s="7"/>
+      <c r="AU449" s="7"/>
+      <c r="AV449" s="7"/>
+      <c r="AW449" s="4"/>
+      <c r="AX449" s="2"/>
+      <c r="AY449" s="7"/>
+      <c r="AZ449" s="4"/>
+      <c r="BA449" s="4"/>
+      <c r="BB449" s="2"/>
+      <c r="BC449" s="2"/>
+      <c r="BD449" s="2"/>
+      <c r="BE449" s="83"/>
+      <c r="BF449" s="84"/>
+      <c r="BG449" s="85"/>
+      <c r="BH449" s="2"/>
+      <c r="BI449" s="2"/>
+      <c r="BJ449" s="3"/>
+    </row>
+    <row r="450" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A450" s="75" t="s">
+        <v>629</v>
+      </c>
+      <c r="B450" s="76" t="s">
+        <v>630</v>
+      </c>
+      <c r="C450" s="77">
+        <v>45384</v>
+      </c>
+      <c r="D450" s="78">
+        <v>3</v>
+      </c>
+      <c r="E450" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F450" s="100" t="s">
+        <v>634</v>
+      </c>
+      <c r="G450" s="4"/>
+      <c r="H450" s="4"/>
+      <c r="I450" s="80"/>
+      <c r="K450" s="81"/>
+      <c r="L450" s="80"/>
+      <c r="M450" s="74">
+        <v>0.2177</v>
+      </c>
+      <c r="O450" s="4"/>
+      <c r="P450" s="80"/>
+      <c r="Q450" s="80"/>
+      <c r="R450" s="82"/>
+      <c r="S450" s="82"/>
+      <c r="T450" s="82"/>
+      <c r="U450" s="82"/>
+      <c r="V450" s="80"/>
+      <c r="W450" s="4"/>
+      <c r="X450" s="4"/>
+      <c r="Y450" s="4"/>
+      <c r="Z450" s="7"/>
+      <c r="AA450" s="7"/>
+      <c r="AB450" s="7"/>
+      <c r="AC450" s="7"/>
+      <c r="AD450" s="7"/>
+      <c r="AE450" s="7"/>
+      <c r="AF450" s="7"/>
+      <c r="AG450" s="7"/>
+      <c r="AH450" s="7"/>
+      <c r="AI450" s="7"/>
+      <c r="AJ450" s="7"/>
+      <c r="AK450" s="7"/>
+      <c r="AL450" s="7"/>
+      <c r="AM450" s="7"/>
+      <c r="AN450" s="7"/>
+      <c r="AO450" s="7"/>
+      <c r="AP450" s="7"/>
+      <c r="AQ450" s="7"/>
+      <c r="AR450" s="7"/>
+      <c r="AS450" s="7"/>
+      <c r="AT450" s="7"/>
+      <c r="AU450" s="7"/>
+      <c r="AV450" s="7"/>
+      <c r="AW450" s="4"/>
+      <c r="AX450" s="2"/>
+      <c r="AY450" s="7"/>
+      <c r="AZ450" s="4"/>
+      <c r="BA450" s="4"/>
+      <c r="BB450" s="2"/>
+      <c r="BC450" s="2"/>
+      <c r="BD450" s="2"/>
+      <c r="BE450" s="83"/>
+      <c r="BF450" s="84"/>
+      <c r="BG450" s="85"/>
+      <c r="BH450" s="2"/>
+      <c r="BI450" s="2"/>
+      <c r="BJ450" s="3"/>
+    </row>
+    <row r="451" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A451" s="75" t="s">
+        <v>629</v>
+      </c>
+      <c r="B451" s="76" t="s">
+        <v>630</v>
+      </c>
+      <c r="C451" s="77">
+        <v>45384</v>
+      </c>
+      <c r="D451" s="78">
+        <v>4</v>
+      </c>
+      <c r="E451" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F451" s="100" t="s">
+        <v>635</v>
+      </c>
+      <c r="G451" s="4"/>
+      <c r="H451" s="4"/>
+      <c r="I451" s="80"/>
+      <c r="K451" s="81"/>
+      <c r="L451" s="80"/>
+      <c r="M451" s="74">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="O451" s="4"/>
+      <c r="P451" s="80"/>
+      <c r="Q451" s="80"/>
+      <c r="R451" s="82"/>
+      <c r="S451" s="82"/>
+      <c r="T451" s="82"/>
+      <c r="U451" s="82"/>
+      <c r="V451" s="80"/>
+      <c r="W451" s="4"/>
+      <c r="X451" s="4"/>
+      <c r="Y451" s="4"/>
+      <c r="Z451" s="7"/>
+      <c r="AA451" s="7"/>
+      <c r="AB451" s="7"/>
+      <c r="AC451" s="7"/>
+      <c r="AD451" s="7"/>
+      <c r="AE451" s="7"/>
+      <c r="AF451" s="7"/>
+      <c r="AG451" s="7"/>
+      <c r="AH451" s="7"/>
+      <c r="AI451" s="7"/>
+      <c r="AJ451" s="7"/>
+      <c r="AK451" s="7"/>
+      <c r="AL451" s="7"/>
+      <c r="AM451" s="7"/>
+      <c r="AN451" s="7"/>
+      <c r="AO451" s="7"/>
+      <c r="AP451" s="7"/>
+      <c r="AQ451" s="7"/>
+      <c r="AR451" s="7"/>
+      <c r="AS451" s="7"/>
+      <c r="AT451" s="7"/>
+      <c r="AU451" s="7"/>
+      <c r="AV451" s="7"/>
+      <c r="AW451" s="4"/>
+      <c r="AX451" s="2"/>
+      <c r="AY451" s="7"/>
+      <c r="AZ451" s="4"/>
+      <c r="BA451" s="4"/>
+      <c r="BB451" s="2"/>
+      <c r="BC451" s="2"/>
+      <c r="BD451" s="2"/>
+      <c r="BE451" s="83"/>
+      <c r="BF451" s="84"/>
+      <c r="BG451" s="85"/>
+      <c r="BH451" s="2"/>
+      <c r="BI451" s="2"/>
+      <c r="BJ451" s="3"/>
+    </row>
+    <row r="452" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A452" s="75" t="s">
+        <v>629</v>
+      </c>
+      <c r="B452" s="76" t="s">
+        <v>631</v>
+      </c>
+      <c r="C452" s="77">
+        <v>45384</v>
+      </c>
+      <c r="D452" s="78">
+        <v>1</v>
+      </c>
+      <c r="E452" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F452" s="100" t="s">
+        <v>634</v>
+      </c>
+      <c r="G452" s="4"/>
+      <c r="H452" s="4"/>
+      <c r="I452" s="80"/>
+      <c r="K452" s="81"/>
+      <c r="L452" s="80"/>
+      <c r="M452" s="74">
+        <v>0.18440000000000001</v>
+      </c>
+      <c r="O452" s="4"/>
+      <c r="P452" s="80"/>
+      <c r="Q452" s="80"/>
+      <c r="R452" s="82"/>
+      <c r="S452" s="82"/>
+      <c r="T452" s="82"/>
+      <c r="U452" s="82"/>
+      <c r="V452" s="80"/>
+      <c r="W452" s="4"/>
+      <c r="X452" s="4"/>
+      <c r="Y452" s="4"/>
+      <c r="Z452" s="7"/>
+      <c r="AA452" s="7"/>
+      <c r="AB452" s="7"/>
+      <c r="AC452" s="7"/>
+      <c r="AD452" s="7"/>
+      <c r="AE452" s="7"/>
+      <c r="AF452" s="7"/>
+      <c r="AG452" s="7"/>
+      <c r="AH452" s="7"/>
+      <c r="AI452" s="7"/>
+      <c r="AJ452" s="7"/>
+      <c r="AK452" s="7"/>
+      <c r="AL452" s="7"/>
+      <c r="AM452" s="7"/>
+      <c r="AN452" s="7"/>
+      <c r="AO452" s="7"/>
+      <c r="AP452" s="7"/>
+      <c r="AQ452" s="7"/>
+      <c r="AR452" s="7"/>
+      <c r="AS452" s="7"/>
+      <c r="AT452" s="7"/>
+      <c r="AU452" s="7"/>
+      <c r="AV452" s="7"/>
+      <c r="AW452" s="4"/>
+      <c r="AX452" s="2"/>
+      <c r="AY452" s="7"/>
+      <c r="AZ452" s="4"/>
+      <c r="BA452" s="4"/>
+      <c r="BB452" s="2"/>
+      <c r="BC452" s="2"/>
+      <c r="BD452" s="2"/>
+      <c r="BE452" s="83"/>
+      <c r="BF452" s="84"/>
+      <c r="BG452" s="85"/>
+      <c r="BH452" s="2"/>
+      <c r="BI452" s="2"/>
+      <c r="BJ452" s="3"/>
+    </row>
+    <row r="453" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A453" s="75" t="s">
+        <v>629</v>
+      </c>
+      <c r="B453" s="76" t="s">
+        <v>631</v>
+      </c>
+      <c r="C453" s="77">
+        <v>45384</v>
+      </c>
+      <c r="D453" s="78">
+        <v>2</v>
+      </c>
+      <c r="E453" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F453" s="100" t="s">
+        <v>635</v>
+      </c>
+      <c r="G453" s="4"/>
+      <c r="H453" s="4"/>
+      <c r="I453" s="80"/>
+      <c r="K453" s="81"/>
+      <c r="L453" s="80"/>
+      <c r="M453" s="74">
+        <v>0.1862</v>
+      </c>
+      <c r="O453" s="4"/>
+      <c r="P453" s="80"/>
+      <c r="Q453" s="80"/>
+      <c r="R453" s="82"/>
+      <c r="S453" s="82"/>
+      <c r="T453" s="82"/>
+      <c r="U453" s="82"/>
+      <c r="V453" s="80"/>
+      <c r="W453" s="4"/>
+      <c r="X453" s="4"/>
+      <c r="Y453" s="4"/>
+      <c r="Z453" s="7"/>
+      <c r="AA453" s="7"/>
+      <c r="AB453" s="7"/>
+      <c r="AC453" s="7"/>
+      <c r="AD453" s="7"/>
+      <c r="AE453" s="7"/>
+      <c r="AF453" s="7"/>
+      <c r="AG453" s="7"/>
+      <c r="AH453" s="7"/>
+      <c r="AI453" s="7"/>
+      <c r="AJ453" s="7"/>
+      <c r="AK453" s="7"/>
+      <c r="AL453" s="7"/>
+      <c r="AM453" s="7"/>
+      <c r="AN453" s="7"/>
+      <c r="AO453" s="7"/>
+      <c r="AP453" s="7"/>
+      <c r="AQ453" s="7"/>
+      <c r="AR453" s="7"/>
+      <c r="AS453" s="7"/>
+      <c r="AT453" s="7"/>
+      <c r="AU453" s="7"/>
+      <c r="AV453" s="7"/>
+      <c r="AW453" s="4"/>
+      <c r="AX453" s="2"/>
+      <c r="AY453" s="7"/>
+      <c r="AZ453" s="4"/>
+      <c r="BA453" s="4"/>
+      <c r="BB453" s="2"/>
+      <c r="BC453" s="2"/>
+      <c r="BD453" s="2"/>
+      <c r="BE453" s="83"/>
+      <c r="BF453" s="84"/>
+      <c r="BG453" s="85"/>
+      <c r="BH453" s="2"/>
+      <c r="BI453" s="2"/>
+      <c r="BJ453" s="3"/>
+    </row>
+    <row r="454" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A454" s="75" t="s">
+        <v>629</v>
+      </c>
+      <c r="B454" s="76" t="s">
+        <v>631</v>
+      </c>
+      <c r="C454" s="77">
+        <v>45384</v>
+      </c>
+      <c r="D454" s="78">
+        <v>3</v>
+      </c>
+      <c r="E454" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F454" s="100" t="s">
+        <v>634</v>
+      </c>
+      <c r="G454" s="4"/>
+      <c r="H454" s="4"/>
+      <c r="I454" s="80"/>
+      <c r="K454" s="81"/>
+      <c r="L454" s="80"/>
+      <c r="M454" s="74">
+        <v>0.1883</v>
+      </c>
+      <c r="O454" s="4"/>
+      <c r="P454" s="80"/>
+      <c r="Q454" s="80"/>
+      <c r="R454" s="82"/>
+      <c r="S454" s="82"/>
+      <c r="T454" s="82"/>
+      <c r="U454" s="82"/>
+      <c r="V454" s="80"/>
+      <c r="W454" s="4"/>
+      <c r="X454" s="4"/>
+      <c r="Y454" s="4"/>
+      <c r="Z454" s="7"/>
+      <c r="AA454" s="7"/>
+      <c r="AB454" s="7"/>
+      <c r="AC454" s="7"/>
+      <c r="AD454" s="7"/>
+      <c r="AE454" s="7"/>
+      <c r="AF454" s="7"/>
+      <c r="AG454" s="7"/>
+      <c r="AH454" s="7"/>
+      <c r="AI454" s="7"/>
+      <c r="AJ454" s="7"/>
+      <c r="AK454" s="7"/>
+      <c r="AL454" s="7"/>
+      <c r="AM454" s="7"/>
+      <c r="AN454" s="7"/>
+      <c r="AO454" s="7"/>
+      <c r="AP454" s="7"/>
+      <c r="AQ454" s="7"/>
+      <c r="AR454" s="7"/>
+      <c r="AS454" s="7"/>
+      <c r="AT454" s="7"/>
+      <c r="AU454" s="7"/>
+      <c r="AV454" s="7"/>
+      <c r="AW454" s="4"/>
+      <c r="AX454" s="2"/>
+      <c r="AY454" s="7"/>
+      <c r="AZ454" s="4"/>
+      <c r="BA454" s="4"/>
+      <c r="BB454" s="2"/>
+      <c r="BC454" s="2"/>
+      <c r="BD454" s="2"/>
+      <c r="BE454" s="83"/>
+      <c r="BF454" s="84"/>
+      <c r="BG454" s="85"/>
+      <c r="BH454" s="2"/>
+      <c r="BI454" s="2"/>
+      <c r="BJ454" s="3"/>
+    </row>
+    <row r="455" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A455" s="75" t="s">
+        <v>629</v>
+      </c>
+      <c r="B455" s="76" t="s">
+        <v>631</v>
+      </c>
+      <c r="C455" s="77">
+        <v>45384</v>
+      </c>
+      <c r="D455" s="78">
+        <v>4</v>
+      </c>
+      <c r="E455" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F455" s="100" t="s">
+        <v>635</v>
+      </c>
+      <c r="G455" s="4"/>
+      <c r="H455" s="4"/>
+      <c r="I455" s="80"/>
+      <c r="K455" s="81"/>
+      <c r="L455" s="80"/>
+      <c r="M455" s="74">
+        <v>0.19539999999999999</v>
+      </c>
+      <c r="O455" s="4"/>
+      <c r="P455" s="80"/>
+      <c r="Q455" s="80"/>
+      <c r="R455" s="82"/>
+      <c r="S455" s="82"/>
+      <c r="T455" s="82"/>
+      <c r="U455" s="82"/>
+      <c r="V455" s="80"/>
+      <c r="W455" s="4"/>
+      <c r="X455" s="4"/>
+      <c r="Y455" s="4"/>
+      <c r="Z455" s="7"/>
+      <c r="AA455" s="7"/>
+      <c r="AB455" s="7"/>
+      <c r="AC455" s="7"/>
+      <c r="AD455" s="7"/>
+      <c r="AE455" s="7"/>
+      <c r="AF455" s="7"/>
+      <c r="AG455" s="7"/>
+      <c r="AH455" s="7"/>
+      <c r="AI455" s="7"/>
+      <c r="AJ455" s="7"/>
+      <c r="AK455" s="7"/>
+      <c r="AL455" s="7"/>
+      <c r="AM455" s="7"/>
+      <c r="AN455" s="7"/>
+      <c r="AO455" s="7"/>
+      <c r="AP455" s="7"/>
+      <c r="AQ455" s="7"/>
+      <c r="AR455" s="7"/>
+      <c r="AS455" s="7"/>
+      <c r="AT455" s="7"/>
+      <c r="AU455" s="7"/>
+      <c r="AV455" s="7"/>
+      <c r="AW455" s="4"/>
+      <c r="AX455" s="2"/>
+      <c r="AY455" s="7"/>
+      <c r="AZ455" s="4"/>
+      <c r="BA455" s="4"/>
+      <c r="BB455" s="2"/>
+      <c r="BC455" s="2"/>
+      <c r="BD455" s="2"/>
+      <c r="BE455" s="83"/>
+      <c r="BF455" s="84"/>
+      <c r="BG455" s="85"/>
+      <c r="BH455" s="2"/>
+      <c r="BI455" s="2"/>
+      <c r="BJ455" s="3"/>
+    </row>
+    <row r="456" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A456" s="75" t="s">
+        <v>629</v>
+      </c>
+      <c r="B456" s="76" t="s">
+        <v>632</v>
+      </c>
+      <c r="C456" s="77">
+        <v>45384</v>
+      </c>
+      <c r="D456" s="78">
+        <v>1</v>
+      </c>
+      <c r="E456" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F456" s="100" t="s">
+        <v>634</v>
+      </c>
+      <c r="G456" s="4"/>
+      <c r="H456" s="4"/>
+      <c r="I456" s="80"/>
+      <c r="K456" s="81"/>
+      <c r="L456" s="80"/>
+      <c r="M456" s="74">
+        <v>0.22670000000000001</v>
+      </c>
+      <c r="O456" s="4"/>
+      <c r="P456" s="80"/>
+      <c r="Q456" s="80"/>
+      <c r="R456" s="82"/>
+      <c r="S456" s="82"/>
+      <c r="T456" s="82"/>
+      <c r="U456" s="82"/>
+      <c r="V456" s="80"/>
+      <c r="W456" s="4"/>
+      <c r="X456" s="4"/>
+      <c r="Y456" s="4"/>
+      <c r="Z456" s="7"/>
+      <c r="AA456" s="7"/>
+      <c r="AB456" s="7"/>
+      <c r="AC456" s="7"/>
+      <c r="AD456" s="7"/>
+      <c r="AE456" s="7"/>
+      <c r="AF456" s="7"/>
+      <c r="AG456" s="7"/>
+      <c r="AH456" s="7"/>
+      <c r="AI456" s="7"/>
+      <c r="AJ456" s="7"/>
+      <c r="AK456" s="7"/>
+      <c r="AL456" s="7"/>
+      <c r="AM456" s="7"/>
+      <c r="AN456" s="7"/>
+      <c r="AO456" s="7"/>
+      <c r="AP456" s="7"/>
+      <c r="AQ456" s="7"/>
+      <c r="AR456" s="7"/>
+      <c r="AS456" s="7"/>
+      <c r="AT456" s="7"/>
+      <c r="AU456" s="7"/>
+      <c r="AV456" s="7"/>
+      <c r="AW456" s="4"/>
+      <c r="AX456" s="2"/>
+      <c r="AY456" s="7"/>
+      <c r="AZ456" s="4"/>
+      <c r="BA456" s="4"/>
+      <c r="BB456" s="2"/>
+      <c r="BC456" s="2"/>
+      <c r="BD456" s="2"/>
+      <c r="BE456" s="83"/>
+      <c r="BF456" s="84"/>
+      <c r="BG456" s="85"/>
+      <c r="BH456" s="2"/>
+      <c r="BI456" s="2"/>
+      <c r="BJ456" s="3"/>
+    </row>
+    <row r="457" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A457" s="75" t="s">
+        <v>629</v>
+      </c>
+      <c r="B457" s="76" t="s">
+        <v>632</v>
+      </c>
+      <c r="C457" s="77">
+        <v>45384</v>
+      </c>
+      <c r="D457" s="78">
+        <v>2</v>
+      </c>
+      <c r="E457" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F457" s="100" t="s">
+        <v>635</v>
+      </c>
+      <c r="G457" s="4"/>
+      <c r="H457" s="4"/>
+      <c r="I457" s="80"/>
+      <c r="K457" s="81"/>
+      <c r="L457" s="80"/>
+      <c r="M457" s="74">
+        <v>0.1993</v>
+      </c>
+      <c r="O457" s="4"/>
+      <c r="P457" s="80"/>
+      <c r="Q457" s="80"/>
+      <c r="R457" s="82"/>
+      <c r="S457" s="82"/>
+      <c r="T457" s="82"/>
+      <c r="U457" s="82"/>
+      <c r="V457" s="80"/>
+      <c r="W457" s="4"/>
+      <c r="X457" s="4"/>
+      <c r="Y457" s="4"/>
+      <c r="Z457" s="7"/>
+      <c r="AA457" s="7"/>
+      <c r="AB457" s="7"/>
+      <c r="AC457" s="7"/>
+      <c r="AD457" s="7"/>
+      <c r="AE457" s="7"/>
+      <c r="AF457" s="7"/>
+      <c r="AG457" s="7"/>
+      <c r="AH457" s="7"/>
+      <c r="AI457" s="7"/>
+      <c r="AJ457" s="7"/>
+      <c r="AK457" s="7"/>
+      <c r="AL457" s="7"/>
+      <c r="AM457" s="7"/>
+      <c r="AN457" s="7"/>
+      <c r="AO457" s="7"/>
+      <c r="AP457" s="7"/>
+      <c r="AQ457" s="7"/>
+      <c r="AR457" s="7"/>
+      <c r="AS457" s="7"/>
+      <c r="AT457" s="7"/>
+      <c r="AU457" s="7"/>
+      <c r="AV457" s="7"/>
+      <c r="AW457" s="4"/>
+      <c r="AX457" s="2"/>
+      <c r="AY457" s="7"/>
+      <c r="AZ457" s="4"/>
+      <c r="BA457" s="4"/>
+      <c r="BB457" s="2"/>
+      <c r="BC457" s="2"/>
+      <c r="BD457" s="2"/>
+      <c r="BE457" s="83"/>
+      <c r="BF457" s="84"/>
+      <c r="BG457" s="85"/>
+      <c r="BH457" s="2"/>
+      <c r="BI457" s="2"/>
+      <c r="BJ457" s="3"/>
+    </row>
+    <row r="458" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A458" s="75" t="s">
+        <v>629</v>
+      </c>
+      <c r="B458" s="76" t="s">
+        <v>632</v>
+      </c>
+      <c r="C458" s="77">
+        <v>45384</v>
+      </c>
+      <c r="D458" s="78">
+        <v>3</v>
+      </c>
+      <c r="E458" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F458" s="100" t="s">
+        <v>634</v>
+      </c>
+      <c r="G458" s="4"/>
+      <c r="H458" s="4"/>
+      <c r="I458" s="80"/>
+      <c r="K458" s="81"/>
+      <c r="L458" s="80"/>
+      <c r="M458" s="74">
+        <v>0.21279999999999999</v>
+      </c>
+      <c r="O458" s="4"/>
+      <c r="P458" s="80"/>
+      <c r="Q458" s="80"/>
+      <c r="R458" s="82"/>
+      <c r="S458" s="82"/>
+      <c r="T458" s="82"/>
+      <c r="U458" s="82"/>
+      <c r="V458" s="80"/>
+      <c r="W458" s="4"/>
+      <c r="X458" s="4"/>
+      <c r="Y458" s="4"/>
+      <c r="Z458" s="7"/>
+      <c r="AA458" s="7"/>
+      <c r="AB458" s="7"/>
+      <c r="AC458" s="7"/>
+      <c r="AD458" s="7"/>
+      <c r="AE458" s="7"/>
+      <c r="AF458" s="7"/>
+      <c r="AG458" s="7"/>
+      <c r="AH458" s="7"/>
+      <c r="AI458" s="7"/>
+      <c r="AJ458" s="7"/>
+      <c r="AK458" s="7"/>
+      <c r="AL458" s="7"/>
+      <c r="AM458" s="7"/>
+      <c r="AN458" s="7"/>
+      <c r="AO458" s="7"/>
+      <c r="AP458" s="7"/>
+      <c r="AQ458" s="7"/>
+      <c r="AR458" s="7"/>
+      <c r="AS458" s="7"/>
+      <c r="AT458" s="7"/>
+      <c r="AU458" s="7"/>
+      <c r="AV458" s="7"/>
+      <c r="AW458" s="4"/>
+      <c r="AX458" s="2"/>
+      <c r="AY458" s="7"/>
+      <c r="AZ458" s="4"/>
+      <c r="BA458" s="4"/>
+      <c r="BB458" s="2"/>
+      <c r="BC458" s="2"/>
+      <c r="BD458" s="2"/>
+      <c r="BE458" s="83"/>
+      <c r="BF458" s="84"/>
+      <c r="BG458" s="85"/>
+      <c r="BH458" s="2"/>
+      <c r="BI458" s="2"/>
+      <c r="BJ458" s="3"/>
+    </row>
+    <row r="459" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A459" s="75" t="s">
+        <v>629</v>
+      </c>
+      <c r="B459" s="76" t="s">
+        <v>632</v>
+      </c>
+      <c r="C459" s="77">
+        <v>45384</v>
+      </c>
+      <c r="D459" s="78">
+        <v>4</v>
+      </c>
+      <c r="E459" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F459" s="100" t="s">
+        <v>635</v>
+      </c>
+      <c r="G459" s="4"/>
+      <c r="H459" s="4"/>
+      <c r="I459" s="80"/>
+      <c r="K459" s="81"/>
+      <c r="L459" s="80"/>
+      <c r="M459" s="74">
+        <v>0.2039</v>
+      </c>
+      <c r="O459" s="4"/>
+      <c r="P459" s="80"/>
+      <c r="Q459" s="80"/>
+      <c r="R459" s="82"/>
+      <c r="S459" s="82"/>
+      <c r="T459" s="82"/>
+      <c r="U459" s="82"/>
+      <c r="V459" s="80"/>
+      <c r="W459" s="4"/>
+      <c r="X459" s="4"/>
+      <c r="Y459" s="4"/>
+      <c r="Z459" s="7"/>
+      <c r="AA459" s="7"/>
+      <c r="AB459" s="7"/>
+      <c r="AC459" s="7"/>
+      <c r="AD459" s="7"/>
+      <c r="AE459" s="7"/>
+      <c r="AF459" s="7"/>
+      <c r="AG459" s="7"/>
+      <c r="AH459" s="7"/>
+      <c r="AI459" s="7"/>
+      <c r="AJ459" s="7"/>
+      <c r="AK459" s="7"/>
+      <c r="AL459" s="7"/>
+      <c r="AM459" s="7"/>
+      <c r="AN459" s="7"/>
+      <c r="AO459" s="7"/>
+      <c r="AP459" s="7"/>
+      <c r="AQ459" s="7"/>
+      <c r="AR459" s="7"/>
+      <c r="AS459" s="7"/>
+      <c r="AT459" s="7"/>
+      <c r="AU459" s="7"/>
+      <c r="AV459" s="7"/>
+      <c r="AW459" s="4"/>
+      <c r="AX459" s="2"/>
+      <c r="AY459" s="7"/>
+      <c r="AZ459" s="4"/>
+      <c r="BA459" s="4"/>
+      <c r="BB459" s="2"/>
+      <c r="BC459" s="2"/>
+      <c r="BD459" s="2"/>
+      <c r="BE459" s="83"/>
+      <c r="BF459" s="84"/>
+      <c r="BG459" s="85"/>
+      <c r="BH459" s="2"/>
+      <c r="BI459" s="2"/>
+      <c r="BJ459" s="3"/>
+    </row>
+    <row r="460" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A460" s="75" t="s">
+        <v>629</v>
+      </c>
+      <c r="B460" s="76" t="s">
+        <v>633</v>
+      </c>
+      <c r="C460" s="77">
+        <v>45384</v>
+      </c>
+      <c r="D460" s="78">
+        <v>1</v>
+      </c>
+      <c r="E460" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F460" s="100" t="s">
+        <v>634</v>
+      </c>
+      <c r="G460" s="4"/>
+      <c r="H460" s="4"/>
+      <c r="I460" s="80"/>
+      <c r="K460" s="81"/>
+      <c r="L460" s="80"/>
+      <c r="M460" s="74">
+        <v>0.2145</v>
+      </c>
+      <c r="O460" s="4"/>
+      <c r="P460" s="80"/>
+      <c r="Q460" s="80"/>
+      <c r="R460" s="82"/>
+      <c r="S460" s="82"/>
+      <c r="T460" s="82"/>
+      <c r="U460" s="82"/>
+      <c r="V460" s="80"/>
+      <c r="W460" s="4"/>
+      <c r="X460" s="4"/>
+      <c r="Y460" s="4"/>
+      <c r="Z460" s="7"/>
+      <c r="AA460" s="7"/>
+      <c r="AB460" s="7"/>
+      <c r="AC460" s="7"/>
+      <c r="AD460" s="7"/>
+      <c r="AE460" s="7"/>
+      <c r="AF460" s="7"/>
+      <c r="AG460" s="7"/>
+      <c r="AH460" s="7"/>
+      <c r="AI460" s="7"/>
+      <c r="AJ460" s="7"/>
+      <c r="AK460" s="7"/>
+      <c r="AL460" s="7"/>
+      <c r="AM460" s="7"/>
+      <c r="AN460" s="7"/>
+      <c r="AO460" s="7"/>
+      <c r="AP460" s="7"/>
+      <c r="AQ460" s="7"/>
+      <c r="AR460" s="7"/>
+      <c r="AS460" s="7"/>
+      <c r="AT460" s="7"/>
+      <c r="AU460" s="7"/>
+      <c r="AV460" s="7"/>
+      <c r="AW460" s="4"/>
+      <c r="AX460" s="2"/>
+      <c r="AY460" s="7"/>
+      <c r="AZ460" s="4"/>
+      <c r="BA460" s="4"/>
+      <c r="BB460" s="2"/>
+      <c r="BC460" s="2"/>
+      <c r="BD460" s="2"/>
+      <c r="BE460" s="83"/>
+      <c r="BF460" s="84"/>
+      <c r="BG460" s="85"/>
+      <c r="BH460" s="2"/>
+      <c r="BI460" s="2"/>
+      <c r="BJ460" s="3"/>
+    </row>
+    <row r="461" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A461" s="75" t="s">
+        <v>629</v>
+      </c>
+      <c r="B461" s="76" t="s">
+        <v>633</v>
+      </c>
+      <c r="C461" s="77">
+        <v>45384</v>
+      </c>
+      <c r="D461" s="78">
+        <v>2</v>
+      </c>
+      <c r="E461" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F461" s="100" t="s">
+        <v>635</v>
+      </c>
+      <c r="G461" s="4"/>
+      <c r="H461" s="4"/>
+      <c r="I461" s="80"/>
+      <c r="K461" s="81"/>
+      <c r="L461" s="80"/>
+      <c r="M461" s="74">
+        <v>0.21629999999999999</v>
+      </c>
+      <c r="O461" s="4"/>
+      <c r="P461" s="80"/>
+      <c r="Q461" s="80"/>
+      <c r="R461" s="82"/>
+      <c r="S461" s="82"/>
+      <c r="T461" s="82"/>
+      <c r="U461" s="82"/>
+      <c r="V461" s="80"/>
+      <c r="W461" s="4"/>
+      <c r="X461" s="4"/>
+      <c r="Y461" s="4"/>
+      <c r="Z461" s="7"/>
+      <c r="AA461" s="7"/>
+      <c r="AB461" s="7"/>
+      <c r="AC461" s="7"/>
+      <c r="AD461" s="7"/>
+      <c r="AE461" s="7"/>
+      <c r="AF461" s="7"/>
+      <c r="AG461" s="7"/>
+      <c r="AH461" s="7"/>
+      <c r="AI461" s="7"/>
+      <c r="AJ461" s="7"/>
+      <c r="AK461" s="7"/>
+      <c r="AL461" s="7"/>
+      <c r="AM461" s="7"/>
+      <c r="AN461" s="7"/>
+      <c r="AO461" s="7"/>
+      <c r="AP461" s="7"/>
+      <c r="AQ461" s="7"/>
+      <c r="AR461" s="7"/>
+      <c r="AS461" s="7"/>
+      <c r="AT461" s="7"/>
+      <c r="AU461" s="7"/>
+      <c r="AV461" s="7"/>
+      <c r="AW461" s="4"/>
+      <c r="AX461" s="2"/>
+      <c r="AY461" s="7"/>
+      <c r="AZ461" s="4"/>
+      <c r="BA461" s="4"/>
+      <c r="BB461" s="2"/>
+      <c r="BC461" s="2"/>
+      <c r="BD461" s="2"/>
+      <c r="BE461" s="83"/>
+      <c r="BF461" s="84"/>
+      <c r="BG461" s="85"/>
+      <c r="BH461" s="2"/>
+      <c r="BI461" s="2"/>
+      <c r="BJ461" s="3"/>
+    </row>
+    <row r="462" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A462" s="75" t="s">
+        <v>629</v>
+      </c>
+      <c r="B462" s="76" t="s">
+        <v>633</v>
+      </c>
+      <c r="C462" s="77">
+        <v>45384</v>
+      </c>
+      <c r="D462" s="78">
+        <v>3</v>
+      </c>
+      <c r="E462" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F462" s="100" t="s">
+        <v>634</v>
+      </c>
+      <c r="G462" s="4"/>
+      <c r="H462" s="4"/>
+      <c r="I462" s="80"/>
+      <c r="K462" s="81"/>
+      <c r="L462" s="80"/>
+      <c r="M462" s="74">
+        <v>0.2185</v>
+      </c>
+      <c r="O462" s="4"/>
+      <c r="P462" s="80"/>
+      <c r="Q462" s="80"/>
+      <c r="R462" s="82"/>
+      <c r="S462" s="82"/>
+      <c r="T462" s="82"/>
+      <c r="U462" s="82"/>
+      <c r="V462" s="80"/>
+      <c r="W462" s="4"/>
+      <c r="X462" s="4"/>
+      <c r="Y462" s="4"/>
+      <c r="Z462" s="7"/>
+      <c r="AA462" s="7"/>
+      <c r="AB462" s="7"/>
+      <c r="AC462" s="7"/>
+      <c r="AD462" s="7"/>
+      <c r="AE462" s="7"/>
+      <c r="AF462" s="7"/>
+      <c r="AG462" s="7"/>
+      <c r="AH462" s="7"/>
+      <c r="AI462" s="7"/>
+      <c r="AJ462" s="7"/>
+      <c r="AK462" s="7"/>
+      <c r="AL462" s="7"/>
+      <c r="AM462" s="7"/>
+      <c r="AN462" s="7"/>
+      <c r="AO462" s="7"/>
+      <c r="AP462" s="7"/>
+      <c r="AQ462" s="7"/>
+      <c r="AR462" s="7"/>
+      <c r="AS462" s="7"/>
+      <c r="AT462" s="7"/>
+      <c r="AU462" s="7"/>
+      <c r="AV462" s="7"/>
+      <c r="AW462" s="4"/>
+      <c r="AX462" s="2"/>
+      <c r="AY462" s="7"/>
+      <c r="AZ462" s="4"/>
+      <c r="BA462" s="4"/>
+      <c r="BB462" s="2"/>
+      <c r="BC462" s="2"/>
+      <c r="BD462" s="2"/>
+      <c r="BE462" s="83"/>
+      <c r="BF462" s="84"/>
+      <c r="BG462" s="85"/>
+      <c r="BH462" s="2"/>
+      <c r="BI462" s="2"/>
+      <c r="BJ462" s="3"/>
+    </row>
+    <row r="463" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A463" s="86" t="s">
+        <v>629</v>
+      </c>
+      <c r="B463" s="87" t="s">
+        <v>633</v>
+      </c>
+      <c r="C463" s="88">
+        <v>45384</v>
+      </c>
+      <c r="D463" s="89">
+        <v>4</v>
+      </c>
+      <c r="E463" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F463" s="100" t="s">
+        <v>635</v>
+      </c>
+      <c r="G463" s="90"/>
+      <c r="H463" s="90"/>
+      <c r="I463" s="91"/>
+      <c r="J463" s="92"/>
+      <c r="K463" s="93"/>
+      <c r="L463" s="91"/>
+      <c r="M463" s="74">
+        <v>0.216</v>
+      </c>
+      <c r="N463" s="92"/>
+      <c r="O463" s="90"/>
+      <c r="P463" s="91"/>
+      <c r="Q463" s="91"/>
+      <c r="R463" s="94"/>
+      <c r="S463" s="94"/>
+      <c r="T463" s="82"/>
+      <c r="U463" s="82"/>
+      <c r="V463" s="80"/>
+      <c r="W463" s="90"/>
+      <c r="X463" s="90"/>
+      <c r="Y463" s="90"/>
+      <c r="Z463" s="92"/>
+      <c r="AA463" s="92"/>
+      <c r="AB463" s="92"/>
+      <c r="AC463" s="92"/>
+      <c r="AD463" s="92"/>
+      <c r="AE463" s="92"/>
+      <c r="AF463" s="92"/>
+      <c r="AG463" s="92"/>
+      <c r="AH463" s="92"/>
+      <c r="AI463" s="92"/>
+      <c r="AJ463" s="92"/>
+      <c r="AK463" s="92"/>
+      <c r="AL463" s="92"/>
+      <c r="AM463" s="92"/>
+      <c r="AN463" s="92"/>
+      <c r="AO463" s="92"/>
+      <c r="AP463" s="92"/>
+      <c r="AQ463" s="92"/>
+      <c r="AR463" s="92"/>
+      <c r="AS463" s="92"/>
+      <c r="AT463" s="92"/>
+      <c r="AU463" s="92"/>
+      <c r="AV463" s="92"/>
+      <c r="AW463" s="90"/>
+      <c r="AX463" s="95"/>
+      <c r="AY463" s="92"/>
+      <c r="AZ463" s="90"/>
+      <c r="BA463" s="90"/>
+      <c r="BB463" s="95"/>
+      <c r="BC463" s="95"/>
+      <c r="BD463" s="95"/>
+      <c r="BE463" s="96"/>
+      <c r="BF463" s="97"/>
+      <c r="BG463" s="98"/>
+      <c r="BH463" s="95"/>
+      <c r="BI463" s="95"/>
+      <c r="BJ463" s="99"/>
+    </row>
+    <row r="464" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A464" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B464" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C464" s="77">
+        <v>45400</v>
+      </c>
+      <c r="D464" s="78">
+        <v>1</v>
+      </c>
+      <c r="E464" s="101" t="s">
+        <v>636</v>
+      </c>
+      <c r="F464" s="74" t="s">
+        <v>354</v>
+      </c>
+      <c r="G464" s="74" t="s">
+        <v>641</v>
+      </c>
+      <c r="H464" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I464" s="74">
+        <v>0.16189999999999999</v>
+      </c>
+      <c r="J464" s="74">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="K464" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="L464" s="80"/>
+      <c r="M464" s="74">
+        <v>0.16270000000000001</v>
+      </c>
+      <c r="O464" s="4"/>
+      <c r="P464" s="80"/>
+      <c r="Q464" s="80"/>
+      <c r="R464" s="82"/>
+      <c r="S464" s="82"/>
+      <c r="T464" s="104">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="U464" s="104">
+        <v>592</v>
+      </c>
+      <c r="V464" s="105">
+        <v>754.2</v>
+      </c>
+      <c r="W464" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="X464" s="4"/>
+      <c r="Y464" s="4"/>
+      <c r="Z464" s="7"/>
+      <c r="AA464" s="7"/>
+      <c r="AB464" s="7"/>
+      <c r="AC464" s="7"/>
+      <c r="AD464" s="7"/>
+      <c r="AE464" s="7"/>
+      <c r="AF464" s="7"/>
+      <c r="AG464" s="7"/>
+      <c r="AH464" s="7"/>
+      <c r="AI464" s="7"/>
+      <c r="AJ464" s="7"/>
+      <c r="AK464" s="7"/>
+      <c r="AL464" s="7"/>
+      <c r="AM464" s="7"/>
+      <c r="AN464" s="7"/>
+      <c r="AO464" s="7"/>
+      <c r="AP464" s="7"/>
+      <c r="AQ464" s="7"/>
+      <c r="AR464" s="7"/>
+      <c r="AS464" s="7"/>
+      <c r="AT464" s="7"/>
+      <c r="AU464" s="7"/>
+      <c r="AV464" s="7"/>
+      <c r="AW464" s="4"/>
+      <c r="AX464" s="2"/>
+      <c r="AY464" s="7"/>
+      <c r="AZ464" s="4"/>
+      <c r="BA464" s="4"/>
+      <c r="BB464" s="2"/>
+      <c r="BC464" s="2"/>
+      <c r="BD464" s="2"/>
+      <c r="BE464" s="83"/>
+      <c r="BF464" s="84"/>
+      <c r="BG464" s="85"/>
+      <c r="BH464" s="2"/>
+      <c r="BI464" s="2"/>
+      <c r="BJ464" s="3"/>
+    </row>
+    <row r="465" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A465" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B465" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C465" s="77">
+        <v>45400</v>
+      </c>
+      <c r="D465" s="78">
+        <v>2</v>
+      </c>
+      <c r="E465" s="101" t="s">
+        <v>637</v>
+      </c>
+      <c r="F465" s="74" t="s">
+        <v>354</v>
+      </c>
+      <c r="G465" s="74" t="s">
+        <v>641</v>
+      </c>
+      <c r="H465" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I465" s="74">
+        <v>0.1633</v>
+      </c>
+      <c r="J465" s="74">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="K465" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="L465" s="80"/>
+      <c r="M465" s="74">
+        <v>0.15959999999999999</v>
+      </c>
+      <c r="O465" s="4"/>
+      <c r="P465" s="80"/>
+      <c r="Q465" s="80"/>
+      <c r="R465" s="82"/>
+      <c r="S465" s="82"/>
+      <c r="T465" s="104">
+        <v>65</v>
+      </c>
+      <c r="U465" s="104">
+        <v>578</v>
+      </c>
+      <c r="V465" s="105">
+        <v>754.1</v>
+      </c>
+      <c r="W465" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="X465" s="4"/>
+      <c r="Y465" s="4"/>
+      <c r="Z465" s="7"/>
+      <c r="AA465" s="7"/>
+      <c r="AB465" s="7"/>
+      <c r="AC465" s="7"/>
+      <c r="AD465" s="7"/>
+      <c r="AE465" s="7"/>
+      <c r="AF465" s="7"/>
+      <c r="AG465" s="7"/>
+      <c r="AH465" s="7"/>
+      <c r="AI465" s="7"/>
+      <c r="AJ465" s="7"/>
+      <c r="AK465" s="7"/>
+      <c r="AL465" s="7"/>
+      <c r="AM465" s="7"/>
+      <c r="AN465" s="7"/>
+      <c r="AO465" s="7"/>
+      <c r="AP465" s="7"/>
+      <c r="AQ465" s="7"/>
+      <c r="AR465" s="7"/>
+      <c r="AS465" s="7"/>
+      <c r="AT465" s="7"/>
+      <c r="AU465" s="7"/>
+      <c r="AV465" s="7"/>
+      <c r="AW465" s="4"/>
+      <c r="AX465" s="2"/>
+      <c r="AY465" s="7"/>
+      <c r="AZ465" s="4"/>
+      <c r="BA465" s="4"/>
+      <c r="BB465" s="2"/>
+      <c r="BC465" s="2"/>
+      <c r="BD465" s="2"/>
+      <c r="BE465" s="83"/>
+      <c r="BF465" s="84"/>
+      <c r="BG465" s="85"/>
+      <c r="BH465" s="2"/>
+      <c r="BI465" s="2"/>
+      <c r="BJ465" s="3"/>
+    </row>
+    <row r="466" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A466" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B466" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C466" s="77">
+        <v>45400</v>
+      </c>
+      <c r="D466" s="78">
+        <v>3</v>
+      </c>
+      <c r="E466" s="101" t="s">
+        <v>638</v>
+      </c>
+      <c r="F466" s="74" t="s">
+        <v>354</v>
+      </c>
+      <c r="G466" s="74" t="s">
+        <v>641</v>
+      </c>
+      <c r="H466" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I466" s="74">
+        <v>0.16070000000000001</v>
+      </c>
+      <c r="J466" s="74">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="K466" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="L466" s="80"/>
+      <c r="M466" s="74">
+        <v>0.15870000000000001</v>
+      </c>
+      <c r="O466" s="4"/>
+      <c r="P466" s="80"/>
+      <c r="Q466" s="80"/>
+      <c r="R466" s="82"/>
+      <c r="S466" s="82"/>
+      <c r="T466" s="104">
+        <v>65.8</v>
+      </c>
+      <c r="U466" s="104">
+        <v>594</v>
+      </c>
+      <c r="V466" s="105">
+        <v>754.9</v>
+      </c>
+      <c r="W466" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="X466" s="4"/>
+      <c r="Y466" s="4"/>
+      <c r="Z466" s="7"/>
+      <c r="AA466" s="7"/>
+      <c r="AB466" s="7"/>
+      <c r="AC466" s="7"/>
+      <c r="AD466" s="7"/>
+      <c r="AE466" s="7"/>
+      <c r="AF466" s="7"/>
+      <c r="AG466" s="7"/>
+      <c r="AH466" s="7"/>
+      <c r="AI466" s="7"/>
+      <c r="AJ466" s="7"/>
+      <c r="AK466" s="7"/>
+      <c r="AL466" s="7"/>
+      <c r="AM466" s="7"/>
+      <c r="AN466" s="7"/>
+      <c r="AO466" s="7"/>
+      <c r="AP466" s="7"/>
+      <c r="AQ466" s="7"/>
+      <c r="AR466" s="7"/>
+      <c r="AS466" s="7"/>
+      <c r="AT466" s="7"/>
+      <c r="AU466" s="7"/>
+      <c r="AV466" s="7"/>
+      <c r="AW466" s="4"/>
+      <c r="AX466" s="2"/>
+      <c r="AY466" s="7"/>
+      <c r="AZ466" s="4"/>
+      <c r="BA466" s="4"/>
+      <c r="BB466" s="2"/>
+      <c r="BC466" s="2"/>
+      <c r="BD466" s="2"/>
+      <c r="BE466" s="83"/>
+      <c r="BF466" s="84"/>
+      <c r="BG466" s="85"/>
+      <c r="BH466" s="2"/>
+      <c r="BI466" s="2"/>
+      <c r="BJ466" s="3"/>
+    </row>
+    <row r="467" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A467" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B467" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C467" s="77">
+        <v>45400</v>
+      </c>
+      <c r="D467" s="78">
+        <v>4</v>
+      </c>
+      <c r="E467" s="101" t="s">
+        <v>639</v>
+      </c>
+      <c r="F467" s="74" t="s">
+        <v>354</v>
+      </c>
+      <c r="G467" s="74" t="s">
+        <v>641</v>
+      </c>
+      <c r="H467" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I467" s="74">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="J467" s="74">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="K467" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="L467" s="80"/>
+      <c r="M467" s="74">
+        <v>0.1618</v>
+      </c>
+      <c r="O467" s="4"/>
+      <c r="P467" s="80"/>
+      <c r="Q467" s="80"/>
+      <c r="R467" s="82"/>
+      <c r="S467" s="82"/>
+      <c r="T467" s="104">
+        <v>64.8</v>
+      </c>
+      <c r="U467" s="104">
+        <v>590</v>
+      </c>
+      <c r="V467" s="105">
+        <v>754.3</v>
+      </c>
+      <c r="W467" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="X467" s="4"/>
+      <c r="Y467" s="4"/>
+      <c r="Z467" s="7"/>
+      <c r="AA467" s="7"/>
+      <c r="AB467" s="7"/>
+      <c r="AC467" s="7"/>
+      <c r="AD467" s="7"/>
+      <c r="AE467" s="7"/>
+      <c r="AF467" s="7"/>
+      <c r="AG467" s="7"/>
+      <c r="AH467" s="7"/>
+      <c r="AI467" s="7"/>
+      <c r="AJ467" s="7"/>
+      <c r="AK467" s="7"/>
+      <c r="AL467" s="7"/>
+      <c r="AM467" s="7"/>
+      <c r="AN467" s="7"/>
+      <c r="AO467" s="7"/>
+      <c r="AP467" s="7"/>
+      <c r="AQ467" s="7"/>
+      <c r="AR467" s="7"/>
+      <c r="AS467" s="7"/>
+      <c r="AT467" s="7"/>
+      <c r="AU467" s="7"/>
+      <c r="AV467" s="7"/>
+      <c r="AW467" s="4"/>
+      <c r="AX467" s="2"/>
+      <c r="AY467" s="7"/>
+      <c r="AZ467" s="4"/>
+      <c r="BA467" s="4"/>
+      <c r="BB467" s="2"/>
+      <c r="BC467" s="2"/>
+      <c r="BD467" s="2"/>
+      <c r="BE467" s="83"/>
+      <c r="BF467" s="84"/>
+      <c r="BG467" s="85"/>
+      <c r="BH467" s="2"/>
+      <c r="BI467" s="2"/>
+      <c r="BJ467" s="3"/>
+    </row>
+    <row r="468" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A468" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B468" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C468" s="77">
+        <v>45400</v>
+      </c>
+      <c r="D468" s="78">
+        <v>5</v>
+      </c>
+      <c r="E468" s="101" t="s">
+        <v>636</v>
+      </c>
+      <c r="F468" s="74" t="s">
+        <v>354</v>
+      </c>
+      <c r="G468" s="74" t="s">
+        <v>641</v>
+      </c>
+      <c r="H468" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I468" s="74">
+        <v>0.1636</v>
+      </c>
+      <c r="J468" s="74">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="K468" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="L468" s="80"/>
+      <c r="M468" s="74">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="O468" s="4"/>
+      <c r="P468" s="80"/>
+      <c r="Q468" s="80"/>
+      <c r="R468" s="82"/>
+      <c r="S468" s="82"/>
+      <c r="T468" s="104">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="U468" s="104">
+        <v>589</v>
+      </c>
+      <c r="V468" s="105">
+        <v>754.5</v>
+      </c>
+      <c r="W468" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="X468" s="4"/>
+      <c r="Y468" s="4"/>
+      <c r="Z468" s="7"/>
+      <c r="AA468" s="7"/>
+      <c r="AB468" s="7"/>
+      <c r="AC468" s="7"/>
+      <c r="AD468" s="7"/>
+      <c r="AE468" s="7"/>
+      <c r="AF468" s="7"/>
+      <c r="AG468" s="7"/>
+      <c r="AH468" s="7"/>
+      <c r="AI468" s="7"/>
+      <c r="AJ468" s="7"/>
+      <c r="AK468" s="7"/>
+      <c r="AL468" s="7"/>
+      <c r="AM468" s="7"/>
+      <c r="AN468" s="7"/>
+      <c r="AO468" s="7"/>
+      <c r="AP468" s="7"/>
+      <c r="AQ468" s="7"/>
+      <c r="AR468" s="7"/>
+      <c r="AS468" s="7"/>
+      <c r="AT468" s="7"/>
+      <c r="AU468" s="7"/>
+      <c r="AV468" s="7"/>
+      <c r="AW468" s="4"/>
+      <c r="AX468" s="2"/>
+      <c r="AY468" s="7"/>
+      <c r="AZ468" s="4"/>
+      <c r="BA468" s="4"/>
+      <c r="BB468" s="2"/>
+      <c r="BC468" s="2"/>
+      <c r="BD468" s="2"/>
+      <c r="BE468" s="83"/>
+      <c r="BF468" s="84"/>
+      <c r="BG468" s="85"/>
+      <c r="BH468" s="2"/>
+      <c r="BI468" s="2"/>
+      <c r="BJ468" s="3"/>
+    </row>
+    <row r="469" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A469" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B469" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C469" s="77">
+        <v>45400</v>
+      </c>
+      <c r="D469" s="78">
+        <v>6</v>
+      </c>
+      <c r="E469" s="101" t="s">
+        <v>637</v>
+      </c>
+      <c r="F469" s="74" t="s">
+        <v>354</v>
+      </c>
+      <c r="G469" s="74" t="s">
+        <v>641</v>
+      </c>
+      <c r="H469" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I469" s="74">
+        <v>0.1643</v>
+      </c>
+      <c r="J469" s="74">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="K469" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="L469" s="80"/>
+      <c r="M469" s="74">
+        <v>0.15909999999999999</v>
+      </c>
+      <c r="O469" s="4"/>
+      <c r="P469" s="80"/>
+      <c r="Q469" s="80"/>
+      <c r="R469" s="82"/>
+      <c r="S469" s="82"/>
+      <c r="T469" s="104">
+        <v>65.3</v>
+      </c>
+      <c r="U469" s="104">
+        <v>582</v>
+      </c>
+      <c r="V469" s="105">
+        <v>754.7</v>
+      </c>
+      <c r="W469" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="X469" s="4"/>
+      <c r="Y469" s="4"/>
+      <c r="Z469" s="7"/>
+      <c r="AA469" s="7"/>
+      <c r="AB469" s="7"/>
+      <c r="AC469" s="7"/>
+      <c r="AD469" s="7"/>
+      <c r="AE469" s="7"/>
+      <c r="AF469" s="7"/>
+      <c r="AG469" s="7"/>
+      <c r="AH469" s="7"/>
+      <c r="AI469" s="7"/>
+      <c r="AJ469" s="7"/>
+      <c r="AK469" s="7"/>
+      <c r="AL469" s="7"/>
+      <c r="AM469" s="7"/>
+      <c r="AN469" s="7"/>
+      <c r="AO469" s="7"/>
+      <c r="AP469" s="7"/>
+      <c r="AQ469" s="7"/>
+      <c r="AR469" s="7"/>
+      <c r="AS469" s="7"/>
+      <c r="AT469" s="7"/>
+      <c r="AU469" s="7"/>
+      <c r="AV469" s="7"/>
+      <c r="AW469" s="4"/>
+      <c r="AX469" s="2"/>
+      <c r="AY469" s="7"/>
+      <c r="AZ469" s="4"/>
+      <c r="BA469" s="4"/>
+      <c r="BB469" s="2"/>
+      <c r="BC469" s="2"/>
+      <c r="BD469" s="2"/>
+      <c r="BE469" s="83"/>
+      <c r="BF469" s="84"/>
+      <c r="BG469" s="85"/>
+      <c r="BH469" s="2"/>
+      <c r="BI469" s="2"/>
+      <c r="BJ469" s="3"/>
+    </row>
+    <row r="470" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A470" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B470" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C470" s="77">
+        <v>45400</v>
+      </c>
+      <c r="D470" s="78">
+        <v>7</v>
+      </c>
+      <c r="E470" s="101" t="s">
+        <v>638</v>
+      </c>
+      <c r="F470" s="74" t="s">
+        <v>354</v>
+      </c>
+      <c r="G470" s="74" t="s">
+        <v>641</v>
+      </c>
+      <c r="H470" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I470" s="74">
+        <v>0.16339999999999999</v>
+      </c>
+      <c r="J470" s="74">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="K470" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="L470" s="80"/>
+      <c r="M470" s="74">
+        <v>0.16120000000000001</v>
+      </c>
+      <c r="O470" s="4"/>
+      <c r="P470" s="80"/>
+      <c r="Q470" s="80"/>
+      <c r="R470" s="82"/>
+      <c r="S470" s="82"/>
+      <c r="T470" s="104">
+        <v>65.3</v>
+      </c>
+      <c r="U470" s="104">
+        <v>596</v>
+      </c>
+      <c r="V470" s="105">
+        <v>754.6</v>
+      </c>
+      <c r="W470" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="X470" s="4"/>
+      <c r="Y470" s="4"/>
+      <c r="Z470" s="7"/>
+      <c r="AA470" s="7"/>
+      <c r="AB470" s="7"/>
+      <c r="AC470" s="7"/>
+      <c r="AD470" s="7"/>
+      <c r="AE470" s="7"/>
+      <c r="AF470" s="7"/>
+      <c r="AG470" s="7"/>
+      <c r="AH470" s="7"/>
+      <c r="AI470" s="7"/>
+      <c r="AJ470" s="7"/>
+      <c r="AK470" s="7"/>
+      <c r="AL470" s="7"/>
+      <c r="AM470" s="7"/>
+      <c r="AN470" s="7"/>
+      <c r="AO470" s="7"/>
+      <c r="AP470" s="7"/>
+      <c r="AQ470" s="7"/>
+      <c r="AR470" s="7"/>
+      <c r="AS470" s="7"/>
+      <c r="AT470" s="7"/>
+      <c r="AU470" s="7"/>
+      <c r="AV470" s="7"/>
+      <c r="AW470" s="4"/>
+      <c r="AX470" s="2"/>
+      <c r="AY470" s="7"/>
+      <c r="AZ470" s="4"/>
+      <c r="BA470" s="4"/>
+      <c r="BB470" s="2"/>
+      <c r="BC470" s="2"/>
+      <c r="BD470" s="2"/>
+      <c r="BE470" s="83"/>
+      <c r="BF470" s="84"/>
+      <c r="BG470" s="85"/>
+      <c r="BH470" s="2"/>
+      <c r="BI470" s="2"/>
+      <c r="BJ470" s="3"/>
+    </row>
+    <row r="471" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A471" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B471" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C471" s="77">
+        <v>45400</v>
+      </c>
+      <c r="D471" s="78">
+        <v>8</v>
+      </c>
+      <c r="E471" s="101" t="s">
+        <v>639</v>
+      </c>
+      <c r="F471" s="74" t="s">
+        <v>354</v>
+      </c>
+      <c r="G471" s="74" t="s">
+        <v>641</v>
+      </c>
+      <c r="H471" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I471" s="74">
+        <v>0.1658</v>
+      </c>
+      <c r="J471" s="74">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="K471" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="L471" s="80"/>
+      <c r="M471" s="74">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="O471" s="4"/>
+      <c r="P471" s="80"/>
+      <c r="Q471" s="80"/>
+      <c r="R471" s="82"/>
+      <c r="S471" s="82"/>
+      <c r="T471" s="104">
+        <v>65</v>
+      </c>
+      <c r="U471" s="104">
+        <v>591</v>
+      </c>
+      <c r="V471" s="105">
+        <v>754.3</v>
+      </c>
+      <c r="W471" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="X471" s="4"/>
+      <c r="Y471" s="4"/>
+      <c r="Z471" s="7"/>
+      <c r="AA471" s="7"/>
+      <c r="AB471" s="7"/>
+      <c r="AC471" s="7"/>
+      <c r="AD471" s="7"/>
+      <c r="AE471" s="7"/>
+      <c r="AF471" s="7"/>
+      <c r="AG471" s="7"/>
+      <c r="AH471" s="7"/>
+      <c r="AI471" s="7"/>
+      <c r="AJ471" s="7"/>
+      <c r="AK471" s="7"/>
+      <c r="AL471" s="7"/>
+      <c r="AM471" s="7"/>
+      <c r="AN471" s="7"/>
+      <c r="AO471" s="7"/>
+      <c r="AP471" s="7"/>
+      <c r="AQ471" s="7"/>
+      <c r="AR471" s="7"/>
+      <c r="AS471" s="7"/>
+      <c r="AT471" s="7"/>
+      <c r="AU471" s="7"/>
+      <c r="AV471" s="7"/>
+      <c r="AW471" s="4"/>
+      <c r="AX471" s="2"/>
+      <c r="AY471" s="7"/>
+      <c r="AZ471" s="4"/>
+      <c r="BA471" s="4"/>
+      <c r="BB471" s="2"/>
+      <c r="BC471" s="2"/>
+      <c r="BD471" s="2"/>
+      <c r="BE471" s="83"/>
+      <c r="BF471" s="84"/>
+      <c r="BG471" s="85"/>
+      <c r="BH471" s="2"/>
+      <c r="BI471" s="2"/>
+      <c r="BJ471" s="3"/>
+    </row>
+    <row r="472" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A472" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="B472" s="76" t="s">
+        <v>79</v>
+      </c>
+      <c r="C472" s="77">
+        <v>45400</v>
+      </c>
+      <c r="D472" s="78">
+        <v>1</v>
+      </c>
+      <c r="E472" s="101" t="s">
+        <v>640</v>
+      </c>
+      <c r="F472" s="74" t="s">
+        <v>216</v>
+      </c>
+      <c r="G472" s="74" t="s">
+        <v>641</v>
+      </c>
+      <c r="H472" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I472" s="74">
+        <v>0.15079999999999999</v>
+      </c>
+      <c r="J472" s="74">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="K472" s="74">
+        <v>1.22</v>
+      </c>
+      <c r="L472" s="80"/>
+      <c r="M472" s="74">
+        <v>0.14480000000000001</v>
+      </c>
+      <c r="O472" s="4"/>
+      <c r="P472" s="80"/>
+      <c r="Q472" s="80"/>
+      <c r="R472" s="82"/>
+      <c r="S472" s="82"/>
+      <c r="T472" s="104">
+        <v>57.7</v>
+      </c>
+      <c r="U472" s="104">
+        <v>395</v>
+      </c>
+      <c r="V472" s="105">
+        <v>755</v>
+      </c>
+      <c r="W472" s="74" t="s">
+        <v>48</v>
+      </c>
+      <c r="X472" s="4"/>
+      <c r="Y472" s="4"/>
+      <c r="Z472" s="7"/>
+      <c r="AA472" s="7"/>
+      <c r="AB472" s="7"/>
+      <c r="AC472" s="7"/>
+      <c r="AD472" s="7"/>
+      <c r="AE472" s="7"/>
+      <c r="AF472" s="7"/>
+      <c r="AG472" s="7"/>
+      <c r="AH472" s="7"/>
+      <c r="AI472" s="7"/>
+      <c r="AJ472" s="7"/>
+      <c r="AK472" s="7"/>
+      <c r="AL472" s="7"/>
+      <c r="AM472" s="7"/>
+      <c r="AN472" s="7"/>
+      <c r="AO472" s="7"/>
+      <c r="AP472" s="7"/>
+      <c r="AQ472" s="7"/>
+      <c r="AR472" s="7"/>
+      <c r="AS472" s="7"/>
+      <c r="AT472" s="7"/>
+      <c r="AU472" s="7"/>
+      <c r="AV472" s="7"/>
+      <c r="AW472" s="4"/>
+      <c r="AX472" s="2"/>
+      <c r="AY472" s="7"/>
+      <c r="AZ472" s="4"/>
+      <c r="BA472" s="4"/>
+      <c r="BB472" s="2"/>
+      <c r="BC472" s="2"/>
+      <c r="BD472" s="2"/>
+      <c r="BE472" s="83"/>
+      <c r="BF472" s="84"/>
+      <c r="BG472" s="85"/>
+      <c r="BH472" s="2"/>
+      <c r="BI472" s="2"/>
+      <c r="BJ472" s="3"/>
+    </row>
+    <row r="473" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A473" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="B473" s="76" t="s">
+        <v>79</v>
+      </c>
+      <c r="C473" s="77">
+        <v>45400</v>
+      </c>
+      <c r="D473" s="78">
+        <v>2</v>
+      </c>
+      <c r="E473" s="101" t="s">
+        <v>640</v>
+      </c>
+      <c r="F473" s="74" t="s">
+        <v>642</v>
+      </c>
+      <c r="G473" s="74" t="s">
+        <v>643</v>
+      </c>
+      <c r="H473" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I473" s="74">
+        <v>0.1517</v>
+      </c>
+      <c r="J473" s="74">
+        <v>2.8E-3</v>
+      </c>
+      <c r="K473" s="74">
+        <v>1.22</v>
+      </c>
+      <c r="L473" s="80"/>
+      <c r="M473" s="74">
+        <v>0.14630000000000001</v>
+      </c>
+      <c r="O473" s="4"/>
+      <c r="P473" s="80"/>
+      <c r="Q473" s="80"/>
+      <c r="R473" s="82"/>
+      <c r="S473" s="82"/>
+      <c r="T473" s="104">
+        <v>61.2</v>
+      </c>
+      <c r="U473" s="104">
+        <v>445</v>
+      </c>
+      <c r="V473" s="105">
+        <v>755.5</v>
+      </c>
+      <c r="W473" s="74" t="s">
+        <v>48</v>
+      </c>
+      <c r="X473" s="4"/>
+      <c r="Y473" s="4"/>
+      <c r="Z473" s="7"/>
+      <c r="AA473" s="7"/>
+      <c r="AB473" s="7"/>
+      <c r="AC473" s="7"/>
+      <c r="AD473" s="7"/>
+      <c r="AE473" s="7"/>
+      <c r="AF473" s="7"/>
+      <c r="AG473" s="7"/>
+      <c r="AH473" s="7"/>
+      <c r="AI473" s="7"/>
+      <c r="AJ473" s="7"/>
+      <c r="AK473" s="7"/>
+      <c r="AL473" s="7"/>
+      <c r="AM473" s="7"/>
+      <c r="AN473" s="7"/>
+      <c r="AO473" s="7"/>
+      <c r="AP473" s="7"/>
+      <c r="AQ473" s="7"/>
+      <c r="AR473" s="7"/>
+      <c r="AS473" s="7"/>
+      <c r="AT473" s="7"/>
+      <c r="AU473" s="7"/>
+      <c r="AV473" s="7"/>
+      <c r="AW473" s="4"/>
+      <c r="AX473" s="2"/>
+      <c r="AY473" s="7"/>
+      <c r="AZ473" s="4"/>
+      <c r="BA473" s="4"/>
+      <c r="BB473" s="2"/>
+      <c r="BC473" s="2"/>
+      <c r="BD473" s="2"/>
+      <c r="BE473" s="83"/>
+      <c r="BF473" s="84"/>
+      <c r="BG473" s="85"/>
+      <c r="BH473" s="2"/>
+      <c r="BI473" s="2"/>
+      <c r="BJ473" s="3"/>
+    </row>
+    <row r="474" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A474" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="B474" s="76" t="s">
+        <v>79</v>
+      </c>
+      <c r="C474" s="77">
+        <v>45400</v>
+      </c>
+      <c r="D474" s="78">
+        <v>3</v>
+      </c>
+      <c r="E474" s="101" t="s">
+        <v>640</v>
+      </c>
+      <c r="F474" s="74" t="s">
+        <v>644</v>
+      </c>
+      <c r="G474" s="74" t="s">
+        <v>645</v>
+      </c>
+      <c r="H474" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I474" s="103"/>
+      <c r="J474" s="103"/>
+      <c r="K474" s="74">
+        <v>1.22</v>
+      </c>
+      <c r="L474" s="80"/>
+      <c r="M474" s="74">
+        <v>0.14910000000000001</v>
+      </c>
+      <c r="O474" s="4"/>
+      <c r="P474" s="80"/>
+      <c r="Q474" s="80"/>
+      <c r="R474" s="82"/>
+      <c r="S474" s="82"/>
+      <c r="T474" s="104">
+        <v>61.2</v>
+      </c>
+      <c r="U474" s="104">
+        <v>453</v>
+      </c>
+      <c r="V474" s="105">
+        <v>755.3</v>
+      </c>
+      <c r="W474" s="74" t="s">
+        <v>48</v>
+      </c>
+      <c r="X474" s="4"/>
+      <c r="Y474" s="4"/>
+      <c r="Z474" s="7"/>
+      <c r="AA474" s="7"/>
+      <c r="AB474" s="7"/>
+      <c r="AC474" s="7"/>
+      <c r="AD474" s="7"/>
+      <c r="AE474" s="7"/>
+      <c r="AF474" s="7"/>
+      <c r="AG474" s="7"/>
+      <c r="AH474" s="7"/>
+      <c r="AI474" s="7"/>
+      <c r="AJ474" s="7"/>
+      <c r="AK474" s="7"/>
+      <c r="AL474" s="7"/>
+      <c r="AM474" s="7"/>
+      <c r="AN474" s="7"/>
+      <c r="AO474" s="7"/>
+      <c r="AP474" s="7"/>
+      <c r="AQ474" s="7"/>
+      <c r="AR474" s="7"/>
+      <c r="AS474" s="7"/>
+      <c r="AT474" s="7"/>
+      <c r="AU474" s="7"/>
+      <c r="AV474" s="7"/>
+      <c r="AW474" s="4"/>
+      <c r="AX474" s="2"/>
+      <c r="AY474" s="7"/>
+      <c r="AZ474" s="4"/>
+      <c r="BA474" s="4"/>
+      <c r="BB474" s="2"/>
+      <c r="BC474" s="2"/>
+      <c r="BD474" s="2"/>
+      <c r="BE474" s="83"/>
+      <c r="BF474" s="84"/>
+      <c r="BG474" s="85"/>
+      <c r="BH474" s="2"/>
+      <c r="BI474" s="2"/>
+      <c r="BJ474" s="3"/>
+    </row>
+    <row r="475" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A475" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="B475" s="76" t="s">
+        <v>79</v>
+      </c>
+      <c r="C475" s="77">
+        <v>45400</v>
+      </c>
+      <c r="D475" s="78">
+        <v>4</v>
+      </c>
+      <c r="E475" s="101" t="s">
+        <v>640</v>
+      </c>
+      <c r="F475" s="74" t="s">
+        <v>646</v>
+      </c>
+      <c r="G475" s="74" t="s">
+        <v>641</v>
+      </c>
+      <c r="H475" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I475" s="74">
+        <v>0.15240000000000001</v>
+      </c>
+      <c r="J475" s="74">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="K475" s="74">
+        <v>1.22</v>
+      </c>
+      <c r="L475" s="80"/>
+      <c r="M475" s="74">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="O475" s="4"/>
+      <c r="P475" s="80"/>
+      <c r="Q475" s="80"/>
+      <c r="R475" s="82"/>
+      <c r="S475" s="82"/>
+      <c r="T475" s="104">
+        <v>62.2</v>
+      </c>
+      <c r="U475" s="104">
+        <v>470</v>
+      </c>
+      <c r="V475" s="105">
+        <v>755.4</v>
+      </c>
+      <c r="W475" s="74" t="s">
+        <v>48</v>
+      </c>
+      <c r="X475" s="4"/>
+      <c r="Y475" s="4"/>
+      <c r="Z475" s="7"/>
+      <c r="AA475" s="7"/>
+      <c r="AB475" s="7"/>
+      <c r="AC475" s="7"/>
+      <c r="AD475" s="7"/>
+      <c r="AE475" s="7"/>
+      <c r="AF475" s="7"/>
+      <c r="AG475" s="7"/>
+      <c r="AH475" s="7"/>
+      <c r="AI475" s="7"/>
+      <c r="AJ475" s="7"/>
+      <c r="AK475" s="7"/>
+      <c r="AL475" s="7"/>
+      <c r="AM475" s="7"/>
+      <c r="AN475" s="7"/>
+      <c r="AO475" s="7"/>
+      <c r="AP475" s="7"/>
+      <c r="AQ475" s="7"/>
+      <c r="AR475" s="7"/>
+      <c r="AS475" s="7"/>
+      <c r="AT475" s="7"/>
+      <c r="AU475" s="7"/>
+      <c r="AV475" s="7"/>
+      <c r="AW475" s="4"/>
+      <c r="AX475" s="2"/>
+      <c r="AY475" s="7"/>
+      <c r="AZ475" s="4"/>
+      <c r="BA475" s="4"/>
+      <c r="BB475" s="2"/>
+      <c r="BC475" s="2"/>
+      <c r="BD475" s="2"/>
+      <c r="BE475" s="83"/>
+      <c r="BF475" s="84"/>
+      <c r="BG475" s="85"/>
+      <c r="BH475" s="2"/>
+      <c r="BI475" s="2"/>
+      <c r="BJ475" s="3"/>
+    </row>
+    <row r="476" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A476" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="B476" s="76" t="s">
+        <v>79</v>
+      </c>
+      <c r="C476" s="77">
+        <v>45400</v>
+      </c>
+      <c r="D476" s="78">
+        <v>5</v>
+      </c>
+      <c r="E476" s="101" t="s">
+        <v>640</v>
+      </c>
+      <c r="F476" s="74" t="s">
+        <v>647</v>
+      </c>
+      <c r="G476" s="74" t="s">
+        <v>643</v>
+      </c>
+      <c r="H476" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I476" s="74">
+        <v>0.1545</v>
+      </c>
+      <c r="J476" s="74">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="K476" s="74">
+        <v>1.22</v>
+      </c>
+      <c r="L476" s="80"/>
+      <c r="M476" s="74">
+        <v>0.1487</v>
+      </c>
+      <c r="O476" s="4"/>
+      <c r="P476" s="80"/>
+      <c r="Q476" s="80"/>
+      <c r="R476" s="82"/>
+      <c r="S476" s="82"/>
+      <c r="T476" s="104">
+        <v>61.8</v>
+      </c>
+      <c r="U476" s="104">
+        <v>444</v>
+      </c>
+      <c r="V476" s="105">
+        <v>755.4</v>
+      </c>
+      <c r="W476" s="74" t="s">
+        <v>48</v>
+      </c>
+      <c r="X476" s="4"/>
+      <c r="Y476" s="4"/>
+      <c r="Z476" s="7"/>
+      <c r="AA476" s="7"/>
+      <c r="AB476" s="7"/>
+      <c r="AC476" s="7"/>
+      <c r="AD476" s="7"/>
+      <c r="AE476" s="7"/>
+      <c r="AF476" s="7"/>
+      <c r="AG476" s="7"/>
+      <c r="AH476" s="7"/>
+      <c r="AI476" s="7"/>
+      <c r="AJ476" s="7"/>
+      <c r="AK476" s="7"/>
+      <c r="AL476" s="7"/>
+      <c r="AM476" s="7"/>
+      <c r="AN476" s="7"/>
+      <c r="AO476" s="7"/>
+      <c r="AP476" s="7"/>
+      <c r="AQ476" s="7"/>
+      <c r="AR476" s="7"/>
+      <c r="AS476" s="7"/>
+      <c r="AT476" s="7"/>
+      <c r="AU476" s="7"/>
+      <c r="AV476" s="7"/>
+      <c r="AW476" s="4"/>
+      <c r="AX476" s="2"/>
+      <c r="AY476" s="7"/>
+      <c r="AZ476" s="4"/>
+      <c r="BA476" s="4"/>
+      <c r="BB476" s="2"/>
+      <c r="BC476" s="2"/>
+      <c r="BD476" s="2"/>
+      <c r="BE476" s="83"/>
+      <c r="BF476" s="84"/>
+      <c r="BG476" s="85"/>
+      <c r="BH476" s="2"/>
+      <c r="BI476" s="2"/>
+      <c r="BJ476" s="3"/>
+    </row>
+    <row r="477" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A477" s="86" t="s">
+        <v>43</v>
+      </c>
+      <c r="B477" s="87" t="s">
+        <v>79</v>
+      </c>
+      <c r="C477" s="88">
+        <v>45400</v>
+      </c>
+      <c r="D477" s="89">
+        <v>6</v>
+      </c>
+      <c r="E477" s="102" t="s">
+        <v>640</v>
+      </c>
+      <c r="F477" s="74" t="s">
+        <v>648</v>
+      </c>
+      <c r="G477" s="74" t="s">
+        <v>645</v>
+      </c>
+      <c r="H477" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I477" s="74">
+        <v>0.15720000000000001</v>
+      </c>
+      <c r="J477" s="74">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="K477" s="74">
+        <v>1.22</v>
+      </c>
+      <c r="L477" s="91"/>
+      <c r="M477" s="74">
+        <v>0.14979999999999999</v>
+      </c>
+      <c r="N477" s="92"/>
+      <c r="O477" s="90"/>
+      <c r="P477" s="91"/>
+      <c r="Q477" s="91"/>
+      <c r="R477" s="94"/>
+      <c r="S477" s="94"/>
+      <c r="T477" s="74">
+        <v>60.8</v>
+      </c>
+      <c r="U477" s="74">
+        <v>426</v>
+      </c>
+      <c r="V477" s="74">
+        <v>754.7</v>
+      </c>
+      <c r="W477" s="74" t="s">
+        <v>48</v>
+      </c>
+      <c r="X477" s="90"/>
+      <c r="Y477" s="90"/>
+      <c r="Z477" s="92"/>
+      <c r="AA477" s="92"/>
+      <c r="AB477" s="92"/>
+      <c r="AC477" s="92"/>
+      <c r="AD477" s="92"/>
+      <c r="AE477" s="92"/>
+      <c r="AF477" s="92"/>
+      <c r="AG477" s="92"/>
+      <c r="AH477" s="92"/>
+      <c r="AI477" s="92"/>
+      <c r="AJ477" s="92"/>
+      <c r="AK477" s="92"/>
+      <c r="AL477" s="92"/>
+      <c r="AM477" s="92"/>
+      <c r="AN477" s="92"/>
+      <c r="AO477" s="92"/>
+      <c r="AP477" s="92"/>
+      <c r="AQ477" s="92"/>
+      <c r="AR477" s="92"/>
+      <c r="AS477" s="92"/>
+      <c r="AT477" s="92"/>
+      <c r="AU477" s="92"/>
+      <c r="AV477" s="92"/>
+      <c r="AW477" s="90"/>
+      <c r="AX477" s="95"/>
+      <c r="AY477" s="92"/>
+      <c r="AZ477" s="90"/>
+      <c r="BA477" s="90"/>
+      <c r="BB477" s="95"/>
+      <c r="BC477" s="95"/>
+      <c r="BD477" s="95"/>
+      <c r="BE477" s="96"/>
+      <c r="BF477" s="97"/>
+      <c r="BG477" s="98"/>
+      <c r="BH477" s="95"/>
+      <c r="BI477" s="95"/>
+      <c r="BJ477" s="99"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -53178,6 +55885,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004F1ECC6B2649324CB24C079D2C04510D" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="608b5d954c2eb0ac10393708da8d34af">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65551c38-962b-4cee-924d-ef2df1bb8b98" xmlns:ns3="ec750ee3-7d64-422f-9b1f-0ca7238893a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af171f03bd4cf151e3e856a6839c0cc7" ns2:_="" ns3:_="">
     <xsd:import namespace="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
@@ -53425,15 +56141,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -53445,6 +56152,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -53459,14 +56174,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DC6A4D-E49D-451D-9CF8-2DE8A1DD66D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A9C3E3-70BA-46B0-BD70-8A24954761C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43320" yWindow="3270" windowWidth="19395" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CdA Track Testing" sheetId="12" r:id="rId1"/>
@@ -2225,7 +2225,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2454,89 +2454,41 @@
     <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -53336,28 +53288,21 @@
       <c r="D448" s="78">
         <v>1</v>
       </c>
-      <c r="E448" s="79" t="s">
+      <c r="E448" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F448" s="100" t="s">
+      <c r="F448" s="85" t="s">
         <v>634</v>
       </c>
       <c r="G448" s="4"/>
       <c r="H448" s="4"/>
-      <c r="I448" s="80"/>
-      <c r="K448" s="81"/>
-      <c r="L448" s="80"/>
+      <c r="I448" s="7"/>
+      <c r="K448" s="50"/>
+      <c r="L448" s="7"/>
       <c r="M448" s="74">
         <v>0.2175</v>
       </c>
       <c r="O448" s="4"/>
-      <c r="P448" s="80"/>
-      <c r="Q448" s="80"/>
-      <c r="R448" s="82"/>
-      <c r="S448" s="82"/>
-      <c r="T448" s="82"/>
-      <c r="U448" s="82"/>
-      <c r="V448" s="80"/>
       <c r="W448" s="4"/>
       <c r="X448" s="4"/>
       <c r="Y448" s="4"/>
@@ -53392,9 +53337,9 @@
       <c r="BB448" s="2"/>
       <c r="BC448" s="2"/>
       <c r="BD448" s="2"/>
-      <c r="BE448" s="83"/>
-      <c r="BF448" s="84"/>
-      <c r="BG448" s="85"/>
+      <c r="BE448" s="79"/>
+      <c r="BF448" s="80"/>
+      <c r="BG448" s="81"/>
       <c r="BH448" s="2"/>
       <c r="BI448" s="2"/>
       <c r="BJ448" s="3"/>
@@ -53412,28 +53357,21 @@
       <c r="D449" s="78">
         <v>2</v>
       </c>
-      <c r="E449" s="79" t="s">
+      <c r="E449" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F449" s="100" t="s">
+      <c r="F449" s="85" t="s">
         <v>635</v>
       </c>
       <c r="G449" s="4"/>
       <c r="H449" s="4"/>
-      <c r="I449" s="80"/>
-      <c r="K449" s="81"/>
-      <c r="L449" s="80"/>
+      <c r="I449" s="7"/>
+      <c r="K449" s="50"/>
+      <c r="L449" s="7"/>
       <c r="M449" s="74">
         <v>0.20380000000000001</v>
       </c>
       <c r="O449" s="4"/>
-      <c r="P449" s="80"/>
-      <c r="Q449" s="80"/>
-      <c r="R449" s="82"/>
-      <c r="S449" s="82"/>
-      <c r="T449" s="82"/>
-      <c r="U449" s="82"/>
-      <c r="V449" s="80"/>
       <c r="W449" s="4"/>
       <c r="X449" s="4"/>
       <c r="Y449" s="4"/>
@@ -53468,9 +53406,9 @@
       <c r="BB449" s="2"/>
       <c r="BC449" s="2"/>
       <c r="BD449" s="2"/>
-      <c r="BE449" s="83"/>
-      <c r="BF449" s="84"/>
-      <c r="BG449" s="85"/>
+      <c r="BE449" s="79"/>
+      <c r="BF449" s="80"/>
+      <c r="BG449" s="81"/>
       <c r="BH449" s="2"/>
       <c r="BI449" s="2"/>
       <c r="BJ449" s="3"/>
@@ -53488,28 +53426,21 @@
       <c r="D450" s="78">
         <v>3</v>
       </c>
-      <c r="E450" s="79" t="s">
+      <c r="E450" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F450" s="100" t="s">
+      <c r="F450" s="85" t="s">
         <v>634</v>
       </c>
       <c r="G450" s="4"/>
       <c r="H450" s="4"/>
-      <c r="I450" s="80"/>
-      <c r="K450" s="81"/>
-      <c r="L450" s="80"/>
+      <c r="I450" s="7"/>
+      <c r="K450" s="50"/>
+      <c r="L450" s="7"/>
       <c r="M450" s="74">
         <v>0.2177</v>
       </c>
       <c r="O450" s="4"/>
-      <c r="P450" s="80"/>
-      <c r="Q450" s="80"/>
-      <c r="R450" s="82"/>
-      <c r="S450" s="82"/>
-      <c r="T450" s="82"/>
-      <c r="U450" s="82"/>
-      <c r="V450" s="80"/>
       <c r="W450" s="4"/>
       <c r="X450" s="4"/>
       <c r="Y450" s="4"/>
@@ -53544,9 +53475,9 @@
       <c r="BB450" s="2"/>
       <c r="BC450" s="2"/>
       <c r="BD450" s="2"/>
-      <c r="BE450" s="83"/>
-      <c r="BF450" s="84"/>
-      <c r="BG450" s="85"/>
+      <c r="BE450" s="79"/>
+      <c r="BF450" s="80"/>
+      <c r="BG450" s="81"/>
       <c r="BH450" s="2"/>
       <c r="BI450" s="2"/>
       <c r="BJ450" s="3"/>
@@ -53564,28 +53495,21 @@
       <c r="D451" s="78">
         <v>4</v>
       </c>
-      <c r="E451" s="79" t="s">
+      <c r="E451" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F451" s="100" t="s">
+      <c r="F451" s="85" t="s">
         <v>635</v>
       </c>
       <c r="G451" s="4"/>
       <c r="H451" s="4"/>
-      <c r="I451" s="80"/>
-      <c r="K451" s="81"/>
-      <c r="L451" s="80"/>
+      <c r="I451" s="7"/>
+      <c r="K451" s="50"/>
+      <c r="L451" s="7"/>
       <c r="M451" s="74">
         <v>0.21099999999999999</v>
       </c>
       <c r="O451" s="4"/>
-      <c r="P451" s="80"/>
-      <c r="Q451" s="80"/>
-      <c r="R451" s="82"/>
-      <c r="S451" s="82"/>
-      <c r="T451" s="82"/>
-      <c r="U451" s="82"/>
-      <c r="V451" s="80"/>
       <c r="W451" s="4"/>
       <c r="X451" s="4"/>
       <c r="Y451" s="4"/>
@@ -53620,9 +53544,9 @@
       <c r="BB451" s="2"/>
       <c r="BC451" s="2"/>
       <c r="BD451" s="2"/>
-      <c r="BE451" s="83"/>
-      <c r="BF451" s="84"/>
-      <c r="BG451" s="85"/>
+      <c r="BE451" s="79"/>
+      <c r="BF451" s="80"/>
+      <c r="BG451" s="81"/>
       <c r="BH451" s="2"/>
       <c r="BI451" s="2"/>
       <c r="BJ451" s="3"/>
@@ -53640,28 +53564,21 @@
       <c r="D452" s="78">
         <v>1</v>
       </c>
-      <c r="E452" s="79" t="s">
+      <c r="E452" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F452" s="100" t="s">
+      <c r="F452" s="85" t="s">
         <v>634</v>
       </c>
       <c r="G452" s="4"/>
       <c r="H452" s="4"/>
-      <c r="I452" s="80"/>
-      <c r="K452" s="81"/>
-      <c r="L452" s="80"/>
+      <c r="I452" s="7"/>
+      <c r="K452" s="50"/>
+      <c r="L452" s="7"/>
       <c r="M452" s="74">
         <v>0.18440000000000001</v>
       </c>
       <c r="O452" s="4"/>
-      <c r="P452" s="80"/>
-      <c r="Q452" s="80"/>
-      <c r="R452" s="82"/>
-      <c r="S452" s="82"/>
-      <c r="T452" s="82"/>
-      <c r="U452" s="82"/>
-      <c r="V452" s="80"/>
       <c r="W452" s="4"/>
       <c r="X452" s="4"/>
       <c r="Y452" s="4"/>
@@ -53696,9 +53613,9 @@
       <c r="BB452" s="2"/>
       <c r="BC452" s="2"/>
       <c r="BD452" s="2"/>
-      <c r="BE452" s="83"/>
-      <c r="BF452" s="84"/>
-      <c r="BG452" s="85"/>
+      <c r="BE452" s="79"/>
+      <c r="BF452" s="80"/>
+      <c r="BG452" s="81"/>
       <c r="BH452" s="2"/>
       <c r="BI452" s="2"/>
       <c r="BJ452" s="3"/>
@@ -53716,28 +53633,21 @@
       <c r="D453" s="78">
         <v>2</v>
       </c>
-      <c r="E453" s="79" t="s">
+      <c r="E453" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F453" s="100" t="s">
+      <c r="F453" s="85" t="s">
         <v>635</v>
       </c>
       <c r="G453" s="4"/>
       <c r="H453" s="4"/>
-      <c r="I453" s="80"/>
-      <c r="K453" s="81"/>
-      <c r="L453" s="80"/>
+      <c r="I453" s="7"/>
+      <c r="K453" s="50"/>
+      <c r="L453" s="7"/>
       <c r="M453" s="74">
         <v>0.1862</v>
       </c>
       <c r="O453" s="4"/>
-      <c r="P453" s="80"/>
-      <c r="Q453" s="80"/>
-      <c r="R453" s="82"/>
-      <c r="S453" s="82"/>
-      <c r="T453" s="82"/>
-      <c r="U453" s="82"/>
-      <c r="V453" s="80"/>
       <c r="W453" s="4"/>
       <c r="X453" s="4"/>
       <c r="Y453" s="4"/>
@@ -53772,9 +53682,9 @@
       <c r="BB453" s="2"/>
       <c r="BC453" s="2"/>
       <c r="BD453" s="2"/>
-      <c r="BE453" s="83"/>
-      <c r="BF453" s="84"/>
-      <c r="BG453" s="85"/>
+      <c r="BE453" s="79"/>
+      <c r="BF453" s="80"/>
+      <c r="BG453" s="81"/>
       <c r="BH453" s="2"/>
       <c r="BI453" s="2"/>
       <c r="BJ453" s="3"/>
@@ -53792,28 +53702,21 @@
       <c r="D454" s="78">
         <v>3</v>
       </c>
-      <c r="E454" s="79" t="s">
+      <c r="E454" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F454" s="100" t="s">
+      <c r="F454" s="85" t="s">
         <v>634</v>
       </c>
       <c r="G454" s="4"/>
       <c r="H454" s="4"/>
-      <c r="I454" s="80"/>
-      <c r="K454" s="81"/>
-      <c r="L454" s="80"/>
+      <c r="I454" s="7"/>
+      <c r="K454" s="50"/>
+      <c r="L454" s="7"/>
       <c r="M454" s="74">
         <v>0.1883</v>
       </c>
       <c r="O454" s="4"/>
-      <c r="P454" s="80"/>
-      <c r="Q454" s="80"/>
-      <c r="R454" s="82"/>
-      <c r="S454" s="82"/>
-      <c r="T454" s="82"/>
-      <c r="U454" s="82"/>
-      <c r="V454" s="80"/>
       <c r="W454" s="4"/>
       <c r="X454" s="4"/>
       <c r="Y454" s="4"/>
@@ -53848,9 +53751,9 @@
       <c r="BB454" s="2"/>
       <c r="BC454" s="2"/>
       <c r="BD454" s="2"/>
-      <c r="BE454" s="83"/>
-      <c r="BF454" s="84"/>
-      <c r="BG454" s="85"/>
+      <c r="BE454" s="79"/>
+      <c r="BF454" s="80"/>
+      <c r="BG454" s="81"/>
       <c r="BH454" s="2"/>
       <c r="BI454" s="2"/>
       <c r="BJ454" s="3"/>
@@ -53868,28 +53771,21 @@
       <c r="D455" s="78">
         <v>4</v>
       </c>
-      <c r="E455" s="79" t="s">
+      <c r="E455" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F455" s="100" t="s">
+      <c r="F455" s="85" t="s">
         <v>635</v>
       </c>
       <c r="G455" s="4"/>
       <c r="H455" s="4"/>
-      <c r="I455" s="80"/>
-      <c r="K455" s="81"/>
-      <c r="L455" s="80"/>
+      <c r="I455" s="7"/>
+      <c r="K455" s="50"/>
+      <c r="L455" s="7"/>
       <c r="M455" s="74">
         <v>0.19539999999999999</v>
       </c>
       <c r="O455" s="4"/>
-      <c r="P455" s="80"/>
-      <c r="Q455" s="80"/>
-      <c r="R455" s="82"/>
-      <c r="S455" s="82"/>
-      <c r="T455" s="82"/>
-      <c r="U455" s="82"/>
-      <c r="V455" s="80"/>
       <c r="W455" s="4"/>
       <c r="X455" s="4"/>
       <c r="Y455" s="4"/>
@@ -53924,9 +53820,9 @@
       <c r="BB455" s="2"/>
       <c r="BC455" s="2"/>
       <c r="BD455" s="2"/>
-      <c r="BE455" s="83"/>
-      <c r="BF455" s="84"/>
-      <c r="BG455" s="85"/>
+      <c r="BE455" s="79"/>
+      <c r="BF455" s="80"/>
+      <c r="BG455" s="81"/>
       <c r="BH455" s="2"/>
       <c r="BI455" s="2"/>
       <c r="BJ455" s="3"/>
@@ -53944,28 +53840,21 @@
       <c r="D456" s="78">
         <v>1</v>
       </c>
-      <c r="E456" s="79" t="s">
+      <c r="E456" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F456" s="100" t="s">
+      <c r="F456" s="85" t="s">
         <v>634</v>
       </c>
       <c r="G456" s="4"/>
       <c r="H456" s="4"/>
-      <c r="I456" s="80"/>
-      <c r="K456" s="81"/>
-      <c r="L456" s="80"/>
+      <c r="I456" s="7"/>
+      <c r="K456" s="50"/>
+      <c r="L456" s="7"/>
       <c r="M456" s="74">
         <v>0.22670000000000001</v>
       </c>
       <c r="O456" s="4"/>
-      <c r="P456" s="80"/>
-      <c r="Q456" s="80"/>
-      <c r="R456" s="82"/>
-      <c r="S456" s="82"/>
-      <c r="T456" s="82"/>
-      <c r="U456" s="82"/>
-      <c r="V456" s="80"/>
       <c r="W456" s="4"/>
       <c r="X456" s="4"/>
       <c r="Y456" s="4"/>
@@ -54000,9 +53889,9 @@
       <c r="BB456" s="2"/>
       <c r="BC456" s="2"/>
       <c r="BD456" s="2"/>
-      <c r="BE456" s="83"/>
-      <c r="BF456" s="84"/>
-      <c r="BG456" s="85"/>
+      <c r="BE456" s="79"/>
+      <c r="BF456" s="80"/>
+      <c r="BG456" s="81"/>
       <c r="BH456" s="2"/>
       <c r="BI456" s="2"/>
       <c r="BJ456" s="3"/>
@@ -54020,28 +53909,21 @@
       <c r="D457" s="78">
         <v>2</v>
       </c>
-      <c r="E457" s="79" t="s">
+      <c r="E457" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F457" s="100" t="s">
+      <c r="F457" s="85" t="s">
         <v>635</v>
       </c>
       <c r="G457" s="4"/>
       <c r="H457" s="4"/>
-      <c r="I457" s="80"/>
-      <c r="K457" s="81"/>
-      <c r="L457" s="80"/>
+      <c r="I457" s="7"/>
+      <c r="K457" s="50"/>
+      <c r="L457" s="7"/>
       <c r="M457" s="74">
         <v>0.1993</v>
       </c>
       <c r="O457" s="4"/>
-      <c r="P457" s="80"/>
-      <c r="Q457" s="80"/>
-      <c r="R457" s="82"/>
-      <c r="S457" s="82"/>
-      <c r="T457" s="82"/>
-      <c r="U457" s="82"/>
-      <c r="V457" s="80"/>
       <c r="W457" s="4"/>
       <c r="X457" s="4"/>
       <c r="Y457" s="4"/>
@@ -54076,9 +53958,9 @@
       <c r="BB457" s="2"/>
       <c r="BC457" s="2"/>
       <c r="BD457" s="2"/>
-      <c r="BE457" s="83"/>
-      <c r="BF457" s="84"/>
-      <c r="BG457" s="85"/>
+      <c r="BE457" s="79"/>
+      <c r="BF457" s="80"/>
+      <c r="BG457" s="81"/>
       <c r="BH457" s="2"/>
       <c r="BI457" s="2"/>
       <c r="BJ457" s="3"/>
@@ -54096,28 +53978,21 @@
       <c r="D458" s="78">
         <v>3</v>
       </c>
-      <c r="E458" s="79" t="s">
+      <c r="E458" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F458" s="100" t="s">
+      <c r="F458" s="85" t="s">
         <v>634</v>
       </c>
       <c r="G458" s="4"/>
       <c r="H458" s="4"/>
-      <c r="I458" s="80"/>
-      <c r="K458" s="81"/>
-      <c r="L458" s="80"/>
+      <c r="I458" s="7"/>
+      <c r="K458" s="50"/>
+      <c r="L458" s="7"/>
       <c r="M458" s="74">
         <v>0.21279999999999999</v>
       </c>
       <c r="O458" s="4"/>
-      <c r="P458" s="80"/>
-      <c r="Q458" s="80"/>
-      <c r="R458" s="82"/>
-      <c r="S458" s="82"/>
-      <c r="T458" s="82"/>
-      <c r="U458" s="82"/>
-      <c r="V458" s="80"/>
       <c r="W458" s="4"/>
       <c r="X458" s="4"/>
       <c r="Y458" s="4"/>
@@ -54152,9 +54027,9 @@
       <c r="BB458" s="2"/>
       <c r="BC458" s="2"/>
       <c r="BD458" s="2"/>
-      <c r="BE458" s="83"/>
-      <c r="BF458" s="84"/>
-      <c r="BG458" s="85"/>
+      <c r="BE458" s="79"/>
+      <c r="BF458" s="80"/>
+      <c r="BG458" s="81"/>
       <c r="BH458" s="2"/>
       <c r="BI458" s="2"/>
       <c r="BJ458" s="3"/>
@@ -54172,28 +54047,21 @@
       <c r="D459" s="78">
         <v>4</v>
       </c>
-      <c r="E459" s="79" t="s">
+      <c r="E459" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F459" s="100" t="s">
+      <c r="F459" s="85" t="s">
         <v>635</v>
       </c>
       <c r="G459" s="4"/>
       <c r="H459" s="4"/>
-      <c r="I459" s="80"/>
-      <c r="K459" s="81"/>
-      <c r="L459" s="80"/>
+      <c r="I459" s="7"/>
+      <c r="K459" s="50"/>
+      <c r="L459" s="7"/>
       <c r="M459" s="74">
         <v>0.2039</v>
       </c>
       <c r="O459" s="4"/>
-      <c r="P459" s="80"/>
-      <c r="Q459" s="80"/>
-      <c r="R459" s="82"/>
-      <c r="S459" s="82"/>
-      <c r="T459" s="82"/>
-      <c r="U459" s="82"/>
-      <c r="V459" s="80"/>
       <c r="W459" s="4"/>
       <c r="X459" s="4"/>
       <c r="Y459" s="4"/>
@@ -54228,9 +54096,9 @@
       <c r="BB459" s="2"/>
       <c r="BC459" s="2"/>
       <c r="BD459" s="2"/>
-      <c r="BE459" s="83"/>
-      <c r="BF459" s="84"/>
-      <c r="BG459" s="85"/>
+      <c r="BE459" s="79"/>
+      <c r="BF459" s="80"/>
+      <c r="BG459" s="81"/>
       <c r="BH459" s="2"/>
       <c r="BI459" s="2"/>
       <c r="BJ459" s="3"/>
@@ -54248,28 +54116,21 @@
       <c r="D460" s="78">
         <v>1</v>
       </c>
-      <c r="E460" s="79" t="s">
+      <c r="E460" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F460" s="100" t="s">
+      <c r="F460" s="85" t="s">
         <v>634</v>
       </c>
       <c r="G460" s="4"/>
       <c r="H460" s="4"/>
-      <c r="I460" s="80"/>
-      <c r="K460" s="81"/>
-      <c r="L460" s="80"/>
+      <c r="I460" s="7"/>
+      <c r="K460" s="50"/>
+      <c r="L460" s="7"/>
       <c r="M460" s="74">
         <v>0.2145</v>
       </c>
       <c r="O460" s="4"/>
-      <c r="P460" s="80"/>
-      <c r="Q460" s="80"/>
-      <c r="R460" s="82"/>
-      <c r="S460" s="82"/>
-      <c r="T460" s="82"/>
-      <c r="U460" s="82"/>
-      <c r="V460" s="80"/>
       <c r="W460" s="4"/>
       <c r="X460" s="4"/>
       <c r="Y460" s="4"/>
@@ -54304,9 +54165,9 @@
       <c r="BB460" s="2"/>
       <c r="BC460" s="2"/>
       <c r="BD460" s="2"/>
-      <c r="BE460" s="83"/>
-      <c r="BF460" s="84"/>
-      <c r="BG460" s="85"/>
+      <c r="BE460" s="79"/>
+      <c r="BF460" s="80"/>
+      <c r="BG460" s="81"/>
       <c r="BH460" s="2"/>
       <c r="BI460" s="2"/>
       <c r="BJ460" s="3"/>
@@ -54324,28 +54185,21 @@
       <c r="D461" s="78">
         <v>2</v>
       </c>
-      <c r="E461" s="79" t="s">
+      <c r="E461" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F461" s="100" t="s">
+      <c r="F461" s="85" t="s">
         <v>635</v>
       </c>
       <c r="G461" s="4"/>
       <c r="H461" s="4"/>
-      <c r="I461" s="80"/>
-      <c r="K461" s="81"/>
-      <c r="L461" s="80"/>
+      <c r="I461" s="7"/>
+      <c r="K461" s="50"/>
+      <c r="L461" s="7"/>
       <c r="M461" s="74">
         <v>0.21629999999999999</v>
       </c>
       <c r="O461" s="4"/>
-      <c r="P461" s="80"/>
-      <c r="Q461" s="80"/>
-      <c r="R461" s="82"/>
-      <c r="S461" s="82"/>
-      <c r="T461" s="82"/>
-      <c r="U461" s="82"/>
-      <c r="V461" s="80"/>
       <c r="W461" s="4"/>
       <c r="X461" s="4"/>
       <c r="Y461" s="4"/>
@@ -54380,9 +54234,9 @@
       <c r="BB461" s="2"/>
       <c r="BC461" s="2"/>
       <c r="BD461" s="2"/>
-      <c r="BE461" s="83"/>
-      <c r="BF461" s="84"/>
-      <c r="BG461" s="85"/>
+      <c r="BE461" s="79"/>
+      <c r="BF461" s="80"/>
+      <c r="BG461" s="81"/>
       <c r="BH461" s="2"/>
       <c r="BI461" s="2"/>
       <c r="BJ461" s="3"/>
@@ -54400,28 +54254,21 @@
       <c r="D462" s="78">
         <v>3</v>
       </c>
-      <c r="E462" s="79" t="s">
+      <c r="E462" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F462" s="100" t="s">
+      <c r="F462" s="85" t="s">
         <v>634</v>
       </c>
       <c r="G462" s="4"/>
       <c r="H462" s="4"/>
-      <c r="I462" s="80"/>
-      <c r="K462" s="81"/>
-      <c r="L462" s="80"/>
+      <c r="I462" s="7"/>
+      <c r="K462" s="50"/>
+      <c r="L462" s="7"/>
       <c r="M462" s="74">
         <v>0.2185</v>
       </c>
       <c r="O462" s="4"/>
-      <c r="P462" s="80"/>
-      <c r="Q462" s="80"/>
-      <c r="R462" s="82"/>
-      <c r="S462" s="82"/>
-      <c r="T462" s="82"/>
-      <c r="U462" s="82"/>
-      <c r="V462" s="80"/>
       <c r="W462" s="4"/>
       <c r="X462" s="4"/>
       <c r="Y462" s="4"/>
@@ -54456,90 +54303,81 @@
       <c r="BB462" s="2"/>
       <c r="BC462" s="2"/>
       <c r="BD462" s="2"/>
-      <c r="BE462" s="83"/>
-      <c r="BF462" s="84"/>
-      <c r="BG462" s="85"/>
+      <c r="BE462" s="79"/>
+      <c r="BF462" s="80"/>
+      <c r="BG462" s="81"/>
       <c r="BH462" s="2"/>
       <c r="BI462" s="2"/>
       <c r="BJ462" s="3"/>
     </row>
     <row r="463" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A463" s="86" t="s">
+      <c r="A463" s="75" t="s">
         <v>629</v>
       </c>
-      <c r="B463" s="87" t="s">
+      <c r="B463" s="76" t="s">
         <v>633</v>
       </c>
-      <c r="C463" s="88">
+      <c r="C463" s="77">
         <v>45384</v>
       </c>
-      <c r="D463" s="89">
+      <c r="D463" s="78">
         <v>4</v>
       </c>
-      <c r="E463" s="79" t="s">
+      <c r="E463" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F463" s="100" t="s">
+      <c r="F463" s="85" t="s">
         <v>635</v>
       </c>
-      <c r="G463" s="90"/>
-      <c r="H463" s="90"/>
-      <c r="I463" s="91"/>
-      <c r="J463" s="92"/>
-      <c r="K463" s="93"/>
-      <c r="L463" s="91"/>
+      <c r="G463" s="4"/>
+      <c r="H463" s="4"/>
+      <c r="I463" s="7"/>
+      <c r="K463" s="50"/>
+      <c r="L463" s="7"/>
       <c r="M463" s="74">
         <v>0.216</v>
       </c>
-      <c r="N463" s="92"/>
-      <c r="O463" s="90"/>
-      <c r="P463" s="91"/>
-      <c r="Q463" s="91"/>
-      <c r="R463" s="94"/>
-      <c r="S463" s="94"/>
-      <c r="T463" s="82"/>
-      <c r="U463" s="82"/>
-      <c r="V463" s="80"/>
-      <c r="W463" s="90"/>
-      <c r="X463" s="90"/>
-      <c r="Y463" s="90"/>
-      <c r="Z463" s="92"/>
-      <c r="AA463" s="92"/>
-      <c r="AB463" s="92"/>
-      <c r="AC463" s="92"/>
-      <c r="AD463" s="92"/>
-      <c r="AE463" s="92"/>
-      <c r="AF463" s="92"/>
-      <c r="AG463" s="92"/>
-      <c r="AH463" s="92"/>
-      <c r="AI463" s="92"/>
-      <c r="AJ463" s="92"/>
-      <c r="AK463" s="92"/>
-      <c r="AL463" s="92"/>
-      <c r="AM463" s="92"/>
-      <c r="AN463" s="92"/>
-      <c r="AO463" s="92"/>
-      <c r="AP463" s="92"/>
-      <c r="AQ463" s="92"/>
-      <c r="AR463" s="92"/>
-      <c r="AS463" s="92"/>
-      <c r="AT463" s="92"/>
-      <c r="AU463" s="92"/>
-      <c r="AV463" s="92"/>
-      <c r="AW463" s="90"/>
-      <c r="AX463" s="95"/>
-      <c r="AY463" s="92"/>
-      <c r="AZ463" s="90"/>
-      <c r="BA463" s="90"/>
-      <c r="BB463" s="95"/>
-      <c r="BC463" s="95"/>
-      <c r="BD463" s="95"/>
-      <c r="BE463" s="96"/>
-      <c r="BF463" s="97"/>
-      <c r="BG463" s="98"/>
-      <c r="BH463" s="95"/>
-      <c r="BI463" s="95"/>
-      <c r="BJ463" s="99"/>
+      <c r="O463" s="4"/>
+      <c r="W463" s="4"/>
+      <c r="X463" s="4"/>
+      <c r="Y463" s="4"/>
+      <c r="Z463" s="7"/>
+      <c r="AA463" s="7"/>
+      <c r="AB463" s="7"/>
+      <c r="AC463" s="7"/>
+      <c r="AD463" s="7"/>
+      <c r="AE463" s="7"/>
+      <c r="AF463" s="7"/>
+      <c r="AG463" s="7"/>
+      <c r="AH463" s="7"/>
+      <c r="AI463" s="7"/>
+      <c r="AJ463" s="7"/>
+      <c r="AK463" s="7"/>
+      <c r="AL463" s="7"/>
+      <c r="AM463" s="7"/>
+      <c r="AN463" s="7"/>
+      <c r="AO463" s="7"/>
+      <c r="AP463" s="7"/>
+      <c r="AQ463" s="7"/>
+      <c r="AR463" s="7"/>
+      <c r="AS463" s="7"/>
+      <c r="AT463" s="7"/>
+      <c r="AU463" s="7"/>
+      <c r="AV463" s="7"/>
+      <c r="AW463" s="4"/>
+      <c r="AX463" s="2"/>
+      <c r="AY463" s="7"/>
+      <c r="AZ463" s="4"/>
+      <c r="BA463" s="4"/>
+      <c r="BB463" s="2"/>
+      <c r="BC463" s="2"/>
+      <c r="BD463" s="2"/>
+      <c r="BE463" s="82"/>
+      <c r="BF463" s="83"/>
+      <c r="BG463" s="84"/>
+      <c r="BH463" s="2"/>
+      <c r="BI463" s="2"/>
+      <c r="BJ463" s="3"/>
     </row>
     <row r="464" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A464" s="75" t="s">
@@ -54554,7 +54392,7 @@
       <c r="D464" s="78">
         <v>1</v>
       </c>
-      <c r="E464" s="101" t="s">
+      <c r="E464" s="75" t="s">
         <v>636</v>
       </c>
       <c r="F464" s="74" t="s">
@@ -54569,28 +54407,27 @@
       <c r="I464" s="74">
         <v>0.16189999999999999</v>
       </c>
-      <c r="J464" s="74">
+      <c r="K464" s="88">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="K464" s="74">
-        <v>1.2569999999999999</v>
-      </c>
-      <c r="L464" s="80"/>
+      <c r="L464" s="7"/>
       <c r="M464" s="74">
         <v>0.16270000000000001</v>
       </c>
+      <c r="N464" s="7">
+        <v>-0.45</v>
+      </c>
       <c r="O464" s="4"/>
-      <c r="P464" s="80"/>
-      <c r="Q464" s="80"/>
-      <c r="R464" s="82"/>
-      <c r="S464" s="82"/>
-      <c r="T464" s="104">
+      <c r="P464" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="T464" s="87">
         <v>64.599999999999994</v>
       </c>
-      <c r="U464" s="104">
+      <c r="U464" s="87">
         <v>592</v>
       </c>
-      <c r="V464" s="105">
+      <c r="V464" s="87">
         <v>754.2</v>
       </c>
       <c r="W464" s="74" t="s">
@@ -54629,9 +54466,9 @@
       <c r="BB464" s="2"/>
       <c r="BC464" s="2"/>
       <c r="BD464" s="2"/>
-      <c r="BE464" s="83"/>
-      <c r="BF464" s="84"/>
-      <c r="BG464" s="85"/>
+      <c r="BE464" s="79"/>
+      <c r="BF464" s="80"/>
+      <c r="BG464" s="81"/>
       <c r="BH464" s="2"/>
       <c r="BI464" s="2"/>
       <c r="BJ464" s="3"/>
@@ -54649,7 +54486,7 @@
       <c r="D465" s="78">
         <v>2</v>
       </c>
-      <c r="E465" s="101" t="s">
+      <c r="E465" s="75" t="s">
         <v>637</v>
       </c>
       <c r="F465" s="74" t="s">
@@ -54664,28 +54501,30 @@
       <c r="I465" s="74">
         <v>0.1633</v>
       </c>
-      <c r="J465" s="74">
+      <c r="J465" s="7">
+        <v>0.1613</v>
+      </c>
+      <c r="K465" s="88">
         <v>5.5999999999999999E-3</v>
       </c>
-      <c r="K465" s="74">
-        <v>1.2569999999999999</v>
-      </c>
-      <c r="L465" s="80"/>
+      <c r="L465" s="7"/>
       <c r="M465" s="74">
         <v>0.15959999999999999</v>
       </c>
+      <c r="N465" s="7">
+        <v>-0.61</v>
+      </c>
       <c r="O465" s="4"/>
-      <c r="P465" s="80"/>
-      <c r="Q465" s="80"/>
-      <c r="R465" s="82"/>
-      <c r="S465" s="82"/>
-      <c r="T465" s="104">
+      <c r="P465" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="T465" s="87">
         <v>65</v>
       </c>
-      <c r="U465" s="104">
+      <c r="U465" s="87">
         <v>578</v>
       </c>
-      <c r="V465" s="105">
+      <c r="V465" s="87">
         <v>754.1</v>
       </c>
       <c r="W465" s="74" t="s">
@@ -54724,9 +54563,9 @@
       <c r="BB465" s="2"/>
       <c r="BC465" s="2"/>
       <c r="BD465" s="2"/>
-      <c r="BE465" s="83"/>
-      <c r="BF465" s="84"/>
-      <c r="BG465" s="85"/>
+      <c r="BE465" s="79"/>
+      <c r="BF465" s="80"/>
+      <c r="BG465" s="81"/>
       <c r="BH465" s="2"/>
       <c r="BI465" s="2"/>
       <c r="BJ465" s="3"/>
@@ -54744,7 +54583,7 @@
       <c r="D466" s="78">
         <v>3</v>
       </c>
-      <c r="E466" s="101" t="s">
+      <c r="E466" s="75" t="s">
         <v>638</v>
       </c>
       <c r="F466" s="74" t="s">
@@ -54759,28 +54598,30 @@
       <c r="I466" s="74">
         <v>0.16070000000000001</v>
       </c>
-      <c r="J466" s="74">
+      <c r="J466" s="7">
+        <v>0.15859999999999999</v>
+      </c>
+      <c r="K466" s="88">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="K466" s="74">
-        <v>1.2569999999999999</v>
-      </c>
-      <c r="L466" s="80"/>
+      <c r="L466" s="7"/>
       <c r="M466" s="74">
         <v>0.15870000000000001</v>
       </c>
+      <c r="N466" s="7">
+        <v>-0.61</v>
+      </c>
       <c r="O466" s="4"/>
-      <c r="P466" s="80"/>
-      <c r="Q466" s="80"/>
-      <c r="R466" s="82"/>
-      <c r="S466" s="82"/>
-      <c r="T466" s="104">
+      <c r="P466" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="T466" s="87">
         <v>65.8</v>
       </c>
-      <c r="U466" s="104">
+      <c r="U466" s="87">
         <v>594</v>
       </c>
-      <c r="V466" s="105">
+      <c r="V466" s="87">
         <v>754.9</v>
       </c>
       <c r="W466" s="74" t="s">
@@ -54819,9 +54660,9 @@
       <c r="BB466" s="2"/>
       <c r="BC466" s="2"/>
       <c r="BD466" s="2"/>
-      <c r="BE466" s="83"/>
-      <c r="BF466" s="84"/>
-      <c r="BG466" s="85"/>
+      <c r="BE466" s="79"/>
+      <c r="BF466" s="80"/>
+      <c r="BG466" s="81"/>
       <c r="BH466" s="2"/>
       <c r="BI466" s="2"/>
       <c r="BJ466" s="3"/>
@@ -54839,7 +54680,7 @@
       <c r="D467" s="78">
         <v>4</v>
       </c>
-      <c r="E467" s="101" t="s">
+      <c r="E467" s="75" t="s">
         <v>639</v>
       </c>
       <c r="F467" s="74" t="s">
@@ -54855,27 +54696,29 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="J467" s="74">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="K467" s="88">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="K467" s="74">
-        <v>1.2569999999999999</v>
-      </c>
-      <c r="L467" s="80"/>
+      <c r="L467" s="7"/>
       <c r="M467" s="74">
         <v>0.1618</v>
       </c>
+      <c r="N467" s="7">
+        <v>-0.56999999999999995</v>
+      </c>
       <c r="O467" s="4"/>
-      <c r="P467" s="80"/>
-      <c r="Q467" s="80"/>
-      <c r="R467" s="82"/>
-      <c r="S467" s="82"/>
-      <c r="T467" s="104">
+      <c r="P467" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="T467" s="87">
         <v>64.8</v>
       </c>
-      <c r="U467" s="104">
+      <c r="U467" s="87">
         <v>590</v>
       </c>
-      <c r="V467" s="105">
+      <c r="V467" s="87">
         <v>754.3</v>
       </c>
       <c r="W467" s="74" t="s">
@@ -54914,9 +54757,9 @@
       <c r="BB467" s="2"/>
       <c r="BC467" s="2"/>
       <c r="BD467" s="2"/>
-      <c r="BE467" s="83"/>
-      <c r="BF467" s="84"/>
-      <c r="BG467" s="85"/>
+      <c r="BE467" s="79"/>
+      <c r="BF467" s="80"/>
+      <c r="BG467" s="81"/>
       <c r="BH467" s="2"/>
       <c r="BI467" s="2"/>
       <c r="BJ467" s="3"/>
@@ -54934,7 +54777,7 @@
       <c r="D468" s="78">
         <v>5</v>
       </c>
-      <c r="E468" s="101" t="s">
+      <c r="E468" s="75" t="s">
         <v>636</v>
       </c>
       <c r="F468" s="74" t="s">
@@ -54950,27 +54793,29 @@
         <v>0.1636</v>
       </c>
       <c r="J468" s="74">
+        <v>0.1636</v>
+      </c>
+      <c r="K468" s="88">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="K468" s="74">
-        <v>1.2569999999999999</v>
-      </c>
-      <c r="L468" s="80"/>
+      <c r="L468" s="7"/>
       <c r="M468" s="74">
         <v>0.16400000000000001</v>
       </c>
+      <c r="N468" s="7">
+        <v>-0.56999999999999995</v>
+      </c>
       <c r="O468" s="4"/>
-      <c r="P468" s="80"/>
-      <c r="Q468" s="80"/>
-      <c r="R468" s="82"/>
-      <c r="S468" s="82"/>
-      <c r="T468" s="104">
+      <c r="P468" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="T468" s="87">
         <v>64.900000000000006</v>
       </c>
-      <c r="U468" s="104">
+      <c r="U468" s="87">
         <v>589</v>
       </c>
-      <c r="V468" s="105">
+      <c r="V468" s="87">
         <v>754.5</v>
       </c>
       <c r="W468" s="74" t="s">
@@ -55009,9 +54854,9 @@
       <c r="BB468" s="2"/>
       <c r="BC468" s="2"/>
       <c r="BD468" s="2"/>
-      <c r="BE468" s="83"/>
-      <c r="BF468" s="84"/>
-      <c r="BG468" s="85"/>
+      <c r="BE468" s="79"/>
+      <c r="BF468" s="80"/>
+      <c r="BG468" s="81"/>
       <c r="BH468" s="2"/>
       <c r="BI468" s="2"/>
       <c r="BJ468" s="3"/>
@@ -55029,7 +54874,7 @@
       <c r="D469" s="78">
         <v>6</v>
       </c>
-      <c r="E469" s="101" t="s">
+      <c r="E469" s="75" t="s">
         <v>637</v>
       </c>
       <c r="F469" s="74" t="s">
@@ -55044,28 +54889,30 @@
       <c r="I469" s="74">
         <v>0.1643</v>
       </c>
-      <c r="J469" s="74">
+      <c r="J469" s="7">
+        <v>0.1623</v>
+      </c>
+      <c r="K469" s="88">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="K469" s="74">
-        <v>1.2569999999999999</v>
-      </c>
-      <c r="L469" s="80"/>
+      <c r="L469" s="7"/>
       <c r="M469" s="74">
         <v>0.15909999999999999</v>
       </c>
+      <c r="N469" s="7">
+        <v>-0.61</v>
+      </c>
       <c r="O469" s="4"/>
-      <c r="P469" s="80"/>
-      <c r="Q469" s="80"/>
-      <c r="R469" s="82"/>
-      <c r="S469" s="82"/>
-      <c r="T469" s="104">
+      <c r="P469" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="T469" s="87">
         <v>65.3</v>
       </c>
-      <c r="U469" s="104">
+      <c r="U469" s="87">
         <v>582</v>
       </c>
-      <c r="V469" s="105">
+      <c r="V469" s="87">
         <v>754.7</v>
       </c>
       <c r="W469" s="74" t="s">
@@ -55104,9 +54951,9 @@
       <c r="BB469" s="2"/>
       <c r="BC469" s="2"/>
       <c r="BD469" s="2"/>
-      <c r="BE469" s="83"/>
-      <c r="BF469" s="84"/>
-      <c r="BG469" s="85"/>
+      <c r="BE469" s="79"/>
+      <c r="BF469" s="80"/>
+      <c r="BG469" s="81"/>
       <c r="BH469" s="2"/>
       <c r="BI469" s="2"/>
       <c r="BJ469" s="3"/>
@@ -55124,7 +54971,7 @@
       <c r="D470" s="78">
         <v>7</v>
       </c>
-      <c r="E470" s="101" t="s">
+      <c r="E470" s="75" t="s">
         <v>638</v>
       </c>
       <c r="F470" s="74" t="s">
@@ -55139,28 +54986,30 @@
       <c r="I470" s="74">
         <v>0.16339999999999999</v>
       </c>
-      <c r="J470" s="74">
+      <c r="J470" s="7">
+        <v>0.1613</v>
+      </c>
+      <c r="K470" s="88">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="K470" s="74">
-        <v>1.2569999999999999</v>
-      </c>
-      <c r="L470" s="80"/>
+      <c r="L470" s="7"/>
       <c r="M470" s="74">
         <v>0.16120000000000001</v>
       </c>
+      <c r="N470" s="7">
+        <v>-0.62</v>
+      </c>
       <c r="O470" s="4"/>
-      <c r="P470" s="80"/>
-      <c r="Q470" s="80"/>
-      <c r="R470" s="82"/>
-      <c r="S470" s="82"/>
-      <c r="T470" s="104">
+      <c r="P470" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="T470" s="87">
         <v>65.3</v>
       </c>
-      <c r="U470" s="104">
+      <c r="U470" s="87">
         <v>596</v>
       </c>
-      <c r="V470" s="105">
+      <c r="V470" s="87">
         <v>754.6</v>
       </c>
       <c r="W470" s="74" t="s">
@@ -55199,9 +55048,9 @@
       <c r="BB470" s="2"/>
       <c r="BC470" s="2"/>
       <c r="BD470" s="2"/>
-      <c r="BE470" s="83"/>
-      <c r="BF470" s="84"/>
-      <c r="BG470" s="85"/>
+      <c r="BE470" s="79"/>
+      <c r="BF470" s="80"/>
+      <c r="BG470" s="81"/>
       <c r="BH470" s="2"/>
       <c r="BI470" s="2"/>
       <c r="BJ470" s="3"/>
@@ -55219,7 +55068,7 @@
       <c r="D471" s="78">
         <v>8</v>
       </c>
-      <c r="E471" s="101" t="s">
+      <c r="E471" s="75" t="s">
         <v>639</v>
       </c>
       <c r="F471" s="74" t="s">
@@ -55235,27 +55084,29 @@
         <v>0.1658</v>
       </c>
       <c r="J471" s="74">
+        <v>0.1658</v>
+      </c>
+      <c r="K471" s="88">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="K471" s="74">
-        <v>1.2569999999999999</v>
-      </c>
-      <c r="L471" s="80"/>
+      <c r="L471" s="7"/>
       <c r="M471" s="74">
         <v>0.16500000000000001</v>
       </c>
+      <c r="N471" s="7">
+        <v>-0.59</v>
+      </c>
       <c r="O471" s="4"/>
-      <c r="P471" s="80"/>
-      <c r="Q471" s="80"/>
-      <c r="R471" s="82"/>
-      <c r="S471" s="82"/>
-      <c r="T471" s="104">
+      <c r="P471" s="74">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="T471" s="87">
         <v>65</v>
       </c>
-      <c r="U471" s="104">
+      <c r="U471" s="87">
         <v>591</v>
       </c>
-      <c r="V471" s="105">
+      <c r="V471" s="87">
         <v>754.3</v>
       </c>
       <c r="W471" s="74" t="s">
@@ -55294,9 +55145,9 @@
       <c r="BB471" s="2"/>
       <c r="BC471" s="2"/>
       <c r="BD471" s="2"/>
-      <c r="BE471" s="83"/>
-      <c r="BF471" s="84"/>
-      <c r="BG471" s="85"/>
+      <c r="BE471" s="79"/>
+      <c r="BF471" s="80"/>
+      <c r="BG471" s="81"/>
       <c r="BH471" s="2"/>
       <c r="BI471" s="2"/>
       <c r="BJ471" s="3"/>
@@ -55314,7 +55165,7 @@
       <c r="D472" s="78">
         <v>1</v>
       </c>
-      <c r="E472" s="101" t="s">
+      <c r="E472" s="75" t="s">
         <v>640</v>
       </c>
       <c r="F472" s="74" t="s">
@@ -55330,27 +55181,29 @@
         <v>0.15079999999999999</v>
       </c>
       <c r="J472" s="74">
+        <v>0.15079999999999999</v>
+      </c>
+      <c r="K472" s="88">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="K472" s="74">
-        <v>1.22</v>
-      </c>
-      <c r="L472" s="80"/>
+      <c r="L472" s="7"/>
       <c r="M472" s="74">
         <v>0.14480000000000001</v>
       </c>
+      <c r="N472" s="7">
+        <v>-0.64</v>
+      </c>
       <c r="O472" s="4"/>
-      <c r="P472" s="80"/>
-      <c r="Q472" s="80"/>
-      <c r="R472" s="82"/>
-      <c r="S472" s="82"/>
-      <c r="T472" s="104">
+      <c r="P472" s="74">
+        <v>1.22</v>
+      </c>
+      <c r="T472" s="87">
         <v>57.7</v>
       </c>
-      <c r="U472" s="104">
+      <c r="U472" s="87">
         <v>395</v>
       </c>
-      <c r="V472" s="105">
+      <c r="V472" s="87">
         <v>755</v>
       </c>
       <c r="W472" s="74" t="s">
@@ -55389,9 +55242,9 @@
       <c r="BB472" s="2"/>
       <c r="BC472" s="2"/>
       <c r="BD472" s="2"/>
-      <c r="BE472" s="83"/>
-      <c r="BF472" s="84"/>
-      <c r="BG472" s="85"/>
+      <c r="BE472" s="79"/>
+      <c r="BF472" s="80"/>
+      <c r="BG472" s="81"/>
       <c r="BH472" s="2"/>
       <c r="BI472" s="2"/>
       <c r="BJ472" s="3"/>
@@ -55409,7 +55262,7 @@
       <c r="D473" s="78">
         <v>2</v>
       </c>
-      <c r="E473" s="101" t="s">
+      <c r="E473" s="75" t="s">
         <v>640</v>
       </c>
       <c r="F473" s="74" t="s">
@@ -55425,27 +55278,29 @@
         <v>0.1517</v>
       </c>
       <c r="J473" s="74">
+        <v>0.1517</v>
+      </c>
+      <c r="K473" s="88">
         <v>2.8E-3</v>
       </c>
-      <c r="K473" s="74">
-        <v>1.22</v>
-      </c>
-      <c r="L473" s="80"/>
+      <c r="L473" s="7"/>
       <c r="M473" s="74">
         <v>0.14630000000000001</v>
       </c>
+      <c r="N473" s="7">
+        <v>-0.69</v>
+      </c>
       <c r="O473" s="4"/>
-      <c r="P473" s="80"/>
-      <c r="Q473" s="80"/>
-      <c r="R473" s="82"/>
-      <c r="S473" s="82"/>
-      <c r="T473" s="104">
+      <c r="P473" s="74">
+        <v>1.22</v>
+      </c>
+      <c r="T473" s="87">
         <v>61.2</v>
       </c>
-      <c r="U473" s="104">
+      <c r="U473" s="87">
         <v>445</v>
       </c>
-      <c r="V473" s="105">
+      <c r="V473" s="87">
         <v>755.5</v>
       </c>
       <c r="W473" s="74" t="s">
@@ -55484,9 +55339,9 @@
       <c r="BB473" s="2"/>
       <c r="BC473" s="2"/>
       <c r="BD473" s="2"/>
-      <c r="BE473" s="83"/>
-      <c r="BF473" s="84"/>
-      <c r="BG473" s="85"/>
+      <c r="BE473" s="79"/>
+      <c r="BF473" s="80"/>
+      <c r="BG473" s="81"/>
       <c r="BH473" s="2"/>
       <c r="BI473" s="2"/>
       <c r="BJ473" s="3"/>
@@ -55504,7 +55359,7 @@
       <c r="D474" s="78">
         <v>3</v>
       </c>
-      <c r="E474" s="101" t="s">
+      <c r="E474" s="75" t="s">
         <v>640</v>
       </c>
       <c r="F474" s="74" t="s">
@@ -55516,27 +55371,25 @@
       <c r="H474" s="74" t="s">
         <v>223</v>
       </c>
-      <c r="I474" s="103"/>
-      <c r="J474" s="103"/>
-      <c r="K474" s="74">
-        <v>1.22</v>
-      </c>
-      <c r="L474" s="80"/>
+      <c r="I474" s="86"/>
+      <c r="J474" s="86"/>
+      <c r="K474" s="89"/>
+      <c r="L474" s="7"/>
       <c r="M474" s="74">
         <v>0.14910000000000001</v>
       </c>
+      <c r="N474" s="89"/>
       <c r="O474" s="4"/>
-      <c r="P474" s="80"/>
-      <c r="Q474" s="80"/>
-      <c r="R474" s="82"/>
-      <c r="S474" s="82"/>
-      <c r="T474" s="104">
+      <c r="P474" s="74">
+        <v>1.22</v>
+      </c>
+      <c r="T474" s="87">
         <v>61.2</v>
       </c>
-      <c r="U474" s="104">
+      <c r="U474" s="87">
         <v>453</v>
       </c>
-      <c r="V474" s="105">
+      <c r="V474" s="87">
         <v>755.3</v>
       </c>
       <c r="W474" s="74" t="s">
@@ -55575,9 +55428,9 @@
       <c r="BB474" s="2"/>
       <c r="BC474" s="2"/>
       <c r="BD474" s="2"/>
-      <c r="BE474" s="83"/>
-      <c r="BF474" s="84"/>
-      <c r="BG474" s="85"/>
+      <c r="BE474" s="79"/>
+      <c r="BF474" s="80"/>
+      <c r="BG474" s="81"/>
       <c r="BH474" s="2"/>
       <c r="BI474" s="2"/>
       <c r="BJ474" s="3"/>
@@ -55595,7 +55448,7 @@
       <c r="D475" s="78">
         <v>4</v>
       </c>
-      <c r="E475" s="101" t="s">
+      <c r="E475" s="75" t="s">
         <v>640</v>
       </c>
       <c r="F475" s="74" t="s">
@@ -55611,27 +55464,29 @@
         <v>0.15240000000000001</v>
       </c>
       <c r="J475" s="74">
+        <v>0.15240000000000001</v>
+      </c>
+      <c r="K475" s="88">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="K475" s="74">
-        <v>1.22</v>
-      </c>
-      <c r="L475" s="80"/>
+      <c r="L475" s="7"/>
       <c r="M475" s="74">
         <v>0.14899999999999999</v>
       </c>
+      <c r="N475" s="7">
+        <v>-0.69</v>
+      </c>
       <c r="O475" s="4"/>
-      <c r="P475" s="80"/>
-      <c r="Q475" s="80"/>
-      <c r="R475" s="82"/>
-      <c r="S475" s="82"/>
-      <c r="T475" s="104">
+      <c r="P475" s="74">
+        <v>1.22</v>
+      </c>
+      <c r="T475" s="87">
         <v>62.2</v>
       </c>
-      <c r="U475" s="104">
+      <c r="U475" s="87">
         <v>470</v>
       </c>
-      <c r="V475" s="105">
+      <c r="V475" s="87">
         <v>755.4</v>
       </c>
       <c r="W475" s="74" t="s">
@@ -55670,9 +55525,9 @@
       <c r="BB475" s="2"/>
       <c r="BC475" s="2"/>
       <c r="BD475" s="2"/>
-      <c r="BE475" s="83"/>
-      <c r="BF475" s="84"/>
-      <c r="BG475" s="85"/>
+      <c r="BE475" s="79"/>
+      <c r="BF475" s="80"/>
+      <c r="BG475" s="81"/>
       <c r="BH475" s="2"/>
       <c r="BI475" s="2"/>
       <c r="BJ475" s="3"/>
@@ -55690,7 +55545,7 @@
       <c r="D476" s="78">
         <v>5</v>
       </c>
-      <c r="E476" s="101" t="s">
+      <c r="E476" s="75" t="s">
         <v>640</v>
       </c>
       <c r="F476" s="74" t="s">
@@ -55706,27 +55561,29 @@
         <v>0.1545</v>
       </c>
       <c r="J476" s="74">
+        <v>0.1545</v>
+      </c>
+      <c r="K476" s="88">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="K476" s="74">
-        <v>1.22</v>
-      </c>
-      <c r="L476" s="80"/>
+      <c r="L476" s="7"/>
       <c r="M476" s="74">
         <v>0.1487</v>
       </c>
+      <c r="N476" s="7">
+        <v>-0.67</v>
+      </c>
       <c r="O476" s="4"/>
-      <c r="P476" s="80"/>
-      <c r="Q476" s="80"/>
-      <c r="R476" s="82"/>
-      <c r="S476" s="82"/>
-      <c r="T476" s="104">
+      <c r="P476" s="74">
+        <v>1.22</v>
+      </c>
+      <c r="T476" s="87">
         <v>61.8</v>
       </c>
-      <c r="U476" s="104">
+      <c r="U476" s="87">
         <v>444</v>
       </c>
-      <c r="V476" s="105">
+      <c r="V476" s="87">
         <v>755.4</v>
       </c>
       <c r="W476" s="74" t="s">
@@ -55765,27 +55622,27 @@
       <c r="BB476" s="2"/>
       <c r="BC476" s="2"/>
       <c r="BD476" s="2"/>
-      <c r="BE476" s="83"/>
-      <c r="BF476" s="84"/>
-      <c r="BG476" s="85"/>
+      <c r="BE476" s="79"/>
+      <c r="BF476" s="80"/>
+      <c r="BG476" s="81"/>
       <c r="BH476" s="2"/>
       <c r="BI476" s="2"/>
       <c r="BJ476" s="3"/>
     </row>
     <row r="477" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A477" s="86" t="s">
+      <c r="A477" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="B477" s="87" t="s">
+      <c r="B477" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="C477" s="88">
+      <c r="C477" s="77">
         <v>45400</v>
       </c>
-      <c r="D477" s="89">
+      <c r="D477" s="78">
         <v>6</v>
       </c>
-      <c r="E477" s="102" t="s">
+      <c r="E477" s="75" t="s">
         <v>640</v>
       </c>
       <c r="F477" s="74" t="s">
@@ -55801,21 +55658,22 @@
         <v>0.15720000000000001</v>
       </c>
       <c r="J477" s="74">
+        <v>0.15720000000000001</v>
+      </c>
+      <c r="K477" s="88">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="K477" s="74">
-        <v>1.22</v>
-      </c>
-      <c r="L477" s="91"/>
+      <c r="L477" s="7"/>
       <c r="M477" s="74">
         <v>0.14979999999999999</v>
       </c>
-      <c r="N477" s="92"/>
-      <c r="O477" s="90"/>
-      <c r="P477" s="91"/>
-      <c r="Q477" s="91"/>
-      <c r="R477" s="94"/>
-      <c r="S477" s="94"/>
+      <c r="N477" s="7">
+        <v>-0.7</v>
+      </c>
+      <c r="O477" s="4"/>
+      <c r="P477" s="74">
+        <v>1.22</v>
+      </c>
       <c r="T477" s="74">
         <v>60.8</v>
       </c>
@@ -55828,45 +55686,45 @@
       <c r="W477" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="X477" s="90"/>
-      <c r="Y477" s="90"/>
-      <c r="Z477" s="92"/>
-      <c r="AA477" s="92"/>
-      <c r="AB477" s="92"/>
-      <c r="AC477" s="92"/>
-      <c r="AD477" s="92"/>
-      <c r="AE477" s="92"/>
-      <c r="AF477" s="92"/>
-      <c r="AG477" s="92"/>
-      <c r="AH477" s="92"/>
-      <c r="AI477" s="92"/>
-      <c r="AJ477" s="92"/>
-      <c r="AK477" s="92"/>
-      <c r="AL477" s="92"/>
-      <c r="AM477" s="92"/>
-      <c r="AN477" s="92"/>
-      <c r="AO477" s="92"/>
-      <c r="AP477" s="92"/>
-      <c r="AQ477" s="92"/>
-      <c r="AR477" s="92"/>
-      <c r="AS477" s="92"/>
-      <c r="AT477" s="92"/>
-      <c r="AU477" s="92"/>
-      <c r="AV477" s="92"/>
-      <c r="AW477" s="90"/>
-      <c r="AX477" s="95"/>
-      <c r="AY477" s="92"/>
-      <c r="AZ477" s="90"/>
-      <c r="BA477" s="90"/>
-      <c r="BB477" s="95"/>
-      <c r="BC477" s="95"/>
-      <c r="BD477" s="95"/>
-      <c r="BE477" s="96"/>
-      <c r="BF477" s="97"/>
-      <c r="BG477" s="98"/>
-      <c r="BH477" s="95"/>
-      <c r="BI477" s="95"/>
-      <c r="BJ477" s="99"/>
+      <c r="X477" s="4"/>
+      <c r="Y477" s="4"/>
+      <c r="Z477" s="7"/>
+      <c r="AA477" s="7"/>
+      <c r="AB477" s="7"/>
+      <c r="AC477" s="7"/>
+      <c r="AD477" s="7"/>
+      <c r="AE477" s="7"/>
+      <c r="AF477" s="7"/>
+      <c r="AG477" s="7"/>
+      <c r="AH477" s="7"/>
+      <c r="AI477" s="7"/>
+      <c r="AJ477" s="7"/>
+      <c r="AK477" s="7"/>
+      <c r="AL477" s="7"/>
+      <c r="AM477" s="7"/>
+      <c r="AN477" s="7"/>
+      <c r="AO477" s="7"/>
+      <c r="AP477" s="7"/>
+      <c r="AQ477" s="7"/>
+      <c r="AR477" s="7"/>
+      <c r="AS477" s="7"/>
+      <c r="AT477" s="7"/>
+      <c r="AU477" s="7"/>
+      <c r="AV477" s="7"/>
+      <c r="AW477" s="4"/>
+      <c r="AX477" s="2"/>
+      <c r="AY477" s="7"/>
+      <c r="AZ477" s="4"/>
+      <c r="BA477" s="4"/>
+      <c r="BB477" s="2"/>
+      <c r="BC477" s="2"/>
+      <c r="BD477" s="2"/>
+      <c r="BE477" s="82"/>
+      <c r="BF477" s="83"/>
+      <c r="BG477" s="84"/>
+      <c r="BH477" s="2"/>
+      <c r="BI477" s="2"/>
+      <c r="BJ477" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -55885,6 +55743,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -55893,7 +55761,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004F1ECC6B2649324CB24C079D2C04510D" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="608b5d954c2eb0ac10393708da8d34af">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65551c38-962b-4cee-924d-ef2df1bb8b98" xmlns:ns3="ec750ee3-7d64-422f-9b1f-0ca7238893a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af171f03bd4cf151e3e856a6839c0cc7" ns2:_="" ns3:_="">
     <xsd:import namespace="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
@@ -56141,17 +56009,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -56159,7 +56034,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -56176,21 +56051,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A9C3E3-70BA-46B0-BD70-8A24954761C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CA4670-7A7A-4279-9155-8C348C6066DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43320" yWindow="3270" windowWidth="19395" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CdA Track Testing" sheetId="12" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3737" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3751" uniqueCount="663">
   <si>
     <t>Squad</t>
   </si>
@@ -1997,6 +1997,48 @@
   </si>
   <si>
     <t>A1/P15</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Tm55Q0Z7lTY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7IxSf81pmKk</t>
+  </si>
+  <si>
+    <t>https://youtu.be/zr4iTJpofDs</t>
+  </si>
+  <si>
+    <t>https://youtu.be/1QharRGYKl8</t>
+  </si>
+  <si>
+    <t>https://youtu.be/5nzGR1qW9oQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/V7UzDJsIToo</t>
+  </si>
+  <si>
+    <t>https://youtu.be/8RbjqVWBJ7U</t>
+  </si>
+  <si>
+    <t>https://youtu.be/zbuH3HLxEyI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/l0jTige5c8Q</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MDWRcf3T2RM</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Gpimn50EVQg</t>
+  </si>
+  <si>
+    <t>https://youtu.be/u-tDLHyqAcU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/8j2DO97oJzw</t>
+  </si>
+  <si>
+    <t>https://youtu.be/dEESiNgApDk</t>
   </si>
 </sst>
 </file>
@@ -54471,7 +54513,9 @@
       <c r="BG464" s="81"/>
       <c r="BH464" s="2"/>
       <c r="BI464" s="2"/>
-      <c r="BJ464" s="3"/>
+      <c r="BJ464" s="3" t="s">
+        <v>649</v>
+      </c>
     </row>
     <row r="465" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A465" s="75" t="s">
@@ -54568,7 +54612,9 @@
       <c r="BG465" s="81"/>
       <c r="BH465" s="2"/>
       <c r="BI465" s="2"/>
-      <c r="BJ465" s="3"/>
+      <c r="BJ465" s="3" t="s">
+        <v>650</v>
+      </c>
     </row>
     <row r="466" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A466" s="75" t="s">
@@ -54665,7 +54711,9 @@
       <c r="BG466" s="81"/>
       <c r="BH466" s="2"/>
       <c r="BI466" s="2"/>
-      <c r="BJ466" s="3"/>
+      <c r="BJ466" s="3" t="s">
+        <v>651</v>
+      </c>
     </row>
     <row r="467" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A467" s="75" t="s">
@@ -54762,7 +54810,9 @@
       <c r="BG467" s="81"/>
       <c r="BH467" s="2"/>
       <c r="BI467" s="2"/>
-      <c r="BJ467" s="3"/>
+      <c r="BJ467" s="3" t="s">
+        <v>652</v>
+      </c>
     </row>
     <row r="468" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A468" s="75" t="s">
@@ -54859,7 +54909,9 @@
       <c r="BG468" s="81"/>
       <c r="BH468" s="2"/>
       <c r="BI468" s="2"/>
-      <c r="BJ468" s="3"/>
+      <c r="BJ468" s="3" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="469" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A469" s="75" t="s">
@@ -54956,7 +55008,9 @@
       <c r="BG469" s="81"/>
       <c r="BH469" s="2"/>
       <c r="BI469" s="2"/>
-      <c r="BJ469" s="3"/>
+      <c r="BJ469" s="3" t="s">
+        <v>654</v>
+      </c>
     </row>
     <row r="470" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A470" s="75" t="s">
@@ -55053,7 +55107,9 @@
       <c r="BG470" s="81"/>
       <c r="BH470" s="2"/>
       <c r="BI470" s="2"/>
-      <c r="BJ470" s="3"/>
+      <c r="BJ470" s="3" t="s">
+        <v>655</v>
+      </c>
     </row>
     <row r="471" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A471" s="75" t="s">
@@ -55150,7 +55206,9 @@
       <c r="BG471" s="81"/>
       <c r="BH471" s="2"/>
       <c r="BI471" s="2"/>
-      <c r="BJ471" s="3"/>
+      <c r="BJ471" s="3" t="s">
+        <v>656</v>
+      </c>
     </row>
     <row r="472" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A472" s="75" t="s">
@@ -55247,7 +55305,9 @@
       <c r="BG472" s="81"/>
       <c r="BH472" s="2"/>
       <c r="BI472" s="2"/>
-      <c r="BJ472" s="3"/>
+      <c r="BJ472" s="3" t="s">
+        <v>657</v>
+      </c>
     </row>
     <row r="473" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A473" s="75" t="s">
@@ -55344,7 +55404,9 @@
       <c r="BG473" s="81"/>
       <c r="BH473" s="2"/>
       <c r="BI473" s="2"/>
-      <c r="BJ473" s="3"/>
+      <c r="BJ473" s="3" t="s">
+        <v>658</v>
+      </c>
     </row>
     <row r="474" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A474" s="75" t="s">
@@ -55433,7 +55495,9 @@
       <c r="BG474" s="81"/>
       <c r="BH474" s="2"/>
       <c r="BI474" s="2"/>
-      <c r="BJ474" s="3"/>
+      <c r="BJ474" s="3" t="s">
+        <v>659</v>
+      </c>
     </row>
     <row r="475" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A475" s="75" t="s">
@@ -55530,7 +55594,9 @@
       <c r="BG475" s="81"/>
       <c r="BH475" s="2"/>
       <c r="BI475" s="2"/>
-      <c r="BJ475" s="3"/>
+      <c r="BJ475" s="3" t="s">
+        <v>660</v>
+      </c>
     </row>
     <row r="476" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A476" s="75" t="s">
@@ -55627,7 +55693,9 @@
       <c r="BG476" s="81"/>
       <c r="BH476" s="2"/>
       <c r="BI476" s="2"/>
-      <c r="BJ476" s="3"/>
+      <c r="BJ476" s="3" t="s">
+        <v>661</v>
+      </c>
     </row>
     <row r="477" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A477" s="75" t="s">
@@ -55724,7 +55792,9 @@
       <c r="BG477" s="84"/>
       <c r="BH477" s="2"/>
       <c r="BI477" s="2"/>
-      <c r="BJ477" s="3"/>
+      <c r="BJ477" s="3" t="s">
+        <v>662</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -55753,15 +55823,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004F1ECC6B2649324CB24C079D2C04510D" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="608b5d954c2eb0ac10393708da8d34af">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65551c38-962b-4cee-924d-ef2df1bb8b98" xmlns:ns3="ec750ee3-7d64-422f-9b1f-0ca7238893a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af171f03bd4cf151e3e856a6839c0cc7" ns2:_="" ns3:_="">
     <xsd:import namespace="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
@@ -56009,6 +56070,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
   <ds:schemaRefs>
@@ -56027,14 +56097,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -56051,4 +56113,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CA4670-7A7A-4279-9155-8C348C6066DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0A24C6-508C-4DF6-B135-1A30F576B253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3751" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3751" uniqueCount="658">
   <si>
     <t>Squad</t>
   </si>
@@ -1978,25 +1978,10 @@
     <t>ImpSport</t>
   </si>
   <si>
-    <t>A1/P11</t>
-  </si>
-  <si>
     <t>Narrow ImpSport</t>
   </si>
   <si>
-    <t>A1/P12</t>
-  </si>
-  <si>
     <t>Wide ImpSport</t>
-  </si>
-  <si>
-    <t>A1/P13</t>
-  </si>
-  <si>
-    <t>A1/P14</t>
-  </si>
-  <si>
-    <t>A1/P15</t>
   </si>
   <si>
     <t>https://youtu.be/Tm55Q0Z7lTY</t>
@@ -54514,7 +54499,7 @@
       <c r="BH464" s="2"/>
       <c r="BI464" s="2"/>
       <c r="BJ464" s="3" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
     </row>
     <row r="465" spans="1:62" x14ac:dyDescent="0.45">
@@ -54613,7 +54598,7 @@
       <c r="BH465" s="2"/>
       <c r="BI465" s="2"/>
       <c r="BJ465" s="3" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
     </row>
     <row r="466" spans="1:62" x14ac:dyDescent="0.45">
@@ -54712,7 +54697,7 @@
       <c r="BH466" s="2"/>
       <c r="BI466" s="2"/>
       <c r="BJ466" s="3" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
     </row>
     <row r="467" spans="1:62" x14ac:dyDescent="0.45">
@@ -54811,7 +54796,7 @@
       <c r="BH467" s="2"/>
       <c r="BI467" s="2"/>
       <c r="BJ467" s="3" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
     </row>
     <row r="468" spans="1:62" x14ac:dyDescent="0.45">
@@ -54910,7 +54895,7 @@
       <c r="BH468" s="2"/>
       <c r="BI468" s="2"/>
       <c r="BJ468" s="3" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="469" spans="1:62" x14ac:dyDescent="0.45">
@@ -55009,7 +54994,7 @@
       <c r="BH469" s="2"/>
       <c r="BI469" s="2"/>
       <c r="BJ469" s="3" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
     </row>
     <row r="470" spans="1:62" x14ac:dyDescent="0.45">
@@ -55108,7 +55093,7 @@
       <c r="BH470" s="2"/>
       <c r="BI470" s="2"/>
       <c r="BJ470" s="3" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
     </row>
     <row r="471" spans="1:62" x14ac:dyDescent="0.45">
@@ -55207,7 +55192,7 @@
       <c r="BH471" s="2"/>
       <c r="BI471" s="2"/>
       <c r="BJ471" s="3" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
     </row>
     <row r="472" spans="1:62" x14ac:dyDescent="0.45">
@@ -55306,7 +55291,7 @@
       <c r="BH472" s="2"/>
       <c r="BI472" s="2"/>
       <c r="BJ472" s="3" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
     </row>
     <row r="473" spans="1:62" x14ac:dyDescent="0.45">
@@ -55326,10 +55311,10 @@
         <v>640</v>
       </c>
       <c r="F473" s="74" t="s">
+        <v>216</v>
+      </c>
+      <c r="G473" s="74" t="s">
         <v>642</v>
-      </c>
-      <c r="G473" s="74" t="s">
-        <v>643</v>
       </c>
       <c r="H473" s="74" t="s">
         <v>223</v>
@@ -55405,7 +55390,7 @@
       <c r="BH473" s="2"/>
       <c r="BI473" s="2"/>
       <c r="BJ473" s="3" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
     </row>
     <row r="474" spans="1:62" x14ac:dyDescent="0.45">
@@ -55425,10 +55410,10 @@
         <v>640</v>
       </c>
       <c r="F474" s="74" t="s">
-        <v>644</v>
+        <v>216</v>
       </c>
       <c r="G474" s="74" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="H474" s="74" t="s">
         <v>223</v>
@@ -55496,7 +55481,7 @@
       <c r="BH474" s="2"/>
       <c r="BI474" s="2"/>
       <c r="BJ474" s="3" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
     </row>
     <row r="475" spans="1:62" x14ac:dyDescent="0.45">
@@ -55516,7 +55501,7 @@
         <v>640</v>
       </c>
       <c r="F475" s="74" t="s">
-        <v>646</v>
+        <v>216</v>
       </c>
       <c r="G475" s="74" t="s">
         <v>641</v>
@@ -55595,7 +55580,7 @@
       <c r="BH475" s="2"/>
       <c r="BI475" s="2"/>
       <c r="BJ475" s="3" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
     </row>
     <row r="476" spans="1:62" x14ac:dyDescent="0.45">
@@ -55615,10 +55600,10 @@
         <v>640</v>
       </c>
       <c r="F476" s="74" t="s">
-        <v>647</v>
+        <v>216</v>
       </c>
       <c r="G476" s="74" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H476" s="74" t="s">
         <v>223</v>
@@ -55694,7 +55679,7 @@
       <c r="BH476" s="2"/>
       <c r="BI476" s="2"/>
       <c r="BJ476" s="3" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
     </row>
     <row r="477" spans="1:62" x14ac:dyDescent="0.45">
@@ -55714,10 +55699,10 @@
         <v>640</v>
       </c>
       <c r="F477" s="74" t="s">
-        <v>648</v>
+        <v>216</v>
       </c>
       <c r="G477" s="74" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="H477" s="74" t="s">
         <v>223</v>
@@ -55793,7 +55778,7 @@
       <c r="BH477" s="2"/>
       <c r="BI477" s="2"/>
       <c r="BJ477" s="3" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>
@@ -55823,6 +55808,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004F1ECC6B2649324CB24C079D2C04510D" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="608b5d954c2eb0ac10393708da8d34af">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65551c38-962b-4cee-924d-ef2df1bb8b98" xmlns:ns3="ec750ee3-7d64-422f-9b1f-0ca7238893a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af171f03bd4cf151e3e856a6839c0cc7" ns2:_="" ns3:_="">
     <xsd:import namespace="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
@@ -56070,15 +56064,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
   <ds:schemaRefs>
@@ -56097,6 +56082,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -56113,12 +56106,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0A24C6-508C-4DF6-B135-1A30F576B253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1D8BC2-8631-4C86-9AD4-47ECAAE15628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CdA Track Testing" sheetId="12" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3751" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3893" uniqueCount="666">
   <si>
     <t>Squad</t>
   </si>
@@ -1788,9 +1788,6 @@
   </si>
   <si>
     <t>FW Seat-10mm</t>
-  </si>
-  <si>
-    <t>Targer CB</t>
   </si>
   <si>
     <t>FW - B +10mm</t>
@@ -1960,30 +1957,9 @@
     <t>Undershirt</t>
   </si>
   <si>
-    <t>Pos-G-FW</t>
-  </si>
-  <si>
-    <t>Pos-H-FW</t>
-  </si>
-  <si>
-    <t>Pos-I-FW</t>
-  </si>
-  <si>
-    <t>Pos-J-FW</t>
-  </si>
-  <si>
-    <t>Pos-A-FW</t>
-  </si>
-  <si>
     <t>ImpSport</t>
   </si>
   <si>
-    <t>Narrow ImpSport</t>
-  </si>
-  <si>
-    <t>Wide ImpSport</t>
-  </si>
-  <si>
     <t>https://youtu.be/Tm55Q0Z7lTY</t>
   </si>
   <si>
@@ -2024,6 +2000,54 @@
   </si>
   <si>
     <t>https://youtu.be/dEESiNgApDk</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0022t1lU2bY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sNw6bftJbHQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/jFcLDGfHqmM</t>
+  </si>
+  <si>
+    <t>https://youtu.be/J4odUNtd08c</t>
+  </si>
+  <si>
+    <t>https://youtu.be/qEKv3gvECd8</t>
+  </si>
+  <si>
+    <t>https://youtu.be/l5NzvuzbDCQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/4OTX8yorhks</t>
+  </si>
+  <si>
+    <t>https://youtu.be/W3Yx8SH2na0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/HQx_hy7Vd5c</t>
+  </si>
+  <si>
+    <t>https://youtu.be/aajyGxQ6UMg</t>
+  </si>
+  <si>
+    <t>https://youtu.be/751O7nXMSZo</t>
+  </si>
+  <si>
+    <t>https://youtu.be/WDSqiLucKDY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ZIGl7AtFRJA</t>
+  </si>
+  <si>
+    <t>https://youtu.be/KTD5bQbm2zA</t>
+  </si>
+  <si>
+    <t>https://youtu.be/8FdBT4m6gAU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/RPw-oaPsoiI</t>
   </si>
 </sst>
 </file>
@@ -2139,6 +2163,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2252,7 +2277,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2516,6 +2541,61 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2922,8 +3002,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Track_TT23" displayName="Track_TT23" ref="A1:BJ477" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
-  <autoFilter ref="A1:BJ477" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Track_TT23" displayName="Track_TT23" ref="A1:BJ509" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+  <autoFilter ref="A1:BJ509" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BJ447">
     <sortCondition ref="C1:C447"/>
   </sortState>
@@ -3258,7 +3338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:BR477"/>
+  <dimension ref="A1:BR509"/>
   <sheetFormatPr defaultColWidth="23.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7.46484375" style="1" customWidth="1"/>
@@ -3312,7 +3392,7 @@
         <v>50</v>
       </c>
       <c r="J1" s="47" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="K1" s="47" t="s">
         <v>209</v>
@@ -3321,10 +3401,10 @@
         <v>32</v>
       </c>
       <c r="M1" s="47" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="N1" s="47" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="O1" s="26" t="s">
         <v>497</v>
@@ -3658,9 +3738,9 @@
       <c r="AX3" s="9">
         <v>8</v>
       </c>
-      <c r="AY3" s="9">
+      <c r="AY3" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>82.399999999999991</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ3" s="7">
         <v>200</v>
@@ -3770,9 +3850,9 @@
       <c r="AX4" s="9">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AY4" s="9">
+      <c r="AY4" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>70</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ4" s="7">
         <v>200</v>
@@ -3991,9 +4071,9 @@
       <c r="AX6" s="9">
         <v>8</v>
       </c>
-      <c r="AY6" s="9">
+      <c r="AY6" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>82.399999999999991</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ6" s="7">
         <v>200</v>
@@ -4103,9 +4183,9 @@
       <c r="AX7" s="9">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AY7" s="9">
+      <c r="AY7" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>70</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ7" s="7">
         <v>200</v>
@@ -4157,7 +4237,7 @@
         <v>15</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>330</v>
@@ -4215,9 +4295,9 @@
       <c r="AX8" s="9">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AY8" s="9">
+      <c r="AY8" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>8.1</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ8" s="7">
         <v>200</v>
@@ -4269,7 +4349,7 @@
         <v>15</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>574</v>
@@ -4327,9 +4407,9 @@
       <c r="AX9" s="9">
         <v>8</v>
       </c>
-      <c r="AY9" s="9">
+      <c r="AY9" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>73.300000000000011</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ9" s="7">
         <v>200</v>
@@ -4381,7 +4461,7 @@
         <v>15</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>223</v>
@@ -4490,7 +4570,7 @@
         <v>15</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>330</v>
@@ -4548,9 +4628,9 @@
       <c r="AX11" s="9">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AY11" s="9">
+      <c r="AY11" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>73.300000000000011</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ11" s="7">
         <v>200</v>
@@ -4602,7 +4682,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>574</v>
@@ -4660,9 +4740,9 @@
       <c r="AX12" s="9">
         <v>8</v>
       </c>
-      <c r="AY12" s="9">
+      <c r="AY12" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>8.1</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ12" s="7">
         <v>200</v>
@@ -4714,7 +4794,7 @@
         <v>15</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>223</v>
@@ -4879,9 +4959,9 @@
       <c r="AX14" s="9">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AY14" s="9">
+      <c r="AY14" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>73.300000000000011</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ14" s="7">
         <v>200</v>
@@ -4989,9 +5069,9 @@
       <c r="AX15" s="9">
         <v>8</v>
       </c>
-      <c r="AY15" s="9">
+      <c r="AY15" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>82.1</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ15" s="7">
         <v>200</v>
@@ -5099,9 +5179,9 @@
       <c r="AX16" s="9">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AY16" s="9">
+      <c r="AY16" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>69.7</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ16" s="7">
         <v>200</v>
@@ -5209,9 +5289,9 @@
       <c r="AX17" s="9">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AY17" s="9">
+      <c r="AY17" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>82.1</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ17" s="7">
         <v>200</v>
@@ -5319,9 +5399,9 @@
       <c r="AX18" s="9">
         <v>8</v>
       </c>
-      <c r="AY18" s="9">
+      <c r="AY18" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>69.7</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ18" s="7">
         <v>200</v>
@@ -5429,9 +5509,9 @@
       <c r="AX19" s="9">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AY19" s="9">
+      <c r="AY19" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>75.900000000000006</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ19" s="7">
         <v>200</v>
@@ -6179,9 +6259,9 @@
       <c r="AX26" s="4">
         <v>7.9</v>
       </c>
-      <c r="AY26" s="9">
+      <c r="AY26" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>71.599999999999994</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ26" s="7">
         <v>200</v>
@@ -6289,9 +6369,9 @@
       <c r="AX27" s="4">
         <v>8</v>
       </c>
-      <c r="AY27" s="9">
+      <c r="AY27" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>75.900000000000006</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ27" s="7">
         <v>200</v>
@@ -6399,9 +6479,9 @@
       <c r="AX28" s="4">
         <v>8.1</v>
       </c>
-      <c r="AY28" s="9">
+      <c r="AY28" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>71.599999999999994</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ28" s="7">
         <v>200</v>
@@ -6507,9 +6587,9 @@
       <c r="AX29" s="4">
         <v>7.9</v>
       </c>
-      <c r="AY29" s="9">
+      <c r="AY29" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>79.599999999999994</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ29" s="7">
         <v>200</v>
@@ -6617,9 +6697,9 @@
       <c r="AX30" s="4">
         <v>8</v>
       </c>
-      <c r="AY30" s="9">
+      <c r="AY30" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>0</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ30" s="7">
         <v>200</v>
@@ -6727,9 +6807,9 @@
       <c r="AX31" s="4">
         <v>8.1</v>
       </c>
-      <c r="AY31" s="9">
+      <c r="AY31" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>0</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ31" s="7">
         <v>200</v>
@@ -6938,9 +7018,9 @@
       <c r="AX33" s="4">
         <v>8</v>
       </c>
-      <c r="AY33" s="9">
+      <c r="AY33" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>0</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ33" s="7">
         <v>200</v>
@@ -7151,9 +7231,9 @@
       <c r="AX35" s="4">
         <v>7.9</v>
       </c>
-      <c r="AY35" s="9">
+      <c r="AY35" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>74.900000000000006</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ35" s="7">
         <v>200</v>
@@ -7259,9 +7339,9 @@
       <c r="AX36" s="4">
         <v>8</v>
       </c>
-      <c r="AY36" s="9">
+      <c r="AY36" s="9" t="e">
         <f>[1]!Track_TT23[[#This Row],[Bike weight ]]+[1]!Track_TT23[[#This Row],[Rider weight ]]</f>
-        <v>74.900000000000006</v>
+        <v>#REF!</v>
       </c>
       <c r="AZ36" s="7">
         <v>200</v>
@@ -22064,7 +22144,7 @@
         <v>3</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F168" s="4" t="s">
         <v>564</v>
@@ -22707,7 +22787,7 @@
         <v>1</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>583</v>
+        <v>212</v>
       </c>
       <c r="F174" s="4" t="s">
         <v>15</v>
@@ -22933,7 +23013,7 @@
         <v>3</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>583</v>
+        <v>212</v>
       </c>
       <c r="F176" s="4" t="s">
         <v>15</v>
@@ -23159,7 +23239,7 @@
         <v>5</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>583</v>
+        <v>212</v>
       </c>
       <c r="F178" s="4" t="s">
         <v>15</v>
@@ -33675,7 +33755,7 @@
       </c>
       <c r="BI268" s="2"/>
       <c r="BJ268" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="BK268"/>
       <c r="BL268"/>
@@ -33792,7 +33872,7 @@
       </c>
       <c r="BI269" s="2"/>
       <c r="BJ269" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="BK269"/>
       <c r="BL269"/>
@@ -33909,7 +33989,7 @@
       </c>
       <c r="BI270" s="2"/>
       <c r="BJ270" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="BK270"/>
       <c r="BL270"/>
@@ -34026,7 +34106,7 @@
       </c>
       <c r="BI271" s="2"/>
       <c r="BJ271" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="BK271"/>
       <c r="BL271"/>
@@ -34143,7 +34223,7 @@
       </c>
       <c r="BI272" s="2"/>
       <c r="BJ272" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="BK272"/>
       <c r="BL272"/>
@@ -34260,7 +34340,7 @@
       </c>
       <c r="BI273" s="2"/>
       <c r="BJ273" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="BK273"/>
       <c r="BL273"/>
@@ -34377,7 +34457,7 @@
       </c>
       <c r="BI274" s="2"/>
       <c r="BJ274" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="BK274"/>
       <c r="BL274"/>
@@ -34494,7 +34574,7 @@
       </c>
       <c r="BI275" s="2"/>
       <c r="BJ275" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="BK275"/>
       <c r="BL275"/>
@@ -51079,7 +51159,7 @@
       <c r="BH422" s="2"/>
       <c r="BI422" s="2"/>
       <c r="BJ422" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="423" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51102,7 +51182,7 @@
         <v>564</v>
       </c>
       <c r="G423" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H423" s="4" t="s">
         <v>378</v>
@@ -51167,7 +51247,7 @@
       <c r="BH423" s="2"/>
       <c r="BI423" s="2"/>
       <c r="BJ423" s="38" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="424" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51255,7 +51335,7 @@
       <c r="BH424" s="2"/>
       <c r="BI424" s="2"/>
       <c r="BJ424" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="425" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51278,7 +51358,7 @@
         <v>564</v>
       </c>
       <c r="G425" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H425" s="4" t="s">
         <v>378</v>
@@ -51343,7 +51423,7 @@
       <c r="BH425" s="2"/>
       <c r="BI425" s="2"/>
       <c r="BJ425" s="3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="426" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51366,7 +51446,7 @@
         <v>564</v>
       </c>
       <c r="G426" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H426" s="4" t="s">
         <v>378</v>
@@ -51431,7 +51511,7 @@
       <c r="BH426" s="2"/>
       <c r="BI426" s="2"/>
       <c r="BJ426" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="427" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51448,7 +51528,7 @@
         <v>1</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F427" s="4" t="s">
         <v>354</v>
@@ -51521,7 +51601,7 @@
       <c r="BH427" s="2"/>
       <c r="BI427" s="2"/>
       <c r="BJ427" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="428" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51611,7 +51691,7 @@
       <c r="BH428" s="2"/>
       <c r="BI428" s="2"/>
       <c r="BJ428" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="429" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51628,7 +51708,7 @@
         <v>3</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F429" s="4" t="s">
         <v>354</v>
@@ -51701,7 +51781,7 @@
       <c r="BH429" s="2"/>
       <c r="BI429" s="2"/>
       <c r="BJ429" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="430" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51718,7 +51798,7 @@
         <v>4</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F430" s="4" t="s">
         <v>354</v>
@@ -51791,7 +51871,7 @@
       <c r="BH430" s="2"/>
       <c r="BI430" s="2"/>
       <c r="BJ430" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="431" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51881,7 +51961,7 @@
       <c r="BH431" s="2"/>
       <c r="BI431" s="2"/>
       <c r="BJ431" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="432" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
@@ -51898,7 +51978,7 @@
         <v>6</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F432" s="4" t="s">
         <v>354</v>
@@ -51971,7 +52051,7 @@
       <c r="BH432" s="2"/>
       <c r="BI432" s="2"/>
       <c r="BJ432" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="433" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52061,7 +52141,7 @@
       <c r="BH433" s="2"/>
       <c r="BI433" s="2"/>
       <c r="BJ433" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="434" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52151,7 +52231,7 @@
       <c r="BH434" s="2"/>
       <c r="BI434" s="2"/>
       <c r="BJ434" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="435" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52168,7 +52248,7 @@
         <v>3</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F435" s="4" t="s">
         <v>354</v>
@@ -52241,7 +52321,7 @@
       <c r="BH435" s="2"/>
       <c r="BI435" s="2"/>
       <c r="BJ435" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="436" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52323,7 +52403,7 @@
       <c r="BH436" s="2"/>
       <c r="BI436" s="2"/>
       <c r="BJ436" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="437" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52413,7 +52493,7 @@
       <c r="BH437" s="2"/>
       <c r="BI437" s="2"/>
       <c r="BJ437" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="438" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52430,7 +52510,7 @@
         <v>6</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F438" s="4" t="s">
         <v>354</v>
@@ -52503,7 +52583,7 @@
       <c r="BH438" s="2"/>
       <c r="BI438" s="2"/>
       <c r="BJ438" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="439" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52593,7 +52673,7 @@
       <c r="BH439" s="2"/>
       <c r="BI439" s="2"/>
       <c r="BJ439" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="440" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52683,7 +52763,7 @@
       <c r="BH440" s="2"/>
       <c r="BI440" s="2"/>
       <c r="BJ440" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="441" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52706,7 +52786,7 @@
         <v>216</v>
       </c>
       <c r="G441" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H441" s="4" t="s">
         <v>572</v>
@@ -52771,7 +52851,7 @@
       <c r="BH441" s="2"/>
       <c r="BI441" s="2"/>
       <c r="BJ441" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="442" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52794,7 +52874,7 @@
         <v>216</v>
       </c>
       <c r="G442" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H442" s="4" t="s">
         <v>572</v>
@@ -52859,7 +52939,7 @@
       <c r="BH442" s="2"/>
       <c r="BI442" s="2"/>
       <c r="BJ442" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="443" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52882,7 +52962,7 @@
         <v>216</v>
       </c>
       <c r="G443" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H443" s="4" t="s">
         <v>572</v>
@@ -52947,7 +53027,7 @@
       <c r="BH443" s="2"/>
       <c r="BI443" s="2"/>
       <c r="BJ443" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="444" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -52970,7 +53050,7 @@
         <v>216</v>
       </c>
       <c r="G444" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H444" s="4" t="s">
         <v>572</v>
@@ -53035,7 +53115,7 @@
       <c r="BH444" s="2"/>
       <c r="BI444" s="2"/>
       <c r="BJ444" s="3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="445" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -53058,7 +53138,7 @@
         <v>216</v>
       </c>
       <c r="G445" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H445" s="4" t="s">
         <v>572</v>
@@ -53123,7 +53203,7 @@
       <c r="BH445" s="2"/>
       <c r="BI445" s="2"/>
       <c r="BJ445" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="446" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -53146,7 +53226,7 @@
         <v>216</v>
       </c>
       <c r="G446" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H446" s="4" t="s">
         <v>572</v>
@@ -53211,7 +53291,7 @@
       <c r="BH446" s="2"/>
       <c r="BI446" s="2"/>
       <c r="BJ446" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="447" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
@@ -53228,13 +53308,13 @@
         <v>7</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F447" s="4" t="s">
         <v>216</v>
       </c>
       <c r="G447" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H447" s="4" t="s">
         <v>572</v>
@@ -53299,15 +53379,15 @@
       <c r="BH447" s="2"/>
       <c r="BI447" s="2"/>
       <c r="BJ447" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="448" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A448" s="75" t="s">
+        <v>628</v>
+      </c>
+      <c r="B448" s="76" t="s">
         <v>629</v>
-      </c>
-      <c r="B448" s="76" t="s">
-        <v>630</v>
       </c>
       <c r="C448" s="77">
         <v>45384</v>
@@ -53319,7 +53399,7 @@
         <v>22</v>
       </c>
       <c r="F448" s="85" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G448" s="4"/>
       <c r="H448" s="4"/>
@@ -53373,10 +53453,10 @@
     </row>
     <row r="449" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A449" s="75" t="s">
+        <v>628</v>
+      </c>
+      <c r="B449" s="76" t="s">
         <v>629</v>
-      </c>
-      <c r="B449" s="76" t="s">
-        <v>630</v>
       </c>
       <c r="C449" s="77">
         <v>45384</v>
@@ -53388,7 +53468,7 @@
         <v>22</v>
       </c>
       <c r="F449" s="85" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G449" s="4"/>
       <c r="H449" s="4"/>
@@ -53442,10 +53522,10 @@
     </row>
     <row r="450" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A450" s="75" t="s">
+        <v>628</v>
+      </c>
+      <c r="B450" s="76" t="s">
         <v>629</v>
-      </c>
-      <c r="B450" s="76" t="s">
-        <v>630</v>
       </c>
       <c r="C450" s="77">
         <v>45384</v>
@@ -53457,7 +53537,7 @@
         <v>22</v>
       </c>
       <c r="F450" s="85" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G450" s="4"/>
       <c r="H450" s="4"/>
@@ -53511,10 +53591,10 @@
     </row>
     <row r="451" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A451" s="75" t="s">
+        <v>628</v>
+      </c>
+      <c r="B451" s="76" t="s">
         <v>629</v>
-      </c>
-      <c r="B451" s="76" t="s">
-        <v>630</v>
       </c>
       <c r="C451" s="77">
         <v>45384</v>
@@ -53526,7 +53606,7 @@
         <v>22</v>
       </c>
       <c r="F451" s="85" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G451" s="4"/>
       <c r="H451" s="4"/>
@@ -53580,10 +53660,10 @@
     </row>
     <row r="452" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A452" s="75" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B452" s="76" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C452" s="77">
         <v>45384</v>
@@ -53595,7 +53675,7 @@
         <v>22</v>
       </c>
       <c r="F452" s="85" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G452" s="4"/>
       <c r="H452" s="4"/>
@@ -53649,10 +53729,10 @@
     </row>
     <row r="453" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A453" s="75" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B453" s="76" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C453" s="77">
         <v>45384</v>
@@ -53664,7 +53744,7 @@
         <v>22</v>
       </c>
       <c r="F453" s="85" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G453" s="4"/>
       <c r="H453" s="4"/>
@@ -53718,10 +53798,10 @@
     </row>
     <row r="454" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A454" s="75" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B454" s="76" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C454" s="77">
         <v>45384</v>
@@ -53733,7 +53813,7 @@
         <v>22</v>
       </c>
       <c r="F454" s="85" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G454" s="4"/>
       <c r="H454" s="4"/>
@@ -53787,10 +53867,10 @@
     </row>
     <row r="455" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A455" s="75" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B455" s="76" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C455" s="77">
         <v>45384</v>
@@ -53802,7 +53882,7 @@
         <v>22</v>
       </c>
       <c r="F455" s="85" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G455" s="4"/>
       <c r="H455" s="4"/>
@@ -53856,10 +53936,10 @@
     </row>
     <row r="456" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A456" s="75" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B456" s="76" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C456" s="77">
         <v>45384</v>
@@ -53871,7 +53951,7 @@
         <v>22</v>
       </c>
       <c r="F456" s="85" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G456" s="4"/>
       <c r="H456" s="4"/>
@@ -53925,10 +54005,10 @@
     </row>
     <row r="457" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A457" s="75" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B457" s="76" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C457" s="77">
         <v>45384</v>
@@ -53940,7 +54020,7 @@
         <v>22</v>
       </c>
       <c r="F457" s="85" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G457" s="4"/>
       <c r="H457" s="4"/>
@@ -53994,10 +54074,10 @@
     </row>
     <row r="458" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A458" s="75" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B458" s="76" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C458" s="77">
         <v>45384</v>
@@ -54009,7 +54089,7 @@
         <v>22</v>
       </c>
       <c r="F458" s="85" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G458" s="4"/>
       <c r="H458" s="4"/>
@@ -54063,10 +54143,10 @@
     </row>
     <row r="459" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A459" s="75" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B459" s="76" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C459" s="77">
         <v>45384</v>
@@ -54078,7 +54158,7 @@
         <v>22</v>
       </c>
       <c r="F459" s="85" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G459" s="4"/>
       <c r="H459" s="4"/>
@@ -54132,10 +54212,10 @@
     </row>
     <row r="460" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A460" s="75" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B460" s="76" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C460" s="77">
         <v>45384</v>
@@ -54147,7 +54227,7 @@
         <v>22</v>
       </c>
       <c r="F460" s="85" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G460" s="4"/>
       <c r="H460" s="4"/>
@@ -54201,10 +54281,10 @@
     </row>
     <row r="461" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A461" s="75" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B461" s="76" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C461" s="77">
         <v>45384</v>
@@ -54216,7 +54296,7 @@
         <v>22</v>
       </c>
       <c r="F461" s="85" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G461" s="4"/>
       <c r="H461" s="4"/>
@@ -54270,10 +54350,10 @@
     </row>
     <row r="462" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A462" s="75" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B462" s="76" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C462" s="77">
         <v>45384</v>
@@ -54285,7 +54365,7 @@
         <v>22</v>
       </c>
       <c r="F462" s="85" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G462" s="4"/>
       <c r="H462" s="4"/>
@@ -54339,10 +54419,10 @@
     </row>
     <row r="463" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A463" s="75" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B463" s="76" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C463" s="77">
         <v>45384</v>
@@ -54354,7 +54434,7 @@
         <v>22</v>
       </c>
       <c r="F463" s="85" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G463" s="4"/>
       <c r="H463" s="4"/>
@@ -54406,7 +54486,7 @@
       <c r="BI463" s="2"/>
       <c r="BJ463" s="3"/>
     </row>
-    <row r="464" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A464" s="75" t="s">
         <v>13</v>
       </c>
@@ -54420,13 +54500,13 @@
         <v>1</v>
       </c>
       <c r="E464" s="75" t="s">
-        <v>636</v>
+        <v>551</v>
       </c>
       <c r="F464" s="74" t="s">
         <v>354</v>
       </c>
-      <c r="G464" s="74" t="s">
-        <v>641</v>
+      <c r="G464" s="4" t="s">
+        <v>578</v>
       </c>
       <c r="H464" s="74" t="s">
         <v>223</v>
@@ -54499,10 +54579,10 @@
       <c r="BH464" s="2"/>
       <c r="BI464" s="2"/>
       <c r="BJ464" s="3" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
     </row>
-    <row r="465" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A465" s="75" t="s">
         <v>13</v>
       </c>
@@ -54516,13 +54596,13 @@
         <v>2</v>
       </c>
       <c r="E465" s="75" t="s">
-        <v>637</v>
+        <v>552</v>
       </c>
       <c r="F465" s="74" t="s">
         <v>354</v>
       </c>
-      <c r="G465" s="74" t="s">
-        <v>641</v>
+      <c r="G465" s="4" t="s">
+        <v>578</v>
       </c>
       <c r="H465" s="74" t="s">
         <v>223</v>
@@ -54598,10 +54678,10 @@
       <c r="BH465" s="2"/>
       <c r="BI465" s="2"/>
       <c r="BJ465" s="3" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
     </row>
-    <row r="466" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A466" s="75" t="s">
         <v>13</v>
       </c>
@@ -54615,13 +54695,13 @@
         <v>3</v>
       </c>
       <c r="E466" s="75" t="s">
-        <v>638</v>
+        <v>553</v>
       </c>
       <c r="F466" s="74" t="s">
         <v>354</v>
       </c>
-      <c r="G466" s="74" t="s">
-        <v>641</v>
+      <c r="G466" s="4" t="s">
+        <v>578</v>
       </c>
       <c r="H466" s="74" t="s">
         <v>223</v>
@@ -54697,10 +54777,10 @@
       <c r="BH466" s="2"/>
       <c r="BI466" s="2"/>
       <c r="BJ466" s="3" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
     </row>
-    <row r="467" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A467" s="75" t="s">
         <v>13</v>
       </c>
@@ -54714,13 +54794,13 @@
         <v>4</v>
       </c>
       <c r="E467" s="75" t="s">
-        <v>639</v>
+        <v>554</v>
       </c>
       <c r="F467" s="74" t="s">
         <v>354</v>
       </c>
-      <c r="G467" s="74" t="s">
-        <v>641</v>
+      <c r="G467" s="4" t="s">
+        <v>578</v>
       </c>
       <c r="H467" s="74" t="s">
         <v>223</v>
@@ -54796,10 +54876,10 @@
       <c r="BH467" s="2"/>
       <c r="BI467" s="2"/>
       <c r="BJ467" s="3" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
     </row>
-    <row r="468" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A468" s="75" t="s">
         <v>13</v>
       </c>
@@ -54813,13 +54893,13 @@
         <v>5</v>
       </c>
       <c r="E468" s="75" t="s">
-        <v>636</v>
+        <v>551</v>
       </c>
       <c r="F468" s="74" t="s">
         <v>354</v>
       </c>
-      <c r="G468" s="74" t="s">
-        <v>641</v>
+      <c r="G468" s="4" t="s">
+        <v>578</v>
       </c>
       <c r="H468" s="74" t="s">
         <v>223</v>
@@ -54895,10 +54975,10 @@
       <c r="BH468" s="2"/>
       <c r="BI468" s="2"/>
       <c r="BJ468" s="3" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
     </row>
-    <row r="469" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A469" s="75" t="s">
         <v>13</v>
       </c>
@@ -54912,13 +54992,13 @@
         <v>6</v>
       </c>
       <c r="E469" s="75" t="s">
-        <v>637</v>
+        <v>552</v>
       </c>
       <c r="F469" s="74" t="s">
         <v>354</v>
       </c>
-      <c r="G469" s="74" t="s">
-        <v>641</v>
+      <c r="G469" s="4" t="s">
+        <v>578</v>
       </c>
       <c r="H469" s="74" t="s">
         <v>223</v>
@@ -54994,10 +55074,10 @@
       <c r="BH469" s="2"/>
       <c r="BI469" s="2"/>
       <c r="BJ469" s="3" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
     </row>
-    <row r="470" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A470" s="75" t="s">
         <v>13</v>
       </c>
@@ -55011,13 +55091,13 @@
         <v>7</v>
       </c>
       <c r="E470" s="75" t="s">
-        <v>638</v>
+        <v>553</v>
       </c>
       <c r="F470" s="74" t="s">
         <v>354</v>
       </c>
-      <c r="G470" s="74" t="s">
-        <v>641</v>
+      <c r="G470" s="4" t="s">
+        <v>578</v>
       </c>
       <c r="H470" s="74" t="s">
         <v>223</v>
@@ -55093,10 +55173,10 @@
       <c r="BH470" s="2"/>
       <c r="BI470" s="2"/>
       <c r="BJ470" s="3" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
     </row>
-    <row r="471" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A471" s="75" t="s">
         <v>13</v>
       </c>
@@ -55110,13 +55190,13 @@
         <v>8</v>
       </c>
       <c r="E471" s="75" t="s">
-        <v>639</v>
+        <v>554</v>
       </c>
       <c r="F471" s="74" t="s">
         <v>354</v>
       </c>
-      <c r="G471" s="74" t="s">
-        <v>641</v>
+      <c r="G471" s="4" t="s">
+        <v>578</v>
       </c>
       <c r="H471" s="74" t="s">
         <v>223</v>
@@ -55192,10 +55272,10 @@
       <c r="BH471" s="2"/>
       <c r="BI471" s="2"/>
       <c r="BJ471" s="3" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
     </row>
-    <row r="472" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A472" s="75" t="s">
         <v>43</v>
       </c>
@@ -55209,13 +55289,13 @@
         <v>1</v>
       </c>
       <c r="E472" s="75" t="s">
-        <v>640</v>
+        <v>213</v>
       </c>
       <c r="F472" s="74" t="s">
         <v>216</v>
       </c>
-      <c r="G472" s="74" t="s">
-        <v>641</v>
+      <c r="G472" s="4" t="s">
+        <v>578</v>
       </c>
       <c r="H472" s="74" t="s">
         <v>223</v>
@@ -55291,10 +55371,10 @@
       <c r="BH472" s="2"/>
       <c r="BI472" s="2"/>
       <c r="BJ472" s="3" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
     </row>
-    <row r="473" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A473" s="75" t="s">
         <v>43</v>
       </c>
@@ -55308,13 +55388,13 @@
         <v>2</v>
       </c>
       <c r="E473" s="75" t="s">
-        <v>640</v>
+        <v>213</v>
       </c>
       <c r="F473" s="74" t="s">
         <v>216</v>
       </c>
-      <c r="G473" s="74" t="s">
-        <v>642</v>
+      <c r="G473" s="4" t="s">
+        <v>600</v>
       </c>
       <c r="H473" s="74" t="s">
         <v>223</v>
@@ -55390,10 +55470,10 @@
       <c r="BH473" s="2"/>
       <c r="BI473" s="2"/>
       <c r="BJ473" s="3" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
     </row>
-    <row r="474" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A474" s="75" t="s">
         <v>43</v>
       </c>
@@ -55407,13 +55487,13 @@
         <v>3</v>
       </c>
       <c r="E474" s="75" t="s">
-        <v>640</v>
+        <v>213</v>
       </c>
       <c r="F474" s="74" t="s">
         <v>216</v>
       </c>
-      <c r="G474" s="74" t="s">
-        <v>643</v>
+      <c r="G474" s="4" t="s">
+        <v>601</v>
       </c>
       <c r="H474" s="74" t="s">
         <v>223</v>
@@ -55481,10 +55561,10 @@
       <c r="BH474" s="2"/>
       <c r="BI474" s="2"/>
       <c r="BJ474" s="3" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
     </row>
-    <row r="475" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A475" s="75" t="s">
         <v>43</v>
       </c>
@@ -55498,13 +55578,13 @@
         <v>4</v>
       </c>
       <c r="E475" s="75" t="s">
-        <v>640</v>
+        <v>213</v>
       </c>
       <c r="F475" s="74" t="s">
         <v>216</v>
       </c>
       <c r="G475" s="74" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="H475" s="74" t="s">
         <v>223</v>
@@ -55580,10 +55660,10 @@
       <c r="BH475" s="2"/>
       <c r="BI475" s="2"/>
       <c r="BJ475" s="3" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
     </row>
-    <row r="476" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A476" s="75" t="s">
         <v>43</v>
       </c>
@@ -55597,13 +55677,13 @@
         <v>5</v>
       </c>
       <c r="E476" s="75" t="s">
-        <v>640</v>
+        <v>213</v>
       </c>
       <c r="F476" s="74" t="s">
         <v>216</v>
       </c>
-      <c r="G476" s="74" t="s">
-        <v>642</v>
+      <c r="G476" s="4" t="s">
+        <v>600</v>
       </c>
       <c r="H476" s="74" t="s">
         <v>223</v>
@@ -55679,10 +55759,10 @@
       <c r="BH476" s="2"/>
       <c r="BI476" s="2"/>
       <c r="BJ476" s="3" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
     </row>
-    <row r="477" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A477" s="75" t="s">
         <v>43</v>
       </c>
@@ -55696,13 +55776,13 @@
         <v>6</v>
       </c>
       <c r="E477" s="75" t="s">
-        <v>640</v>
+        <v>213</v>
       </c>
       <c r="F477" s="74" t="s">
         <v>216</v>
       </c>
-      <c r="G477" s="74" t="s">
-        <v>643</v>
+      <c r="G477" s="4" t="s">
+        <v>601</v>
       </c>
       <c r="H477" s="74" t="s">
         <v>223</v>
@@ -55778,8 +55858,2866 @@
       <c r="BH477" s="2"/>
       <c r="BI477" s="2"/>
       <c r="BJ477" s="3" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="478" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A478" s="107" t="s">
+        <v>13</v>
+      </c>
+      <c r="B478" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C478" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D478" s="90">
+        <v>1</v>
+      </c>
+      <c r="E478" s="91" t="s">
+        <v>551</v>
+      </c>
+      <c r="F478" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="G478" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="H478" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I478" s="74">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="J478" s="74">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="K478" s="74">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="L478" s="92"/>
+      <c r="M478" s="74">
+        <v>0.1615</v>
+      </c>
+      <c r="N478" s="7">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="O478" s="4"/>
+      <c r="P478" s="74">
+        <v>1.2424999999999999</v>
+      </c>
+      <c r="Q478" s="92"/>
+      <c r="R478" s="94"/>
+      <c r="S478" s="94"/>
+      <c r="T478" s="74">
+        <v>65.099999999999994</v>
+      </c>
+      <c r="U478" s="74">
+        <v>583</v>
+      </c>
+      <c r="V478" s="74">
+        <v>754.7</v>
+      </c>
+      <c r="W478" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="X478" s="4"/>
+      <c r="Y478" s="4"/>
+      <c r="Z478" s="7"/>
+      <c r="AA478" s="7"/>
+      <c r="AB478" s="7"/>
+      <c r="AC478" s="7"/>
+      <c r="AD478" s="7"/>
+      <c r="AE478" s="7"/>
+      <c r="AF478" s="7"/>
+      <c r="AG478" s="7"/>
+      <c r="AH478" s="7"/>
+      <c r="AI478" s="7"/>
+      <c r="AJ478" s="7"/>
+      <c r="AK478" s="7"/>
+      <c r="AL478" s="7"/>
+      <c r="AM478" s="7"/>
+      <c r="AN478" s="7"/>
+      <c r="AO478" s="7"/>
+      <c r="AP478" s="7"/>
+      <c r="AQ478" s="7"/>
+      <c r="AR478" s="7"/>
+      <c r="AS478" s="7"/>
+      <c r="AT478" s="7"/>
+      <c r="AU478" s="7"/>
+      <c r="AV478" s="7"/>
+      <c r="AW478" s="4"/>
+      <c r="AX478" s="2"/>
+      <c r="AY478" s="7"/>
+      <c r="AZ478" s="4"/>
+      <c r="BA478" s="74">
+        <v>115.2</v>
+      </c>
+      <c r="BB478" s="2"/>
+      <c r="BC478" s="2"/>
+      <c r="BD478" s="74">
+        <v>25.3</v>
+      </c>
+      <c r="BE478" s="74">
+        <v>1004.3</v>
+      </c>
+      <c r="BF478" s="74">
+        <v>45.2</v>
+      </c>
+      <c r="BG478" s="74"/>
+      <c r="BH478" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI478" s="2"/>
+      <c r="BJ478" s="107" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="479" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A479" s="107" t="s">
+        <v>13</v>
+      </c>
+      <c r="B479" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C479" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D479" s="90">
+        <v>2</v>
+      </c>
+      <c r="E479" s="91" t="s">
+        <v>551</v>
+      </c>
+      <c r="F479" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="G479" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="H479" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I479" s="86"/>
+      <c r="J479" s="86"/>
+      <c r="K479" s="86"/>
+      <c r="L479" s="92"/>
+      <c r="M479" s="74">
+        <v>0.16139999999999999</v>
+      </c>
+      <c r="N479" s="86"/>
+      <c r="O479" s="4"/>
+      <c r="P479" s="74">
+        <v>1.2424999999999999</v>
+      </c>
+      <c r="Q479" s="92"/>
+      <c r="R479" s="94"/>
+      <c r="S479" s="94"/>
+      <c r="T479" s="74">
+        <v>65.8</v>
+      </c>
+      <c r="U479" s="74">
+        <v>593</v>
+      </c>
+      <c r="V479" s="74">
+        <v>755.6</v>
+      </c>
+      <c r="W479" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="X479" s="4"/>
+      <c r="Y479" s="4"/>
+      <c r="Z479" s="7"/>
+      <c r="AA479" s="7"/>
+      <c r="AB479" s="7"/>
+      <c r="AC479" s="7"/>
+      <c r="AD479" s="7"/>
+      <c r="AE479" s="7"/>
+      <c r="AF479" s="7"/>
+      <c r="AG479" s="7"/>
+      <c r="AH479" s="7"/>
+      <c r="AI479" s="7"/>
+      <c r="AJ479" s="7"/>
+      <c r="AK479" s="7"/>
+      <c r="AL479" s="7"/>
+      <c r="AM479" s="7"/>
+      <c r="AN479" s="7"/>
+      <c r="AO479" s="7"/>
+      <c r="AP479" s="7"/>
+      <c r="AQ479" s="7"/>
+      <c r="AR479" s="7"/>
+      <c r="AS479" s="7"/>
+      <c r="AT479" s="7"/>
+      <c r="AU479" s="7"/>
+      <c r="AV479" s="7"/>
+      <c r="AW479" s="4"/>
+      <c r="AX479" s="2"/>
+      <c r="AY479" s="7"/>
+      <c r="AZ479" s="4"/>
+      <c r="BA479" s="74">
+        <v>115.2</v>
+      </c>
+      <c r="BB479" s="2"/>
+      <c r="BC479" s="2"/>
+      <c r="BD479" s="74">
+        <v>25.3</v>
+      </c>
+      <c r="BE479" s="74">
+        <v>1004.3</v>
+      </c>
+      <c r="BF479" s="74">
+        <v>45.2</v>
+      </c>
+      <c r="BG479" s="74"/>
+      <c r="BH479" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI479" s="2"/>
+      <c r="BJ479" s="3" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="480" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A480" s="107" t="s">
+        <v>13</v>
+      </c>
+      <c r="B480" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C480" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D480" s="90">
+        <v>3</v>
+      </c>
+      <c r="E480" s="91" t="s">
+        <v>551</v>
+      </c>
+      <c r="F480" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="G480" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="H480" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I480" s="74">
+        <v>0.16550000000000001</v>
+      </c>
+      <c r="J480" s="74">
+        <v>0.16550000000000001</v>
+      </c>
+      <c r="K480" s="74">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="L480" s="92"/>
+      <c r="M480" s="74">
+        <v>0.1605</v>
+      </c>
+      <c r="N480" s="7">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="O480" s="4"/>
+      <c r="P480" s="74">
+        <v>1.2424999999999999</v>
+      </c>
+      <c r="Q480" s="92"/>
+      <c r="R480" s="94"/>
+      <c r="S480" s="94"/>
+      <c r="T480" s="74">
+        <v>66</v>
+      </c>
+      <c r="U480" s="74">
+        <v>602</v>
+      </c>
+      <c r="V480" s="74">
+        <v>755.5</v>
+      </c>
+      <c r="W480" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="X480" s="4"/>
+      <c r="Y480" s="4"/>
+      <c r="Z480" s="7"/>
+      <c r="AA480" s="7"/>
+      <c r="AB480" s="7"/>
+      <c r="AC480" s="7"/>
+      <c r="AD480" s="7"/>
+      <c r="AE480" s="7"/>
+      <c r="AF480" s="7"/>
+      <c r="AG480" s="7"/>
+      <c r="AH480" s="7"/>
+      <c r="AI480" s="7"/>
+      <c r="AJ480" s="7"/>
+      <c r="AK480" s="7"/>
+      <c r="AL480" s="7"/>
+      <c r="AM480" s="7"/>
+      <c r="AN480" s="7"/>
+      <c r="AO480" s="7"/>
+      <c r="AP480" s="7"/>
+      <c r="AQ480" s="7"/>
+      <c r="AR480" s="7"/>
+      <c r="AS480" s="7"/>
+      <c r="AT480" s="7"/>
+      <c r="AU480" s="7"/>
+      <c r="AV480" s="7"/>
+      <c r="AW480" s="4"/>
+      <c r="AX480" s="2"/>
+      <c r="AY480" s="7"/>
+      <c r="AZ480" s="4"/>
+      <c r="BA480" s="74">
+        <v>115.2</v>
+      </c>
+      <c r="BB480" s="2"/>
+      <c r="BC480" s="2"/>
+      <c r="BD480" s="74">
+        <v>25.8</v>
+      </c>
+      <c r="BE480" s="74">
+        <v>1004</v>
+      </c>
+      <c r="BF480" s="74">
+        <v>45</v>
+      </c>
+      <c r="BG480" s="74"/>
+      <c r="BH480" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI480" s="2"/>
+      <c r="BJ480" s="3" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="481" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A481" s="107" t="s">
+        <v>13</v>
+      </c>
+      <c r="B481" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C481" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D481" s="90">
+        <v>4</v>
+      </c>
+      <c r="E481" s="91" t="s">
+        <v>551</v>
+      </c>
+      <c r="F481" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="G481" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="H481" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I481" s="74">
+        <v>0.16189999999999999</v>
+      </c>
+      <c r="J481" s="74">
+        <v>0.16189999999999999</v>
+      </c>
+      <c r="K481" s="74">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="L481" s="92"/>
+      <c r="M481" s="74">
+        <v>0.1628</v>
+      </c>
+      <c r="N481" s="7">
+        <v>-0.52</v>
+      </c>
+      <c r="O481" s="4"/>
+      <c r="P481" s="74">
+        <v>1.2424999999999999</v>
+      </c>
+      <c r="Q481" s="92"/>
+      <c r="R481" s="94"/>
+      <c r="S481" s="94"/>
+      <c r="T481" s="74">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="U481" s="74">
+        <v>616</v>
+      </c>
+      <c r="V481" s="74">
+        <v>754.9</v>
+      </c>
+      <c r="W481" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="X481" s="4"/>
+      <c r="Y481" s="4"/>
+      <c r="Z481" s="7"/>
+      <c r="AA481" s="7"/>
+      <c r="AB481" s="7"/>
+      <c r="AC481" s="7"/>
+      <c r="AD481" s="7"/>
+      <c r="AE481" s="7"/>
+      <c r="AF481" s="7"/>
+      <c r="AG481" s="7"/>
+      <c r="AH481" s="7"/>
+      <c r="AI481" s="7"/>
+      <c r="AJ481" s="7"/>
+      <c r="AK481" s="7"/>
+      <c r="AL481" s="7"/>
+      <c r="AM481" s="7"/>
+      <c r="AN481" s="7"/>
+      <c r="AO481" s="7"/>
+      <c r="AP481" s="7"/>
+      <c r="AQ481" s="7"/>
+      <c r="AR481" s="7"/>
+      <c r="AS481" s="7"/>
+      <c r="AT481" s="7"/>
+      <c r="AU481" s="7"/>
+      <c r="AV481" s="7"/>
+      <c r="AW481" s="4"/>
+      <c r="AX481" s="2"/>
+      <c r="AY481" s="7"/>
+      <c r="AZ481" s="4"/>
+      <c r="BA481" s="74">
+        <v>115.2</v>
+      </c>
+      <c r="BB481" s="2"/>
+      <c r="BC481" s="2"/>
+      <c r="BD481" s="74">
+        <v>25.8</v>
+      </c>
+      <c r="BE481" s="74">
+        <v>1004</v>
+      </c>
+      <c r="BF481" s="74">
+        <v>45</v>
+      </c>
+      <c r="BG481" s="74"/>
+      <c r="BH481" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI481" s="2"/>
+      <c r="BJ481" s="3" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="482" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A482" s="107" t="s">
+        <v>13</v>
+      </c>
+      <c r="B482" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C482" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D482" s="90">
+        <v>5</v>
+      </c>
+      <c r="E482" s="91" t="s">
+        <v>551</v>
+      </c>
+      <c r="F482" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="G482" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="H482" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I482" s="74">
+        <v>0.16109999999999999</v>
+      </c>
+      <c r="J482" s="74">
+        <v>0.16109999999999999</v>
+      </c>
+      <c r="K482" s="74">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="L482" s="92"/>
+      <c r="M482" s="74">
+        <v>0.1588</v>
+      </c>
+      <c r="N482" s="7">
+        <v>-0.56000000000000005</v>
+      </c>
+      <c r="O482" s="4"/>
+      <c r="P482" s="74">
+        <v>1.2424999999999999</v>
+      </c>
+      <c r="Q482" s="92"/>
+      <c r="R482" s="94"/>
+      <c r="S482" s="94"/>
+      <c r="T482" s="74">
+        <v>66.900000000000006</v>
+      </c>
+      <c r="U482" s="74">
+        <v>630</v>
+      </c>
+      <c r="V482" s="74">
+        <v>755.8</v>
+      </c>
+      <c r="W482" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="X482" s="4"/>
+      <c r="Y482" s="4"/>
+      <c r="Z482" s="7"/>
+      <c r="AA482" s="7"/>
+      <c r="AB482" s="7"/>
+      <c r="AC482" s="7"/>
+      <c r="AD482" s="7"/>
+      <c r="AE482" s="7"/>
+      <c r="AF482" s="7"/>
+      <c r="AG482" s="7"/>
+      <c r="AH482" s="7"/>
+      <c r="AI482" s="7"/>
+      <c r="AJ482" s="7"/>
+      <c r="AK482" s="7"/>
+      <c r="AL482" s="7"/>
+      <c r="AM482" s="7"/>
+      <c r="AN482" s="7"/>
+      <c r="AO482" s="7"/>
+      <c r="AP482" s="7"/>
+      <c r="AQ482" s="7"/>
+      <c r="AR482" s="7"/>
+      <c r="AS482" s="7"/>
+      <c r="AT482" s="7"/>
+      <c r="AU482" s="7"/>
+      <c r="AV482" s="7"/>
+      <c r="AW482" s="4"/>
+      <c r="AX482" s="2"/>
+      <c r="AY482" s="7"/>
+      <c r="AZ482" s="4"/>
+      <c r="BA482" s="74">
+        <v>115.2</v>
+      </c>
+      <c r="BB482" s="2"/>
+      <c r="BC482" s="2"/>
+      <c r="BD482" s="74">
+        <v>25.8</v>
+      </c>
+      <c r="BE482" s="74">
+        <v>1004</v>
+      </c>
+      <c r="BF482" s="74">
+        <v>45</v>
+      </c>
+      <c r="BG482" s="74"/>
+      <c r="BH482" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI482" s="2"/>
+      <c r="BJ482" s="3" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="483" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A483" s="107" t="s">
+        <v>13</v>
+      </c>
+      <c r="B483" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C483" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D483" s="90">
+        <v>6</v>
+      </c>
+      <c r="E483" s="91" t="s">
+        <v>551</v>
+      </c>
+      <c r="F483" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="G483" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="H483" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I483" s="74">
+        <v>0.161</v>
+      </c>
+      <c r="J483" s="74">
+        <v>0.161</v>
+      </c>
+      <c r="K483" s="74">
+        <v>2E-3</v>
+      </c>
+      <c r="L483" s="92"/>
+      <c r="M483" s="74">
+        <v>0.1578</v>
+      </c>
+      <c r="N483" s="7">
+        <v>-0.56000000000000005</v>
+      </c>
+      <c r="O483" s="4"/>
+      <c r="P483" s="74">
+        <v>1.2424999999999999</v>
+      </c>
+      <c r="Q483" s="92"/>
+      <c r="R483" s="94"/>
+      <c r="S483" s="94"/>
+      <c r="T483" s="74">
+        <v>63.5</v>
+      </c>
+      <c r="U483" s="74">
+        <v>608</v>
+      </c>
+      <c r="V483" s="74">
+        <v>755.5</v>
+      </c>
+      <c r="W483" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="X483" s="4"/>
+      <c r="Y483" s="4"/>
+      <c r="Z483" s="7"/>
+      <c r="AA483" s="7"/>
+      <c r="AB483" s="7"/>
+      <c r="AC483" s="7"/>
+      <c r="AD483" s="7"/>
+      <c r="AE483" s="7"/>
+      <c r="AF483" s="7"/>
+      <c r="AG483" s="7"/>
+      <c r="AH483" s="7"/>
+      <c r="AI483" s="7"/>
+      <c r="AJ483" s="7"/>
+      <c r="AK483" s="7"/>
+      <c r="AL483" s="7"/>
+      <c r="AM483" s="7"/>
+      <c r="AN483" s="7"/>
+      <c r="AO483" s="7"/>
+      <c r="AP483" s="7"/>
+      <c r="AQ483" s="7"/>
+      <c r="AR483" s="7"/>
+      <c r="AS483" s="7"/>
+      <c r="AT483" s="7"/>
+      <c r="AU483" s="7"/>
+      <c r="AV483" s="7"/>
+      <c r="AW483" s="4"/>
+      <c r="AX483" s="2"/>
+      <c r="AY483" s="7"/>
+      <c r="AZ483" s="4"/>
+      <c r="BA483" s="74">
+        <v>115.2</v>
+      </c>
+      <c r="BB483" s="2"/>
+      <c r="BC483" s="2"/>
+      <c r="BD483" s="74">
+        <v>26.1</v>
+      </c>
+      <c r="BE483" s="74">
+        <v>1003.4</v>
+      </c>
+      <c r="BF483" s="74">
+        <v>44</v>
+      </c>
+      <c r="BG483" s="74"/>
+      <c r="BH483" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI483" s="2"/>
+      <c r="BJ483" s="3"/>
+    </row>
+    <row r="484" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A484" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="B484" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="C484" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D484" s="90">
+        <v>1</v>
+      </c>
+      <c r="E484" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="F484" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G484" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="H484" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I484" s="74">
+        <v>0.16209999999999999</v>
+      </c>
+      <c r="J484" s="74">
+        <v>0.16209999999999999</v>
+      </c>
+      <c r="K484" s="74">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="L484" s="92"/>
+      <c r="M484" s="74">
+        <v>0.16120000000000001</v>
+      </c>
+      <c r="N484" s="7">
+        <v>-0.48</v>
+      </c>
+      <c r="O484" s="4"/>
+      <c r="P484" s="74">
+        <v>1.2629999999999999</v>
+      </c>
+      <c r="Q484" s="92"/>
+      <c r="R484" s="94"/>
+      <c r="S484" s="94"/>
+      <c r="T484" s="74">
+        <v>62.2</v>
+      </c>
+      <c r="U484" s="74">
+        <v>510</v>
+      </c>
+      <c r="V484" s="74">
+        <v>754.6</v>
+      </c>
+      <c r="W484" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="X484" s="4"/>
+      <c r="Y484" s="4"/>
+      <c r="Z484" s="7"/>
+      <c r="AA484" s="7"/>
+      <c r="AB484" s="7"/>
+      <c r="AC484" s="7"/>
+      <c r="AD484" s="7"/>
+      <c r="AE484" s="7"/>
+      <c r="AF484" s="7"/>
+      <c r="AG484" s="7"/>
+      <c r="AH484" s="7"/>
+      <c r="AI484" s="7"/>
+      <c r="AJ484" s="7"/>
+      <c r="AK484" s="7"/>
+      <c r="AL484" s="7"/>
+      <c r="AM484" s="7"/>
+      <c r="AN484" s="7"/>
+      <c r="AO484" s="7"/>
+      <c r="AP484" s="7"/>
+      <c r="AQ484" s="7"/>
+      <c r="AR484" s="7"/>
+      <c r="AS484" s="7"/>
+      <c r="AT484" s="7"/>
+      <c r="AU484" s="7"/>
+      <c r="AV484" s="7"/>
+      <c r="AW484" s="4"/>
+      <c r="AX484" s="2"/>
+      <c r="AY484" s="7"/>
+      <c r="AZ484" s="4"/>
+      <c r="BA484" s="74">
+        <v>113.4</v>
+      </c>
+      <c r="BB484" s="2"/>
+      <c r="BC484" s="2"/>
+      <c r="BD484" s="74">
+        <v>25.3</v>
+      </c>
+      <c r="BE484" s="74">
+        <v>1004.3</v>
+      </c>
+      <c r="BF484" s="74">
+        <v>45.2</v>
+      </c>
+      <c r="BG484" s="74"/>
+      <c r="BH484" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI484" s="2"/>
+      <c r="BJ484" s="3" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="485" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A485" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="B485" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="C485" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D485" s="90">
+        <v>2</v>
+      </c>
+      <c r="E485" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="F485" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G485" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="H485" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I485" s="74">
+        <v>0.1603</v>
+      </c>
+      <c r="J485" s="74">
+        <v>0.1603</v>
+      </c>
+      <c r="K485" s="74">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="L485" s="92"/>
+      <c r="M485" s="74">
+        <v>0.1578</v>
+      </c>
+      <c r="N485" s="7">
+        <v>-0.5</v>
+      </c>
+      <c r="O485" s="4"/>
+      <c r="P485" s="74">
+        <v>1.2629999999999999</v>
+      </c>
+      <c r="Q485" s="92"/>
+      <c r="R485" s="94"/>
+      <c r="S485" s="94"/>
+      <c r="T485" s="74">
+        <v>61.6</v>
+      </c>
+      <c r="U485" s="74">
+        <v>487</v>
+      </c>
+      <c r="V485" s="74">
+        <v>753.8</v>
+      </c>
+      <c r="W485" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="X485" s="4"/>
+      <c r="Y485" s="4"/>
+      <c r="Z485" s="7"/>
+      <c r="AA485" s="7"/>
+      <c r="AB485" s="7"/>
+      <c r="AC485" s="7"/>
+      <c r="AD485" s="7"/>
+      <c r="AE485" s="7"/>
+      <c r="AF485" s="7"/>
+      <c r="AG485" s="7"/>
+      <c r="AH485" s="7"/>
+      <c r="AI485" s="7"/>
+      <c r="AJ485" s="7"/>
+      <c r="AK485" s="7"/>
+      <c r="AL485" s="7"/>
+      <c r="AM485" s="7"/>
+      <c r="AN485" s="7"/>
+      <c r="AO485" s="7"/>
+      <c r="AP485" s="7"/>
+      <c r="AQ485" s="7"/>
+      <c r="AR485" s="7"/>
+      <c r="AS485" s="7"/>
+      <c r="AT485" s="7"/>
+      <c r="AU485" s="7"/>
+      <c r="AV485" s="7"/>
+      <c r="AW485" s="4"/>
+      <c r="AX485" s="2"/>
+      <c r="AY485" s="7"/>
+      <c r="AZ485" s="4"/>
+      <c r="BA485" s="74">
+        <v>113.4</v>
+      </c>
+      <c r="BB485" s="2"/>
+      <c r="BC485" s="2"/>
+      <c r="BD485" s="74">
+        <v>25.3</v>
+      </c>
+      <c r="BE485" s="74">
+        <v>1004.3</v>
+      </c>
+      <c r="BF485" s="74">
+        <v>45.2</v>
+      </c>
+      <c r="BG485" s="74"/>
+      <c r="BH485" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI485" s="2"/>
+      <c r="BJ485" s="3" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="486" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A486" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="B486" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="C486" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D486" s="90">
+        <v>3</v>
+      </c>
+      <c r="E486" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="F486" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G486" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="H486" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I486" s="74">
+        <v>0.1661</v>
+      </c>
+      <c r="J486" s="74">
+        <v>0.1661</v>
+      </c>
+      <c r="K486" s="74">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="L486" s="92"/>
+      <c r="M486" s="74">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="N486" s="7">
+        <v>-0.52</v>
+      </c>
+      <c r="O486" s="4"/>
+      <c r="P486" s="74">
+        <v>1.2629999999999999</v>
+      </c>
+      <c r="Q486" s="92"/>
+      <c r="R486" s="94"/>
+      <c r="S486" s="94"/>
+      <c r="T486" s="74">
+        <v>61.7</v>
+      </c>
+      <c r="U486" s="74">
+        <v>507</v>
+      </c>
+      <c r="V486" s="74">
+        <v>753.7</v>
+      </c>
+      <c r="W486" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="X486" s="4"/>
+      <c r="Y486" s="4"/>
+      <c r="Z486" s="7"/>
+      <c r="AA486" s="7"/>
+      <c r="AB486" s="7"/>
+      <c r="AC486" s="7"/>
+      <c r="AD486" s="7"/>
+      <c r="AE486" s="7"/>
+      <c r="AF486" s="7"/>
+      <c r="AG486" s="7"/>
+      <c r="AH486" s="7"/>
+      <c r="AI486" s="7"/>
+      <c r="AJ486" s="7"/>
+      <c r="AK486" s="7"/>
+      <c r="AL486" s="7"/>
+      <c r="AM486" s="7"/>
+      <c r="AN486" s="7"/>
+      <c r="AO486" s="7"/>
+      <c r="AP486" s="7"/>
+      <c r="AQ486" s="7"/>
+      <c r="AR486" s="7"/>
+      <c r="AS486" s="7"/>
+      <c r="AT486" s="7"/>
+      <c r="AU486" s="7"/>
+      <c r="AV486" s="7"/>
+      <c r="AW486" s="4"/>
+      <c r="AX486" s="2"/>
+      <c r="AY486" s="7"/>
+      <c r="AZ486" s="4"/>
+      <c r="BA486" s="74">
+        <v>113.4</v>
+      </c>
+      <c r="BB486" s="2"/>
+      <c r="BC486" s="2"/>
+      <c r="BD486" s="74">
+        <v>25.8</v>
+      </c>
+      <c r="BE486" s="74">
+        <v>1004</v>
+      </c>
+      <c r="BF486" s="74">
+        <v>45</v>
+      </c>
+      <c r="BG486" s="74"/>
+      <c r="BH486" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI486" s="2"/>
+      <c r="BJ486" s="3" t="s">
         <v>657</v>
       </c>
+    </row>
+    <row r="487" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A487" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="B487" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="C487" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D487" s="90">
+        <v>4</v>
+      </c>
+      <c r="E487" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="F487" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G487" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="H487" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I487" s="74">
+        <v>0.1593</v>
+      </c>
+      <c r="J487" s="74">
+        <v>0.1593</v>
+      </c>
+      <c r="K487" s="74">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="L487" s="92"/>
+      <c r="M487" s="74">
+        <v>0.1565</v>
+      </c>
+      <c r="N487" s="7">
+        <v>-0.51</v>
+      </c>
+      <c r="O487" s="4"/>
+      <c r="P487" s="74">
+        <v>1.2629999999999999</v>
+      </c>
+      <c r="Q487" s="92"/>
+      <c r="R487" s="94"/>
+      <c r="S487" s="94"/>
+      <c r="T487" s="74">
+        <v>62.2</v>
+      </c>
+      <c r="U487" s="74">
+        <v>507</v>
+      </c>
+      <c r="V487" s="74">
+        <v>753.8</v>
+      </c>
+      <c r="W487" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="X487" s="4"/>
+      <c r="Y487" s="4"/>
+      <c r="Z487" s="7"/>
+      <c r="AA487" s="7"/>
+      <c r="AB487" s="7"/>
+      <c r="AC487" s="7"/>
+      <c r="AD487" s="7"/>
+      <c r="AE487" s="7"/>
+      <c r="AF487" s="7"/>
+      <c r="AG487" s="7"/>
+      <c r="AH487" s="7"/>
+      <c r="AI487" s="7"/>
+      <c r="AJ487" s="7"/>
+      <c r="AK487" s="7"/>
+      <c r="AL487" s="7"/>
+      <c r="AM487" s="7"/>
+      <c r="AN487" s="7"/>
+      <c r="AO487" s="7"/>
+      <c r="AP487" s="7"/>
+      <c r="AQ487" s="7"/>
+      <c r="AR487" s="7"/>
+      <c r="AS487" s="7"/>
+      <c r="AT487" s="7"/>
+      <c r="AU487" s="7"/>
+      <c r="AV487" s="7"/>
+      <c r="AW487" s="4"/>
+      <c r="AX487" s="2"/>
+      <c r="AY487" s="7"/>
+      <c r="AZ487" s="4"/>
+      <c r="BA487" s="74">
+        <v>113.4</v>
+      </c>
+      <c r="BB487" s="2"/>
+      <c r="BC487" s="2"/>
+      <c r="BD487" s="74">
+        <v>25.8</v>
+      </c>
+      <c r="BE487" s="74">
+        <v>1004</v>
+      </c>
+      <c r="BF487" s="74">
+        <v>45</v>
+      </c>
+      <c r="BG487" s="74"/>
+      <c r="BH487" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI487" s="2"/>
+      <c r="BJ487" s="3" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="488" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A488" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="B488" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="C488" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D488" s="90">
+        <v>5</v>
+      </c>
+      <c r="E488" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="F488" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G488" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="H488" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I488" s="74">
+        <v>0.1618</v>
+      </c>
+      <c r="J488" s="74">
+        <v>0.1618</v>
+      </c>
+      <c r="K488" s="74">
+        <v>6.1000000000000004E-3</v>
+      </c>
+      <c r="L488" s="92"/>
+      <c r="M488" s="74">
+        <v>0.1573</v>
+      </c>
+      <c r="N488" s="7">
+        <v>-0.52</v>
+      </c>
+      <c r="O488" s="4"/>
+      <c r="P488" s="74">
+        <v>1.2629999999999999</v>
+      </c>
+      <c r="Q488" s="92"/>
+      <c r="R488" s="94"/>
+      <c r="S488" s="94"/>
+      <c r="T488" s="74">
+        <v>62.3</v>
+      </c>
+      <c r="U488" s="74">
+        <v>510</v>
+      </c>
+      <c r="V488" s="74">
+        <v>754</v>
+      </c>
+      <c r="W488" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="X488" s="4"/>
+      <c r="Y488" s="4"/>
+      <c r="Z488" s="7"/>
+      <c r="AA488" s="7"/>
+      <c r="AB488" s="7"/>
+      <c r="AC488" s="7"/>
+      <c r="AD488" s="7"/>
+      <c r="AE488" s="7"/>
+      <c r="AF488" s="7"/>
+      <c r="AG488" s="7"/>
+      <c r="AH488" s="7"/>
+      <c r="AI488" s="7"/>
+      <c r="AJ488" s="7"/>
+      <c r="AK488" s="7"/>
+      <c r="AL488" s="7"/>
+      <c r="AM488" s="7"/>
+      <c r="AN488" s="7"/>
+      <c r="AO488" s="7"/>
+      <c r="AP488" s="7"/>
+      <c r="AQ488" s="7"/>
+      <c r="AR488" s="7"/>
+      <c r="AS488" s="7"/>
+      <c r="AT488" s="7"/>
+      <c r="AU488" s="7"/>
+      <c r="AV488" s="7"/>
+      <c r="AW488" s="4"/>
+      <c r="AX488" s="2"/>
+      <c r="AY488" s="7"/>
+      <c r="AZ488" s="4"/>
+      <c r="BA488" s="74">
+        <v>113.4</v>
+      </c>
+      <c r="BB488" s="2"/>
+      <c r="BC488" s="2"/>
+      <c r="BD488" s="74">
+        <v>25.8</v>
+      </c>
+      <c r="BE488" s="74">
+        <v>1004</v>
+      </c>
+      <c r="BF488" s="74">
+        <v>45</v>
+      </c>
+      <c r="BG488" s="74"/>
+      <c r="BH488" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI488" s="2"/>
+      <c r="BJ488" s="3" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="489" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A489" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="B489" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="C489" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D489" s="90">
+        <v>6</v>
+      </c>
+      <c r="E489" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="F489" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G489" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="H489" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I489" s="74">
+        <v>0.1681</v>
+      </c>
+      <c r="J489" s="74">
+        <v>0.1681</v>
+      </c>
+      <c r="K489" s="74">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="L489" s="92"/>
+      <c r="M489" s="74">
+        <v>0.16370000000000001</v>
+      </c>
+      <c r="N489" s="7">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="O489" s="4"/>
+      <c r="P489" s="74">
+        <v>1.2629999999999999</v>
+      </c>
+      <c r="Q489" s="92"/>
+      <c r="R489" s="94"/>
+      <c r="S489" s="94"/>
+      <c r="T489" s="74">
+        <v>62</v>
+      </c>
+      <c r="U489" s="74">
+        <v>507</v>
+      </c>
+      <c r="V489" s="74">
+        <v>753.8</v>
+      </c>
+      <c r="W489" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="X489" s="4"/>
+      <c r="Y489" s="4"/>
+      <c r="Z489" s="7"/>
+      <c r="AA489" s="7"/>
+      <c r="AB489" s="7"/>
+      <c r="AC489" s="7"/>
+      <c r="AD489" s="7"/>
+      <c r="AE489" s="7"/>
+      <c r="AF489" s="7"/>
+      <c r="AG489" s="7"/>
+      <c r="AH489" s="7"/>
+      <c r="AI489" s="7"/>
+      <c r="AJ489" s="7"/>
+      <c r="AK489" s="7"/>
+      <c r="AL489" s="7"/>
+      <c r="AM489" s="7"/>
+      <c r="AN489" s="7"/>
+      <c r="AO489" s="7"/>
+      <c r="AP489" s="7"/>
+      <c r="AQ489" s="7"/>
+      <c r="AR489" s="7"/>
+      <c r="AS489" s="7"/>
+      <c r="AT489" s="7"/>
+      <c r="AU489" s="7"/>
+      <c r="AV489" s="7"/>
+      <c r="AW489" s="4"/>
+      <c r="AX489" s="2"/>
+      <c r="AY489" s="7"/>
+      <c r="AZ489" s="4"/>
+      <c r="BA489" s="74">
+        <v>113.4</v>
+      </c>
+      <c r="BB489" s="2"/>
+      <c r="BC489" s="2"/>
+      <c r="BD489" s="74">
+        <v>26.1</v>
+      </c>
+      <c r="BE489" s="74">
+        <v>1003.4</v>
+      </c>
+      <c r="BF489" s="74">
+        <v>44</v>
+      </c>
+      <c r="BG489" s="74"/>
+      <c r="BH489" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI489" s="2"/>
+      <c r="BJ489" s="3" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="490" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A490" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="B490" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="C490" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D490" s="90">
+        <v>1</v>
+      </c>
+      <c r="E490" s="91" t="s">
+        <v>545</v>
+      </c>
+      <c r="F490" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G490" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="H490" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="I490" s="74">
+        <v>0.17319999999999999</v>
+      </c>
+      <c r="J490" s="74">
+        <v>0.17319999999999999</v>
+      </c>
+      <c r="K490" s="74">
+        <v>3.8E-3</v>
+      </c>
+      <c r="L490" s="92"/>
+      <c r="M490" s="74">
+        <v>0.16919999999999999</v>
+      </c>
+      <c r="N490" s="7">
+        <v>-0.6</v>
+      </c>
+      <c r="O490" s="4"/>
+      <c r="P490" s="74">
+        <v>1.26</v>
+      </c>
+      <c r="Q490" s="92"/>
+      <c r="R490" s="94"/>
+      <c r="S490" s="94"/>
+      <c r="T490" s="74">
+        <v>59.9</v>
+      </c>
+      <c r="U490" s="74">
+        <v>459</v>
+      </c>
+      <c r="V490" s="74">
+        <v>754.3</v>
+      </c>
+      <c r="W490" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="X490" s="4"/>
+      <c r="Y490" s="4"/>
+      <c r="Z490" s="7"/>
+      <c r="AA490" s="7"/>
+      <c r="AB490" s="7"/>
+      <c r="AC490" s="7"/>
+      <c r="AD490" s="7"/>
+      <c r="AE490" s="7"/>
+      <c r="AF490" s="7"/>
+      <c r="AG490" s="7"/>
+      <c r="AH490" s="7"/>
+      <c r="AI490" s="7"/>
+      <c r="AJ490" s="7"/>
+      <c r="AK490" s="7"/>
+      <c r="AL490" s="7"/>
+      <c r="AM490" s="7"/>
+      <c r="AN490" s="7"/>
+      <c r="AO490" s="7"/>
+      <c r="AP490" s="7"/>
+      <c r="AQ490" s="7"/>
+      <c r="AR490" s="7"/>
+      <c r="AS490" s="7"/>
+      <c r="AT490" s="7"/>
+      <c r="AU490" s="7"/>
+      <c r="AV490" s="7"/>
+      <c r="AW490" s="4"/>
+      <c r="AX490" s="2"/>
+      <c r="AY490" s="7"/>
+      <c r="AZ490" s="4"/>
+      <c r="BA490" s="74">
+        <v>111.6</v>
+      </c>
+      <c r="BB490" s="2"/>
+      <c r="BC490" s="2"/>
+      <c r="BD490" s="74">
+        <v>25.3</v>
+      </c>
+      <c r="BE490" s="74">
+        <v>1004.3</v>
+      </c>
+      <c r="BF490" s="74">
+        <v>45.2</v>
+      </c>
+      <c r="BG490" s="74"/>
+      <c r="BH490" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI490" s="2"/>
+      <c r="BJ490" s="3" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="491" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A491" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="B491" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="C491" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D491" s="90">
+        <v>2</v>
+      </c>
+      <c r="E491" s="91" t="s">
+        <v>545</v>
+      </c>
+      <c r="F491" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G491" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="H491" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="I491" s="74">
+        <v>0.16969999999999999</v>
+      </c>
+      <c r="J491" s="74">
+        <v>0.16969999999999999</v>
+      </c>
+      <c r="K491" s="74">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="L491" s="92"/>
+      <c r="M491" s="74">
+        <v>0.1686</v>
+      </c>
+      <c r="N491" s="7">
+        <v>-0.62</v>
+      </c>
+      <c r="O491" s="4"/>
+      <c r="P491" s="74">
+        <v>1.26</v>
+      </c>
+      <c r="Q491" s="92"/>
+      <c r="R491" s="94"/>
+      <c r="S491" s="94"/>
+      <c r="T491" s="74">
+        <v>58.7</v>
+      </c>
+      <c r="U491" s="74">
+        <v>470</v>
+      </c>
+      <c r="V491" s="74">
+        <v>754.4</v>
+      </c>
+      <c r="W491" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="X491" s="4"/>
+      <c r="Y491" s="4"/>
+      <c r="Z491" s="7"/>
+      <c r="AA491" s="7"/>
+      <c r="AB491" s="7"/>
+      <c r="AC491" s="7"/>
+      <c r="AD491" s="7"/>
+      <c r="AE491" s="7"/>
+      <c r="AF491" s="7"/>
+      <c r="AG491" s="7"/>
+      <c r="AH491" s="7"/>
+      <c r="AI491" s="7"/>
+      <c r="AJ491" s="7"/>
+      <c r="AK491" s="7"/>
+      <c r="AL491" s="7"/>
+      <c r="AM491" s="7"/>
+      <c r="AN491" s="7"/>
+      <c r="AO491" s="7"/>
+      <c r="AP491" s="7"/>
+      <c r="AQ491" s="7"/>
+      <c r="AR491" s="7"/>
+      <c r="AS491" s="7"/>
+      <c r="AT491" s="7"/>
+      <c r="AU491" s="7"/>
+      <c r="AV491" s="7"/>
+      <c r="AW491" s="4"/>
+      <c r="AX491" s="2"/>
+      <c r="AY491" s="7"/>
+      <c r="AZ491" s="4"/>
+      <c r="BA491" s="74">
+        <v>111.6</v>
+      </c>
+      <c r="BB491" s="2"/>
+      <c r="BC491" s="2"/>
+      <c r="BD491" s="74">
+        <v>25.3</v>
+      </c>
+      <c r="BE491" s="74">
+        <v>1004.3</v>
+      </c>
+      <c r="BF491" s="74">
+        <v>45.2</v>
+      </c>
+      <c r="BG491" s="74"/>
+      <c r="BH491" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI491" s="2"/>
+      <c r="BJ491" s="3" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="492" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A492" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="B492" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="C492" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D492" s="90">
+        <v>3</v>
+      </c>
+      <c r="E492" s="91" t="s">
+        <v>545</v>
+      </c>
+      <c r="F492" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G492" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="H492" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="I492" s="74">
+        <v>0.1729</v>
+      </c>
+      <c r="J492" s="74">
+        <v>0.1729</v>
+      </c>
+      <c r="K492" s="74">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="L492" s="92"/>
+      <c r="M492" s="74">
+        <v>0.16969999999999999</v>
+      </c>
+      <c r="N492" s="7">
+        <v>-0.69</v>
+      </c>
+      <c r="O492" s="4"/>
+      <c r="P492" s="74">
+        <v>1.26</v>
+      </c>
+      <c r="Q492" s="92"/>
+      <c r="R492" s="94"/>
+      <c r="S492" s="94"/>
+      <c r="T492" s="74">
+        <v>59.1</v>
+      </c>
+      <c r="U492" s="74">
+        <v>463</v>
+      </c>
+      <c r="V492" s="74">
+        <v>754.2</v>
+      </c>
+      <c r="W492" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="X492" s="4"/>
+      <c r="Y492" s="4"/>
+      <c r="Z492" s="7"/>
+      <c r="AA492" s="7"/>
+      <c r="AB492" s="7"/>
+      <c r="AC492" s="7"/>
+      <c r="AD492" s="7"/>
+      <c r="AE492" s="7"/>
+      <c r="AF492" s="7"/>
+      <c r="AG492" s="7"/>
+      <c r="AH492" s="7"/>
+      <c r="AI492" s="7"/>
+      <c r="AJ492" s="7"/>
+      <c r="AK492" s="7"/>
+      <c r="AL492" s="7"/>
+      <c r="AM492" s="7"/>
+      <c r="AN492" s="7"/>
+      <c r="AO492" s="7"/>
+      <c r="AP492" s="7"/>
+      <c r="AQ492" s="7"/>
+      <c r="AR492" s="7"/>
+      <c r="AS492" s="7"/>
+      <c r="AT492" s="7"/>
+      <c r="AU492" s="7"/>
+      <c r="AV492" s="7"/>
+      <c r="AW492" s="4"/>
+      <c r="AX492" s="2"/>
+      <c r="AY492" s="7"/>
+      <c r="AZ492" s="4"/>
+      <c r="BA492" s="74">
+        <v>111.6</v>
+      </c>
+      <c r="BB492" s="2"/>
+      <c r="BC492" s="2"/>
+      <c r="BD492" s="74">
+        <v>25.8</v>
+      </c>
+      <c r="BE492" s="74">
+        <v>1004</v>
+      </c>
+      <c r="BF492" s="74">
+        <v>45</v>
+      </c>
+      <c r="BG492" s="74"/>
+      <c r="BH492" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI492" s="2"/>
+      <c r="BJ492" s="3"/>
+    </row>
+    <row r="493" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A493" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="B493" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="C493" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D493" s="90">
+        <v>4</v>
+      </c>
+      <c r="E493" s="91" t="s">
+        <v>545</v>
+      </c>
+      <c r="F493" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G493" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="H493" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="I493" s="74">
+        <v>0.17380000000000001</v>
+      </c>
+      <c r="J493" s="74">
+        <v>0.17380000000000001</v>
+      </c>
+      <c r="K493" s="74">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="L493" s="92"/>
+      <c r="M493" s="74">
+        <v>0.17169999999999999</v>
+      </c>
+      <c r="N493" s="7">
+        <v>-0.7</v>
+      </c>
+      <c r="O493" s="4"/>
+      <c r="P493" s="74">
+        <v>1.26</v>
+      </c>
+      <c r="Q493" s="92"/>
+      <c r="R493" s="94"/>
+      <c r="S493" s="94"/>
+      <c r="T493" s="74">
+        <v>59.6</v>
+      </c>
+      <c r="U493" s="74">
+        <v>479</v>
+      </c>
+      <c r="V493" s="74">
+        <v>754.3</v>
+      </c>
+      <c r="W493" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="X493" s="4"/>
+      <c r="Y493" s="4"/>
+      <c r="Z493" s="7"/>
+      <c r="AA493" s="7"/>
+      <c r="AB493" s="7"/>
+      <c r="AC493" s="7"/>
+      <c r="AD493" s="7"/>
+      <c r="AE493" s="7"/>
+      <c r="AF493" s="7"/>
+      <c r="AG493" s="7"/>
+      <c r="AH493" s="7"/>
+      <c r="AI493" s="7"/>
+      <c r="AJ493" s="7"/>
+      <c r="AK493" s="7"/>
+      <c r="AL493" s="7"/>
+      <c r="AM493" s="7"/>
+      <c r="AN493" s="7"/>
+      <c r="AO493" s="7"/>
+      <c r="AP493" s="7"/>
+      <c r="AQ493" s="7"/>
+      <c r="AR493" s="7"/>
+      <c r="AS493" s="7"/>
+      <c r="AT493" s="7"/>
+      <c r="AU493" s="7"/>
+      <c r="AV493" s="7"/>
+      <c r="AW493" s="4"/>
+      <c r="AX493" s="2"/>
+      <c r="AY493" s="7"/>
+      <c r="AZ493" s="4"/>
+      <c r="BA493" s="74">
+        <v>111.6</v>
+      </c>
+      <c r="BB493" s="2"/>
+      <c r="BC493" s="2"/>
+      <c r="BD493" s="74">
+        <v>25.8</v>
+      </c>
+      <c r="BE493" s="74">
+        <v>1004</v>
+      </c>
+      <c r="BF493" s="74">
+        <v>45</v>
+      </c>
+      <c r="BG493" s="74"/>
+      <c r="BH493" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI493" s="2"/>
+      <c r="BJ493" s="3" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="494" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A494" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="B494" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="C494" s="77">
+        <v>45414</v>
+      </c>
+      <c r="D494" s="90">
+        <v>5</v>
+      </c>
+      <c r="E494" s="91" t="s">
+        <v>545</v>
+      </c>
+      <c r="F494" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G494" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="H494" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="I494" s="74">
+        <v>0.16889999999999999</v>
+      </c>
+      <c r="J494" s="74">
+        <v>0.16889999999999999</v>
+      </c>
+      <c r="K494" s="74">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="L494" s="92"/>
+      <c r="M494" s="74">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="N494" s="7">
+        <v>-0.5</v>
+      </c>
+      <c r="O494" s="4"/>
+      <c r="P494" s="74">
+        <v>1.26</v>
+      </c>
+      <c r="Q494" s="92"/>
+      <c r="R494" s="94"/>
+      <c r="S494" s="94"/>
+      <c r="T494" s="74">
+        <v>60.5</v>
+      </c>
+      <c r="U494" s="74">
+        <v>487</v>
+      </c>
+      <c r="V494" s="74">
+        <v>754.9</v>
+      </c>
+      <c r="W494" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="X494" s="4"/>
+      <c r="Y494" s="4"/>
+      <c r="Z494" s="7"/>
+      <c r="AA494" s="7"/>
+      <c r="AB494" s="7"/>
+      <c r="AC494" s="7"/>
+      <c r="AD494" s="7"/>
+      <c r="AE494" s="7"/>
+      <c r="AF494" s="7"/>
+      <c r="AG494" s="7"/>
+      <c r="AH494" s="7"/>
+      <c r="AI494" s="7"/>
+      <c r="AJ494" s="7"/>
+      <c r="AK494" s="7"/>
+      <c r="AL494" s="7"/>
+      <c r="AM494" s="7"/>
+      <c r="AN494" s="7"/>
+      <c r="AO494" s="7"/>
+      <c r="AP494" s="7"/>
+      <c r="AQ494" s="7"/>
+      <c r="AR494" s="7"/>
+      <c r="AS494" s="7"/>
+      <c r="AT494" s="7"/>
+      <c r="AU494" s="7"/>
+      <c r="AV494" s="7"/>
+      <c r="AW494" s="4"/>
+      <c r="AX494" s="2"/>
+      <c r="AY494" s="7"/>
+      <c r="AZ494" s="4"/>
+      <c r="BA494" s="74">
+        <v>111.6</v>
+      </c>
+      <c r="BB494" s="2"/>
+      <c r="BC494" s="2"/>
+      <c r="BD494" s="74">
+        <v>25.8</v>
+      </c>
+      <c r="BE494" s="74">
+        <v>1004</v>
+      </c>
+      <c r="BF494" s="74">
+        <v>45</v>
+      </c>
+      <c r="BG494" s="74"/>
+      <c r="BH494" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI494" s="2"/>
+      <c r="BJ494" s="3" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="495" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A495" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="B495" s="99" t="s">
+        <v>210</v>
+      </c>
+      <c r="C495" s="100">
+        <v>45414</v>
+      </c>
+      <c r="D495" s="101">
+        <v>6</v>
+      </c>
+      <c r="E495" s="91" t="s">
+        <v>545</v>
+      </c>
+      <c r="F495" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G495" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="H495" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="I495" s="74">
+        <v>0.16259999999999999</v>
+      </c>
+      <c r="J495" s="74">
+        <v>0.16259999999999999</v>
+      </c>
+      <c r="K495" s="74">
+        <v>2.8E-3</v>
+      </c>
+      <c r="L495" s="103"/>
+      <c r="M495" s="74">
+        <v>0.1623</v>
+      </c>
+      <c r="N495" s="7">
+        <v>-0.52</v>
+      </c>
+      <c r="O495" s="102"/>
+      <c r="P495" s="74">
+        <v>1.26</v>
+      </c>
+      <c r="Q495" s="103"/>
+      <c r="R495" s="105"/>
+      <c r="S495" s="105"/>
+      <c r="T495" s="74">
+        <v>60.8</v>
+      </c>
+      <c r="U495" s="74">
+        <v>485</v>
+      </c>
+      <c r="V495" s="74">
+        <v>754.8</v>
+      </c>
+      <c r="W495" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="X495" s="102"/>
+      <c r="Y495" s="102"/>
+      <c r="Z495" s="104"/>
+      <c r="AA495" s="104"/>
+      <c r="AB495" s="104"/>
+      <c r="AC495" s="104"/>
+      <c r="AD495" s="104"/>
+      <c r="AE495" s="104"/>
+      <c r="AF495" s="104"/>
+      <c r="AG495" s="104"/>
+      <c r="AH495" s="104"/>
+      <c r="AI495" s="104"/>
+      <c r="AJ495" s="104"/>
+      <c r="AK495" s="104"/>
+      <c r="AL495" s="104"/>
+      <c r="AM495" s="104"/>
+      <c r="AN495" s="104"/>
+      <c r="AO495" s="104"/>
+      <c r="AP495" s="104"/>
+      <c r="AQ495" s="104"/>
+      <c r="AR495" s="104"/>
+      <c r="AS495" s="104"/>
+      <c r="AT495" s="104"/>
+      <c r="AU495" s="104"/>
+      <c r="AV495" s="104"/>
+      <c r="AW495" s="102"/>
+      <c r="AX495" s="98"/>
+      <c r="AY495" s="104"/>
+      <c r="AZ495" s="102"/>
+      <c r="BA495" s="74">
+        <v>111.6</v>
+      </c>
+      <c r="BB495" s="98"/>
+      <c r="BC495" s="98"/>
+      <c r="BD495" s="74">
+        <v>26.1</v>
+      </c>
+      <c r="BE495" s="74">
+        <v>1003.4</v>
+      </c>
+      <c r="BF495" s="74">
+        <v>44</v>
+      </c>
+      <c r="BG495" s="74"/>
+      <c r="BH495" s="74">
+        <v>2096</v>
+      </c>
+      <c r="BI495" s="98"/>
+      <c r="BJ495" s="106" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="496" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A496" s="75"/>
+      <c r="B496" s="54"/>
+      <c r="D496" s="108"/>
+      <c r="E496" s="91"/>
+      <c r="F496" s="4"/>
+      <c r="G496" s="4"/>
+      <c r="H496" s="4"/>
+      <c r="I496" s="92"/>
+      <c r="K496" s="93"/>
+      <c r="L496" s="92"/>
+      <c r="M496" s="94"/>
+      <c r="O496" s="4"/>
+      <c r="P496" s="92"/>
+      <c r="Q496" s="92"/>
+      <c r="R496" s="94"/>
+      <c r="S496" s="94"/>
+      <c r="T496" s="94"/>
+      <c r="U496" s="94"/>
+      <c r="V496" s="92"/>
+      <c r="W496" s="74"/>
+      <c r="X496" s="4"/>
+      <c r="Y496" s="4"/>
+      <c r="Z496" s="7"/>
+      <c r="AA496" s="7"/>
+      <c r="AB496" s="7"/>
+      <c r="AC496" s="7"/>
+      <c r="AD496" s="7"/>
+      <c r="AE496" s="7"/>
+      <c r="AF496" s="7"/>
+      <c r="AG496" s="7"/>
+      <c r="AH496" s="7"/>
+      <c r="AI496" s="7"/>
+      <c r="AJ496" s="7"/>
+      <c r="AK496" s="7"/>
+      <c r="AL496" s="7"/>
+      <c r="AM496" s="7"/>
+      <c r="AN496" s="7"/>
+      <c r="AO496" s="7"/>
+      <c r="AP496" s="7"/>
+      <c r="AQ496" s="7"/>
+      <c r="AR496" s="7"/>
+      <c r="AS496" s="7"/>
+      <c r="AT496" s="7"/>
+      <c r="AU496" s="7"/>
+      <c r="AV496" s="7"/>
+      <c r="AW496" s="4"/>
+      <c r="AX496" s="2"/>
+      <c r="AY496" s="7"/>
+      <c r="AZ496" s="4"/>
+      <c r="BA496" s="4"/>
+      <c r="BB496" s="2"/>
+      <c r="BC496" s="2"/>
+      <c r="BD496" s="2"/>
+      <c r="BE496" s="95"/>
+      <c r="BF496" s="96"/>
+      <c r="BG496" s="97"/>
+      <c r="BH496" s="2"/>
+      <c r="BI496" s="2"/>
+      <c r="BJ496" s="3"/>
+    </row>
+    <row r="497" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A497" s="75"/>
+      <c r="B497" s="54"/>
+      <c r="D497" s="108"/>
+      <c r="E497" s="91"/>
+      <c r="F497" s="4"/>
+      <c r="G497" s="4"/>
+      <c r="H497" s="4"/>
+      <c r="I497" s="92"/>
+      <c r="K497" s="93"/>
+      <c r="L497" s="92"/>
+      <c r="M497" s="94"/>
+      <c r="O497" s="4"/>
+      <c r="P497" s="92"/>
+      <c r="Q497" s="92"/>
+      <c r="R497" s="94"/>
+      <c r="S497" s="94"/>
+      <c r="T497" s="94"/>
+      <c r="U497" s="94"/>
+      <c r="V497" s="92"/>
+      <c r="W497" s="74"/>
+      <c r="X497" s="4"/>
+      <c r="Y497" s="4"/>
+      <c r="Z497" s="7"/>
+      <c r="AA497" s="7"/>
+      <c r="AB497" s="7"/>
+      <c r="AC497" s="7"/>
+      <c r="AD497" s="7"/>
+      <c r="AE497" s="7"/>
+      <c r="AF497" s="7"/>
+      <c r="AG497" s="7"/>
+      <c r="AH497" s="7"/>
+      <c r="AI497" s="7"/>
+      <c r="AJ497" s="7"/>
+      <c r="AK497" s="7"/>
+      <c r="AL497" s="7"/>
+      <c r="AM497" s="7"/>
+      <c r="AN497" s="7"/>
+      <c r="AO497" s="7"/>
+      <c r="AP497" s="7"/>
+      <c r="AQ497" s="7"/>
+      <c r="AR497" s="7"/>
+      <c r="AS497" s="7"/>
+      <c r="AT497" s="7"/>
+      <c r="AU497" s="7"/>
+      <c r="AV497" s="7"/>
+      <c r="AW497" s="4"/>
+      <c r="AX497" s="2"/>
+      <c r="AY497" s="7"/>
+      <c r="AZ497" s="4"/>
+      <c r="BA497" s="4"/>
+      <c r="BB497" s="2"/>
+      <c r="BC497" s="2"/>
+      <c r="BD497" s="2"/>
+      <c r="BE497" s="95"/>
+      <c r="BF497" s="96"/>
+      <c r="BG497" s="97"/>
+      <c r="BH497" s="2"/>
+      <c r="BI497" s="2"/>
+      <c r="BJ497" s="3"/>
+    </row>
+    <row r="498" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A498" s="75"/>
+      <c r="B498" s="54"/>
+      <c r="D498" s="108"/>
+      <c r="E498" s="91"/>
+      <c r="F498" s="4"/>
+      <c r="G498" s="4"/>
+      <c r="H498" s="4"/>
+      <c r="I498" s="92"/>
+      <c r="K498" s="93"/>
+      <c r="L498" s="92"/>
+      <c r="M498" s="94"/>
+      <c r="O498" s="4"/>
+      <c r="P498" s="92"/>
+      <c r="Q498" s="92"/>
+      <c r="R498" s="94"/>
+      <c r="S498" s="94"/>
+      <c r="T498" s="94"/>
+      <c r="U498" s="94"/>
+      <c r="V498" s="92"/>
+      <c r="W498" s="74"/>
+      <c r="X498" s="4"/>
+      <c r="Y498" s="4"/>
+      <c r="Z498" s="7"/>
+      <c r="AA498" s="7"/>
+      <c r="AB498" s="7"/>
+      <c r="AC498" s="7"/>
+      <c r="AD498" s="7"/>
+      <c r="AE498" s="7"/>
+      <c r="AF498" s="7"/>
+      <c r="AG498" s="7"/>
+      <c r="AH498" s="7"/>
+      <c r="AI498" s="7"/>
+      <c r="AJ498" s="7"/>
+      <c r="AK498" s="7"/>
+      <c r="AL498" s="7"/>
+      <c r="AM498" s="7"/>
+      <c r="AN498" s="7"/>
+      <c r="AO498" s="7"/>
+      <c r="AP498" s="7"/>
+      <c r="AQ498" s="7"/>
+      <c r="AR498" s="7"/>
+      <c r="AS498" s="7"/>
+      <c r="AT498" s="7"/>
+      <c r="AU498" s="7"/>
+      <c r="AV498" s="7"/>
+      <c r="AW498" s="4"/>
+      <c r="AX498" s="2"/>
+      <c r="AY498" s="7"/>
+      <c r="AZ498" s="4"/>
+      <c r="BA498" s="4"/>
+      <c r="BB498" s="2"/>
+      <c r="BC498" s="2"/>
+      <c r="BD498" s="2"/>
+      <c r="BE498" s="95"/>
+      <c r="BF498" s="96"/>
+      <c r="BG498" s="97"/>
+      <c r="BH498" s="2"/>
+      <c r="BI498" s="2"/>
+      <c r="BJ498" s="3"/>
+    </row>
+    <row r="499" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A499" s="75"/>
+      <c r="B499" s="54"/>
+      <c r="D499" s="108"/>
+      <c r="E499" s="91"/>
+      <c r="F499" s="4"/>
+      <c r="G499" s="4"/>
+      <c r="H499" s="4"/>
+      <c r="I499" s="92"/>
+      <c r="K499" s="93"/>
+      <c r="L499" s="92"/>
+      <c r="M499" s="94"/>
+      <c r="O499" s="4"/>
+      <c r="P499" s="92"/>
+      <c r="Q499" s="92"/>
+      <c r="R499" s="94"/>
+      <c r="S499" s="94"/>
+      <c r="T499" s="94"/>
+      <c r="U499" s="94"/>
+      <c r="V499" s="92"/>
+      <c r="W499" s="74"/>
+      <c r="X499" s="4"/>
+      <c r="Y499" s="4"/>
+      <c r="Z499" s="7"/>
+      <c r="AA499" s="7"/>
+      <c r="AB499" s="7"/>
+      <c r="AC499" s="7"/>
+      <c r="AD499" s="7"/>
+      <c r="AE499" s="7"/>
+      <c r="AF499" s="7"/>
+      <c r="AG499" s="7"/>
+      <c r="AH499" s="7"/>
+      <c r="AI499" s="7"/>
+      <c r="AJ499" s="7"/>
+      <c r="AK499" s="7"/>
+      <c r="AL499" s="7"/>
+      <c r="AM499" s="7"/>
+      <c r="AN499" s="7"/>
+      <c r="AO499" s="7"/>
+      <c r="AP499" s="7"/>
+      <c r="AQ499" s="7"/>
+      <c r="AR499" s="7"/>
+      <c r="AS499" s="7"/>
+      <c r="AT499" s="7"/>
+      <c r="AU499" s="7"/>
+      <c r="AV499" s="7"/>
+      <c r="AW499" s="4"/>
+      <c r="AX499" s="2"/>
+      <c r="AY499" s="7"/>
+      <c r="AZ499" s="4"/>
+      <c r="BA499" s="4"/>
+      <c r="BB499" s="2"/>
+      <c r="BC499" s="2"/>
+      <c r="BD499" s="2"/>
+      <c r="BE499" s="95"/>
+      <c r="BF499" s="96"/>
+      <c r="BG499" s="97"/>
+      <c r="BH499" s="2"/>
+      <c r="BI499" s="2"/>
+      <c r="BJ499" s="3"/>
+    </row>
+    <row r="500" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A500" s="75"/>
+      <c r="B500" s="54"/>
+      <c r="D500" s="108"/>
+      <c r="E500" s="91"/>
+      <c r="F500" s="4"/>
+      <c r="G500" s="4"/>
+      <c r="H500" s="4"/>
+      <c r="I500" s="92"/>
+      <c r="K500" s="93"/>
+      <c r="L500" s="92"/>
+      <c r="M500" s="94"/>
+      <c r="O500" s="4"/>
+      <c r="P500" s="92"/>
+      <c r="Q500" s="92"/>
+      <c r="R500" s="94"/>
+      <c r="S500" s="94"/>
+      <c r="T500" s="94"/>
+      <c r="U500" s="94"/>
+      <c r="V500" s="92"/>
+      <c r="W500" s="74"/>
+      <c r="X500" s="4"/>
+      <c r="Y500" s="4"/>
+      <c r="Z500" s="7"/>
+      <c r="AA500" s="7"/>
+      <c r="AB500" s="7"/>
+      <c r="AC500" s="7"/>
+      <c r="AD500" s="7"/>
+      <c r="AE500" s="7"/>
+      <c r="AF500" s="7"/>
+      <c r="AG500" s="7"/>
+      <c r="AH500" s="7"/>
+      <c r="AI500" s="7"/>
+      <c r="AJ500" s="7"/>
+      <c r="AK500" s="7"/>
+      <c r="AL500" s="7"/>
+      <c r="AM500" s="7"/>
+      <c r="AN500" s="7"/>
+      <c r="AO500" s="7"/>
+      <c r="AP500" s="7"/>
+      <c r="AQ500" s="7"/>
+      <c r="AR500" s="7"/>
+      <c r="AS500" s="7"/>
+      <c r="AT500" s="7"/>
+      <c r="AU500" s="7"/>
+      <c r="AV500" s="7"/>
+      <c r="AW500" s="4"/>
+      <c r="AX500" s="2"/>
+      <c r="AY500" s="7"/>
+      <c r="AZ500" s="4"/>
+      <c r="BA500" s="4"/>
+      <c r="BB500" s="2"/>
+      <c r="BC500" s="2"/>
+      <c r="BD500" s="2"/>
+      <c r="BE500" s="95"/>
+      <c r="BF500" s="96"/>
+      <c r="BG500" s="97"/>
+      <c r="BH500" s="2"/>
+      <c r="BI500" s="2"/>
+      <c r="BJ500" s="3"/>
+    </row>
+    <row r="501" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A501" s="75"/>
+      <c r="B501" s="54"/>
+      <c r="D501" s="108"/>
+      <c r="E501" s="91"/>
+      <c r="F501" s="4"/>
+      <c r="G501" s="4"/>
+      <c r="H501" s="4"/>
+      <c r="I501" s="92"/>
+      <c r="K501" s="93"/>
+      <c r="L501" s="92"/>
+      <c r="M501" s="94"/>
+      <c r="O501" s="4"/>
+      <c r="P501" s="92"/>
+      <c r="Q501" s="92"/>
+      <c r="R501" s="94"/>
+      <c r="S501" s="94"/>
+      <c r="T501" s="94"/>
+      <c r="U501" s="94"/>
+      <c r="V501" s="92"/>
+      <c r="W501" s="74"/>
+      <c r="X501" s="4"/>
+      <c r="Y501" s="4"/>
+      <c r="Z501" s="7"/>
+      <c r="AA501" s="7"/>
+      <c r="AB501" s="7"/>
+      <c r="AC501" s="7"/>
+      <c r="AD501" s="7"/>
+      <c r="AE501" s="7"/>
+      <c r="AF501" s="7"/>
+      <c r="AG501" s="7"/>
+      <c r="AH501" s="7"/>
+      <c r="AI501" s="7"/>
+      <c r="AJ501" s="7"/>
+      <c r="AK501" s="7"/>
+      <c r="AL501" s="7"/>
+      <c r="AM501" s="7"/>
+      <c r="AN501" s="7"/>
+      <c r="AO501" s="7"/>
+      <c r="AP501" s="7"/>
+      <c r="AQ501" s="7"/>
+      <c r="AR501" s="7"/>
+      <c r="AS501" s="7"/>
+      <c r="AT501" s="7"/>
+      <c r="AU501" s="7"/>
+      <c r="AV501" s="7"/>
+      <c r="AW501" s="4"/>
+      <c r="AX501" s="2"/>
+      <c r="AY501" s="7"/>
+      <c r="AZ501" s="4"/>
+      <c r="BA501" s="4"/>
+      <c r="BB501" s="2"/>
+      <c r="BC501" s="2"/>
+      <c r="BD501" s="2"/>
+      <c r="BE501" s="95"/>
+      <c r="BF501" s="96"/>
+      <c r="BG501" s="97"/>
+      <c r="BH501" s="2"/>
+      <c r="BI501" s="2"/>
+      <c r="BJ501" s="3"/>
+    </row>
+    <row r="502" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A502" s="75"/>
+      <c r="B502" s="54"/>
+      <c r="D502" s="108"/>
+      <c r="E502" s="91"/>
+      <c r="F502" s="4"/>
+      <c r="G502" s="4"/>
+      <c r="H502" s="4"/>
+      <c r="I502" s="92"/>
+      <c r="K502" s="93"/>
+      <c r="L502" s="92"/>
+      <c r="M502" s="94"/>
+      <c r="O502" s="4"/>
+      <c r="P502" s="92"/>
+      <c r="Q502" s="92"/>
+      <c r="R502" s="94"/>
+      <c r="S502" s="94"/>
+      <c r="T502" s="94"/>
+      <c r="U502" s="94"/>
+      <c r="V502" s="92"/>
+      <c r="W502" s="74"/>
+      <c r="X502" s="4"/>
+      <c r="Y502" s="4"/>
+      <c r="Z502" s="7"/>
+      <c r="AA502" s="7"/>
+      <c r="AB502" s="7"/>
+      <c r="AC502" s="7"/>
+      <c r="AD502" s="7"/>
+      <c r="AE502" s="7"/>
+      <c r="AF502" s="7"/>
+      <c r="AG502" s="7"/>
+      <c r="AH502" s="7"/>
+      <c r="AI502" s="7"/>
+      <c r="AJ502" s="7"/>
+      <c r="AK502" s="7"/>
+      <c r="AL502" s="7"/>
+      <c r="AM502" s="7"/>
+      <c r="AN502" s="7"/>
+      <c r="AO502" s="7"/>
+      <c r="AP502" s="7"/>
+      <c r="AQ502" s="7"/>
+      <c r="AR502" s="7"/>
+      <c r="AS502" s="7"/>
+      <c r="AT502" s="7"/>
+      <c r="AU502" s="7"/>
+      <c r="AV502" s="7"/>
+      <c r="AW502" s="4"/>
+      <c r="AX502" s="2"/>
+      <c r="AY502" s="7"/>
+      <c r="AZ502" s="4"/>
+      <c r="BA502" s="4"/>
+      <c r="BB502" s="2"/>
+      <c r="BC502" s="2"/>
+      <c r="BD502" s="2"/>
+      <c r="BE502" s="95"/>
+      <c r="BF502" s="96"/>
+      <c r="BG502" s="97"/>
+      <c r="BH502" s="2"/>
+      <c r="BI502" s="2"/>
+      <c r="BJ502" s="3"/>
+    </row>
+    <row r="503" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A503" s="75"/>
+      <c r="B503" s="54"/>
+      <c r="D503" s="108"/>
+      <c r="E503" s="91"/>
+      <c r="F503" s="4"/>
+      <c r="G503" s="4"/>
+      <c r="H503" s="4"/>
+      <c r="I503" s="92"/>
+      <c r="K503" s="93"/>
+      <c r="L503" s="92"/>
+      <c r="M503" s="94"/>
+      <c r="O503" s="4"/>
+      <c r="P503" s="92"/>
+      <c r="Q503" s="92"/>
+      <c r="R503" s="94"/>
+      <c r="S503" s="94"/>
+      <c r="T503" s="94"/>
+      <c r="U503" s="94"/>
+      <c r="V503" s="92"/>
+      <c r="W503" s="74"/>
+      <c r="X503" s="4"/>
+      <c r="Y503" s="4"/>
+      <c r="Z503" s="7"/>
+      <c r="AA503" s="7"/>
+      <c r="AB503" s="7"/>
+      <c r="AC503" s="7"/>
+      <c r="AD503" s="7"/>
+      <c r="AE503" s="7"/>
+      <c r="AF503" s="7"/>
+      <c r="AG503" s="7"/>
+      <c r="AH503" s="7"/>
+      <c r="AI503" s="7"/>
+      <c r="AJ503" s="7"/>
+      <c r="AK503" s="7"/>
+      <c r="AL503" s="7"/>
+      <c r="AM503" s="7"/>
+      <c r="AN503" s="7"/>
+      <c r="AO503" s="7"/>
+      <c r="AP503" s="7"/>
+      <c r="AQ503" s="7"/>
+      <c r="AR503" s="7"/>
+      <c r="AS503" s="7"/>
+      <c r="AT503" s="7"/>
+      <c r="AU503" s="7"/>
+      <c r="AV503" s="7"/>
+      <c r="AW503" s="4"/>
+      <c r="AX503" s="2"/>
+      <c r="AY503" s="7"/>
+      <c r="AZ503" s="4"/>
+      <c r="BA503" s="4"/>
+      <c r="BB503" s="2"/>
+      <c r="BC503" s="2"/>
+      <c r="BD503" s="2"/>
+      <c r="BE503" s="95"/>
+      <c r="BF503" s="96"/>
+      <c r="BG503" s="97"/>
+      <c r="BH503" s="2"/>
+      <c r="BI503" s="2"/>
+      <c r="BJ503" s="3"/>
+    </row>
+    <row r="504" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A504" s="75"/>
+      <c r="B504" s="54"/>
+      <c r="D504" s="108"/>
+      <c r="E504" s="91"/>
+      <c r="F504" s="4"/>
+      <c r="G504" s="4"/>
+      <c r="H504" s="4"/>
+      <c r="I504" s="92"/>
+      <c r="K504" s="93"/>
+      <c r="L504" s="92"/>
+      <c r="M504" s="94"/>
+      <c r="O504" s="4"/>
+      <c r="P504" s="92"/>
+      <c r="Q504" s="92"/>
+      <c r="R504" s="94"/>
+      <c r="S504" s="94"/>
+      <c r="T504" s="94"/>
+      <c r="U504" s="94"/>
+      <c r="V504" s="92"/>
+      <c r="W504" s="74"/>
+      <c r="X504" s="4"/>
+      <c r="Y504" s="4"/>
+      <c r="Z504" s="7"/>
+      <c r="AA504" s="7"/>
+      <c r="AB504" s="7"/>
+      <c r="AC504" s="7"/>
+      <c r="AD504" s="7"/>
+      <c r="AE504" s="7"/>
+      <c r="AF504" s="7"/>
+      <c r="AG504" s="7"/>
+      <c r="AH504" s="7"/>
+      <c r="AI504" s="7"/>
+      <c r="AJ504" s="7"/>
+      <c r="AK504" s="7"/>
+      <c r="AL504" s="7"/>
+      <c r="AM504" s="7"/>
+      <c r="AN504" s="7"/>
+      <c r="AO504" s="7"/>
+      <c r="AP504" s="7"/>
+      <c r="AQ504" s="7"/>
+      <c r="AR504" s="7"/>
+      <c r="AS504" s="7"/>
+      <c r="AT504" s="7"/>
+      <c r="AU504" s="7"/>
+      <c r="AV504" s="7"/>
+      <c r="AW504" s="4"/>
+      <c r="AX504" s="2"/>
+      <c r="AY504" s="7"/>
+      <c r="AZ504" s="4"/>
+      <c r="BA504" s="4"/>
+      <c r="BB504" s="2"/>
+      <c r="BC504" s="2"/>
+      <c r="BD504" s="2"/>
+      <c r="BE504" s="95"/>
+      <c r="BF504" s="96"/>
+      <c r="BG504" s="97"/>
+      <c r="BH504" s="2"/>
+      <c r="BI504" s="2"/>
+      <c r="BJ504" s="3"/>
+    </row>
+    <row r="505" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A505" s="75"/>
+      <c r="B505" s="54"/>
+      <c r="D505" s="108"/>
+      <c r="E505" s="91"/>
+      <c r="F505" s="4"/>
+      <c r="G505" s="4"/>
+      <c r="H505" s="4"/>
+      <c r="I505" s="92"/>
+      <c r="K505" s="93"/>
+      <c r="L505" s="92"/>
+      <c r="M505" s="94"/>
+      <c r="O505" s="4"/>
+      <c r="P505" s="92"/>
+      <c r="Q505" s="92"/>
+      <c r="R505" s="94"/>
+      <c r="S505" s="94"/>
+      <c r="T505" s="94"/>
+      <c r="U505" s="94"/>
+      <c r="V505" s="92"/>
+      <c r="W505" s="74"/>
+      <c r="X505" s="4"/>
+      <c r="Y505" s="4"/>
+      <c r="Z505" s="7"/>
+      <c r="AA505" s="7"/>
+      <c r="AB505" s="7"/>
+      <c r="AC505" s="7"/>
+      <c r="AD505" s="7"/>
+      <c r="AE505" s="7"/>
+      <c r="AF505" s="7"/>
+      <c r="AG505" s="7"/>
+      <c r="AH505" s="7"/>
+      <c r="AI505" s="7"/>
+      <c r="AJ505" s="7"/>
+      <c r="AK505" s="7"/>
+      <c r="AL505" s="7"/>
+      <c r="AM505" s="7"/>
+      <c r="AN505" s="7"/>
+      <c r="AO505" s="7"/>
+      <c r="AP505" s="7"/>
+      <c r="AQ505" s="7"/>
+      <c r="AR505" s="7"/>
+      <c r="AS505" s="7"/>
+      <c r="AT505" s="7"/>
+      <c r="AU505" s="7"/>
+      <c r="AV505" s="7"/>
+      <c r="AW505" s="4"/>
+      <c r="AX505" s="2"/>
+      <c r="AY505" s="7"/>
+      <c r="AZ505" s="4"/>
+      <c r="BA505" s="4"/>
+      <c r="BB505" s="2"/>
+      <c r="BC505" s="2"/>
+      <c r="BD505" s="2"/>
+      <c r="BE505" s="95"/>
+      <c r="BF505" s="96"/>
+      <c r="BG505" s="97"/>
+      <c r="BH505" s="2"/>
+      <c r="BI505" s="2"/>
+      <c r="BJ505" s="3"/>
+    </row>
+    <row r="506" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A506" s="75"/>
+      <c r="B506" s="54"/>
+      <c r="D506" s="108"/>
+      <c r="E506" s="91"/>
+      <c r="F506" s="4"/>
+      <c r="G506" s="4"/>
+      <c r="H506" s="4"/>
+      <c r="I506" s="92"/>
+      <c r="K506" s="93"/>
+      <c r="L506" s="92"/>
+      <c r="M506" s="94"/>
+      <c r="O506" s="4"/>
+      <c r="P506" s="92"/>
+      <c r="Q506" s="92"/>
+      <c r="R506" s="94"/>
+      <c r="S506" s="94"/>
+      <c r="T506" s="94"/>
+      <c r="U506" s="94"/>
+      <c r="V506" s="92"/>
+      <c r="W506" s="74"/>
+      <c r="X506" s="4"/>
+      <c r="Y506" s="4"/>
+      <c r="Z506" s="7"/>
+      <c r="AA506" s="7"/>
+      <c r="AB506" s="7"/>
+      <c r="AC506" s="7"/>
+      <c r="AD506" s="7"/>
+      <c r="AE506" s="7"/>
+      <c r="AF506" s="7"/>
+      <c r="AG506" s="7"/>
+      <c r="AH506" s="7"/>
+      <c r="AI506" s="7"/>
+      <c r="AJ506" s="7"/>
+      <c r="AK506" s="7"/>
+      <c r="AL506" s="7"/>
+      <c r="AM506" s="7"/>
+      <c r="AN506" s="7"/>
+      <c r="AO506" s="7"/>
+      <c r="AP506" s="7"/>
+      <c r="AQ506" s="7"/>
+      <c r="AR506" s="7"/>
+      <c r="AS506" s="7"/>
+      <c r="AT506" s="7"/>
+      <c r="AU506" s="7"/>
+      <c r="AV506" s="7"/>
+      <c r="AW506" s="4"/>
+      <c r="AX506" s="2"/>
+      <c r="AY506" s="7"/>
+      <c r="AZ506" s="4"/>
+      <c r="BA506" s="4"/>
+      <c r="BB506" s="2"/>
+      <c r="BC506" s="2"/>
+      <c r="BD506" s="2"/>
+      <c r="BE506" s="95"/>
+      <c r="BF506" s="96"/>
+      <c r="BG506" s="97"/>
+      <c r="BH506" s="2"/>
+      <c r="BI506" s="2"/>
+      <c r="BJ506" s="3"/>
+    </row>
+    <row r="507" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A507" s="75"/>
+      <c r="B507" s="54"/>
+      <c r="D507" s="108"/>
+      <c r="E507" s="91"/>
+      <c r="F507" s="4"/>
+      <c r="G507" s="4"/>
+      <c r="H507" s="4"/>
+      <c r="I507" s="92"/>
+      <c r="K507" s="93"/>
+      <c r="L507" s="92"/>
+      <c r="M507" s="94"/>
+      <c r="O507" s="4"/>
+      <c r="P507" s="92"/>
+      <c r="Q507" s="92"/>
+      <c r="R507" s="94"/>
+      <c r="S507" s="94"/>
+      <c r="T507" s="94"/>
+      <c r="U507" s="94"/>
+      <c r="V507" s="92"/>
+      <c r="W507" s="74"/>
+      <c r="X507" s="4"/>
+      <c r="Y507" s="4"/>
+      <c r="Z507" s="7"/>
+      <c r="AA507" s="7"/>
+      <c r="AB507" s="7"/>
+      <c r="AC507" s="7"/>
+      <c r="AD507" s="7"/>
+      <c r="AE507" s="7"/>
+      <c r="AF507" s="7"/>
+      <c r="AG507" s="7"/>
+      <c r="AH507" s="7"/>
+      <c r="AI507" s="7"/>
+      <c r="AJ507" s="7"/>
+      <c r="AK507" s="7"/>
+      <c r="AL507" s="7"/>
+      <c r="AM507" s="7"/>
+      <c r="AN507" s="7"/>
+      <c r="AO507" s="7"/>
+      <c r="AP507" s="7"/>
+      <c r="AQ507" s="7"/>
+      <c r="AR507" s="7"/>
+      <c r="AS507" s="7"/>
+      <c r="AT507" s="7"/>
+      <c r="AU507" s="7"/>
+      <c r="AV507" s="7"/>
+      <c r="AW507" s="4"/>
+      <c r="AX507" s="2"/>
+      <c r="AY507" s="7"/>
+      <c r="AZ507" s="4"/>
+      <c r="BA507" s="4"/>
+      <c r="BB507" s="2"/>
+      <c r="BC507" s="2"/>
+      <c r="BD507" s="2"/>
+      <c r="BE507" s="95"/>
+      <c r="BF507" s="96"/>
+      <c r="BG507" s="97"/>
+      <c r="BH507" s="2"/>
+      <c r="BI507" s="2"/>
+      <c r="BJ507" s="3"/>
+    </row>
+    <row r="508" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A508" s="75"/>
+      <c r="B508" s="54"/>
+      <c r="D508" s="108"/>
+      <c r="E508" s="91"/>
+      <c r="F508" s="4"/>
+      <c r="G508" s="4"/>
+      <c r="H508" s="4"/>
+      <c r="I508" s="92"/>
+      <c r="K508" s="93"/>
+      <c r="L508" s="92"/>
+      <c r="M508" s="94"/>
+      <c r="O508" s="4"/>
+      <c r="P508" s="92"/>
+      <c r="Q508" s="92"/>
+      <c r="R508" s="94"/>
+      <c r="S508" s="94"/>
+      <c r="T508" s="94"/>
+      <c r="U508" s="94"/>
+      <c r="V508" s="92"/>
+      <c r="W508" s="74"/>
+      <c r="X508" s="4"/>
+      <c r="Y508" s="4"/>
+      <c r="Z508" s="7"/>
+      <c r="AA508" s="7"/>
+      <c r="AB508" s="7"/>
+      <c r="AC508" s="7"/>
+      <c r="AD508" s="7"/>
+      <c r="AE508" s="7"/>
+      <c r="AF508" s="7"/>
+      <c r="AG508" s="7"/>
+      <c r="AH508" s="7"/>
+      <c r="AI508" s="7"/>
+      <c r="AJ508" s="7"/>
+      <c r="AK508" s="7"/>
+      <c r="AL508" s="7"/>
+      <c r="AM508" s="7"/>
+      <c r="AN508" s="7"/>
+      <c r="AO508" s="7"/>
+      <c r="AP508" s="7"/>
+      <c r="AQ508" s="7"/>
+      <c r="AR508" s="7"/>
+      <c r="AS508" s="7"/>
+      <c r="AT508" s="7"/>
+      <c r="AU508" s="7"/>
+      <c r="AV508" s="7"/>
+      <c r="AW508" s="4"/>
+      <c r="AX508" s="2"/>
+      <c r="AY508" s="7"/>
+      <c r="AZ508" s="4"/>
+      <c r="BA508" s="4"/>
+      <c r="BB508" s="2"/>
+      <c r="BC508" s="2"/>
+      <c r="BD508" s="2"/>
+      <c r="BE508" s="95"/>
+      <c r="BF508" s="96"/>
+      <c r="BG508" s="97"/>
+      <c r="BH508" s="2"/>
+      <c r="BI508" s="2"/>
+      <c r="BJ508" s="3"/>
+    </row>
+    <row r="509" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A509" s="75"/>
+      <c r="B509" s="54"/>
+      <c r="D509" s="108"/>
+      <c r="E509" s="91"/>
+      <c r="F509" s="4"/>
+      <c r="G509" s="4"/>
+      <c r="H509" s="4"/>
+      <c r="I509" s="92"/>
+      <c r="K509" s="93"/>
+      <c r="L509" s="92"/>
+      <c r="M509" s="94"/>
+      <c r="O509" s="4"/>
+      <c r="P509" s="92"/>
+      <c r="Q509" s="92"/>
+      <c r="R509" s="94"/>
+      <c r="S509" s="94"/>
+      <c r="T509" s="94"/>
+      <c r="U509" s="94"/>
+      <c r="V509" s="92"/>
+      <c r="W509" s="74"/>
+      <c r="X509" s="4"/>
+      <c r="Y509" s="4"/>
+      <c r="Z509" s="7"/>
+      <c r="AA509" s="7"/>
+      <c r="AB509" s="7"/>
+      <c r="AC509" s="7"/>
+      <c r="AD509" s="7"/>
+      <c r="AE509" s="7"/>
+      <c r="AF509" s="7"/>
+      <c r="AG509" s="7"/>
+      <c r="AH509" s="7"/>
+      <c r="AI509" s="7"/>
+      <c r="AJ509" s="7"/>
+      <c r="AK509" s="7"/>
+      <c r="AL509" s="7"/>
+      <c r="AM509" s="7"/>
+      <c r="AN509" s="7"/>
+      <c r="AO509" s="7"/>
+      <c r="AP509" s="7"/>
+      <c r="AQ509" s="7"/>
+      <c r="AR509" s="7"/>
+      <c r="AS509" s="7"/>
+      <c r="AT509" s="7"/>
+      <c r="AU509" s="7"/>
+      <c r="AV509" s="7"/>
+      <c r="AW509" s="4"/>
+      <c r="AX509" s="2"/>
+      <c r="AY509" s="7"/>
+      <c r="AZ509" s="4"/>
+      <c r="BA509" s="4"/>
+      <c r="BB509" s="2"/>
+      <c r="BC509" s="2"/>
+      <c r="BD509" s="2"/>
+      <c r="BE509" s="95"/>
+      <c r="BF509" s="96"/>
+      <c r="BG509" s="97"/>
+      <c r="BH509" s="2"/>
+      <c r="BI509" s="2"/>
+      <c r="BJ509" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -55798,25 +58736,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004F1ECC6B2649324CB24C079D2C04510D" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="608b5d954c2eb0ac10393708da8d34af">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65551c38-962b-4cee-924d-ef2df1bb8b98" xmlns:ns3="ec750ee3-7d64-422f-9b1f-0ca7238893a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af171f03bd4cf151e3e856a6839c0cc7" ns2:_="" ns3:_="">
     <xsd:import namespace="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
@@ -56064,32 +58983,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DCC068A-FED0-450E-AAE1-E4245F13E99B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -56106,4 +59019,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
+++ b/pages/CdA Testing/Track CdA Testing Streamlit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1D8BC2-8631-4C86-9AD4-47ECAAE15628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5467FA80-78E0-4BDF-87E5-BE3A84591AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="15" yWindow="1005" windowWidth="19185" windowHeight="10995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CdA Track Testing" sheetId="12" r:id="rId1"/>
@@ -2277,7 +2277,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2542,61 +2542,7 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -55862,7 +55808,7 @@
       </c>
     </row>
     <row r="478" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A478" s="107" t="s">
+      <c r="A478" s="90" t="s">
         <v>13</v>
       </c>
       <c r="B478" s="76" t="s">
@@ -55871,10 +55817,10 @@
       <c r="C478" s="77">
         <v>45414</v>
       </c>
-      <c r="D478" s="90">
+      <c r="D478" s="78">
         <v>1</v>
       </c>
-      <c r="E478" s="91" t="s">
+      <c r="E478" s="2" t="s">
         <v>551</v>
       </c>
       <c r="F478" s="4" t="s">
@@ -55895,7 +55841,7 @@
       <c r="K478" s="74">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="L478" s="92"/>
+      <c r="L478" s="7"/>
       <c r="M478" s="74">
         <v>0.1615</v>
       </c>
@@ -55906,9 +55852,6 @@
       <c r="P478" s="74">
         <v>1.2424999999999999</v>
       </c>
-      <c r="Q478" s="92"/>
-      <c r="R478" s="94"/>
-      <c r="S478" s="94"/>
       <c r="T478" s="74">
         <v>65.099999999999994</v>
       </c>
@@ -55969,12 +55912,12 @@
         <v>2096</v>
       </c>
       <c r="BI478" s="2"/>
-      <c r="BJ478" s="107" t="s">
+      <c r="BJ478" s="90" t="s">
         <v>650</v>
       </c>
     </row>
     <row r="479" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A479" s="107" t="s">
+      <c r="A479" s="90" t="s">
         <v>13</v>
       </c>
       <c r="B479" s="76" t="s">
@@ -55983,10 +55926,10 @@
       <c r="C479" s="77">
         <v>45414</v>
       </c>
-      <c r="D479" s="90">
+      <c r="D479" s="78">
         <v>2</v>
       </c>
-      <c r="E479" s="91" t="s">
+      <c r="E479" s="2" t="s">
         <v>551</v>
       </c>
       <c r="F479" s="4" t="s">
@@ -56001,7 +55944,7 @@
       <c r="I479" s="86"/>
       <c r="J479" s="86"/>
       <c r="K479" s="86"/>
-      <c r="L479" s="92"/>
+      <c r="L479" s="7"/>
       <c r="M479" s="74">
         <v>0.16139999999999999</v>
       </c>
@@ -56010,9 +55953,6 @@
       <c r="P479" s="74">
         <v>1.2424999999999999</v>
       </c>
-      <c r="Q479" s="92"/>
-      <c r="R479" s="94"/>
-      <c r="S479" s="94"/>
       <c r="T479" s="74">
         <v>65.8</v>
       </c>
@@ -56078,7 +56018,7 @@
       </c>
     </row>
     <row r="480" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A480" s="107" t="s">
+      <c r="A480" s="90" t="s">
         <v>13</v>
       </c>
       <c r="B480" s="76" t="s">
@@ -56087,10 +56027,10 @@
       <c r="C480" s="77">
         <v>45414</v>
       </c>
-      <c r="D480" s="90">
+      <c r="D480" s="78">
         <v>3</v>
       </c>
-      <c r="E480" s="91" t="s">
+      <c r="E480" s="2" t="s">
         <v>551</v>
       </c>
       <c r="F480" s="4" t="s">
@@ -56111,7 +56051,7 @@
       <c r="K480" s="74">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="L480" s="92"/>
+      <c r="L480" s="7"/>
       <c r="M480" s="74">
         <v>0.1605</v>
       </c>
@@ -56122,9 +56062,6 @@
       <c r="P480" s="74">
         <v>1.2424999999999999</v>
       </c>
-      <c r="Q480" s="92"/>
-      <c r="R480" s="94"/>
-      <c r="S480" s="94"/>
       <c r="T480" s="74">
         <v>66</v>
       </c>
@@ -56190,7 +56127,7 @@
       </c>
     </row>
     <row r="481" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A481" s="107" t="s">
+      <c r="A481" s="90" t="s">
         <v>13</v>
       </c>
       <c r="B481" s="76" t="s">
@@ -56199,10 +56136,10 @@
       <c r="C481" s="77">
         <v>45414</v>
       </c>
-      <c r="D481" s="90">
+      <c r="D481" s="78">
         <v>4</v>
       </c>
-      <c r="E481" s="91" t="s">
+      <c r="E481" s="2" t="s">
         <v>551</v>
       </c>
       <c r="F481" s="4" t="s">
@@ -56223,7 +56160,7 @@
       <c r="K481" s="74">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="L481" s="92"/>
+      <c r="L481" s="7"/>
       <c r="M481" s="74">
         <v>0.1628</v>
       </c>
@@ -56234,9 +56171,6 @@
       <c r="P481" s="74">
         <v>1.2424999999999999</v>
       </c>
-      <c r="Q481" s="92"/>
-      <c r="R481" s="94"/>
-      <c r="S481" s="94"/>
       <c r="T481" s="74">
         <v>66.400000000000006</v>
       </c>
@@ -56302,7 +56236,7 @@
       </c>
     </row>
     <row r="482" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A482" s="107" t="s">
+      <c r="A482" s="90" t="s">
         <v>13</v>
       </c>
       <c r="B482" s="76" t="s">
@@ -56311,10 +56245,10 @@
       <c r="C482" s="77">
         <v>45414</v>
       </c>
-      <c r="D482" s="90">
+      <c r="D482" s="78">
         <v>5</v>
       </c>
-      <c r="E482" s="91" t="s">
+      <c r="E482" s="2" t="s">
         <v>551</v>
       </c>
       <c r="F482" s="4" t="s">
@@ -56335,7 +56269,7 @@
       <c r="K482" s="74">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="L482" s="92"/>
+      <c r="L482" s="7"/>
       <c r="M482" s="74">
         <v>0.1588</v>
       </c>
@@ -56346,9 +56280,6 @@
       <c r="P482" s="74">
         <v>1.2424999999999999</v>
       </c>
-      <c r="Q482" s="92"/>
-      <c r="R482" s="94"/>
-      <c r="S482" s="94"/>
       <c r="T482" s="74">
         <v>66.900000000000006</v>
       </c>
@@ -56414,7 +56345,7 @@
       </c>
     </row>
     <row r="483" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A483" s="107" t="s">
+      <c r="A483" s="90" t="s">
         <v>13</v>
       </c>
       <c r="B483" s="76" t="s">
@@ -56423,10 +56354,10 @@
       <c r="C483" s="77">
         <v>45414</v>
       </c>
-      <c r="D483" s="90">
+      <c r="D483" s="78">
         <v>6</v>
       </c>
-      <c r="E483" s="91" t="s">
+      <c r="E483" s="2" t="s">
         <v>551</v>
       </c>
       <c r="F483" s="4" t="s">
@@ -56447,7 +56378,7 @@
       <c r="K483" s="74">
         <v>2E-3</v>
       </c>
-      <c r="L483" s="92"/>
+      <c r="L483" s="7"/>
       <c r="M483" s="74">
         <v>0.1578</v>
       </c>
@@ -56458,9 +56389,6 @@
       <c r="P483" s="74">
         <v>1.2424999999999999</v>
       </c>
-      <c r="Q483" s="92"/>
-      <c r="R483" s="94"/>
-      <c r="S483" s="94"/>
       <c r="T483" s="74">
         <v>63.5</v>
       </c>
@@ -56524,7 +56452,7 @@
       <c r="BJ483" s="3"/>
     </row>
     <row r="484" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A484" s="107" t="s">
+      <c r="A484" s="90" t="s">
         <v>43</v>
       </c>
       <c r="B484" s="76" t="s">
@@ -56533,10 +56461,10 @@
       <c r="C484" s="77">
         <v>45414</v>
       </c>
-      <c r="D484" s="90">
+      <c r="D484" s="78">
         <v>1</v>
       </c>
-      <c r="E484" s="91" t="s">
+      <c r="E484" s="2" t="s">
         <v>213</v>
       </c>
       <c r="F484" s="4" t="s">
@@ -56557,7 +56485,7 @@
       <c r="K484" s="74">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="L484" s="92"/>
+      <c r="L484" s="7"/>
       <c r="M484" s="74">
         <v>0.16120000000000001</v>
       </c>
@@ -56568,9 +56496,6 @@
       <c r="P484" s="74">
         <v>1.2629999999999999</v>
       </c>
-      <c r="Q484" s="92"/>
-      <c r="R484" s="94"/>
-      <c r="S484" s="94"/>
       <c r="T484" s="74">
         <v>62.2</v>
       </c>
@@ -56636,7 +56561,7 @@
       </c>
     </row>
     <row r="485" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A485" s="107" t="s">
+      <c r="A485" s="90" t="s">
         <v>43</v>
       </c>
       <c r="B485" s="76" t="s">
@@ -56645,10 +56570,10 @@
       <c r="C485" s="77">
         <v>45414</v>
       </c>
-      <c r="D485" s="90">
+      <c r="D485" s="78">
         <v>2</v>
       </c>
-      <c r="E485" s="91" t="s">
+      <c r="E485" s="2" t="s">
         <v>213</v>
       </c>
       <c r="F485" s="4" t="s">
@@ -56669,7 +56594,7 @@
       <c r="K485" s="74">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="L485" s="92"/>
+      <c r="L485" s="7"/>
       <c r="M485" s="74">
         <v>0.1578</v>
       </c>
@@ -56680,9 +56605,6 @@
       <c r="P485" s="74">
         <v>1.2629999999999999</v>
       </c>
-      <c r="Q485" s="92"/>
-      <c r="R485" s="94"/>
-      <c r="S485" s="94"/>
       <c r="T485" s="74">
         <v>61.6</v>
       </c>
@@ -56748,7 +56670,7 @@
       </c>
     </row>
     <row r="486" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A486" s="107" t="s">
+      <c r="A486" s="90" t="s">
         <v>43</v>
       </c>
       <c r="B486" s="76" t="s">
@@ -56757,10 +56679,10 @@
       <c r="C486" s="77">
         <v>45414</v>
       </c>
-      <c r="D486" s="90">
+      <c r="D486" s="78">
         <v>3</v>
       </c>
-      <c r="E486" s="91" t="s">
+      <c r="E486" s="2" t="s">
         <v>213</v>
       </c>
       <c r="F486" s="4" t="s">
@@ -56781,7 +56703,7 @@
       <c r="K486" s="74">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="L486" s="92"/>
+      <c r="L486" s="7"/>
       <c r="M486" s="74">
         <v>0.16400000000000001</v>
       </c>
@@ -56792,9 +56714,6 @@
       <c r="P486" s="74">
         <v>1.2629999999999999</v>
       </c>
-      <c r="Q486" s="92"/>
-      <c r="R486" s="94"/>
-      <c r="S486" s="94"/>
       <c r="T486" s="74">
         <v>61.7</v>
       </c>
@@ -56860,7 +56779,7 @@
       </c>
     </row>
     <row r="487" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A487" s="107" t="s">
+      <c r="A487" s="90" t="s">
         <v>43</v>
       </c>
       <c r="B487" s="76" t="s">
@@ -56869,10 +56788,10 @@
       <c r="C487" s="77">
         <v>45414</v>
       </c>
-      <c r="D487" s="90">
+      <c r="D487" s="78">
         <v>4</v>
       </c>
-      <c r="E487" s="91" t="s">
+      <c r="E487" s="2" t="s">
         <v>213</v>
       </c>
       <c r="F487" s="4" t="s">
@@ -56893,7 +56812,7 @@
       <c r="K487" s="74">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="L487" s="92"/>
+      <c r="L487" s="7"/>
       <c r="M487" s="74">
         <v>0.1565</v>
       </c>
@@ -56904,9 +56823,6 @@
       <c r="P487" s="74">
         <v>1.2629999999999999</v>
       </c>
-      <c r="Q487" s="92"/>
-      <c r="R487" s="94"/>
-      <c r="S487" s="94"/>
       <c r="T487" s="74">
         <v>62.2</v>
       </c>
@@ -56972,7 +56888,7 @@
       </c>
     </row>
     <row r="488" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A488" s="107" t="s">
+      <c r="A488" s="90" t="s">
         <v>43</v>
       </c>
       <c r="B488" s="76" t="s">
@@ -56981,10 +56897,10 @@
       <c r="C488" s="77">
         <v>45414</v>
       </c>
-      <c r="D488" s="90">
+      <c r="D488" s="78">
         <v>5</v>
       </c>
-      <c r="E488" s="91" t="s">
+      <c r="E488" s="2" t="s">
         <v>213</v>
       </c>
       <c r="F488" s="4" t="s">
@@ -57005,7 +56921,7 @@
       <c r="K488" s="74">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="L488" s="92"/>
+      <c r="L488" s="7"/>
       <c r="M488" s="74">
         <v>0.1573</v>
       </c>
@@ -57016,9 +56932,6 @@
       <c r="P488" s="74">
         <v>1.2629999999999999</v>
       </c>
-      <c r="Q488" s="92"/>
-      <c r="R488" s="94"/>
-      <c r="S488" s="94"/>
       <c r="T488" s="74">
         <v>62.3</v>
       </c>
@@ -57084,7 +56997,7 @@
       </c>
     </row>
     <row r="489" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A489" s="107" t="s">
+      <c r="A489" s="90" t="s">
         <v>43</v>
       </c>
       <c r="B489" s="76" t="s">
@@ -57093,10 +57006,10 @@
       <c r="C489" s="77">
         <v>45414</v>
       </c>
-      <c r="D489" s="90">
+      <c r="D489" s="78">
         <v>6</v>
       </c>
-      <c r="E489" s="91" t="s">
+      <c r="E489" s="2" t="s">
         <v>213</v>
       </c>
       <c r="F489" s="4" t="s">
@@ -57117,7 +57030,7 @@
       <c r="K489" s="74">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="L489" s="92"/>
+      <c r="L489" s="7"/>
       <c r="M489" s="74">
         <v>0.16370000000000001</v>
       </c>
@@ -57128,9 +57041,6 @@
       <c r="P489" s="74">
         <v>1.2629999999999999</v>
       </c>
-      <c r="Q489" s="92"/>
-      <c r="R489" s="94"/>
-      <c r="S489" s="94"/>
       <c r="T489" s="74">
         <v>62</v>
       </c>
@@ -57196,7 +57106,7 @@
       </c>
     </row>
     <row r="490" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A490" s="107" t="s">
+      <c r="A490" s="90" t="s">
         <v>43</v>
       </c>
       <c r="B490" s="76" t="s">
@@ -57205,10 +57115,10 @@
       <c r="C490" s="77">
         <v>45414</v>
       </c>
-      <c r="D490" s="90">
+      <c r="D490" s="78">
         <v>1</v>
       </c>
-      <c r="E490" s="91" t="s">
+      <c r="E490" s="2" t="s">
         <v>545</v>
       </c>
       <c r="F490" s="4" t="s">
@@ -57229,7 +57139,7 @@
       <c r="K490" s="74">
         <v>3.8E-3</v>
       </c>
-      <c r="L490" s="92"/>
+      <c r="L490" s="7"/>
       <c r="M490" s="74">
         <v>0.16919999999999999</v>
       </c>
@@ -57240,9 +57150,6 @@
       <c r="P490" s="74">
         <v>1.26</v>
       </c>
-      <c r="Q490" s="92"/>
-      <c r="R490" s="94"/>
-      <c r="S490" s="94"/>
       <c r="T490" s="74">
         <v>59.9</v>
       </c>
@@ -57308,7 +57215,7 @@
       </c>
     </row>
     <row r="491" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A491" s="107" t="s">
+      <c r="A491" s="90" t="s">
         <v>43</v>
       </c>
       <c r="B491" s="76" t="s">
@@ -57317,10 +57224,10 @@
       <c r="C491" s="77">
         <v>45414</v>
       </c>
-      <c r="D491" s="90">
+      <c r="D491" s="78">
         <v>2</v>
       </c>
-      <c r="E491" s="91" t="s">
+      <c r="E491" s="2" t="s">
         <v>545</v>
       </c>
       <c r="F491" s="4" t="s">
@@ -57341,7 +57248,7 @@
       <c r="K491" s="74">
         <v>5.5999999999999999E-3</v>
       </c>
-      <c r="L491" s="92"/>
+      <c r="L491" s="7"/>
       <c r="M491" s="74">
         <v>0.1686</v>
       </c>
@@ -57352,9 +57259,6 @@
       <c r="P491" s="74">
         <v>1.26</v>
       </c>
-      <c r="Q491" s="92"/>
-      <c r="R491" s="94"/>
-      <c r="S491" s="94"/>
       <c r="T491" s="74">
         <v>58.7</v>
       </c>
@@ -57420,7 +57324,7 @@
       </c>
     </row>
     <row r="492" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A492" s="107" t="s">
+      <c r="A492" s="90" t="s">
         <v>43</v>
       </c>
       <c r="B492" s="76" t="s">
@@ -57429,10 +57333,10 @@
       <c r="C492" s="77">
         <v>45414</v>
       </c>
-      <c r="D492" s="90">
+      <c r="D492" s="78">
         <v>3</v>
       </c>
-      <c r="E492" s="91" t="s">
+      <c r="E492" s="2" t="s">
         <v>545</v>
       </c>
       <c r="F492" s="4" t="s">
@@ -57453,7 +57357,7 @@
       <c r="K492" s="74">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="L492" s="92"/>
+      <c r="L492" s="7"/>
       <c r="M492" s="74">
         <v>0.16969999999999999</v>
       </c>
@@ -57464,9 +57368,6 @@
       <c r="P492" s="74">
         <v>1.26</v>
       </c>
-      <c r="Q492" s="92"/>
-      <c r="R492" s="94"/>
-      <c r="S492" s="94"/>
       <c r="T492" s="74">
         <v>59.1</v>
       </c>
@@ -57530,7 +57431,7 @@
       <c r="BJ492" s="3"/>
     </row>
     <row r="493" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A493" s="107" t="s">
+      <c r="A493" s="90" t="s">
         <v>43</v>
       </c>
       <c r="B493" s="76" t="s">
@@ -57539,10 +57440,10 @@
       <c r="C493" s="77">
         <v>45414</v>
       </c>
-      <c r="D493" s="90">
+      <c r="D493" s="78">
         <v>4</v>
       </c>
-      <c r="E493" s="91" t="s">
+      <c r="E493" s="2" t="s">
         <v>545</v>
       </c>
       <c r="F493" s="4" t="s">
@@ -57563,7 +57464,7 @@
       <c r="K493" s="74">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="L493" s="92"/>
+      <c r="L493" s="7"/>
       <c r="M493" s="74">
         <v>0.17169999999999999</v>
       </c>
@@ -57574,9 +57475,6 @@
       <c r="P493" s="74">
         <v>1.26</v>
       </c>
-      <c r="Q493" s="92"/>
-      <c r="R493" s="94"/>
-      <c r="S493" s="94"/>
       <c r="T493" s="74">
         <v>59.6</v>
       </c>
@@ -57642,7 +57540,7 @@
       </c>
     </row>
     <row r="494" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A494" s="107" t="s">
+      <c r="A494" s="90" t="s">
         <v>43</v>
       </c>
       <c r="B494" s="76" t="s">
@@ -57651,10 +57549,10 @@
       <c r="C494" s="77">
         <v>45414</v>
       </c>
-      <c r="D494" s="90">
+      <c r="D494" s="78">
         <v>5</v>
       </c>
-      <c r="E494" s="91" t="s">
+      <c r="E494" s="2" t="s">
         <v>545</v>
       </c>
       <c r="F494" s="4" t="s">
@@ -57675,7 +57573,7 @@
       <c r="K494" s="74">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="L494" s="92"/>
+      <c r="L494" s="7"/>
       <c r="M494" s="74">
         <v>0.16400000000000001</v>
       </c>
@@ -57686,9 +57584,6 @@
       <c r="P494" s="74">
         <v>1.26</v>
       </c>
-      <c r="Q494" s="92"/>
-      <c r="R494" s="94"/>
-      <c r="S494" s="94"/>
       <c r="T494" s="74">
         <v>60.5</v>
       </c>
@@ -57754,19 +57649,19 @@
       </c>
     </row>
     <row r="495" spans="1:62" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A495" s="107" t="s">
+      <c r="A495" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="B495" s="99" t="s">
+      <c r="B495" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="C495" s="100">
+      <c r="C495" s="77">
         <v>45414</v>
       </c>
-      <c r="D495" s="101">
+      <c r="D495" s="78">
         <v>6</v>
       </c>
-      <c r="E495" s="91" t="s">
+      <c r="E495" s="2" t="s">
         <v>545</v>
       </c>
       <c r="F495" s="4" t="s">
@@ -57787,20 +57682,17 @@
       <c r="K495" s="74">
         <v>2.8E-3</v>
       </c>
-      <c r="L495" s="103"/>
+      <c r="L495" s="7"/>
       <c r="M495" s="74">
         <v>0.1623</v>
       </c>
       <c r="N495" s="7">
         <v>-0.52</v>
       </c>
-      <c r="O495" s="102"/>
+      <c r="O495" s="4"/>
       <c r="P495" s="74">
         <v>1.26</v>
       </c>
-      <c r="Q495" s="103"/>
-      <c r="R495" s="105"/>
-      <c r="S495" s="105"/>
       <c r="T495" s="74">
         <v>60.8</v>
       </c>
@@ -57813,40 +57705,40 @@
       <c r="W495" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="X495" s="102"/>
-      <c r="Y495" s="102"/>
-      <c r="Z495" s="104"/>
-      <c r="AA495" s="104"/>
-      <c r="AB495" s="104"/>
-      <c r="AC495" s="104"/>
-      <c r="AD495" s="104"/>
-      <c r="AE495" s="104"/>
-      <c r="AF495" s="104"/>
-      <c r="AG495" s="104"/>
-      <c r="AH495" s="104"/>
-      <c r="AI495" s="104"/>
-      <c r="AJ495" s="104"/>
-      <c r="AK495" s="104"/>
-      <c r="AL495" s="104"/>
-      <c r="AM495" s="104"/>
-      <c r="AN495" s="104"/>
-      <c r="AO495" s="104"/>
-      <c r="AP495" s="104"/>
-      <c r="AQ495" s="104"/>
-      <c r="AR495" s="104"/>
-      <c r="AS495" s="104"/>
-      <c r="AT495" s="104"/>
-      <c r="AU495" s="104"/>
-      <c r="AV495" s="104"/>
-      <c r="AW495" s="102"/>
-      <c r="AX495" s="98"/>
-      <c r="AY495" s="104"/>
-      <c r="AZ495" s="102"/>
+      <c r="X495" s="4"/>
+      <c r="Y495" s="4"/>
+      <c r="Z495" s="7"/>
+      <c r="AA495" s="7"/>
+      <c r="AB495" s="7"/>
+      <c r="AC495" s="7"/>
+      <c r="AD495" s="7"/>
+      <c r="AE495" s="7"/>
+      <c r="AF495" s="7"/>
+      <c r="AG495" s="7"/>
+      <c r="AH495" s="7"/>
+      <c r="AI495" s="7"/>
+      <c r="AJ495" s="7"/>
+      <c r="AK495" s="7"/>
+      <c r="AL495" s="7"/>
+      <c r="AM495" s="7"/>
+      <c r="AN495" s="7"/>
+      <c r="AO495" s="7"/>
+      <c r="AP495" s="7"/>
+      <c r="AQ495" s="7"/>
+      <c r="AR495" s="7"/>
+      <c r="AS495" s="7"/>
+      <c r="AT495" s="7"/>
+      <c r="AU495" s="7"/>
+      <c r="AV495" s="7"/>
+      <c r="AW495" s="4"/>
+      <c r="AX495" s="2"/>
+      <c r="AY495" s="7"/>
+      <c r="AZ495" s="4"/>
       <c r="BA495" s="74">
         <v>111.6</v>
       </c>
-      <c r="BB495" s="98"/>
-      <c r="BC495" s="98"/>
+      <c r="BB495" s="2"/>
+      <c r="BC495" s="2"/>
       <c r="BD495" s="74">
         <v>26.1</v>
       </c>
@@ -57860,31 +57752,23 @@
       <c r="BH495" s="74">
         <v>2096</v>
       </c>
-      <c r="BI495" s="98"/>
-      <c r="BJ495" s="106" t="s">
+      <c r="BI495" s="2"/>
+      <c r="BJ495" s="3" t="s">
         <v>665</v>
       </c>
     </row>
     <row r="496" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A496" s="75"/>
       <c r="B496" s="54"/>
-      <c r="D496" s="108"/>
-      <c r="E496" s="91"/>
+      <c r="D496" s="8"/>
+      <c r="E496" s="2"/>
       <c r="F496" s="4"/>
       <c r="G496" s="4"/>
       <c r="H496" s="4"/>
-      <c r="I496" s="92"/>
-      <c r="K496" s="93"/>
-      <c r="L496" s="92"/>
-      <c r="M496" s="94"/>
+      <c r="I496" s="7"/>
+      <c r="K496" s="50"/>
+      <c r="L496" s="7"/>
       <c r="O496" s="4"/>
-      <c r="P496" s="92"/>
-      <c r="Q496" s="92"/>
-      <c r="R496" s="94"/>
-      <c r="S496" s="94"/>
-      <c r="T496" s="94"/>
-      <c r="U496" s="94"/>
-      <c r="V496" s="92"/>
       <c r="W496" s="74"/>
       <c r="X496" s="4"/>
       <c r="Y496" s="4"/>
@@ -57919,9 +57803,9 @@
       <c r="BB496" s="2"/>
       <c r="BC496" s="2"/>
       <c r="BD496" s="2"/>
-      <c r="BE496" s="95"/>
-      <c r="BF496" s="96"/>
-      <c r="BG496" s="97"/>
+      <c r="BE496" s="42"/>
+      <c r="BF496" s="43"/>
+      <c r="BG496" s="44"/>
       <c r="BH496" s="2"/>
       <c r="BI496" s="2"/>
       <c r="BJ496" s="3"/>
@@ -57929,23 +57813,15 @@
     <row r="497" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A497" s="75"/>
       <c r="B497" s="54"/>
-      <c r="D497" s="108"/>
-      <c r="E497" s="91"/>
+      <c r="D497" s="8"/>
+      <c r="E497" s="2"/>
       <c r="F497" s="4"/>
       <c r="G497" s="4"/>
       <c r="H497" s="4"/>
-      <c r="I497" s="92"/>
-      <c r="K497" s="93"/>
-      <c r="L497" s="92"/>
-      <c r="M497" s="94"/>
+      <c r="I497" s="7"/>
+      <c r="K497" s="50"/>
+      <c r="L497" s="7"/>
       <c r="O497" s="4"/>
-      <c r="P497" s="92"/>
-      <c r="Q497" s="92"/>
-      <c r="R497" s="94"/>
-      <c r="S497" s="94"/>
-      <c r="T497" s="94"/>
-      <c r="U497" s="94"/>
-      <c r="V497" s="92"/>
       <c r="W497" s="74"/>
       <c r="X497" s="4"/>
       <c r="Y497" s="4"/>
@@ -57980,9 +57856,9 @@
       <c r="BB497" s="2"/>
       <c r="BC497" s="2"/>
       <c r="BD497" s="2"/>
-      <c r="BE497" s="95"/>
-      <c r="BF497" s="96"/>
-      <c r="BG497" s="97"/>
+      <c r="BE497" s="42"/>
+      <c r="BF497" s="43"/>
+      <c r="BG497" s="44"/>
       <c r="BH497" s="2"/>
       <c r="BI497" s="2"/>
       <c r="BJ497" s="3"/>
@@ -57990,23 +57866,15 @@
     <row r="498" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A498" s="75"/>
       <c r="B498" s="54"/>
-      <c r="D498" s="108"/>
-      <c r="E498" s="91"/>
+      <c r="D498" s="8"/>
+      <c r="E498" s="2"/>
       <c r="F498" s="4"/>
       <c r="G498" s="4"/>
       <c r="H498" s="4"/>
-      <c r="I498" s="92"/>
-      <c r="K498" s="93"/>
-      <c r="L498" s="92"/>
-      <c r="M498" s="94"/>
+      <c r="I498" s="7"/>
+      <c r="K498" s="50"/>
+      <c r="L498" s="7"/>
       <c r="O498" s="4"/>
-      <c r="P498" s="92"/>
-      <c r="Q498" s="92"/>
-      <c r="R498" s="94"/>
-      <c r="S498" s="94"/>
-      <c r="T498" s="94"/>
-      <c r="U498" s="94"/>
-      <c r="V498" s="92"/>
       <c r="W498" s="74"/>
       <c r="X498" s="4"/>
       <c r="Y498" s="4"/>
@@ -58041,9 +57909,9 @@
       <c r="BB498" s="2"/>
       <c r="BC498" s="2"/>
       <c r="BD498" s="2"/>
-      <c r="BE498" s="95"/>
-      <c r="BF498" s="96"/>
-      <c r="BG498" s="97"/>
+      <c r="BE498" s="42"/>
+      <c r="BF498" s="43"/>
+      <c r="BG498" s="44"/>
       <c r="BH498" s="2"/>
       <c r="BI498" s="2"/>
       <c r="BJ498" s="3"/>
@@ -58051,23 +57919,15 @@
     <row r="499" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A499" s="75"/>
       <c r="B499" s="54"/>
-      <c r="D499" s="108"/>
-      <c r="E499" s="91"/>
+      <c r="D499" s="8"/>
+      <c r="E499" s="2"/>
       <c r="F499" s="4"/>
       <c r="G499" s="4"/>
       <c r="H499" s="4"/>
-      <c r="I499" s="92"/>
-      <c r="K499" s="93"/>
-      <c r="L499" s="92"/>
-      <c r="M499" s="94"/>
+      <c r="I499" s="7"/>
+      <c r="K499" s="50"/>
+      <c r="L499" s="7"/>
       <c r="O499" s="4"/>
-      <c r="P499" s="92"/>
-      <c r="Q499" s="92"/>
-      <c r="R499" s="94"/>
-      <c r="S499" s="94"/>
-      <c r="T499" s="94"/>
-      <c r="U499" s="94"/>
-      <c r="V499" s="92"/>
       <c r="W499" s="74"/>
       <c r="X499" s="4"/>
       <c r="Y499" s="4"/>
@@ -58102,9 +57962,9 @@
       <c r="BB499" s="2"/>
       <c r="BC499" s="2"/>
       <c r="BD499" s="2"/>
-      <c r="BE499" s="95"/>
-      <c r="BF499" s="96"/>
-      <c r="BG499" s="97"/>
+      <c r="BE499" s="42"/>
+      <c r="BF499" s="43"/>
+      <c r="BG499" s="44"/>
       <c r="BH499" s="2"/>
       <c r="BI499" s="2"/>
       <c r="BJ499" s="3"/>
@@ -58112,23 +57972,15 @@
     <row r="500" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A500" s="75"/>
       <c r="B500" s="54"/>
-      <c r="D500" s="108"/>
-      <c r="E500" s="91"/>
+      <c r="D500" s="8"/>
+      <c r="E500" s="2"/>
       <c r="F500" s="4"/>
       <c r="G500" s="4"/>
       <c r="H500" s="4"/>
-      <c r="I500" s="92"/>
-      <c r="K500" s="93"/>
-      <c r="L500" s="92"/>
-      <c r="M500" s="94"/>
+      <c r="I500" s="7"/>
+      <c r="K500" s="50"/>
+      <c r="L500" s="7"/>
       <c r="O500" s="4"/>
-      <c r="P500" s="92"/>
-      <c r="Q500" s="92"/>
-      <c r="R500" s="94"/>
-      <c r="S500" s="94"/>
-      <c r="T500" s="94"/>
-      <c r="U500" s="94"/>
-      <c r="V500" s="92"/>
       <c r="W500" s="74"/>
       <c r="X500" s="4"/>
       <c r="Y500" s="4"/>
@@ -58163,9 +58015,9 @@
       <c r="BB500" s="2"/>
       <c r="BC500" s="2"/>
       <c r="BD500" s="2"/>
-      <c r="BE500" s="95"/>
-      <c r="BF500" s="96"/>
-      <c r="BG500" s="97"/>
+      <c r="BE500" s="42"/>
+      <c r="BF500" s="43"/>
+      <c r="BG500" s="44"/>
       <c r="BH500" s="2"/>
       <c r="BI500" s="2"/>
       <c r="BJ500" s="3"/>
@@ -58173,23 +58025,15 @@
     <row r="501" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A501" s="75"/>
       <c r="B501" s="54"/>
-      <c r="D501" s="108"/>
-      <c r="E501" s="91"/>
+      <c r="D501" s="8"/>
+      <c r="E501" s="2"/>
       <c r="F501" s="4"/>
       <c r="G501" s="4"/>
       <c r="H501" s="4"/>
-      <c r="I501" s="92"/>
-      <c r="K501" s="93"/>
-      <c r="L501" s="92"/>
-      <c r="M501" s="94"/>
+      <c r="I501" s="7"/>
+      <c r="K501" s="50"/>
+      <c r="L501" s="7"/>
       <c r="O501" s="4"/>
-      <c r="P501" s="92"/>
-      <c r="Q501" s="92"/>
-      <c r="R501" s="94"/>
-      <c r="S501" s="94"/>
-      <c r="T501" s="94"/>
-      <c r="U501" s="94"/>
-      <c r="V501" s="92"/>
       <c r="W501" s="74"/>
       <c r="X501" s="4"/>
       <c r="Y501" s="4"/>
@@ -58224,9 +58068,9 @@
       <c r="BB501" s="2"/>
       <c r="BC501" s="2"/>
       <c r="BD501" s="2"/>
-      <c r="BE501" s="95"/>
-      <c r="BF501" s="96"/>
-      <c r="BG501" s="97"/>
+      <c r="BE501" s="42"/>
+      <c r="BF501" s="43"/>
+      <c r="BG501" s="44"/>
       <c r="BH501" s="2"/>
       <c r="BI501" s="2"/>
       <c r="BJ501" s="3"/>
@@ -58234,23 +58078,15 @@
     <row r="502" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A502" s="75"/>
       <c r="B502" s="54"/>
-      <c r="D502" s="108"/>
-      <c r="E502" s="91"/>
+      <c r="D502" s="8"/>
+      <c r="E502" s="2"/>
       <c r="F502" s="4"/>
       <c r="G502" s="4"/>
       <c r="H502" s="4"/>
-      <c r="I502" s="92"/>
-      <c r="K502" s="93"/>
-      <c r="L502" s="92"/>
-      <c r="M502" s="94"/>
+      <c r="I502" s="7"/>
+      <c r="K502" s="50"/>
+      <c r="L502" s="7"/>
       <c r="O502" s="4"/>
-      <c r="P502" s="92"/>
-      <c r="Q502" s="92"/>
-      <c r="R502" s="94"/>
-      <c r="S502" s="94"/>
-      <c r="T502" s="94"/>
-      <c r="U502" s="94"/>
-      <c r="V502" s="92"/>
       <c r="W502" s="74"/>
       <c r="X502" s="4"/>
       <c r="Y502" s="4"/>
@@ -58285,9 +58121,9 @@
       <c r="BB502" s="2"/>
       <c r="BC502" s="2"/>
       <c r="BD502" s="2"/>
-      <c r="BE502" s="95"/>
-      <c r="BF502" s="96"/>
-      <c r="BG502" s="97"/>
+      <c r="BE502" s="42"/>
+      <c r="BF502" s="43"/>
+      <c r="BG502" s="44"/>
       <c r="BH502" s="2"/>
       <c r="BI502" s="2"/>
       <c r="BJ502" s="3"/>
@@ -58295,23 +58131,15 @@
     <row r="503" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A503" s="75"/>
       <c r="B503" s="54"/>
-      <c r="D503" s="108"/>
-      <c r="E503" s="91"/>
+      <c r="D503" s="8"/>
+      <c r="E503" s="2"/>
       <c r="F503" s="4"/>
       <c r="G503" s="4"/>
       <c r="H503" s="4"/>
-      <c r="I503" s="92"/>
-      <c r="K503" s="93"/>
-      <c r="L503" s="92"/>
-      <c r="M503" s="94"/>
+      <c r="I503" s="7"/>
+      <c r="K503" s="50"/>
+      <c r="L503" s="7"/>
       <c r="O503" s="4"/>
-      <c r="P503" s="92"/>
-      <c r="Q503" s="92"/>
-      <c r="R503" s="94"/>
-      <c r="S503" s="94"/>
-      <c r="T503" s="94"/>
-      <c r="U503" s="94"/>
-      <c r="V503" s="92"/>
       <c r="W503" s="74"/>
       <c r="X503" s="4"/>
       <c r="Y503" s="4"/>
@@ -58346,9 +58174,9 @@
       <c r="BB503" s="2"/>
       <c r="BC503" s="2"/>
       <c r="BD503" s="2"/>
-      <c r="BE503" s="95"/>
-      <c r="BF503" s="96"/>
-      <c r="BG503" s="97"/>
+      <c r="BE503" s="42"/>
+      <c r="BF503" s="43"/>
+      <c r="BG503" s="44"/>
       <c r="BH503" s="2"/>
       <c r="BI503" s="2"/>
       <c r="BJ503" s="3"/>
@@ -58356,23 +58184,15 @@
     <row r="504" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A504" s="75"/>
       <c r="B504" s="54"/>
-      <c r="D504" s="108"/>
-      <c r="E504" s="91"/>
+      <c r="D504" s="8"/>
+      <c r="E504" s="2"/>
       <c r="F504" s="4"/>
       <c r="G504" s="4"/>
       <c r="H504" s="4"/>
-      <c r="I504" s="92"/>
-      <c r="K504" s="93"/>
-      <c r="L504" s="92"/>
-      <c r="M504" s="94"/>
+      <c r="I504" s="7"/>
+      <c r="K504" s="50"/>
+      <c r="L504" s="7"/>
       <c r="O504" s="4"/>
-      <c r="P504" s="92"/>
-      <c r="Q504" s="92"/>
-      <c r="R504" s="94"/>
-      <c r="S504" s="94"/>
-      <c r="T504" s="94"/>
-      <c r="U504" s="94"/>
-      <c r="V504" s="92"/>
       <c r="W504" s="74"/>
       <c r="X504" s="4"/>
       <c r="Y504" s="4"/>
@@ -58407,9 +58227,9 @@
       <c r="BB504" s="2"/>
       <c r="BC504" s="2"/>
       <c r="BD504" s="2"/>
-      <c r="BE504" s="95"/>
-      <c r="BF504" s="96"/>
-      <c r="BG504" s="97"/>
+      <c r="BE504" s="42"/>
+      <c r="BF504" s="43"/>
+      <c r="BG504" s="44"/>
       <c r="BH504" s="2"/>
       <c r="BI504" s="2"/>
       <c r="BJ504" s="3"/>
@@ -58417,23 +58237,15 @@
     <row r="505" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A505" s="75"/>
       <c r="B505" s="54"/>
-      <c r="D505" s="108"/>
-      <c r="E505" s="91"/>
+      <c r="D505" s="8"/>
+      <c r="E505" s="2"/>
       <c r="F505" s="4"/>
       <c r="G505" s="4"/>
       <c r="H505" s="4"/>
-      <c r="I505" s="92"/>
-      <c r="K505" s="93"/>
-      <c r="L505" s="92"/>
-      <c r="M505" s="94"/>
+      <c r="I505" s="7"/>
+      <c r="K505" s="50"/>
+      <c r="L505" s="7"/>
       <c r="O505" s="4"/>
-      <c r="P505" s="92"/>
-      <c r="Q505" s="92"/>
-      <c r="R505" s="94"/>
-      <c r="S505" s="94"/>
-      <c r="T505" s="94"/>
-      <c r="U505" s="94"/>
-      <c r="V505" s="92"/>
       <c r="W505" s="74"/>
       <c r="X505" s="4"/>
       <c r="Y505" s="4"/>
@@ -58468,9 +58280,9 @@
       <c r="BB505" s="2"/>
       <c r="BC505" s="2"/>
       <c r="BD505" s="2"/>
-      <c r="BE505" s="95"/>
-      <c r="BF505" s="96"/>
-      <c r="BG505" s="97"/>
+      <c r="BE505" s="42"/>
+      <c r="BF505" s="43"/>
+      <c r="BG505" s="44"/>
       <c r="BH505" s="2"/>
       <c r="BI505" s="2"/>
       <c r="BJ505" s="3"/>
@@ -58478,23 +58290,15 @@
     <row r="506" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A506" s="75"/>
       <c r="B506" s="54"/>
-      <c r="D506" s="108"/>
-      <c r="E506" s="91"/>
+      <c r="D506" s="8"/>
+      <c r="E506" s="2"/>
       <c r="F506" s="4"/>
       <c r="G506" s="4"/>
       <c r="H506" s="4"/>
-      <c r="I506" s="92"/>
-      <c r="K506" s="93"/>
-      <c r="L506" s="92"/>
-      <c r="M506" s="94"/>
+      <c r="I506" s="7"/>
+      <c r="K506" s="50"/>
+      <c r="L506" s="7"/>
       <c r="O506" s="4"/>
-      <c r="P506" s="92"/>
-      <c r="Q506" s="92"/>
-      <c r="R506" s="94"/>
-      <c r="S506" s="94"/>
-      <c r="T506" s="94"/>
-      <c r="U506" s="94"/>
-      <c r="V506" s="92"/>
       <c r="W506" s="74"/>
       <c r="X506" s="4"/>
       <c r="Y506" s="4"/>
@@ -58529,9 +58333,9 @@
       <c r="BB506" s="2"/>
       <c r="BC506" s="2"/>
       <c r="BD506" s="2"/>
-      <c r="BE506" s="95"/>
-      <c r="BF506" s="96"/>
-      <c r="BG506" s="97"/>
+      <c r="BE506" s="42"/>
+      <c r="BF506" s="43"/>
+      <c r="BG506" s="44"/>
       <c r="BH506" s="2"/>
       <c r="BI506" s="2"/>
       <c r="BJ506" s="3"/>
@@ -58539,23 +58343,15 @@
     <row r="507" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A507" s="75"/>
       <c r="B507" s="54"/>
-      <c r="D507" s="108"/>
-      <c r="E507" s="91"/>
+      <c r="D507" s="8"/>
+      <c r="E507" s="2"/>
       <c r="F507" s="4"/>
       <c r="G507" s="4"/>
       <c r="H507" s="4"/>
-      <c r="I507" s="92"/>
-      <c r="K507" s="93"/>
-      <c r="L507" s="92"/>
-      <c r="M507" s="94"/>
+      <c r="I507" s="7"/>
+      <c r="K507" s="50"/>
+      <c r="L507" s="7"/>
       <c r="O507" s="4"/>
-      <c r="P507" s="92"/>
-      <c r="Q507" s="92"/>
-      <c r="R507" s="94"/>
-      <c r="S507" s="94"/>
-      <c r="T507" s="94"/>
-      <c r="U507" s="94"/>
-      <c r="V507" s="92"/>
       <c r="W507" s="74"/>
       <c r="X507" s="4"/>
       <c r="Y507" s="4"/>
@@ -58590,9 +58386,9 @@
       <c r="BB507" s="2"/>
       <c r="BC507" s="2"/>
       <c r="BD507" s="2"/>
-      <c r="BE507" s="95"/>
-      <c r="BF507" s="96"/>
-      <c r="BG507" s="97"/>
+      <c r="BE507" s="42"/>
+      <c r="BF507" s="43"/>
+      <c r="BG507" s="44"/>
       <c r="BH507" s="2"/>
       <c r="BI507" s="2"/>
       <c r="BJ507" s="3"/>
@@ -58600,23 +58396,15 @@
     <row r="508" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A508" s="75"/>
       <c r="B508" s="54"/>
-      <c r="D508" s="108"/>
-      <c r="E508" s="91"/>
+      <c r="D508" s="8"/>
+      <c r="E508" s="2"/>
       <c r="F508" s="4"/>
       <c r="G508" s="4"/>
       <c r="H508" s="4"/>
-      <c r="I508" s="92"/>
-      <c r="K508" s="93"/>
-      <c r="L508" s="92"/>
-      <c r="M508" s="94"/>
+      <c r="I508" s="7"/>
+      <c r="K508" s="50"/>
+      <c r="L508" s="7"/>
       <c r="O508" s="4"/>
-      <c r="P508" s="92"/>
-      <c r="Q508" s="92"/>
-      <c r="R508" s="94"/>
-      <c r="S508" s="94"/>
-      <c r="T508" s="94"/>
-      <c r="U508" s="94"/>
-      <c r="V508" s="92"/>
       <c r="W508" s="74"/>
       <c r="X508" s="4"/>
       <c r="Y508" s="4"/>
@@ -58651,9 +58439,9 @@
       <c r="BB508" s="2"/>
       <c r="BC508" s="2"/>
       <c r="BD508" s="2"/>
-      <c r="BE508" s="95"/>
-      <c r="BF508" s="96"/>
-      <c r="BG508" s="97"/>
+      <c r="BE508" s="42"/>
+      <c r="BF508" s="43"/>
+      <c r="BG508" s="44"/>
       <c r="BH508" s="2"/>
       <c r="BI508" s="2"/>
       <c r="BJ508" s="3"/>
@@ -58661,23 +58449,15 @@
     <row r="509" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A509" s="75"/>
       <c r="B509" s="54"/>
-      <c r="D509" s="108"/>
-      <c r="E509" s="91"/>
+      <c r="D509" s="8"/>
+      <c r="E509" s="2"/>
       <c r="F509" s="4"/>
       <c r="G509" s="4"/>
       <c r="H509" s="4"/>
-      <c r="I509" s="92"/>
-      <c r="K509" s="93"/>
-      <c r="L509" s="92"/>
-      <c r="M509" s="94"/>
+      <c r="I509" s="7"/>
+      <c r="K509" s="50"/>
+      <c r="L509" s="7"/>
       <c r="O509" s="4"/>
-      <c r="P509" s="92"/>
-      <c r="Q509" s="92"/>
-      <c r="R509" s="94"/>
-      <c r="S509" s="94"/>
-      <c r="T509" s="94"/>
-      <c r="U509" s="94"/>
-      <c r="V509" s="92"/>
       <c r="W509" s="74"/>
       <c r="X509" s="4"/>
       <c r="Y509" s="4"/>
@@ -58712,9 +58492,9 @@
       <c r="BB509" s="2"/>
       <c r="BC509" s="2"/>
       <c r="BD509" s="2"/>
-      <c r="BE509" s="95"/>
-      <c r="BF509" s="96"/>
-      <c r="BG509" s="97"/>
+      <c r="BE509" s="42"/>
+      <c r="BF509" s="43"/>
+      <c r="BG509" s="44"/>
       <c r="BH509" s="2"/>
       <c r="BI509" s="2"/>
       <c r="BJ509" s="3"/>
